--- a/outputs/hr_rankings.xlsx
+++ b/outputs/hr_rankings.xlsx
@@ -3535,47 +3535,47 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>571970</t>
+          <t>664023</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Max Muncy</t>
+          <t>Ian Happ</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>CHC</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-06-11T22:40:00Z</t>
+          <t>2026-06-11T19:10:00Z</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Mitch Keller</t>
+          <t>Ryan Feltner</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>656605</t>
+          <t>663372</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -3584,7 +3584,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>62.2</v>
+        <v>62.3</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -3598,26 +3598,26 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Strong Barrel, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>65.7</v>
+        <v>55.2</v>
       </c>
       <c r="Q12" t="n">
-        <v>36.3</v>
+        <v>53.3</v>
       </c>
       <c r="R12" t="n">
-        <v>68.3</v>
+        <v>57.2</v>
       </c>
       <c r="S12" t="n">
-        <v>86.40000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="U12" t="n">
-        <v>45</v>
+        <v>54.4</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
@@ -3631,7 +3631,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
@@ -3669,27 +3669,27 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Contact streak: 10/22 over last 7 games</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.1% barrel, 9.8 HR allowed</t>
+          <t>switch hitter; pitcher baseline 10.0% barrel, 4.7 HR allowed</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
@@ -3699,112 +3699,112 @@
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>16.05</t>
+          <t>13.9</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>49.96</t>
+          <t>46.22</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>91.09</t>
+          <t>90.56</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>102.3127</t>
+          <t>101.9188</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.5369</t>
+          <t>0.4577</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>0.2716</t>
+          <t>0.2322</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>0.3873</t>
+          <t>0.3456</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>71.41</t>
+          <t>71.98</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>12.4</t>
+          <t>20.35</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>53.32</t>
+          <t>43.77</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>34.32</t>
+          <t>33.16</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>15.5</t>
+          <t>17.4</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>0.2431</t>
+          <t>0.2351</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>9.98</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>40.44</t>
+          <t>42.07</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>88.63</t>
+          <t>89.65</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>0.4216</t>
+          <t>0.4729</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
-          <t>0.1493</t>
+          <t>0.2157</t>
         </is>
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>22.09</t>
+          <t>29.72</t>
         </is>
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>Out To LF</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>PNC Park</t>
+          <t>Coors Field</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr"/>
@@ -3815,47 +3815,47 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>664023</t>
+          <t>571970</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ian Happ</t>
+          <t>Max Muncy</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>CHC</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-06-11T19:10:00Z</t>
+          <t>2026-06-11T22:40:00Z</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Ryan Feltner</t>
+          <t>Mitch Keller</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>663372</t>
+          <t>656605</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -3864,7 +3864,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>62</v>
+        <v>62.2</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -3878,26 +3878,26 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>55.2</v>
+        <v>65.7</v>
       </c>
       <c r="Q13" t="n">
-        <v>53.3</v>
+        <v>36.3</v>
       </c>
       <c r="R13" t="n">
-        <v>57.2</v>
+        <v>68.3</v>
       </c>
       <c r="S13" t="n">
-        <v>94.90000000000001</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="U13" t="n">
-        <v>48.7</v>
+        <v>45</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
@@ -3911,7 +3911,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -3949,27 +3949,27 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Contact streak: 10/22 over last 7 games</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 10.0% barrel, 4.7 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.1% barrel, 9.8 HR allowed</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
@@ -3979,112 +3979,112 @@
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>13.9</t>
+          <t>16.05</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>46.22</t>
+          <t>49.96</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>90.56</t>
+          <t>91.09</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>101.9188</t>
+          <t>102.3127</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>0.4577</t>
+          <t>0.5369</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>0.2322</t>
+          <t>0.2716</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>0.3456</t>
+          <t>0.3873</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>71.98</t>
+          <t>71.41</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>20.35</t>
+          <t>12.4</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>43.77</t>
+          <t>53.32</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>33.16</t>
+          <t>34.32</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>17.4</t>
+          <t>15.5</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>0.2351</t>
+          <t>0.2431</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>9.98</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>42.07</t>
+          <t>40.44</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>89.65</t>
+          <t>88.63</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>0.4729</t>
+          <t>0.4216</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
-          <t>0.2157</t>
+          <t>0.1493</t>
         </is>
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>29.72</t>
+          <t>22.09</t>
         </is>
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>In From CF</t>
+          <t>Out To LF</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>84</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
         <is>
-          <t>Coors Field</t>
+          <t>PNC Park</t>
         </is>
       </c>
       <c r="BJ13" t="inlineStr"/>
@@ -4144,7 +4144,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>60.6</v>
+        <v>60.5</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -4177,7 +4177,7 @@
         <v>80</v>
       </c>
       <c r="U14" t="n">
-        <v>48.3</v>
+        <v>46.5</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
@@ -4234,7 +4234,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
@@ -4244,7 +4244,7 @@
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Contact streak: 8/25 over last 7 games</t>
+          <t>Last 7 games: 8/26, 1 HR</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
@@ -5495,47 +5495,47 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>518692</t>
+          <t>695600</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Freddie Freeman</t>
+          <t>Carter Jensen</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-06-11T22:40:00Z</t>
+          <t>2026-06-11T18:10:00Z</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Mitch Keller</t>
+          <t>Kumar Rocker</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>656605</t>
+          <t>677958</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -5562,22 +5562,22 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>49.4</v>
+        <v>53.5</v>
       </c>
       <c r="Q19" t="n">
-        <v>36.3</v>
+        <v>48</v>
       </c>
       <c r="R19" t="n">
-        <v>68.3</v>
+        <v>52.7</v>
       </c>
       <c r="S19" t="n">
-        <v>96.59999999999999</v>
+        <v>93.2</v>
       </c>
       <c r="T19" t="n">
         <v>80</v>
       </c>
       <c r="U19" t="n">
-        <v>53.9</v>
+        <v>28.1</v>
       </c>
       <c r="V19" t="inlineStr">
         <is>
@@ -5591,7 +5591,7 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
@@ -5629,12 +5629,12 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
@@ -5644,12 +5644,12 @@
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Contact streak: 10/28 over last 7 games</t>
+          <t>Last 7 games: 5/27, 1 HR</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.1% barrel, 9.8 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.3% barrel, 7.5 HR allowed</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
@@ -5659,7 +5659,7 @@
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>11.38</t>
+          <t>13.45</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
@@ -5669,92 +5669,92 @@
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>90.97</t>
+          <t>91.9</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>101.0569</t>
+          <t>102.7456</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>0.4887</t>
+          <t>0.4279</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
         <is>
-          <t>0.2126</t>
+          <t>0.1927</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>0.3675</t>
+          <t>0.3231</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>70.11</t>
+          <t>74.48</t>
         </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>7.56</t>
+          <t>42.88</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>35.77</t>
+          <t>40.58</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>28.75</t>
+          <t>31.61</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>14.2</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>0.2014</t>
+          <t>0.1933</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>9.28</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>40.44</t>
+          <t>43.79</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>88.63</t>
+          <t>90.08</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>0.4216</t>
+          <t>0.4423</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
-          <t>0.1493</t>
+          <t>0.1766</t>
         </is>
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>22.09</t>
+          <t>22.44</t>
         </is>
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>Out To LF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
@@ -5764,7 +5764,7 @@
       </c>
       <c r="BI19" t="inlineStr">
         <is>
-          <t>PNC Park</t>
+          <t>Kauffman Stadium</t>
         </is>
       </c>
       <c r="BJ19" t="inlineStr"/>
@@ -5775,47 +5775,47 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>695600</t>
+          <t>518692</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Carter Jensen</t>
+          <t>Freddie Freeman</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-06-11T18:10:00Z</t>
+          <t>2026-06-11T22:40:00Z</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Kumar Rocker</t>
+          <t>Mitch Keller</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>677958</t>
+          <t>656605</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -5824,7 +5824,7 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>58.5</v>
+        <v>58.7</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
@@ -5842,22 +5842,22 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>53.5</v>
+        <v>49.4</v>
       </c>
       <c r="Q20" t="n">
-        <v>48</v>
+        <v>36.3</v>
       </c>
       <c r="R20" t="n">
-        <v>52.7</v>
+        <v>68.3</v>
       </c>
       <c r="S20" t="n">
-        <v>93.2</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T20" t="n">
         <v>80</v>
       </c>
       <c r="U20" t="n">
-        <v>23.4</v>
+        <v>53.9</v>
       </c>
       <c r="V20" t="inlineStr">
         <is>
@@ -5871,7 +5871,7 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
@@ -5909,12 +5909,12 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
@@ -5924,12 +5924,12 @@
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/26, 1 HR</t>
+          <t>Contact streak: 10/28 over last 7 games</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 9.3% barrel, 7.5 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.1% barrel, 9.8 HR allowed</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
@@ -5939,7 +5939,7 @@
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>13.45</t>
+          <t>11.38</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
@@ -5949,92 +5949,92 @@
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>91.9</t>
+          <t>90.97</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>102.7456</t>
+          <t>101.0569</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>0.4279</t>
+          <t>0.4887</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
         <is>
-          <t>0.1927</t>
+          <t>0.2126</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>0.3231</t>
+          <t>0.3675</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
         <is>
-          <t>74.48</t>
+          <t>70.11</t>
         </is>
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>42.88</t>
+          <t>7.56</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>40.58</t>
+          <t>35.77</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>31.61</t>
+          <t>28.75</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>14.2</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>0.1933</t>
+          <t>0.2014</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>9.28</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>43.79</t>
+          <t>40.44</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>90.08</t>
+          <t>88.63</t>
         </is>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>0.4423</t>
+          <t>0.4216</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
-          <t>0.1766</t>
+          <t>0.1493</t>
         </is>
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>22.44</t>
+          <t>22.09</t>
         </is>
       </c>
       <c r="BG20" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>Out To LF</t>
         </is>
       </c>
       <c r="BH20" t="inlineStr">
@@ -6044,7 +6044,7 @@
       </c>
       <c r="BI20" t="inlineStr">
         <is>
-          <t>Kauffman Stadium</t>
+          <t>PNC Park</t>
         </is>
       </c>
       <c r="BJ20" t="inlineStr"/>
@@ -6137,7 +6137,7 @@
         <v>50</v>
       </c>
       <c r="U21" t="n">
-        <v>16.6</v>
+        <v>15.3</v>
       </c>
       <c r="V21" t="inlineStr">
         <is>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
@@ -6204,7 +6204,7 @@
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/26, 0 HR</t>
+          <t>Last 7 games: 6/27, 0 HR</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
@@ -7455,47 +7455,47 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>694212</t>
+          <t>666397</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Samuel Basallo</t>
+          <t>Edouard Julien</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>CHC</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-06-11T23:05:00Z</t>
+          <t>2026-06-11T19:10:00Z</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Bryan Woo</t>
+          <t>Edward Cabrera</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>693433</t>
+          <t>665795</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -7504,7 +7504,7 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>56.7</v>
+        <v>56.8</v>
       </c>
       <c r="M26" t="inlineStr">
         <is>
@@ -7518,26 +7518,26 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>Strong Barrel, Good Environment, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P26" t="n">
-        <v>51.2</v>
+        <v>39.3</v>
       </c>
       <c r="Q26" t="n">
-        <v>39</v>
+        <v>55.7</v>
       </c>
       <c r="R26" t="n">
-        <v>74.59999999999999</v>
+        <v>57.2</v>
       </c>
       <c r="S26" t="n">
-        <v>86.40000000000001</v>
+        <v>93.2</v>
       </c>
       <c r="T26" t="n">
         <v>80</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="V26" t="inlineStr">
         <is>
@@ -7551,7 +7551,7 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">
@@ -7589,12 +7589,12 @@
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AJ26" t="inlineStr">
@@ -7604,127 +7604,127 @@
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>Last 7 games: 1/16, 0 HR</t>
+          <t>Contact streak: 6/18 over last 7 games</t>
         </is>
       </c>
       <c r="AL26" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.3% barrel, 12.7 HR allowed</t>
+          <t>platoon edge; pitcher baseline 11.6% barrel, 12.8 HR allowed</t>
         </is>
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN26" t="inlineStr">
         <is>
-          <t>11.35</t>
+          <t>8.84</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>46.29</t>
+          <t>47.69</t>
         </is>
       </c>
       <c r="AP26" t="inlineStr">
         <is>
-          <t>91.2</t>
+          <t>90.53</t>
         </is>
       </c>
       <c r="AQ26" t="inlineStr">
         <is>
-          <t>103.4467</t>
+          <t>100.1892</t>
         </is>
       </c>
       <c r="AR26" t="inlineStr">
         <is>
-          <t>0.4604</t>
+          <t>0.4191</t>
         </is>
       </c>
       <c r="AS26" t="inlineStr">
         <is>
-          <t>0.2064</t>
+          <t>0.1666</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr">
         <is>
-          <t>0.3351</t>
+          <t>0.3374</t>
         </is>
       </c>
       <c r="AU26" t="inlineStr">
         <is>
-          <t>75.08</t>
+          <t>71.11</t>
         </is>
       </c>
       <c r="AV26" t="inlineStr">
         <is>
-          <t>53.08</t>
+          <t>13.05</t>
         </is>
       </c>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>40.71</t>
+          <t>35.02</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>28.21</t>
+          <t>20.28</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
-          <t>7.5</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>0.1979</t>
+          <t>0.0886</t>
         </is>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
-          <t>7.28</t>
+          <t>11.61</t>
         </is>
       </c>
       <c r="BB26" t="inlineStr">
         <is>
-          <t>43.48</t>
+          <t>42.55</t>
         </is>
       </c>
       <c r="BC26" t="inlineStr">
         <is>
-          <t>89.45</t>
+          <t>91.21</t>
         </is>
       </c>
       <c r="BD26" t="inlineStr">
         <is>
-          <t>0.3632</t>
+          <t>0.4276</t>
         </is>
       </c>
       <c r="BE26" t="inlineStr">
         <is>
-          <t>0.1408</t>
+          <t>0.1728</t>
         </is>
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>30.16</t>
+          <t>24.21</t>
         </is>
       </c>
       <c r="BG26" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI26" t="inlineStr">
         <is>
-          <t>Oriole Park at Camden Yards</t>
+          <t>Coors Field</t>
         </is>
       </c>
       <c r="BJ26" t="inlineStr"/>
@@ -7735,47 +7735,47 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>666397</t>
+          <t>694212</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Edouard Julien</t>
+          <t>Samuel Basallo</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>CHC</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-06-11T19:10:00Z</t>
+          <t>2026-06-11T23:05:00Z</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Edward Cabrera</t>
+          <t>Bryan Woo</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>665795</t>
+          <t>693433</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -7784,7 +7784,7 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>56.5</v>
+        <v>56.7</v>
       </c>
       <c r="M27" t="inlineStr">
         <is>
@@ -7798,26 +7798,26 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Good Environment, Platoon Edge</t>
         </is>
       </c>
       <c r="P27" t="n">
-        <v>39.3</v>
+        <v>51.2</v>
       </c>
       <c r="Q27" t="n">
-        <v>55.7</v>
+        <v>39</v>
       </c>
       <c r="R27" t="n">
-        <v>57.2</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="S27" t="n">
-        <v>93.2</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T27" t="n">
         <v>80</v>
       </c>
       <c r="U27" t="n">
-        <v>26.1</v>
+        <v>0</v>
       </c>
       <c r="V27" t="inlineStr">
         <is>
@@ -7831,7 +7831,7 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr">
@@ -7869,12 +7869,12 @@
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AJ27" t="inlineStr">
@@ -7884,127 +7884,127 @@
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/17, 0 HR</t>
+          <t>Last 7 games: 1/16, 0 HR</t>
         </is>
       </c>
       <c r="AL27" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 11.6% barrel, 12.8 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.3% barrel, 12.7 HR allowed</t>
         </is>
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN27" t="inlineStr">
         <is>
-          <t>8.84</t>
+          <t>11.35</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>47.69</t>
+          <t>46.29</t>
         </is>
       </c>
       <c r="AP27" t="inlineStr">
         <is>
-          <t>90.53</t>
+          <t>91.2</t>
         </is>
       </c>
       <c r="AQ27" t="inlineStr">
         <is>
-          <t>100.1892</t>
+          <t>103.4467</t>
         </is>
       </c>
       <c r="AR27" t="inlineStr">
         <is>
-          <t>0.4191</t>
+          <t>0.4604</t>
         </is>
       </c>
       <c r="AS27" t="inlineStr">
         <is>
-          <t>0.1666</t>
+          <t>0.2064</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr">
         <is>
-          <t>0.3374</t>
+          <t>0.3351</t>
         </is>
       </c>
       <c r="AU27" t="inlineStr">
         <is>
-          <t>71.11</t>
+          <t>75.08</t>
         </is>
       </c>
       <c r="AV27" t="inlineStr">
         <is>
-          <t>13.05</t>
+          <t>53.08</t>
         </is>
       </c>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>35.02</t>
+          <t>40.71</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>20.28</t>
+          <t>28.21</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>7.5</t>
         </is>
       </c>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>0.0886</t>
+          <t>0.1979</t>
         </is>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
-          <t>11.61</t>
+          <t>7.28</t>
         </is>
       </c>
       <c r="BB27" t="inlineStr">
         <is>
-          <t>42.55</t>
+          <t>43.48</t>
         </is>
       </c>
       <c r="BC27" t="inlineStr">
         <is>
-          <t>91.21</t>
+          <t>89.45</t>
         </is>
       </c>
       <c r="BD27" t="inlineStr">
         <is>
-          <t>0.4276</t>
+          <t>0.3632</t>
         </is>
       </c>
       <c r="BE27" t="inlineStr">
         <is>
-          <t>0.1728</t>
+          <t>0.1408</t>
         </is>
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>24.21</t>
+          <t>30.16</t>
         </is>
       </c>
       <c r="BG27" t="inlineStr">
         <is>
-          <t>In From CF</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>91</t>
         </is>
       </c>
       <c r="BI27" t="inlineStr">
         <is>
-          <t>Coors Field</t>
+          <t>Oriole Park at Camden Yards</t>
         </is>
       </c>
       <c r="BJ27" t="inlineStr"/>
@@ -8064,7 +8064,7 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>56.3</v>
+        <v>56.2</v>
       </c>
       <c r="M28" t="inlineStr">
         <is>
@@ -8097,7 +8097,7 @@
         <v>50</v>
       </c>
       <c r="U28" t="n">
-        <v>68.7</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="V28" t="inlineStr">
         <is>
@@ -8154,7 +8154,7 @@
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ28" t="inlineStr">
@@ -10815,56 +10815,56 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>542303</t>
+          <t>686469</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Marcell Ozuna</t>
+          <t>Vinnie Pasquantino</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-06-11T22:40:00Z</t>
+          <t>2026-06-11T18:10:00Z</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Justin Wrobleski</t>
+          <t>Kumar Rocker</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>680736</t>
+          <t>677958</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L38" t="n">
-        <v>53.4</v>
+        <v>53.5</v>
       </c>
       <c r="M38" t="inlineStr">
         <is>
@@ -10882,22 +10882,22 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>39.8</v>
+        <v>36</v>
       </c>
       <c r="Q38" t="n">
-        <v>36.9</v>
+        <v>48</v>
       </c>
       <c r="R38" t="n">
-        <v>68.3</v>
+        <v>52.7</v>
       </c>
       <c r="S38" t="n">
-        <v>94.90000000000001</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T38" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U38" t="n">
-        <v>16.6</v>
+        <v>30</v>
       </c>
       <c r="V38" t="inlineStr">
         <is>
@@ -10911,7 +10911,7 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y38" t="inlineStr">
@@ -10949,12 +10949,12 @@
       </c>
       <c r="AH38" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI38" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ38" t="inlineStr">
@@ -10964,12 +10964,12 @@
       </c>
       <c r="AK38" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/26, 0 HR</t>
+          <t>Contact streak: 8/25 over last 7 games</t>
         </is>
       </c>
       <c r="AL38" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.0% barrel, 4.6 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.3% barrel, 7.5 HR allowed</t>
         </is>
       </c>
       <c r="AM38" t="inlineStr">
@@ -10979,102 +10979,102 @@
       </c>
       <c r="AN38" t="inlineStr">
         <is>
-          <t>9.19</t>
+          <t>8.56</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>40.82</t>
+          <t>40.5</t>
         </is>
       </c>
       <c r="AP38" t="inlineStr">
         <is>
-          <t>89.69</t>
+          <t>89.5</t>
         </is>
       </c>
       <c r="AQ38" t="inlineStr">
         <is>
-          <t>100.2815</t>
+          <t>99.7536</t>
         </is>
       </c>
       <c r="AR38" t="inlineStr">
         <is>
-          <t>0.4109</t>
+          <t>0.4168</t>
         </is>
       </c>
       <c r="AS38" t="inlineStr">
         <is>
-          <t>0.181</t>
+          <t>0.1679</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr">
         <is>
-          <t>0.3218</t>
+          <t>0.3228</t>
         </is>
       </c>
       <c r="AU38" t="inlineStr">
         <is>
-          <t>73.32</t>
+          <t>70.89</t>
         </is>
       </c>
       <c r="AV38" t="inlineStr">
         <is>
-          <t>34.68</t>
+          <t>13.66</t>
         </is>
       </c>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>40.31</t>
+          <t>43.77</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>29.94</t>
+          <t>28.23</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr">
         <is>
-          <t>9.8</t>
+          <t>13.8</t>
         </is>
       </c>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>0.126</t>
+          <t>0.155</t>
         </is>
       </c>
       <c r="BA38" t="inlineStr">
         <is>
-          <t>6.04</t>
+          <t>9.28</t>
         </is>
       </c>
       <c r="BB38" t="inlineStr">
         <is>
-          <t>44.09</t>
+          <t>43.79</t>
         </is>
       </c>
       <c r="BC38" t="inlineStr">
         <is>
-          <t>90.53</t>
+          <t>90.08</t>
         </is>
       </c>
       <c r="BD38" t="inlineStr">
         <is>
-          <t>0.3954</t>
+          <t>0.4423</t>
         </is>
       </c>
       <c r="BE38" t="inlineStr">
         <is>
-          <t>0.1416</t>
+          <t>0.1766</t>
         </is>
       </c>
       <c r="BF38" t="inlineStr">
         <is>
-          <t>28.14</t>
+          <t>22.44</t>
         </is>
       </c>
       <c r="BG38" t="inlineStr">
         <is>
-          <t>Out To LF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH38" t="inlineStr">
@@ -11084,7 +11084,7 @@
       </c>
       <c r="BI38" t="inlineStr">
         <is>
-          <t>PNC Park</t>
+          <t>Kauffman Stadium</t>
         </is>
       </c>
       <c r="BJ38" t="inlineStr"/>
@@ -11095,56 +11095,56 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>686469</t>
+          <t>542303</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Vinnie Pasquantino</t>
+          <t>Marcell Ozuna</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-06-11T18:10:00Z</t>
+          <t>2026-06-11T22:40:00Z</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Kumar Rocker</t>
+          <t>Justin Wrobleski</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>677958</t>
+          <t>680736</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L39" t="n">
-        <v>53.3</v>
+        <v>53.4</v>
       </c>
       <c r="M39" t="inlineStr">
         <is>
@@ -11162,22 +11162,22 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>36</v>
+        <v>39.8</v>
       </c>
       <c r="Q39" t="n">
-        <v>48</v>
+        <v>36.9</v>
       </c>
       <c r="R39" t="n">
-        <v>52.7</v>
+        <v>68.3</v>
       </c>
       <c r="S39" t="n">
-        <v>96.59999999999999</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T39" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="U39" t="n">
-        <v>25.8</v>
+        <v>16.6</v>
       </c>
       <c r="V39" t="inlineStr">
         <is>
@@ -11191,7 +11191,7 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y39" t="inlineStr">
@@ -11229,12 +11229,12 @@
       </c>
       <c r="AH39" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI39" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ39" t="inlineStr">
@@ -11244,12 +11244,12 @@
       </c>
       <c r="AK39" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/24, 0 HR</t>
+          <t>Last 7 games: 6/26, 0 HR</t>
         </is>
       </c>
       <c r="AL39" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 9.3% barrel, 7.5 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.0% barrel, 4.6 HR allowed</t>
         </is>
       </c>
       <c r="AM39" t="inlineStr">
@@ -11259,102 +11259,102 @@
       </c>
       <c r="AN39" t="inlineStr">
         <is>
-          <t>8.56</t>
+          <t>9.19</t>
         </is>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>40.5</t>
+          <t>40.82</t>
         </is>
       </c>
       <c r="AP39" t="inlineStr">
         <is>
-          <t>89.5</t>
+          <t>89.69</t>
         </is>
       </c>
       <c r="AQ39" t="inlineStr">
         <is>
-          <t>99.7536</t>
+          <t>100.2815</t>
         </is>
       </c>
       <c r="AR39" t="inlineStr">
         <is>
-          <t>0.4168</t>
+          <t>0.4109</t>
         </is>
       </c>
       <c r="AS39" t="inlineStr">
         <is>
-          <t>0.1679</t>
+          <t>0.181</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr">
         <is>
-          <t>0.3228</t>
+          <t>0.3218</t>
         </is>
       </c>
       <c r="AU39" t="inlineStr">
         <is>
-          <t>70.89</t>
+          <t>73.32</t>
         </is>
       </c>
       <c r="AV39" t="inlineStr">
         <is>
-          <t>13.66</t>
+          <t>34.68</t>
         </is>
       </c>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>43.77</t>
+          <t>40.31</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>28.23</t>
+          <t>29.94</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr">
         <is>
-          <t>13.8</t>
+          <t>9.8</t>
         </is>
       </c>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>0.155</t>
+          <t>0.126</t>
         </is>
       </c>
       <c r="BA39" t="inlineStr">
         <is>
-          <t>9.28</t>
+          <t>6.04</t>
         </is>
       </c>
       <c r="BB39" t="inlineStr">
         <is>
-          <t>43.79</t>
+          <t>44.09</t>
         </is>
       </c>
       <c r="BC39" t="inlineStr">
         <is>
-          <t>90.08</t>
+          <t>90.53</t>
         </is>
       </c>
       <c r="BD39" t="inlineStr">
         <is>
-          <t>0.4423</t>
+          <t>0.3954</t>
         </is>
       </c>
       <c r="BE39" t="inlineStr">
         <is>
-          <t>0.1766</t>
+          <t>0.1416</t>
         </is>
       </c>
       <c r="BF39" t="inlineStr">
         <is>
-          <t>22.44</t>
+          <t>28.14</t>
         </is>
       </c>
       <c r="BG39" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>Out To LF</t>
         </is>
       </c>
       <c r="BH39" t="inlineStr">
@@ -11364,7 +11364,7 @@
       </c>
       <c r="BI39" t="inlineStr">
         <is>
-          <t>Kauffman Stadium</t>
+          <t>PNC Park</t>
         </is>
       </c>
       <c r="BJ39" t="inlineStr"/>
@@ -11457,7 +11457,7 @@
         <v>75</v>
       </c>
       <c r="U40" t="n">
-        <v>44.8</v>
+        <v>43.2</v>
       </c>
       <c r="V40" t="inlineStr">
         <is>
@@ -11514,7 +11514,7 @@
       </c>
       <c r="AI40" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ40" t="inlineStr">
@@ -11524,7 +11524,7 @@
       </c>
       <c r="AK40" t="inlineStr">
         <is>
-          <t>Last 7 games: 8/27, 1 HR</t>
+          <t>Last 7 games: 8/28, 1 HR</t>
         </is>
       </c>
       <c r="AL40" t="inlineStr">
@@ -12577,7 +12577,7 @@
         <v>80</v>
       </c>
       <c r="U44" t="n">
-        <v>20.8</v>
+        <v>19.9</v>
       </c>
       <c r="V44" t="inlineStr">
         <is>
@@ -12634,7 +12634,7 @@
       </c>
       <c r="AI44" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ44" t="inlineStr">
@@ -12644,7 +12644,7 @@
       </c>
       <c r="AK44" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/22, 1 HR</t>
+          <t>Last 7 games: 3/23, 1 HR</t>
         </is>
       </c>
       <c r="AL44" t="inlineStr">
@@ -14784,7 +14784,7 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>50</v>
+        <v>49.9</v>
       </c>
       <c r="M52" t="inlineStr">
         <is>
@@ -14817,7 +14817,7 @@
         <v>50</v>
       </c>
       <c r="U52" t="n">
-        <v>50.3</v>
+        <v>47.7</v>
       </c>
       <c r="V52" t="inlineStr">
         <is>
@@ -14874,7 +14874,7 @@
       </c>
       <c r="AI52" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AJ52" t="inlineStr">
@@ -14884,7 +14884,7 @@
       </c>
       <c r="AK52" t="inlineStr">
         <is>
-          <t>Contact streak: 6/18 over last 7 games</t>
+          <t>Last 7 games: 6/19, 1 HR</t>
         </is>
       </c>
       <c r="AL52" t="inlineStr">
@@ -15015,56 +15015,56 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>643289</t>
+          <t>608324</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Mauricio Dubón</t>
+          <t>Alex Bregman</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>CHC</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-06-11T23:40:00Z</t>
+          <t>2026-06-11T19:10:00Z</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Anthony Kay</t>
+          <t>Ryan Feltner</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>641743</t>
+          <t>663372</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L53" t="n">
-        <v>49.8</v>
+        <v>49.9</v>
       </c>
       <c r="M53" t="inlineStr">
         <is>
@@ -15078,26 +15078,26 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P53" t="n">
-        <v>13.9</v>
+        <v>26.2</v>
       </c>
       <c r="Q53" t="n">
-        <v>50.9</v>
+        <v>53.8</v>
       </c>
       <c r="R53" t="n">
-        <v>55.6</v>
+        <v>57.2</v>
       </c>
       <c r="S53" t="n">
-        <v>93.2</v>
+        <v>100</v>
       </c>
       <c r="T53" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U53" t="n">
-        <v>91</v>
+        <v>25.3</v>
       </c>
       <c r="V53" t="inlineStr">
         <is>
@@ -15111,7 +15111,7 @@
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y53" t="inlineStr">
@@ -15132,7 +15132,7 @@
       <c r="AB53" t="inlineStr"/>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD53" t="inlineStr"/>
@@ -15149,27 +15149,27 @@
       </c>
       <c r="AH53" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI53" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
         <is>
-          <t>Hot streak: 3 HR in last 7 games</t>
+          <t>Last 7 games: 4/24, 1 HR</t>
         </is>
       </c>
       <c r="AL53" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 10.3% barrel, 10.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 10.0% barrel, 4.7 HR allowed</t>
         </is>
       </c>
       <c r="AM53" t="inlineStr">
@@ -15179,112 +15179,112 @@
       </c>
       <c r="AN53" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>5.48</t>
         </is>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
-          <t>27.77</t>
+          <t>40.48</t>
         </is>
       </c>
       <c r="AP53" t="inlineStr">
         <is>
-          <t>85.97</t>
+          <t>88.7</t>
         </is>
       </c>
       <c r="AQ53" t="inlineStr">
         <is>
-          <t>96.2627</t>
+          <t>98.6862</t>
         </is>
       </c>
       <c r="AR53" t="inlineStr">
         <is>
-          <t>0.3737</t>
+          <t>0.3878</t>
         </is>
       </c>
       <c r="AS53" t="inlineStr">
         <is>
-          <t>0.1169</t>
+          <t>0.139</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr">
         <is>
-          <t>0.3032</t>
+          <t>0.3195</t>
         </is>
       </c>
       <c r="AU53" t="inlineStr">
         <is>
-          <t>68.76</t>
+          <t>70.16</t>
         </is>
       </c>
       <c r="AV53" t="inlineStr">
         <is>
-          <t>2.77</t>
+          <t>5.29</t>
         </is>
       </c>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>30.63</t>
+          <t>47.14</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>26.56</t>
+          <t>23.94</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
         <is>
-          <t>6.3</t>
+          <t>8.9</t>
         </is>
       </c>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>0.1385</t>
+          <t>0.1246</t>
         </is>
       </c>
       <c r="BA53" t="inlineStr">
         <is>
-          <t>10.3</t>
+          <t>9.98</t>
         </is>
       </c>
       <c r="BB53" t="inlineStr">
         <is>
-          <t>41.6</t>
+          <t>42.07</t>
         </is>
       </c>
       <c r="BC53" t="inlineStr">
         <is>
-          <t>89.6</t>
+          <t>89.65</t>
         </is>
       </c>
       <c r="BD53" t="inlineStr">
         <is>
-          <t>0.465</t>
+          <t>0.4729</t>
         </is>
       </c>
       <c r="BE53" t="inlineStr">
         <is>
-          <t>0.183</t>
+          <t>0.2157</t>
         </is>
       </c>
       <c r="BF53" t="inlineStr">
         <is>
-          <t>22.3</t>
+          <t>29.72</t>
         </is>
       </c>
       <c r="BG53" t="inlineStr">
         <is>
-          <t>In From RF</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BH53" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI53" t="inlineStr">
         <is>
-          <t>Rate Field</t>
+          <t>Coors Field</t>
         </is>
       </c>
       <c r="BJ53" t="inlineStr"/>
@@ -15295,27 +15295,27 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>663656</t>
+          <t>643289</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Kyle Tucker</t>
+          <t>Mauricio Dubón</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-06-11T22:40:00Z</t>
+          <t>2026-06-11T23:40:00Z</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -15325,26 +15325,26 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Mitch Keller</t>
+          <t>Anthony Kay</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>656605</t>
+          <t>641743</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L54" t="n">
-        <v>49.4</v>
+        <v>49.8</v>
       </c>
       <c r="M54" t="inlineStr">
         <is>
@@ -15358,26 +15358,26 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P54" t="n">
-        <v>32.9</v>
+        <v>13.9</v>
       </c>
       <c r="Q54" t="n">
-        <v>36.3</v>
+        <v>50.9</v>
       </c>
       <c r="R54" t="n">
-        <v>68.3</v>
+        <v>55.6</v>
       </c>
       <c r="S54" t="n">
-        <v>76.2</v>
+        <v>93.2</v>
       </c>
       <c r="T54" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="U54" t="n">
-        <v>34.9</v>
+        <v>91</v>
       </c>
       <c r="V54" t="inlineStr">
         <is>
@@ -15391,7 +15391,7 @@
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y54" t="inlineStr">
@@ -15412,7 +15412,7 @@
       <c r="AB54" t="inlineStr"/>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD54" t="inlineStr"/>
@@ -15429,27 +15429,27 @@
       </c>
       <c r="AH54" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI54" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AK54" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/26, 1 HR</t>
+          <t>Hot streak: 3 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL54" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.1% barrel, 9.8 HR allowed</t>
+          <t>platoon edge; pitcher baseline 10.3% barrel, 10.0 HR allowed</t>
         </is>
       </c>
       <c r="AM54" t="inlineStr">
@@ -15459,112 +15459,112 @@
       </c>
       <c r="AN54" t="inlineStr">
         <is>
-          <t>7.02</t>
+          <t>4.7</t>
         </is>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
-          <t>39.77</t>
+          <t>27.77</t>
         </is>
       </c>
       <c r="AP54" t="inlineStr">
         <is>
-          <t>89.33</t>
+          <t>85.97</t>
         </is>
       </c>
       <c r="AQ54" t="inlineStr">
         <is>
-          <t>98.9906</t>
+          <t>96.2627</t>
         </is>
       </c>
       <c r="AR54" t="inlineStr">
         <is>
-          <t>0.4102</t>
+          <t>0.3737</t>
         </is>
       </c>
       <c r="AS54" t="inlineStr">
         <is>
-          <t>0.1542</t>
+          <t>0.1169</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr">
         <is>
-          <t>0.3405</t>
+          <t>0.3032</t>
         </is>
       </c>
       <c r="AU54" t="inlineStr">
         <is>
-          <t>71.51</t>
+          <t>68.76</t>
         </is>
       </c>
       <c r="AV54" t="inlineStr">
         <is>
-          <t>23.04</t>
+          <t>2.77</t>
         </is>
       </c>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>44.22</t>
+          <t>30.63</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>31.02</t>
+          <t>26.56</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>6.3</t>
         </is>
       </c>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>0.1637</t>
+          <t>0.1385</t>
         </is>
       </c>
       <c r="BA54" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>10.3</t>
         </is>
       </c>
       <c r="BB54" t="inlineStr">
         <is>
-          <t>40.44</t>
+          <t>41.6</t>
         </is>
       </c>
       <c r="BC54" t="inlineStr">
         <is>
-          <t>88.63</t>
+          <t>89.6</t>
         </is>
       </c>
       <c r="BD54" t="inlineStr">
         <is>
-          <t>0.4216</t>
+          <t>0.465</t>
         </is>
       </c>
       <c r="BE54" t="inlineStr">
         <is>
-          <t>0.1493</t>
+          <t>0.183</t>
         </is>
       </c>
       <c r="BF54" t="inlineStr">
         <is>
-          <t>22.09</t>
+          <t>22.3</t>
         </is>
       </c>
       <c r="BG54" t="inlineStr">
         <is>
-          <t>Out To LF</t>
+          <t>In From RF</t>
         </is>
       </c>
       <c r="BH54" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>82</t>
         </is>
       </c>
       <c r="BI54" t="inlineStr">
         <is>
-          <t>PNC Park</t>
+          <t>Rate Field</t>
         </is>
       </c>
       <c r="BJ54" t="inlineStr"/>
@@ -15575,27 +15575,27 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>702284</t>
+          <t>663656</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Cole Young</t>
+          <t>Kyle Tucker</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-06-11T23:05:00Z</t>
+          <t>2026-06-11T22:40:00Z</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -15605,17 +15605,17 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Kyle Bradish</t>
+          <t>Mitch Keller</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>680694</t>
+          <t>656605</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -15624,7 +15624,7 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>49.2</v>
+        <v>49.4</v>
       </c>
       <c r="M55" t="inlineStr">
         <is>
@@ -15638,26 +15638,26 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>Good Environment, Premium Lineup Spot, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P55" t="n">
-        <v>23.3</v>
+        <v>32.9</v>
       </c>
       <c r="Q55" t="n">
-        <v>38.4</v>
+        <v>36.3</v>
       </c>
       <c r="R55" t="n">
-        <v>74.59999999999999</v>
+        <v>68.3</v>
       </c>
       <c r="S55" t="n">
-        <v>93.2</v>
+        <v>76.2</v>
       </c>
       <c r="T55" t="n">
         <v>80</v>
       </c>
       <c r="U55" t="n">
-        <v>17</v>
+        <v>34.9</v>
       </c>
       <c r="V55" t="inlineStr">
         <is>
@@ -15671,7 +15671,7 @@
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y55" t="inlineStr">
@@ -15709,27 +15709,27 @@
       </c>
       <c r="AH55" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI55" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/30, 0 HR</t>
+          <t>Last 7 games: 6/26, 1 HR</t>
         </is>
       </c>
       <c r="AL55" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 9.8% barrel, 6.5 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.1% barrel, 9.8 HR allowed</t>
         </is>
       </c>
       <c r="AM55" t="inlineStr">
@@ -15739,112 +15739,112 @@
       </c>
       <c r="AN55" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>7.02</t>
         </is>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
-          <t>35.3</t>
+          <t>39.77</t>
         </is>
       </c>
       <c r="AP55" t="inlineStr">
         <is>
-          <t>87.6</t>
+          <t>89.33</t>
         </is>
       </c>
       <c r="AQ55" t="inlineStr">
         <is>
-          <t>98.6007</t>
+          <t>98.9906</t>
         </is>
       </c>
       <c r="AR55" t="inlineStr">
         <is>
-          <t>0.3907</t>
+          <t>0.4102</t>
         </is>
       </c>
       <c r="AS55" t="inlineStr">
         <is>
-          <t>0.1345</t>
+          <t>0.1542</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr">
         <is>
-          <t>0.3187</t>
+          <t>0.3405</t>
         </is>
       </c>
       <c r="AU55" t="inlineStr">
         <is>
-          <t>71.54</t>
+          <t>71.51</t>
         </is>
       </c>
       <c r="AV55" t="inlineStr">
         <is>
-          <t>22.37</t>
+          <t>23.04</t>
         </is>
       </c>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>45.2</t>
+          <t>44.22</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>26.45</t>
+          <t>31.02</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>0.0968</t>
+          <t>0.1637</t>
         </is>
       </c>
       <c r="BA55" t="inlineStr">
         <is>
-          <t>9.85</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="BB55" t="inlineStr">
         <is>
-          <t>37.01</t>
+          <t>40.44</t>
         </is>
       </c>
       <c r="BC55" t="inlineStr">
         <is>
-          <t>88.54</t>
+          <t>88.63</t>
         </is>
       </c>
       <c r="BD55" t="inlineStr">
         <is>
-          <t>0.3774</t>
+          <t>0.4216</t>
         </is>
       </c>
       <c r="BE55" t="inlineStr">
         <is>
-          <t>0.1513</t>
+          <t>0.1493</t>
         </is>
       </c>
       <c r="BF55" t="inlineStr">
         <is>
-          <t>21.96</t>
+          <t>22.09</t>
         </is>
       </c>
       <c r="BG55" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>Out To LF</t>
         </is>
       </c>
       <c r="BH55" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>84</t>
         </is>
       </c>
       <c r="BI55" t="inlineStr">
         <is>
-          <t>Oriole Park at Camden Yards</t>
+          <t>PNC Park</t>
         </is>
       </c>
       <c r="BJ55" t="inlineStr"/>
@@ -15855,47 +15855,47 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>608324</t>
+          <t>702284</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Alex Bregman</t>
+          <t>Cole Young</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>CHC</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-06-11T19:10:00Z</t>
+          <t>2026-06-11T23:05:00Z</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Ryan Feltner</t>
+          <t>Kyle Bradish</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>663372</t>
+          <t>680694</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -15904,7 +15904,7 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>48.7</v>
+        <v>49.2</v>
       </c>
       <c r="M56" t="inlineStr">
         <is>
@@ -15918,26 +15918,26 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot</t>
+          <t>Good Environment, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P56" t="n">
-        <v>26.2</v>
+        <v>23.3</v>
       </c>
       <c r="Q56" t="n">
-        <v>53.8</v>
+        <v>38.4</v>
       </c>
       <c r="R56" t="n">
-        <v>57.2</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="S56" t="n">
-        <v>100</v>
+        <v>93.2</v>
       </c>
       <c r="T56" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U56" t="n">
-        <v>1.6</v>
+        <v>17</v>
       </c>
       <c r="V56" t="inlineStr">
         <is>
@@ -15951,7 +15951,7 @@
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y56" t="inlineStr">
@@ -15989,12 +15989,12 @@
       </c>
       <c r="AH56" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI56" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AJ56" t="inlineStr">
@@ -16004,12 +16004,12 @@
       </c>
       <c r="AK56" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/23, 0 HR</t>
+          <t>Last 7 games: 7/30, 0 HR</t>
         </is>
       </c>
       <c r="AL56" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 10.0% barrel, 4.7 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.8% barrel, 6.5 HR allowed</t>
         </is>
       </c>
       <c r="AM56" t="inlineStr">
@@ -16019,112 +16019,112 @@
       </c>
       <c r="AN56" t="inlineStr">
         <is>
-          <t>5.48</t>
+          <t>5.25</t>
         </is>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
-          <t>40.48</t>
+          <t>35.3</t>
         </is>
       </c>
       <c r="AP56" t="inlineStr">
         <is>
-          <t>88.7</t>
+          <t>87.6</t>
         </is>
       </c>
       <c r="AQ56" t="inlineStr">
         <is>
-          <t>98.6862</t>
+          <t>98.6007</t>
         </is>
       </c>
       <c r="AR56" t="inlineStr">
         <is>
-          <t>0.3878</t>
+          <t>0.3907</t>
         </is>
       </c>
       <c r="AS56" t="inlineStr">
         <is>
-          <t>0.139</t>
+          <t>0.1345</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr">
         <is>
-          <t>0.3195</t>
+          <t>0.3187</t>
         </is>
       </c>
       <c r="AU56" t="inlineStr">
         <is>
-          <t>70.16</t>
+          <t>71.54</t>
         </is>
       </c>
       <c r="AV56" t="inlineStr">
         <is>
-          <t>5.29</t>
+          <t>22.37</t>
         </is>
       </c>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>47.14</t>
+          <t>45.2</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>23.94</t>
+          <t>26.45</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr">
         <is>
-          <t>8.9</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>0.1246</t>
+          <t>0.0968</t>
         </is>
       </c>
       <c r="BA56" t="inlineStr">
         <is>
-          <t>9.98</t>
+          <t>9.85</t>
         </is>
       </c>
       <c r="BB56" t="inlineStr">
         <is>
-          <t>42.07</t>
+          <t>37.01</t>
         </is>
       </c>
       <c r="BC56" t="inlineStr">
         <is>
-          <t>89.65</t>
+          <t>88.54</t>
         </is>
       </c>
       <c r="BD56" t="inlineStr">
         <is>
-          <t>0.4729</t>
+          <t>0.3774</t>
         </is>
       </c>
       <c r="BE56" t="inlineStr">
         <is>
-          <t>0.2157</t>
+          <t>0.1513</t>
         </is>
       </c>
       <c r="BF56" t="inlineStr">
         <is>
-          <t>29.72</t>
+          <t>21.96</t>
         </is>
       </c>
       <c r="BG56" t="inlineStr">
         <is>
-          <t>In From CF</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BH56" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>91</t>
         </is>
       </c>
       <c r="BI56" t="inlineStr">
         <is>
-          <t>Coors Field</t>
+          <t>Oriole Park at Camden Yards</t>
         </is>
       </c>
       <c r="BJ56" t="inlineStr"/>
@@ -18939,52 +18939,52 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>642201</t>
+          <t>553869</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Eli White</t>
+          <t>Elias Díaz</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-06-11T23:40:00Z</t>
+          <t>2026-06-11T18:10:00Z</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Anthony Kay</t>
+          <t>Michael Wacha</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>641743</t>
+          <t>608379</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L67" t="n">
@@ -19002,26 +19002,26 @@
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Strong Barrel</t>
         </is>
       </c>
       <c r="P67" t="n">
-        <v>25.9</v>
+        <v>42.5</v>
       </c>
       <c r="Q67" t="n">
-        <v>50.9</v>
+        <v>37</v>
       </c>
       <c r="R67" t="n">
-        <v>55.6</v>
+        <v>52.7</v>
       </c>
       <c r="S67" t="n">
-        <v>64.3</v>
+        <v>52.4</v>
       </c>
       <c r="T67" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U67" t="n">
-        <v>0</v>
+        <v>50.3</v>
       </c>
       <c r="V67" t="inlineStr">
         <is>
@@ -19035,7 +19035,7 @@
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y67" t="inlineStr">
@@ -19056,7 +19056,7 @@
       <c r="AB67" t="inlineStr"/>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD67" t="inlineStr"/>
@@ -19073,27 +19073,27 @@
       </c>
       <c r="AH67" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI67" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
         <is>
-          <t>Last 7 games: 0/5, 0 HR</t>
+          <t>Contact streak: 5/15 over last 7 games</t>
         </is>
       </c>
       <c r="AL67" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 10.3% barrel, 10.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.0% barrel, 10.8 HR allowed</t>
         </is>
       </c>
       <c r="AM67" t="inlineStr">
@@ -19103,112 +19103,112 @@
       </c>
       <c r="AN67" t="inlineStr">
         <is>
-          <t>7.42</t>
+          <t>12.78</t>
         </is>
       </c>
       <c r="AO67" t="inlineStr">
         <is>
-          <t>36.62</t>
+          <t>43.11</t>
         </is>
       </c>
       <c r="AP67" t="inlineStr">
         <is>
-          <t>87.42</t>
+          <t>88.96</t>
         </is>
       </c>
       <c r="AQ67" t="inlineStr">
         <is>
-          <t>99.0505</t>
+          <t>100.9833</t>
         </is>
       </c>
       <c r="AR67" t="inlineStr">
         <is>
-          <t>0.3769</t>
+          <t>0.3792</t>
         </is>
       </c>
       <c r="AS67" t="inlineStr">
         <is>
-          <t>0.1241</t>
+          <t>0.1471</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr">
         <is>
-          <t>0.2988</t>
+          <t>0.2838</t>
         </is>
       </c>
       <c r="AU67" t="inlineStr">
         <is>
-          <t>73.25</t>
+          <t>74.69</t>
         </is>
       </c>
       <c r="AV67" t="inlineStr">
         <is>
-          <t>33.73</t>
+          <t>47.74</t>
         </is>
       </c>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>37.03</t>
+          <t>39.61</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>22.54</t>
+          <t>29.55</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr">
         <is>
-          <t>4.4</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>0.1475</t>
+          <t>0.2737</t>
         </is>
       </c>
       <c r="BA67" t="inlineStr">
         <is>
-          <t>10.3</t>
+          <t>7.05</t>
         </is>
       </c>
       <c r="BB67" t="inlineStr">
         <is>
-          <t>41.6</t>
+          <t>37.05</t>
         </is>
       </c>
       <c r="BC67" t="inlineStr">
         <is>
-          <t>89.6</t>
+          <t>88.41</t>
         </is>
       </c>
       <c r="BD67" t="inlineStr">
         <is>
-          <t>0.465</t>
+          <t>0.4196</t>
         </is>
       </c>
       <c r="BE67" t="inlineStr">
         <is>
-          <t>0.183</t>
+          <t>0.1668</t>
         </is>
       </c>
       <c r="BF67" t="inlineStr">
         <is>
-          <t>22.3</t>
+          <t>27.55</t>
         </is>
       </c>
       <c r="BG67" t="inlineStr">
         <is>
-          <t>In From RF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH67" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>84</t>
         </is>
       </c>
       <c r="BI67" t="inlineStr">
         <is>
-          <t>Rate Field</t>
+          <t>Kauffman Stadium</t>
         </is>
       </c>
       <c r="BJ67" t="inlineStr"/>
@@ -19219,56 +19219,56 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>553869</t>
+          <t>642201</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Elias Díaz</t>
+          <t>Eli White</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-06-11T18:10:00Z</t>
+          <t>2026-06-11T23:40:00Z</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Michael Wacha</t>
+          <t>Anthony Kay</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>608379</t>
+          <t>641743</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L68" t="n">
-        <v>44.8</v>
+        <v>45.1</v>
       </c>
       <c r="M68" t="inlineStr">
         <is>
@@ -19282,26 +19282,26 @@
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>Strong Barrel</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P68" t="n">
-        <v>42.5</v>
+        <v>25.9</v>
       </c>
       <c r="Q68" t="n">
-        <v>37</v>
+        <v>50.9</v>
       </c>
       <c r="R68" t="n">
-        <v>52.7</v>
+        <v>55.6</v>
       </c>
       <c r="S68" t="n">
-        <v>52.4</v>
+        <v>64.3</v>
       </c>
       <c r="T68" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U68" t="n">
-        <v>43.2</v>
+        <v>0</v>
       </c>
       <c r="V68" t="inlineStr">
         <is>
@@ -19315,7 +19315,7 @@
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y68" t="inlineStr">
@@ -19336,7 +19336,7 @@
       <c r="AB68" t="inlineStr"/>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD68" t="inlineStr"/>
@@ -19353,27 +19353,27 @@
       </c>
       <c r="AH68" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AI68" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK68" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/14, 1 HR</t>
+          <t>Last 7 games: 0/5, 0 HR</t>
         </is>
       </c>
       <c r="AL68" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.0% barrel, 10.8 HR allowed</t>
+          <t>platoon edge; pitcher baseline 10.3% barrel, 10.0 HR allowed</t>
         </is>
       </c>
       <c r="AM68" t="inlineStr">
@@ -19383,112 +19383,112 @@
       </c>
       <c r="AN68" t="inlineStr">
         <is>
-          <t>12.78</t>
+          <t>7.42</t>
         </is>
       </c>
       <c r="AO68" t="inlineStr">
         <is>
-          <t>43.11</t>
+          <t>36.62</t>
         </is>
       </c>
       <c r="AP68" t="inlineStr">
         <is>
-          <t>88.96</t>
+          <t>87.42</t>
         </is>
       </c>
       <c r="AQ68" t="inlineStr">
         <is>
-          <t>100.9833</t>
+          <t>99.0505</t>
         </is>
       </c>
       <c r="AR68" t="inlineStr">
         <is>
-          <t>0.3792</t>
+          <t>0.3769</t>
         </is>
       </c>
       <c r="AS68" t="inlineStr">
         <is>
-          <t>0.1471</t>
+          <t>0.1241</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr">
         <is>
-          <t>0.2838</t>
+          <t>0.2988</t>
         </is>
       </c>
       <c r="AU68" t="inlineStr">
         <is>
-          <t>74.69</t>
+          <t>73.25</t>
         </is>
       </c>
       <c r="AV68" t="inlineStr">
         <is>
-          <t>47.74</t>
+          <t>33.73</t>
         </is>
       </c>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>39.61</t>
+          <t>37.03</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>29.55</t>
+          <t>22.54</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>4.4</t>
         </is>
       </c>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>0.2737</t>
+          <t>0.1475</t>
         </is>
       </c>
       <c r="BA68" t="inlineStr">
         <is>
-          <t>7.05</t>
+          <t>10.3</t>
         </is>
       </c>
       <c r="BB68" t="inlineStr">
         <is>
-          <t>37.05</t>
+          <t>41.6</t>
         </is>
       </c>
       <c r="BC68" t="inlineStr">
         <is>
-          <t>88.41</t>
+          <t>89.6</t>
         </is>
       </c>
       <c r="BD68" t="inlineStr">
         <is>
-          <t>0.4196</t>
+          <t>0.465</t>
         </is>
       </c>
       <c r="BE68" t="inlineStr">
         <is>
-          <t>0.1668</t>
+          <t>0.183</t>
         </is>
       </c>
       <c r="BF68" t="inlineStr">
         <is>
-          <t>27.55</t>
+          <t>22.3</t>
         </is>
       </c>
       <c r="BG68" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>In From RF</t>
         </is>
       </c>
       <c r="BH68" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>82</t>
         </is>
       </c>
       <c r="BI68" t="inlineStr">
         <is>
-          <t>Kauffman Stadium</t>
+          <t>Rate Field</t>
         </is>
       </c>
       <c r="BJ68" t="inlineStr"/>
@@ -19499,47 +19499,47 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>621020</t>
+          <t>640902</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Dansby Swanson</t>
+          <t>Jhonny Pereda</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>CHC</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-06-11T19:10:00Z</t>
+          <t>2026-06-11T23:05:00Z</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Ryan Feltner</t>
+          <t>Kyle Bradish</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>663372</t>
+          <t>680694</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -19562,26 +19562,26 @@
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>No major boost</t>
+          <t>Good Environment</t>
         </is>
       </c>
       <c r="P69" t="n">
-        <v>36.8</v>
+        <v>28.3</v>
       </c>
       <c r="Q69" t="n">
-        <v>53.8</v>
+        <v>38.4</v>
       </c>
       <c r="R69" t="n">
-        <v>57.2</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="S69" t="n">
-        <v>44.8</v>
+        <v>52.4</v>
       </c>
       <c r="T69" t="n">
         <v>50</v>
       </c>
       <c r="U69" t="n">
-        <v>4.5</v>
+        <v>60.3</v>
       </c>
       <c r="V69" t="inlineStr">
         <is>
@@ -19595,7 +19595,7 @@
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y69" t="inlineStr">
@@ -19633,27 +19633,27 @@
       </c>
       <c r="AH69" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AI69" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/20, 0 HR</t>
+          <t>Contact streak: 10/25 over last 7 games</t>
         </is>
       </c>
       <c r="AL69" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 10.0% barrel, 4.7 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 9.8% barrel, 6.5 HR allowed</t>
         </is>
       </c>
       <c r="AM69" t="inlineStr">
@@ -19663,112 +19663,112 @@
       </c>
       <c r="AN69" t="inlineStr">
         <is>
-          <t>8.48</t>
+          <t>4.38</t>
         </is>
       </c>
       <c r="AO69" t="inlineStr">
         <is>
-          <t>43.04</t>
+          <t>48.47</t>
         </is>
       </c>
       <c r="AP69" t="inlineStr">
         <is>
-          <t>89.73</t>
+          <t>90.22</t>
         </is>
       </c>
       <c r="AQ69" t="inlineStr">
         <is>
-          <t>99.8545</t>
+          <t>100.6499</t>
         </is>
       </c>
       <c r="AR69" t="inlineStr">
         <is>
-          <t>0.3825</t>
+          <t>0.4039</t>
         </is>
       </c>
       <c r="AS69" t="inlineStr">
         <is>
-          <t>0.1659</t>
+          <t>0.1157</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr">
         <is>
-          <t>0.3065</t>
+          <t>0.3366</t>
         </is>
       </c>
       <c r="AU69" t="inlineStr">
         <is>
-          <t>71.18</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="AV69" t="inlineStr">
         <is>
-          <t>7.8</t>
+          <t>8.95</t>
         </is>
       </c>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>45.03</t>
+          <t>32.07</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>31.08</t>
+          <t>16.4</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="AZ69" t="inlineStr">
         <is>
+          <t>0.1073</t>
+        </is>
+      </c>
+      <c r="BA69" t="inlineStr">
+        <is>
+          <t>9.85</t>
+        </is>
+      </c>
+      <c r="BB69" t="inlineStr">
+        <is>
+          <t>37.01</t>
+        </is>
+      </c>
+      <c r="BC69" t="inlineStr">
+        <is>
+          <t>88.54</t>
+        </is>
+      </c>
+      <c r="BD69" t="inlineStr">
+        <is>
+          <t>0.3774</t>
+        </is>
+      </c>
+      <c r="BE69" t="inlineStr">
+        <is>
           <t>0.1513</t>
         </is>
       </c>
-      <c r="BA69" t="inlineStr">
-        <is>
-          <t>9.98</t>
-        </is>
-      </c>
-      <c r="BB69" t="inlineStr">
-        <is>
-          <t>42.07</t>
-        </is>
-      </c>
-      <c r="BC69" t="inlineStr">
-        <is>
-          <t>89.65</t>
-        </is>
-      </c>
-      <c r="BD69" t="inlineStr">
-        <is>
-          <t>0.4729</t>
-        </is>
-      </c>
-      <c r="BE69" t="inlineStr">
-        <is>
-          <t>0.2157</t>
-        </is>
-      </c>
       <c r="BF69" t="inlineStr">
         <is>
-          <t>29.72</t>
+          <t>21.96</t>
         </is>
       </c>
       <c r="BG69" t="inlineStr">
         <is>
-          <t>In From CF</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BH69" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>91</t>
         </is>
       </c>
       <c r="BI69" t="inlineStr">
         <is>
-          <t>Coors Field</t>
+          <t>Oriole Park at Camden Yards</t>
         </is>
       </c>
       <c r="BJ69" t="inlineStr"/>
@@ -19779,47 +19779,47 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>640902</t>
+          <t>694249</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Jhonny Pereda</t>
+          <t>Cole Carrigg</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>CHC</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-06-11T23:05:00Z</t>
+          <t>2026-06-11T19:10:00Z</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Kyle Bradish</t>
+          <t>Edward Cabrera</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>680694</t>
+          <t>665795</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -19828,7 +19828,7 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>44.6</v>
+        <v>44.5</v>
       </c>
       <c r="M70" t="inlineStr">
         <is>
@@ -19842,26 +19842,26 @@
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>Good Environment</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P70" t="n">
-        <v>28.3</v>
+        <v>9.6</v>
       </c>
       <c r="Q70" t="n">
-        <v>38.4</v>
+        <v>54.4</v>
       </c>
       <c r="R70" t="n">
-        <v>74.59999999999999</v>
+        <v>57.2</v>
       </c>
       <c r="S70" t="n">
-        <v>52.4</v>
+        <v>76.2</v>
       </c>
       <c r="T70" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="U70" t="n">
-        <v>60.3</v>
+        <v>45.3</v>
       </c>
       <c r="V70" t="inlineStr">
         <is>
@@ -19875,7 +19875,7 @@
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y70" t="inlineStr">
@@ -19896,7 +19896,7 @@
       <c r="AB70" t="inlineStr"/>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD70" t="inlineStr"/>
@@ -19908,19 +19908,19 @@
       </c>
       <c r="AG70" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AH70" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AI70" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="AI70" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
       <c r="AJ70" t="inlineStr">
         <is>
           <t>1</t>
@@ -19928,127 +19928,127 @@
       </c>
       <c r="AK70" t="inlineStr">
         <is>
-          <t>Contact streak: 10/25 over last 7 games</t>
+          <t>Last 3 games: 3/10, 1 HR</t>
         </is>
       </c>
       <c r="AL70" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 9.8% barrel, 6.5 HR allowed</t>
+          <t>switch hitter; pitcher baseline 11.6% barrel, 12.8 HR allowed</t>
         </is>
       </c>
       <c r="AM70" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN70" t="inlineStr">
         <is>
-          <t>4.38</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AO70" t="inlineStr">
         <is>
-          <t>48.47</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="AP70" t="inlineStr">
         <is>
-          <t>90.22</t>
+          <t>76.3</t>
         </is>
       </c>
       <c r="AQ70" t="inlineStr">
         <is>
-          <t>100.6499</t>
+          <t>89.41</t>
         </is>
       </c>
       <c r="AR70" t="inlineStr">
         <is>
-          <t>0.4039</t>
+          <t>0.136</t>
         </is>
       </c>
       <c r="AS70" t="inlineStr">
         <is>
-          <t>0.1157</t>
+          <t>0.048</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr">
         <is>
-          <t>0.3366</t>
+          <t>0.172</t>
         </is>
       </c>
       <c r="AU70" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="AV70" t="inlineStr">
         <is>
-          <t>8.95</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>32.07</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>16.4</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>0.1073</t>
+          <t>0.286</t>
         </is>
       </c>
       <c r="BA70" t="inlineStr">
         <is>
-          <t>9.85</t>
+          <t>11.61</t>
         </is>
       </c>
       <c r="BB70" t="inlineStr">
         <is>
-          <t>37.01</t>
+          <t>42.55</t>
         </is>
       </c>
       <c r="BC70" t="inlineStr">
         <is>
-          <t>88.54</t>
+          <t>91.21</t>
         </is>
       </c>
       <c r="BD70" t="inlineStr">
         <is>
-          <t>0.3774</t>
+          <t>0.4276</t>
         </is>
       </c>
       <c r="BE70" t="inlineStr">
         <is>
-          <t>0.1513</t>
+          <t>0.1728</t>
         </is>
       </c>
       <c r="BF70" t="inlineStr">
         <is>
-          <t>21.96</t>
+          <t>24.21</t>
         </is>
       </c>
       <c r="BG70" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BH70" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI70" t="inlineStr">
         <is>
-          <t>Oriole Park at Camden Yards</t>
+          <t>Coors Field</t>
         </is>
       </c>
       <c r="BJ70" t="inlineStr"/>
@@ -20059,24 +20059,24 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>694249</t>
+          <t>608348</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Cole Carrigg</t>
+          <t>Carson Kelly</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
+          <t>CHC</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
           <t>COL</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>CHC</t>
-        </is>
-      </c>
       <c r="F71" t="inlineStr">
         <is>
           <t>2026-06-11T19:10:00Z</t>
@@ -20089,17 +20089,17 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Edward Cabrera</t>
+          <t>Ryan Feltner</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>665795</t>
+          <t>663372</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -20108,7 +20108,7 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>44.5</v>
+        <v>43.9</v>
       </c>
       <c r="M71" t="inlineStr">
         <is>
@@ -20122,26 +20122,26 @@
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P71" t="n">
-        <v>9.6</v>
+        <v>29.7</v>
       </c>
       <c r="Q71" t="n">
-        <v>54.4</v>
+        <v>53.8</v>
       </c>
       <c r="R71" t="n">
         <v>57.2</v>
       </c>
       <c r="S71" t="n">
-        <v>76.2</v>
+        <v>44.8</v>
       </c>
       <c r="T71" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U71" t="n">
-        <v>45.3</v>
+        <v>36</v>
       </c>
       <c r="V71" t="inlineStr">
         <is>
@@ -20155,7 +20155,7 @@
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y71" t="inlineStr">
@@ -20165,7 +20165,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -20173,10 +20173,14 @@
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB71" t="inlineStr"/>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>order MLB 9 vs RotoWire 8</t>
+        </is>
+      </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD71" t="inlineStr"/>
@@ -20188,17 +20192,17 @@
       </c>
       <c r="AG71" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AH71" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI71" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ71" t="inlineStr">
@@ -20208,112 +20212,112 @@
       </c>
       <c r="AK71" t="inlineStr">
         <is>
-          <t>Last 3 games: 3/10, 1 HR</t>
+          <t>Last 7 games: 5/21, 1 HR</t>
         </is>
       </c>
       <c r="AL71" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 11.6% barrel, 12.8 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 10.0% barrel, 4.7 HR allowed</t>
         </is>
       </c>
       <c r="AM71" t="inlineStr">
         <is>
-          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN71" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.22</t>
         </is>
       </c>
       <c r="AO71" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>40.3</t>
         </is>
       </c>
       <c r="AP71" t="inlineStr">
         <is>
-          <t>76.3</t>
+          <t>88.94</t>
         </is>
       </c>
       <c r="AQ71" t="inlineStr">
         <is>
-          <t>89.41</t>
+          <t>99.448</t>
         </is>
       </c>
       <c r="AR71" t="inlineStr">
         <is>
-          <t>0.136</t>
+          <t>0.3879</t>
         </is>
       </c>
       <c r="AS71" t="inlineStr">
         <is>
-          <t>0.048</t>
+          <t>0.1407</t>
         </is>
       </c>
       <c r="AT71" t="inlineStr">
         <is>
-          <t>0.172</t>
+          <t>0.3182</t>
         </is>
       </c>
       <c r="AU71" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>70.89</t>
         </is>
       </c>
       <c r="AV71" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>37.89</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>24.66</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>0.286</t>
+          <t>0.1062</t>
         </is>
       </c>
       <c r="BA71" t="inlineStr">
         <is>
-          <t>11.61</t>
+          <t>9.98</t>
         </is>
       </c>
       <c r="BB71" t="inlineStr">
         <is>
-          <t>42.55</t>
+          <t>42.07</t>
         </is>
       </c>
       <c r="BC71" t="inlineStr">
         <is>
-          <t>91.21</t>
+          <t>89.65</t>
         </is>
       </c>
       <c r="BD71" t="inlineStr">
         <is>
-          <t>0.4276</t>
+          <t>0.4729</t>
         </is>
       </c>
       <c r="BE71" t="inlineStr">
         <is>
-          <t>0.1728</t>
+          <t>0.2157</t>
         </is>
       </c>
       <c r="BF71" t="inlineStr">
         <is>
-          <t>24.21</t>
+          <t>29.72</t>
         </is>
       </c>
       <c r="BG71" t="inlineStr">
@@ -20619,27 +20623,27 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>608348</t>
+          <t>657041</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Carson Kelly</t>
+          <t>Lane Thomas</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>CHC</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-06-11T19:10:00Z</t>
+          <t>2026-06-11T18:10:00Z</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -20649,17 +20653,17 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Ryan Feltner</t>
+          <t>Kumar Rocker</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>663372</t>
+          <t>677958</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -20668,7 +20672,7 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>43.7</v>
+        <v>42.7</v>
       </c>
       <c r="M73" t="inlineStr">
         <is>
@@ -20686,22 +20690,22 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>29.7</v>
+        <v>15.4</v>
       </c>
       <c r="Q73" t="n">
-        <v>53.8</v>
+        <v>48</v>
       </c>
       <c r="R73" t="n">
-        <v>57.2</v>
+        <v>52.7</v>
       </c>
       <c r="S73" t="n">
-        <v>52.4</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T73" t="n">
         <v>50</v>
       </c>
       <c r="U73" t="n">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="V73" t="inlineStr">
         <is>
@@ -20715,7 +20719,7 @@
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y73" t="inlineStr">
@@ -20753,12 +20757,12 @@
       </c>
       <c r="AH73" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI73" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AJ73" t="inlineStr">
@@ -20768,12 +20772,12 @@
       </c>
       <c r="AK73" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/20, 0 HR</t>
+          <t>Contact streak: 5/15 over last 7 games</t>
         </is>
       </c>
       <c r="AL73" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 10.0% barrel, 4.7 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 9.3% barrel, 7.5 HR allowed</t>
         </is>
       </c>
       <c r="AM73" t="inlineStr">
@@ -20783,112 +20787,112 @@
       </c>
       <c r="AN73" t="inlineStr">
         <is>
-          <t>7.22</t>
+          <t>3.68</t>
         </is>
       </c>
       <c r="AO73" t="inlineStr">
         <is>
-          <t>40.3</t>
+          <t>33.96</t>
         </is>
       </c>
       <c r="AP73" t="inlineStr">
         <is>
-          <t>88.94</t>
+          <t>86.96</t>
         </is>
       </c>
       <c r="AQ73" t="inlineStr">
         <is>
-          <t>99.448</t>
+          <t>98.04</t>
         </is>
       </c>
       <c r="AR73" t="inlineStr">
         <is>
-          <t>0.3879</t>
+          <t>0.3028</t>
         </is>
       </c>
       <c r="AS73" t="inlineStr">
         <is>
-          <t>0.1407</t>
+          <t>0.0942</t>
         </is>
       </c>
       <c r="AT73" t="inlineStr">
         <is>
-          <t>0.3182</t>
+          <t>0.2913</t>
         </is>
       </c>
       <c r="AU73" t="inlineStr">
         <is>
-          <t>70.89</t>
+          <t>72.28</t>
         </is>
       </c>
       <c r="AV73" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>20.7</t>
         </is>
       </c>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>37.89</t>
+          <t>40.65</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>24.66</t>
+          <t>30.69</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>0.1062</t>
+          <t>0.0903</t>
         </is>
       </c>
       <c r="BA73" t="inlineStr">
         <is>
-          <t>9.98</t>
+          <t>9.28</t>
         </is>
       </c>
       <c r="BB73" t="inlineStr">
         <is>
-          <t>42.07</t>
+          <t>43.79</t>
         </is>
       </c>
       <c r="BC73" t="inlineStr">
         <is>
-          <t>89.65</t>
+          <t>90.08</t>
         </is>
       </c>
       <c r="BD73" t="inlineStr">
         <is>
-          <t>0.4729</t>
+          <t>0.4423</t>
         </is>
       </c>
       <c r="BE73" t="inlineStr">
         <is>
-          <t>0.2157</t>
+          <t>0.1766</t>
         </is>
       </c>
       <c r="BF73" t="inlineStr">
         <is>
-          <t>29.72</t>
+          <t>22.44</t>
         </is>
       </c>
       <c r="BG73" t="inlineStr">
         <is>
-          <t>In From CF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH73" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>84</t>
         </is>
       </c>
       <c r="BI73" t="inlineStr">
         <is>
-          <t>Coors Field</t>
+          <t>Kauffman Stadium</t>
         </is>
       </c>
       <c r="BJ73" t="inlineStr"/>
@@ -20899,47 +20903,47 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>657041</t>
+          <t>690976</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Lane Thomas</t>
+          <t>Alex Freeland</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-06-11T18:10:00Z</t>
+          <t>2026-06-11T22:40:00Z</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Kumar Rocker</t>
+          <t>Mitch Keller</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>677958</t>
+          <t>656605</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -20948,7 +20952,7 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>42.7</v>
+        <v>42.3</v>
       </c>
       <c r="M74" t="inlineStr">
         <is>
@@ -20962,26 +20966,26 @@
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>No major boost</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P74" t="n">
-        <v>15.4</v>
+        <v>28.5</v>
       </c>
       <c r="Q74" t="n">
-        <v>48</v>
+        <v>35.2</v>
       </c>
       <c r="R74" t="n">
-        <v>52.7</v>
+        <v>68.3</v>
       </c>
       <c r="S74" t="n">
-        <v>86.40000000000001</v>
+        <v>44.8</v>
       </c>
       <c r="T74" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="U74" t="n">
-        <v>32</v>
+        <v>23.7</v>
       </c>
       <c r="V74" t="inlineStr">
         <is>
@@ -20995,7 +20999,7 @@
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y74" t="inlineStr">
@@ -21038,7 +21042,7 @@
       </c>
       <c r="AI74" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AJ74" t="inlineStr">
@@ -21048,12 +21052,12 @@
       </c>
       <c r="AK74" t="inlineStr">
         <is>
-          <t>Contact streak: 5/15 over last 7 games</t>
+          <t>Last 7 games: 5/18, 0 HR</t>
         </is>
       </c>
       <c r="AL74" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 9.3% barrel, 7.5 HR allowed</t>
+          <t>switch hitter; pitcher baseline 7.1% barrel, 9.8 HR allowed</t>
         </is>
       </c>
       <c r="AM74" t="inlineStr">
@@ -21063,102 +21067,102 @@
       </c>
       <c r="AN74" t="inlineStr">
         <is>
-          <t>3.68</t>
+          <t>7.65</t>
         </is>
       </c>
       <c r="AO74" t="inlineStr">
         <is>
-          <t>33.96</t>
+          <t>38.49</t>
         </is>
       </c>
       <c r="AP74" t="inlineStr">
         <is>
-          <t>86.96</t>
+          <t>89.58</t>
         </is>
       </c>
       <c r="AQ74" t="inlineStr">
         <is>
-          <t>98.04</t>
+          <t>98.9415</t>
         </is>
       </c>
       <c r="AR74" t="inlineStr">
         <is>
-          <t>0.3028</t>
+          <t>0.341</t>
         </is>
       </c>
       <c r="AS74" t="inlineStr">
         <is>
-          <t>0.0942</t>
+          <t>0.1308</t>
         </is>
       </c>
       <c r="AT74" t="inlineStr">
         <is>
-          <t>0.2913</t>
+          <t>0.2915</t>
         </is>
       </c>
       <c r="AU74" t="inlineStr">
         <is>
-          <t>72.28</t>
+          <t>70.63</t>
         </is>
       </c>
       <c r="AV74" t="inlineStr">
         <is>
-          <t>20.7</t>
+          <t>9.68</t>
         </is>
       </c>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>40.65</t>
+          <t>34.01</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>30.69</t>
+          <t>26.46</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>2.7</t>
         </is>
       </c>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>0.0903</t>
+          <t>0.113</t>
         </is>
       </c>
       <c r="BA74" t="inlineStr">
         <is>
-          <t>9.28</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="BB74" t="inlineStr">
         <is>
-          <t>43.79</t>
+          <t>40.44</t>
         </is>
       </c>
       <c r="BC74" t="inlineStr">
         <is>
-          <t>90.08</t>
+          <t>88.63</t>
         </is>
       </c>
       <c r="BD74" t="inlineStr">
         <is>
-          <t>0.4423</t>
+          <t>0.4216</t>
         </is>
       </c>
       <c r="BE74" t="inlineStr">
         <is>
-          <t>0.1766</t>
+          <t>0.1493</t>
         </is>
       </c>
       <c r="BF74" t="inlineStr">
         <is>
-          <t>22.44</t>
+          <t>22.09</t>
         </is>
       </c>
       <c r="BG74" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>Out To LF</t>
         </is>
       </c>
       <c r="BH74" t="inlineStr">
@@ -21168,7 +21172,7 @@
       </c>
       <c r="BI74" t="inlineStr">
         <is>
-          <t>Kauffman Stadium</t>
+          <t>PNC Park</t>
         </is>
       </c>
       <c r="BJ74" t="inlineStr"/>
@@ -21179,47 +21183,47 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>690976</t>
+          <t>694497</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Alex Freeland</t>
+          <t>Evan Carter</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-06-11T22:40:00Z</t>
+          <t>2026-06-11T18:10:00Z</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Mitch Keller</t>
+          <t>Michael Wacha</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>656605</t>
+          <t>608379</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -21228,7 +21232,7 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>42.3</v>
+        <v>41.9</v>
       </c>
       <c r="M75" t="inlineStr">
         <is>
@@ -21246,22 +21250,22 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>28.5</v>
+        <v>25.6</v>
       </c>
       <c r="Q75" t="n">
-        <v>35.2</v>
+        <v>37</v>
       </c>
       <c r="R75" t="n">
-        <v>68.3</v>
+        <v>52.7</v>
       </c>
       <c r="S75" t="n">
-        <v>44.8</v>
+        <v>64.3</v>
       </c>
       <c r="T75" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="U75" t="n">
-        <v>23.7</v>
+        <v>10.1</v>
       </c>
       <c r="V75" t="inlineStr">
         <is>
@@ -21275,7 +21279,7 @@
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y75" t="inlineStr">
@@ -21313,12 +21317,12 @@
       </c>
       <c r="AH75" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI75" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AJ75" t="inlineStr">
@@ -21328,12 +21332,12 @@
       </c>
       <c r="AK75" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/18, 0 HR</t>
+          <t>Last 7 games: 3/16, 0 HR</t>
         </is>
       </c>
       <c r="AL75" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 7.1% barrel, 9.8 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.0% barrel, 10.8 HR allowed</t>
         </is>
       </c>
       <c r="AM75" t="inlineStr">
@@ -21343,102 +21347,102 @@
       </c>
       <c r="AN75" t="inlineStr">
         <is>
-          <t>7.65</t>
+          <t>6.74</t>
         </is>
       </c>
       <c r="AO75" t="inlineStr">
         <is>
-          <t>38.49</t>
+          <t>36.91</t>
         </is>
       </c>
       <c r="AP75" t="inlineStr">
         <is>
-          <t>89.58</t>
+          <t>87.54</t>
         </is>
       </c>
       <c r="AQ75" t="inlineStr">
         <is>
-          <t>98.9415</t>
+          <t>98.8808</t>
         </is>
       </c>
       <c r="AR75" t="inlineStr">
         <is>
-          <t>0.341</t>
+          <t>0.3474</t>
         </is>
       </c>
       <c r="AS75" t="inlineStr">
         <is>
-          <t>0.1308</t>
+          <t>0.1351</t>
         </is>
       </c>
       <c r="AT75" t="inlineStr">
         <is>
-          <t>0.2915</t>
+          <t>0.3017</t>
         </is>
       </c>
       <c r="AU75" t="inlineStr">
         <is>
-          <t>70.63</t>
+          <t>70.91</t>
         </is>
       </c>
       <c r="AV75" t="inlineStr">
         <is>
-          <t>9.68</t>
+          <t>17.12</t>
         </is>
       </c>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>34.01</t>
+          <t>36.18</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>26.46</t>
+          <t>31.55</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t>5.7</t>
         </is>
       </c>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>0.113</t>
+          <t>0.1485</t>
         </is>
       </c>
       <c r="BA75" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>7.05</t>
         </is>
       </c>
       <c r="BB75" t="inlineStr">
         <is>
-          <t>40.44</t>
+          <t>37.05</t>
         </is>
       </c>
       <c r="BC75" t="inlineStr">
         <is>
-          <t>88.63</t>
+          <t>88.41</t>
         </is>
       </c>
       <c r="BD75" t="inlineStr">
         <is>
-          <t>0.4216</t>
+          <t>0.4196</t>
         </is>
       </c>
       <c r="BE75" t="inlineStr">
         <is>
-          <t>0.1493</t>
+          <t>0.1668</t>
         </is>
       </c>
       <c r="BF75" t="inlineStr">
         <is>
-          <t>22.09</t>
+          <t>27.55</t>
         </is>
       </c>
       <c r="BG75" t="inlineStr">
         <is>
-          <t>Out To LF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH75" t="inlineStr">
@@ -21448,7 +21452,7 @@
       </c>
       <c r="BI75" t="inlineStr">
         <is>
-          <t>PNC Park</t>
+          <t>Kauffman Stadium</t>
         </is>
       </c>
       <c r="BJ75" t="inlineStr"/>
@@ -21459,47 +21463,47 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>694497</t>
+          <t>806068</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Evan Carter</t>
+          <t>Colt Emerson</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-06-11T18:10:00Z</t>
+          <t>2026-06-11T23:05:00Z</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Michael Wacha</t>
+          <t>Kyle Bradish</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>608379</t>
+          <t>680694</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -21508,7 +21512,7 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>42</v>
+        <v>41.9</v>
       </c>
       <c r="M76" t="inlineStr">
         <is>
@@ -21522,26 +21526,26 @@
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Good Environment, Platoon Edge</t>
         </is>
       </c>
       <c r="P76" t="n">
-        <v>25.6</v>
+        <v>15.7</v>
       </c>
       <c r="Q76" t="n">
-        <v>37</v>
+        <v>38.4</v>
       </c>
       <c r="R76" t="n">
-        <v>52.7</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="S76" t="n">
-        <v>64.3</v>
+        <v>44.8</v>
       </c>
       <c r="T76" t="n">
         <v>80</v>
       </c>
       <c r="U76" t="n">
-        <v>12</v>
+        <v>56.2</v>
       </c>
       <c r="V76" t="inlineStr">
         <is>
@@ -21555,7 +21559,7 @@
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y76" t="inlineStr">
@@ -21576,7 +21580,7 @@
       <c r="AB76" t="inlineStr"/>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD76" t="inlineStr"/>
@@ -21593,27 +21597,27 @@
       </c>
       <c r="AH76" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI76" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK76" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/15, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL76" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.0% barrel, 10.8 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.8% barrel, 6.5 HR allowed</t>
         </is>
       </c>
       <c r="AM76" t="inlineStr">
@@ -21623,112 +21627,112 @@
       </c>
       <c r="AN76" t="inlineStr">
         <is>
-          <t>6.74</t>
+          <t>4.9</t>
         </is>
       </c>
       <c r="AO76" t="inlineStr">
         <is>
-          <t>36.91</t>
+          <t>31.7</t>
         </is>
       </c>
       <c r="AP76" t="inlineStr">
         <is>
-          <t>87.54</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AQ76" t="inlineStr">
         <is>
-          <t>98.8808</t>
+          <t>97.4401</t>
         </is>
       </c>
       <c r="AR76" t="inlineStr">
         <is>
-          <t>0.3474</t>
+          <t>0.257</t>
         </is>
       </c>
       <c r="AS76" t="inlineStr">
         <is>
-          <t>0.1351</t>
+          <t>0.099</t>
         </is>
       </c>
       <c r="AT76" t="inlineStr">
         <is>
-          <t>0.3017</t>
+          <t>0.232</t>
         </is>
       </c>
       <c r="AU76" t="inlineStr">
         <is>
-          <t>70.91</t>
+          <t>72.4</t>
         </is>
       </c>
       <c r="AV76" t="inlineStr">
         <is>
-          <t>17.12</t>
+          <t>24.8</t>
         </is>
       </c>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>36.18</t>
+          <t>43.9</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>31.55</t>
+          <t>19.5</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr">
         <is>
-          <t>5.7</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>0.1485</t>
+          <t>0.306</t>
         </is>
       </c>
       <c r="BA76" t="inlineStr">
         <is>
-          <t>7.05</t>
+          <t>9.85</t>
         </is>
       </c>
       <c r="BB76" t="inlineStr">
         <is>
-          <t>37.05</t>
+          <t>37.01</t>
         </is>
       </c>
       <c r="BC76" t="inlineStr">
         <is>
-          <t>88.41</t>
+          <t>88.54</t>
         </is>
       </c>
       <c r="BD76" t="inlineStr">
         <is>
-          <t>0.4196</t>
+          <t>0.3774</t>
         </is>
       </c>
       <c r="BE76" t="inlineStr">
         <is>
-          <t>0.1668</t>
+          <t>0.1513</t>
         </is>
       </c>
       <c r="BF76" t="inlineStr">
         <is>
-          <t>27.55</t>
+          <t>21.96</t>
         </is>
       </c>
       <c r="BG76" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BH76" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>91</t>
         </is>
       </c>
       <c r="BI76" t="inlineStr">
         <is>
-          <t>Kauffman Stadium</t>
+          <t>Oriole Park at Camden Yards</t>
         </is>
       </c>
       <c r="BJ76" t="inlineStr"/>
@@ -21739,47 +21743,47 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>806068</t>
+          <t>677649</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Colt Emerson</t>
+          <t>Ezequiel Duran</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-06-11T23:05:00Z</t>
+          <t>2026-06-11T18:10:00Z</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Kyle Bradish</t>
+          <t>Michael Wacha</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>680694</t>
+          <t>608379</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -21788,7 +21792,7 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>41.9</v>
+        <v>41.7</v>
       </c>
       <c r="M77" t="inlineStr">
         <is>
@@ -21802,26 +21806,26 @@
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>Good Environment, Platoon Edge</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P77" t="n">
-        <v>15.7</v>
+        <v>21.3</v>
       </c>
       <c r="Q77" t="n">
-        <v>38.4</v>
+        <v>37</v>
       </c>
       <c r="R77" t="n">
-        <v>74.59999999999999</v>
+        <v>52.7</v>
       </c>
       <c r="S77" t="n">
-        <v>44.8</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T77" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U77" t="n">
-        <v>56.2</v>
+        <v>25.8</v>
       </c>
       <c r="V77" t="inlineStr">
         <is>
@@ -21835,7 +21839,7 @@
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y77" t="inlineStr">
@@ -21856,7 +21860,7 @@
       <c r="AB77" t="inlineStr"/>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD77" t="inlineStr"/>
@@ -21873,7 +21877,7 @@
       </c>
       <c r="AH77" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI77" t="inlineStr">
@@ -21883,17 +21887,17 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 7/24, 0 HR</t>
         </is>
       </c>
       <c r="AL77" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 9.8% barrel, 6.5 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.0% barrel, 10.8 HR allowed</t>
         </is>
       </c>
       <c r="AM77" t="inlineStr">
@@ -21903,112 +21907,112 @@
       </c>
       <c r="AN77" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>5.19</t>
         </is>
       </c>
       <c r="AO77" t="inlineStr">
         <is>
-          <t>31.7</t>
+          <t>36.5</t>
         </is>
       </c>
       <c r="AP77" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>88.73</t>
         </is>
       </c>
       <c r="AQ77" t="inlineStr">
         <is>
-          <t>97.4401</t>
+          <t>99.3418</t>
         </is>
       </c>
       <c r="AR77" t="inlineStr">
         <is>
-          <t>0.257</t>
+          <t>0.3552</t>
         </is>
       </c>
       <c r="AS77" t="inlineStr">
         <is>
-          <t>0.099</t>
+          <t>0.1062</t>
         </is>
       </c>
       <c r="AT77" t="inlineStr">
         <is>
-          <t>0.232</t>
+          <t>0.2946</t>
         </is>
       </c>
       <c r="AU77" t="inlineStr">
         <is>
-          <t>72.4</t>
+          <t>72.48</t>
         </is>
       </c>
       <c r="AV77" t="inlineStr">
         <is>
-          <t>24.8</t>
+          <t>25.81</t>
         </is>
       </c>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>43.9</t>
+          <t>34.75</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>19.5</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>0.306</t>
+          <t>0.1334</t>
         </is>
       </c>
       <c r="BA77" t="inlineStr">
         <is>
-          <t>9.85</t>
+          <t>7.05</t>
         </is>
       </c>
       <c r="BB77" t="inlineStr">
         <is>
-          <t>37.01</t>
+          <t>37.05</t>
         </is>
       </c>
       <c r="BC77" t="inlineStr">
         <is>
-          <t>88.54</t>
+          <t>88.41</t>
         </is>
       </c>
       <c r="BD77" t="inlineStr">
         <is>
-          <t>0.3774</t>
+          <t>0.4196</t>
         </is>
       </c>
       <c r="BE77" t="inlineStr">
         <is>
-          <t>0.1513</t>
+          <t>0.1668</t>
         </is>
       </c>
       <c r="BF77" t="inlineStr">
         <is>
-          <t>21.96</t>
+          <t>27.55</t>
         </is>
       </c>
       <c r="BG77" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH77" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>84</t>
         </is>
       </c>
       <c r="BI77" t="inlineStr">
         <is>
-          <t>Oriole Park at Camden Yards</t>
+          <t>Kauffman Stadium</t>
         </is>
       </c>
       <c r="BJ77" t="inlineStr"/>
@@ -22019,27 +22023,27 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>677649</t>
+          <t>691720</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Ezequiel Duran</t>
+          <t>Kyle Karros</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>CHC</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-06-11T18:10:00Z</t>
+          <t>2026-06-11T19:10:00Z</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -22049,17 +22053,17 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Michael Wacha</t>
+          <t>Edward Cabrera</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>608379</t>
+          <t>665795</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -22068,7 +22072,7 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>41.8</v>
+        <v>41.5</v>
       </c>
       <c r="M78" t="inlineStr">
         <is>
@@ -22086,46 +22090,38 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>21.3</v>
+        <v>20</v>
       </c>
       <c r="Q78" t="n">
-        <v>37</v>
+        <v>55.7</v>
       </c>
       <c r="R78" t="n">
-        <v>52.7</v>
+        <v>57.2</v>
       </c>
       <c r="S78" t="n">
-        <v>86.40000000000001</v>
+        <v>52.4</v>
       </c>
       <c r="T78" t="n">
         <v>50</v>
       </c>
       <c r="U78" t="n">
-        <v>27.7</v>
+        <v>21.5</v>
       </c>
       <c r="V78" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W78" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="X78" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+      <c r="W78" t="inlineStr"/>
+      <c r="X78" t="inlineStr"/>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -22133,7 +22129,11 @@
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB78" t="inlineStr"/>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>not found on RotoWire</t>
+        </is>
+      </c>
       <c r="AC78" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -22153,12 +22153,12 @@
       </c>
       <c r="AH78" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI78" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AJ78" t="inlineStr">
@@ -22168,12 +22168,12 @@
       </c>
       <c r="AK78" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/23, 0 HR</t>
+          <t>Last 7 games: 5/19, 0 HR</t>
         </is>
       </c>
       <c r="AL78" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.0% barrel, 10.8 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 11.6% barrel, 12.8 HR allowed</t>
         </is>
       </c>
       <c r="AM78" t="inlineStr">
@@ -22183,112 +22183,112 @@
       </c>
       <c r="AN78" t="inlineStr">
         <is>
-          <t>5.19</t>
+          <t>4.78</t>
         </is>
       </c>
       <c r="AO78" t="inlineStr">
         <is>
-          <t>36.5</t>
+          <t>38.88</t>
         </is>
       </c>
       <c r="AP78" t="inlineStr">
         <is>
-          <t>88.73</t>
+          <t>88.67</t>
         </is>
       </c>
       <c r="AQ78" t="inlineStr">
         <is>
-          <t>99.3418</t>
+          <t>99.3561</t>
         </is>
       </c>
       <c r="AR78" t="inlineStr">
         <is>
-          <t>0.3552</t>
+          <t>0.3446</t>
         </is>
       </c>
       <c r="AS78" t="inlineStr">
         <is>
-          <t>0.1062</t>
+          <t>0.1054</t>
         </is>
       </c>
       <c r="AT78" t="inlineStr">
         <is>
-          <t>0.2946</t>
+          <t>0.3105</t>
         </is>
       </c>
       <c r="AU78" t="inlineStr">
         <is>
-          <t>72.48</t>
+          <t>69.87</t>
         </is>
       </c>
       <c r="AV78" t="inlineStr">
         <is>
-          <t>25.81</t>
+          <t>4.67</t>
         </is>
       </c>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>34.75</t>
+          <t>37.33</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>20.98</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>0.1334</t>
+          <t>0.0895</t>
         </is>
       </c>
       <c r="BA78" t="inlineStr">
         <is>
-          <t>7.05</t>
+          <t>11.61</t>
         </is>
       </c>
       <c r="BB78" t="inlineStr">
         <is>
-          <t>37.05</t>
+          <t>42.55</t>
         </is>
       </c>
       <c r="BC78" t="inlineStr">
         <is>
-          <t>88.41</t>
+          <t>91.21</t>
         </is>
       </c>
       <c r="BD78" t="inlineStr">
         <is>
-          <t>0.4196</t>
+          <t>0.4276</t>
         </is>
       </c>
       <c r="BE78" t="inlineStr">
         <is>
-          <t>0.1668</t>
+          <t>0.1728</t>
         </is>
       </c>
       <c r="BF78" t="inlineStr">
         <is>
-          <t>27.55</t>
+          <t>24.21</t>
         </is>
       </c>
       <c r="BG78" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BH78" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI78" t="inlineStr">
         <is>
-          <t>Kauffman Stadium</t>
+          <t>Coors Field</t>
         </is>
       </c>
       <c r="BJ78" t="inlineStr"/>
@@ -22299,27 +22299,27 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>691720</t>
+          <t>670224</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Kyle Karros</t>
+          <t>Kameron Misner</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>CHC</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-06-11T19:10:00Z</t>
+          <t>2026-06-11T18:10:00Z</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -22329,17 +22329,17 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Edward Cabrera</t>
+          <t>Kumar Rocker</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>665795</t>
+          <t>677958</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
@@ -22348,7 +22348,7 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>41.5</v>
+        <v>41.4</v>
       </c>
       <c r="M79" t="inlineStr">
         <is>
@@ -22362,57 +22362,61 @@
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>No major boost</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P79" t="n">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="Q79" t="n">
-        <v>55.7</v>
+        <v>48</v>
       </c>
       <c r="R79" t="n">
-        <v>57.2</v>
+        <v>52.7</v>
       </c>
       <c r="S79" t="n">
-        <v>52.4</v>
+        <v>64.3</v>
       </c>
       <c r="T79" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U79" t="n">
-        <v>21.5</v>
+        <v>0</v>
       </c>
       <c r="V79" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W79" t="inlineStr"/>
-      <c r="X79" t="inlineStr"/>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="Y79" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z79" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z79" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB79" t="inlineStr">
-        <is>
-          <t>not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB79" t="inlineStr"/>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD79" t="inlineStr"/>
@@ -22424,17 +22428,17 @@
       </c>
       <c r="AG79" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AH79" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AI79" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AJ79" t="inlineStr">
@@ -22444,12 +22448,12 @@
       </c>
       <c r="AK79" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/19, 0 HR</t>
+          <t>Last 2 games: 0/1, 0 HR</t>
         </is>
       </c>
       <c r="AL79" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 11.6% barrel, 12.8 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.3% barrel, 7.5 HR allowed</t>
         </is>
       </c>
       <c r="AM79" t="inlineStr">
@@ -22459,112 +22463,112 @@
       </c>
       <c r="AN79" t="inlineStr">
         <is>
-          <t>4.78</t>
+          <t>5.3</t>
         </is>
       </c>
       <c r="AO79" t="inlineStr">
         <is>
-          <t>38.88</t>
+          <t>29.8</t>
         </is>
       </c>
       <c r="AP79" t="inlineStr">
         <is>
-          <t>88.67</t>
+          <t>87.6</t>
         </is>
       </c>
       <c r="AQ79" t="inlineStr">
         <is>
-          <t>99.3561</t>
+          <t>98.4049</t>
         </is>
       </c>
       <c r="AR79" t="inlineStr">
         <is>
-          <t>0.3446</t>
+          <t>0.299</t>
         </is>
       </c>
       <c r="AS79" t="inlineStr">
         <is>
-          <t>0.1054</t>
+          <t>0.108</t>
         </is>
       </c>
       <c r="AT79" t="inlineStr">
         <is>
-          <t>0.3105</t>
+          <t>0.247</t>
         </is>
       </c>
       <c r="AU79" t="inlineStr">
         <is>
-          <t>69.87</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="AV79" t="inlineStr">
         <is>
-          <t>4.67</t>
+          <t>32.4</t>
         </is>
       </c>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>37.33</t>
+          <t>38.9</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>20.98</t>
+          <t>26.7</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>0.0895</t>
+          <t>0.132</t>
         </is>
       </c>
       <c r="BA79" t="inlineStr">
         <is>
-          <t>11.61</t>
+          <t>9.28</t>
         </is>
       </c>
       <c r="BB79" t="inlineStr">
         <is>
-          <t>42.55</t>
+          <t>43.79</t>
         </is>
       </c>
       <c r="BC79" t="inlineStr">
         <is>
-          <t>91.21</t>
+          <t>90.08</t>
         </is>
       </c>
       <c r="BD79" t="inlineStr">
         <is>
-          <t>0.4276</t>
+          <t>0.4423</t>
         </is>
       </c>
       <c r="BE79" t="inlineStr">
         <is>
-          <t>0.1728</t>
+          <t>0.1766</t>
         </is>
       </c>
       <c r="BF79" t="inlineStr">
         <is>
-          <t>24.21</t>
+          <t>22.44</t>
         </is>
       </c>
       <c r="BG79" t="inlineStr">
         <is>
-          <t>In From CF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH79" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>84</t>
         </is>
       </c>
       <c r="BI79" t="inlineStr">
         <is>
-          <t>Coors Field</t>
+          <t>Kauffman Stadium</t>
         </is>
       </c>
       <c r="BJ79" t="inlineStr"/>
@@ -22575,32 +22579,32 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>670224</t>
+          <t>700337</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Kameron Misner</t>
+          <t>Edgar Quero</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-06-11T18:10:00Z</t>
+          <t>2026-06-11T23:40:00Z</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -22610,17 +22614,17 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Kumar Rocker</t>
+          <t>Martín Pérez</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>677958</t>
+          <t>527048</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L80" t="n">
@@ -22642,22 +22646,22 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>17.5</v>
+        <v>15.7</v>
       </c>
       <c r="Q80" t="n">
-        <v>48</v>
+        <v>44.4</v>
       </c>
       <c r="R80" t="n">
-        <v>52.7</v>
+        <v>55.6</v>
       </c>
       <c r="S80" t="n">
         <v>64.3</v>
       </c>
       <c r="T80" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="U80" t="n">
-        <v>0</v>
+        <v>28.9</v>
       </c>
       <c r="V80" t="inlineStr">
         <is>
@@ -22692,7 +22696,7 @@
       <c r="AB80" t="inlineStr"/>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>H:2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD80" t="inlineStr"/>
@@ -22704,32 +22708,32 @@
       </c>
       <c r="AG80" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AH80" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI80" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="AJ80" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AJ80" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AK80" t="inlineStr">
         <is>
-          <t>Last 2 games: 0/1, 0 HR</t>
+          <t>Last 7 games: 4/21, 1 HR</t>
         </is>
       </c>
       <c r="AL80" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 9.3% barrel, 7.5 HR allowed</t>
+          <t>switch hitter; pitcher baseline 9.9% barrel, 6.0 HR allowed</t>
         </is>
       </c>
       <c r="AM80" t="inlineStr">
@@ -22739,112 +22743,112 @@
       </c>
       <c r="AN80" t="inlineStr">
         <is>
-          <t>5.3</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="AO80" t="inlineStr">
         <is>
-          <t>29.8</t>
+          <t>36.78</t>
         </is>
       </c>
       <c r="AP80" t="inlineStr">
         <is>
-          <t>87.6</t>
+          <t>90.47</t>
         </is>
       </c>
       <c r="AQ80" t="inlineStr">
         <is>
-          <t>98.4049</t>
+          <t>98.5819</t>
         </is>
       </c>
       <c r="AR80" t="inlineStr">
         <is>
-          <t>0.299</t>
+          <t>0.2935</t>
         </is>
       </c>
       <c r="AS80" t="inlineStr">
         <is>
-          <t>0.108</t>
+          <t>0.0848</t>
         </is>
       </c>
       <c r="AT80" t="inlineStr">
         <is>
-          <t>0.247</t>
+          <t>0.2634</t>
         </is>
       </c>
       <c r="AU80" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>68.2</t>
         </is>
       </c>
       <c r="AV80" t="inlineStr">
         <is>
-          <t>32.4</t>
+          <t>3.22</t>
         </is>
       </c>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>38.9</t>
+          <t>32.6</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>26.7</t>
+          <t>24.73</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>2.9</t>
         </is>
       </c>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>0.132</t>
+          <t>0.0635</t>
         </is>
       </c>
       <c r="BA80" t="inlineStr">
         <is>
-          <t>9.28</t>
+          <t>9.89</t>
         </is>
       </c>
       <c r="BB80" t="inlineStr">
         <is>
-          <t>43.79</t>
+          <t>39.61</t>
         </is>
       </c>
       <c r="BC80" t="inlineStr">
         <is>
-          <t>90.08</t>
+          <t>88.76</t>
         </is>
       </c>
       <c r="BD80" t="inlineStr">
         <is>
-          <t>0.4423</t>
+          <t>0.4199</t>
         </is>
       </c>
       <c r="BE80" t="inlineStr">
         <is>
-          <t>0.1766</t>
+          <t>0.1737</t>
         </is>
       </c>
       <c r="BF80" t="inlineStr">
         <is>
-          <t>22.44</t>
+          <t>27.07</t>
         </is>
       </c>
       <c r="BG80" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>In From RF</t>
         </is>
       </c>
       <c r="BH80" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>82</t>
         </is>
       </c>
       <c r="BI80" t="inlineStr">
         <is>
-          <t>Kauffman Stadium</t>
+          <t>Rate Field</t>
         </is>
       </c>
       <c r="BJ80" t="inlineStr"/>
@@ -22855,56 +22859,56 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>700337</t>
+          <t>686555</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Edgar Quero</t>
+          <t>Isaac Collins</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-06-11T23:40:00Z</t>
+          <t>2026-06-11T18:10:00Z</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Martín Pérez</t>
+          <t>Kumar Rocker</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>527048</t>
+          <t>677958</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L81" t="n">
-        <v>41.4</v>
+        <v>41.1</v>
       </c>
       <c r="M81" t="inlineStr">
         <is>
@@ -22922,22 +22926,22 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>15.7</v>
+        <v>23.9</v>
       </c>
       <c r="Q81" t="n">
-        <v>44.4</v>
+        <v>47.2</v>
       </c>
       <c r="R81" t="n">
-        <v>55.6</v>
+        <v>52.7</v>
       </c>
       <c r="S81" t="n">
-        <v>64.3</v>
+        <v>44.8</v>
       </c>
       <c r="T81" t="n">
         <v>75</v>
       </c>
       <c r="U81" t="n">
-        <v>28.9</v>
+        <v>19.5</v>
       </c>
       <c r="V81" t="inlineStr">
         <is>
@@ -22951,7 +22955,7 @@
       </c>
       <c r="X81" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y81" t="inlineStr">
@@ -22989,27 +22993,27 @@
       </c>
       <c r="AH81" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI81" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/21, 1 HR</t>
+          <t>Last 7 games: 5/20, 0 HR</t>
         </is>
       </c>
       <c r="AL81" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 9.9% barrel, 6.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 9.3% barrel, 7.5 HR allowed</t>
         </is>
       </c>
       <c r="AM81" t="inlineStr">
@@ -23019,112 +23023,112 @@
       </c>
       <c r="AN81" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>6.86</t>
         </is>
       </c>
       <c r="AO81" t="inlineStr">
         <is>
-          <t>36.78</t>
+          <t>38.06</t>
         </is>
       </c>
       <c r="AP81" t="inlineStr">
         <is>
-          <t>90.47</t>
+          <t>88.38</t>
         </is>
       </c>
       <c r="AQ81" t="inlineStr">
         <is>
-          <t>98.5819</t>
+          <t>99.6134</t>
         </is>
       </c>
       <c r="AR81" t="inlineStr">
         <is>
-          <t>0.2935</t>
+          <t>0.3226</t>
         </is>
       </c>
       <c r="AS81" t="inlineStr">
         <is>
-          <t>0.0848</t>
+          <t>0.0962</t>
         </is>
       </c>
       <c r="AT81" t="inlineStr">
         <is>
-          <t>0.2634</t>
+          <t>0.308</t>
         </is>
       </c>
       <c r="AU81" t="inlineStr">
         <is>
-          <t>68.2</t>
+          <t>73.19</t>
         </is>
       </c>
       <c r="AV81" t="inlineStr">
         <is>
-          <t>3.22</t>
+          <t>30.34</t>
         </is>
       </c>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>32.6</t>
+          <t>41.38</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>24.73</t>
+          <t>25.88</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr">
         <is>
-          <t>2.9</t>
+          <t>4.8</t>
         </is>
       </c>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>0.0635</t>
+          <t>0.1095</t>
         </is>
       </c>
       <c r="BA81" t="inlineStr">
         <is>
-          <t>9.89</t>
+          <t>9.28</t>
         </is>
       </c>
       <c r="BB81" t="inlineStr">
         <is>
-          <t>39.61</t>
+          <t>43.79</t>
         </is>
       </c>
       <c r="BC81" t="inlineStr">
         <is>
-          <t>88.76</t>
+          <t>90.08</t>
         </is>
       </c>
       <c r="BD81" t="inlineStr">
         <is>
-          <t>0.4199</t>
+          <t>0.4423</t>
         </is>
       </c>
       <c r="BE81" t="inlineStr">
         <is>
-          <t>0.1737</t>
+          <t>0.1766</t>
         </is>
       </c>
       <c r="BF81" t="inlineStr">
         <is>
-          <t>27.07</t>
+          <t>22.44</t>
         </is>
       </c>
       <c r="BG81" t="inlineStr">
         <is>
-          <t>In From RF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH81" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>84</t>
         </is>
       </c>
       <c r="BI81" t="inlineStr">
         <is>
-          <t>Rate Field</t>
+          <t>Kauffman Stadium</t>
         </is>
       </c>
       <c r="BJ81" t="inlineStr"/>
@@ -23135,56 +23139,56 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>686555</t>
+          <t>682668</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Isaac Collins</t>
+          <t>Luisangel Acuña</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-06-11T18:10:00Z</t>
+          <t>2026-06-11T23:40:00Z</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Kumar Rocker</t>
+          <t>Martín Pérez</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>677958</t>
+          <t>527048</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L82" t="n">
-        <v>41.2</v>
+        <v>40.7</v>
       </c>
       <c r="M82" t="inlineStr">
         <is>
@@ -23202,22 +23206,22 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>23.9</v>
+        <v>14.9</v>
       </c>
       <c r="Q82" t="n">
-        <v>47.2</v>
+        <v>45.1</v>
       </c>
       <c r="R82" t="n">
-        <v>52.7</v>
+        <v>55.6</v>
       </c>
       <c r="S82" t="n">
-        <v>44.8</v>
+        <v>52.4</v>
       </c>
       <c r="T82" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="U82" t="n">
-        <v>21.5</v>
+        <v>45</v>
       </c>
       <c r="V82" t="inlineStr">
         <is>
@@ -23231,7 +23235,7 @@
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y82" t="inlineStr">
@@ -23269,12 +23273,12 @@
       </c>
       <c r="AH82" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI82" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AJ82" t="inlineStr">
@@ -23284,12 +23288,12 @@
       </c>
       <c r="AK82" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/19, 0 HR</t>
+          <t>Contact streak: 6/12 over last 7 games</t>
         </is>
       </c>
       <c r="AL82" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 9.3% barrel, 7.5 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.9% barrel, 6.0 HR allowed</t>
         </is>
       </c>
       <c r="AM82" t="inlineStr">
@@ -23299,112 +23303,112 @@
       </c>
       <c r="AN82" t="inlineStr">
         <is>
-          <t>6.86</t>
+          <t>2.59</t>
         </is>
       </c>
       <c r="AO82" t="inlineStr">
         <is>
-          <t>38.06</t>
+          <t>37.32</t>
         </is>
       </c>
       <c r="AP82" t="inlineStr">
         <is>
-          <t>88.38</t>
+          <t>88.95</t>
         </is>
       </c>
       <c r="AQ82" t="inlineStr">
         <is>
-          <t>99.6134</t>
+          <t>99.7966</t>
         </is>
       </c>
       <c r="AR82" t="inlineStr">
         <is>
-          <t>0.3226</t>
+          <t>0.3074</t>
         </is>
       </c>
       <c r="AS82" t="inlineStr">
         <is>
-          <t>0.0962</t>
+          <t>0.0665</t>
         </is>
       </c>
       <c r="AT82" t="inlineStr">
         <is>
-          <t>0.308</t>
+          <t>0.2717</t>
         </is>
       </c>
       <c r="AU82" t="inlineStr">
         <is>
-          <t>73.19</t>
+          <t>71.68</t>
         </is>
       </c>
       <c r="AV82" t="inlineStr">
         <is>
-          <t>30.34</t>
+          <t>24.71</t>
         </is>
       </c>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>41.38</t>
+          <t>33.06</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>25.88</t>
+          <t>17.56</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ82" t="inlineStr">
         <is>
-          <t>0.1095</t>
+          <t>0.0239</t>
         </is>
       </c>
       <c r="BA82" t="inlineStr">
         <is>
-          <t>9.28</t>
+          <t>9.89</t>
         </is>
       </c>
       <c r="BB82" t="inlineStr">
         <is>
-          <t>43.79</t>
+          <t>39.61</t>
         </is>
       </c>
       <c r="BC82" t="inlineStr">
         <is>
-          <t>90.08</t>
+          <t>88.76</t>
         </is>
       </c>
       <c r="BD82" t="inlineStr">
         <is>
-          <t>0.4423</t>
+          <t>0.4199</t>
         </is>
       </c>
       <c r="BE82" t="inlineStr">
         <is>
-          <t>0.1766</t>
+          <t>0.1737</t>
         </is>
       </c>
       <c r="BF82" t="inlineStr">
         <is>
-          <t>22.44</t>
+          <t>27.07</t>
         </is>
       </c>
       <c r="BG82" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>In From RF</t>
         </is>
       </c>
       <c r="BH82" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>82</t>
         </is>
       </c>
       <c r="BI82" t="inlineStr">
         <is>
-          <t>Kauffman Stadium</t>
+          <t>Rate Field</t>
         </is>
       </c>
       <c r="BJ82" t="inlineStr"/>
@@ -23415,56 +23419,56 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>682668</t>
+          <t>663538</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Luisangel Acuña</t>
+          <t>Nico Hoerner</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>CHC</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-06-11T23:40:00Z</t>
+          <t>2026-06-11T19:10:00Z</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>Martín Pérez</t>
+          <t>Ryan Feltner</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>527048</t>
+          <t>663372</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L83" t="n">
-        <v>40.7</v>
+        <v>40.2</v>
       </c>
       <c r="M83" t="inlineStr">
         <is>
@@ -23478,26 +23482,26 @@
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P83" t="n">
-        <v>14.9</v>
+        <v>9.1</v>
       </c>
       <c r="Q83" t="n">
-        <v>45.1</v>
+        <v>53.8</v>
       </c>
       <c r="R83" t="n">
-        <v>55.6</v>
+        <v>57.2</v>
       </c>
       <c r="S83" t="n">
-        <v>52.4</v>
+        <v>76.2</v>
       </c>
       <c r="T83" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U83" t="n">
-        <v>45</v>
+        <v>10.8</v>
       </c>
       <c r="V83" t="inlineStr">
         <is>
@@ -23511,7 +23515,7 @@
       </c>
       <c r="X83" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y83" t="inlineStr">
@@ -23549,12 +23553,12 @@
       </c>
       <c r="AH83" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI83" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ83" t="inlineStr">
@@ -23564,12 +23568,12 @@
       </c>
       <c r="AK83" t="inlineStr">
         <is>
-          <t>Contact streak: 6/12 over last 7 games</t>
+          <t>Last 7 games: 5/26, 0 HR</t>
         </is>
       </c>
       <c r="AL83" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 9.9% barrel, 6.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 10.0% barrel, 4.7 HR allowed</t>
         </is>
       </c>
       <c r="AM83" t="inlineStr">
@@ -23579,112 +23583,112 @@
       </c>
       <c r="AN83" t="inlineStr">
         <is>
-          <t>2.59</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="AO83" t="inlineStr">
         <is>
-          <t>37.32</t>
+          <t>28.69</t>
         </is>
       </c>
       <c r="AP83" t="inlineStr">
         <is>
-          <t>88.95</t>
+          <t>86.21</t>
         </is>
       </c>
       <c r="AQ83" t="inlineStr">
         <is>
-          <t>99.7966</t>
+          <t>96.1991</t>
         </is>
       </c>
       <c r="AR83" t="inlineStr">
         <is>
-          <t>0.3074</t>
+          <t>0.3819</t>
         </is>
       </c>
       <c r="AS83" t="inlineStr">
         <is>
-          <t>0.0665</t>
+          <t>0.0878</t>
         </is>
       </c>
       <c r="AT83" t="inlineStr">
         <is>
-          <t>0.2717</t>
+          <t>0.3318</t>
         </is>
       </c>
       <c r="AU83" t="inlineStr">
         <is>
-          <t>71.68</t>
+          <t>68.43</t>
         </is>
       </c>
       <c r="AV83" t="inlineStr">
         <is>
-          <t>24.71</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>33.06</t>
+          <t>32.66</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>17.56</t>
+          <t>22.26</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.9</t>
         </is>
       </c>
       <c r="AZ83" t="inlineStr">
         <is>
-          <t>0.0239</t>
+          <t>0.0998</t>
         </is>
       </c>
       <c r="BA83" t="inlineStr">
         <is>
-          <t>9.89</t>
+          <t>9.98</t>
         </is>
       </c>
       <c r="BB83" t="inlineStr">
         <is>
-          <t>39.61</t>
+          <t>42.07</t>
         </is>
       </c>
       <c r="BC83" t="inlineStr">
         <is>
-          <t>88.76</t>
+          <t>89.65</t>
         </is>
       </c>
       <c r="BD83" t="inlineStr">
         <is>
-          <t>0.4199</t>
+          <t>0.4729</t>
         </is>
       </c>
       <c r="BE83" t="inlineStr">
         <is>
-          <t>0.1737</t>
+          <t>0.2157</t>
         </is>
       </c>
       <c r="BF83" t="inlineStr">
         <is>
-          <t>27.07</t>
+          <t>29.72</t>
         </is>
       </c>
       <c r="BG83" t="inlineStr">
         <is>
-          <t>In From RF</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BH83" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI83" t="inlineStr">
         <is>
-          <t>Rate Field</t>
+          <t>Coors Field</t>
         </is>
       </c>
       <c r="BJ83" t="inlineStr"/>
@@ -23695,56 +23699,56 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>663538</t>
+          <t>803011</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Nico Hoerner</t>
+          <t>Sam Antonacci</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>CHC</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-06-11T19:10:00Z</t>
+          <t>2026-06-11T23:40:00Z</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>Ryan Feltner</t>
+          <t>Martín Pérez</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>663372</t>
+          <t>527048</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L84" t="n">
-        <v>40.3</v>
+        <v>39.5</v>
       </c>
       <c r="M84" t="inlineStr">
         <is>
@@ -23762,22 +23766,22 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>9.1</v>
+        <v>24.1</v>
       </c>
       <c r="Q84" t="n">
-        <v>53.8</v>
+        <v>45.1</v>
       </c>
       <c r="R84" t="n">
-        <v>57.2</v>
+        <v>55.6</v>
       </c>
       <c r="S84" t="n">
-        <v>76.2</v>
+        <v>44.8</v>
       </c>
       <c r="T84" t="n">
         <v>50</v>
       </c>
       <c r="U84" t="n">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="V84" t="inlineStr">
         <is>
@@ -23791,7 +23795,7 @@
       </c>
       <c r="X84" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y84" t="inlineStr">
@@ -23812,7 +23816,7 @@
       <c r="AB84" t="inlineStr"/>
       <c r="AC84" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD84" t="inlineStr"/>
@@ -23829,12 +23833,12 @@
       </c>
       <c r="AH84" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI84" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ84" t="inlineStr">
@@ -23844,12 +23848,12 @@
       </c>
       <c r="AK84" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/25, 0 HR</t>
+          <t>Contact streak: 9/27 over last 7 games</t>
         </is>
       </c>
       <c r="AL84" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 10.0% barrel, 4.7 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 9.9% barrel, 6.0 HR allowed</t>
         </is>
       </c>
       <c r="AM84" t="inlineStr">
@@ -23859,112 +23863,112 @@
       </c>
       <c r="AN84" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AO84" t="inlineStr">
         <is>
-          <t>28.69</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="AP84" t="inlineStr">
         <is>
-          <t>86.21</t>
+          <t>87.9</t>
         </is>
       </c>
       <c r="AQ84" t="inlineStr">
         <is>
-          <t>96.1991</t>
+          <t>98.0684</t>
         </is>
       </c>
       <c r="AR84" t="inlineStr">
         <is>
-          <t>0.3819</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="AS84" t="inlineStr">
         <is>
-          <t>0.0878</t>
+          <t>0.124</t>
         </is>
       </c>
       <c r="AT84" t="inlineStr">
         <is>
-          <t>0.3318</t>
+          <t>0.374</t>
         </is>
       </c>
       <c r="AU84" t="inlineStr">
         <is>
-          <t>68.43</t>
+          <t>70.1</t>
         </is>
       </c>
       <c r="AV84" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>32.66</t>
+          <t>28.1</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>22.26</t>
+          <t>20.1</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AZ84" t="inlineStr">
         <is>
-          <t>0.0998</t>
+          <t>0.091</t>
         </is>
       </c>
       <c r="BA84" t="inlineStr">
         <is>
-          <t>9.98</t>
+          <t>9.89</t>
         </is>
       </c>
       <c r="BB84" t="inlineStr">
         <is>
-          <t>42.07</t>
+          <t>39.61</t>
         </is>
       </c>
       <c r="BC84" t="inlineStr">
         <is>
-          <t>89.65</t>
+          <t>88.76</t>
         </is>
       </c>
       <c r="BD84" t="inlineStr">
         <is>
-          <t>0.4729</t>
+          <t>0.4199</t>
         </is>
       </c>
       <c r="BE84" t="inlineStr">
         <is>
-          <t>0.2157</t>
+          <t>0.1737</t>
         </is>
       </c>
       <c r="BF84" t="inlineStr">
         <is>
-          <t>29.72</t>
+          <t>27.07</t>
         </is>
       </c>
       <c r="BG84" t="inlineStr">
         <is>
-          <t>In From CF</t>
+          <t>In From RF</t>
         </is>
       </c>
       <c r="BH84" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>82</t>
         </is>
       </c>
       <c r="BI84" t="inlineStr">
         <is>
-          <t>Coors Field</t>
+          <t>Rate Field</t>
         </is>
       </c>
       <c r="BJ84" t="inlineStr"/>
@@ -24024,7 +24028,7 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>39.5</v>
+        <v>39.4</v>
       </c>
       <c r="M85" t="inlineStr">
         <is>
@@ -24057,7 +24061,7 @@
         <v>50</v>
       </c>
       <c r="U85" t="n">
-        <v>43.2</v>
+        <v>41.2</v>
       </c>
       <c r="V85" t="inlineStr">
         <is>
@@ -24114,7 +24118,7 @@
       </c>
       <c r="AI85" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ85" t="inlineStr">
@@ -24124,7 +24128,7 @@
       </c>
       <c r="AK85" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/21, 1 HR</t>
+          <t>Last 7 games: 6/22, 1 HR</t>
         </is>
       </c>
       <c r="AL85" t="inlineStr">
@@ -24255,56 +24259,56 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>803011</t>
+          <t>807713</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Sam Antonacci</t>
+          <t>Matt Shaw</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>CHC</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-06-11T23:40:00Z</t>
+          <t>2026-06-11T19:10:00Z</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>Martín Pérez</t>
+          <t>Ryan Feltner</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>527048</t>
+          <t>663372</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L86" t="n">
-        <v>39.5</v>
+        <v>39.2</v>
       </c>
       <c r="M86" t="inlineStr">
         <is>
@@ -24322,46 +24326,38 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>24.1</v>
+        <v>17.7</v>
       </c>
       <c r="Q86" t="n">
-        <v>45.1</v>
+        <v>53.8</v>
       </c>
       <c r="R86" t="n">
-        <v>55.6</v>
+        <v>57.2</v>
       </c>
       <c r="S86" t="n">
-        <v>44.8</v>
+        <v>52.4</v>
       </c>
       <c r="T86" t="n">
         <v>50</v>
       </c>
       <c r="U86" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="V86" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W86" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="X86" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+      <c r="W86" t="inlineStr"/>
+      <c r="X86" t="inlineStr"/>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -24369,10 +24365,14 @@
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB86" t="inlineStr"/>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>not found on RotoWire</t>
+        </is>
+      </c>
       <c r="AC86" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD86" t="inlineStr"/>
@@ -24389,12 +24389,12 @@
       </c>
       <c r="AH86" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AI86" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AJ86" t="inlineStr">
@@ -24404,12 +24404,12 @@
       </c>
       <c r="AK86" t="inlineStr">
         <is>
-          <t>Contact streak: 9/27 over last 7 games</t>
+          <t>Last 7 games: 0/7, 0 HR</t>
         </is>
       </c>
       <c r="AL86" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 9.9% barrel, 6.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 10.0% barrel, 4.7 HR allowed</t>
         </is>
       </c>
       <c r="AM86" t="inlineStr">
@@ -24419,112 +24419,112 @@
       </c>
       <c r="AN86" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>5.6</t>
         </is>
       </c>
       <c r="AO86" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>33.32</t>
         </is>
       </c>
       <c r="AP86" t="inlineStr">
         <is>
-          <t>87.9</t>
+          <t>85.81</t>
         </is>
       </c>
       <c r="AQ86" t="inlineStr">
         <is>
-          <t>98.0684</t>
+          <t>96.9848</t>
         </is>
       </c>
       <c r="AR86" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.3785</t>
         </is>
       </c>
       <c r="AS86" t="inlineStr">
         <is>
-          <t>0.124</t>
+          <t>0.1317</t>
         </is>
       </c>
       <c r="AT86" t="inlineStr">
         <is>
-          <t>0.374</t>
+          <t>0.2985</t>
         </is>
       </c>
       <c r="AU86" t="inlineStr">
         <is>
-          <t>70.1</t>
+          <t>68.55</t>
         </is>
       </c>
       <c r="AV86" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>6.46</t>
         </is>
       </c>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>28.1</t>
+          <t>34.18</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>20.1</t>
+          <t>22.62</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="AZ86" t="inlineStr">
         <is>
-          <t>0.091</t>
+          <t>0.1596</t>
         </is>
       </c>
       <c r="BA86" t="inlineStr">
         <is>
-          <t>9.89</t>
+          <t>9.98</t>
         </is>
       </c>
       <c r="BB86" t="inlineStr">
         <is>
-          <t>39.61</t>
+          <t>42.07</t>
         </is>
       </c>
       <c r="BC86" t="inlineStr">
         <is>
-          <t>88.76</t>
+          <t>89.65</t>
         </is>
       </c>
       <c r="BD86" t="inlineStr">
         <is>
-          <t>0.4199</t>
+          <t>0.4729</t>
         </is>
       </c>
       <c r="BE86" t="inlineStr">
         <is>
-          <t>0.1737</t>
+          <t>0.2157</t>
         </is>
       </c>
       <c r="BF86" t="inlineStr">
         <is>
-          <t>27.07</t>
+          <t>29.72</t>
         </is>
       </c>
       <c r="BG86" t="inlineStr">
         <is>
-          <t>In From RF</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BH86" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI86" t="inlineStr">
         <is>
-          <t>Rate Field</t>
+          <t>Coors Field</t>
         </is>
       </c>
       <c r="BJ86" t="inlineStr"/>
@@ -25704,7 +25704,7 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>33.6</v>
+        <v>33.5</v>
       </c>
       <c r="M91" t="inlineStr">
         <is>
@@ -25737,7 +25737,7 @@
         <v>80</v>
       </c>
       <c r="U91" t="n">
-        <v>40.3</v>
+        <v>37.3</v>
       </c>
       <c r="V91" t="inlineStr">
         <is>
@@ -25794,7 +25794,7 @@
       </c>
       <c r="AI91" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AJ91" t="inlineStr">
@@ -25804,7 +25804,7 @@
       </c>
       <c r="AK91" t="inlineStr">
         <is>
-          <t>Contact streak: 7/18 over last 7 games</t>
+          <t>Contact streak: 7/19 over last 7 games</t>
         </is>
       </c>
       <c r="AL91" t="inlineStr">
@@ -29061,47 +29061,47 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>571970</t>
+          <t>664023</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Max Muncy</t>
+          <t>Ian Happ</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>CHC</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-06-11T22:40:00Z</t>
+          <t>2026-06-11T19:10:00Z</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Mitch Keller</t>
+          <t>Ryan Feltner</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>656605</t>
+          <t>663372</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -29110,7 +29110,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>62.2</v>
+        <v>62.3</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -29124,26 +29124,26 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Strong Barrel, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>65.7</v>
+        <v>55.2</v>
       </c>
       <c r="Q12" t="n">
-        <v>36.3</v>
+        <v>53.3</v>
       </c>
       <c r="R12" t="n">
-        <v>68.3</v>
+        <v>57.2</v>
       </c>
       <c r="S12" t="n">
-        <v>86.40000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="U12" t="n">
-        <v>45</v>
+        <v>54.4</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
@@ -29157,7 +29157,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
@@ -29195,27 +29195,27 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Contact streak: 10/22 over last 7 games</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.1% barrel, 9.8 HR allowed</t>
+          <t>switch hitter; pitcher baseline 10.0% barrel, 4.7 HR allowed</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
@@ -29225,112 +29225,112 @@
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>16.05</t>
+          <t>13.9</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>49.96</t>
+          <t>46.22</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>91.09</t>
+          <t>90.56</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>102.3127</t>
+          <t>101.9188</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.5369</t>
+          <t>0.4577</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>0.2716</t>
+          <t>0.2322</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>0.3873</t>
+          <t>0.3456</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>71.41</t>
+          <t>71.98</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>12.4</t>
+          <t>20.35</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>53.32</t>
+          <t>43.77</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>34.32</t>
+          <t>33.16</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>15.5</t>
+          <t>17.4</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>0.2431</t>
+          <t>0.2351</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>9.98</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>40.44</t>
+          <t>42.07</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>88.63</t>
+          <t>89.65</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>0.4216</t>
+          <t>0.4729</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
-          <t>0.1493</t>
+          <t>0.2157</t>
         </is>
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>22.09</t>
+          <t>29.72</t>
         </is>
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>Out To LF</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>PNC Park</t>
+          <t>Coors Field</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr"/>
@@ -29341,47 +29341,47 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>664023</t>
+          <t>571970</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ian Happ</t>
+          <t>Max Muncy</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>CHC</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-06-11T19:10:00Z</t>
+          <t>2026-06-11T22:40:00Z</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Ryan Feltner</t>
+          <t>Mitch Keller</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>663372</t>
+          <t>656605</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -29390,7 +29390,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>62</v>
+        <v>62.2</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -29404,26 +29404,26 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>55.2</v>
+        <v>65.7</v>
       </c>
       <c r="Q13" t="n">
-        <v>53.3</v>
+        <v>36.3</v>
       </c>
       <c r="R13" t="n">
-        <v>57.2</v>
+        <v>68.3</v>
       </c>
       <c r="S13" t="n">
-        <v>94.90000000000001</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="U13" t="n">
-        <v>48.7</v>
+        <v>45</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
@@ -29437,7 +29437,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -29475,27 +29475,27 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Contact streak: 10/22 over last 7 games</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 10.0% barrel, 4.7 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.1% barrel, 9.8 HR allowed</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
@@ -29505,112 +29505,112 @@
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>13.9</t>
+          <t>16.05</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>46.22</t>
+          <t>49.96</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>90.56</t>
+          <t>91.09</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>101.9188</t>
+          <t>102.3127</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>0.4577</t>
+          <t>0.5369</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>0.2322</t>
+          <t>0.2716</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>0.3456</t>
+          <t>0.3873</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>71.98</t>
+          <t>71.41</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>20.35</t>
+          <t>12.4</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>43.77</t>
+          <t>53.32</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>33.16</t>
+          <t>34.32</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>17.4</t>
+          <t>15.5</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>0.2351</t>
+          <t>0.2431</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>9.98</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>42.07</t>
+          <t>40.44</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>89.65</t>
+          <t>88.63</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>0.4729</t>
+          <t>0.4216</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
-          <t>0.2157</t>
+          <t>0.1493</t>
         </is>
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>29.72</t>
+          <t>22.09</t>
         </is>
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>In From CF</t>
+          <t>Out To LF</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>84</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
         <is>
-          <t>Coors Field</t>
+          <t>PNC Park</t>
         </is>
       </c>
       <c r="BJ13" t="inlineStr"/>
@@ -29670,7 +29670,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>60.6</v>
+        <v>60.5</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -29703,7 +29703,7 @@
         <v>80</v>
       </c>
       <c r="U14" t="n">
-        <v>48.3</v>
+        <v>46.5</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
@@ -29760,7 +29760,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
@@ -29770,7 +29770,7 @@
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Contact streak: 8/25 over last 7 games</t>
+          <t>Last 7 games: 8/26, 1 HR</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
@@ -31021,47 +31021,47 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>518692</t>
+          <t>695600</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Freddie Freeman</t>
+          <t>Carter Jensen</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-06-11T22:40:00Z</t>
+          <t>2026-06-11T18:10:00Z</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Mitch Keller</t>
+          <t>Kumar Rocker</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>656605</t>
+          <t>677958</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -31088,22 +31088,22 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>49.4</v>
+        <v>53.5</v>
       </c>
       <c r="Q19" t="n">
-        <v>36.3</v>
+        <v>48</v>
       </c>
       <c r="R19" t="n">
-        <v>68.3</v>
+        <v>52.7</v>
       </c>
       <c r="S19" t="n">
-        <v>96.59999999999999</v>
+        <v>93.2</v>
       </c>
       <c r="T19" t="n">
         <v>80</v>
       </c>
       <c r="U19" t="n">
-        <v>53.9</v>
+        <v>28.1</v>
       </c>
       <c r="V19" t="inlineStr">
         <is>
@@ -31117,7 +31117,7 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
@@ -31155,12 +31155,12 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
@@ -31170,12 +31170,12 @@
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Contact streak: 10/28 over last 7 games</t>
+          <t>Last 7 games: 5/27, 1 HR</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.1% barrel, 9.8 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.3% barrel, 7.5 HR allowed</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
@@ -31185,7 +31185,7 @@
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>11.38</t>
+          <t>13.45</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
@@ -31195,92 +31195,92 @@
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>90.97</t>
+          <t>91.9</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>101.0569</t>
+          <t>102.7456</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>0.4887</t>
+          <t>0.4279</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
         <is>
-          <t>0.2126</t>
+          <t>0.1927</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>0.3675</t>
+          <t>0.3231</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>70.11</t>
+          <t>74.48</t>
         </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>7.56</t>
+          <t>42.88</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>35.77</t>
+          <t>40.58</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>28.75</t>
+          <t>31.61</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>14.2</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>0.2014</t>
+          <t>0.1933</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>9.28</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>40.44</t>
+          <t>43.79</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>88.63</t>
+          <t>90.08</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>0.4216</t>
+          <t>0.4423</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
-          <t>0.1493</t>
+          <t>0.1766</t>
         </is>
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>22.09</t>
+          <t>22.44</t>
         </is>
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>Out To LF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
@@ -31290,7 +31290,7 @@
       </c>
       <c r="BI19" t="inlineStr">
         <is>
-          <t>PNC Park</t>
+          <t>Kauffman Stadium</t>
         </is>
       </c>
       <c r="BJ19" t="inlineStr"/>
@@ -31301,47 +31301,47 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>695600</t>
+          <t>518692</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Carter Jensen</t>
+          <t>Freddie Freeman</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-06-11T18:10:00Z</t>
+          <t>2026-06-11T22:40:00Z</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Kumar Rocker</t>
+          <t>Mitch Keller</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>677958</t>
+          <t>656605</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -31350,7 +31350,7 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>58.5</v>
+        <v>58.7</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
@@ -31368,22 +31368,22 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>53.5</v>
+        <v>49.4</v>
       </c>
       <c r="Q20" t="n">
-        <v>48</v>
+        <v>36.3</v>
       </c>
       <c r="R20" t="n">
-        <v>52.7</v>
+        <v>68.3</v>
       </c>
       <c r="S20" t="n">
-        <v>93.2</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T20" t="n">
         <v>80</v>
       </c>
       <c r="U20" t="n">
-        <v>23.4</v>
+        <v>53.9</v>
       </c>
       <c r="V20" t="inlineStr">
         <is>
@@ -31397,7 +31397,7 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
@@ -31435,12 +31435,12 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
@@ -31450,12 +31450,12 @@
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/26, 1 HR</t>
+          <t>Contact streak: 10/28 over last 7 games</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 9.3% barrel, 7.5 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.1% barrel, 9.8 HR allowed</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
@@ -31465,7 +31465,7 @@
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>13.45</t>
+          <t>11.38</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
@@ -31475,92 +31475,92 @@
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>91.9</t>
+          <t>90.97</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>102.7456</t>
+          <t>101.0569</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>0.4279</t>
+          <t>0.4887</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
         <is>
-          <t>0.1927</t>
+          <t>0.2126</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>0.3231</t>
+          <t>0.3675</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
         <is>
-          <t>74.48</t>
+          <t>70.11</t>
         </is>
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>42.88</t>
+          <t>7.56</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>40.58</t>
+          <t>35.77</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>31.61</t>
+          <t>28.75</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>14.2</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>0.1933</t>
+          <t>0.2014</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>9.28</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>43.79</t>
+          <t>40.44</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>90.08</t>
+          <t>88.63</t>
         </is>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>0.4423</t>
+          <t>0.4216</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
-          <t>0.1766</t>
+          <t>0.1493</t>
         </is>
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>22.44</t>
+          <t>22.09</t>
         </is>
       </c>
       <c r="BG20" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>Out To LF</t>
         </is>
       </c>
       <c r="BH20" t="inlineStr">
@@ -31570,7 +31570,7 @@
       </c>
       <c r="BI20" t="inlineStr">
         <is>
-          <t>Kauffman Stadium</t>
+          <t>PNC Park</t>
         </is>
       </c>
       <c r="BJ20" t="inlineStr"/>
@@ -31663,7 +31663,7 @@
         <v>50</v>
       </c>
       <c r="U21" t="n">
-        <v>16.6</v>
+        <v>15.3</v>
       </c>
       <c r="V21" t="inlineStr">
         <is>
@@ -31720,7 +31720,7 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
@@ -31730,7 +31730,7 @@
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/26, 0 HR</t>
+          <t>Last 7 games: 6/27, 0 HR</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">

--- a/outputs/hr_rankings.xlsx
+++ b/outputs/hr_rankings.xlsx
@@ -3300,7 +3300,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>62.8</v>
+        <v>62.6</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -3324,7 +3324,7 @@
         <v>39.7</v>
       </c>
       <c r="R11" t="n">
-        <v>68.90000000000001</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="S11" t="n">
         <v>93.2</v>
@@ -3515,7 +3515,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>71</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -8016,7 +8016,7 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>58.4</v>
+        <v>58.3</v>
       </c>
       <c r="M28" t="inlineStr">
         <is>
@@ -8040,7 +8040,7 @@
         <v>33.1</v>
       </c>
       <c r="R28" t="n">
-        <v>68.90000000000001</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="S28" t="n">
         <v>96.59999999999999</v>
@@ -8231,7 +8231,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>71</t>
         </is>
       </c>
       <c r="BI28" t="inlineStr">
@@ -8296,7 +8296,7 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>58.4</v>
+        <v>58.2</v>
       </c>
       <c r="M29" t="inlineStr">
         <is>
@@ -8320,7 +8320,7 @@
         <v>33.1</v>
       </c>
       <c r="R29" t="n">
-        <v>68.90000000000001</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="S29" t="n">
         <v>94.90000000000001</v>
@@ -8511,7 +8511,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>71</t>
         </is>
       </c>
       <c r="BI29" t="inlineStr">
@@ -9919,27 +9919,27 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>682987</t>
+          <t>701398</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Spencer Jones</t>
+          <t>Sal Stewart</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-06-13T19:07:00Z</t>
+          <t>2026-06-13T20:10:00Z</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -9949,17 +9949,17 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Kevin Gausman</t>
+          <t>Michael Soroka</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>592332</t>
+          <t>647336</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -9982,26 +9982,26 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P35" t="n">
-        <v>49.9</v>
+        <v>61.7</v>
       </c>
       <c r="Q35" t="n">
-        <v>39.7</v>
+        <v>33.9</v>
       </c>
       <c r="R35" t="n">
-        <v>68.90000000000001</v>
+        <v>61.3</v>
       </c>
       <c r="S35" t="n">
-        <v>76.2</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T35" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U35" t="n">
-        <v>58.7</v>
+        <v>28.1</v>
       </c>
       <c r="V35" t="inlineStr">
         <is>
@@ -10015,7 +10015,7 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y35" t="inlineStr">
@@ -10036,7 +10036,7 @@
       <c r="AB35" t="inlineStr"/>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD35" t="inlineStr"/>
@@ -10053,12 +10053,12 @@
       </c>
       <c r="AH35" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI35" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ35" t="inlineStr">
@@ -10068,12 +10068,12 @@
       </c>
       <c r="AK35" t="inlineStr">
         <is>
-          <t>Contact streak: 7/18 over last 7 games</t>
+          <t>Last 7 games: 5/27, 1 HR</t>
         </is>
       </c>
       <c r="AL35" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.4% barrel, 12.6 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.6% barrel, 7.8 HR allowed</t>
         </is>
       </c>
       <c r="AM35" t="inlineStr">
@@ -10083,112 +10083,112 @@
       </c>
       <c r="AN35" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>15.66</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>44.17</t>
         </is>
       </c>
       <c r="AP35" t="inlineStr">
         <is>
-          <t>98.3</t>
+          <t>92.04</t>
         </is>
       </c>
       <c r="AQ35" t="inlineStr">
         <is>
-          <t>105.6184</t>
+          <t>101.5658</t>
         </is>
       </c>
       <c r="AR35" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.5189</t>
         </is>
       </c>
       <c r="AS35" t="inlineStr">
         <is>
-          <t>0.159</t>
+          <t>0.253</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr">
         <is>
-          <t>0.283</t>
+          <t>0.3714</t>
         </is>
       </c>
       <c r="AU35" t="inlineStr">
         <is>
-          <t>77.7</t>
+          <t>72.24</t>
         </is>
       </c>
       <c r="AV35" t="inlineStr">
         <is>
-          <t>77.7</t>
+          <t>26.65</t>
         </is>
       </c>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>36.68</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>35.0</t>
+          <t>30.83</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>10.6</t>
         </is>
       </c>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>0.105</t>
+          <t>0.2291</t>
         </is>
       </c>
       <c r="BA35" t="inlineStr">
         <is>
-          <t>8.36</t>
+          <t>7.61</t>
         </is>
       </c>
       <c r="BB35" t="inlineStr">
         <is>
-          <t>38.81</t>
+          <t>35.43</t>
         </is>
       </c>
       <c r="BC35" t="inlineStr">
         <is>
-          <t>88.46</t>
+          <t>88.15</t>
         </is>
       </c>
       <c r="BD35" t="inlineStr">
         <is>
-          <t>0.3993</t>
+          <t>0.3895</t>
         </is>
       </c>
       <c r="BE35" t="inlineStr">
         <is>
-          <t>0.1592</t>
+          <t>0.1497</t>
         </is>
       </c>
       <c r="BF35" t="inlineStr">
         <is>
-          <t>25.88</t>
+          <t>27.8</t>
         </is>
       </c>
       <c r="BG35" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>81</t>
         </is>
       </c>
       <c r="BI35" t="inlineStr">
         <is>
-          <t>Rogers Centre</t>
+          <t>Great American Ball Park</t>
         </is>
       </c>
       <c r="BJ35" t="inlineStr"/>
@@ -10199,27 +10199,27 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>701398</t>
+          <t>682987</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Sal Stewart</t>
+          <t>Spencer Jones</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-06-13T20:10:00Z</t>
+          <t>2026-06-13T19:07:00Z</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -10229,17 +10229,17 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Michael Soroka</t>
+          <t>Kevin Gausman</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>647336</t>
+          <t>592332</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -10248,7 +10248,7 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>57.1</v>
+        <v>57</v>
       </c>
       <c r="M36" t="inlineStr">
         <is>
@@ -10262,26 +10262,26 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P36" t="n">
-        <v>61.7</v>
+        <v>49.9</v>
       </c>
       <c r="Q36" t="n">
-        <v>33.9</v>
+        <v>39.7</v>
       </c>
       <c r="R36" t="n">
-        <v>61.3</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="S36" t="n">
-        <v>96.59999999999999</v>
+        <v>76.2</v>
       </c>
       <c r="T36" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U36" t="n">
-        <v>28.1</v>
+        <v>58.7</v>
       </c>
       <c r="V36" t="inlineStr">
         <is>
@@ -10295,7 +10295,7 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y36" t="inlineStr">
@@ -10316,7 +10316,7 @@
       <c r="AB36" t="inlineStr"/>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD36" t="inlineStr"/>
@@ -10333,12 +10333,12 @@
       </c>
       <c r="AH36" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI36" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AJ36" t="inlineStr">
@@ -10348,12 +10348,12 @@
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/27, 1 HR</t>
+          <t>Contact streak: 7/18 over last 7 games</t>
         </is>
       </c>
       <c r="AL36" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.6% barrel, 7.8 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.4% barrel, 12.6 HR allowed</t>
         </is>
       </c>
       <c r="AM36" t="inlineStr">
@@ -10363,112 +10363,112 @@
       </c>
       <c r="AN36" t="inlineStr">
         <is>
-          <t>15.66</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>44.17</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AP36" t="inlineStr">
         <is>
-          <t>92.04</t>
+          <t>98.3</t>
         </is>
       </c>
       <c r="AQ36" t="inlineStr">
         <is>
-          <t>101.5658</t>
+          <t>105.6184</t>
         </is>
       </c>
       <c r="AR36" t="inlineStr">
         <is>
-          <t>0.5189</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="AS36" t="inlineStr">
         <is>
-          <t>0.253</t>
+          <t>0.159</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr">
         <is>
-          <t>0.3714</t>
+          <t>0.283</t>
         </is>
       </c>
       <c r="AU36" t="inlineStr">
         <is>
-          <t>72.24</t>
+          <t>77.7</t>
         </is>
       </c>
       <c r="AV36" t="inlineStr">
         <is>
-          <t>26.65</t>
+          <t>77.7</t>
         </is>
       </c>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>36.68</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>30.83</t>
+          <t>35.0</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">
         <is>
-          <t>10.6</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>0.2291</t>
+          <t>0.105</t>
         </is>
       </c>
       <c r="BA36" t="inlineStr">
         <is>
-          <t>7.61</t>
+          <t>8.36</t>
         </is>
       </c>
       <c r="BB36" t="inlineStr">
         <is>
-          <t>35.43</t>
+          <t>38.81</t>
         </is>
       </c>
       <c r="BC36" t="inlineStr">
         <is>
-          <t>88.15</t>
+          <t>88.46</t>
         </is>
       </c>
       <c r="BD36" t="inlineStr">
         <is>
-          <t>0.3895</t>
+          <t>0.3993</t>
         </is>
       </c>
       <c r="BE36" t="inlineStr">
         <is>
-          <t>0.1497</t>
+          <t>0.1592</t>
         </is>
       </c>
       <c r="BF36" t="inlineStr">
         <is>
-          <t>27.8</t>
+          <t>25.88</t>
         </is>
       </c>
       <c r="BG36" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>71</t>
         </is>
       </c>
       <c r="BI36" t="inlineStr">
         <is>
-          <t>Great American Ball Park</t>
+          <t>Rogers Centre</t>
         </is>
       </c>
       <c r="BJ36" t="inlineStr"/>
@@ -14436,7 +14436,7 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>55.4</v>
+        <v>55.3</v>
       </c>
       <c r="M51" t="inlineStr">
         <is>
@@ -14460,7 +14460,7 @@
         <v>39.7</v>
       </c>
       <c r="R51" t="n">
-        <v>68.90000000000001</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="S51" t="n">
         <v>96.59999999999999</v>
@@ -14651,7 +14651,7 @@
       </c>
       <c r="BH51" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>71</t>
         </is>
       </c>
       <c r="BI51" t="inlineStr">
@@ -15227,27 +15227,27 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>665862</t>
+          <t>702616</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Jazz Chisholm Jr.</t>
+          <t>Jackson Holliday</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-06-13T19:07:00Z</t>
+          <t>2026-06-13T20:05:00Z</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -15257,17 +15257,17 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Kevin Gausman</t>
+          <t>Randy Vásquez</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>592332</t>
+          <t>681190</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -15294,22 +15294,22 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>40.8</v>
+        <v>45.6</v>
       </c>
       <c r="Q54" t="n">
-        <v>39.7</v>
+        <v>69.5</v>
       </c>
       <c r="R54" t="n">
-        <v>68.90000000000001</v>
+        <v>47.6</v>
       </c>
       <c r="S54" t="n">
-        <v>86.40000000000001</v>
+        <v>52.4</v>
       </c>
       <c r="T54" t="n">
         <v>80</v>
       </c>
       <c r="U54" t="n">
-        <v>43.7</v>
+        <v>28.9</v>
       </c>
       <c r="V54" t="inlineStr">
         <is>
@@ -15318,30 +15318,34 @@
       </c>
       <c r="W54" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X54" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y54" t="inlineStr">
+      <c r="Z54" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB54" t="inlineStr"/>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>RotoWire not confirmed; order MLB 8 vs RotoWire 9</t>
+        </is>
+      </c>
       <c r="AC54" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -15366,22 +15370,22 @@
       </c>
       <c r="AI54" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK54" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 4/21, 1 HR</t>
         </is>
       </c>
       <c r="AL54" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.4% barrel, 12.6 HR allowed</t>
+          <t>platoon edge; pitcher baseline 12.7% barrel, 11.8 HR allowed</t>
         </is>
       </c>
       <c r="AM54" t="inlineStr">
@@ -15391,112 +15395,112 @@
       </c>
       <c r="AN54" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>12.98</t>
         </is>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
-          <t>40.92</t>
+          <t>42.69</t>
         </is>
       </c>
       <c r="AP54" t="inlineStr">
         <is>
-          <t>89.63</t>
+          <t>88.87</t>
         </is>
       </c>
       <c r="AQ54" t="inlineStr">
         <is>
-          <t>100.103</t>
+          <t>99.7498</t>
         </is>
       </c>
       <c r="AR54" t="inlineStr">
         <is>
-          <t>0.3984</t>
+          <t>0.4341</t>
         </is>
       </c>
       <c r="AS54" t="inlineStr">
         <is>
-          <t>0.1791</t>
+          <t>0.1952</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr">
         <is>
-          <t>0.3096</t>
+          <t>0.3336</t>
         </is>
       </c>
       <c r="AU54" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>70.46</t>
         </is>
       </c>
       <c r="AV54" t="inlineStr">
         <is>
-          <t>32.59</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>52.05</t>
+          <t>36.04</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>31.03</t>
+          <t>31.89</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
         <is>
-          <t>15.6</t>
+          <t>7.2</t>
         </is>
       </c>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>0.1928</t>
+          <t>0.1694</t>
         </is>
       </c>
       <c r="BA54" t="inlineStr">
         <is>
-          <t>8.36</t>
+          <t>12.72</t>
         </is>
       </c>
       <c r="BB54" t="inlineStr">
         <is>
-          <t>38.81</t>
+          <t>44.69</t>
         </is>
       </c>
       <c r="BC54" t="inlineStr">
         <is>
-          <t>88.46</t>
+          <t>90.64</t>
         </is>
       </c>
       <c r="BD54" t="inlineStr">
         <is>
-          <t>0.3993</t>
+          <t>0.5286</t>
         </is>
       </c>
       <c r="BE54" t="inlineStr">
         <is>
-          <t>0.1592</t>
+          <t>0.2378</t>
         </is>
       </c>
       <c r="BF54" t="inlineStr">
         <is>
-          <t>25.88</t>
+          <t>29.51</t>
         </is>
       </c>
       <c r="BG54" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>In From LF</t>
         </is>
       </c>
       <c r="BH54" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>85</t>
         </is>
       </c>
       <c r="BI54" t="inlineStr">
         <is>
-          <t>Rogers Centre</t>
+          <t>Oriole Park at Camden Yards</t>
         </is>
       </c>
       <c r="BJ54" t="inlineStr"/>
@@ -15507,52 +15511,52 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>702616</t>
+          <t>691016</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Jackson Holliday</t>
+          <t>Tyler Soderstrom</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-06-13T20:05:00Z</t>
+          <t>2026-06-14T02:05:00Z</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Randy Vásquez</t>
+          <t>Kyle Freeland</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>681190</t>
+          <t>607536</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L55" t="n">
@@ -15570,60 +15574,60 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>Strong Barrel, Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P55" t="n">
-        <v>45.6</v>
+        <v>46.7</v>
       </c>
       <c r="Q55" t="n">
-        <v>69.5</v>
+        <v>59.2</v>
       </c>
       <c r="R55" t="n">
-        <v>47.6</v>
+        <v>27.6</v>
       </c>
       <c r="S55" t="n">
-        <v>52.4</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="T55" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U55" t="n">
-        <v>28.9</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="V55" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W55" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X55" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y55" t="inlineStr">
+      <c r="Z55" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>RotoWire not confirmed; order MLB 8 vs RotoWire 9</t>
+          <t>lineup projected / unconfirmed</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
@@ -15645,27 +15649,27 @@
       </c>
       <c r="AH55" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI55" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/21, 1 HR</t>
+          <t>Hot streak: 3 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL55" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 12.7% barrel, 11.8 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 9.6% barrel, 15.7 HR allowed</t>
         </is>
       </c>
       <c r="AM55" t="inlineStr">
@@ -15675,112 +15679,104 @@
       </c>
       <c r="AN55" t="inlineStr">
         <is>
-          <t>12.98</t>
+          <t>11.05</t>
         </is>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
-          <t>42.69</t>
+          <t>46.51</t>
         </is>
       </c>
       <c r="AP55" t="inlineStr">
         <is>
-          <t>88.87</t>
+          <t>90.41</t>
         </is>
       </c>
       <c r="AQ55" t="inlineStr">
         <is>
-          <t>99.7498</t>
+          <t>101.9879</t>
         </is>
       </c>
       <c r="AR55" t="inlineStr">
         <is>
-          <t>0.4341</t>
+          <t>0.4332</t>
         </is>
       </c>
       <c r="AS55" t="inlineStr">
         <is>
-          <t>0.1952</t>
+          <t>0.1827</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr">
         <is>
-          <t>0.3336</t>
+          <t>0.3361</t>
         </is>
       </c>
       <c r="AU55" t="inlineStr">
         <is>
-          <t>70.46</t>
+          <t>74.14</t>
         </is>
       </c>
       <c r="AV55" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>40.63</t>
         </is>
       </c>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>36.04</t>
+          <t>36.07</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>31.89</t>
+          <t>27.7</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
         <is>
-          <t>7.2</t>
+          <t>15.2</t>
         </is>
       </c>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>0.1694</t>
+          <t>0.2148</t>
         </is>
       </c>
       <c r="BA55" t="inlineStr">
         <is>
-          <t>12.72</t>
+          <t>9.61</t>
         </is>
       </c>
       <c r="BB55" t="inlineStr">
         <is>
-          <t>44.69</t>
+          <t>45.06</t>
         </is>
       </c>
       <c r="BC55" t="inlineStr">
         <is>
-          <t>90.64</t>
+          <t>90.89</t>
         </is>
       </c>
       <c r="BD55" t="inlineStr">
         <is>
-          <t>0.5286</t>
+          <t>0.5038</t>
         </is>
       </c>
       <c r="BE55" t="inlineStr">
         <is>
-          <t>0.2378</t>
+          <t>0.2001</t>
         </is>
       </c>
       <c r="BF55" t="inlineStr">
         <is>
-          <t>29.51</t>
-        </is>
-      </c>
-      <c r="BG55" t="inlineStr">
-        <is>
-          <t>In From LF</t>
-        </is>
-      </c>
-      <c r="BH55" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
+          <t>28.66</t>
+        </is>
+      </c>
+      <c r="BG55" t="inlineStr"/>
+      <c r="BH55" t="inlineStr"/>
       <c r="BI55" t="inlineStr">
         <is>
-          <t>Oriole Park at Camden Yards</t>
+          <t>Las Vegas Ballpark</t>
         </is>
       </c>
       <c r="BJ55" t="inlineStr"/>
@@ -15791,56 +15787,56 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>691016</t>
+          <t>680776</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Tyler Soderstrom</t>
+          <t>Jarren Duran</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-06-14T02:05:00Z</t>
+          <t>2026-06-13T20:10:00Z</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Kyle Freeland</t>
+          <t>Jacob deGrom</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>607536</t>
+          <t>594798</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L56" t="n">
-        <v>54.8</v>
+        <v>54.7</v>
       </c>
       <c r="M56" t="inlineStr">
         <is>
@@ -15854,62 +15850,58 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Hot Hitter/Streak</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P56" t="n">
-        <v>46.7</v>
+        <v>41.1</v>
       </c>
       <c r="Q56" t="n">
-        <v>59.2</v>
+        <v>55.3</v>
       </c>
       <c r="R56" t="n">
-        <v>27.6</v>
+        <v>56.2</v>
       </c>
       <c r="S56" t="n">
-        <v>90.40000000000001</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T56" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U56" t="n">
-        <v>77.90000000000001</v>
+        <v>2.7</v>
       </c>
       <c r="V56" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W56" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X56" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y56" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr"/>
       <c r="AC56" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -15929,134 +15921,142 @@
       </c>
       <c r="AH56" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI56" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK56" t="inlineStr">
         <is>
-          <t>Hot streak: 3 HR in last 7 games</t>
+          <t>Last 7 games: 4/29, 0 HR</t>
         </is>
       </c>
       <c r="AL56" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 9.6% barrel, 15.7 HR allowed</t>
+          <t>platoon edge; pitcher baseline 10.1% barrel, 16.9 HR allowed</t>
         </is>
       </c>
       <c r="AM56" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN56" t="inlineStr">
         <is>
-          <t>11.05</t>
+          <t>10.68</t>
         </is>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
-          <t>46.51</t>
+          <t>41.97</t>
         </is>
       </c>
       <c r="AP56" t="inlineStr">
         <is>
-          <t>90.41</t>
+          <t>90.82</t>
         </is>
       </c>
       <c r="AQ56" t="inlineStr">
         <is>
-          <t>101.9879</t>
+          <t>102.2729</t>
         </is>
       </c>
       <c r="AR56" t="inlineStr">
         <is>
-          <t>0.4332</t>
+          <t>0.3904</t>
         </is>
       </c>
       <c r="AS56" t="inlineStr">
         <is>
-          <t>0.1827</t>
+          <t>0.1564</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr">
         <is>
-          <t>0.3361</t>
+          <t>0.3029</t>
         </is>
       </c>
       <c r="AU56" t="inlineStr">
         <is>
-          <t>74.14</t>
+          <t>75.15</t>
         </is>
       </c>
       <c r="AV56" t="inlineStr">
         <is>
-          <t>40.63</t>
+          <t>52.4</t>
         </is>
       </c>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>36.07</t>
+          <t>40.58</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>27.7</t>
+          <t>22.51</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr">
         <is>
-          <t>15.2</t>
+          <t>11.8</t>
         </is>
       </c>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>0.2148</t>
+          <t>0.1748</t>
         </is>
       </c>
       <c r="BA56" t="inlineStr">
         <is>
-          <t>9.61</t>
+          <t>10.07</t>
         </is>
       </c>
       <c r="BB56" t="inlineStr">
         <is>
-          <t>45.06</t>
+          <t>43.93</t>
         </is>
       </c>
       <c r="BC56" t="inlineStr">
         <is>
-          <t>90.89</t>
+          <t>90.87</t>
         </is>
       </c>
       <c r="BD56" t="inlineStr">
         <is>
-          <t>0.5038</t>
+          <t>0.4134</t>
         </is>
       </c>
       <c r="BE56" t="inlineStr">
         <is>
-          <t>0.2001</t>
+          <t>0.1826</t>
         </is>
       </c>
       <c r="BF56" t="inlineStr">
         <is>
-          <t>28.66</t>
-        </is>
-      </c>
-      <c r="BG56" t="inlineStr"/>
-      <c r="BH56" t="inlineStr"/>
+          <t>32.12</t>
+        </is>
+      </c>
+      <c r="BG56" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH56" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
       <c r="BI56" t="inlineStr">
         <is>
-          <t>Las Vegas Ballpark</t>
+          <t>Fenway Park</t>
         </is>
       </c>
       <c r="BJ56" t="inlineStr"/>
@@ -16067,27 +16067,27 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>680776</t>
+          <t>665862</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Jarren Duran</t>
+          <t>Jazz Chisholm Jr.</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-06-13T20:10:00Z</t>
+          <t>2026-06-13T19:07:00Z</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -16102,12 +16102,12 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Jacob deGrom</t>
+          <t>Kevin Gausman</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>594798</t>
+          <t>592332</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -16116,7 +16116,7 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>54.7</v>
+        <v>54.6</v>
       </c>
       <c r="M57" t="inlineStr">
         <is>
@@ -16134,13 +16134,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>41.1</v>
+        <v>40.8</v>
       </c>
       <c r="Q57" t="n">
-        <v>55.3</v>
+        <v>39.7</v>
       </c>
       <c r="R57" t="n">
-        <v>56.2</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="S57" t="n">
         <v>86.40000000000001</v>
@@ -16149,7 +16149,7 @@
         <v>80</v>
       </c>
       <c r="U57" t="n">
-        <v>2.7</v>
+        <v>43.7</v>
       </c>
       <c r="V57" t="inlineStr">
         <is>
@@ -16206,137 +16206,137 @@
       </c>
       <c r="AI57" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/29, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL57" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 10.1% barrel, 16.9 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.4% barrel, 12.6 HR allowed</t>
         </is>
       </c>
       <c r="AM57" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN57" t="inlineStr">
         <is>
-          <t>10.68</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
-          <t>41.97</t>
+          <t>40.92</t>
         </is>
       </c>
       <c r="AP57" t="inlineStr">
         <is>
-          <t>90.82</t>
+          <t>89.63</t>
         </is>
       </c>
       <c r="AQ57" t="inlineStr">
         <is>
-          <t>102.2729</t>
+          <t>100.103</t>
         </is>
       </c>
       <c r="AR57" t="inlineStr">
         <is>
-          <t>0.3904</t>
+          <t>0.3984</t>
         </is>
       </c>
       <c r="AS57" t="inlineStr">
         <is>
-          <t>0.1564</t>
+          <t>0.1791</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr">
         <is>
-          <t>0.3029</t>
+          <t>0.3096</t>
         </is>
       </c>
       <c r="AU57" t="inlineStr">
         <is>
-          <t>75.15</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="AV57" t="inlineStr">
         <is>
-          <t>52.4</t>
+          <t>32.59</t>
         </is>
       </c>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>40.58</t>
+          <t>52.05</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>22.51</t>
+          <t>31.03</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr">
         <is>
-          <t>11.8</t>
+          <t>15.6</t>
         </is>
       </c>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>0.1748</t>
+          <t>0.1928</t>
         </is>
       </c>
       <c r="BA57" t="inlineStr">
         <is>
-          <t>10.07</t>
+          <t>8.36</t>
         </is>
       </c>
       <c r="BB57" t="inlineStr">
         <is>
-          <t>43.93</t>
+          <t>38.81</t>
         </is>
       </c>
       <c r="BC57" t="inlineStr">
         <is>
-          <t>90.87</t>
+          <t>88.46</t>
         </is>
       </c>
       <c r="BD57" t="inlineStr">
         <is>
-          <t>0.4134</t>
+          <t>0.3993</t>
         </is>
       </c>
       <c r="BE57" t="inlineStr">
         <is>
-          <t>0.1826</t>
+          <t>0.1592</t>
         </is>
       </c>
       <c r="BF57" t="inlineStr">
         <is>
-          <t>32.12</t>
+          <t>25.88</t>
         </is>
       </c>
       <c r="BG57" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BH57" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>71</t>
         </is>
       </c>
       <c r="BI57" t="inlineStr">
         <is>
-          <t>Fenway Park</t>
+          <t>Rogers Centre</t>
         </is>
       </c>
       <c r="BJ57" t="inlineStr"/>
@@ -18352,7 +18352,7 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>53.9</v>
+        <v>53.8</v>
       </c>
       <c r="M65" t="inlineStr">
         <is>
@@ -18376,7 +18376,7 @@
         <v>39.7</v>
       </c>
       <c r="R65" t="n">
-        <v>68.90000000000001</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="S65" t="n">
         <v>94.90000000000001</v>
@@ -18567,7 +18567,7 @@
       </c>
       <c r="BH65" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>71</t>
         </is>
       </c>
       <c r="BI65" t="inlineStr">
@@ -19411,47 +19411,47 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>641857</t>
+          <t>686611</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Ryan McMahon</t>
+          <t>Dylan Crews</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>WSH</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-06-13T19:07:00Z</t>
+          <t>2026-06-13T20:05:00Z</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Kevin Gausman</t>
+          <t>Luis Castillo</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>592332</t>
+          <t>622491</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -19474,58 +19474,62 @@
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>Strong Barrel, Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P69" t="n">
-        <v>50.1</v>
+        <v>46.2</v>
       </c>
       <c r="Q69" t="n">
-        <v>39.7</v>
+        <v>57.8</v>
       </c>
       <c r="R69" t="n">
-        <v>68.90000000000001</v>
+        <v>28.2</v>
       </c>
       <c r="S69" t="n">
-        <v>52.4</v>
+        <v>95.5</v>
       </c>
       <c r="T69" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U69" t="n">
-        <v>47.2</v>
+        <v>41.7</v>
       </c>
       <c r="V69" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W69" t="inlineStr">
+      <c r="Z69" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X69" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y69" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z69" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB69" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC69" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -19545,27 +19549,27 @@
       </c>
       <c r="AH69" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI69" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/16, 1 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL69" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.4% barrel, 12.6 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 10.8% barrel, 12.5 HR allowed</t>
         </is>
       </c>
       <c r="AM69" t="inlineStr">
@@ -19575,112 +19579,104 @@
       </c>
       <c r="AN69" t="inlineStr">
         <is>
-          <t>11.19</t>
+          <t>10.08</t>
         </is>
       </c>
       <c r="AO69" t="inlineStr">
         <is>
-          <t>50.78</t>
+          <t>44.86</t>
         </is>
       </c>
       <c r="AP69" t="inlineStr">
         <is>
-          <t>91.69</t>
+          <t>91.03</t>
         </is>
       </c>
       <c r="AQ69" t="inlineStr">
         <is>
-          <t>102.2341</t>
+          <t>101.8356</t>
         </is>
       </c>
       <c r="AR69" t="inlineStr">
         <is>
-          <t>0.398</t>
+          <t>0.4476</t>
         </is>
       </c>
       <c r="AS69" t="inlineStr">
         <is>
-          <t>0.1765</t>
+          <t>0.1916</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr">
         <is>
-          <t>0.3024</t>
+          <t>0.3287</t>
         </is>
       </c>
       <c r="AU69" t="inlineStr">
         <is>
-          <t>74.49</t>
+          <t>73.86</t>
         </is>
       </c>
       <c r="AV69" t="inlineStr">
         <is>
-          <t>47.17</t>
+          <t>36.93</t>
         </is>
       </c>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>37.35</t>
+          <t>34.5</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>32.94</t>
+          <t>27.63</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr">
         <is>
-          <t>10.9</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>0.1537</t>
+          <t>0.1377</t>
         </is>
       </c>
       <c r="BA69" t="inlineStr">
         <is>
-          <t>8.36</t>
+          <t>10.82</t>
         </is>
       </c>
       <c r="BB69" t="inlineStr">
         <is>
-          <t>38.81</t>
+          <t>47.03</t>
         </is>
       </c>
       <c r="BC69" t="inlineStr">
         <is>
-          <t>88.46</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="BD69" t="inlineStr">
         <is>
-          <t>0.3993</t>
+          <t>0.439</t>
         </is>
       </c>
       <c r="BE69" t="inlineStr">
         <is>
-          <t>0.1592</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="BF69" t="inlineStr">
         <is>
-          <t>25.88</t>
-        </is>
-      </c>
-      <c r="BG69" t="inlineStr">
-        <is>
-          <t>Out To RF</t>
-        </is>
-      </c>
-      <c r="BH69" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
+          <t>28.21</t>
+        </is>
+      </c>
+      <c r="BG69" t="inlineStr"/>
+      <c r="BH69" t="inlineStr"/>
       <c r="BI69" t="inlineStr">
         <is>
-          <t>Rogers Centre</t>
+          <t>Nationals Park</t>
         </is>
       </c>
       <c r="BJ69" t="inlineStr"/>
@@ -19691,47 +19687,47 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>686611</t>
+          <t>641857</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Dylan Crews</t>
+          <t>Ryan McMahon</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>WSH</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-06-13T20:05:00Z</t>
+          <t>2026-06-13T19:07:00Z</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Luis Castillo</t>
+          <t>Kevin Gausman</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>622491</t>
+          <t>592332</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -19740,7 +19736,7 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>53.3</v>
+        <v>53.1</v>
       </c>
       <c r="M70" t="inlineStr">
         <is>
@@ -19754,62 +19750,58 @@
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P70" t="n">
-        <v>46.2</v>
+        <v>50.1</v>
       </c>
       <c r="Q70" t="n">
-        <v>57.8</v>
+        <v>39.7</v>
       </c>
       <c r="R70" t="n">
-        <v>28.2</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="S70" t="n">
-        <v>95.5</v>
+        <v>52.4</v>
       </c>
       <c r="T70" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U70" t="n">
-        <v>41.7</v>
+        <v>47.2</v>
       </c>
       <c r="V70" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z70" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W70" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X70" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y70" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z70" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB70" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr"/>
       <c r="AC70" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -19829,27 +19821,27 @@
       </c>
       <c r="AH70" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI70" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK70" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 5/16, 1 HR</t>
         </is>
       </c>
       <c r="AL70" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 10.8% barrel, 12.5 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.4% barrel, 12.6 HR allowed</t>
         </is>
       </c>
       <c r="AM70" t="inlineStr">
@@ -19859,104 +19851,112 @@
       </c>
       <c r="AN70" t="inlineStr">
         <is>
-          <t>10.08</t>
+          <t>11.19</t>
         </is>
       </c>
       <c r="AO70" t="inlineStr">
         <is>
-          <t>44.86</t>
+          <t>50.78</t>
         </is>
       </c>
       <c r="AP70" t="inlineStr">
         <is>
-          <t>91.03</t>
+          <t>91.69</t>
         </is>
       </c>
       <c r="AQ70" t="inlineStr">
         <is>
-          <t>101.8356</t>
+          <t>102.2341</t>
         </is>
       </c>
       <c r="AR70" t="inlineStr">
         <is>
-          <t>0.4476</t>
+          <t>0.398</t>
         </is>
       </c>
       <c r="AS70" t="inlineStr">
         <is>
-          <t>0.1916</t>
+          <t>0.1765</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr">
         <is>
-          <t>0.3287</t>
+          <t>0.3024</t>
         </is>
       </c>
       <c r="AU70" t="inlineStr">
         <is>
-          <t>73.86</t>
+          <t>74.49</t>
         </is>
       </c>
       <c r="AV70" t="inlineStr">
         <is>
-          <t>36.93</t>
+          <t>47.17</t>
         </is>
       </c>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>34.5</t>
+          <t>37.35</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>27.63</t>
+          <t>32.94</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>10.9</t>
         </is>
       </c>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>0.1377</t>
+          <t>0.1537</t>
         </is>
       </c>
       <c r="BA70" t="inlineStr">
         <is>
-          <t>10.82</t>
+          <t>8.36</t>
         </is>
       </c>
       <c r="BB70" t="inlineStr">
         <is>
-          <t>47.03</t>
+          <t>38.81</t>
         </is>
       </c>
       <c r="BC70" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>88.46</t>
         </is>
       </c>
       <c r="BD70" t="inlineStr">
         <is>
-          <t>0.439</t>
+          <t>0.3993</t>
         </is>
       </c>
       <c r="BE70" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>0.1592</t>
         </is>
       </c>
       <c r="BF70" t="inlineStr">
         <is>
-          <t>28.21</t>
-        </is>
-      </c>
-      <c r="BG70" t="inlineStr"/>
-      <c r="BH70" t="inlineStr"/>
+          <t>25.88</t>
+        </is>
+      </c>
+      <c r="BG70" t="inlineStr">
+        <is>
+          <t>Out To RF</t>
+        </is>
+      </c>
+      <c r="BH70" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
       <c r="BI70" t="inlineStr">
         <is>
-          <t>Nationals Park</t>
+          <t>Rogers Centre</t>
         </is>
       </c>
       <c r="BJ70" t="inlineStr"/>
@@ -20531,27 +20531,27 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>678218</t>
+          <t>663330</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Brandon Valenzuela</t>
+          <t>Jahmai Jones</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-06-13T19:07:00Z</t>
+          <t>2026-06-13T20:10:00Z</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -20561,22 +20561,22 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Cam Schlittler</t>
+          <t>Joey Cantillo</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>693645</t>
+          <t>676282</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L73" t="n">
@@ -20594,61 +20594,65 @@
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>Platoon Edge, Hot Hitter/Streak</t>
+          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P73" t="n">
-        <v>38.1</v>
+        <v>48.8</v>
       </c>
       <c r="Q73" t="n">
-        <v>32.5</v>
+        <v>42</v>
       </c>
       <c r="R73" t="n">
-        <v>68.90000000000001</v>
+        <v>53.6</v>
       </c>
       <c r="S73" t="n">
-        <v>76.2</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T73" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="U73" t="n">
-        <v>91.5</v>
+        <v>0</v>
       </c>
       <c r="V73" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W73" t="inlineStr">
+      <c r="Z73" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X73" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y73" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z73" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB73" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD73" t="inlineStr"/>
@@ -20665,142 +20669,142 @@
       </c>
       <c r="AH73" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AI73" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
         <is>
-          <t>Hot streak: 3 HR in last 7 games</t>
+          <t>Last 7 games: 0/11, 0 HR</t>
         </is>
       </c>
       <c r="AL73" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 7.4% barrel, 5.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.7% barrel, 10.7 HR allowed</t>
         </is>
       </c>
       <c r="AM73" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN73" t="inlineStr">
         <is>
-          <t>9.3</t>
+          <t>10.6</t>
         </is>
       </c>
       <c r="AO73" t="inlineStr">
         <is>
-          <t>37.1</t>
+          <t>47.79</t>
         </is>
       </c>
       <c r="AP73" t="inlineStr">
         <is>
-          <t>89.3</t>
+          <t>91.29</t>
         </is>
       </c>
       <c r="AQ73" t="inlineStr">
         <is>
-          <t>99.4131</t>
+          <t>102.0909</t>
         </is>
       </c>
       <c r="AR73" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.449</t>
         </is>
       </c>
       <c r="AS73" t="inlineStr">
         <is>
-          <t>0.186</t>
+          <t>0.1954</t>
         </is>
       </c>
       <c r="AT73" t="inlineStr">
         <is>
-          <t>0.349</t>
+          <t>0.3423</t>
         </is>
       </c>
       <c r="AU73" t="inlineStr">
         <is>
-          <t>72.6</t>
+          <t>72.97</t>
         </is>
       </c>
       <c r="AV73" t="inlineStr">
         <is>
-          <t>23.3</t>
+          <t>32.98</t>
         </is>
       </c>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>47.66</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>25.8</t>
+          <t>29.88</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>0.205</t>
+          <t>0.1503</t>
         </is>
       </c>
       <c r="BA73" t="inlineStr">
         <is>
-          <t>7.36</t>
+          <t>8.74</t>
         </is>
       </c>
       <c r="BB73" t="inlineStr">
         <is>
-          <t>40.97</t>
+          <t>38.93</t>
         </is>
       </c>
       <c r="BC73" t="inlineStr">
         <is>
-          <t>88.58</t>
+          <t>88.52</t>
         </is>
       </c>
       <c r="BD73" t="inlineStr">
         <is>
-          <t>0.3567</t>
+          <t>0.3994</t>
         </is>
       </c>
       <c r="BE73" t="inlineStr">
         <is>
-          <t>0.1344</t>
+          <t>0.1634</t>
         </is>
       </c>
       <c r="BF73" t="inlineStr">
         <is>
-          <t>27.02</t>
+          <t>30.87</t>
         </is>
       </c>
       <c r="BG73" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH73" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>81</t>
         </is>
       </c>
       <c r="BI73" t="inlineStr">
         <is>
-          <t>Rogers Centre</t>
+          <t>Progressive Field</t>
         </is>
       </c>
       <c r="BJ73" t="inlineStr"/>
@@ -20811,27 +20815,27 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>663330</t>
+          <t>678218</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Jahmai Jones</t>
+          <t>Brandon Valenzuela</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-06-13T20:10:00Z</t>
+          <t>2026-06-13T19:07:00Z</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -20841,26 +20845,26 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Joey Cantillo</t>
+          <t>Cam Schlittler</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>676282</t>
+          <t>693645</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L74" t="n">
-        <v>52.7</v>
+        <v>52.6</v>
       </c>
       <c r="M74" t="inlineStr">
         <is>
@@ -20874,65 +20878,61 @@
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P74" t="n">
-        <v>48.8</v>
+        <v>38.1</v>
       </c>
       <c r="Q74" t="n">
-        <v>42</v>
+        <v>32.5</v>
       </c>
       <c r="R74" t="n">
-        <v>53.6</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="S74" t="n">
-        <v>81.90000000000001</v>
+        <v>76.2</v>
       </c>
       <c r="T74" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="U74" t="n">
-        <v>0</v>
+        <v>91.5</v>
       </c>
       <c r="V74" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z74" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W74" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X74" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y74" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z74" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB74" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr"/>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD74" t="inlineStr"/>
@@ -20949,142 +20949,142 @@
       </c>
       <c r="AH74" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI74" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AK74" t="inlineStr">
         <is>
-          <t>Last 7 games: 0/11, 0 HR</t>
+          <t>Hot streak: 3 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL74" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.7% barrel, 10.7 HR allowed</t>
+          <t>switch hitter; pitcher baseline 7.4% barrel, 5.2 HR allowed</t>
         </is>
       </c>
       <c r="AM74" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN74" t="inlineStr">
         <is>
-          <t>10.6</t>
+          <t>9.3</t>
         </is>
       </c>
       <c r="AO74" t="inlineStr">
         <is>
-          <t>47.79</t>
+          <t>37.1</t>
         </is>
       </c>
       <c r="AP74" t="inlineStr">
         <is>
-          <t>91.29</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="AQ74" t="inlineStr">
         <is>
-          <t>102.0909</t>
+          <t>99.4131</t>
         </is>
       </c>
       <c r="AR74" t="inlineStr">
         <is>
-          <t>0.449</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="AS74" t="inlineStr">
         <is>
-          <t>0.1954</t>
+          <t>0.186</t>
         </is>
       </c>
       <c r="AT74" t="inlineStr">
         <is>
-          <t>0.3423</t>
+          <t>0.349</t>
         </is>
       </c>
       <c r="AU74" t="inlineStr">
         <is>
-          <t>72.97</t>
+          <t>72.6</t>
         </is>
       </c>
       <c r="AV74" t="inlineStr">
         <is>
-          <t>32.98</t>
+          <t>23.3</t>
         </is>
       </c>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>47.66</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>29.88</t>
+          <t>25.8</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>0.1503</t>
+          <t>0.205</t>
         </is>
       </c>
       <c r="BA74" t="inlineStr">
         <is>
-          <t>8.74</t>
+          <t>7.36</t>
         </is>
       </c>
       <c r="BB74" t="inlineStr">
         <is>
-          <t>38.93</t>
+          <t>40.97</t>
         </is>
       </c>
       <c r="BC74" t="inlineStr">
         <is>
-          <t>88.52</t>
+          <t>88.58</t>
         </is>
       </c>
       <c r="BD74" t="inlineStr">
         <is>
-          <t>0.3994</t>
+          <t>0.3567</t>
         </is>
       </c>
       <c r="BE74" t="inlineStr">
         <is>
-          <t>0.1634</t>
+          <t>0.1344</t>
         </is>
       </c>
       <c r="BF74" t="inlineStr">
         <is>
-          <t>30.87</t>
+          <t>27.02</t>
         </is>
       </c>
       <c r="BG74" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BH74" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>71</t>
         </is>
       </c>
       <c r="BI74" t="inlineStr">
         <is>
-          <t>Progressive Field</t>
+          <t>Rogers Centre</t>
         </is>
       </c>
       <c r="BJ74" t="inlineStr"/>
@@ -24748,7 +24748,7 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>50.9</v>
+        <v>50.7</v>
       </c>
       <c r="M88" t="inlineStr">
         <is>
@@ -24772,7 +24772,7 @@
         <v>33.1</v>
       </c>
       <c r="R88" t="n">
-        <v>68.90000000000001</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="S88" t="n">
         <v>93.2</v>
@@ -24963,7 +24963,7 @@
       </c>
       <c r="BH88" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>71</t>
         </is>
       </c>
       <c r="BI88" t="inlineStr">
@@ -26140,7 +26140,7 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>50.3</v>
+        <v>50.2</v>
       </c>
       <c r="M93" t="inlineStr">
         <is>
@@ -26164,7 +26164,7 @@
         <v>38.3</v>
       </c>
       <c r="R93" t="n">
-        <v>68.90000000000001</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="S93" t="n">
         <v>100</v>
@@ -26355,7 +26355,7 @@
       </c>
       <c r="BH93" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>71</t>
         </is>
       </c>
       <c r="BI93" t="inlineStr">
@@ -29375,27 +29375,27 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>682818</t>
+          <t>687221</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Yohendrick Piñango</t>
+          <t>Dalton Rushing</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-06-13T19:07:00Z</t>
+          <t>2026-06-13T20:10:00Z</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -29405,17 +29405,17 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>Cam Schlittler</t>
+          <t>Sean Burke</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>693645</t>
+          <t>680732</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
@@ -29438,61 +29438,65 @@
       </c>
       <c r="O105" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P105" t="n">
-        <v>38.4</v>
+        <v>42.4</v>
       </c>
       <c r="Q105" t="n">
-        <v>33.1</v>
+        <v>39.6</v>
       </c>
       <c r="R105" t="n">
-        <v>68.90000000000001</v>
+        <v>59.6</v>
       </c>
       <c r="S105" t="n">
-        <v>64.3</v>
+        <v>47.9</v>
       </c>
       <c r="T105" t="n">
         <v>80</v>
       </c>
       <c r="U105" t="n">
-        <v>39.5</v>
+        <v>54.3</v>
       </c>
       <c r="V105" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W105" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X105" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y105" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W105" t="inlineStr">
+      <c r="Z105" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X105" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y105" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z105" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB105" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB105" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC105" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD105" t="inlineStr"/>
@@ -29509,12 +29513,12 @@
       </c>
       <c r="AH105" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI105" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ105" t="inlineStr">
@@ -29524,12 +29528,12 @@
       </c>
       <c r="AK105" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/23, 1 HR</t>
+          <t>Contact streak: 9/25 over last 7 games</t>
         </is>
       </c>
       <c r="AL105" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.4% barrel, 5.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.8% barrel, 11.8 HR allowed</t>
         </is>
       </c>
       <c r="AM105" t="inlineStr">
@@ -29539,112 +29543,112 @@
       </c>
       <c r="AN105" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>11.06</t>
         </is>
       </c>
       <c r="AO105" t="inlineStr">
         <is>
-          <t>44.8</t>
+          <t>41.73</t>
         </is>
       </c>
       <c r="AP105" t="inlineStr">
         <is>
-          <t>91.3</t>
+          <t>89.05</t>
         </is>
       </c>
       <c r="AQ105" t="inlineStr">
         <is>
-          <t>102.1842</t>
+          <t>101.2084</t>
         </is>
       </c>
       <c r="AR105" t="inlineStr">
         <is>
-          <t>0.422</t>
+          <t>0.4413</t>
         </is>
       </c>
       <c r="AS105" t="inlineStr">
         <is>
-          <t>0.141</t>
+          <t>0.1879</t>
         </is>
       </c>
       <c r="AT105" t="inlineStr">
         <is>
-          <t>0.321</t>
+          <t>0.3397</t>
         </is>
       </c>
       <c r="AU105" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>72.61</t>
         </is>
       </c>
       <c r="AV105" t="inlineStr">
         <is>
-          <t>55.4</t>
+          <t>17.75</t>
         </is>
       </c>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>31.0</t>
+          <t>47.26</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>19.5</t>
+          <t>26.5</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>6.8</t>
         </is>
       </c>
       <c r="AZ105" t="inlineStr">
         <is>
-          <t>0.147</t>
+          <t>0.2173</t>
         </is>
       </c>
       <c r="BA105" t="inlineStr">
         <is>
-          <t>7.36</t>
+          <t>7.77</t>
         </is>
       </c>
       <c r="BB105" t="inlineStr">
         <is>
-          <t>40.97</t>
+          <t>38.15</t>
         </is>
       </c>
       <c r="BC105" t="inlineStr">
         <is>
-          <t>88.58</t>
+          <t>89.32</t>
         </is>
       </c>
       <c r="BD105" t="inlineStr">
         <is>
-          <t>0.3567</t>
+          <t>0.3961</t>
         </is>
       </c>
       <c r="BE105" t="inlineStr">
         <is>
-          <t>0.1344</t>
+          <t>0.1557</t>
         </is>
       </c>
       <c r="BF105" t="inlineStr">
         <is>
-          <t>27.02</t>
+          <t>29.3</t>
         </is>
       </c>
       <c r="BG105" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH105" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>81</t>
         </is>
       </c>
       <c r="BI105" t="inlineStr">
         <is>
-          <t>Rogers Centre</t>
+          <t>Rate Field</t>
         </is>
       </c>
       <c r="BJ105" t="inlineStr"/>
@@ -29655,27 +29659,27 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>687221</t>
+          <t>682818</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Dalton Rushing</t>
+          <t>Yohendrick Piñango</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-06-13T20:10:00Z</t>
+          <t>2026-06-13T19:07:00Z</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
@@ -29685,17 +29689,17 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>Sean Burke</t>
+          <t>Cam Schlittler</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>680732</t>
+          <t>693645</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
@@ -29704,7 +29708,7 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>49.1</v>
+        <v>49</v>
       </c>
       <c r="M106" t="inlineStr">
         <is>
@@ -29718,65 +29722,61 @@
       </c>
       <c r="O106" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P106" t="n">
-        <v>42.4</v>
+        <v>38.4</v>
       </c>
       <c r="Q106" t="n">
-        <v>39.6</v>
+        <v>33.1</v>
       </c>
       <c r="R106" t="n">
-        <v>59.6</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="S106" t="n">
-        <v>47.9</v>
+        <v>64.3</v>
       </c>
       <c r="T106" t="n">
         <v>80</v>
       </c>
       <c r="U106" t="n">
-        <v>54.3</v>
+        <v>39.5</v>
       </c>
       <c r="V106" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W106" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X106" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y106" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z106" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W106" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X106" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y106" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z106" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB106" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB106" t="inlineStr"/>
       <c r="AC106" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD106" t="inlineStr"/>
@@ -29793,12 +29793,12 @@
       </c>
       <c r="AH106" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI106" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ106" t="inlineStr">
@@ -29808,12 +29808,12 @@
       </c>
       <c r="AK106" t="inlineStr">
         <is>
-          <t>Contact streak: 9/25 over last 7 games</t>
+          <t>Last 7 games: 6/23, 1 HR</t>
         </is>
       </c>
       <c r="AL106" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.8% barrel, 11.8 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.4% barrel, 5.2 HR allowed</t>
         </is>
       </c>
       <c r="AM106" t="inlineStr">
@@ -29823,112 +29823,112 @@
       </c>
       <c r="AN106" t="inlineStr">
         <is>
-          <t>11.06</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="AO106" t="inlineStr">
         <is>
-          <t>41.73</t>
+          <t>44.8</t>
         </is>
       </c>
       <c r="AP106" t="inlineStr">
         <is>
-          <t>89.05</t>
+          <t>91.3</t>
         </is>
       </c>
       <c r="AQ106" t="inlineStr">
         <is>
-          <t>101.2084</t>
+          <t>102.1842</t>
         </is>
       </c>
       <c r="AR106" t="inlineStr">
         <is>
-          <t>0.4413</t>
+          <t>0.422</t>
         </is>
       </c>
       <c r="AS106" t="inlineStr">
         <is>
-          <t>0.1879</t>
+          <t>0.141</t>
         </is>
       </c>
       <c r="AT106" t="inlineStr">
         <is>
-          <t>0.3397</t>
+          <t>0.321</t>
         </is>
       </c>
       <c r="AU106" t="inlineStr">
         <is>
-          <t>72.61</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AV106" t="inlineStr">
         <is>
-          <t>17.75</t>
+          <t>55.4</t>
         </is>
       </c>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>47.26</t>
+          <t>31.0</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>26.5</t>
+          <t>19.5</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr">
         <is>
-          <t>6.8</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AZ106" t="inlineStr">
         <is>
-          <t>0.2173</t>
+          <t>0.147</t>
         </is>
       </c>
       <c r="BA106" t="inlineStr">
         <is>
-          <t>7.77</t>
+          <t>7.36</t>
         </is>
       </c>
       <c r="BB106" t="inlineStr">
         <is>
-          <t>38.15</t>
+          <t>40.97</t>
         </is>
       </c>
       <c r="BC106" t="inlineStr">
         <is>
-          <t>89.32</t>
+          <t>88.58</t>
         </is>
       </c>
       <c r="BD106" t="inlineStr">
         <is>
-          <t>0.3961</t>
+          <t>0.3567</t>
         </is>
       </c>
       <c r="BE106" t="inlineStr">
         <is>
-          <t>0.1557</t>
+          <t>0.1344</t>
         </is>
       </c>
       <c r="BF106" t="inlineStr">
         <is>
-          <t>29.3</t>
+          <t>27.02</t>
         </is>
       </c>
       <c r="BG106" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BH106" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>71</t>
         </is>
       </c>
       <c r="BI106" t="inlineStr">
         <is>
-          <t>Rate Field</t>
+          <t>Rogers Centre</t>
         </is>
       </c>
       <c r="BJ106" t="inlineStr"/>
@@ -42467,27 +42467,27 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>807727</t>
+          <t>553993</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Charles McAdoo</t>
+          <t>Eugenio Suárez</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>2026-06-13T19:07:00Z</t>
+          <t>2026-06-13T20:10:00Z</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
@@ -42497,17 +42497,17 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>Cam Schlittler</t>
+          <t>Michael Soroka</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>693645</t>
+          <t>647336</t>
         </is>
       </c>
       <c r="K152" t="inlineStr">
@@ -42534,22 +42534,22 @@
         </is>
       </c>
       <c r="P152" t="n">
-        <v>38.7</v>
+        <v>31.1</v>
       </c>
       <c r="Q152" t="n">
-        <v>33.1</v>
+        <v>33.9</v>
       </c>
       <c r="R152" t="n">
-        <v>68.90000000000001</v>
+        <v>61.3</v>
       </c>
       <c r="S152" t="n">
-        <v>52.4</v>
+        <v>76.2</v>
       </c>
       <c r="T152" t="n">
         <v>50</v>
       </c>
       <c r="U152" t="n">
-        <v>28.5</v>
+        <v>31.4</v>
       </c>
       <c r="V152" t="inlineStr">
         <is>
@@ -42563,7 +42563,7 @@
       </c>
       <c r="X152" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y152" t="inlineStr">
@@ -42584,7 +42584,7 @@
       <c r="AB152" t="inlineStr"/>
       <c r="AC152" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD152" t="inlineStr"/>
@@ -42596,17 +42596,17 @@
       </c>
       <c r="AG152" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AH152" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI152" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ152" t="inlineStr">
@@ -42616,12 +42616,12 @@
       </c>
       <c r="AK152" t="inlineStr">
         <is>
-          <t>Last 5 games: 3/16, 1 HR</t>
+          <t>Last 7 games: 6/29, 1 HR</t>
         </is>
       </c>
       <c r="AL152" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.4% barrel, 5.2 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.6% barrel, 7.8 HR allowed</t>
         </is>
       </c>
       <c r="AM152" t="inlineStr">
@@ -42631,112 +42631,112 @@
       </c>
       <c r="AN152" t="inlineStr">
         <is>
-          <t>9.1</t>
+          <t>9.33</t>
         </is>
       </c>
       <c r="AO152" t="inlineStr">
         <is>
-          <t>45.5</t>
+          <t>33.67</t>
         </is>
       </c>
       <c r="AP152" t="inlineStr">
         <is>
-          <t>90.2</t>
+          <t>87.61</t>
         </is>
       </c>
       <c r="AQ152" t="inlineStr">
         <is>
-          <t>98.5074</t>
+          <t>99.1737</t>
         </is>
       </c>
       <c r="AR152" t="inlineStr">
         <is>
-          <t>0.374</t>
+          <t>0.3804</t>
         </is>
       </c>
       <c r="AS152" t="inlineStr">
         <is>
-          <t>0.157</t>
+          <t>0.1652</t>
         </is>
       </c>
       <c r="AT152" t="inlineStr">
         <is>
-          <t>0.255</t>
+          <t>0.2927</t>
         </is>
       </c>
       <c r="AU152" t="inlineStr">
         <is>
-          <t>72.8</t>
+          <t>71.53</t>
         </is>
       </c>
       <c r="AV152" t="inlineStr">
         <is>
-          <t>28.0</t>
+          <t>18.24</t>
         </is>
       </c>
       <c r="AW152" t="inlineStr">
         <is>
+          <t>46.77</t>
+        </is>
+      </c>
+      <c r="AX152" t="inlineStr">
+        <is>
+          <t>28.93</t>
+        </is>
+      </c>
+      <c r="AY152" t="inlineStr">
+        <is>
           <t>18.2</t>
         </is>
       </c>
-      <c r="AX152" t="inlineStr">
-        <is>
-          <t>27.3</t>
-        </is>
-      </c>
-      <c r="AY152" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
       <c r="AZ152" t="inlineStr">
         <is>
-          <t>0.187</t>
+          <t>0.1867</t>
         </is>
       </c>
       <c r="BA152" t="inlineStr">
         <is>
-          <t>7.36</t>
+          <t>7.61</t>
         </is>
       </c>
       <c r="BB152" t="inlineStr">
         <is>
-          <t>40.97</t>
+          <t>35.43</t>
         </is>
       </c>
       <c r="BC152" t="inlineStr">
         <is>
-          <t>88.58</t>
+          <t>88.15</t>
         </is>
       </c>
       <c r="BD152" t="inlineStr">
         <is>
-          <t>0.3567</t>
+          <t>0.3895</t>
         </is>
       </c>
       <c r="BE152" t="inlineStr">
         <is>
-          <t>0.1344</t>
+          <t>0.1497</t>
         </is>
       </c>
       <c r="BF152" t="inlineStr">
         <is>
-          <t>27.02</t>
+          <t>27.8</t>
         </is>
       </c>
       <c r="BG152" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH152" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>81</t>
         </is>
       </c>
       <c r="BI152" t="inlineStr">
         <is>
-          <t>Rogers Centre</t>
+          <t>Great American Ball Park</t>
         </is>
       </c>
       <c r="BJ152" t="inlineStr"/>
@@ -42747,47 +42747,47 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>553993</t>
+          <t>691720</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Eugenio Suárez</t>
+          <t>Kyle Karros</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>2026-06-13T20:10:00Z</t>
+          <t>2026-06-14T02:05:00Z</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>Michael Soroka</t>
+          <t>Joey Estes</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>647336</t>
+          <t>683155</t>
         </is>
       </c>
       <c r="K153" t="inlineStr">
@@ -42810,61 +42810,65 @@
       </c>
       <c r="O153" t="inlineStr">
         <is>
-          <t>No major boost</t>
+          <t>Projected Lineup, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P153" t="n">
-        <v>31.1</v>
+        <v>19.9</v>
       </c>
       <c r="Q153" t="n">
-        <v>33.9</v>
+        <v>58.2</v>
       </c>
       <c r="R153" t="n">
-        <v>61.3</v>
+        <v>27.6</v>
       </c>
       <c r="S153" t="n">
-        <v>76.2</v>
+        <v>95.5</v>
       </c>
       <c r="T153" t="n">
         <v>50</v>
       </c>
       <c r="U153" t="n">
-        <v>31.4</v>
+        <v>34.5</v>
       </c>
       <c r="V153" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W153" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X153" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y153" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W153" t="inlineStr">
+      <c r="Z153" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X153" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y153" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z153" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA153" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB153" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB153" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC153" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2025</t>
         </is>
       </c>
       <c r="AD153" t="inlineStr"/>
@@ -42881,142 +42885,134 @@
       </c>
       <c r="AH153" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI153" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/29, 1 HR</t>
+          <t>Contact streak: 7/20 over last 7 games</t>
         </is>
       </c>
       <c r="AL153" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.6% barrel, 7.8 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 11.9% barrel, 4.0 HR allowed</t>
         </is>
       </c>
       <c r="AM153" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN153" t="inlineStr">
         <is>
-          <t>9.33</t>
+          <t>4.64</t>
         </is>
       </c>
       <c r="AO153" t="inlineStr">
         <is>
-          <t>33.67</t>
+          <t>39.16</t>
         </is>
       </c>
       <c r="AP153" t="inlineStr">
         <is>
-          <t>87.61</t>
+          <t>88.74</t>
         </is>
       </c>
       <c r="AQ153" t="inlineStr">
         <is>
-          <t>99.1737</t>
+          <t>99.4316</t>
         </is>
       </c>
       <c r="AR153" t="inlineStr">
         <is>
-          <t>0.3804</t>
+          <t>0.3439</t>
         </is>
       </c>
       <c r="AS153" t="inlineStr">
         <is>
-          <t>0.1652</t>
+          <t>0.1033</t>
         </is>
       </c>
       <c r="AT153" t="inlineStr">
         <is>
-          <t>0.2927</t>
+          <t>0.3098</t>
         </is>
       </c>
       <c r="AU153" t="inlineStr">
         <is>
-          <t>71.53</t>
+          <t>69.87</t>
         </is>
       </c>
       <c r="AV153" t="inlineStr">
         <is>
-          <t>18.24</t>
+          <t>4.6</t>
         </is>
       </c>
       <c r="AW153" t="inlineStr">
         <is>
-          <t>46.77</t>
+          <t>37.68</t>
         </is>
       </c>
       <c r="AX153" t="inlineStr">
         <is>
-          <t>28.93</t>
+          <t>21.33</t>
         </is>
       </c>
       <c r="AY153" t="inlineStr">
         <is>
-          <t>18.2</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="AZ153" t="inlineStr">
         <is>
-          <t>0.1867</t>
+          <t>0.0874</t>
         </is>
       </c>
       <c r="BA153" t="inlineStr">
         <is>
-          <t>7.61</t>
+          <t>11.9</t>
         </is>
       </c>
       <c r="BB153" t="inlineStr">
         <is>
-          <t>35.43</t>
+          <t>33.3</t>
         </is>
       </c>
       <c r="BC153" t="inlineStr">
         <is>
-          <t>88.15</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="BD153" t="inlineStr">
         <is>
-          <t>0.3895</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="BE153" t="inlineStr">
         <is>
-          <t>0.1497</t>
+          <t>0.224</t>
         </is>
       </c>
       <c r="BF153" t="inlineStr">
         <is>
-          <t>27.8</t>
-        </is>
-      </c>
-      <c r="BG153" t="inlineStr">
-        <is>
-          <t>L To R</t>
-        </is>
-      </c>
-      <c r="BH153" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
+          <t>45.2</t>
+        </is>
+      </c>
+      <c r="BG153" t="inlineStr"/>
+      <c r="BH153" t="inlineStr"/>
       <c r="BI153" t="inlineStr">
         <is>
-          <t>Great American Ball Park</t>
+          <t>Las Vegas Ballpark</t>
         </is>
       </c>
       <c r="BJ153" t="inlineStr"/>
@@ -43027,47 +43023,47 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>691720</t>
+          <t>807727</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Kyle Karros</t>
+          <t>Charles McAdoo</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>2026-06-14T02:05:00Z</t>
+          <t>2026-06-13T19:07:00Z</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>Joey Estes</t>
+          <t>Cam Schlittler</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>683155</t>
+          <t>693645</t>
         </is>
       </c>
       <c r="K154" t="inlineStr">
@@ -43076,7 +43072,7 @@
         </is>
       </c>
       <c r="L154" t="n">
-        <v>44.3</v>
+        <v>44.1</v>
       </c>
       <c r="M154" t="inlineStr">
         <is>
@@ -43090,65 +43086,61 @@
       </c>
       <c r="O154" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P154" t="n">
-        <v>19.9</v>
+        <v>38.7</v>
       </c>
       <c r="Q154" t="n">
-        <v>58.2</v>
+        <v>33.1</v>
       </c>
       <c r="R154" t="n">
-        <v>27.6</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="S154" t="n">
-        <v>95.5</v>
+        <v>52.4</v>
       </c>
       <c r="T154" t="n">
         <v>50</v>
       </c>
       <c r="U154" t="n">
-        <v>34.5</v>
+        <v>28.5</v>
       </c>
       <c r="V154" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W154" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X154" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y154" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z154" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W154" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X154" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y154" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z154" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA154" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB154" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB154" t="inlineStr"/>
       <c r="AC154" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD154" t="inlineStr"/>
@@ -43160,139 +43152,147 @@
       </c>
       <c r="AG154" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AH154" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI154" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK154" t="inlineStr">
         <is>
-          <t>Contact streak: 7/20 over last 7 games</t>
+          <t>Last 5 games: 3/16, 1 HR</t>
         </is>
       </c>
       <c r="AL154" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 11.9% barrel, 4.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.4% barrel, 5.2 HR allowed</t>
         </is>
       </c>
       <c r="AM154" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN154" t="inlineStr">
         <is>
-          <t>4.64</t>
+          <t>9.1</t>
         </is>
       </c>
       <c r="AO154" t="inlineStr">
         <is>
-          <t>39.16</t>
+          <t>45.5</t>
         </is>
       </c>
       <c r="AP154" t="inlineStr">
         <is>
-          <t>88.74</t>
+          <t>90.2</t>
         </is>
       </c>
       <c r="AQ154" t="inlineStr">
         <is>
-          <t>99.4316</t>
+          <t>98.5074</t>
         </is>
       </c>
       <c r="AR154" t="inlineStr">
         <is>
-          <t>0.3439</t>
+          <t>0.374</t>
         </is>
       </c>
       <c r="AS154" t="inlineStr">
         <is>
-          <t>0.1033</t>
+          <t>0.157</t>
         </is>
       </c>
       <c r="AT154" t="inlineStr">
         <is>
-          <t>0.3098</t>
+          <t>0.255</t>
         </is>
       </c>
       <c r="AU154" t="inlineStr">
         <is>
-          <t>69.87</t>
+          <t>72.8</t>
         </is>
       </c>
       <c r="AV154" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>28.0</t>
         </is>
       </c>
       <c r="AW154" t="inlineStr">
         <is>
-          <t>37.68</t>
+          <t>18.2</t>
         </is>
       </c>
       <c r="AX154" t="inlineStr">
         <is>
-          <t>21.33</t>
+          <t>27.3</t>
         </is>
       </c>
       <c r="AY154" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AZ154" t="inlineStr">
         <is>
-          <t>0.0874</t>
+          <t>0.187</t>
         </is>
       </c>
       <c r="BA154" t="inlineStr">
         <is>
-          <t>11.9</t>
+          <t>7.36</t>
         </is>
       </c>
       <c r="BB154" t="inlineStr">
         <is>
-          <t>33.3</t>
+          <t>40.97</t>
         </is>
       </c>
       <c r="BC154" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>88.58</t>
         </is>
       </c>
       <c r="BD154" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.3567</t>
         </is>
       </c>
       <c r="BE154" t="inlineStr">
         <is>
-          <t>0.224</t>
+          <t>0.1344</t>
         </is>
       </c>
       <c r="BF154" t="inlineStr">
         <is>
-          <t>45.2</t>
-        </is>
-      </c>
-      <c r="BG154" t="inlineStr"/>
-      <c r="BH154" t="inlineStr"/>
+          <t>27.02</t>
+        </is>
+      </c>
+      <c r="BG154" t="inlineStr">
+        <is>
+          <t>Out To RF</t>
+        </is>
+      </c>
+      <c r="BH154" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
       <c r="BI154" t="inlineStr">
         <is>
-          <t>Las Vegas Ballpark</t>
+          <t>Rogers Centre</t>
         </is>
       </c>
       <c r="BJ154" t="inlineStr"/>
@@ -43303,27 +43303,27 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>664770</t>
+          <t>663837</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Nathan Lukes</t>
+          <t>Matt Vierling</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>2026-06-13T19:07:00Z</t>
+          <t>2026-06-13T20:10:00Z</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
@@ -43333,22 +43333,22 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>Cam Schlittler</t>
+          <t>Joey Cantillo</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>693645</t>
+          <t>676282</t>
         </is>
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L155" t="n">
@@ -43366,58 +43366,62 @@
       </c>
       <c r="O155" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P155" t="n">
-        <v>11.3</v>
+        <v>32</v>
       </c>
       <c r="Q155" t="n">
-        <v>33.1</v>
+        <v>42</v>
       </c>
       <c r="R155" t="n">
-        <v>68.90000000000001</v>
+        <v>53.6</v>
       </c>
       <c r="S155" t="n">
-        <v>100</v>
+        <v>59.8</v>
       </c>
       <c r="T155" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="U155" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="V155" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W155" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X155" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y155" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W155" t="inlineStr">
+      <c r="Z155" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X155" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y155" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z155" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA155" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB155" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB155" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC155" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -43437,12 +43441,12 @@
       </c>
       <c r="AH155" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AI155" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AJ155" t="inlineStr">
@@ -43452,127 +43456,127 @@
       </c>
       <c r="AK155" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/25, 0 HR</t>
+          <t>Last 7 games: 1/15, 0 HR</t>
         </is>
       </c>
       <c r="AL155" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.4% barrel, 5.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.7% barrel, 10.7 HR allowed</t>
         </is>
       </c>
       <c r="AM155" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN155" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>8.04</t>
         </is>
       </c>
       <c r="AO155" t="inlineStr">
         <is>
-          <t>33.71</t>
+          <t>37.45</t>
         </is>
       </c>
       <c r="AP155" t="inlineStr">
         <is>
-          <t>86.92</t>
+          <t>88.49</t>
         </is>
       </c>
       <c r="AQ155" t="inlineStr">
         <is>
-          <t>97.5781</t>
+          <t>98.7956</t>
         </is>
       </c>
       <c r="AR155" t="inlineStr">
         <is>
-          <t>0.3717</t>
+          <t>0.4017</t>
         </is>
       </c>
       <c r="AS155" t="inlineStr">
         <is>
-          <t>0.0931</t>
+          <t>0.1531</t>
         </is>
       </c>
       <c r="AT155" t="inlineStr">
         <is>
-          <t>0.3136</t>
+          <t>0.3177</t>
         </is>
       </c>
       <c r="AU155" t="inlineStr">
         <is>
-          <t>67.58</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="AV155" t="inlineStr">
         <is>
-          <t>4.56</t>
+          <t>7.78</t>
         </is>
       </c>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>33.59</t>
+          <t>33.02</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>18.29</t>
+          <t>32.18</t>
         </is>
       </c>
       <c r="AY155" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="AZ155" t="inlineStr">
         <is>
-          <t>0.103</t>
+          <t>0.1184</t>
         </is>
       </c>
       <c r="BA155" t="inlineStr">
         <is>
-          <t>7.36</t>
+          <t>8.74</t>
         </is>
       </c>
       <c r="BB155" t="inlineStr">
         <is>
-          <t>40.97</t>
+          <t>38.93</t>
         </is>
       </c>
       <c r="BC155" t="inlineStr">
         <is>
-          <t>88.58</t>
+          <t>88.52</t>
         </is>
       </c>
       <c r="BD155" t="inlineStr">
         <is>
-          <t>0.3567</t>
+          <t>0.3994</t>
         </is>
       </c>
       <c r="BE155" t="inlineStr">
         <is>
-          <t>0.1344</t>
+          <t>0.1634</t>
         </is>
       </c>
       <c r="BF155" t="inlineStr">
         <is>
-          <t>27.02</t>
+          <t>30.87</t>
         </is>
       </c>
       <c r="BG155" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH155" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>81</t>
         </is>
       </c>
       <c r="BI155" t="inlineStr">
         <is>
-          <t>Rogers Centre</t>
+          <t>Progressive Field</t>
         </is>
       </c>
       <c r="BJ155" t="inlineStr"/>
@@ -43583,27 +43587,27 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>663837</t>
+          <t>664770</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Matt Vierling</t>
+          <t>Nathan Lukes</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>2026-06-13T20:10:00Z</t>
+          <t>2026-06-13T19:07:00Z</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
@@ -43613,26 +43617,26 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>Joey Cantillo</t>
+          <t>Cam Schlittler</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>676282</t>
+          <t>693645</t>
         </is>
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L156" t="n">
-        <v>44.1</v>
+        <v>44</v>
       </c>
       <c r="M156" t="inlineStr">
         <is>
@@ -43646,62 +43650,58 @@
       </c>
       <c r="O156" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P156" t="n">
-        <v>32</v>
+        <v>11.3</v>
       </c>
       <c r="Q156" t="n">
-        <v>42</v>
+        <v>33.1</v>
       </c>
       <c r="R156" t="n">
-        <v>53.6</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="S156" t="n">
-        <v>59.8</v>
+        <v>100</v>
       </c>
       <c r="T156" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U156" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="V156" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W156" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X156" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y156" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z156" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W156" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X156" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y156" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z156" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA156" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB156" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB156" t="inlineStr"/>
       <c r="AC156" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -43721,12 +43721,12 @@
       </c>
       <c r="AH156" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI156" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ156" t="inlineStr">
@@ -43736,127 +43736,127 @@
       </c>
       <c r="AK156" t="inlineStr">
         <is>
-          <t>Last 7 games: 1/15, 0 HR</t>
+          <t>Last 7 games: 6/25, 0 HR</t>
         </is>
       </c>
       <c r="AL156" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.7% barrel, 10.7 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.4% barrel, 5.2 HR allowed</t>
         </is>
       </c>
       <c r="AM156" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN156" t="inlineStr">
         <is>
-          <t>8.04</t>
+          <t>2.21</t>
         </is>
       </c>
       <c r="AO156" t="inlineStr">
         <is>
-          <t>37.45</t>
+          <t>33.71</t>
         </is>
       </c>
       <c r="AP156" t="inlineStr">
         <is>
-          <t>88.49</t>
+          <t>86.92</t>
         </is>
       </c>
       <c r="AQ156" t="inlineStr">
         <is>
-          <t>98.7956</t>
+          <t>97.5781</t>
         </is>
       </c>
       <c r="AR156" t="inlineStr">
         <is>
-          <t>0.4017</t>
+          <t>0.3717</t>
         </is>
       </c>
       <c r="AS156" t="inlineStr">
         <is>
-          <t>0.1531</t>
+          <t>0.0931</t>
         </is>
       </c>
       <c r="AT156" t="inlineStr">
         <is>
-          <t>0.3177</t>
+          <t>0.3136</t>
         </is>
       </c>
       <c r="AU156" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>67.58</t>
         </is>
       </c>
       <c r="AV156" t="inlineStr">
         <is>
-          <t>7.78</t>
+          <t>4.56</t>
         </is>
       </c>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>33.02</t>
+          <t>33.59</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>32.18</t>
+          <t>18.29</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="AZ156" t="inlineStr">
         <is>
-          <t>0.1184</t>
+          <t>0.103</t>
         </is>
       </c>
       <c r="BA156" t="inlineStr">
         <is>
-          <t>8.74</t>
+          <t>7.36</t>
         </is>
       </c>
       <c r="BB156" t="inlineStr">
         <is>
-          <t>38.93</t>
+          <t>40.97</t>
         </is>
       </c>
       <c r="BC156" t="inlineStr">
         <is>
-          <t>88.52</t>
+          <t>88.58</t>
         </is>
       </c>
       <c r="BD156" t="inlineStr">
         <is>
-          <t>0.3994</t>
+          <t>0.3567</t>
         </is>
       </c>
       <c r="BE156" t="inlineStr">
         <is>
-          <t>0.1634</t>
+          <t>0.1344</t>
         </is>
       </c>
       <c r="BF156" t="inlineStr">
         <is>
-          <t>30.87</t>
+          <t>27.02</t>
         </is>
       </c>
       <c r="BG156" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BH156" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>71</t>
         </is>
       </c>
       <c r="BI156" t="inlineStr">
         <is>
-          <t>Progressive Field</t>
+          <t>Rogers Centre</t>
         </is>
       </c>
       <c r="BJ156" t="inlineStr"/>
@@ -55767,27 +55767,27 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>676391</t>
+          <t>694371</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Ernie Clement</t>
+          <t>Tommy Troy</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>2026-06-13T19:07:00Z</t>
+          <t>2026-06-13T20:10:00Z</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
@@ -55797,17 +55797,17 @@
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>Cam Schlittler</t>
+          <t>Rhett Lowder</t>
         </is>
       </c>
       <c r="J200" t="inlineStr">
         <is>
-          <t>693645</t>
+          <t>695076</t>
         </is>
       </c>
       <c r="K200" t="inlineStr">
@@ -55834,57 +55834,53 @@
         </is>
       </c>
       <c r="P200" t="n">
-        <v>7.2</v>
+        <v>22.7</v>
       </c>
       <c r="Q200" t="n">
-        <v>33.1</v>
+        <v>40.2</v>
       </c>
       <c r="R200" t="n">
-        <v>68.90000000000001</v>
+        <v>61.3</v>
       </c>
       <c r="S200" t="n">
-        <v>86.40000000000001</v>
+        <v>64.3</v>
       </c>
       <c r="T200" t="n">
         <v>50</v>
       </c>
       <c r="U200" t="n">
-        <v>61.5</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="V200" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W200" t="inlineStr">
+      <c r="W200" t="inlineStr"/>
+      <c r="X200" t="inlineStr"/>
+      <c r="Y200" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z200" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X200" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y200" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z200" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA200" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB200" t="inlineStr"/>
+      <c r="AB200" t="inlineStr">
+        <is>
+          <t>not found on RotoWire</t>
+        </is>
+      </c>
       <c r="AC200" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026</t>
         </is>
       </c>
       <c r="AD200" t="inlineStr"/>
@@ -55901,27 +55897,27 @@
       </c>
       <c r="AH200" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI200" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ200" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK200" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 4/22, 0 HR</t>
         </is>
       </c>
       <c r="AL200" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.4% barrel, 5.2 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.1% barrel, 2.0 HR allowed</t>
         </is>
       </c>
       <c r="AM200" t="inlineStr">
@@ -55931,112 +55927,112 @@
       </c>
       <c r="AN200" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="AO200" t="inlineStr">
         <is>
-          <t>25.44</t>
+          <t>28.2</t>
         </is>
       </c>
       <c r="AP200" t="inlineStr">
         <is>
-          <t>85.69</t>
+          <t>85.3</t>
         </is>
       </c>
       <c r="AQ200" t="inlineStr">
         <is>
-          <t>95.3697</t>
+          <t>97.6142</t>
         </is>
       </c>
       <c r="AR200" t="inlineStr">
         <is>
-          <t>0.3513</t>
+          <t>0.383</t>
         </is>
       </c>
       <c r="AS200" t="inlineStr">
         <is>
-          <t>0.0958</t>
+          <t>0.148</t>
         </is>
       </c>
       <c r="AT200" t="inlineStr">
         <is>
-          <t>0.2778</t>
+          <t>0.325</t>
         </is>
       </c>
       <c r="AU200" t="inlineStr">
         <is>
-          <t>67.67</t>
+          <t>71.7</t>
         </is>
       </c>
       <c r="AV200" t="inlineStr">
         <is>
-          <t>2.89</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="AW200" t="inlineStr">
         <is>
-          <t>42.97</t>
+          <t>28.2</t>
         </is>
       </c>
       <c r="AX200" t="inlineStr">
         <is>
-          <t>26.78</t>
+          <t>30.8</t>
         </is>
       </c>
       <c r="AY200" t="inlineStr">
         <is>
-          <t>7.6</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AZ200" t="inlineStr">
         <is>
-          <t>0.1483</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="BA200" t="inlineStr">
         <is>
-          <t>7.36</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="BB200" t="inlineStr">
         <is>
-          <t>40.97</t>
+          <t>40.2</t>
         </is>
       </c>
       <c r="BC200" t="inlineStr">
         <is>
-          <t>88.58</t>
+          <t>90.5</t>
         </is>
       </c>
       <c r="BD200" t="inlineStr">
         <is>
-          <t>0.3567</t>
+          <t>0.419</t>
         </is>
       </c>
       <c r="BE200" t="inlineStr">
         <is>
-          <t>0.1344</t>
+          <t>0.149</t>
         </is>
       </c>
       <c r="BF200" t="inlineStr">
         <is>
-          <t>27.02</t>
+          <t>25.2</t>
         </is>
       </c>
       <c r="BG200" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH200" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>81</t>
         </is>
       </c>
       <c r="BI200" t="inlineStr">
         <is>
-          <t>Rogers Centre</t>
+          <t>Great American Ball Park</t>
         </is>
       </c>
       <c r="BJ200" t="inlineStr"/>
@@ -56047,27 +56043,27 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>694371</t>
+          <t>676391</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Tommy Troy</t>
+          <t>Ernie Clement</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>2026-06-13T20:10:00Z</t>
+          <t>2026-06-13T19:07:00Z</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
@@ -56077,17 +56073,17 @@
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>Rhett Lowder</t>
+          <t>Cam Schlittler</t>
         </is>
       </c>
       <c r="J201" t="inlineStr">
         <is>
-          <t>695076</t>
+          <t>693645</t>
         </is>
       </c>
       <c r="K201" t="inlineStr">
@@ -56096,7 +56092,7 @@
         </is>
       </c>
       <c r="L201" t="n">
-        <v>40.3</v>
+        <v>40.2</v>
       </c>
       <c r="M201" t="inlineStr">
         <is>
@@ -56114,53 +56110,57 @@
         </is>
       </c>
       <c r="P201" t="n">
-        <v>22.7</v>
+        <v>7.2</v>
       </c>
       <c r="Q201" t="n">
-        <v>40.2</v>
+        <v>33.1</v>
       </c>
       <c r="R201" t="n">
-        <v>61.3</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="S201" t="n">
-        <v>64.3</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T201" t="n">
         <v>50</v>
       </c>
       <c r="U201" t="n">
-        <v>9.300000000000001</v>
+        <v>61.5</v>
       </c>
       <c r="V201" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W201" t="inlineStr"/>
-      <c r="X201" t="inlineStr"/>
+      <c r="W201" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X201" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="Y201" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z201" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z201" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA201" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB201" t="inlineStr">
-        <is>
-          <t>not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB201" t="inlineStr"/>
       <c r="AC201" t="inlineStr">
         <is>
-          <t>H:2026 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD201" t="inlineStr"/>
@@ -56177,27 +56177,27 @@
       </c>
       <c r="AH201" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI201" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ201" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK201" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/22, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL201" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.1% barrel, 2.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.4% barrel, 5.2 HR allowed</t>
         </is>
       </c>
       <c r="AM201" t="inlineStr">
@@ -56207,112 +56207,112 @@
       </c>
       <c r="AN201" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="AO201" t="inlineStr">
         <is>
-          <t>28.2</t>
+          <t>25.44</t>
         </is>
       </c>
       <c r="AP201" t="inlineStr">
         <is>
-          <t>85.3</t>
+          <t>85.69</t>
         </is>
       </c>
       <c r="AQ201" t="inlineStr">
         <is>
-          <t>97.6142</t>
+          <t>95.3697</t>
         </is>
       </c>
       <c r="AR201" t="inlineStr">
         <is>
-          <t>0.383</t>
+          <t>0.3513</t>
         </is>
       </c>
       <c r="AS201" t="inlineStr">
         <is>
-          <t>0.148</t>
+          <t>0.0958</t>
         </is>
       </c>
       <c r="AT201" t="inlineStr">
         <is>
-          <t>0.325</t>
+          <t>0.2778</t>
         </is>
       </c>
       <c r="AU201" t="inlineStr">
         <is>
-          <t>71.7</t>
+          <t>67.67</t>
         </is>
       </c>
       <c r="AV201" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>2.89</t>
         </is>
       </c>
       <c r="AW201" t="inlineStr">
         <is>
-          <t>28.2</t>
+          <t>42.97</t>
         </is>
       </c>
       <c r="AX201" t="inlineStr">
         <is>
-          <t>30.8</t>
+          <t>26.78</t>
         </is>
       </c>
       <c r="AY201" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>7.6</t>
         </is>
       </c>
       <c r="AZ201" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.1483</t>
         </is>
       </c>
       <c r="BA201" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>7.36</t>
         </is>
       </c>
       <c r="BB201" t="inlineStr">
         <is>
-          <t>40.2</t>
+          <t>40.97</t>
         </is>
       </c>
       <c r="BC201" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>88.58</t>
         </is>
       </c>
       <c r="BD201" t="inlineStr">
         <is>
-          <t>0.419</t>
+          <t>0.3567</t>
         </is>
       </c>
       <c r="BE201" t="inlineStr">
         <is>
-          <t>0.149</t>
+          <t>0.1344</t>
         </is>
       </c>
       <c r="BF201" t="inlineStr">
         <is>
-          <t>25.2</t>
+          <t>27.02</t>
         </is>
       </c>
       <c r="BG201" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BH201" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>71</t>
         </is>
       </c>
       <c r="BI201" t="inlineStr">
         <is>
-          <t>Great American Ball Park</t>
+          <t>Rogers Centre</t>
         </is>
       </c>
       <c r="BJ201" t="inlineStr"/>
@@ -58283,52 +58283,52 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>641555</t>
+          <t>514888</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>J.C. Escarra</t>
+          <t>Jose Altuve</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>2026-06-13T19:07:00Z</t>
+          <t>2026-06-13T23:10:00Z</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>Kevin Gausman</t>
+          <t>Noah Cameron</t>
         </is>
       </c>
       <c r="J209" t="inlineStr">
         <is>
-          <t>592332</t>
+          <t>702070</t>
         </is>
       </c>
       <c r="K209" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L209" t="n">
@@ -58346,58 +58346,62 @@
       </c>
       <c r="O209" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P209" t="n">
-        <v>18.8</v>
+        <v>16.5</v>
       </c>
       <c r="Q209" t="n">
-        <v>39.7</v>
+        <v>42.1</v>
       </c>
       <c r="R209" t="n">
-        <v>68.90000000000001</v>
+        <v>23.2</v>
       </c>
       <c r="S209" t="n">
-        <v>44.8</v>
+        <v>88.7</v>
       </c>
       <c r="T209" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="U209" t="n">
-        <v>0</v>
+        <v>20.8</v>
       </c>
       <c r="V209" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W209" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X209" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y209" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W209" t="inlineStr">
+      <c r="Z209" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X209" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y209" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z209" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA209" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB209" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB209" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC209" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -58417,27 +58421,27 @@
       </c>
       <c r="AH209" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AI209" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="AJ209" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AI209" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AJ209" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AK209" t="inlineStr">
         <is>
-          <t>Last 7 games: 1/15, 0 HR</t>
+          <t>Last 7 games: 3/22, 1 HR</t>
         </is>
       </c>
       <c r="AL209" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.4% barrel, 12.6 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.4% barrel, 9.6 HR allowed</t>
         </is>
       </c>
       <c r="AM209" t="inlineStr">
@@ -58447,112 +58451,104 @@
       </c>
       <c r="AN209" t="inlineStr">
         <is>
-          <t>4.34</t>
+          <t>5.85</t>
         </is>
       </c>
       <c r="AO209" t="inlineStr">
         <is>
-          <t>35.4</t>
+          <t>33.42</t>
         </is>
       </c>
       <c r="AP209" t="inlineStr">
         <is>
-          <t>89.54</t>
+          <t>85.66</t>
         </is>
       </c>
       <c r="AQ209" t="inlineStr">
         <is>
-          <t>99.2378</t>
+          <t>97.6463</t>
         </is>
       </c>
       <c r="AR209" t="inlineStr">
         <is>
-          <t>0.3231</t>
+          <t>0.3602</t>
         </is>
       </c>
       <c r="AS209" t="inlineStr">
         <is>
-          <t>0.1076</t>
+          <t>0.1218</t>
         </is>
       </c>
       <c r="AT209" t="inlineStr">
         <is>
-          <t>0.2727</t>
+          <t>0.3007</t>
         </is>
       </c>
       <c r="AU209" t="inlineStr">
         <is>
-          <t>70.77</t>
+          <t>69.21</t>
         </is>
       </c>
       <c r="AV209" t="inlineStr">
         <is>
-          <t>10.93</t>
+          <t>9.74</t>
         </is>
       </c>
       <c r="AW209" t="inlineStr">
         <is>
-          <t>34.46</t>
+          <t>46.83</t>
         </is>
       </c>
       <c r="AX209" t="inlineStr">
         <is>
-          <t>17.72</t>
+          <t>19.85</t>
         </is>
       </c>
       <c r="AY209" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>11.3</t>
         </is>
       </c>
       <c r="AZ209" t="inlineStr">
         <is>
-          <t>0.0995</t>
+          <t>0.1483</t>
         </is>
       </c>
       <c r="BA209" t="inlineStr">
         <is>
-          <t>8.36</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="BB209" t="inlineStr">
         <is>
-          <t>38.81</t>
+          <t>39.92</t>
         </is>
       </c>
       <c r="BC209" t="inlineStr">
         <is>
-          <t>88.46</t>
+          <t>89.02</t>
         </is>
       </c>
       <c r="BD209" t="inlineStr">
         <is>
-          <t>0.3993</t>
+          <t>0.4198</t>
         </is>
       </c>
       <c r="BE209" t="inlineStr">
         <is>
-          <t>0.1592</t>
+          <t>0.1688</t>
         </is>
       </c>
       <c r="BF209" t="inlineStr">
         <is>
-          <t>25.88</t>
-        </is>
-      </c>
-      <c r="BG209" t="inlineStr">
-        <is>
-          <t>Out To RF</t>
-        </is>
-      </c>
-      <c r="BH209" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
+          <t>25.96</t>
+        </is>
+      </c>
+      <c r="BG209" t="inlineStr"/>
+      <c r="BH209" t="inlineStr"/>
       <c r="BI209" t="inlineStr">
         <is>
-          <t>Rogers Centre</t>
+          <t>Kauffman Stadium</t>
         </is>
       </c>
       <c r="BJ209" t="inlineStr"/>
@@ -58563,56 +58559,56 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>514888</t>
+          <t>641555</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Jose Altuve</t>
+          <t>J.C. Escarra</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>2026-06-13T23:10:00Z</t>
+          <t>2026-06-13T19:07:00Z</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t>Noah Cameron</t>
+          <t>Kevin Gausman</t>
         </is>
       </c>
       <c r="J210" t="inlineStr">
         <is>
-          <t>702070</t>
+          <t>592332</t>
         </is>
       </c>
       <c r="K210" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L210" t="n">
-        <v>39.5</v>
+        <v>39.4</v>
       </c>
       <c r="M210" t="inlineStr">
         <is>
@@ -58626,62 +58622,58 @@
       </c>
       <c r="O210" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P210" t="n">
-        <v>16.5</v>
+        <v>18.8</v>
       </c>
       <c r="Q210" t="n">
-        <v>42.1</v>
+        <v>39.7</v>
       </c>
       <c r="R210" t="n">
-        <v>23.2</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="S210" t="n">
-        <v>88.7</v>
+        <v>44.8</v>
       </c>
       <c r="T210" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U210" t="n">
-        <v>20.8</v>
+        <v>0</v>
       </c>
       <c r="V210" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W210" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X210" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y210" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z210" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W210" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X210" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y210" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z210" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA210" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB210" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB210" t="inlineStr"/>
       <c r="AC210" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -58701,27 +58693,27 @@
       </c>
       <c r="AH210" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AI210" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AJ210" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK210" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/22, 1 HR</t>
+          <t>Last 7 games: 1/15, 0 HR</t>
         </is>
       </c>
       <c r="AL210" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.4% barrel, 9.6 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.4% barrel, 12.6 HR allowed</t>
         </is>
       </c>
       <c r="AM210" t="inlineStr">
@@ -58731,104 +58723,112 @@
       </c>
       <c r="AN210" t="inlineStr">
         <is>
-          <t>5.85</t>
+          <t>4.34</t>
         </is>
       </c>
       <c r="AO210" t="inlineStr">
         <is>
-          <t>33.42</t>
+          <t>35.4</t>
         </is>
       </c>
       <c r="AP210" t="inlineStr">
         <is>
-          <t>85.66</t>
+          <t>89.54</t>
         </is>
       </c>
       <c r="AQ210" t="inlineStr">
         <is>
-          <t>97.6463</t>
+          <t>99.2378</t>
         </is>
       </c>
       <c r="AR210" t="inlineStr">
         <is>
-          <t>0.3602</t>
+          <t>0.3231</t>
         </is>
       </c>
       <c r="AS210" t="inlineStr">
         <is>
-          <t>0.1218</t>
+          <t>0.1076</t>
         </is>
       </c>
       <c r="AT210" t="inlineStr">
         <is>
-          <t>0.3007</t>
+          <t>0.2727</t>
         </is>
       </c>
       <c r="AU210" t="inlineStr">
         <is>
-          <t>69.21</t>
+          <t>70.77</t>
         </is>
       </c>
       <c r="AV210" t="inlineStr">
         <is>
-          <t>9.74</t>
+          <t>10.93</t>
         </is>
       </c>
       <c r="AW210" t="inlineStr">
         <is>
-          <t>46.83</t>
+          <t>34.46</t>
         </is>
       </c>
       <c r="AX210" t="inlineStr">
         <is>
-          <t>19.85</t>
+          <t>17.72</t>
         </is>
       </c>
       <c r="AY210" t="inlineStr">
         <is>
-          <t>11.3</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="AZ210" t="inlineStr">
         <is>
-          <t>0.1483</t>
+          <t>0.0995</t>
         </is>
       </c>
       <c r="BA210" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.36</t>
         </is>
       </c>
       <c r="BB210" t="inlineStr">
         <is>
-          <t>39.92</t>
+          <t>38.81</t>
         </is>
       </c>
       <c r="BC210" t="inlineStr">
         <is>
-          <t>89.02</t>
+          <t>88.46</t>
         </is>
       </c>
       <c r="BD210" t="inlineStr">
         <is>
-          <t>0.4198</t>
+          <t>0.3993</t>
         </is>
       </c>
       <c r="BE210" t="inlineStr">
         <is>
-          <t>0.1688</t>
+          <t>0.1592</t>
         </is>
       </c>
       <c r="BF210" t="inlineStr">
         <is>
-          <t>25.96</t>
-        </is>
-      </c>
-      <c r="BG210" t="inlineStr"/>
-      <c r="BH210" t="inlineStr"/>
+          <t>25.88</t>
+        </is>
+      </c>
+      <c r="BG210" t="inlineStr">
+        <is>
+          <t>Out To RF</t>
+        </is>
+      </c>
+      <c r="BH210" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
       <c r="BI210" t="inlineStr">
         <is>
-          <t>Kauffman Stadium</t>
+          <t>Rogers Centre</t>
         </is>
       </c>
       <c r="BJ210" t="inlineStr"/>
@@ -61536,7 +61536,7 @@
         </is>
       </c>
       <c r="L221" t="n">
-        <v>37.9</v>
+        <v>37.7</v>
       </c>
       <c r="M221" t="inlineStr">
         <is>
@@ -61560,7 +61560,7 @@
         <v>39.7</v>
       </c>
       <c r="R221" t="n">
-        <v>68.90000000000001</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="S221" t="n">
         <v>64.3</v>
@@ -61751,7 +61751,7 @@
       </c>
       <c r="BH221" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>71</t>
         </is>
       </c>
       <c r="BI221" t="inlineStr">
@@ -65927,47 +65927,47 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>665926</t>
+          <t>608324</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Andrés Giménez</t>
+          <t>Alex Bregman</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>CHC</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>2026-06-13T19:07:00Z</t>
+          <t>2026-06-14T02:05:00Z</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I237" t="inlineStr">
         <is>
-          <t>Cam Schlittler</t>
+          <t>Trevor McDonald</t>
         </is>
       </c>
       <c r="J237" t="inlineStr">
         <is>
-          <t>693645</t>
+          <t>686790</t>
         </is>
       </c>
       <c r="K237" t="inlineStr">
@@ -65976,7 +65976,7 @@
         </is>
       </c>
       <c r="L237" t="n">
-        <v>35.4</v>
+        <v>35.3</v>
       </c>
       <c r="M237" t="inlineStr">
         <is>
@@ -65990,58 +65990,62 @@
       </c>
       <c r="O237" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Projected Lineup, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P237" t="n">
-        <v>6.5</v>
+        <v>26.9</v>
       </c>
       <c r="Q237" t="n">
-        <v>33.1</v>
+        <v>21.3</v>
       </c>
       <c r="R237" t="n">
-        <v>68.90000000000001</v>
+        <v>19.3</v>
       </c>
       <c r="S237" t="n">
-        <v>44.8</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="T237" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U237" t="n">
-        <v>29.7</v>
+        <v>24.3</v>
       </c>
       <c r="V237" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W237" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X237" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y237" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W237" t="inlineStr">
+      <c r="Z237" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X237" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y237" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z237" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA237" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB237" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB237" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC237" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -66061,27 +66065,27 @@
       </c>
       <c r="AH237" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI237" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ237" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK237" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/22, 0 HR</t>
+          <t>Last 7 games: 4/25, 1 HR</t>
         </is>
       </c>
       <c r="AL237" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.4% barrel, 5.2 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 3.9% barrel, 2.4 HR allowed</t>
         </is>
       </c>
       <c r="AM237" t="inlineStr">
@@ -66091,112 +66095,104 @@
       </c>
       <c r="AN237" t="inlineStr">
         <is>
-          <t>3.28</t>
+          <t>5.69</t>
         </is>
       </c>
       <c r="AO237" t="inlineStr">
         <is>
-          <t>24.83</t>
+          <t>40.41</t>
         </is>
       </c>
       <c r="AP237" t="inlineStr">
         <is>
-          <t>86.09</t>
+          <t>88.77</t>
         </is>
       </c>
       <c r="AQ237" t="inlineStr">
         <is>
-          <t>95.7604</t>
+          <t>98.6791</t>
         </is>
       </c>
       <c r="AR237" t="inlineStr">
         <is>
-          <t>0.3232</t>
+          <t>0.3913</t>
         </is>
       </c>
       <c r="AS237" t="inlineStr">
         <is>
-          <t>0.0929</t>
+          <t>0.1425</t>
         </is>
       </c>
       <c r="AT237" t="inlineStr">
         <is>
-          <t>0.2758</t>
+          <t>0.3209</t>
         </is>
       </c>
       <c r="AU237" t="inlineStr">
         <is>
-          <t>68.32</t>
+          <t>70.16</t>
         </is>
       </c>
       <c r="AV237" t="inlineStr">
         <is>
-          <t>4.72</t>
+          <t>5.15</t>
         </is>
       </c>
       <c r="AW237" t="inlineStr">
         <is>
-          <t>36.77</t>
+          <t>46.86</t>
         </is>
       </c>
       <c r="AX237" t="inlineStr">
         <is>
-          <t>22.74</t>
+          <t>23.87</t>
         </is>
       </c>
       <c r="AY237" t="inlineStr">
         <is>
-          <t>6.3</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="AZ237" t="inlineStr">
         <is>
-          <t>0.1226</t>
+          <t>0.133</t>
         </is>
       </c>
       <c r="BA237" t="inlineStr">
         <is>
-          <t>7.36</t>
+          <t>3.87</t>
         </is>
       </c>
       <c r="BB237" t="inlineStr">
         <is>
-          <t>40.97</t>
+          <t>39.93</t>
         </is>
       </c>
       <c r="BC237" t="inlineStr">
         <is>
-          <t>88.58</t>
+          <t>89.65</t>
         </is>
       </c>
       <c r="BD237" t="inlineStr">
         <is>
-          <t>0.3567</t>
+          <t>0.3557</t>
         </is>
       </c>
       <c r="BE237" t="inlineStr">
         <is>
-          <t>0.1344</t>
+          <t>0.1094</t>
         </is>
       </c>
       <c r="BF237" t="inlineStr">
         <is>
-          <t>27.02</t>
-        </is>
-      </c>
-      <c r="BG237" t="inlineStr">
-        <is>
-          <t>Out To RF</t>
-        </is>
-      </c>
-      <c r="BH237" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
+          <t>11.7</t>
+        </is>
+      </c>
+      <c r="BG237" t="inlineStr"/>
+      <c r="BH237" t="inlineStr"/>
       <c r="BI237" t="inlineStr">
         <is>
-          <t>Rogers Centre</t>
+          <t>Oracle Park</t>
         </is>
       </c>
       <c r="BJ237" t="inlineStr"/>
@@ -66207,47 +66203,47 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>608324</t>
+          <t>665926</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Alex Bregman</t>
+          <t>Andrés Giménez</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>CHC</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>2026-06-14T02:05:00Z</t>
+          <t>2026-06-13T19:07:00Z</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I238" t="inlineStr">
         <is>
-          <t>Trevor McDonald</t>
+          <t>Cam Schlittler</t>
         </is>
       </c>
       <c r="J238" t="inlineStr">
         <is>
-          <t>686790</t>
+          <t>693645</t>
         </is>
       </c>
       <c r="K238" t="inlineStr">
@@ -66256,7 +66252,7 @@
         </is>
       </c>
       <c r="L238" t="n">
-        <v>35.3</v>
+        <v>35.2</v>
       </c>
       <c r="M238" t="inlineStr">
         <is>
@@ -66270,62 +66266,58 @@
       </c>
       <c r="O238" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P238" t="n">
-        <v>26.9</v>
+        <v>6.5</v>
       </c>
       <c r="Q238" t="n">
-        <v>21.3</v>
+        <v>33.1</v>
       </c>
       <c r="R238" t="n">
-        <v>19.3</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="S238" t="n">
-        <v>90.40000000000001</v>
+        <v>44.8</v>
       </c>
       <c r="T238" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U238" t="n">
-        <v>24.3</v>
+        <v>29.7</v>
       </c>
       <c r="V238" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W238" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X238" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y238" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z238" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W238" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X238" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y238" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z238" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA238" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB238" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB238" t="inlineStr"/>
       <c r="AC238" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -66345,27 +66337,27 @@
       </c>
       <c r="AH238" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI238" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ238" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK238" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/25, 1 HR</t>
+          <t>Last 7 games: 7/22, 0 HR</t>
         </is>
       </c>
       <c r="AL238" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 3.9% barrel, 2.4 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.4% barrel, 5.2 HR allowed</t>
         </is>
       </c>
       <c r="AM238" t="inlineStr">
@@ -66375,104 +66367,112 @@
       </c>
       <c r="AN238" t="inlineStr">
         <is>
-          <t>5.69</t>
+          <t>3.28</t>
         </is>
       </c>
       <c r="AO238" t="inlineStr">
         <is>
-          <t>40.41</t>
+          <t>24.83</t>
         </is>
       </c>
       <c r="AP238" t="inlineStr">
         <is>
-          <t>88.77</t>
+          <t>86.09</t>
         </is>
       </c>
       <c r="AQ238" t="inlineStr">
         <is>
-          <t>98.6791</t>
+          <t>95.7604</t>
         </is>
       </c>
       <c r="AR238" t="inlineStr">
         <is>
-          <t>0.3913</t>
+          <t>0.3232</t>
         </is>
       </c>
       <c r="AS238" t="inlineStr">
         <is>
-          <t>0.1425</t>
+          <t>0.0929</t>
         </is>
       </c>
       <c r="AT238" t="inlineStr">
         <is>
-          <t>0.3209</t>
+          <t>0.2758</t>
         </is>
       </c>
       <c r="AU238" t="inlineStr">
         <is>
-          <t>70.16</t>
+          <t>68.32</t>
         </is>
       </c>
       <c r="AV238" t="inlineStr">
         <is>
-          <t>5.15</t>
+          <t>4.72</t>
         </is>
       </c>
       <c r="AW238" t="inlineStr">
         <is>
-          <t>46.86</t>
+          <t>36.77</t>
         </is>
       </c>
       <c r="AX238" t="inlineStr">
         <is>
-          <t>23.87</t>
+          <t>22.74</t>
         </is>
       </c>
       <c r="AY238" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>6.3</t>
         </is>
       </c>
       <c r="AZ238" t="inlineStr">
         <is>
-          <t>0.133</t>
+          <t>0.1226</t>
         </is>
       </c>
       <c r="BA238" t="inlineStr">
         <is>
-          <t>3.87</t>
+          <t>7.36</t>
         </is>
       </c>
       <c r="BB238" t="inlineStr">
         <is>
-          <t>39.93</t>
+          <t>40.97</t>
         </is>
       </c>
       <c r="BC238" t="inlineStr">
         <is>
-          <t>89.65</t>
+          <t>88.58</t>
         </is>
       </c>
       <c r="BD238" t="inlineStr">
         <is>
-          <t>0.3557</t>
+          <t>0.3567</t>
         </is>
       </c>
       <c r="BE238" t="inlineStr">
         <is>
-          <t>0.1094</t>
+          <t>0.1344</t>
         </is>
       </c>
       <c r="BF238" t="inlineStr">
         <is>
-          <t>11.7</t>
-        </is>
-      </c>
-      <c r="BG238" t="inlineStr"/>
-      <c r="BH238" t="inlineStr"/>
+          <t>27.02</t>
+        </is>
+      </c>
+      <c r="BG238" t="inlineStr">
+        <is>
+          <t>Out To RF</t>
+        </is>
+      </c>
+      <c r="BH238" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
       <c r="BI238" t="inlineStr">
         <is>
-          <t>Oracle Park</t>
+          <t>Rogers Centre</t>
         </is>
       </c>
       <c r="BJ238" t="inlineStr"/>
@@ -78474,7 +78474,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>62.8</v>
+        <v>62.6</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -78498,7 +78498,7 @@
         <v>39.7</v>
       </c>
       <c r="R11" t="n">
-        <v>68.90000000000001</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="S11" t="n">
         <v>93.2</v>
@@ -78689,7 +78689,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>71</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">

--- a/outputs/hr_rankings.xlsx
+++ b/outputs/hr_rankings.xlsx
@@ -3264,7 +3264,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -4656,7 +4656,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -4960,7 +4960,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>59</v>
+        <v>58.9</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -4993,7 +4993,7 @@
         <v>50</v>
       </c>
       <c r="U17" t="n">
-        <v>40.3</v>
+        <v>37.8</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
@@ -5050,7 +5050,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
@@ -5060,7 +5060,7 @@
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/15, 1 HR</t>
+          <t>Last 7 games: 4/16, 1 HR</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
@@ -5496,7 +5496,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -6031,47 +6031,47 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>665019</t>
+          <t>663993</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Kody Clemens</t>
+          <t>Nathaniel Lowe</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-06-21T02:10:00Z</t>
+          <t>2026-06-20T17:35:00Z</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Zac Gallen</t>
+          <t>Will Warren</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>668678</t>
+          <t>701542</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -6080,7 +6080,7 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>58.4</v>
+        <v>58.5</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
@@ -6094,62 +6094,58 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Good Environment, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P21" t="n">
-        <v>52.4</v>
+        <v>43.4</v>
       </c>
       <c r="Q21" t="n">
-        <v>57.3</v>
+        <v>39.4</v>
       </c>
       <c r="R21" t="n">
-        <v>28.2</v>
+        <v>84.7</v>
       </c>
       <c r="S21" t="n">
-        <v>92.09999999999999</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T21" t="n">
         <v>80</v>
       </c>
       <c r="U21" t="n">
-        <v>60</v>
+        <v>32</v>
       </c>
       <c r="V21" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y21" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr"/>
       <c r="AC21" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -6169,134 +6165,142 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Contact streak: 5/15 over last 7 games</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 9.7% barrel, 18.4 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.6% barrel, 11.5 HR allowed</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>lift-pull EV profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>12.56</t>
+          <t>10.85</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>45.64</t>
+          <t>41.15</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>92.2</t>
+          <t>88.93</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>101.6676</t>
+          <t>100.9649</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>0.4559</t>
+          <t>0.457</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
         <is>
-          <t>0.2041</t>
+          <t>0.1975</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>0.3331</t>
+          <t>0.3492</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
         <is>
-          <t>71.92</t>
+          <t>73.82</t>
         </is>
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>13.68</t>
+          <t>35.71</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>43.28</t>
+          <t>40.56</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>31.15</t>
+          <t>25.43</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>13.4</t>
+          <t>11.7</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>0.228</t>
+          <t>0.2062</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>9.7</t>
+          <t>7.61</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>44.54</t>
+          <t>40.75</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>90.73</t>
+          <t>90.37</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>0.4725</t>
+          <t>0.3812</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
-          <t>0.1892</t>
+          <t>0.1407</t>
         </is>
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>28.69</t>
-        </is>
-      </c>
-      <c r="BG21" t="inlineStr"/>
-      <c r="BH21" t="inlineStr"/>
+          <t>26.41</t>
+        </is>
+      </c>
+      <c r="BG21" t="inlineStr">
+        <is>
+          <t>Out To RF</t>
+        </is>
+      </c>
+      <c r="BH21" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
       <c r="BI21" t="inlineStr">
         <is>
-          <t>Chase Field</t>
+          <t>Yankee Stadium</t>
         </is>
       </c>
       <c r="BJ21" t="inlineStr"/>
@@ -6307,47 +6311,47 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>663993</t>
+          <t>665019</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Nathaniel Lowe</t>
+          <t>Kody Clemens</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-06-20T17:35:00Z</t>
+          <t>2026-06-21T02:10:00Z</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Will Warren</t>
+          <t>Zac Gallen</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>701542</t>
+          <t>668678</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -6356,7 +6360,7 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>58.2</v>
+        <v>58.4</v>
       </c>
       <c r="M22" t="inlineStr">
         <is>
@@ -6370,58 +6374,62 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>Strong Barrel, Good Environment, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P22" t="n">
-        <v>43.4</v>
+        <v>52.4</v>
       </c>
       <c r="Q22" t="n">
-        <v>39.4</v>
+        <v>57.3</v>
       </c>
       <c r="R22" t="n">
-        <v>84.7</v>
+        <v>28.2</v>
       </c>
       <c r="S22" t="n">
-        <v>94.90000000000001</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="T22" t="n">
         <v>80</v>
       </c>
       <c r="U22" t="n">
-        <v>24.9</v>
+        <v>60</v>
       </c>
       <c r="V22" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W22" t="inlineStr">
+      <c r="Z22" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y22" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC22" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -6441,142 +6449,134 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/14, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.6% barrel, 11.5 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.7% barrel, 18.4 HR allowed</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>lift-pull EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>10.85</t>
+          <t>12.56</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>41.15</t>
+          <t>45.64</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>88.93</t>
+          <t>92.2</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>100.9649</t>
+          <t>101.6676</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>0.457</t>
+          <t>0.4559</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
         <is>
-          <t>0.1975</t>
+          <t>0.2041</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>0.3492</t>
+          <t>0.3331</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
         <is>
-          <t>73.82</t>
+          <t>71.92</t>
         </is>
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>35.71</t>
+          <t>13.68</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>40.56</t>
+          <t>43.28</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>25.43</t>
+          <t>31.15</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>11.7</t>
+          <t>13.4</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>0.2062</t>
+          <t>0.228</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>7.61</t>
+          <t>9.7</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>40.75</t>
+          <t>44.54</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>90.37</t>
+          <t>90.73</t>
         </is>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>0.3812</t>
+          <t>0.4725</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
-          <t>0.1407</t>
+          <t>0.1892</t>
         </is>
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>26.41</t>
-        </is>
-      </c>
-      <c r="BG22" t="inlineStr">
-        <is>
-          <t>Out To RF</t>
-        </is>
-      </c>
-      <c r="BH22" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
+          <t>28.69</t>
+        </is>
+      </c>
+      <c r="BG22" t="inlineStr"/>
+      <c r="BH22" t="inlineStr"/>
       <c r="BI22" t="inlineStr">
         <is>
-          <t>Yankee Stadium</t>
+          <t>Chase Field</t>
         </is>
       </c>
       <c r="BJ22" t="inlineStr"/>
@@ -6612,7 +6612,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -7452,7 +7452,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -9676,7 +9676,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -11348,7 +11348,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -11628,7 +11628,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -12464,7 +12464,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -13414,7 +13414,7 @@
       </c>
       <c r="AI47" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AJ47" t="inlineStr">
@@ -13424,7 +13424,7 @@
       </c>
       <c r="AK47" t="inlineStr">
         <is>
-          <t>Last 7 games: 1/17, 1 HR</t>
+          <t>Last 7 games: 1/18, 1 HR</t>
         </is>
       </c>
       <c r="AL47" t="inlineStr">
@@ -18872,7 +18872,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -21124,7 +21124,7 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>50.5</v>
+        <v>50.4</v>
       </c>
       <c r="M75" t="inlineStr">
         <is>
@@ -21157,7 +21157,7 @@
         <v>50</v>
       </c>
       <c r="U75" t="n">
-        <v>76.09999999999999</v>
+        <v>74.5</v>
       </c>
       <c r="V75" t="inlineStr">
         <is>
@@ -21214,7 +21214,7 @@
       </c>
       <c r="AI75" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ75" t="inlineStr">
@@ -22764,7 +22764,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -25832,7 +25832,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -34022,7 +34022,7 @@
       </c>
       <c r="AI121" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AJ121" t="inlineStr">
@@ -34032,7 +34032,7 @@
       </c>
       <c r="AK121" t="inlineStr">
         <is>
-          <t>Last 7 games: 0/17, 0 HR</t>
+          <t>Last 7 games: 0/18, 0 HR</t>
         </is>
       </c>
       <c r="AL121" t="inlineStr">
@@ -34188,7 +34188,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -38360,7 +38360,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -39476,7 +39476,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -41424,7 +41424,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -41704,7 +41704,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -55028,7 +55028,7 @@
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
@@ -71146,7 +71146,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -72538,7 +72538,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -72842,7 +72842,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>59</v>
+        <v>58.9</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -72875,7 +72875,7 @@
         <v>50</v>
       </c>
       <c r="U17" t="n">
-        <v>40.3</v>
+        <v>37.8</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
@@ -72932,7 +72932,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
@@ -72942,7 +72942,7 @@
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/15, 1 HR</t>
+          <t>Last 7 games: 4/16, 1 HR</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
@@ -73378,7 +73378,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -73913,47 +73913,47 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>665019</t>
+          <t>663993</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Kody Clemens</t>
+          <t>Nathaniel Lowe</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-06-21T02:10:00Z</t>
+          <t>2026-06-20T17:35:00Z</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Zac Gallen</t>
+          <t>Will Warren</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>668678</t>
+          <t>701542</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -73962,7 +73962,7 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>58.4</v>
+        <v>58.5</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
@@ -73976,62 +73976,58 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Good Environment, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P21" t="n">
-        <v>52.4</v>
+        <v>43.4</v>
       </c>
       <c r="Q21" t="n">
-        <v>57.3</v>
+        <v>39.4</v>
       </c>
       <c r="R21" t="n">
-        <v>28.2</v>
+        <v>84.7</v>
       </c>
       <c r="S21" t="n">
-        <v>92.09999999999999</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T21" t="n">
         <v>80</v>
       </c>
       <c r="U21" t="n">
-        <v>60</v>
+        <v>32</v>
       </c>
       <c r="V21" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y21" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr"/>
       <c r="AC21" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -74051,134 +74047,142 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Contact streak: 5/15 over last 7 games</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 9.7% barrel, 18.4 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.6% barrel, 11.5 HR allowed</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>lift-pull EV profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>12.56</t>
+          <t>10.85</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>45.64</t>
+          <t>41.15</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>92.2</t>
+          <t>88.93</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>101.6676</t>
+          <t>100.9649</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>0.4559</t>
+          <t>0.457</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
         <is>
-          <t>0.2041</t>
+          <t>0.1975</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>0.3331</t>
+          <t>0.3492</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
         <is>
-          <t>71.92</t>
+          <t>73.82</t>
         </is>
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>13.68</t>
+          <t>35.71</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>43.28</t>
+          <t>40.56</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>31.15</t>
+          <t>25.43</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>13.4</t>
+          <t>11.7</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>0.228</t>
+          <t>0.2062</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>9.7</t>
+          <t>7.61</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>44.54</t>
+          <t>40.75</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>90.73</t>
+          <t>90.37</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>0.4725</t>
+          <t>0.3812</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
-          <t>0.1892</t>
+          <t>0.1407</t>
         </is>
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>28.69</t>
-        </is>
-      </c>
-      <c r="BG21" t="inlineStr"/>
-      <c r="BH21" t="inlineStr"/>
+          <t>26.41</t>
+        </is>
+      </c>
+      <c r="BG21" t="inlineStr">
+        <is>
+          <t>Out To RF</t>
+        </is>
+      </c>
+      <c r="BH21" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
       <c r="BI21" t="inlineStr">
         <is>
-          <t>Chase Field</t>
+          <t>Yankee Stadium</t>
         </is>
       </c>
       <c r="BJ21" t="inlineStr"/>

--- a/outputs/hr_rankings.xlsx
+++ b/outputs/hr_rankings.xlsx
@@ -4928,7 +4928,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -7448,7 +7448,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -9075,27 +9075,27 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>694192</t>
+          <t>669065</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Jackson Chourio</t>
+          <t>Kyle Stowers</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-06-21T17:35:00Z</t>
+          <t>2026-06-21T17:40:00Z</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -9105,17 +9105,17 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Bryce Elder</t>
+          <t>Logan Webb</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>693821</t>
+          <t>657277</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -9124,7 +9124,7 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>55.2</v>
+        <v>55.5</v>
       </c>
       <c r="M32" t="inlineStr">
         <is>
@@ -9138,26 +9138,26 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P32" t="n">
-        <v>55.6</v>
+        <v>55.5</v>
       </c>
       <c r="Q32" t="n">
-        <v>30.7</v>
+        <v>32</v>
       </c>
       <c r="R32" t="n">
-        <v>54.9</v>
+        <v>35</v>
       </c>
       <c r="S32" t="n">
-        <v>100</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T32" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U32" t="n">
-        <v>54.7</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="V32" t="inlineStr">
         <is>
@@ -9171,7 +9171,7 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
@@ -9214,22 +9214,22 @@
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Hot streak: 3 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL32" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 5.0% barrel, 13.5 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.3% barrel, 7.0 HR allowed</t>
         </is>
       </c>
       <c r="AM32" t="inlineStr">
@@ -9239,112 +9239,112 @@
       </c>
       <c r="AN32" t="inlineStr">
         <is>
-          <t>12.85</t>
+          <t>12.8</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>46.85</t>
+          <t>51.44</t>
         </is>
       </c>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>91.47</t>
+          <t>90.75</t>
         </is>
       </c>
       <c r="AQ32" t="inlineStr">
         <is>
-          <t>102.4017</t>
+          <t>102.6403</t>
         </is>
       </c>
       <c r="AR32" t="inlineStr">
         <is>
-          <t>0.4813</t>
+          <t>0.4572</t>
         </is>
       </c>
       <c r="AS32" t="inlineStr">
         <is>
-          <t>0.2203</t>
+          <t>0.2153</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr">
         <is>
-          <t>0.3399</t>
+          <t>0.3407</t>
         </is>
       </c>
       <c r="AU32" t="inlineStr">
         <is>
-          <t>74.6</t>
+          <t>74.93</t>
         </is>
       </c>
       <c r="AV32" t="inlineStr">
         <is>
-          <t>48.54</t>
+          <t>49.88</t>
         </is>
       </c>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>31.08</t>
+          <t>46.34</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>29.62</t>
+          <t>28.56</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
-          <t>13.3</t>
+          <t>12.4</t>
         </is>
       </c>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>0.2301</t>
+          <t>0.2021</t>
         </is>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>6.34</t>
         </is>
       </c>
       <c r="BB32" t="inlineStr">
         <is>
-          <t>39.95</t>
+          <t>43.07</t>
         </is>
       </c>
       <c r="BC32" t="inlineStr">
         <is>
-          <t>89.65</t>
+          <t>89.91</t>
         </is>
       </c>
       <c r="BD32" t="inlineStr">
         <is>
-          <t>0.3745</t>
+          <t>0.3738</t>
         </is>
       </c>
       <c r="BE32" t="inlineStr">
         <is>
-          <t>0.1316</t>
+          <t>0.1212</t>
         </is>
       </c>
       <c r="BF32" t="inlineStr">
         <is>
-          <t>25.8</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="BG32" t="inlineStr">
         <is>
-          <t>R To L</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI32" t="inlineStr">
         <is>
-          <t>Truist Park</t>
+          <t>loanDepot park</t>
         </is>
       </c>
       <c r="BJ32" t="inlineStr"/>
@@ -9355,47 +9355,47 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>656811</t>
+          <t>694192</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Ryan O'Hearn</t>
+          <t>Jackson Chourio</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-06-21T19:10:00Z</t>
+          <t>2026-06-21T17:35:00Z</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Michael Lorenzen</t>
+          <t>Bryce Elder</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>547179</t>
+          <t>693821</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -9418,26 +9418,26 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P33" t="n">
-        <v>33.7</v>
+        <v>55.6</v>
       </c>
       <c r="Q33" t="n">
-        <v>51.6</v>
+        <v>30.7</v>
       </c>
       <c r="R33" t="n">
-        <v>60.2</v>
+        <v>54.9</v>
       </c>
       <c r="S33" t="n">
-        <v>94.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="T33" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U33" t="n">
-        <v>43.9</v>
+        <v>54.7</v>
       </c>
       <c r="V33" t="inlineStr">
         <is>
@@ -9451,7 +9451,7 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr">
@@ -9489,27 +9489,27 @@
       </c>
       <c r="AH33" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>Last 7 games: 9/31, 1 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL33" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 9.0% barrel, 15.9 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 5.0% barrel, 13.5 HR allowed</t>
         </is>
       </c>
       <c r="AM33" t="inlineStr">
@@ -9519,112 +9519,112 @@
       </c>
       <c r="AN33" t="inlineStr">
         <is>
-          <t>6.69</t>
+          <t>12.85</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>43.55</t>
+          <t>46.85</t>
         </is>
       </c>
       <c r="AP33" t="inlineStr">
         <is>
-          <t>89.54</t>
+          <t>91.47</t>
         </is>
       </c>
       <c r="AQ33" t="inlineStr">
         <is>
-          <t>99.5306</t>
+          <t>102.4017</t>
         </is>
       </c>
       <c r="AR33" t="inlineStr">
         <is>
-          <t>0.4157</t>
+          <t>0.4813</t>
         </is>
       </c>
       <c r="AS33" t="inlineStr">
         <is>
-          <t>0.1558</t>
+          <t>0.2203</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr">
         <is>
-          <t>0.3276</t>
+          <t>0.3399</t>
         </is>
       </c>
       <c r="AU33" t="inlineStr">
         <is>
-          <t>71.03</t>
+          <t>74.6</t>
         </is>
       </c>
       <c r="AV33" t="inlineStr">
         <is>
-          <t>12.06</t>
+          <t>48.54</t>
         </is>
       </c>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>36.42</t>
+          <t>31.08</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>28.08</t>
+          <t>29.62</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
-          <t>12.8</t>
+          <t>13.3</t>
         </is>
       </c>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>0.1728</t>
+          <t>0.2301</t>
         </is>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
-          <t>9.01</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BB33" t="inlineStr">
         <is>
-          <t>43.61</t>
+          <t>39.95</t>
         </is>
       </c>
       <c r="BC33" t="inlineStr">
         <is>
-          <t>89.72</t>
+          <t>89.65</t>
         </is>
       </c>
       <c r="BD33" t="inlineStr">
         <is>
-          <t>0.4699</t>
+          <t>0.3745</t>
         </is>
       </c>
       <c r="BE33" t="inlineStr">
         <is>
-          <t>0.1847</t>
+          <t>0.1316</t>
         </is>
       </c>
       <c r="BF33" t="inlineStr">
         <is>
-          <t>25.59</t>
+          <t>25.8</t>
         </is>
       </c>
       <c r="BG33" t="inlineStr">
         <is>
-          <t>In From LF</t>
+          <t>R To L</t>
         </is>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>77</t>
         </is>
       </c>
       <c r="BI33" t="inlineStr">
         <is>
-          <t>Coors Field</t>
+          <t>Truist Park</t>
         </is>
       </c>
       <c r="BJ33" t="inlineStr"/>
@@ -9635,32 +9635,32 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>682985</t>
+          <t>656811</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Riley Greene</t>
+          <t>Ryan O'Hearn</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-06-21T17:40:00Z</t>
+          <t>2026-06-21T19:10:00Z</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -9670,12 +9670,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Davis Martin</t>
+          <t>Michael Lorenzen</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>663436</t>
+          <t>547179</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -9684,7 +9684,7 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>55.1</v>
+        <v>55.2</v>
       </c>
       <c r="M34" t="inlineStr">
         <is>
@@ -9698,17 +9698,17 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P34" t="n">
-        <v>57.1</v>
+        <v>33.7</v>
       </c>
       <c r="Q34" t="n">
-        <v>42</v>
+        <v>51.6</v>
       </c>
       <c r="R34" t="n">
-        <v>35.6</v>
+        <v>60.2</v>
       </c>
       <c r="S34" t="n">
         <v>94.90000000000001</v>
@@ -9717,7 +9717,7 @@
         <v>80</v>
       </c>
       <c r="U34" t="n">
-        <v>7</v>
+        <v>43.9</v>
       </c>
       <c r="V34" t="inlineStr">
         <is>
@@ -9769,27 +9769,27 @@
       </c>
       <c r="AH34" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>31</t>
         </is>
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/24, 0 HR</t>
+          <t>Last 7 games: 9/31, 1 HR</t>
         </is>
       </c>
       <c r="AL34" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.4% barrel, 10.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.0% barrel, 15.9 HR allowed</t>
         </is>
       </c>
       <c r="AM34" t="inlineStr">
@@ -9799,97 +9799,97 @@
       </c>
       <c r="AN34" t="inlineStr">
         <is>
-          <t>14.09</t>
+          <t>6.69</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>48.3</t>
+          <t>43.55</t>
         </is>
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>90.88</t>
+          <t>89.54</t>
         </is>
       </c>
       <c r="AQ34" t="inlineStr">
         <is>
-          <t>102.6039</t>
+          <t>99.5306</t>
         </is>
       </c>
       <c r="AR34" t="inlineStr">
         <is>
-          <t>0.4602</t>
+          <t>0.4157</t>
         </is>
       </c>
       <c r="AS34" t="inlineStr">
         <is>
-          <t>0.213</t>
+          <t>0.1558</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr">
         <is>
-          <t>0.3446</t>
+          <t>0.3276</t>
         </is>
       </c>
       <c r="AU34" t="inlineStr">
         <is>
-          <t>75.46</t>
+          <t>71.03</t>
         </is>
       </c>
       <c r="AV34" t="inlineStr">
         <is>
-          <t>56.57</t>
+          <t>12.06</t>
         </is>
       </c>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>37.58</t>
+          <t>36.42</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>31.84</t>
+          <t>28.08</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
-          <t>16.4</t>
+          <t>12.8</t>
         </is>
       </c>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>0.1727</t>
+          <t>0.1728</t>
         </is>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
-          <t>7.42</t>
+          <t>9.01</t>
         </is>
       </c>
       <c r="BB34" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>43.61</t>
         </is>
       </c>
       <c r="BC34" t="inlineStr">
         <is>
-          <t>90.42</t>
+          <t>89.72</t>
         </is>
       </c>
       <c r="BD34" t="inlineStr">
         <is>
-          <t>0.4111</t>
+          <t>0.4699</t>
         </is>
       </c>
       <c r="BE34" t="inlineStr">
         <is>
-          <t>0.1475</t>
+          <t>0.1847</t>
         </is>
       </c>
       <c r="BF34" t="inlineStr">
         <is>
-          <t>22.22</t>
+          <t>25.59</t>
         </is>
       </c>
       <c r="BG34" t="inlineStr">
@@ -9899,12 +9899,12 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>89</t>
         </is>
       </c>
       <c r="BI34" t="inlineStr">
         <is>
-          <t>Comerica Park</t>
+          <t>Coors Field</t>
         </is>
       </c>
       <c r="BJ34" t="inlineStr"/>
@@ -9915,47 +9915,47 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>663457</t>
+          <t>682985</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Lars Nootbaar</t>
+          <t>Riley Greene</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-06-21T18:10:00Z</t>
+          <t>2026-06-21T17:40:00Z</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Stephen Kolek</t>
+          <t>Davis Martin</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>663568</t>
+          <t>663436</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -9978,26 +9978,26 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>Strong Barrel, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P35" t="n">
-        <v>60.5</v>
+        <v>57.1</v>
       </c>
       <c r="Q35" t="n">
-        <v>31.7</v>
+        <v>42</v>
       </c>
       <c r="R35" t="n">
-        <v>45.7</v>
+        <v>35.6</v>
       </c>
       <c r="S35" t="n">
-        <v>86.40000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T35" t="n">
         <v>80</v>
       </c>
       <c r="U35" t="n">
-        <v>27.7</v>
+        <v>7</v>
       </c>
       <c r="V35" t="inlineStr">
         <is>
@@ -10011,7 +10011,7 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y35" t="inlineStr">
@@ -10049,12 +10049,12 @@
       </c>
       <c r="AH35" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI35" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ35" t="inlineStr">
@@ -10064,117 +10064,117 @@
       </c>
       <c r="AK35" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/23, 0 HR</t>
+          <t>Last 7 games: 4/24, 0 HR</t>
         </is>
       </c>
       <c r="AL35" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.5% barrel, 6.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.4% barrel, 10.2 HR allowed</t>
         </is>
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>EV profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN35" t="inlineStr">
         <is>
-          <t>11.53</t>
+          <t>14.09</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>55.32</t>
+          <t>48.3</t>
         </is>
       </c>
       <c r="AP35" t="inlineStr">
         <is>
-          <t>93.82</t>
+          <t>90.88</t>
         </is>
       </c>
       <c r="AQ35" t="inlineStr">
         <is>
-          <t>102.1345</t>
+          <t>102.6039</t>
         </is>
       </c>
       <c r="AR35" t="inlineStr">
         <is>
-          <t>0.4812</t>
+          <t>0.4602</t>
         </is>
       </c>
       <c r="AS35" t="inlineStr">
         <is>
-          <t>0.2243</t>
+          <t>0.213</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr">
         <is>
-          <t>0.352</t>
+          <t>0.3446</t>
         </is>
       </c>
       <c r="AU35" t="inlineStr">
         <is>
-          <t>74.03</t>
+          <t>75.46</t>
         </is>
       </c>
       <c r="AV35" t="inlineStr">
         <is>
-          <t>45.22</t>
+          <t>56.57</t>
         </is>
       </c>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>33.45</t>
+          <t>37.58</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>31.14</t>
+          <t>31.84</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
         <is>
-          <t>5.3</t>
+          <t>16.4</t>
         </is>
       </c>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>0.162</t>
+          <t>0.1727</t>
         </is>
       </c>
       <c r="BA35" t="inlineStr">
         <is>
-          <t>6.45</t>
+          <t>7.42</t>
         </is>
       </c>
       <c r="BB35" t="inlineStr">
         <is>
-          <t>41.42</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="BC35" t="inlineStr">
         <is>
-          <t>89.7</t>
+          <t>90.42</t>
         </is>
       </c>
       <c r="BD35" t="inlineStr">
         <is>
-          <t>0.378</t>
+          <t>0.4111</t>
         </is>
       </c>
       <c r="BE35" t="inlineStr">
         <is>
-          <t>0.1215</t>
+          <t>0.1475</t>
         </is>
       </c>
       <c r="BF35" t="inlineStr">
         <is>
-          <t>21.81</t>
+          <t>22.22</t>
         </is>
       </c>
       <c r="BG35" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>In From LF</t>
         </is>
       </c>
       <c r="BH35" t="inlineStr">
@@ -10184,7 +10184,7 @@
       </c>
       <c r="BI35" t="inlineStr">
         <is>
-          <t>Kauffman Stadium</t>
+          <t>Comerica Park</t>
         </is>
       </c>
       <c r="BJ35" t="inlineStr"/>
@@ -10195,47 +10195,47 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>687263</t>
+          <t>663457</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Zach Neto</t>
+          <t>Lars Nootbaar</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-06-21T20:05:00Z</t>
+          <t>2026-06-21T18:10:00Z</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Jack Perkins</t>
+          <t>Stephen Kolek</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>678022</t>
+          <t>663568</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -10258,26 +10258,26 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P36" t="n">
-        <v>50.5</v>
+        <v>60.5</v>
       </c>
       <c r="Q36" t="n">
-        <v>30.2</v>
+        <v>31.7</v>
       </c>
       <c r="R36" t="n">
-        <v>68.40000000000001</v>
+        <v>45.7</v>
       </c>
       <c r="S36" t="n">
-        <v>93.2</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T36" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U36" t="n">
-        <v>68</v>
+        <v>27.7</v>
       </c>
       <c r="V36" t="inlineStr">
         <is>
@@ -10291,7 +10291,7 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y36" t="inlineStr">
@@ -10329,142 +10329,142 @@
       </c>
       <c r="AH36" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI36" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>Hot streak: 3 HR in last 7 games</t>
+          <t>Last 7 games: 7/23, 0 HR</t>
         </is>
       </c>
       <c r="AL36" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.2% barrel, 4.7 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.5% barrel, 6.2 HR allowed</t>
         </is>
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>fly-ball profile; pitcher allows elevated contact</t>
+          <t>EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN36" t="inlineStr">
         <is>
-          <t>13.58</t>
+          <t>11.53</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>40.58</t>
+          <t>55.32</t>
         </is>
       </c>
       <c r="AP36" t="inlineStr">
         <is>
-          <t>90.23</t>
+          <t>93.82</t>
         </is>
       </c>
       <c r="AQ36" t="inlineStr">
         <is>
-          <t>99.9843</t>
+          <t>102.1345</t>
         </is>
       </c>
       <c r="AR36" t="inlineStr">
         <is>
-          <t>0.439</t>
+          <t>0.4812</t>
         </is>
       </c>
       <c r="AS36" t="inlineStr">
         <is>
-          <t>0.2209</t>
+          <t>0.2243</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr">
         <is>
-          <t>0.3272</t>
+          <t>0.352</t>
         </is>
       </c>
       <c r="AU36" t="inlineStr">
         <is>
-          <t>70.91</t>
+          <t>74.03</t>
         </is>
       </c>
       <c r="AV36" t="inlineStr">
         <is>
-          <t>10.5</t>
+          <t>45.22</t>
         </is>
       </c>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>49.51</t>
+          <t>33.45</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>36.29</t>
+          <t>31.14</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>5.3</t>
         </is>
       </c>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>0.2226</t>
+          <t>0.162</t>
         </is>
       </c>
       <c r="BA36" t="inlineStr">
         <is>
-          <t>7.15</t>
+          <t>6.45</t>
         </is>
       </c>
       <c r="BB36" t="inlineStr">
         <is>
-          <t>35.04</t>
+          <t>41.42</t>
         </is>
       </c>
       <c r="BC36" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>89.7</t>
         </is>
       </c>
       <c r="BD36" t="inlineStr">
         <is>
-          <t>0.3587</t>
+          <t>0.378</t>
         </is>
       </c>
       <c r="BE36" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.1215</t>
         </is>
       </c>
       <c r="BF36" t="inlineStr">
         <is>
-          <t>30.74</t>
+          <t>21.81</t>
         </is>
       </c>
       <c r="BG36" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>74</t>
         </is>
       </c>
       <c r="BI36" t="inlineStr">
         <is>
-          <t>Sutter Health Park</t>
+          <t>Kauffman Stadium</t>
         </is>
       </c>
       <c r="BJ36" t="inlineStr"/>
@@ -10475,27 +10475,27 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>680776</t>
+          <t>687263</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Jarren Duran</t>
+          <t>Zach Neto</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-06-21T20:10:00Z</t>
+          <t>2026-06-21T20:05:00Z</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -10505,17 +10505,17 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Logan Gilbert</t>
+          <t>Jack Perkins</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>669302</t>
+          <t>678022</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -10538,26 +10538,26 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>Strong Barrel, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P37" t="n">
-        <v>41.4</v>
+        <v>50.5</v>
       </c>
       <c r="Q37" t="n">
-        <v>54.9</v>
+        <v>30.2</v>
       </c>
       <c r="R37" t="n">
-        <v>44.4</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="S37" t="n">
-        <v>86.40000000000001</v>
+        <v>93.2</v>
       </c>
       <c r="T37" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U37" t="n">
-        <v>46.4</v>
+        <v>68</v>
       </c>
       <c r="V37" t="inlineStr">
         <is>
@@ -10571,7 +10571,7 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y37" t="inlineStr">
@@ -10609,142 +10609,142 @@
       </c>
       <c r="AH37" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI37" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Hot streak: 3 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL37" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 10.8% barrel, 15.1 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.2% barrel, 4.7 HR allowed</t>
         </is>
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>fly-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN37" t="inlineStr">
         <is>
-          <t>11.03</t>
+          <t>13.58</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>41.76</t>
+          <t>40.58</t>
         </is>
       </c>
       <c r="AP37" t="inlineStr">
         <is>
-          <t>90.54</t>
+          <t>90.23</t>
         </is>
       </c>
       <c r="AQ37" t="inlineStr">
         <is>
-          <t>102.3517</t>
+          <t>99.9843</t>
         </is>
       </c>
       <c r="AR37" t="inlineStr">
         <is>
-          <t>0.3953</t>
+          <t>0.439</t>
         </is>
       </c>
       <c r="AS37" t="inlineStr">
         <is>
-          <t>0.1606</t>
+          <t>0.2209</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr">
         <is>
-          <t>0.3043</t>
+          <t>0.3272</t>
         </is>
       </c>
       <c r="AU37" t="inlineStr">
         <is>
-          <t>75.22</t>
+          <t>70.91</t>
         </is>
       </c>
       <c r="AV37" t="inlineStr">
         <is>
-          <t>52.26</t>
+          <t>10.5</t>
         </is>
       </c>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>40.51</t>
+          <t>49.51</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>21.39</t>
+          <t>36.29</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr">
         <is>
-          <t>13.2</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>0.1783</t>
+          <t>0.2226</t>
         </is>
       </c>
       <c r="BA37" t="inlineStr">
         <is>
-          <t>10.84</t>
+          <t>7.15</t>
         </is>
       </c>
       <c r="BB37" t="inlineStr">
         <is>
-          <t>44.01</t>
+          <t>35.04</t>
         </is>
       </c>
       <c r="BC37" t="inlineStr">
         <is>
-          <t>90.73</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="BD37" t="inlineStr">
         <is>
-          <t>0.4041</t>
+          <t>0.3587</t>
         </is>
       </c>
       <c r="BE37" t="inlineStr">
         <is>
-          <t>0.1729</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="BF37" t="inlineStr">
         <is>
-          <t>29.94</t>
+          <t>30.74</t>
         </is>
       </c>
       <c r="BG37" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>83</t>
         </is>
       </c>
       <c r="BI37" t="inlineStr">
         <is>
-          <t>T-Mobile Park</t>
+          <t>Sutter Health Park</t>
         </is>
       </c>
       <c r="BJ37" t="inlineStr"/>
@@ -10755,32 +10755,32 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>641343</t>
+          <t>680776</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Jake Bauers</t>
+          <t>Jarren Duran</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-06-21T17:35:00Z</t>
+          <t>2026-06-21T20:10:00Z</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -10790,12 +10790,12 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Bryce Elder</t>
+          <t>Logan Gilbert</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>693821</t>
+          <t>669302</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -10804,7 +10804,7 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>55</v>
+        <v>55.1</v>
       </c>
       <c r="M38" t="inlineStr">
         <is>
@@ -10822,13 +10822,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>59.8</v>
+        <v>41.4</v>
       </c>
       <c r="Q38" t="n">
-        <v>30.7</v>
+        <v>54.9</v>
       </c>
       <c r="R38" t="n">
-        <v>54.9</v>
+        <v>44.4</v>
       </c>
       <c r="S38" t="n">
         <v>86.40000000000001</v>
@@ -10837,7 +10837,7 @@
         <v>80</v>
       </c>
       <c r="U38" t="n">
-        <v>7</v>
+        <v>46.4</v>
       </c>
       <c r="V38" t="inlineStr">
         <is>
@@ -10889,142 +10889,142 @@
       </c>
       <c r="AH38" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI38" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK38" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/18, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL38" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 5.0% barrel, 13.5 HR allowed</t>
+          <t>platoon edge; pitcher baseline 10.8% barrel, 15.1 HR allowed</t>
         </is>
       </c>
       <c r="AM38" t="inlineStr">
         <is>
-          <t>EV profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN38" t="inlineStr">
         <is>
-          <t>13.49</t>
+          <t>11.03</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>51.55</t>
+          <t>41.76</t>
         </is>
       </c>
       <c r="AP38" t="inlineStr">
         <is>
-          <t>92.33</t>
+          <t>90.54</t>
         </is>
       </c>
       <c r="AQ38" t="inlineStr">
         <is>
-          <t>103.2106</t>
+          <t>102.3517</t>
         </is>
       </c>
       <c r="AR38" t="inlineStr">
         <is>
-          <t>0.4626</t>
+          <t>0.3953</t>
         </is>
       </c>
       <c r="AS38" t="inlineStr">
         <is>
-          <t>0.2153</t>
+          <t>0.1606</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr">
         <is>
-          <t>0.3575</t>
+          <t>0.3043</t>
         </is>
       </c>
       <c r="AU38" t="inlineStr">
         <is>
-          <t>76.78</t>
+          <t>75.22</t>
         </is>
       </c>
       <c r="AV38" t="inlineStr">
         <is>
-          <t>72.8</t>
+          <t>52.26</t>
         </is>
       </c>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>38.52</t>
+          <t>40.51</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>28.93</t>
+          <t>21.39</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr">
         <is>
-          <t>11.2</t>
+          <t>13.2</t>
         </is>
       </c>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>0.2109</t>
+          <t>0.1783</t>
         </is>
       </c>
       <c r="BA38" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>10.84</t>
         </is>
       </c>
       <c r="BB38" t="inlineStr">
         <is>
-          <t>39.95</t>
+          <t>44.01</t>
         </is>
       </c>
       <c r="BC38" t="inlineStr">
         <is>
-          <t>89.65</t>
+          <t>90.73</t>
         </is>
       </c>
       <c r="BD38" t="inlineStr">
         <is>
-          <t>0.3745</t>
+          <t>0.4041</t>
         </is>
       </c>
       <c r="BE38" t="inlineStr">
         <is>
-          <t>0.1316</t>
+          <t>0.1729</t>
         </is>
       </c>
       <c r="BF38" t="inlineStr">
         <is>
-          <t>25.8</t>
+          <t>29.94</t>
         </is>
       </c>
       <c r="BG38" t="inlineStr">
         <is>
-          <t>R To L</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI38" t="inlineStr">
         <is>
-          <t>Truist Park</t>
+          <t>T-Mobile Park</t>
         </is>
       </c>
       <c r="BJ38" t="inlineStr"/>
@@ -11035,27 +11035,27 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>693307</t>
+          <t>641343</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Dillon Dingler</t>
+          <t>Jake Bauers</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-06-21T17:40:00Z</t>
+          <t>2026-06-21T17:35:00Z</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -11065,17 +11065,17 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Davis Martin</t>
+          <t>Bryce Elder</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>663436</t>
+          <t>693821</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -11098,26 +11098,26 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P39" t="n">
-        <v>54.4</v>
+        <v>59.8</v>
       </c>
       <c r="Q39" t="n">
-        <v>42</v>
+        <v>30.7</v>
       </c>
       <c r="R39" t="n">
-        <v>35.6</v>
+        <v>54.9</v>
       </c>
       <c r="S39" t="n">
-        <v>100</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T39" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U39" t="n">
-        <v>62.8</v>
+        <v>7</v>
       </c>
       <c r="V39" t="inlineStr">
         <is>
@@ -11131,7 +11131,7 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y39" t="inlineStr">
@@ -11169,142 +11169,142 @@
       </c>
       <c r="AH39" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI39" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
         <is>
-          <t>Contact streak: 10/24 over last 7 games</t>
+          <t>Last 7 games: 3/18, 0 HR</t>
         </is>
       </c>
       <c r="AL39" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.4% barrel, 10.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 5.0% barrel, 13.5 HR allowed</t>
         </is>
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN39" t="inlineStr">
         <is>
-          <t>11.65</t>
+          <t>13.49</t>
         </is>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>48.36</t>
+          <t>51.55</t>
         </is>
       </c>
       <c r="AP39" t="inlineStr">
         <is>
-          <t>90.42</t>
+          <t>92.33</t>
         </is>
       </c>
       <c r="AQ39" t="inlineStr">
         <is>
-          <t>101.468</t>
+          <t>103.2106</t>
         </is>
       </c>
       <c r="AR39" t="inlineStr">
         <is>
-          <t>0.5338</t>
+          <t>0.4626</t>
         </is>
       </c>
       <c r="AS39" t="inlineStr">
         <is>
-          <t>0.2382</t>
+          <t>0.2153</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr">
         <is>
-          <t>0.3832</t>
+          <t>0.3575</t>
         </is>
       </c>
       <c r="AU39" t="inlineStr">
         <is>
-          <t>71.84</t>
+          <t>76.78</t>
         </is>
       </c>
       <c r="AV39" t="inlineStr">
         <is>
-          <t>16.28</t>
+          <t>72.8</t>
         </is>
       </c>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>41.64</t>
+          <t>38.52</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>29.48</t>
+          <t>28.93</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr">
         <is>
-          <t>15.8</t>
+          <t>11.2</t>
         </is>
       </c>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>0.2331</t>
+          <t>0.2109</t>
         </is>
       </c>
       <c r="BA39" t="inlineStr">
         <is>
-          <t>7.42</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BB39" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>39.95</t>
         </is>
       </c>
       <c r="BC39" t="inlineStr">
         <is>
-          <t>90.42</t>
+          <t>89.65</t>
         </is>
       </c>
       <c r="BD39" t="inlineStr">
         <is>
-          <t>0.4111</t>
+          <t>0.3745</t>
         </is>
       </c>
       <c r="BE39" t="inlineStr">
         <is>
-          <t>0.1475</t>
+          <t>0.1316</t>
         </is>
       </c>
       <c r="BF39" t="inlineStr">
         <is>
-          <t>22.22</t>
+          <t>25.8</t>
         </is>
       </c>
       <c r="BG39" t="inlineStr">
         <is>
-          <t>In From LF</t>
+          <t>R To L</t>
         </is>
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>77</t>
         </is>
       </c>
       <c r="BI39" t="inlineStr">
         <is>
-          <t>Comerica Park</t>
+          <t>Truist Park</t>
         </is>
       </c>
       <c r="BJ39" t="inlineStr"/>
@@ -11315,32 +11315,32 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>650489</t>
+          <t>693307</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Willi Castro</t>
+          <t>Dillon Dingler</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-06-21T19:10:00Z</t>
+          <t>2026-06-21T17:40:00Z</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -11350,12 +11350,12 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Jared Jones</t>
+          <t>Davis Martin</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>683003</t>
+          <t>663436</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -11364,7 +11364,7 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>54.8</v>
+        <v>55</v>
       </c>
       <c r="M40" t="inlineStr">
         <is>
@@ -11378,26 +11378,26 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P40" t="n">
-        <v>27.2</v>
+        <v>54.4</v>
       </c>
       <c r="Q40" t="n">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="R40" t="n">
-        <v>60.2</v>
+        <v>35.6</v>
       </c>
       <c r="S40" t="n">
         <v>100</v>
       </c>
       <c r="T40" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U40" t="n">
-        <v>70.8</v>
+        <v>62.8</v>
       </c>
       <c r="V40" t="inlineStr">
         <is>
@@ -11432,7 +11432,7 @@
       <c r="AB40" t="inlineStr"/>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD40" t="inlineStr"/>
@@ -11449,27 +11449,27 @@
       </c>
       <c r="AH40" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AI40" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Contact streak: 10/24 over last 7 games</t>
         </is>
       </c>
       <c r="AL40" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 9.3% barrel, 4.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.4% barrel, 10.2 HR allowed</t>
         </is>
       </c>
       <c r="AM40" t="inlineStr">
@@ -11479,97 +11479,97 @@
       </c>
       <c r="AN40" t="inlineStr">
         <is>
-          <t>5.87</t>
+          <t>11.65</t>
         </is>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>40.59</t>
+          <t>48.36</t>
         </is>
       </c>
       <c r="AP40" t="inlineStr">
         <is>
-          <t>88.03</t>
+          <t>90.42</t>
         </is>
       </c>
       <c r="AQ40" t="inlineStr">
         <is>
-          <t>99.923</t>
+          <t>101.468</t>
         </is>
       </c>
       <c r="AR40" t="inlineStr">
         <is>
-          <t>0.3617</t>
+          <t>0.5338</t>
         </is>
       </c>
       <c r="AS40" t="inlineStr">
         <is>
-          <t>0.1295</t>
+          <t>0.2382</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr">
         <is>
-          <t>0.3025</t>
+          <t>0.3832</t>
         </is>
       </c>
       <c r="AU40" t="inlineStr">
         <is>
-          <t>72.37</t>
+          <t>71.84</t>
         </is>
       </c>
       <c r="AV40" t="inlineStr">
         <is>
-          <t>23.62</t>
+          <t>16.28</t>
         </is>
       </c>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>42.88</t>
+          <t>41.64</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>30.9</t>
+          <t>29.48</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr">
         <is>
-          <t>6.8</t>
+          <t>15.8</t>
         </is>
       </c>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>0.1295</t>
+          <t>0.2331</t>
         </is>
       </c>
       <c r="BA40" t="inlineStr">
         <is>
-          <t>9.3</t>
+          <t>7.42</t>
         </is>
       </c>
       <c r="BB40" t="inlineStr">
         <is>
-          <t>42.6</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="BC40" t="inlineStr">
         <is>
-          <t>89.7</t>
+          <t>90.42</t>
         </is>
       </c>
       <c r="BD40" t="inlineStr">
         <is>
-          <t>0.481</t>
+          <t>0.4111</t>
         </is>
       </c>
       <c r="BE40" t="inlineStr">
         <is>
-          <t>0.212</t>
+          <t>0.1475</t>
         </is>
       </c>
       <c r="BF40" t="inlineStr">
         <is>
-          <t>29.6</t>
+          <t>22.22</t>
         </is>
       </c>
       <c r="BG40" t="inlineStr">
@@ -11579,12 +11579,12 @@
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>74</t>
         </is>
       </c>
       <c r="BI40" t="inlineStr">
         <is>
-          <t>Coors Field</t>
+          <t>Comerica Park</t>
         </is>
       </c>
       <c r="BJ40" t="inlineStr"/>
@@ -11595,32 +11595,32 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>643217</t>
+          <t>650489</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Andrew Benintendi</t>
+          <t>Willi Castro</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-06-21T17:40:00Z</t>
+          <t>2026-06-21T19:10:00Z</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -11630,12 +11630,12 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Keider Montero</t>
+          <t>Jared Jones</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>672456</t>
+          <t>683003</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -11644,7 +11644,7 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>54.6</v>
+        <v>54.8</v>
       </c>
       <c r="M41" t="inlineStr">
         <is>
@@ -11658,26 +11658,26 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P41" t="n">
-        <v>43.8</v>
+        <v>27.2</v>
       </c>
       <c r="Q41" t="n">
-        <v>43.3</v>
+        <v>52</v>
       </c>
       <c r="R41" t="n">
-        <v>35.6</v>
+        <v>60.2</v>
       </c>
       <c r="S41" t="n">
         <v>100</v>
       </c>
       <c r="T41" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="U41" t="n">
-        <v>64.8</v>
+        <v>70.8</v>
       </c>
       <c r="V41" t="inlineStr">
         <is>
@@ -11712,7 +11712,7 @@
       <c r="AB41" t="inlineStr"/>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD41" t="inlineStr"/>
@@ -11729,12 +11729,12 @@
       </c>
       <c r="AH41" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI41" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ41" t="inlineStr">
@@ -11749,7 +11749,7 @@
       </c>
       <c r="AL41" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.3% barrel, 10.4 HR allowed</t>
+          <t>switch hitter; pitcher baseline 9.3% barrel, 4.0 HR allowed</t>
         </is>
       </c>
       <c r="AM41" t="inlineStr">
@@ -11759,97 +11759,97 @@
       </c>
       <c r="AN41" t="inlineStr">
         <is>
-          <t>11.24</t>
+          <t>5.87</t>
         </is>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>45.16</t>
+          <t>40.59</t>
         </is>
       </c>
       <c r="AP41" t="inlineStr">
         <is>
-          <t>89.19</t>
+          <t>88.03</t>
         </is>
       </c>
       <c r="AQ41" t="inlineStr">
         <is>
-          <t>98.9804</t>
+          <t>99.923</t>
         </is>
       </c>
       <c r="AR41" t="inlineStr">
         <is>
-          <t>0.4342</t>
+          <t>0.3617</t>
         </is>
       </c>
       <c r="AS41" t="inlineStr">
         <is>
-          <t>0.1907</t>
+          <t>0.1295</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr">
         <is>
-          <t>0.3221</t>
+          <t>0.3025</t>
         </is>
       </c>
       <c r="AU41" t="inlineStr">
         <is>
-          <t>69.33</t>
+          <t>72.37</t>
         </is>
       </c>
       <c r="AV41" t="inlineStr">
         <is>
-          <t>4.01</t>
+          <t>23.62</t>
         </is>
       </c>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>51.71</t>
+          <t>42.88</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>33.18</t>
+          <t>30.9</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr">
         <is>
-          <t>12.3</t>
+          <t>6.8</t>
         </is>
       </c>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>0.1931</t>
+          <t>0.1295</t>
         </is>
       </c>
       <c r="BA41" t="inlineStr">
         <is>
-          <t>8.34</t>
+          <t>9.3</t>
         </is>
       </c>
       <c r="BB41" t="inlineStr">
         <is>
-          <t>39.68</t>
+          <t>42.6</t>
         </is>
       </c>
       <c r="BC41" t="inlineStr">
         <is>
-          <t>89.45</t>
+          <t>89.7</t>
         </is>
       </c>
       <c r="BD41" t="inlineStr">
         <is>
-          <t>0.4159</t>
+          <t>0.481</t>
         </is>
       </c>
       <c r="BE41" t="inlineStr">
         <is>
-          <t>0.1727</t>
+          <t>0.212</t>
         </is>
       </c>
       <c r="BF41" t="inlineStr">
         <is>
-          <t>27.66</t>
+          <t>29.6</t>
         </is>
       </c>
       <c r="BG41" t="inlineStr">
@@ -11859,12 +11859,12 @@
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>89</t>
         </is>
       </c>
       <c r="BI41" t="inlineStr">
         <is>
-          <t>Comerica Park</t>
+          <t>Coors Field</t>
         </is>
       </c>
       <c r="BJ41" t="inlineStr"/>
@@ -11875,47 +11875,47 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>676475</t>
+          <t>643217</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Alec Burleson</t>
+          <t>Andrew Benintendi</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-06-21T18:10:00Z</t>
+          <t>2026-06-21T17:40:00Z</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Stephen Kolek</t>
+          <t>Keider Montero</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>663568</t>
+          <t>672456</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -11924,7 +11924,7 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>54.5</v>
+        <v>54.6</v>
       </c>
       <c r="M42" t="inlineStr">
         <is>
@@ -11942,22 +11942,22 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>53.9</v>
+        <v>43.8</v>
       </c>
       <c r="Q42" t="n">
-        <v>31.7</v>
+        <v>43.3</v>
       </c>
       <c r="R42" t="n">
-        <v>45.7</v>
+        <v>35.6</v>
       </c>
       <c r="S42" t="n">
-        <v>96.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="T42" t="n">
         <v>80</v>
       </c>
       <c r="U42" t="n">
-        <v>31.4</v>
+        <v>64.8</v>
       </c>
       <c r="V42" t="inlineStr">
         <is>
@@ -11971,7 +11971,7 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y42" t="inlineStr">
@@ -12009,27 +12009,27 @@
       </c>
       <c r="AH42" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI42" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/29, 1 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL42" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.5% barrel, 6.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.3% barrel, 10.4 HR allowed</t>
         </is>
       </c>
       <c r="AM42" t="inlineStr">
@@ -12039,102 +12039,102 @@
       </c>
       <c r="AN42" t="inlineStr">
         <is>
-          <t>10.69</t>
+          <t>11.24</t>
         </is>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>46.71</t>
+          <t>45.16</t>
         </is>
       </c>
       <c r="AP42" t="inlineStr">
         <is>
-          <t>91.42</t>
+          <t>89.19</t>
         </is>
       </c>
       <c r="AQ42" t="inlineStr">
         <is>
-          <t>101.6192</t>
+          <t>98.9804</t>
         </is>
       </c>
       <c r="AR42" t="inlineStr">
         <is>
-          <t>0.527</t>
+          <t>0.4342</t>
         </is>
       </c>
       <c r="AS42" t="inlineStr">
         <is>
-          <t>0.2389</t>
+          <t>0.1907</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr">
         <is>
-          <t>0.3744</t>
+          <t>0.3221</t>
         </is>
       </c>
       <c r="AU42" t="inlineStr">
         <is>
-          <t>72.68</t>
+          <t>69.33</t>
         </is>
       </c>
       <c r="AV42" t="inlineStr">
         <is>
-          <t>27.31</t>
+          <t>4.01</t>
         </is>
       </c>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>43.05</t>
+          <t>51.71</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>29.5</t>
+          <t>33.18</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr">
         <is>
-          <t>14.5</t>
+          <t>12.3</t>
         </is>
       </c>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>0.1921</t>
+          <t>0.1931</t>
         </is>
       </c>
       <c r="BA42" t="inlineStr">
         <is>
-          <t>6.45</t>
+          <t>8.34</t>
         </is>
       </c>
       <c r="BB42" t="inlineStr">
         <is>
-          <t>41.42</t>
+          <t>39.68</t>
         </is>
       </c>
       <c r="BC42" t="inlineStr">
         <is>
-          <t>89.7</t>
+          <t>89.45</t>
         </is>
       </c>
       <c r="BD42" t="inlineStr">
         <is>
-          <t>0.378</t>
+          <t>0.4159</t>
         </is>
       </c>
       <c r="BE42" t="inlineStr">
         <is>
-          <t>0.1215</t>
+          <t>0.1727</t>
         </is>
       </c>
       <c r="BF42" t="inlineStr">
         <is>
-          <t>21.81</t>
+          <t>27.66</t>
         </is>
       </c>
       <c r="BG42" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>In From LF</t>
         </is>
       </c>
       <c r="BH42" t="inlineStr">
@@ -12144,7 +12144,7 @@
       </c>
       <c r="BI42" t="inlineStr">
         <is>
-          <t>Kauffman Stadium</t>
+          <t>Comerica Park</t>
         </is>
       </c>
       <c r="BJ42" t="inlineStr"/>
@@ -12155,27 +12155,27 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>669065</t>
+          <t>676475</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Kyle Stowers</t>
+          <t>Alec Burleson</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-06-21T17:40:00Z</t>
+          <t>2026-06-21T18:10:00Z</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -12185,17 +12185,17 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Logan Webb</t>
+          <t>Stephen Kolek</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>657277</t>
+          <t>663568</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -12204,7 +12204,7 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>54.4</v>
+        <v>54.5</v>
       </c>
       <c r="M43" t="inlineStr">
         <is>
@@ -12222,22 +12222,22 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>55.5</v>
+        <v>53.9</v>
       </c>
       <c r="Q43" t="n">
-        <v>32</v>
+        <v>31.7</v>
       </c>
       <c r="R43" t="n">
-        <v>35</v>
+        <v>45.7</v>
       </c>
       <c r="S43" t="n">
-        <v>94.90000000000001</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T43" t="n">
         <v>80</v>
       </c>
       <c r="U43" t="n">
-        <v>52.8</v>
+        <v>31.4</v>
       </c>
       <c r="V43" t="inlineStr">
         <is>
@@ -12251,7 +12251,7 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y43" t="inlineStr">
@@ -12289,27 +12289,27 @@
       </c>
       <c r="AH43" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI43" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 6/29, 1 HR</t>
         </is>
       </c>
       <c r="AL43" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.3% barrel, 7.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.5% barrel, 6.2 HR allowed</t>
         </is>
       </c>
       <c r="AM43" t="inlineStr">
@@ -12319,112 +12319,112 @@
       </c>
       <c r="AN43" t="inlineStr">
         <is>
-          <t>12.8</t>
+          <t>10.69</t>
         </is>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>51.44</t>
+          <t>46.71</t>
         </is>
       </c>
       <c r="AP43" t="inlineStr">
         <is>
-          <t>90.75</t>
+          <t>91.42</t>
         </is>
       </c>
       <c r="AQ43" t="inlineStr">
         <is>
-          <t>102.6403</t>
+          <t>101.6192</t>
         </is>
       </c>
       <c r="AR43" t="inlineStr">
         <is>
-          <t>0.4572</t>
+          <t>0.527</t>
         </is>
       </c>
       <c r="AS43" t="inlineStr">
         <is>
-          <t>0.2153</t>
+          <t>0.2389</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr">
         <is>
-          <t>0.3407</t>
+          <t>0.3744</t>
         </is>
       </c>
       <c r="AU43" t="inlineStr">
         <is>
-          <t>74.93</t>
+          <t>72.68</t>
         </is>
       </c>
       <c r="AV43" t="inlineStr">
         <is>
-          <t>49.88</t>
+          <t>27.31</t>
         </is>
       </c>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>46.34</t>
+          <t>43.05</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>28.56</t>
+          <t>29.5</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">
         <is>
-          <t>12.4</t>
+          <t>14.5</t>
         </is>
       </c>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>0.2021</t>
+          <t>0.1921</t>
         </is>
       </c>
       <c r="BA43" t="inlineStr">
         <is>
-          <t>6.34</t>
+          <t>6.45</t>
         </is>
       </c>
       <c r="BB43" t="inlineStr">
         <is>
-          <t>43.07</t>
+          <t>41.42</t>
         </is>
       </c>
       <c r="BC43" t="inlineStr">
         <is>
-          <t>89.91</t>
+          <t>89.7</t>
         </is>
       </c>
       <c r="BD43" t="inlineStr">
         <is>
-          <t>0.3738</t>
+          <t>0.378</t>
         </is>
       </c>
       <c r="BE43" t="inlineStr">
         <is>
-          <t>0.1212</t>
+          <t>0.1215</t>
         </is>
       </c>
       <c r="BF43" t="inlineStr">
         <is>
-          <t>17.25</t>
+          <t>21.81</t>
         </is>
       </c>
       <c r="BG43" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH43" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>74</t>
         </is>
       </c>
       <c r="BI43" t="inlineStr">
         <is>
-          <t>loanDepot park</t>
+          <t>Kauffman Stadium</t>
         </is>
       </c>
       <c r="BJ43" t="inlineStr"/>
@@ -12740,7 +12740,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -21132,7 +21132,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -22812,7 +22812,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -25588,7 +25588,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -29224,7 +29224,7 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>48.6</v>
+        <v>48.5</v>
       </c>
       <c r="M104" t="inlineStr">
         <is>
@@ -29257,7 +29257,7 @@
         <v>80</v>
       </c>
       <c r="U104" t="n">
-        <v>63.7</v>
+        <v>61.5</v>
       </c>
       <c r="V104" t="inlineStr">
         <is>
@@ -29314,7 +29314,7 @@
       </c>
       <c r="AI104" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ104" t="inlineStr">
@@ -30600,7 +30600,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -37032,7 +37032,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -39828,7 +39828,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -46764,7 +46764,7 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -48156,7 +48156,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -54804,7 +54804,7 @@
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
@@ -55364,7 +55364,7 @@
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
@@ -58111,27 +58111,27 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>665923</t>
+          <t>682622</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Esteury Ruiz</t>
+          <t>Noelvi Marte</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>2026-06-21T17:40:00Z</t>
+          <t>2026-06-21T17:35:00Z</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
@@ -58146,12 +58146,12 @@
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t>Logan Webb</t>
+          <t>Elmer Rodríguez</t>
         </is>
       </c>
       <c r="J208" t="inlineStr">
         <is>
-          <t>657277</t>
+          <t>695684</t>
         </is>
       </c>
       <c r="K208" t="inlineStr">
@@ -58160,7 +58160,7 @@
         </is>
       </c>
       <c r="L208" t="n">
-        <v>37.5</v>
+        <v>37.4</v>
       </c>
       <c r="M208" t="inlineStr">
         <is>
@@ -58178,13 +58178,13 @@
         </is>
       </c>
       <c r="P208" t="n">
-        <v>24.1</v>
+        <v>26.6</v>
       </c>
       <c r="Q208" t="n">
-        <v>32</v>
+        <v>17.3</v>
       </c>
       <c r="R208" t="n">
-        <v>35</v>
+        <v>50.7</v>
       </c>
       <c r="S208" t="n">
         <v>64.3</v>
@@ -58193,7 +58193,7 @@
         <v>50</v>
       </c>
       <c r="U208" t="n">
-        <v>63.3</v>
+        <v>68.3</v>
       </c>
       <c r="V208" t="inlineStr">
         <is>
@@ -58228,7 +58228,7 @@
       <c r="AB208" t="inlineStr"/>
       <c r="AC208" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD208" t="inlineStr"/>
@@ -58245,27 +58245,27 @@
       </c>
       <c r="AH208" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI208" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ208" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AK208" t="inlineStr">
         <is>
-          <t>Contact streak: 6/14 over last 7 games</t>
+          <t>Hot streak: 3 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL208" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.3% barrel, 7.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 4.3% barrel, 0.0 HR allowed</t>
         </is>
       </c>
       <c r="AM208" t="inlineStr">
@@ -58275,112 +58275,112 @@
       </c>
       <c r="AN208" t="inlineStr">
         <is>
-          <t>8.26</t>
+          <t>7.14</t>
         </is>
       </c>
       <c r="AO208" t="inlineStr">
         <is>
-          <t>30.73</t>
+          <t>32.31</t>
         </is>
       </c>
       <c r="AP208" t="inlineStr">
         <is>
-          <t>85.63</t>
+          <t>88.57</t>
         </is>
       </c>
       <c r="AQ208" t="inlineStr">
         <is>
-          <t>96.5176</t>
+          <t>99.2676</t>
         </is>
       </c>
       <c r="AR208" t="inlineStr">
         <is>
-          <t>0.3489</t>
+          <t>0.3781</t>
         </is>
       </c>
       <c r="AS208" t="inlineStr">
         <is>
-          <t>0.1582</t>
+          <t>0.1569</t>
         </is>
       </c>
       <c r="AT208" t="inlineStr">
         <is>
-          <t>0.2889</t>
+          <t>0.2844</t>
         </is>
       </c>
       <c r="AU208" t="inlineStr">
         <is>
-          <t>71.45</t>
+          <t>72.53</t>
         </is>
       </c>
       <c r="AV208" t="inlineStr">
         <is>
-          <t>15.65</t>
+          <t>26.06</t>
         </is>
       </c>
       <c r="AW208" t="inlineStr">
         <is>
-          <t>44.8</t>
+          <t>50.52</t>
         </is>
       </c>
       <c r="AX208" t="inlineStr">
         <is>
-          <t>27.79</t>
+          <t>19.03</t>
         </is>
       </c>
       <c r="AY208" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>6.3</t>
         </is>
       </c>
       <c r="AZ208" t="inlineStr">
         <is>
-          <t>0.2529</t>
+          <t>0.1808</t>
         </is>
       </c>
       <c r="BA208" t="inlineStr">
         <is>
-          <t>6.34</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="BB208" t="inlineStr">
         <is>
-          <t>43.07</t>
+          <t>37.0</t>
         </is>
       </c>
       <c r="BC208" t="inlineStr">
         <is>
-          <t>89.91</t>
+          <t>88.1</t>
         </is>
       </c>
       <c r="BD208" t="inlineStr">
         <is>
-          <t>0.3738</t>
+          <t>0.375</t>
         </is>
       </c>
       <c r="BE208" t="inlineStr">
         <is>
-          <t>0.1212</t>
+          <t>0.089</t>
         </is>
       </c>
       <c r="BF208" t="inlineStr">
         <is>
-          <t>17.25</t>
+          <t>19.6</t>
         </is>
       </c>
       <c r="BG208" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>In From LF</t>
         </is>
       </c>
       <c r="BH208" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>79</t>
         </is>
       </c>
       <c r="BI208" t="inlineStr">
         <is>
-          <t>loanDepot park</t>
+          <t>Yankee Stadium</t>
         </is>
       </c>
       <c r="BJ208" t="inlineStr"/>
@@ -58391,27 +58391,27 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>682622</t>
+          <t>665923</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Noelvi Marte</t>
+          <t>Esteury Ruiz</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>2026-06-21T17:35:00Z</t>
+          <t>2026-06-21T17:40:00Z</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
@@ -58426,12 +58426,12 @@
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>Elmer Rodríguez</t>
+          <t>Logan Webb</t>
         </is>
       </c>
       <c r="J209" t="inlineStr">
         <is>
-          <t>695684</t>
+          <t>657277</t>
         </is>
       </c>
       <c r="K209" t="inlineStr">
@@ -58458,13 +58458,13 @@
         </is>
       </c>
       <c r="P209" t="n">
-        <v>26.6</v>
+        <v>24.1</v>
       </c>
       <c r="Q209" t="n">
-        <v>17.3</v>
+        <v>32</v>
       </c>
       <c r="R209" t="n">
-        <v>50.7</v>
+        <v>35</v>
       </c>
       <c r="S209" t="n">
         <v>64.3</v>
@@ -58473,7 +58473,7 @@
         <v>50</v>
       </c>
       <c r="U209" t="n">
-        <v>68.3</v>
+        <v>60.3</v>
       </c>
       <c r="V209" t="inlineStr">
         <is>
@@ -58508,7 +58508,7 @@
       <c r="AB209" t="inlineStr"/>
       <c r="AC209" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD209" t="inlineStr"/>
@@ -58525,27 +58525,27 @@
       </c>
       <c r="AH209" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI209" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AJ209" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK209" t="inlineStr">
         <is>
-          <t>Hot streak: 3 HR in last 7 games</t>
+          <t>Contact streak: 6/15 over last 7 games</t>
         </is>
       </c>
       <c r="AL209" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 4.3% barrel, 0.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.3% barrel, 7.0 HR allowed</t>
         </is>
       </c>
       <c r="AM209" t="inlineStr">
@@ -58555,112 +58555,112 @@
       </c>
       <c r="AN209" t="inlineStr">
         <is>
-          <t>7.14</t>
+          <t>8.26</t>
         </is>
       </c>
       <c r="AO209" t="inlineStr">
         <is>
-          <t>32.31</t>
+          <t>30.73</t>
         </is>
       </c>
       <c r="AP209" t="inlineStr">
         <is>
-          <t>88.57</t>
+          <t>85.63</t>
         </is>
       </c>
       <c r="AQ209" t="inlineStr">
         <is>
-          <t>99.2676</t>
+          <t>96.5176</t>
         </is>
       </c>
       <c r="AR209" t="inlineStr">
         <is>
-          <t>0.3781</t>
+          <t>0.3489</t>
         </is>
       </c>
       <c r="AS209" t="inlineStr">
         <is>
-          <t>0.1569</t>
+          <t>0.1582</t>
         </is>
       </c>
       <c r="AT209" t="inlineStr">
         <is>
-          <t>0.2844</t>
+          <t>0.2889</t>
         </is>
       </c>
       <c r="AU209" t="inlineStr">
         <is>
-          <t>72.53</t>
+          <t>71.45</t>
         </is>
       </c>
       <c r="AV209" t="inlineStr">
         <is>
-          <t>26.06</t>
+          <t>15.65</t>
         </is>
       </c>
       <c r="AW209" t="inlineStr">
         <is>
-          <t>50.52</t>
+          <t>44.8</t>
         </is>
       </c>
       <c r="AX209" t="inlineStr">
         <is>
-          <t>19.03</t>
+          <t>27.79</t>
         </is>
       </c>
       <c r="AY209" t="inlineStr">
         <is>
-          <t>6.3</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="AZ209" t="inlineStr">
         <is>
-          <t>0.1808</t>
+          <t>0.2529</t>
         </is>
       </c>
       <c r="BA209" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>6.34</t>
         </is>
       </c>
       <c r="BB209" t="inlineStr">
         <is>
-          <t>37.0</t>
+          <t>43.07</t>
         </is>
       </c>
       <c r="BC209" t="inlineStr">
         <is>
-          <t>88.1</t>
+          <t>89.91</t>
         </is>
       </c>
       <c r="BD209" t="inlineStr">
         <is>
-          <t>0.375</t>
+          <t>0.3738</t>
         </is>
       </c>
       <c r="BE209" t="inlineStr">
         <is>
-          <t>0.089</t>
+          <t>0.1212</t>
         </is>
       </c>
       <c r="BF209" t="inlineStr">
         <is>
-          <t>19.6</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="BG209" t="inlineStr">
         <is>
-          <t>In From LF</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH209" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI209" t="inlineStr">
         <is>
-          <t>Yankee Stadium</t>
+          <t>loanDepot park</t>
         </is>
       </c>
       <c r="BJ209" t="inlineStr"/>
@@ -60656,7 +60656,7 @@
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
@@ -61192,7 +61192,7 @@
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
@@ -61752,7 +61752,7 @@
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
@@ -64934,7 +64934,7 @@
       </c>
       <c r="AI232" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AJ232" t="inlineStr">
@@ -64944,7 +64944,7 @@
       </c>
       <c r="AK232" t="inlineStr">
         <is>
-          <t>Last 7 games: 1/13, 0 HR</t>
+          <t>Last 7 games: 1/14, 0 HR</t>
         </is>
       </c>
       <c r="AL232" t="inlineStr">
@@ -65075,32 +65075,32 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>702284</t>
+          <t>682668</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Cole Young</t>
+          <t>Luisangel Acuña</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>2026-06-21T20:10:00Z</t>
+          <t>2026-06-21T17:40:00Z</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
@@ -65110,21 +65110,21 @@
       </c>
       <c r="I233" t="inlineStr">
         <is>
-          <t>Payton Tolle</t>
+          <t>Keider Montero</t>
         </is>
       </c>
       <c r="J233" t="inlineStr">
         <is>
-          <t>801139</t>
+          <t>672456</t>
         </is>
       </c>
       <c r="K233" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L233" t="n">
-        <v>33</v>
+        <v>33.1</v>
       </c>
       <c r="M233" t="inlineStr">
         <is>
@@ -65142,13 +65142,13 @@
         </is>
       </c>
       <c r="P233" t="n">
-        <v>24.6</v>
+        <v>14.5</v>
       </c>
       <c r="Q233" t="n">
-        <v>24.8</v>
+        <v>43.3</v>
       </c>
       <c r="R233" t="n">
-        <v>44.4</v>
+        <v>35.6</v>
       </c>
       <c r="S233" t="n">
         <v>44.8</v>
@@ -65157,7 +65157,7 @@
         <v>50</v>
       </c>
       <c r="U233" t="n">
-        <v>29.2</v>
+        <v>35.6</v>
       </c>
       <c r="V233" t="inlineStr">
         <is>
@@ -65214,22 +65214,22 @@
       </c>
       <c r="AI233" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AJ233" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK233" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/26, 1 HR</t>
+          <t>Contact streak: 5/14 over last 7 games</t>
         </is>
       </c>
       <c r="AL233" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.0% barrel, 5.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.3% barrel, 10.4 HR allowed</t>
         </is>
       </c>
       <c r="AM233" t="inlineStr">
@@ -65239,112 +65239,112 @@
       </c>
       <c r="AN233" t="inlineStr">
         <is>
-          <t>5.32</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="AO233" t="inlineStr">
         <is>
-          <t>36.21</t>
+          <t>37.18</t>
         </is>
       </c>
       <c r="AP233" t="inlineStr">
         <is>
-          <t>87.95</t>
+          <t>88.81</t>
         </is>
       </c>
       <c r="AQ233" t="inlineStr">
         <is>
-          <t>98.7983</t>
+          <t>99.6106</t>
         </is>
       </c>
       <c r="AR233" t="inlineStr">
         <is>
-          <t>0.3935</t>
+          <t>0.3025</t>
         </is>
       </c>
       <c r="AS233" t="inlineStr">
         <is>
-          <t>0.1359</t>
+          <t>0.0637</t>
         </is>
       </c>
       <c r="AT233" t="inlineStr">
         <is>
-          <t>0.3187</t>
+          <t>0.2675</t>
         </is>
       </c>
       <c r="AU233" t="inlineStr">
         <is>
-          <t>71.68</t>
+          <t>71.61</t>
         </is>
       </c>
       <c r="AV233" t="inlineStr">
         <is>
-          <t>23.28</t>
+          <t>25.2</t>
         </is>
       </c>
       <c r="AW233" t="inlineStr">
         <is>
-          <t>44.01</t>
+          <t>33.55</t>
         </is>
       </c>
       <c r="AX233" t="inlineStr">
         <is>
-          <t>27.01</t>
+          <t>16.86</t>
         </is>
       </c>
       <c r="AY233" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ233" t="inlineStr">
         <is>
-          <t>0.1052</t>
+          <t>0.0232</t>
         </is>
       </c>
       <c r="BA233" t="inlineStr">
         <is>
-          <t>5.98</t>
+          <t>8.34</t>
         </is>
       </c>
       <c r="BB233" t="inlineStr">
         <is>
-          <t>34.52</t>
+          <t>39.68</t>
         </is>
       </c>
       <c r="BC233" t="inlineStr">
         <is>
-          <t>87.73</t>
+          <t>89.45</t>
         </is>
       </c>
       <c r="BD233" t="inlineStr">
         <is>
-          <t>0.3469</t>
+          <t>0.4159</t>
         </is>
       </c>
       <c r="BE233" t="inlineStr">
         <is>
-          <t>0.131</t>
+          <t>0.1727</t>
         </is>
       </c>
       <c r="BF233" t="inlineStr">
         <is>
-          <t>28.44</t>
+          <t>27.66</t>
         </is>
       </c>
       <c r="BG233" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>In From LF</t>
         </is>
       </c>
       <c r="BH233" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>74</t>
         </is>
       </c>
       <c r="BI233" t="inlineStr">
         <is>
-          <t>T-Mobile Park</t>
+          <t>Comerica Park</t>
         </is>
       </c>
       <c r="BJ233" t="inlineStr"/>
@@ -65355,32 +65355,32 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>673490</t>
+          <t>702284</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Ha-Seong Kim</t>
+          <t>Cole Young</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>2026-06-21T17:35:00Z</t>
+          <t>2026-06-21T20:10:00Z</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
@@ -65390,12 +65390,12 @@
       </c>
       <c r="I234" t="inlineStr">
         <is>
-          <t>Robert Gasser</t>
+          <t>Payton Tolle</t>
         </is>
       </c>
       <c r="J234" t="inlineStr">
         <is>
-          <t>688107</t>
+          <t>801139</t>
         </is>
       </c>
       <c r="K234" t="inlineStr">
@@ -65404,7 +65404,7 @@
         </is>
       </c>
       <c r="L234" t="n">
-        <v>32.9</v>
+        <v>33</v>
       </c>
       <c r="M234" t="inlineStr">
         <is>
@@ -65418,26 +65418,26 @@
       </c>
       <c r="O234" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P234" t="n">
-        <v>9.300000000000001</v>
+        <v>24.6</v>
       </c>
       <c r="Q234" t="n">
-        <v>34.4</v>
+        <v>24.8</v>
       </c>
       <c r="R234" t="n">
-        <v>54.9</v>
+        <v>44.4</v>
       </c>
       <c r="S234" t="n">
         <v>44.8</v>
       </c>
       <c r="T234" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U234" t="n">
-        <v>0</v>
+        <v>29.2</v>
       </c>
       <c r="V234" t="inlineStr">
         <is>
@@ -65489,142 +65489,142 @@
       </c>
       <c r="AH234" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI234" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ234" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK234" t="inlineStr">
         <is>
-          <t>Last 7 games: 0/10, 0 HR</t>
+          <t>Last 7 games: 5/26, 1 HR</t>
         </is>
       </c>
       <c r="AL234" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.4% barrel, 4.5 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.0% barrel, 5.0 HR allowed</t>
         </is>
       </c>
       <c r="AM234" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN234" t="inlineStr">
         <is>
-          <t>3.24</t>
+          <t>5.32</t>
         </is>
       </c>
       <c r="AO234" t="inlineStr">
         <is>
-          <t>27.62</t>
+          <t>36.21</t>
         </is>
       </c>
       <c r="AP234" t="inlineStr">
         <is>
-          <t>86.13</t>
+          <t>87.95</t>
         </is>
       </c>
       <c r="AQ234" t="inlineStr">
         <is>
-          <t>95.6299</t>
+          <t>98.7983</t>
         </is>
       </c>
       <c r="AR234" t="inlineStr">
         <is>
-          <t>0.2461</t>
+          <t>0.3935</t>
         </is>
       </c>
       <c r="AS234" t="inlineStr">
         <is>
-          <t>0.0657</t>
+          <t>0.1359</t>
         </is>
       </c>
       <c r="AT234" t="inlineStr">
         <is>
-          <t>0.2382</t>
+          <t>0.3187</t>
         </is>
       </c>
       <c r="AU234" t="inlineStr">
         <is>
-          <t>71.55</t>
+          <t>71.68</t>
         </is>
       </c>
       <c r="AV234" t="inlineStr">
         <is>
-          <t>18.88</t>
+          <t>23.28</t>
         </is>
       </c>
       <c r="AW234" t="inlineStr">
         <is>
-          <t>46.25</t>
+          <t>44.01</t>
         </is>
       </c>
       <c r="AX234" t="inlineStr">
         <is>
-          <t>30.2</t>
+          <t>27.01</t>
         </is>
       </c>
       <c r="AY234" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>5.4</t>
         </is>
       </c>
       <c r="AZ234" t="inlineStr">
         <is>
-          <t>0.0333</t>
+          <t>0.1052</t>
         </is>
       </c>
       <c r="BA234" t="inlineStr">
         <is>
-          <t>8.37</t>
+          <t>5.98</t>
         </is>
       </c>
       <c r="BB234" t="inlineStr">
         <is>
-          <t>33.62</t>
+          <t>34.52</t>
         </is>
       </c>
       <c r="BC234" t="inlineStr">
         <is>
-          <t>88.34</t>
+          <t>87.73</t>
         </is>
       </c>
       <c r="BD234" t="inlineStr">
         <is>
-          <t>0.354</t>
+          <t>0.3469</t>
         </is>
       </c>
       <c r="BE234" t="inlineStr">
         <is>
-          <t>0.1628</t>
+          <t>0.131</t>
         </is>
       </c>
       <c r="BF234" t="inlineStr">
         <is>
-          <t>31.02</t>
+          <t>28.44</t>
         </is>
       </c>
       <c r="BG234" t="inlineStr">
         <is>
-          <t>R To L</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH234" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI234" t="inlineStr">
         <is>
-          <t>Truist Park</t>
+          <t>T-Mobile Park</t>
         </is>
       </c>
       <c r="BJ234" t="inlineStr"/>
@@ -65635,27 +65635,27 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>682668</t>
+          <t>673490</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Luisangel Acuña</t>
+          <t>Ha-Seong Kim</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>2026-06-21T17:40:00Z</t>
+          <t>2026-06-21T17:35:00Z</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
@@ -65670,17 +65670,17 @@
       </c>
       <c r="I235" t="inlineStr">
         <is>
-          <t>Keider Montero</t>
+          <t>Robert Gasser</t>
         </is>
       </c>
       <c r="J235" t="inlineStr">
         <is>
-          <t>672456</t>
+          <t>688107</t>
         </is>
       </c>
       <c r="K235" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L235" t="n">
@@ -65698,26 +65698,26 @@
       </c>
       <c r="O235" t="inlineStr">
         <is>
-          <t>No major boost</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P235" t="n">
-        <v>14.5</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="Q235" t="n">
-        <v>43.3</v>
+        <v>34.4</v>
       </c>
       <c r="R235" t="n">
-        <v>35.6</v>
+        <v>54.9</v>
       </c>
       <c r="S235" t="n">
         <v>44.8</v>
       </c>
       <c r="T235" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U235" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="V235" t="inlineStr">
         <is>
@@ -65769,12 +65769,12 @@
       </c>
       <c r="AH235" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AI235" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AJ235" t="inlineStr">
@@ -65784,127 +65784,127 @@
       </c>
       <c r="AK235" t="inlineStr">
         <is>
-          <t>Contact streak: 5/15 over last 7 games</t>
+          <t>Last 7 games: 0/10, 0 HR</t>
         </is>
       </c>
       <c r="AL235" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.3% barrel, 10.4 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.4% barrel, 4.5 HR allowed</t>
         </is>
       </c>
       <c r="AM235" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN235" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>3.24</t>
         </is>
       </c>
       <c r="AO235" t="inlineStr">
         <is>
-          <t>37.18</t>
+          <t>27.62</t>
         </is>
       </c>
       <c r="AP235" t="inlineStr">
         <is>
-          <t>88.81</t>
+          <t>86.13</t>
         </is>
       </c>
       <c r="AQ235" t="inlineStr">
         <is>
-          <t>99.6106</t>
+          <t>95.6299</t>
         </is>
       </c>
       <c r="AR235" t="inlineStr">
         <is>
-          <t>0.3025</t>
+          <t>0.2461</t>
         </is>
       </c>
       <c r="AS235" t="inlineStr">
         <is>
-          <t>0.0637</t>
+          <t>0.0657</t>
         </is>
       </c>
       <c r="AT235" t="inlineStr">
         <is>
-          <t>0.2675</t>
+          <t>0.2382</t>
         </is>
       </c>
       <c r="AU235" t="inlineStr">
         <is>
-          <t>71.61</t>
+          <t>71.55</t>
         </is>
       </c>
       <c r="AV235" t="inlineStr">
         <is>
-          <t>25.2</t>
+          <t>18.88</t>
         </is>
       </c>
       <c r="AW235" t="inlineStr">
         <is>
-          <t>33.55</t>
+          <t>46.25</t>
         </is>
       </c>
       <c r="AX235" t="inlineStr">
         <is>
-          <t>16.86</t>
+          <t>30.2</t>
         </is>
       </c>
       <c r="AY235" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="AZ235" t="inlineStr">
         <is>
-          <t>0.0232</t>
+          <t>0.0333</t>
         </is>
       </c>
       <c r="BA235" t="inlineStr">
         <is>
-          <t>8.34</t>
+          <t>8.37</t>
         </is>
       </c>
       <c r="BB235" t="inlineStr">
         <is>
-          <t>39.68</t>
+          <t>33.62</t>
         </is>
       </c>
       <c r="BC235" t="inlineStr">
         <is>
-          <t>89.45</t>
+          <t>88.34</t>
         </is>
       </c>
       <c r="BD235" t="inlineStr">
         <is>
-          <t>0.4159</t>
+          <t>0.354</t>
         </is>
       </c>
       <c r="BE235" t="inlineStr">
         <is>
-          <t>0.1727</t>
+          <t>0.1628</t>
         </is>
       </c>
       <c r="BF235" t="inlineStr">
         <is>
-          <t>27.66</t>
+          <t>31.02</t>
         </is>
       </c>
       <c r="BG235" t="inlineStr">
         <is>
-          <t>In From LF</t>
+          <t>R To L</t>
         </is>
       </c>
       <c r="BH235" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>77</t>
         </is>
       </c>
       <c r="BI235" t="inlineStr">
         <is>
-          <t>Comerica Park</t>
+          <t>Truist Park</t>
         </is>
       </c>
       <c r="BJ235" t="inlineStr"/>
@@ -67422,7 +67422,7 @@
       </c>
       <c r="AI241" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AJ241" t="inlineStr">
@@ -67432,7 +67432,7 @@
       </c>
       <c r="AK241" t="inlineStr">
         <is>
-          <t>Last 2 games: 0/3, 0 HR</t>
+          <t>Last 2 games: 0/4, 0 HR</t>
         </is>
       </c>
       <c r="AL241" t="inlineStr">
@@ -75414,7 +75414,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">

--- a/outputs/hr_rankings.xlsx
+++ b/outputs/hr_rankings.xlsx
@@ -1624,7 +1624,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>64.5</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1638,7 +1638,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Elite Power, Strong Barrel, Premium Lineup Spot</t>
+          <t>Elite Power, Strong Barrel, Premium Lineup Spot, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P5" t="n">
@@ -1657,7 +1657,7 @@
         <v>50</v>
       </c>
       <c r="U5" t="n">
-        <v>66.7</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
@@ -1709,22 +1709,22 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Hot streak: 3 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Game Over</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Game Over</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -3593,7 +3593,7 @@
         <v>80</v>
       </c>
       <c r="U12" t="n">
-        <v>57.8</v>
+        <v>56.2</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
@@ -3650,7 +3650,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
@@ -4911,27 +4911,27 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>650489</t>
+          <t>680776</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Willi Castro</t>
+          <t>Jarren Duran</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-06-21T19:10:00Z</t>
+          <t>2026-06-21T20:10:00Z</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -4941,17 +4941,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Jared Jones</t>
+          <t>Logan Gilbert</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>683003</t>
+          <t>669302</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -4974,26 +4974,26 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>27.2</v>
+        <v>41.4</v>
       </c>
       <c r="Q17" t="n">
-        <v>52</v>
+        <v>54.9</v>
       </c>
       <c r="R17" t="n">
-        <v>66.7</v>
+        <v>56.4</v>
       </c>
       <c r="S17" t="n">
-        <v>100</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T17" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="U17" t="n">
-        <v>72.7</v>
+        <v>23.4</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
@@ -5007,7 +5007,7 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
@@ -5028,7 +5028,7 @@
       <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD17" t="inlineStr"/>
@@ -5045,27 +5045,27 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 4/26, 1 HR</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 9.3% barrel, 4.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 10.8% barrel, 15.1 HR allowed</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
@@ -5075,112 +5075,112 @@
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>5.87</t>
+          <t>11.03</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>40.59</t>
+          <t>41.76</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>88.03</t>
+          <t>90.54</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>99.923</t>
+          <t>102.3517</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>0.3617</t>
+          <t>0.3953</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>0.1295</t>
+          <t>0.1606</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>0.3025</t>
+          <t>0.3043</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>72.37</t>
+          <t>75.22</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>23.62</t>
+          <t>52.26</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>42.88</t>
+          <t>40.51</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>30.9</t>
+          <t>21.39</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>6.8</t>
+          <t>13.2</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>0.1295</t>
+          <t>0.1783</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>9.3</t>
+          <t>10.84</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>42.6</t>
+          <t>44.01</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>89.7</t>
+          <t>90.73</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>0.481</t>
+          <t>0.4041</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
-          <t>0.212</t>
+          <t>0.1729</t>
         </is>
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>29.6</t>
+          <t>29.94</t>
         </is>
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>In From LF</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>70</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
         <is>
-          <t>Coors Field</t>
+          <t>T-Mobile Park</t>
         </is>
       </c>
       <c r="BJ17" t="inlineStr"/>
@@ -5191,47 +5191,47 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>680776</t>
+          <t>656811</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Jarren Duran</t>
+          <t>Ryan O'Hearn</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-06-21T20:10:00Z</t>
+          <t>2026-06-21T19:10:00Z</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Game Over</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Logan Gilbert</t>
+          <t>Michael Lorenzen</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>669302</t>
+          <t>547179</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -5240,7 +5240,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>55.8</v>
+        <v>55.7</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -5254,26 +5254,26 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Strong Barrel, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>41.4</v>
+        <v>33.7</v>
       </c>
       <c r="Q18" t="n">
-        <v>54.9</v>
+        <v>51.6</v>
       </c>
       <c r="R18" t="n">
-        <v>56.4</v>
+        <v>66.7</v>
       </c>
       <c r="S18" t="n">
-        <v>86.40000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T18" t="n">
         <v>80</v>
       </c>
       <c r="U18" t="n">
-        <v>23.4</v>
+        <v>34.2</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
@@ -5287,7 +5287,7 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
@@ -5325,12 +5325,12 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>31</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
@@ -5340,12 +5340,12 @@
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/26, 1 HR</t>
+          <t>Last 7 games: 7/31, 1 HR</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 10.8% barrel, 15.1 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.0% barrel, 15.9 HR allowed</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
@@ -5355,112 +5355,112 @@
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>11.03</t>
+          <t>6.69</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>41.76</t>
+          <t>43.55</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>90.54</t>
+          <t>89.54</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>102.3517</t>
+          <t>99.5306</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>0.3953</t>
+          <t>0.4157</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>0.1606</t>
+          <t>0.1558</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>0.3043</t>
+          <t>0.3276</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>75.22</t>
+          <t>71.03</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>52.26</t>
+          <t>12.06</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>40.51</t>
+          <t>36.42</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>21.39</t>
+          <t>28.08</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>13.2</t>
+          <t>12.8</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>0.1783</t>
+          <t>0.1728</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>10.84</t>
+          <t>9.01</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>44.01</t>
+          <t>43.61</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>90.73</t>
+          <t>89.72</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>0.4041</t>
+          <t>0.4699</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
-          <t>0.1729</t>
+          <t>0.1847</t>
         </is>
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>29.94</t>
+          <t>25.59</t>
         </is>
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>In From LF</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>88</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
         <is>
-          <t>T-Mobile Park</t>
+          <t>Coors Field</t>
         </is>
       </c>
       <c r="BJ18" t="inlineStr"/>
@@ -5471,24 +5471,24 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>656811</t>
+          <t>650489</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Ryan O'Hearn</t>
+          <t>Willi Castro</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
+          <t>COL</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
           <t>PIT</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>COL</t>
-        </is>
-      </c>
       <c r="F19" t="inlineStr">
         <is>
           <t>2026-06-21T19:10:00Z</t>
@@ -5496,22 +5496,22 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Game Over</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Michael Lorenzen</t>
+          <t>Jared Jones</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>547179</t>
+          <t>683003</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -5534,26 +5534,26 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P19" t="n">
-        <v>33.7</v>
+        <v>27.2</v>
       </c>
       <c r="Q19" t="n">
-        <v>51.6</v>
+        <v>52</v>
       </c>
       <c r="R19" t="n">
         <v>66.7</v>
       </c>
       <c r="S19" t="n">
-        <v>94.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="T19" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="U19" t="n">
-        <v>34.2</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="V19" t="inlineStr">
         <is>
@@ -5567,7 +5567,7 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
@@ -5588,7 +5588,7 @@
       <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD19" t="inlineStr"/>
@@ -5605,27 +5605,27 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/31, 1 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 9.0% barrel, 15.9 HR allowed</t>
+          <t>switch hitter; pitcher baseline 9.3% barrel, 4.0 HR allowed</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
@@ -5635,97 +5635,97 @@
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>6.69</t>
+          <t>5.87</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>43.55</t>
+          <t>40.59</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>89.54</t>
+          <t>88.03</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>99.5306</t>
+          <t>99.923</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>0.4157</t>
+          <t>0.3617</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
         <is>
-          <t>0.1558</t>
+          <t>0.1295</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>0.3276</t>
+          <t>0.3025</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>71.03</t>
+          <t>72.37</t>
         </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>12.06</t>
+          <t>23.62</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>36.42</t>
+          <t>42.88</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>28.08</t>
+          <t>30.9</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>12.8</t>
+          <t>6.8</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>0.1728</t>
+          <t>0.1295</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>9.01</t>
+          <t>9.3</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>43.61</t>
+          <t>42.6</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>89.72</t>
+          <t>89.7</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>0.4699</t>
+          <t>0.481</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
-          <t>0.1847</t>
+          <t>0.212</t>
         </is>
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>25.59</t>
+          <t>29.6</t>
         </is>
       </c>
       <c r="BG19" t="inlineStr">
@@ -6868,7 +6868,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Game Over</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -7428,7 +7428,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Game Over</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -7712,7 +7712,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Game Over</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -7992,7 +7992,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Game Over</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -8272,7 +8272,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Game Over</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -9136,7 +9136,7 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>53.2</v>
+        <v>53.1</v>
       </c>
       <c r="M32" t="inlineStr">
         <is>
@@ -9169,7 +9169,7 @@
         <v>78</v>
       </c>
       <c r="U32" t="n">
-        <v>78.7</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="V32" t="inlineStr">
         <is>
@@ -9226,7 +9226,7 @@
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ32" t="inlineStr">
@@ -10203,22 +10203,22 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>605141</t>
+          <t>677594</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Mookie Betts</t>
+          <t>Julio Rodríguez</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -10233,22 +10233,22 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Brandon Young</t>
+          <t>Payton Tolle</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>687064</t>
+          <t>801139</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L36" t="n">
@@ -10266,26 +10266,26 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Hot Hitter/Streak</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P36" t="n">
-        <v>33.4</v>
+        <v>47.1</v>
       </c>
       <c r="Q36" t="n">
-        <v>42.1</v>
+        <v>24.8</v>
       </c>
       <c r="R36" t="n">
-        <v>61.6</v>
+        <v>56.4</v>
       </c>
       <c r="S36" t="n">
-        <v>94.90000000000001</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T36" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U36" t="n">
-        <v>72.7</v>
+        <v>25.3</v>
       </c>
       <c r="V36" t="inlineStr">
         <is>
@@ -10299,7 +10299,7 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y36" t="inlineStr">
@@ -10337,142 +10337,142 @@
       </c>
       <c r="AH36" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI36" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 4/24, 1 HR</t>
         </is>
       </c>
       <c r="AL36" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.0% barrel, 7.8 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.0% barrel, 5.0 HR allowed</t>
         </is>
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN36" t="inlineStr">
         <is>
-          <t>7.46</t>
+          <t>9.38</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>36.5</t>
+          <t>44.85</t>
         </is>
       </c>
       <c r="AP36" t="inlineStr">
         <is>
-          <t>89.59</t>
+          <t>90.54</t>
         </is>
       </c>
       <c r="AQ36" t="inlineStr">
         <is>
-          <t>98.2946</t>
+          <t>102.8449</t>
         </is>
       </c>
       <c r="AR36" t="inlineStr">
         <is>
-          <t>0.4318</t>
+          <t>0.4685</t>
         </is>
       </c>
       <c r="AS36" t="inlineStr">
         <is>
-          <t>0.1595</t>
+          <t>0.2034</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr">
         <is>
-          <t>0.3342</t>
+          <t>0.3419</t>
         </is>
       </c>
       <c r="AU36" t="inlineStr">
         <is>
-          <t>69.35</t>
+          <t>76.54</t>
         </is>
       </c>
       <c r="AV36" t="inlineStr">
         <is>
-          <t>8.07</t>
+          <t>66.28</t>
         </is>
       </c>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>40.59</t>
+          <t>36.25</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>36.6</t>
+          <t>25.28</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">
         <is>
-          <t>11.6</t>
+          <t>19.4</t>
         </is>
       </c>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>0.1711</t>
+          <t>0.1916</t>
         </is>
       </c>
       <c r="BA36" t="inlineStr">
         <is>
-          <t>8.03</t>
+          <t>5.98</t>
         </is>
       </c>
       <c r="BB36" t="inlineStr">
         <is>
-          <t>41.57</t>
+          <t>34.52</t>
         </is>
       </c>
       <c r="BC36" t="inlineStr">
         <is>
-          <t>89.19</t>
+          <t>87.73</t>
         </is>
       </c>
       <c r="BD36" t="inlineStr">
         <is>
-          <t>0.4215</t>
+          <t>0.3469</t>
         </is>
       </c>
       <c r="BE36" t="inlineStr">
         <is>
-          <t>0.1707</t>
+          <t>0.131</t>
         </is>
       </c>
       <c r="BF36" t="inlineStr">
         <is>
-          <t>26.17</t>
+          <t>28.44</t>
         </is>
       </c>
       <c r="BG36" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>70</t>
         </is>
       </c>
       <c r="BI36" t="inlineStr">
         <is>
-          <t>UNIQLO Field at Dodger Stadium</t>
+          <t>T-Mobile Park</t>
         </is>
       </c>
       <c r="BJ36" t="inlineStr"/>
@@ -10483,22 +10483,22 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>677594</t>
+          <t>681624</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Julio Rodríguez</t>
+          <t>Andy Pages</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -10513,26 +10513,26 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Payton Tolle</t>
+          <t>Brandon Young</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>801139</t>
+          <t>687064</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L37" t="n">
-        <v>51.8</v>
+        <v>51.7</v>
       </c>
       <c r="M37" t="inlineStr">
         <is>
@@ -10546,26 +10546,26 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P37" t="n">
-        <v>47.1</v>
+        <v>40.6</v>
       </c>
       <c r="Q37" t="n">
-        <v>24.8</v>
+        <v>42.1</v>
       </c>
       <c r="R37" t="n">
-        <v>56.4</v>
+        <v>61.6</v>
       </c>
       <c r="S37" t="n">
-        <v>96.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="T37" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U37" t="n">
-        <v>25.3</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="V37" t="inlineStr">
         <is>
@@ -10579,7 +10579,7 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y37" t="inlineStr">
@@ -10617,27 +10617,27 @@
       </c>
       <c r="AH37" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI37" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/24, 1 HR</t>
+          <t>Last 7 games: 5/28, 0 HR</t>
         </is>
       </c>
       <c r="AL37" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.0% barrel, 5.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.0% barrel, 7.8 HR allowed</t>
         </is>
       </c>
       <c r="AM37" t="inlineStr">
@@ -10647,112 +10647,112 @@
       </c>
       <c r="AN37" t="inlineStr">
         <is>
-          <t>9.38</t>
+          <t>8.75</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>44.85</t>
+          <t>43.92</t>
         </is>
       </c>
       <c r="AP37" t="inlineStr">
         <is>
-          <t>90.54</t>
+          <t>89.23</t>
         </is>
       </c>
       <c r="AQ37" t="inlineStr">
         <is>
-          <t>102.8449</t>
+          <t>100.4685</t>
         </is>
       </c>
       <c r="AR37" t="inlineStr">
         <is>
-          <t>0.4685</t>
+          <t>0.4539</t>
         </is>
       </c>
       <c r="AS37" t="inlineStr">
         <is>
-          <t>0.2034</t>
+          <t>0.1819</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr">
         <is>
-          <t>0.3419</t>
+          <t>0.3342</t>
         </is>
       </c>
       <c r="AU37" t="inlineStr">
         <is>
-          <t>76.54</t>
+          <t>72.81</t>
         </is>
       </c>
       <c r="AV37" t="inlineStr">
         <is>
-          <t>66.28</t>
+          <t>24.93</t>
         </is>
       </c>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>36.25</t>
+          <t>35.87</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>25.28</t>
+          <t>28.37</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr">
         <is>
-          <t>19.4</t>
+          <t>18.6</t>
         </is>
       </c>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>0.1916</t>
+          <t>0.2086</t>
         </is>
       </c>
       <c r="BA37" t="inlineStr">
         <is>
-          <t>5.98</t>
+          <t>8.03</t>
         </is>
       </c>
       <c r="BB37" t="inlineStr">
         <is>
-          <t>34.52</t>
+          <t>41.57</t>
         </is>
       </c>
       <c r="BC37" t="inlineStr">
         <is>
-          <t>87.73</t>
+          <t>89.19</t>
         </is>
       </c>
       <c r="BD37" t="inlineStr">
         <is>
-          <t>0.3469</t>
+          <t>0.4215</t>
         </is>
       </c>
       <c r="BE37" t="inlineStr">
         <is>
-          <t>0.131</t>
+          <t>0.1707</t>
         </is>
       </c>
       <c r="BF37" t="inlineStr">
         <is>
-          <t>28.44</t>
+          <t>26.17</t>
         </is>
       </c>
       <c r="BG37" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>74</t>
         </is>
       </c>
       <c r="BI37" t="inlineStr">
         <is>
-          <t>T-Mobile Park</t>
+          <t>UNIQLO Field at Dodger Stadium</t>
         </is>
       </c>
       <c r="BJ37" t="inlineStr"/>
@@ -10763,12 +10763,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>681624</t>
+          <t>605141</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Andy Pages</t>
+          <t>Mookie Betts</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -10793,7 +10793,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -10826,11 +10826,11 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot</t>
+          <t>Premium Lineup Spot, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P38" t="n">
-        <v>40.6</v>
+        <v>33.4</v>
       </c>
       <c r="Q38" t="n">
         <v>42.1</v>
@@ -10839,13 +10839,13 @@
         <v>61.6</v>
       </c>
       <c r="S38" t="n">
-        <v>100</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T38" t="n">
         <v>50</v>
       </c>
       <c r="U38" t="n">
-        <v>8.800000000000001</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="V38" t="inlineStr">
         <is>
@@ -10859,7 +10859,7 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y38" t="inlineStr">
@@ -10897,22 +10897,22 @@
       </c>
       <c r="AH38" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI38" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK38" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/28, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL38" t="inlineStr">
@@ -10922,37 +10922,37 @@
       </c>
       <c r="AM38" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN38" t="inlineStr">
         <is>
-          <t>8.75</t>
+          <t>7.46</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>43.92</t>
+          <t>36.5</t>
         </is>
       </c>
       <c r="AP38" t="inlineStr">
         <is>
-          <t>89.23</t>
+          <t>89.59</t>
         </is>
       </c>
       <c r="AQ38" t="inlineStr">
         <is>
-          <t>100.4685</t>
+          <t>98.2946</t>
         </is>
       </c>
       <c r="AR38" t="inlineStr">
         <is>
-          <t>0.4539</t>
+          <t>0.4318</t>
         </is>
       </c>
       <c r="AS38" t="inlineStr">
         <is>
-          <t>0.1819</t>
+          <t>0.1595</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr">
@@ -10962,32 +10962,32 @@
       </c>
       <c r="AU38" t="inlineStr">
         <is>
-          <t>72.81</t>
+          <t>69.35</t>
         </is>
       </c>
       <c r="AV38" t="inlineStr">
         <is>
-          <t>24.93</t>
+          <t>8.07</t>
         </is>
       </c>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>35.87</t>
+          <t>40.59</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>28.37</t>
+          <t>36.6</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr">
         <is>
-          <t>18.6</t>
+          <t>11.6</t>
         </is>
       </c>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>0.2086</t>
+          <t>0.1711</t>
         </is>
       </c>
       <c r="BA38" t="inlineStr">
@@ -11628,7 +11628,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Game Over</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -12468,7 +12468,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Game Over</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -16060,7 +16060,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Game Over</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -19136,7 +19136,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Game Over</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -21096,7 +21096,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Game Over</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -21660,7 +21660,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Game Over</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -23028,7 +23028,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Game Over</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -26397,7 +26397,7 @@
         <v>78</v>
       </c>
       <c r="U94" t="n">
-        <v>40.7</v>
+        <v>39.2</v>
       </c>
       <c r="V94" t="inlineStr">
         <is>
@@ -26454,7 +26454,7 @@
       </c>
       <c r="AI94" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ94" t="inlineStr">
@@ -26464,7 +26464,7 @@
       </c>
       <c r="AK94" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/26, 1 HR</t>
+          <t>Last 7 games: 7/27, 1 HR</t>
         </is>
       </c>
       <c r="AL94" t="inlineStr">
@@ -26620,7 +26620,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Game Over</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -27964,7 +27964,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Game Over</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -31906,7 +31906,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>64.5</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -31920,7 +31920,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Elite Power, Strong Barrel, Premium Lineup Spot</t>
+          <t>Elite Power, Strong Barrel, Premium Lineup Spot, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P5" t="n">
@@ -31939,7 +31939,7 @@
         <v>50</v>
       </c>
       <c r="U5" t="n">
-        <v>66.7</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
@@ -31991,22 +31991,22 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Hot streak: 3 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
@@ -32162,7 +32162,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Game Over</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -32442,7 +32442,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Game Over</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -33875,7 +33875,7 @@
         <v>80</v>
       </c>
       <c r="U12" t="n">
-        <v>57.8</v>
+        <v>56.2</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
@@ -33932,7 +33932,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
@@ -35193,27 +35193,27 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>650489</t>
+          <t>680776</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Willi Castro</t>
+          <t>Jarren Duran</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-06-21T19:10:00Z</t>
+          <t>2026-06-21T20:10:00Z</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -35223,17 +35223,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Jared Jones</t>
+          <t>Logan Gilbert</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>683003</t>
+          <t>669302</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -35256,26 +35256,26 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>27.2</v>
+        <v>41.4</v>
       </c>
       <c r="Q17" t="n">
-        <v>52</v>
+        <v>54.9</v>
       </c>
       <c r="R17" t="n">
-        <v>66.7</v>
+        <v>56.4</v>
       </c>
       <c r="S17" t="n">
-        <v>100</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T17" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="U17" t="n">
-        <v>72.7</v>
+        <v>23.4</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
@@ -35289,7 +35289,7 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
@@ -35310,7 +35310,7 @@
       <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD17" t="inlineStr"/>
@@ -35327,27 +35327,27 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 4/26, 1 HR</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 9.3% barrel, 4.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 10.8% barrel, 15.1 HR allowed</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
@@ -35357,112 +35357,112 @@
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>5.87</t>
+          <t>11.03</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>40.59</t>
+          <t>41.76</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>88.03</t>
+          <t>90.54</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>99.923</t>
+          <t>102.3517</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>0.3617</t>
+          <t>0.3953</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>0.1295</t>
+          <t>0.1606</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>0.3025</t>
+          <t>0.3043</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>72.37</t>
+          <t>75.22</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>23.62</t>
+          <t>52.26</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>42.88</t>
+          <t>40.51</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>30.9</t>
+          <t>21.39</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>6.8</t>
+          <t>13.2</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>0.1295</t>
+          <t>0.1783</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>9.3</t>
+          <t>10.84</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>42.6</t>
+          <t>44.01</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>89.7</t>
+          <t>90.73</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>0.481</t>
+          <t>0.4041</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
-          <t>0.212</t>
+          <t>0.1729</t>
         </is>
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>29.6</t>
+          <t>29.94</t>
         </is>
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>In From LF</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>70</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
         <is>
-          <t>Coors Field</t>
+          <t>T-Mobile Park</t>
         </is>
       </c>
       <c r="BJ17" t="inlineStr"/>
@@ -35473,47 +35473,47 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>680776</t>
+          <t>656811</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Jarren Duran</t>
+          <t>Ryan O'Hearn</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-06-21T20:10:00Z</t>
+          <t>2026-06-21T19:10:00Z</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Game Over</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Logan Gilbert</t>
+          <t>Michael Lorenzen</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>669302</t>
+          <t>547179</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -35522,7 +35522,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>55.8</v>
+        <v>55.7</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -35536,26 +35536,26 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Strong Barrel, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>41.4</v>
+        <v>33.7</v>
       </c>
       <c r="Q18" t="n">
-        <v>54.9</v>
+        <v>51.6</v>
       </c>
       <c r="R18" t="n">
-        <v>56.4</v>
+        <v>66.7</v>
       </c>
       <c r="S18" t="n">
-        <v>86.40000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T18" t="n">
         <v>80</v>
       </c>
       <c r="U18" t="n">
-        <v>23.4</v>
+        <v>34.2</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
@@ -35569,7 +35569,7 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
@@ -35607,12 +35607,12 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>31</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
@@ -35622,12 +35622,12 @@
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/26, 1 HR</t>
+          <t>Last 7 games: 7/31, 1 HR</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 10.8% barrel, 15.1 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.0% barrel, 15.9 HR allowed</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
@@ -35637,112 +35637,112 @@
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>11.03</t>
+          <t>6.69</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>41.76</t>
+          <t>43.55</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>90.54</t>
+          <t>89.54</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>102.3517</t>
+          <t>99.5306</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>0.3953</t>
+          <t>0.4157</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>0.1606</t>
+          <t>0.1558</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>0.3043</t>
+          <t>0.3276</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>75.22</t>
+          <t>71.03</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>52.26</t>
+          <t>12.06</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>40.51</t>
+          <t>36.42</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>21.39</t>
+          <t>28.08</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>13.2</t>
+          <t>12.8</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>0.1783</t>
+          <t>0.1728</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>10.84</t>
+          <t>9.01</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>44.01</t>
+          <t>43.61</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>90.73</t>
+          <t>89.72</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>0.4041</t>
+          <t>0.4699</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
-          <t>0.1729</t>
+          <t>0.1847</t>
         </is>
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>29.94</t>
+          <t>25.59</t>
         </is>
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>In From LF</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>88</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
         <is>
-          <t>T-Mobile Park</t>
+          <t>Coors Field</t>
         </is>
       </c>
       <c r="BJ18" t="inlineStr"/>
@@ -35753,24 +35753,24 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>656811</t>
+          <t>650489</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Ryan O'Hearn</t>
+          <t>Willi Castro</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
+          <t>COL</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
           <t>PIT</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>COL</t>
-        </is>
-      </c>
       <c r="F19" t="inlineStr">
         <is>
           <t>2026-06-21T19:10:00Z</t>
@@ -35778,22 +35778,22 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Game Over</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Michael Lorenzen</t>
+          <t>Jared Jones</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>547179</t>
+          <t>683003</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -35816,26 +35816,26 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P19" t="n">
-        <v>33.7</v>
+        <v>27.2</v>
       </c>
       <c r="Q19" t="n">
-        <v>51.6</v>
+        <v>52</v>
       </c>
       <c r="R19" t="n">
         <v>66.7</v>
       </c>
       <c r="S19" t="n">
-        <v>94.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="T19" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="U19" t="n">
-        <v>34.2</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="V19" t="inlineStr">
         <is>
@@ -35849,7 +35849,7 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
@@ -35870,7 +35870,7 @@
       <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD19" t="inlineStr"/>
@@ -35887,27 +35887,27 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/31, 1 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 9.0% barrel, 15.9 HR allowed</t>
+          <t>switch hitter; pitcher baseline 9.3% barrel, 4.0 HR allowed</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
@@ -35917,97 +35917,97 @@
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>6.69</t>
+          <t>5.87</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>43.55</t>
+          <t>40.59</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>89.54</t>
+          <t>88.03</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>99.5306</t>
+          <t>99.923</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>0.4157</t>
+          <t>0.3617</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
         <is>
-          <t>0.1558</t>
+          <t>0.1295</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>0.3276</t>
+          <t>0.3025</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>71.03</t>
+          <t>72.37</t>
         </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>12.06</t>
+          <t>23.62</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>36.42</t>
+          <t>42.88</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>28.08</t>
+          <t>30.9</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>12.8</t>
+          <t>6.8</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>0.1728</t>
+          <t>0.1295</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>9.01</t>
+          <t>9.3</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>43.61</t>
+          <t>42.6</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>89.72</t>
+          <t>89.7</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>0.4699</t>
+          <t>0.481</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
-          <t>0.1847</t>
+          <t>0.212</t>
         </is>
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>25.59</t>
+          <t>29.6</t>
         </is>
       </c>
       <c r="BG19" t="inlineStr">

--- a/outputs/hr_rankings.xlsx
+++ b/outputs/hr_rankings.xlsx
@@ -2506,34 +2506,30 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 3 vs RotoWire 4</t>
-        </is>
-      </c>
+      <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -8110,34 +8106,30 @@
       </c>
       <c r="W28" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y28" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB28" t="inlineStr"/>
       <c r="AC28" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8394,34 +8386,30 @@
       </c>
       <c r="W29" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y29" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB29" t="inlineStr"/>
       <c r="AC29" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9798,34 +9786,30 @@
       </c>
       <c r="W34" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X34" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y34" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 4 vs RotoWire 3</t>
-        </is>
-      </c>
+      <c r="AB34" t="inlineStr"/>
       <c r="AC34" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -12006,34 +11990,30 @@
       </c>
       <c r="W42" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X42" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y42" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB42" t="inlineStr"/>
       <c r="AC42" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -18082,34 +18062,30 @@
       </c>
       <c r="W64" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X64" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y64" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB64" t="inlineStr"/>
       <c r="AC64" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -20058,34 +20034,30 @@
       </c>
       <c r="W71" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X71" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y71" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB71" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB71" t="inlineStr"/>
       <c r="AC71" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -23426,34 +23398,30 @@
       </c>
       <c r="W83" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z83" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X83" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y83" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z83" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB83" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB83" t="inlineStr"/>
       <c r="AC83" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -23710,34 +23678,30 @@
       </c>
       <c r="W84" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z84" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X84" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y84" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z84" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB84" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB84" t="inlineStr"/>
       <c r="AC84" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -28174,34 +28138,30 @@
       </c>
       <c r="W100" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y100" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z100" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X100" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y100" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z100" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA100" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB100" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB100" t="inlineStr"/>
       <c r="AC100" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -31544,28 +31504,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W112" t="inlineStr"/>
-      <c r="X112" t="inlineStr"/>
+      <c r="W112" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X112" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="Y112" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z112" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z112" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA112" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB112" t="inlineStr">
-        <is>
-          <t>not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB112" t="inlineStr"/>
       <c r="AC112" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -41554,34 +41518,30 @@
       </c>
       <c r="W148" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X148" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y148" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z148" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X148" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y148" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z148" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA148" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB148" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB148" t="inlineStr"/>
       <c r="AC148" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -51278,34 +51238,30 @@
       </c>
       <c r="W183" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X183" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y183" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z183" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X183" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y183" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z183" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA183" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB183" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 8 vs RotoWire 7</t>
-        </is>
-      </c>
+      <c r="AB183" t="inlineStr"/>
       <c r="AC183" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -53794,34 +53750,30 @@
       </c>
       <c r="W192" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X192" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y192" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z192" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X192" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y192" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z192" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA192" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB192" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB192" t="inlineStr"/>
       <c r="AC192" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -56560,28 +56512,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W202" t="inlineStr"/>
-      <c r="X202" t="inlineStr"/>
+      <c r="W202" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X202" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="Y202" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z202" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z202" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA202" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB202" t="inlineStr">
-        <is>
-          <t>not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB202" t="inlineStr"/>
       <c r="AC202" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -57406,34 +57362,30 @@
       </c>
       <c r="W205" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X205" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y205" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z205" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X205" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y205" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z205" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA205" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB205" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB205" t="inlineStr"/>
       <c r="AC205" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -60474,34 +60426,30 @@
       </c>
       <c r="W216" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X216" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y216" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z216" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X216" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y216" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z216" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA216" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB216" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB216" t="inlineStr"/>
       <c r="AC216" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -66542,34 +66490,30 @@
       </c>
       <c r="W238" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X238" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y238" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z238" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X238" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y238" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z238" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA238" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB238" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB238" t="inlineStr"/>
       <c r="AC238" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -75448,34 +75392,30 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 3 vs RotoWire 4</t>
-        </is>
-      </c>
+      <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>

--- a/outputs/hr_rankings.xlsx
+++ b/outputs/hr_rankings.xlsx
@@ -1955,7 +1955,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1975,7 +1975,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>RotoWire not confirmed; order MLB 4 vs RotoWire 3</t>
+          <t>RotoWire not confirmed</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -8959,7 +8959,7 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
@@ -8979,7 +8979,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>RotoWire not confirmed; order MLB 3 vs RotoWire 2</t>
+          <t>RotoWire not confirmed</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
@@ -19327,7 +19327,7 @@
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y68" t="inlineStr">
@@ -19347,7 +19347,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>RotoWire not confirmed; order MLB 5 vs RotoWire 4</t>
+          <t>RotoWire not confirmed</t>
         </is>
       </c>
       <c r="AC68" t="inlineStr">
@@ -19891,7 +19891,7 @@
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y70" t="inlineStr">
@@ -19911,7 +19911,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>RotoWire not confirmed; order MLB 9 vs RotoWire 8</t>
+          <t>RotoWire not confirmed</t>
         </is>
       </c>
       <c r="AC70" t="inlineStr">
@@ -22987,7 +22987,7 @@
       </c>
       <c r="X81" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y81" t="inlineStr">
@@ -23007,7 +23007,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>RotoWire not confirmed; order MLB 2 vs RotoWire 6</t>
+          <t>RotoWire not confirmed</t>
         </is>
       </c>
       <c r="AC81" t="inlineStr">
@@ -25496,11 +25496,19 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W90" t="inlineStr"/>
-      <c r="X90" t="inlineStr"/>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="Z90" t="inlineStr">
@@ -25515,7 +25523,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>not found on RotoWire</t>
+          <t>RotoWire not confirmed</t>
         </is>
       </c>
       <c r="AC90" t="inlineStr">
@@ -29131,7 +29139,7 @@
       </c>
       <c r="X103" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y103" t="inlineStr">
@@ -29151,7 +29159,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>RotoWire not confirmed; order MLB 8 vs RotoWire 9</t>
+          <t>RotoWire not confirmed</t>
         </is>
       </c>
       <c r="AC103" t="inlineStr">
@@ -35033,7 +35041,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -35053,7 +35061,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>RotoWire not confirmed; order MLB 4 vs RotoWire 3</t>
+          <t>RotoWire not confirmed</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">

--- a/outputs/hr_rankings.xlsx
+++ b/outputs/hr_rankings.xlsx
@@ -1950,34 +1950,30 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -2168,7 +2164,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -3564,7 +3560,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -4692,7 +4688,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -4972,7 +4968,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -7212,7 +7208,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -8670,34 +8666,30 @@
       </c>
       <c r="W30" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y30" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB30" t="inlineStr"/>
       <c r="AC30" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8954,34 +8946,30 @@
       </c>
       <c r="W31" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X31" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y31" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB31" t="inlineStr"/>
       <c r="AC31" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -10292,7 +10280,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -12322,34 +12310,30 @@
       </c>
       <c r="W43" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X43" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y43" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB43" t="inlineStr"/>
       <c r="AC43" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -13380,7 +13364,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -13660,7 +13644,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -14508,7 +14492,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -14788,7 +14772,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -19322,34 +19306,30 @@
       </c>
       <c r="W68" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z68" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X68" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y68" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z68" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB68" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB68" t="inlineStr"/>
       <c r="AC68" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -19886,34 +19866,30 @@
       </c>
       <c r="W70" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z70" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X70" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y70" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z70" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB70" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB70" t="inlineStr"/>
       <c r="AC70" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -20956,7 +20932,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -22360,7 +22336,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -22982,34 +22958,30 @@
       </c>
       <c r="W81" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z81" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X81" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y81" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z81" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB81" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB81" t="inlineStr"/>
       <c r="AC81" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -23200,7 +23172,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -24316,7 +24288,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -25498,34 +25470,30 @@
       </c>
       <c r="W90" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z90" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X90" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y90" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z90" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA90" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB90" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB90" t="inlineStr"/>
       <c r="AC90" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -26272,7 +26240,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -28504,7 +28472,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -29134,34 +29102,30 @@
       </c>
       <c r="W103" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X103" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y103" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z103" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X103" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y103" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z103" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA103" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB103" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB103" t="inlineStr"/>
       <c r="AC103" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -32684,7 +32648,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -32964,7 +32928,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -35036,34 +35000,30 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -35254,7 +35214,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -36650,7 +36610,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -37778,7 +37738,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -38058,7 +38018,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">

--- a/outputs/hr_rankings.xlsx
+++ b/outputs/hr_rankings.xlsx
@@ -1102,34 +1102,30 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1386,34 +1382,30 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -4442,34 +4434,30 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -4726,34 +4714,30 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -6966,34 +6950,30 @@
       </c>
       <c r="W24" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y24" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB24" t="inlineStr"/>
       <c r="AC24" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8296,7 +8276,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -13106,34 +13086,30 @@
       </c>
       <c r="W46" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X46" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y46" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB46" t="inlineStr"/>
       <c r="AC46" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -19136,7 +19112,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -19696,7 +19672,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -19976,7 +19952,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -22542,34 +22518,30 @@
       </c>
       <c r="W80" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z80" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X80" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y80" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z80" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB80" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB80" t="inlineStr"/>
       <c r="AC80" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -23588,7 +23560,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -27748,7 +27720,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -28370,34 +28342,30 @@
       </c>
       <c r="W101" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y101" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z101" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y101" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z101" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA101" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB101" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB101" t="inlineStr"/>
       <c r="AC101" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -29210,34 +29178,30 @@
       </c>
       <c r="W104" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X104" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y104" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z104" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X104" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y104" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z104" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA104" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB104" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 6 vs RotoWire 8</t>
-        </is>
-      </c>
+      <c r="AB104" t="inlineStr"/>
       <c r="AC104" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -29708,7 +29672,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -32488,7 +32452,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -34226,34 +34190,30 @@
       </c>
       <c r="W122" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X122" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y122" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z122" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X122" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y122" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z122" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA122" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB122" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB122" t="inlineStr"/>
       <c r="AC122" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -35614,34 +35574,30 @@
       </c>
       <c r="W127" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X127" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y127" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z127" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X127" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y127" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z127" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA127" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB127" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB127" t="inlineStr"/>
       <c r="AC127" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -35832,7 +35788,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -36664,7 +36620,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -38876,7 +38832,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -40260,7 +40216,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -42818,34 +42774,30 @@
       </c>
       <c r="W153" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X153" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y153" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z153" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X153" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y153" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z153" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA153" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB153" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB153" t="inlineStr"/>
       <c r="AC153" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -48106,34 +48058,30 @@
       </c>
       <c r="W172" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X172" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y172" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z172" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X172" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y172" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z172" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA172" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB172" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB172" t="inlineStr"/>
       <c r="AC172" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -48390,34 +48338,30 @@
       </c>
       <c r="W173" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X173" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y173" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z173" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X173" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y173" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z173" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA173" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB173" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB173" t="inlineStr"/>
       <c r="AC173" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -49164,7 +49108,7 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
@@ -50062,34 +50006,30 @@
       </c>
       <c r="W179" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X179" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y179" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z179" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X179" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y179" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z179" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA179" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB179" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB179" t="inlineStr"/>
       <c r="AC179" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -52216,7 +52156,7 @@
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
@@ -55828,7 +55768,7 @@
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
@@ -57566,34 +57506,30 @@
       </c>
       <c r="W206" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X206" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y206" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z206" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X206" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y206" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z206" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA206" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB206" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 8 vs RotoWire 9</t>
-        </is>
-      </c>
+      <c r="AB206" t="inlineStr"/>
       <c r="AC206" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -58402,34 +58338,30 @@
       </c>
       <c r="W209" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X209" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y209" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z209" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X209" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y209" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z209" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA209" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB209" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB209" t="inlineStr"/>
       <c r="AC209" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -63048,7 +62980,7 @@
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
@@ -65820,7 +65752,7 @@
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
@@ -70316,28 +70248,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W252" t="inlineStr"/>
-      <c r="X252" t="inlineStr"/>
+      <c r="W252" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X252" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="Y252" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z252" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z252" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA252" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB252" t="inlineStr">
-        <is>
-          <t>not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB252" t="inlineStr"/>
       <c r="AC252" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -70804,7 +70740,7 @@
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
@@ -73960,34 +73896,30 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -74244,34 +74176,30 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -77300,34 +77228,30 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -77584,34 +77508,30 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>

--- a/outputs/hr_rankings.xlsx
+++ b/outputs/hr_rankings.xlsx
@@ -6706,34 +6706,30 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y23" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 2 vs RotoWire 6</t>
-        </is>
-      </c>
+      <c r="AB23" t="inlineStr"/>
       <c r="AC23" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -6990,34 +6986,30 @@
       </c>
       <c r="W24" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y24" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 4 vs RotoWire 3</t>
-        </is>
-      </c>
+      <c r="AB24" t="inlineStr"/>
       <c r="AC24" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8394,34 +8386,30 @@
       </c>
       <c r="W29" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y29" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB29" t="inlineStr"/>
       <c r="AC29" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -19856,28 +19844,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W70" t="inlineStr"/>
-      <c r="X70" t="inlineStr"/>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="Y70" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z70" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z70" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB70" t="inlineStr">
-        <is>
-          <t>not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB70" t="inlineStr"/>
       <c r="AC70" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -25166,34 +25158,30 @@
       </c>
       <c r="W89" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z89" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X89" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y89" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z89" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA89" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB89" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 3 vs RotoWire 2</t>
-        </is>
-      </c>
+      <c r="AB89" t="inlineStr"/>
       <c r="AC89" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -27130,34 +27118,30 @@
       </c>
       <c r="W96" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z96" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X96" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y96" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z96" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA96" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB96" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 8 vs RotoWire 9</t>
-        </is>
-      </c>
+      <c r="AB96" t="inlineStr"/>
       <c r="AC96" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -31598,34 +31582,30 @@
       </c>
       <c r="W112" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X112" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y112" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z112" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X112" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y112" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z112" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA112" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB112" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 6 vs RotoWire 5</t>
-        </is>
-      </c>
+      <c r="AB112" t="inlineStr"/>
       <c r="AC112" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -36900,28 +36880,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W131" t="inlineStr"/>
-      <c r="X131" t="inlineStr"/>
+      <c r="W131" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X131" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="Y131" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z131" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z131" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA131" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB131" t="inlineStr">
-        <is>
-          <t>not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB131" t="inlineStr"/>
       <c r="AC131" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -62848,28 +62832,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W224" t="inlineStr"/>
-      <c r="X224" t="inlineStr"/>
+      <c r="W224" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X224" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="Y224" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z224" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z224" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA224" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB224" t="inlineStr">
-        <is>
-          <t>not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB224" t="inlineStr"/>
       <c r="AC224" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>

--- a/outputs/hr_rankings.xlsx
+++ b/outputs/hr_rankings.xlsx
@@ -2786,34 +2786,30 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3068,28 +3064,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr"/>
-      <c r="X10" t="inlineStr"/>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="Y10" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3906,34 +3906,30 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 3 vs RotoWire 5</t>
-        </is>
-      </c>
+      <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -5318,34 +5314,30 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -5602,34 +5594,30 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9506,34 +9494,30 @@
       </c>
       <c r="W33" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y33" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 4 vs RotoWire 3</t>
-        </is>
-      </c>
+      <c r="AB33" t="inlineStr"/>
       <c r="AC33" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -14242,34 +14226,30 @@
       </c>
       <c r="W50" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X50" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y50" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB50" t="inlineStr"/>
       <c r="AC50" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -19542,34 +19522,30 @@
       </c>
       <c r="W69" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z69" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X69" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y69" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z69" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB69" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB69" t="inlineStr"/>
       <c r="AC69" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -21506,34 +21482,30 @@
       </c>
       <c r="W76" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z76" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X76" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y76" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z76" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB76" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB76" t="inlineStr"/>
       <c r="AC76" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -23462,34 +23434,30 @@
       </c>
       <c r="W83" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z83" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X83" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y83" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z83" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB83" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 6 vs RotoWire 7</t>
-        </is>
-      </c>
+      <c r="AB83" t="inlineStr"/>
       <c r="AC83" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -27922,34 +27890,30 @@
       </c>
       <c r="W99" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z99" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X99" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y99" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z99" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA99" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB99" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB99" t="inlineStr"/>
       <c r="AC99" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -30434,34 +30398,30 @@
       </c>
       <c r="W108" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X108" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y108" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z108" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X108" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y108" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z108" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA108" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB108" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB108" t="inlineStr"/>
       <c r="AC108" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -33230,34 +33190,30 @@
       </c>
       <c r="W118" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X118" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y118" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z118" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X118" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y118" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z118" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA118" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB118" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB118" t="inlineStr"/>
       <c r="AC118" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -40470,34 +40426,30 @@
       </c>
       <c r="W144" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X144" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y144" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z144" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X144" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y144" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z144" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA144" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB144" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB144" t="inlineStr"/>
       <c r="AC144" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -43258,34 +43210,30 @@
       </c>
       <c r="W154" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X154" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y154" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z154" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X154" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y154" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z154" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA154" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB154" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB154" t="inlineStr"/>
       <c r="AC154" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -45218,34 +45166,30 @@
       </c>
       <c r="W161" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X161" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y161" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z161" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X161" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y161" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z161" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA161" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB161" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 7 vs RotoWire 8</t>
-        </is>
-      </c>
+      <c r="AB161" t="inlineStr"/>
       <c r="AC161" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -46614,34 +46558,30 @@
       </c>
       <c r="W166" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X166" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y166" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z166" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X166" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y166" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z166" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA166" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB166" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB166" t="inlineStr"/>
       <c r="AC166" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -54698,34 +54638,30 @@
       </c>
       <c r="W195" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X195" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y195" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z195" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X195" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y195" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z195" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA195" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB195" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 8 vs RotoWire 6</t>
-        </is>
-      </c>
+      <c r="AB195" t="inlineStr"/>
       <c r="AC195" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -65828,34 +65764,30 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -66110,28 +66042,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr"/>
-      <c r="X10" t="inlineStr"/>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="Y10" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -66948,34 +66884,30 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 3 vs RotoWire 5</t>
-        </is>
-      </c>
+      <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -68360,34 +68292,30 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -68644,34 +68572,30 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>

--- a/outputs/hr_rankings.xlsx
+++ b/outputs/hr_rankings.xlsx
@@ -4984,7 +4984,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>61.7</v>
+        <v>61.6</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -5017,7 +5017,7 @@
         <v>80</v>
       </c>
       <c r="U17" t="n">
-        <v>37.8</v>
+        <v>36.3</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
@@ -5074,7 +5074,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
@@ -5084,7 +5084,7 @@
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/24, 1 HR</t>
+          <t>Last 7 games: 6/25, 1 HR</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
@@ -11628,7 +11628,7 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>57.4</v>
+        <v>57.3</v>
       </c>
       <c r="M41" t="inlineStr">
         <is>
@@ -11661,7 +11661,7 @@
         <v>75</v>
       </c>
       <c r="U41" t="n">
-        <v>34.9</v>
+        <v>33.7</v>
       </c>
       <c r="V41" t="inlineStr">
         <is>
@@ -11718,7 +11718,7 @@
       </c>
       <c r="AI41" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ41" t="inlineStr">
@@ -11728,7 +11728,7 @@
       </c>
       <c r="AK41" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/26, 1 HR</t>
+          <t>Last 7 games: 6/27, 1 HR</t>
         </is>
       </c>
       <c r="AL41" t="inlineStr">
@@ -13584,7 +13584,7 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>56.2</v>
+        <v>56.1</v>
       </c>
       <c r="M48" t="inlineStr">
         <is>
@@ -13617,7 +13617,7 @@
         <v>80</v>
       </c>
       <c r="U48" t="n">
-        <v>44.1</v>
+        <v>42.3</v>
       </c>
       <c r="V48" t="inlineStr">
         <is>
@@ -13674,7 +13674,7 @@
       </c>
       <c r="AI48" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ48" t="inlineStr">
@@ -13684,7 +13684,7 @@
       </c>
       <c r="AK48" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/24, 1 HR</t>
+          <t>Last 7 games: 7/25, 1 HR</t>
         </is>
       </c>
       <c r="AL48" t="inlineStr">
@@ -18036,7 +18036,7 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>54.3</v>
+        <v>54.2</v>
       </c>
       <c r="M64" t="inlineStr">
         <is>
@@ -18069,7 +18069,7 @@
         <v>50</v>
       </c>
       <c r="U64" t="n">
-        <v>37.8</v>
+        <v>36</v>
       </c>
       <c r="V64" t="inlineStr">
         <is>
@@ -18126,7 +18126,7 @@
       </c>
       <c r="AI64" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ64" t="inlineStr">
@@ -18136,7 +18136,7 @@
       </c>
       <c r="AK64" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/20, 1 HR</t>
+          <t>Last 7 games: 5/21, 1 HR</t>
         </is>
       </c>
       <c r="AL64" t="inlineStr">
@@ -22991,27 +22991,27 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>592626</t>
+          <t>641355</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Joc Pederson</t>
+          <t>Cody Bellinger</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-07-01T17:10:00Z</t>
+          <t>2026-07-01T17:35:00Z</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -23021,26 +23021,26 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Joey Cantillo</t>
+          <t>Troy Melton</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>676282</t>
+          <t>675512</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L82" t="n">
-        <v>52</v>
+        <v>51.9</v>
       </c>
       <c r="M82" t="inlineStr">
         <is>
@@ -23054,54 +23054,58 @@
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>Strong Barrel, Hot Hitter/Streak</t>
+          <t>Good Environment, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P82" t="n">
-        <v>48.6</v>
+        <v>32.7</v>
       </c>
       <c r="Q82" t="n">
-        <v>38.6</v>
+        <v>35.8</v>
       </c>
       <c r="R82" t="n">
-        <v>47.6</v>
+        <v>78.7</v>
       </c>
       <c r="S82" t="n">
-        <v>76.2</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T82" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U82" t="n">
-        <v>87</v>
+        <v>0</v>
       </c>
       <c r="V82" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W82" t="inlineStr"/>
-      <c r="X82" t="inlineStr"/>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="Y82" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z82" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z82" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB82" t="inlineStr">
-        <is>
-          <t>not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB82" t="inlineStr"/>
       <c r="AC82" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -23121,142 +23125,142 @@
       </c>
       <c r="AH82" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI82" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK82" t="inlineStr">
         <is>
-          <t>Hot streak: 5 HR in last 7 games</t>
+          <t>Last 7 games: 2/25, 0 HR</t>
         </is>
       </c>
       <c r="AL82" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.4% barrel, 11.4 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.1% barrel, 7.0 HR allowed</t>
         </is>
       </c>
       <c r="AM82" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN82" t="inlineStr">
         <is>
-          <t>10.97</t>
+          <t>7.5</t>
         </is>
       </c>
       <c r="AO82" t="inlineStr">
         <is>
-          <t>48.44</t>
+          <t>37.55</t>
         </is>
       </c>
       <c r="AP82" t="inlineStr">
         <is>
-          <t>91.83</t>
+          <t>88.93</t>
         </is>
       </c>
       <c r="AQ82" t="inlineStr">
         <is>
-          <t>101.8811</t>
+          <t>98.6226</t>
         </is>
       </c>
       <c r="AR82" t="inlineStr">
         <is>
-          <t>0.4343</t>
+          <t>0.4362</t>
         </is>
       </c>
       <c r="AS82" t="inlineStr">
         <is>
-          <t>0.188</t>
+          <t>0.1624</t>
         </is>
       </c>
       <c r="AT82" t="inlineStr">
         <is>
-          <t>0.3437</t>
+          <t>0.3524</t>
         </is>
       </c>
       <c r="AU82" t="inlineStr">
         <is>
-          <t>72.35</t>
+          <t>69.68</t>
         </is>
       </c>
       <c r="AV82" t="inlineStr">
         <is>
-          <t>23.19</t>
+          <t>3.63</t>
         </is>
       </c>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>40.94</t>
+          <t>42.05</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>27.93</t>
+          <t>32.41</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr">
         <is>
-          <t>12.5</t>
+          <t>16.4</t>
         </is>
       </c>
       <c r="AZ82" t="inlineStr">
         <is>
-          <t>0.2072</t>
+          <t>0.1898</t>
         </is>
       </c>
       <c r="BA82" t="inlineStr">
         <is>
-          <t>8.39</t>
+          <t>7.06</t>
         </is>
       </c>
       <c r="BB82" t="inlineStr">
         <is>
-          <t>38.16</t>
+          <t>37.86</t>
         </is>
       </c>
       <c r="BC82" t="inlineStr">
         <is>
-          <t>88.1</t>
+          <t>89.33</t>
         </is>
       </c>
       <c r="BD82" t="inlineStr">
         <is>
-          <t>0.3854</t>
+          <t>0.3808</t>
         </is>
       </c>
       <c r="BE82" t="inlineStr">
         <is>
-          <t>0.1522</t>
+          <t>0.161</t>
         </is>
       </c>
       <c r="BF82" t="inlineStr">
         <is>
-          <t>30.1</t>
+          <t>28.55</t>
         </is>
       </c>
       <c r="BG82" t="inlineStr">
         <is>
-          <t>In From LF</t>
+          <t>Out To LF</t>
         </is>
       </c>
       <c r="BH82" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>95</t>
         </is>
       </c>
       <c r="BI82" t="inlineStr">
         <is>
-          <t>Progressive Field</t>
+          <t>Yankee Stadium</t>
         </is>
       </c>
       <c r="BJ82" t="inlineStr"/>
@@ -23267,47 +23271,47 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>641355</t>
+          <t>572233</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Cody Bellinger</t>
+          <t>Christian Walker</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-07-01T17:35:00Z</t>
+          <t>2026-07-02T00:10:00Z</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>Troy Melton</t>
+          <t>Taj Bradley</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>675512</t>
+          <t>671737</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
@@ -23330,58 +23334,62 @@
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>Good Environment, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P83" t="n">
-        <v>32.7</v>
+        <v>44.2</v>
       </c>
       <c r="Q83" t="n">
-        <v>35.8</v>
+        <v>50.8</v>
       </c>
       <c r="R83" t="n">
-        <v>78.7</v>
+        <v>40.1</v>
       </c>
       <c r="S83" t="n">
-        <v>96.59999999999999</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="T83" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U83" t="n">
-        <v>0</v>
+        <v>40.3</v>
       </c>
       <c r="V83" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W83" t="inlineStr">
+      <c r="Z83" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X83" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y83" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z83" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB83" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC83" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -23401,142 +23409,142 @@
       </c>
       <c r="AH83" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI83" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/25, 0 HR</t>
+          <t>Last 7 games: 8/30, 1 HR</t>
         </is>
       </c>
       <c r="AL83" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.1% barrel, 7.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 9.5% barrel, 14.1 HR allowed</t>
         </is>
       </c>
       <c r="AM83" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN83" t="inlineStr">
         <is>
-          <t>7.5</t>
+          <t>10.73</t>
         </is>
       </c>
       <c r="AO83" t="inlineStr">
         <is>
-          <t>37.55</t>
+          <t>44.56</t>
         </is>
       </c>
       <c r="AP83" t="inlineStr">
         <is>
-          <t>88.93</t>
+          <t>90.2</t>
         </is>
       </c>
       <c r="AQ83" t="inlineStr">
         <is>
-          <t>98.6226</t>
+          <t>101.8076</t>
         </is>
       </c>
       <c r="AR83" t="inlineStr">
         <is>
-          <t>0.4362</t>
+          <t>0.4063</t>
         </is>
       </c>
       <c r="AS83" t="inlineStr">
         <is>
-          <t>0.1624</t>
+          <t>0.1771</t>
         </is>
       </c>
       <c r="AT83" t="inlineStr">
         <is>
-          <t>0.3524</t>
+          <t>0.3063</t>
         </is>
       </c>
       <c r="AU83" t="inlineStr">
         <is>
-          <t>69.68</t>
+          <t>74.17</t>
         </is>
       </c>
       <c r="AV83" t="inlineStr">
         <is>
-          <t>3.63</t>
+          <t>42.25</t>
         </is>
       </c>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>42.05</t>
+          <t>43.67</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>32.41</t>
+          <t>28.77</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr">
         <is>
-          <t>16.4</t>
+          <t>21.4</t>
         </is>
       </c>
       <c r="AZ83" t="inlineStr">
         <is>
-          <t>0.1898</t>
+          <t>0.2166</t>
         </is>
       </c>
       <c r="BA83" t="inlineStr">
         <is>
-          <t>7.06</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="BB83" t="inlineStr">
         <is>
-          <t>37.86</t>
+          <t>44.24</t>
         </is>
       </c>
       <c r="BC83" t="inlineStr">
         <is>
-          <t>89.33</t>
+          <t>90.95</t>
         </is>
       </c>
       <c r="BD83" t="inlineStr">
         <is>
-          <t>0.3808</t>
+          <t>0.398</t>
         </is>
       </c>
       <c r="BE83" t="inlineStr">
         <is>
-          <t>0.161</t>
+          <t>0.1631</t>
         </is>
       </c>
       <c r="BF83" t="inlineStr">
         <is>
-          <t>28.55</t>
+          <t>30.17</t>
         </is>
       </c>
       <c r="BG83" t="inlineStr">
         <is>
-          <t>Out To LF</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH83" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>70</t>
         </is>
       </c>
       <c r="BI83" t="inlineStr">
         <is>
-          <t>Yankee Stadium</t>
+          <t>Daikin Park</t>
         </is>
       </c>
       <c r="BJ83" t="inlineStr"/>
@@ -23547,56 +23555,56 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>572233</t>
+          <t>592626</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Christian Walker</t>
+          <t>Joc Pederson</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-07-02T00:10:00Z</t>
+          <t>2026-07-01T17:10:00Z</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>Taj Bradley</t>
+          <t>Joey Cantillo</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>671737</t>
+          <t>676282</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L84" t="n">
-        <v>51.9</v>
+        <v>51.7</v>
       </c>
       <c r="M84" t="inlineStr">
         <is>
@@ -23610,60 +23618,52 @@
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P84" t="n">
-        <v>44.2</v>
+        <v>48.6</v>
       </c>
       <c r="Q84" t="n">
-        <v>50.8</v>
+        <v>38.6</v>
       </c>
       <c r="R84" t="n">
-        <v>40.1</v>
+        <v>47.6</v>
       </c>
       <c r="S84" t="n">
-        <v>90.40000000000001</v>
+        <v>76.2</v>
       </c>
       <c r="T84" t="n">
         <v>50</v>
       </c>
       <c r="U84" t="n">
-        <v>40.3</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="V84" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr"/>
+      <c r="X84" t="inlineStr"/>
+      <c r="Y84" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W84" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X84" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y84" t="inlineStr">
+      <c r="Z84" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z84" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>not found on RotoWire</t>
         </is>
       </c>
       <c r="AC84" t="inlineStr">
@@ -23690,22 +23690,22 @@
       </c>
       <c r="AI84" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AK84" t="inlineStr">
         <is>
-          <t>Last 7 games: 8/30, 1 HR</t>
+          <t>Hot streak: 5 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL84" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 9.5% barrel, 14.1 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.4% barrel, 11.4 HR allowed</t>
         </is>
       </c>
       <c r="AM84" t="inlineStr">
@@ -23715,112 +23715,112 @@
       </c>
       <c r="AN84" t="inlineStr">
         <is>
-          <t>10.73</t>
+          <t>10.97</t>
         </is>
       </c>
       <c r="AO84" t="inlineStr">
         <is>
-          <t>44.56</t>
+          <t>48.44</t>
         </is>
       </c>
       <c r="AP84" t="inlineStr">
         <is>
-          <t>90.2</t>
+          <t>91.83</t>
         </is>
       </c>
       <c r="AQ84" t="inlineStr">
         <is>
-          <t>101.8076</t>
+          <t>101.8811</t>
         </is>
       </c>
       <c r="AR84" t="inlineStr">
         <is>
-          <t>0.4063</t>
+          <t>0.4343</t>
         </is>
       </c>
       <c r="AS84" t="inlineStr">
         <is>
-          <t>0.1771</t>
+          <t>0.188</t>
         </is>
       </c>
       <c r="AT84" t="inlineStr">
         <is>
-          <t>0.3063</t>
+          <t>0.3437</t>
         </is>
       </c>
       <c r="AU84" t="inlineStr">
         <is>
-          <t>74.17</t>
+          <t>72.35</t>
         </is>
       </c>
       <c r="AV84" t="inlineStr">
         <is>
-          <t>42.25</t>
+          <t>23.19</t>
         </is>
       </c>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>43.67</t>
+          <t>40.94</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>28.77</t>
+          <t>27.93</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr">
         <is>
-          <t>21.4</t>
+          <t>12.5</t>
         </is>
       </c>
       <c r="AZ84" t="inlineStr">
         <is>
-          <t>0.2166</t>
+          <t>0.2072</t>
         </is>
       </c>
       <c r="BA84" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>8.39</t>
         </is>
       </c>
       <c r="BB84" t="inlineStr">
         <is>
-          <t>44.24</t>
+          <t>38.16</t>
         </is>
       </c>
       <c r="BC84" t="inlineStr">
         <is>
-          <t>90.95</t>
+          <t>88.1</t>
         </is>
       </c>
       <c r="BD84" t="inlineStr">
         <is>
-          <t>0.398</t>
+          <t>0.3854</t>
         </is>
       </c>
       <c r="BE84" t="inlineStr">
         <is>
-          <t>0.1631</t>
+          <t>0.1522</t>
         </is>
       </c>
       <c r="BF84" t="inlineStr">
         <is>
-          <t>30.17</t>
+          <t>30.1</t>
         </is>
       </c>
       <c r="BG84" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>In From LF</t>
         </is>
       </c>
       <c r="BH84" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>90</t>
         </is>
       </c>
       <c r="BI84" t="inlineStr">
         <is>
-          <t>Daikin Park</t>
+          <t>Progressive Field</t>
         </is>
       </c>
       <c r="BJ84" t="inlineStr"/>
@@ -26636,7 +26636,7 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>50.6</v>
+        <v>50.5</v>
       </c>
       <c r="M95" t="inlineStr">
         <is>
@@ -26669,7 +26669,7 @@
         <v>50</v>
       </c>
       <c r="U95" t="n">
-        <v>29.7</v>
+        <v>27.7</v>
       </c>
       <c r="V95" t="inlineStr">
         <is>
@@ -26726,7 +26726,7 @@
       </c>
       <c r="AI95" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ95" t="inlineStr">
@@ -26736,7 +26736,7 @@
       </c>
       <c r="AK95" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/22, 0 HR</t>
+          <t>Last 7 games: 7/23, 0 HR</t>
         </is>
       </c>
       <c r="AL95" t="inlineStr">
@@ -29091,47 +29091,47 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>663586</t>
+          <t>621020</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Austin Riley</t>
+          <t>Dansby Swanson</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>CHC</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-07-01T23:15:00Z</t>
+          <t>2026-07-01T18:20:00Z</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>Michael McGreevy</t>
+          <t>Walker Buehler</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>700241</t>
+          <t>621111</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
@@ -29154,26 +29154,26 @@
       </c>
       <c r="O104" t="inlineStr">
         <is>
-          <t>Strong Barrel</t>
+          <t>Good Environment, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P104" t="n">
-        <v>49</v>
+        <v>39.3</v>
       </c>
       <c r="Q104" t="n">
-        <v>51.1</v>
+        <v>41.4</v>
       </c>
       <c r="R104" t="n">
-        <v>47.9</v>
+        <v>78.8</v>
       </c>
       <c r="S104" t="n">
-        <v>64.3</v>
+        <v>44.8</v>
       </c>
       <c r="T104" t="n">
         <v>50</v>
       </c>
       <c r="U104" t="n">
-        <v>6</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="V104" t="inlineStr">
         <is>
@@ -29187,7 +29187,7 @@
       </c>
       <c r="X104" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y104" t="inlineStr">
@@ -29225,27 +29225,27 @@
       </c>
       <c r="AH104" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AI104" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="AJ104" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AI104" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="AJ104" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AK104" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/25, 0 HR</t>
+          <t>Hot streak: 4 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL104" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 9.0% barrel, 12.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.4% barrel, 10.8 HR allowed</t>
         </is>
       </c>
       <c r="AM104" t="inlineStr">
@@ -29255,112 +29255,112 @@
       </c>
       <c r="AN104" t="inlineStr">
         <is>
-          <t>11.42</t>
+          <t>8.97</t>
         </is>
       </c>
       <c r="AO104" t="inlineStr">
         <is>
-          <t>45.79</t>
+          <t>44.02</t>
         </is>
       </c>
       <c r="AP104" t="inlineStr">
         <is>
-          <t>91.25</t>
+          <t>90.01</t>
         </is>
       </c>
       <c r="AQ104" t="inlineStr">
         <is>
-          <t>102.393</t>
+          <t>100.0782</t>
         </is>
       </c>
       <c r="AR104" t="inlineStr">
         <is>
-          <t>0.4027</t>
+          <t>0.3965</t>
         </is>
       </c>
       <c r="AS104" t="inlineStr">
         <is>
-          <t>0.1851</t>
+          <t>0.1722</t>
         </is>
       </c>
       <c r="AT104" t="inlineStr">
         <is>
-          <t>0.3034</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="AU104" t="inlineStr">
         <is>
-          <t>75.69</t>
+          <t>71.25</t>
         </is>
       </c>
       <c r="AV104" t="inlineStr">
         <is>
-          <t>58.26</t>
+          <t>8.43</t>
         </is>
       </c>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>40.78</t>
+          <t>45.1</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>31.71</t>
+          <t>31.43</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr">
         <is>
-          <t>10.4</t>
+          <t>16.3</t>
         </is>
       </c>
       <c r="AZ104" t="inlineStr">
         <is>
-          <t>0.1386</t>
+          <t>0.1863</t>
         </is>
       </c>
       <c r="BA104" t="inlineStr">
         <is>
-          <t>9.01</t>
+          <t>8.38</t>
         </is>
       </c>
       <c r="BB104" t="inlineStr">
         <is>
-          <t>40.1</t>
+          <t>40.67</t>
         </is>
       </c>
       <c r="BC104" t="inlineStr">
         <is>
-          <t>89.8</t>
+          <t>89.86</t>
         </is>
       </c>
       <c r="BD104" t="inlineStr">
         <is>
-          <t>0.4892</t>
+          <t>0.4185</t>
         </is>
       </c>
       <c r="BE104" t="inlineStr">
         <is>
-          <t>0.2012</t>
+          <t>0.1519</t>
         </is>
       </c>
       <c r="BF104" t="inlineStr">
         <is>
-          <t>25.43</t>
+          <t>20.99</t>
         </is>
       </c>
       <c r="BG104" t="inlineStr">
         <is>
-          <t>In From LF</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH104" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>92</t>
         </is>
       </c>
       <c r="BI104" t="inlineStr">
         <is>
-          <t>Truist Park</t>
+          <t>Wrigley Field</t>
         </is>
       </c>
       <c r="BJ104" t="inlineStr"/>
@@ -29371,47 +29371,47 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>621020</t>
+          <t>663586</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Dansby Swanson</t>
+          <t>Austin Riley</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>CHC</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-07-01T18:20:00Z</t>
+          <t>2026-07-01T23:15:00Z</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>Walker Buehler</t>
+          <t>Michael McGreevy</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>621111</t>
+          <t>700241</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
@@ -29420,7 +29420,7 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>49.1</v>
+        <v>49.4</v>
       </c>
       <c r="M105" t="inlineStr">
         <is>
@@ -29434,26 +29434,26 @@
       </c>
       <c r="O105" t="inlineStr">
         <is>
-          <t>Good Environment, Hot Hitter/Streak</t>
+          <t>Strong Barrel</t>
         </is>
       </c>
       <c r="P105" t="n">
-        <v>39.3</v>
+        <v>49</v>
       </c>
       <c r="Q105" t="n">
-        <v>41.4</v>
+        <v>51.1</v>
       </c>
       <c r="R105" t="n">
-        <v>78.8</v>
+        <v>47.9</v>
       </c>
       <c r="S105" t="n">
-        <v>44.8</v>
+        <v>64.3</v>
       </c>
       <c r="T105" t="n">
         <v>50</v>
       </c>
       <c r="U105" t="n">
-        <v>73</v>
+        <v>6</v>
       </c>
       <c r="V105" t="inlineStr">
         <is>
@@ -29467,7 +29467,7 @@
       </c>
       <c r="X105" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y105" t="inlineStr">
@@ -29505,7 +29505,7 @@
       </c>
       <c r="AH105" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI105" t="inlineStr">
@@ -29515,17 +29515,17 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
         <is>
-          <t>Hot streak: 3 HR in last 7 games</t>
+          <t>Last 7 games: 4/25, 0 HR</t>
         </is>
       </c>
       <c r="AL105" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.4% barrel, 10.8 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 9.0% barrel, 12.0 HR allowed</t>
         </is>
       </c>
       <c r="AM105" t="inlineStr">
@@ -29535,112 +29535,112 @@
       </c>
       <c r="AN105" t="inlineStr">
         <is>
-          <t>8.97</t>
+          <t>11.42</t>
         </is>
       </c>
       <c r="AO105" t="inlineStr">
         <is>
-          <t>44.02</t>
+          <t>45.79</t>
         </is>
       </c>
       <c r="AP105" t="inlineStr">
         <is>
-          <t>90.01</t>
+          <t>91.25</t>
         </is>
       </c>
       <c r="AQ105" t="inlineStr">
         <is>
-          <t>100.0782</t>
+          <t>102.393</t>
         </is>
       </c>
       <c r="AR105" t="inlineStr">
         <is>
-          <t>0.3965</t>
+          <t>0.4027</t>
         </is>
       </c>
       <c r="AS105" t="inlineStr">
         <is>
-          <t>0.1722</t>
+          <t>0.1851</t>
         </is>
       </c>
       <c r="AT105" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.3034</t>
         </is>
       </c>
       <c r="AU105" t="inlineStr">
         <is>
-          <t>71.25</t>
+          <t>75.69</t>
         </is>
       </c>
       <c r="AV105" t="inlineStr">
         <is>
-          <t>8.43</t>
+          <t>58.26</t>
         </is>
       </c>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>45.1</t>
+          <t>40.78</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>31.43</t>
+          <t>31.71</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr">
         <is>
-          <t>16.3</t>
+          <t>10.4</t>
         </is>
       </c>
       <c r="AZ105" t="inlineStr">
         <is>
-          <t>0.1863</t>
+          <t>0.1386</t>
         </is>
       </c>
       <c r="BA105" t="inlineStr">
         <is>
-          <t>8.38</t>
+          <t>9.01</t>
         </is>
       </c>
       <c r="BB105" t="inlineStr">
         <is>
-          <t>40.67</t>
+          <t>40.1</t>
         </is>
       </c>
       <c r="BC105" t="inlineStr">
         <is>
-          <t>89.86</t>
+          <t>89.8</t>
         </is>
       </c>
       <c r="BD105" t="inlineStr">
         <is>
-          <t>0.4185</t>
+          <t>0.4892</t>
         </is>
       </c>
       <c r="BE105" t="inlineStr">
         <is>
-          <t>0.1519</t>
+          <t>0.2012</t>
         </is>
       </c>
       <c r="BF105" t="inlineStr">
         <is>
-          <t>20.99</t>
+          <t>25.43</t>
         </is>
       </c>
       <c r="BG105" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>In From LF</t>
         </is>
       </c>
       <c r="BH105" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>90</t>
         </is>
       </c>
       <c r="BI105" t="inlineStr">
         <is>
-          <t>Wrigley Field</t>
+          <t>Truist Park</t>
         </is>
       </c>
       <c r="BJ105" t="inlineStr"/>
@@ -31887,27 +31887,27 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>678011</t>
+          <t>630105</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Anthony Seigler</t>
+          <t>Jake Cronenworth</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>WSH</t>
+          <t>CHC</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2026-07-01T17:35:00Z</t>
+          <t>2026-07-01T18:20:00Z</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
@@ -31917,17 +31917,17 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>Brad Lord</t>
+          <t>Colin Rea</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>695418</t>
+          <t>607067</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
@@ -31950,26 +31950,26 @@
       </c>
       <c r="O114" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge</t>
+          <t>Good Environment, Platoon Edge</t>
         </is>
       </c>
       <c r="P114" t="n">
-        <v>21.7</v>
+        <v>17.9</v>
       </c>
       <c r="Q114" t="n">
-        <v>31.7</v>
+        <v>55.5</v>
       </c>
       <c r="R114" t="n">
-        <v>69.2</v>
+        <v>78.8</v>
       </c>
       <c r="S114" t="n">
-        <v>93.2</v>
+        <v>64.3</v>
       </c>
       <c r="T114" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="U114" t="n">
-        <v>57.5</v>
+        <v>10.1</v>
       </c>
       <c r="V114" t="inlineStr">
         <is>
@@ -31983,7 +31983,7 @@
       </c>
       <c r="X114" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y114" t="inlineStr">
@@ -32021,27 +32021,27 @@
       </c>
       <c r="AH114" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI114" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK114" t="inlineStr">
         <is>
-          <t>Contact streak: 8/21 over last 7 games</t>
+          <t>Last 7 games: 3/16, 0 HR</t>
         </is>
       </c>
       <c r="AL114" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 6.3% barrel, 9.3 HR allowed</t>
+          <t>platoon edge; pitcher baseline 10.9% barrel, 14.4 HR allowed</t>
         </is>
       </c>
       <c r="AM114" t="inlineStr">
@@ -32051,112 +32051,112 @@
       </c>
       <c r="AN114" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>5.43</t>
         </is>
       </c>
       <c r="AO114" t="inlineStr">
         <is>
-          <t>45.13</t>
+          <t>32.98</t>
         </is>
       </c>
       <c r="AP114" t="inlineStr">
         <is>
-          <t>90.28</t>
+          <t>87.45</t>
         </is>
       </c>
       <c r="AQ114" t="inlineStr">
         <is>
-          <t>98.1914</t>
+          <t>97.9991</t>
         </is>
       </c>
       <c r="AR114" t="inlineStr">
         <is>
-          <t>0.3754</t>
+          <t>0.3271</t>
         </is>
       </c>
       <c r="AS114" t="inlineStr">
         <is>
-          <t>0.109</t>
+          <t>0.1105</t>
         </is>
       </c>
       <c r="AT114" t="inlineStr">
         <is>
-          <t>0.3198</t>
+          <t>0.3029</t>
         </is>
       </c>
       <c r="AU114" t="inlineStr">
         <is>
-          <t>67.67</t>
+          <t>71.81</t>
         </is>
       </c>
       <c r="AV114" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>19.98</t>
         </is>
       </c>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>30.29</t>
+          <t>33.71</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>15.27</t>
+          <t>21.39</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AZ114" t="inlineStr">
         <is>
-          <t>0.1448</t>
+          <t>0.0736</t>
         </is>
       </c>
       <c r="BA114" t="inlineStr">
         <is>
-          <t>6.33</t>
+          <t>10.86</t>
         </is>
       </c>
       <c r="BB114" t="inlineStr">
         <is>
-          <t>42.29</t>
+          <t>41.21</t>
         </is>
       </c>
       <c r="BC114" t="inlineStr">
         <is>
-          <t>88.01</t>
+          <t>89.87</t>
         </is>
       </c>
       <c r="BD114" t="inlineStr">
         <is>
-          <t>0.4027</t>
+          <t>0.4639</t>
         </is>
       </c>
       <c r="BE114" t="inlineStr">
         <is>
-          <t>0.1502</t>
+          <t>0.1959</t>
         </is>
       </c>
       <c r="BF114" t="inlineStr">
         <is>
-          <t>19.69</t>
+          <t>26.12</t>
         </is>
       </c>
       <c r="BG114" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH114" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>92</t>
         </is>
       </c>
       <c r="BI114" t="inlineStr">
         <is>
-          <t>Fenway Park</t>
+          <t>Wrigley Field</t>
         </is>
       </c>
       <c r="BJ114" t="inlineStr"/>
@@ -32723,22 +32723,22 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>681546</t>
+          <t>678011</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>James Outman</t>
+          <t>Anthony Seigler</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>WSH</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -32753,17 +32753,17 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>Will Warren</t>
+          <t>Brad Lord</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>701542</t>
+          <t>695418</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
@@ -32786,26 +32786,26 @@
       </c>
       <c r="O117" t="inlineStr">
         <is>
-          <t>Good Environment, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P117" t="n">
-        <v>26.4</v>
+        <v>21.7</v>
       </c>
       <c r="Q117" t="n">
-        <v>42.9</v>
+        <v>31.7</v>
       </c>
       <c r="R117" t="n">
-        <v>78.7</v>
+        <v>69.2</v>
       </c>
       <c r="S117" t="n">
-        <v>52.4</v>
+        <v>93.2</v>
       </c>
       <c r="T117" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="U117" t="n">
-        <v>47.2</v>
+        <v>54.9</v>
       </c>
       <c r="V117" t="inlineStr">
         <is>
@@ -32819,7 +32819,7 @@
       </c>
       <c r="X117" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y117" t="inlineStr">
@@ -32857,27 +32857,27 @@
       </c>
       <c r="AH117" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI117" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Contact streak: 8/22 over last 7 games</t>
         </is>
       </c>
       <c r="AL117" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.3% barrel, 12.9 HR allowed</t>
+          <t>switch hitter; pitcher baseline 6.3% barrel, 9.3 HR allowed</t>
         </is>
       </c>
       <c r="AM117" t="inlineStr">
@@ -32887,102 +32887,102 @@
       </c>
       <c r="AN117" t="inlineStr">
         <is>
-          <t>9.13</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="AO117" t="inlineStr">
         <is>
-          <t>33.38</t>
+          <t>45.13</t>
         </is>
       </c>
       <c r="AP117" t="inlineStr">
         <is>
-          <t>87.44</t>
+          <t>90.28</t>
         </is>
       </c>
       <c r="AQ117" t="inlineStr">
         <is>
-          <t>98.2712</t>
+          <t>98.1914</t>
         </is>
       </c>
       <c r="AR117" t="inlineStr">
         <is>
-          <t>0.2943</t>
+          <t>0.3754</t>
         </is>
       </c>
       <c r="AS117" t="inlineStr">
         <is>
-          <t>0.137</t>
+          <t>0.109</t>
         </is>
       </c>
       <c r="AT117" t="inlineStr">
         <is>
-          <t>0.2405</t>
+          <t>0.3198</t>
         </is>
       </c>
       <c r="AU117" t="inlineStr">
         <is>
-          <t>72.11</t>
+          <t>67.67</t>
         </is>
       </c>
       <c r="AV117" t="inlineStr">
         <is>
-          <t>19.27</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>58.4</t>
+          <t>30.29</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>28.97</t>
+          <t>15.27</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr">
         <is>
-          <t>3.9</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="AZ117" t="inlineStr">
         <is>
-          <t>0.1639</t>
+          <t>0.1448</t>
         </is>
       </c>
       <c r="BA117" t="inlineStr">
         <is>
-          <t>8.31</t>
+          <t>6.33</t>
         </is>
       </c>
       <c r="BB117" t="inlineStr">
         <is>
-          <t>40.33</t>
+          <t>42.29</t>
         </is>
       </c>
       <c r="BC117" t="inlineStr">
         <is>
-          <t>90.16</t>
+          <t>88.01</t>
         </is>
       </c>
       <c r="BD117" t="inlineStr">
         <is>
-          <t>0.4064</t>
+          <t>0.4027</t>
         </is>
       </c>
       <c r="BE117" t="inlineStr">
         <is>
-          <t>0.1568</t>
+          <t>0.1502</t>
         </is>
       </c>
       <c r="BF117" t="inlineStr">
         <is>
-          <t>24.94</t>
+          <t>19.69</t>
         </is>
       </c>
       <c r="BG117" t="inlineStr">
         <is>
-          <t>Out To LF</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BH117" t="inlineStr">
@@ -32992,7 +32992,7 @@
       </c>
       <c r="BI117" t="inlineStr">
         <is>
-          <t>Yankee Stadium</t>
+          <t>Fenway Park</t>
         </is>
       </c>
       <c r="BJ117" t="inlineStr"/>
@@ -33003,47 +33003,47 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>671976</t>
+          <t>681546</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Tristan Peters</t>
+          <t>James Outman</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2026-07-01T16:35:00Z</t>
+          <t>2026-07-01T17:35:00Z</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Game Over</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>Dean Kremer</t>
+          <t>Will Warren</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>665152</t>
+          <t>701542</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
@@ -33052,7 +33052,7 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>47.6</v>
+        <v>47.7</v>
       </c>
       <c r="M118" t="inlineStr">
         <is>
@@ -33070,22 +33070,22 @@
         </is>
       </c>
       <c r="P118" t="n">
-        <v>9.699999999999999</v>
+        <v>26.4</v>
       </c>
       <c r="Q118" t="n">
-        <v>63.1</v>
+        <v>42.9</v>
       </c>
       <c r="R118" t="n">
-        <v>73.59999999999999</v>
+        <v>78.7</v>
       </c>
       <c r="S118" t="n">
-        <v>64.3</v>
+        <v>52.4</v>
       </c>
       <c r="T118" t="n">
         <v>80</v>
       </c>
       <c r="U118" t="n">
-        <v>40.7</v>
+        <v>47.2</v>
       </c>
       <c r="V118" t="inlineStr">
         <is>
@@ -33099,7 +33099,7 @@
       </c>
       <c r="X118" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y118" t="inlineStr">
@@ -33137,127 +33137,127 @@
       </c>
       <c r="AH118" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI118" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK118" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/26, 1 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL118" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 13.8% barrel, 9.4 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.3% barrel, 12.9 HR allowed</t>
         </is>
       </c>
       <c r="AM118" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN118" t="inlineStr">
         <is>
-          <t>3.15</t>
+          <t>9.13</t>
         </is>
       </c>
       <c r="AO118" t="inlineStr">
         <is>
-          <t>32.58</t>
+          <t>33.38</t>
         </is>
       </c>
       <c r="AP118" t="inlineStr">
         <is>
-          <t>86.66</t>
+          <t>87.44</t>
         </is>
       </c>
       <c r="AQ118" t="inlineStr">
         <is>
-          <t>97.7683</t>
+          <t>98.2712</t>
         </is>
       </c>
       <c r="AR118" t="inlineStr">
         <is>
-          <t>0.3124</t>
+          <t>0.2943</t>
         </is>
       </c>
       <c r="AS118" t="inlineStr">
         <is>
-          <t>0.0896</t>
+          <t>0.137</t>
         </is>
       </c>
       <c r="AT118" t="inlineStr">
         <is>
-          <t>0.2565</t>
+          <t>0.2405</t>
         </is>
       </c>
       <c r="AU118" t="inlineStr">
         <is>
-          <t>69.28</t>
+          <t>72.11</t>
         </is>
       </c>
       <c r="AV118" t="inlineStr">
         <is>
-          <t>4.83</t>
+          <t>19.27</t>
         </is>
       </c>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>41.42</t>
+          <t>58.4</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>16.94</t>
+          <t>28.97</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>3.9</t>
         </is>
       </c>
       <c r="AZ118" t="inlineStr">
         <is>
-          <t>0.1064</t>
+          <t>0.1639</t>
         </is>
       </c>
       <c r="BA118" t="inlineStr">
         <is>
-          <t>13.81</t>
+          <t>8.31</t>
         </is>
       </c>
       <c r="BB118" t="inlineStr">
         <is>
-          <t>35.94</t>
+          <t>40.33</t>
         </is>
       </c>
       <c r="BC118" t="inlineStr">
         <is>
-          <t>87.75</t>
+          <t>90.16</t>
         </is>
       </c>
       <c r="BD118" t="inlineStr">
         <is>
-          <t>0.4711</t>
+          <t>0.4064</t>
         </is>
       </c>
       <c r="BE118" t="inlineStr">
         <is>
-          <t>0.2415</t>
+          <t>0.1568</t>
         </is>
       </c>
       <c r="BF118" t="inlineStr">
         <is>
-          <t>39.32</t>
+          <t>24.94</t>
         </is>
       </c>
       <c r="BG118" t="inlineStr">
@@ -33267,12 +33267,12 @@
       </c>
       <c r="BH118" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>95</t>
         </is>
       </c>
       <c r="BI118" t="inlineStr">
         <is>
-          <t>Oriole Park at Camden Yards</t>
+          <t>Yankee Stadium</t>
         </is>
       </c>
       <c r="BJ118" t="inlineStr"/>
@@ -33283,47 +33283,47 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>660710</t>
+          <t>671976</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Rodolfo Durán</t>
+          <t>Tristan Peters</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>CHC</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>2026-07-01T18:20:00Z</t>
+          <t>2026-07-01T16:35:00Z</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Game Over</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>Colin Rea</t>
+          <t>Dean Kremer</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>607067</t>
+          <t>665152</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
@@ -33346,26 +33346,26 @@
       </c>
       <c r="O119" t="inlineStr">
         <is>
-          <t>Strong Barrel, Good Environment</t>
+          <t>Good Environment, Platoon Edge</t>
         </is>
       </c>
       <c r="P119" t="n">
-        <v>32.3</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="Q119" t="n">
-        <v>55.5</v>
+        <v>63.1</v>
       </c>
       <c r="R119" t="n">
-        <v>78.8</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="S119" t="n">
-        <v>52.4</v>
+        <v>64.3</v>
       </c>
       <c r="T119" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U119" t="n">
-        <v>0</v>
+        <v>40.7</v>
       </c>
       <c r="V119" t="inlineStr">
         <is>
@@ -33379,7 +33379,7 @@
       </c>
       <c r="X119" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y119" t="inlineStr">
@@ -33400,7 +33400,7 @@
       <c r="AB119" t="inlineStr"/>
       <c r="AC119" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD119" t="inlineStr"/>
@@ -33417,142 +33417,142 @@
       </c>
       <c r="AH119" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI119" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK119" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/18, 0 HR</t>
+          <t>Last 7 games: 7/26, 1 HR</t>
         </is>
       </c>
       <c r="AL119" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 10.9% barrel, 14.4 HR allowed</t>
+          <t>platoon edge; pitcher baseline 13.8% barrel, 9.4 HR allowed</t>
         </is>
       </c>
       <c r="AM119" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN119" t="inlineStr">
         <is>
-          <t>10.6</t>
+          <t>3.15</t>
         </is>
       </c>
       <c r="AO119" t="inlineStr">
         <is>
-          <t>29.8</t>
+          <t>32.58</t>
         </is>
       </c>
       <c r="AP119" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>86.66</t>
         </is>
       </c>
       <c r="AQ119" t="inlineStr">
         <is>
-          <t>97.8572</t>
+          <t>97.7683</t>
         </is>
       </c>
       <c r="AR119" t="inlineStr">
         <is>
-          <t>0.356</t>
+          <t>0.3124</t>
         </is>
       </c>
       <c r="AS119" t="inlineStr">
         <is>
-          <t>0.171</t>
+          <t>0.0896</t>
         </is>
       </c>
       <c r="AT119" t="inlineStr">
         <is>
-          <t>0.281</t>
+          <t>0.2565</t>
         </is>
       </c>
       <c r="AU119" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>69.28</t>
         </is>
       </c>
       <c r="AV119" t="inlineStr">
         <is>
-          <t>35.2</t>
+          <t>4.83</t>
         </is>
       </c>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>42.6</t>
+          <t>41.42</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>31.9</t>
+          <t>16.94</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="AZ119" t="inlineStr">
         <is>
-          <t>0.203</t>
+          <t>0.1064</t>
         </is>
       </c>
       <c r="BA119" t="inlineStr">
         <is>
-          <t>10.86</t>
+          <t>13.81</t>
         </is>
       </c>
       <c r="BB119" t="inlineStr">
         <is>
-          <t>41.21</t>
+          <t>35.94</t>
         </is>
       </c>
       <c r="BC119" t="inlineStr">
         <is>
-          <t>89.87</t>
+          <t>87.75</t>
         </is>
       </c>
       <c r="BD119" t="inlineStr">
         <is>
-          <t>0.4639</t>
+          <t>0.4711</t>
         </is>
       </c>
       <c r="BE119" t="inlineStr">
         <is>
-          <t>0.1959</t>
+          <t>0.2415</t>
         </is>
       </c>
       <c r="BF119" t="inlineStr">
         <is>
-          <t>26.12</t>
+          <t>39.32</t>
         </is>
       </c>
       <c r="BG119" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>Out To LF</t>
         </is>
       </c>
       <c r="BH119" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>91</t>
         </is>
       </c>
       <c r="BI119" t="inlineStr">
         <is>
-          <t>Wrigley Field</t>
+          <t>Oriole Park at Camden Yards</t>
         </is>
       </c>
       <c r="BJ119" t="inlineStr"/>
@@ -33563,52 +33563,52 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>677870</t>
+          <t>660710</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Leo Jimenez</t>
+          <t>Rodolfo Durán</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>CHC</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>2026-07-02T00:40:00Z</t>
+          <t>2026-07-01T18:20:00Z</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>Kyle Freeland</t>
+          <t>Colin Rea</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>607536</t>
+          <t>607067</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L120" t="n">
@@ -33626,65 +33626,61 @@
       </c>
       <c r="O120" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Strong Barrel, Good Environment</t>
         </is>
       </c>
       <c r="P120" t="n">
-        <v>29.1</v>
+        <v>32.3</v>
       </c>
       <c r="Q120" t="n">
-        <v>62.5</v>
+        <v>55.5</v>
       </c>
       <c r="R120" t="n">
-        <v>38.7</v>
+        <v>78.8</v>
       </c>
       <c r="S120" t="n">
-        <v>59.8</v>
+        <v>52.4</v>
       </c>
       <c r="T120" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U120" t="n">
-        <v>34.9</v>
+        <v>0</v>
       </c>
       <c r="V120" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W120" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X120" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y120" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z120" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W120" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X120" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y120" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z120" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA120" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB120" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB120" t="inlineStr"/>
       <c r="AC120" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD120" t="inlineStr"/>
@@ -33701,12 +33697,12 @@
       </c>
       <c r="AH120" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI120" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AJ120" t="inlineStr">
@@ -33716,12 +33712,12 @@
       </c>
       <c r="AK120" t="inlineStr">
         <is>
-          <t>Contact streak: 6/17 over last 7 games</t>
+          <t>Last 7 games: 2/18, 0 HR</t>
         </is>
       </c>
       <c r="AL120" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 10.7% barrel, 17.8 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 10.9% barrel, 14.4 HR allowed</t>
         </is>
       </c>
       <c r="AM120" t="inlineStr">
@@ -33731,104 +33727,112 @@
       </c>
       <c r="AN120" t="inlineStr">
         <is>
-          <t>6.02</t>
+          <t>10.6</t>
         </is>
       </c>
       <c r="AO120" t="inlineStr">
         <is>
-          <t>45.17</t>
+          <t>29.8</t>
         </is>
       </c>
       <c r="AP120" t="inlineStr">
         <is>
-          <t>91.58</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="AQ120" t="inlineStr">
         <is>
-          <t>100.7363</t>
+          <t>97.8572</t>
         </is>
       </c>
       <c r="AR120" t="inlineStr">
         <is>
-          <t>0.328</t>
+          <t>0.356</t>
         </is>
       </c>
       <c r="AS120" t="inlineStr">
         <is>
-          <t>0.1031</t>
+          <t>0.171</t>
         </is>
       </c>
       <c r="AT120" t="inlineStr">
         <is>
-          <t>0.2939</t>
+          <t>0.281</t>
         </is>
       </c>
       <c r="AU120" t="inlineStr">
         <is>
-          <t>71.51</t>
+          <t>73.3</t>
         </is>
       </c>
       <c r="AV120" t="inlineStr">
         <is>
-          <t>12.38</t>
+          <t>35.2</t>
         </is>
       </c>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>29.26</t>
+          <t>42.6</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>24.59</t>
+          <t>31.9</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AZ120" t="inlineStr">
         <is>
-          <t>0.0631</t>
+          <t>0.203</t>
         </is>
       </c>
       <c r="BA120" t="inlineStr">
         <is>
-          <t>10.66</t>
+          <t>10.86</t>
         </is>
       </c>
       <c r="BB120" t="inlineStr">
         <is>
-          <t>45.13</t>
+          <t>41.21</t>
         </is>
       </c>
       <c r="BC120" t="inlineStr">
         <is>
-          <t>90.89</t>
+          <t>89.87</t>
         </is>
       </c>
       <c r="BD120" t="inlineStr">
         <is>
-          <t>0.4968</t>
+          <t>0.4639</t>
         </is>
       </c>
       <c r="BE120" t="inlineStr">
         <is>
-          <t>0.2029</t>
+          <t>0.1959</t>
         </is>
       </c>
       <c r="BF120" t="inlineStr">
         <is>
-          <t>29.64</t>
-        </is>
-      </c>
-      <c r="BG120" t="inlineStr"/>
-      <c r="BH120" t="inlineStr"/>
+          <t>26.12</t>
+        </is>
+      </c>
+      <c r="BG120" t="inlineStr">
+        <is>
+          <t>Out To CF</t>
+        </is>
+      </c>
+      <c r="BH120" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
       <c r="BI120" t="inlineStr">
         <is>
-          <t>Coors Field</t>
+          <t>Wrigley Field</t>
         </is>
       </c>
       <c r="BJ120" t="inlineStr"/>
@@ -33839,27 +33843,27 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>671218</t>
+          <t>677870</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Heliot Ramos</t>
+          <t>Leo Jimenez</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>2026-07-02T01:40:00Z</t>
+          <t>2026-07-02T00:40:00Z</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
@@ -33869,22 +33873,22 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>Zac Gallen</t>
+          <t>Kyle Freeland</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>668678</t>
+          <t>607536</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L121" t="n">
@@ -33902,26 +33906,26 @@
       </c>
       <c r="O121" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P121" t="n">
-        <v>50.5</v>
+        <v>29.1</v>
       </c>
       <c r="Q121" t="n">
-        <v>59.3</v>
+        <v>62.5</v>
       </c>
       <c r="R121" t="n">
-        <v>28.2</v>
+        <v>38.7</v>
       </c>
       <c r="S121" t="n">
-        <v>47.9</v>
+        <v>59.8</v>
       </c>
       <c r="T121" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U121" t="n">
-        <v>25.3</v>
+        <v>34.9</v>
       </c>
       <c r="V121" t="inlineStr">
         <is>
@@ -33935,7 +33939,7 @@
       </c>
       <c r="X121" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y121" t="inlineStr">
@@ -33977,27 +33981,27 @@
       </c>
       <c r="AH121" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI121" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/24, 1 HR</t>
+          <t>Contact streak: 6/17 over last 7 games</t>
         </is>
       </c>
       <c r="AL121" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 10.1% barrel, 19.8 HR allowed</t>
+          <t>platoon edge; pitcher baseline 10.7% barrel, 17.8 HR allowed</t>
         </is>
       </c>
       <c r="AM121" t="inlineStr">
@@ -34007,104 +34011,104 @@
       </c>
       <c r="AN121" t="inlineStr">
         <is>
-          <t>12.72</t>
+          <t>6.02</t>
         </is>
       </c>
       <c r="AO121" t="inlineStr">
         <is>
-          <t>48.66</t>
+          <t>45.17</t>
         </is>
       </c>
       <c r="AP121" t="inlineStr">
         <is>
-          <t>91.8</t>
+          <t>91.58</t>
         </is>
       </c>
       <c r="AQ121" t="inlineStr">
         <is>
-          <t>103.0202</t>
+          <t>100.7363</t>
         </is>
       </c>
       <c r="AR121" t="inlineStr">
         <is>
-          <t>0.4471</t>
+          <t>0.328</t>
         </is>
       </c>
       <c r="AS121" t="inlineStr">
         <is>
-          <t>0.1834</t>
+          <t>0.1031</t>
         </is>
       </c>
       <c r="AT121" t="inlineStr">
         <is>
-          <t>0.3284</t>
+          <t>0.2939</t>
         </is>
       </c>
       <c r="AU121" t="inlineStr">
         <is>
-          <t>72.6</t>
+          <t>71.51</t>
         </is>
       </c>
       <c r="AV121" t="inlineStr">
         <is>
-          <t>28.74</t>
+          <t>12.38</t>
         </is>
       </c>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>35.62</t>
+          <t>29.26</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>23.51</t>
+          <t>24.59</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr">
         <is>
-          <t>9.8</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="AZ121" t="inlineStr">
         <is>
-          <t>0.1594</t>
+          <t>0.0631</t>
         </is>
       </c>
       <c r="BA121" t="inlineStr">
         <is>
-          <t>10.05</t>
+          <t>10.66</t>
         </is>
       </c>
       <c r="BB121" t="inlineStr">
         <is>
-          <t>43.63</t>
+          <t>45.13</t>
         </is>
       </c>
       <c r="BC121" t="inlineStr">
         <is>
-          <t>90.38</t>
+          <t>90.89</t>
         </is>
       </c>
       <c r="BD121" t="inlineStr">
         <is>
-          <t>0.4907</t>
+          <t>0.4968</t>
         </is>
       </c>
       <c r="BE121" t="inlineStr">
         <is>
-          <t>0.2018</t>
+          <t>0.2029</t>
         </is>
       </c>
       <c r="BF121" t="inlineStr">
         <is>
-          <t>28.69</t>
+          <t>29.64</t>
         </is>
       </c>
       <c r="BG121" t="inlineStr"/>
       <c r="BH121" t="inlineStr"/>
       <c r="BI121" t="inlineStr">
         <is>
-          <t>Chase Field</t>
+          <t>Coors Field</t>
         </is>
       </c>
       <c r="BJ121" t="inlineStr"/>
@@ -34115,47 +34119,47 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>630105</t>
+          <t>671218</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Jake Cronenworth</t>
+          <t>Heliot Ramos</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>CHC</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>2026-07-01T18:20:00Z</t>
+          <t>2026-07-02T01:40:00Z</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>Colin Rea</t>
+          <t>Zac Gallen</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>607067</t>
+          <t>668678</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
@@ -34164,7 +34168,7 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>47.4</v>
+        <v>47.6</v>
       </c>
       <c r="M122" t="inlineStr">
         <is>
@@ -34178,58 +34182,62 @@
       </c>
       <c r="O122" t="inlineStr">
         <is>
-          <t>Good Environment, Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel</t>
         </is>
       </c>
       <c r="P122" t="n">
-        <v>17.9</v>
+        <v>50.5</v>
       </c>
       <c r="Q122" t="n">
-        <v>55.5</v>
+        <v>59.3</v>
       </c>
       <c r="R122" t="n">
-        <v>78.8</v>
+        <v>28.2</v>
       </c>
       <c r="S122" t="n">
-        <v>64.3</v>
+        <v>47.9</v>
       </c>
       <c r="T122" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U122" t="n">
-        <v>2</v>
+        <v>25.3</v>
       </c>
       <c r="V122" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W122" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X122" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y122" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W122" t="inlineStr">
+      <c r="Z122" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X122" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y122" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z122" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA122" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB122" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB122" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC122" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -34249,27 +34257,27 @@
       </c>
       <c r="AH122" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI122" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ122" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK122" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/15, 0 HR</t>
+          <t>Last 7 games: 4/24, 1 HR</t>
         </is>
       </c>
       <c r="AL122" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 10.9% barrel, 14.4 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 10.1% barrel, 19.8 HR allowed</t>
         </is>
       </c>
       <c r="AM122" t="inlineStr">
@@ -34279,112 +34287,104 @@
       </c>
       <c r="AN122" t="inlineStr">
         <is>
-          <t>5.43</t>
+          <t>12.72</t>
         </is>
       </c>
       <c r="AO122" t="inlineStr">
         <is>
-          <t>32.98</t>
+          <t>48.66</t>
         </is>
       </c>
       <c r="AP122" t="inlineStr">
         <is>
-          <t>87.45</t>
+          <t>91.8</t>
         </is>
       </c>
       <c r="AQ122" t="inlineStr">
         <is>
-          <t>97.9991</t>
+          <t>103.0202</t>
         </is>
       </c>
       <c r="AR122" t="inlineStr">
         <is>
-          <t>0.3271</t>
+          <t>0.4471</t>
         </is>
       </c>
       <c r="AS122" t="inlineStr">
         <is>
-          <t>0.1105</t>
+          <t>0.1834</t>
         </is>
       </c>
       <c r="AT122" t="inlineStr">
         <is>
-          <t>0.3029</t>
+          <t>0.3284</t>
         </is>
       </c>
       <c r="AU122" t="inlineStr">
         <is>
-          <t>71.81</t>
+          <t>72.6</t>
         </is>
       </c>
       <c r="AV122" t="inlineStr">
         <is>
-          <t>19.98</t>
+          <t>28.74</t>
         </is>
       </c>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>33.71</t>
+          <t>35.62</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>21.39</t>
+          <t>23.51</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>9.8</t>
         </is>
       </c>
       <c r="AZ122" t="inlineStr">
         <is>
-          <t>0.0736</t>
+          <t>0.1594</t>
         </is>
       </c>
       <c r="BA122" t="inlineStr">
         <is>
-          <t>10.86</t>
+          <t>10.05</t>
         </is>
       </c>
       <c r="BB122" t="inlineStr">
         <is>
-          <t>41.21</t>
+          <t>43.63</t>
         </is>
       </c>
       <c r="BC122" t="inlineStr">
         <is>
-          <t>89.87</t>
+          <t>90.38</t>
         </is>
       </c>
       <c r="BD122" t="inlineStr">
         <is>
-          <t>0.4639</t>
+          <t>0.4907</t>
         </is>
       </c>
       <c r="BE122" t="inlineStr">
         <is>
-          <t>0.1959</t>
+          <t>0.2018</t>
         </is>
       </c>
       <c r="BF122" t="inlineStr">
         <is>
-          <t>26.12</t>
-        </is>
-      </c>
-      <c r="BG122" t="inlineStr">
-        <is>
-          <t>Out To CF</t>
-        </is>
-      </c>
-      <c r="BH122" t="inlineStr">
-        <is>
-          <t>92</t>
-        </is>
-      </c>
+          <t>28.69</t>
+        </is>
+      </c>
+      <c r="BG122" t="inlineStr"/>
+      <c r="BH122" t="inlineStr"/>
       <c r="BI122" t="inlineStr">
         <is>
-          <t>Wrigley Field</t>
+          <t>Chase Field</t>
         </is>
       </c>
       <c r="BJ122" t="inlineStr"/>
@@ -50290,7 +50290,7 @@
       </c>
       <c r="AI180" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ180" t="inlineStr">
@@ -50300,7 +50300,7 @@
       </c>
       <c r="AK180" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/19, 0 HR</t>
+          <t>Last 7 games: 2/20, 0 HR</t>
         </is>
       </c>
       <c r="AL180" t="inlineStr">
@@ -57647,32 +57647,32 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>657136</t>
+          <t>606992</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Connor Wong</t>
+          <t>Eric Haase</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>WSH</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>2026-07-01T17:35:00Z</t>
+          <t>2026-07-02T01:40:00Z</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
@@ -57682,12 +57682,12 @@
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>Brad Lord</t>
+          <t>Zac Gallen</t>
         </is>
       </c>
       <c r="J207" t="inlineStr">
         <is>
-          <t>695418</t>
+          <t>668678</t>
         </is>
       </c>
       <c r="K207" t="inlineStr">
@@ -57710,58 +57710,62 @@
       </c>
       <c r="O207" t="inlineStr">
         <is>
-          <t>No major boost</t>
+          <t>Projected Lineup, Strong Barrel</t>
         </is>
       </c>
       <c r="P207" t="n">
-        <v>20.1</v>
+        <v>30.5</v>
       </c>
       <c r="Q207" t="n">
-        <v>32.7</v>
+        <v>59.3</v>
       </c>
       <c r="R207" t="n">
-        <v>69.2</v>
+        <v>28.2</v>
       </c>
       <c r="S207" t="n">
-        <v>44.8</v>
+        <v>40.2</v>
       </c>
       <c r="T207" t="n">
         <v>50</v>
       </c>
       <c r="U207" t="n">
-        <v>60.3</v>
+        <v>0</v>
       </c>
       <c r="V207" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W207" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X207" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y207" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W207" t="inlineStr">
+      <c r="Z207" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X207" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y207" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z207" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA207" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB207" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB207" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC207" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -57781,27 +57785,27 @@
       </c>
       <c r="AH207" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AI207" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AJ207" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK207" t="inlineStr">
         <is>
-          <t>Contact streak: 6/15 over last 7 games</t>
+          <t>Last 7 games: 1/19, 0 HR</t>
         </is>
       </c>
       <c r="AL207" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.3% barrel, 9.3 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 10.1% barrel, 19.8 HR allowed</t>
         </is>
       </c>
       <c r="AM207" t="inlineStr">
@@ -57811,112 +57815,104 @@
       </c>
       <c r="AN207" t="inlineStr">
         <is>
-          <t>4.78</t>
+          <t>13.92</t>
         </is>
       </c>
       <c r="AO207" t="inlineStr">
         <is>
-          <t>38.07</t>
+          <t>26.98</t>
         </is>
       </c>
       <c r="AP207" t="inlineStr">
         <is>
-          <t>86.97</t>
+          <t>84.89</t>
         </is>
       </c>
       <c r="AQ207" t="inlineStr">
         <is>
-          <t>99.6376</t>
+          <t>96.5647</t>
         </is>
       </c>
       <c r="AR207" t="inlineStr">
         <is>
-          <t>0.3545</t>
+          <t>0.3694</t>
         </is>
       </c>
       <c r="AS207" t="inlineStr">
         <is>
-          <t>0.1111</t>
+          <t>0.1718</t>
         </is>
       </c>
       <c r="AT207" t="inlineStr">
         <is>
-          <t>0.3101</t>
+          <t>0.2744</t>
         </is>
       </c>
       <c r="AU207" t="inlineStr">
         <is>
-          <t>72.37</t>
+          <t>71.44</t>
         </is>
       </c>
       <c r="AV207" t="inlineStr">
         <is>
-          <t>22.78</t>
+          <t>13.95</t>
         </is>
       </c>
       <c r="AW207" t="inlineStr">
         <is>
-          <t>39.19</t>
+          <t>34.56</t>
         </is>
       </c>
       <c r="AX207" t="inlineStr">
         <is>
-          <t>23.56</t>
+          <t>23.04</t>
         </is>
       </c>
       <c r="AY207" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>3.4</t>
         </is>
       </c>
       <c r="AZ207" t="inlineStr">
         <is>
-          <t>0.097</t>
+          <t>0.1973</t>
         </is>
       </c>
       <c r="BA207" t="inlineStr">
         <is>
-          <t>6.33</t>
+          <t>10.05</t>
         </is>
       </c>
       <c r="BB207" t="inlineStr">
         <is>
-          <t>42.29</t>
+          <t>43.63</t>
         </is>
       </c>
       <c r="BC207" t="inlineStr">
         <is>
-          <t>88.01</t>
+          <t>90.38</t>
         </is>
       </c>
       <c r="BD207" t="inlineStr">
         <is>
-          <t>0.4027</t>
+          <t>0.4907</t>
         </is>
       </c>
       <c r="BE207" t="inlineStr">
         <is>
-          <t>0.1502</t>
+          <t>0.2018</t>
         </is>
       </c>
       <c r="BF207" t="inlineStr">
         <is>
-          <t>19.69</t>
-        </is>
-      </c>
-      <c r="BG207" t="inlineStr">
-        <is>
-          <t>Out To RF</t>
-        </is>
-      </c>
-      <c r="BH207" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
+          <t>28.69</t>
+        </is>
+      </c>
+      <c r="BG207" t="inlineStr"/>
+      <c r="BH207" t="inlineStr"/>
       <c r="BI207" t="inlineStr">
         <is>
-          <t>Fenway Park</t>
+          <t>Chase Field</t>
         </is>
       </c>
       <c r="BJ207" t="inlineStr"/>
@@ -57927,27 +57923,27 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>606992</t>
+          <t>678662</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Eric Haase</t>
+          <t>Ezequiel Tovar</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>2026-07-02T01:40:00Z</t>
+          <t>2026-07-02T00:40:00Z</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
@@ -57957,17 +57953,17 @@
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t>Zac Gallen</t>
+          <t>Max Meyer</t>
         </is>
       </c>
       <c r="J208" t="inlineStr">
         <is>
-          <t>668678</t>
+          <t>676974</t>
         </is>
       </c>
       <c r="K208" t="inlineStr">
@@ -57976,40 +57972,40 @@
         </is>
       </c>
       <c r="L208" t="n">
+        <v>38.6</v>
+      </c>
+      <c r="M208" t="inlineStr">
+        <is>
+          <t>Longshot</t>
+        </is>
+      </c>
+      <c r="N208" t="inlineStr">
+        <is>
+          <t>Watch List</t>
+        </is>
+      </c>
+      <c r="O208" t="inlineStr">
+        <is>
+          <t>Projected Lineup</t>
+        </is>
+      </c>
+      <c r="P208" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="Q208" t="n">
+        <v>42.7</v>
+      </c>
+      <c r="R208" t="n">
         <v>38.7</v>
       </c>
-      <c r="M208" t="inlineStr">
-        <is>
-          <t>Longshot</t>
-        </is>
-      </c>
-      <c r="N208" t="inlineStr">
-        <is>
-          <t>Watch List</t>
-        </is>
-      </c>
-      <c r="O208" t="inlineStr">
-        <is>
-          <t>Projected Lineup, Strong Barrel</t>
-        </is>
-      </c>
-      <c r="P208" t="n">
-        <v>30.5</v>
-      </c>
-      <c r="Q208" t="n">
-        <v>59.3</v>
-      </c>
-      <c r="R208" t="n">
-        <v>28.2</v>
-      </c>
       <c r="S208" t="n">
-        <v>40.2</v>
+        <v>47.9</v>
       </c>
       <c r="T208" t="n">
         <v>50</v>
       </c>
       <c r="U208" t="n">
-        <v>0</v>
+        <v>25.3</v>
       </c>
       <c r="V208" t="inlineStr">
         <is>
@@ -58023,7 +58019,7 @@
       </c>
       <c r="X208" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y208" t="inlineStr">
@@ -58065,27 +58061,27 @@
       </c>
       <c r="AH208" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AI208" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="AJ208" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AI208" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="AJ208" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AK208" t="inlineStr">
         <is>
-          <t>Last 7 games: 1/19, 0 HR</t>
+          <t>Last 7 games: 4/24, 1 HR</t>
         </is>
       </c>
       <c r="AL208" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 10.1% barrel, 19.8 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.4% barrel, 9.2 HR allowed</t>
         </is>
       </c>
       <c r="AM208" t="inlineStr">
@@ -58095,104 +58091,104 @@
       </c>
       <c r="AN208" t="inlineStr">
         <is>
-          <t>13.92</t>
+          <t>7.69</t>
         </is>
       </c>
       <c r="AO208" t="inlineStr">
         <is>
-          <t>26.98</t>
+          <t>35.82</t>
         </is>
       </c>
       <c r="AP208" t="inlineStr">
         <is>
-          <t>84.89</t>
+          <t>88.21</t>
         </is>
       </c>
       <c r="AQ208" t="inlineStr">
         <is>
-          <t>96.5647</t>
+          <t>99.1247</t>
         </is>
       </c>
       <c r="AR208" t="inlineStr">
         <is>
-          <t>0.3694</t>
+          <t>0.3885</t>
         </is>
       </c>
       <c r="AS208" t="inlineStr">
         <is>
-          <t>0.1718</t>
+          <t>0.1562</t>
         </is>
       </c>
       <c r="AT208" t="inlineStr">
         <is>
-          <t>0.2744</t>
+          <t>0.2889</t>
         </is>
       </c>
       <c r="AU208" t="inlineStr">
         <is>
-          <t>71.44</t>
+          <t>71.81</t>
         </is>
       </c>
       <c r="AV208" t="inlineStr">
         <is>
-          <t>13.95</t>
+          <t>19.66</t>
         </is>
       </c>
       <c r="AW208" t="inlineStr">
         <is>
-          <t>34.56</t>
+          <t>39.08</t>
         </is>
       </c>
       <c r="AX208" t="inlineStr">
         <is>
-          <t>23.04</t>
+          <t>31.32</t>
         </is>
       </c>
       <c r="AY208" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t>6.9</t>
         </is>
       </c>
       <c r="AZ208" t="inlineStr">
         <is>
-          <t>0.1973</t>
+          <t>0.1295</t>
         </is>
       </c>
       <c r="BA208" t="inlineStr">
         <is>
-          <t>10.05</t>
+          <t>8.36</t>
         </is>
       </c>
       <c r="BB208" t="inlineStr">
         <is>
-          <t>43.63</t>
+          <t>42.88</t>
         </is>
       </c>
       <c r="BC208" t="inlineStr">
         <is>
-          <t>90.38</t>
+          <t>89.87</t>
         </is>
       </c>
       <c r="BD208" t="inlineStr">
         <is>
-          <t>0.4907</t>
+          <t>0.3914</t>
         </is>
       </c>
       <c r="BE208" t="inlineStr">
         <is>
-          <t>0.2018</t>
+          <t>0.1581</t>
         </is>
       </c>
       <c r="BF208" t="inlineStr">
         <is>
-          <t>28.69</t>
+          <t>26.35</t>
         </is>
       </c>
       <c r="BG208" t="inlineStr"/>
       <c r="BH208" t="inlineStr"/>
       <c r="BI208" t="inlineStr">
         <is>
-          <t>Chase Field</t>
+          <t>Coors Field</t>
         </is>
       </c>
       <c r="BJ208" t="inlineStr"/>
@@ -58203,47 +58199,47 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>678662</t>
+          <t>657136</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Ezequiel Tovar</t>
+          <t>Connor Wong</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>WSH</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>2026-07-02T00:40:00Z</t>
+          <t>2026-07-01T17:35:00Z</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>Max Meyer</t>
+          <t>Brad Lord</t>
         </is>
       </c>
       <c r="J209" t="inlineStr">
         <is>
-          <t>676974</t>
+          <t>695418</t>
         </is>
       </c>
       <c r="K209" t="inlineStr">
@@ -58252,7 +58248,7 @@
         </is>
       </c>
       <c r="L209" t="n">
-        <v>38.6</v>
+        <v>38.5</v>
       </c>
       <c r="M209" t="inlineStr">
         <is>
@@ -58266,62 +58262,58 @@
       </c>
       <c r="O209" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P209" t="n">
-        <v>30.6</v>
+        <v>20.1</v>
       </c>
       <c r="Q209" t="n">
-        <v>42.7</v>
+        <v>32.7</v>
       </c>
       <c r="R209" t="n">
-        <v>38.7</v>
+        <v>69.2</v>
       </c>
       <c r="S209" t="n">
-        <v>47.9</v>
+        <v>44.8</v>
       </c>
       <c r="T209" t="n">
         <v>50</v>
       </c>
       <c r="U209" t="n">
-        <v>25.3</v>
+        <v>56.6</v>
       </c>
       <c r="V209" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W209" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X209" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y209" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z209" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W209" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X209" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y209" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z209" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA209" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB209" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB209" t="inlineStr"/>
       <c r="AC209" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -58341,12 +58333,12 @@
       </c>
       <c r="AH209" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI209" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AJ209" t="inlineStr">
@@ -58356,12 +58348,12 @@
       </c>
       <c r="AK209" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/24, 1 HR</t>
+          <t>Contact streak: 6/16 over last 7 games</t>
         </is>
       </c>
       <c r="AL209" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.4% barrel, 9.2 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.3% barrel, 9.3 HR allowed</t>
         </is>
       </c>
       <c r="AM209" t="inlineStr">
@@ -58371,104 +58363,112 @@
       </c>
       <c r="AN209" t="inlineStr">
         <is>
-          <t>7.69</t>
+          <t>4.78</t>
         </is>
       </c>
       <c r="AO209" t="inlineStr">
         <is>
-          <t>35.82</t>
+          <t>38.07</t>
         </is>
       </c>
       <c r="AP209" t="inlineStr">
         <is>
-          <t>88.21</t>
+          <t>86.97</t>
         </is>
       </c>
       <c r="AQ209" t="inlineStr">
         <is>
-          <t>99.1247</t>
+          <t>99.6376</t>
         </is>
       </c>
       <c r="AR209" t="inlineStr">
         <is>
-          <t>0.3885</t>
+          <t>0.3545</t>
         </is>
       </c>
       <c r="AS209" t="inlineStr">
         <is>
-          <t>0.1562</t>
+          <t>0.1111</t>
         </is>
       </c>
       <c r="AT209" t="inlineStr">
         <is>
-          <t>0.2889</t>
+          <t>0.3101</t>
         </is>
       </c>
       <c r="AU209" t="inlineStr">
         <is>
-          <t>71.81</t>
+          <t>72.37</t>
         </is>
       </c>
       <c r="AV209" t="inlineStr">
         <is>
-          <t>19.66</t>
+          <t>22.78</t>
         </is>
       </c>
       <c r="AW209" t="inlineStr">
         <is>
-          <t>39.08</t>
+          <t>39.19</t>
         </is>
       </c>
       <c r="AX209" t="inlineStr">
         <is>
-          <t>31.32</t>
+          <t>23.56</t>
         </is>
       </c>
       <c r="AY209" t="inlineStr">
         <is>
-          <t>6.9</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="AZ209" t="inlineStr">
         <is>
-          <t>0.1295</t>
+          <t>0.097</t>
         </is>
       </c>
       <c r="BA209" t="inlineStr">
         <is>
-          <t>8.36</t>
+          <t>6.33</t>
         </is>
       </c>
       <c r="BB209" t="inlineStr">
         <is>
-          <t>42.88</t>
+          <t>42.29</t>
         </is>
       </c>
       <c r="BC209" t="inlineStr">
         <is>
-          <t>89.87</t>
+          <t>88.01</t>
         </is>
       </c>
       <c r="BD209" t="inlineStr">
         <is>
-          <t>0.3914</t>
+          <t>0.4027</t>
         </is>
       </c>
       <c r="BE209" t="inlineStr">
         <is>
-          <t>0.1581</t>
+          <t>0.1502</t>
         </is>
       </c>
       <c r="BF209" t="inlineStr">
         <is>
-          <t>26.35</t>
-        </is>
-      </c>
-      <c r="BG209" t="inlineStr"/>
-      <c r="BH209" t="inlineStr"/>
+          <t>19.69</t>
+        </is>
+      </c>
+      <c r="BG209" t="inlineStr">
+        <is>
+          <t>Out To RF</t>
+        </is>
+      </c>
+      <c r="BH209" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
       <c r="BI209" t="inlineStr">
         <is>
-          <t>Coors Field</t>
+          <t>Fenway Park</t>
         </is>
       </c>
       <c r="BJ209" t="inlineStr"/>
@@ -62099,47 +62099,47 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>669701</t>
+          <t>686555</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Josh Smith</t>
+          <t>Isaac Collins</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>2026-07-01T17:10:00Z</t>
+          <t>2026-07-01T23:40:00Z</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
         <is>
-          <t>Joey Cantillo</t>
+          <t>Shane McClanahan</t>
         </is>
       </c>
       <c r="J223" t="inlineStr">
         <is>
-          <t>676282</t>
+          <t>663556</t>
         </is>
       </c>
       <c r="K223" t="inlineStr">
@@ -62162,39 +62162,47 @@
       </c>
       <c r="O223" t="inlineStr">
         <is>
-          <t>No major boost</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P223" t="n">
-        <v>16.5</v>
+        <v>23.7</v>
       </c>
       <c r="Q223" t="n">
-        <v>38.6</v>
+        <v>45.7</v>
       </c>
       <c r="R223" t="n">
-        <v>47.6</v>
+        <v>23.2</v>
       </c>
       <c r="S223" t="n">
-        <v>52.4</v>
+        <v>40.2</v>
       </c>
       <c r="T223" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="U223" t="n">
-        <v>37.3</v>
+        <v>19.5</v>
       </c>
       <c r="V223" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W223" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X223" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y223" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W223" t="inlineStr"/>
-      <c r="X223" t="inlineStr"/>
-      <c r="Y223" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="Z223" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -62202,17 +62210,17 @@
       </c>
       <c r="AA223" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
         </is>
       </c>
       <c r="AB223" t="inlineStr">
         <is>
-          <t>not found on RotoWire</t>
+          <t>lineup projected / unconfirmed</t>
         </is>
       </c>
       <c r="AC223" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD223" t="inlineStr"/>
@@ -62229,12 +62237,12 @@
       </c>
       <c r="AH223" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI223" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ223" t="inlineStr">
@@ -62244,127 +62252,119 @@
       </c>
       <c r="AK223" t="inlineStr">
         <is>
-          <t>Contact streak: 7/19 over last 7 games</t>
+          <t>Last 7 games: 5/20, 0 HR</t>
         </is>
       </c>
       <c r="AL223" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.4% barrel, 11.4 HR allowed</t>
+          <t>switch hitter; pitcher baseline 9.6% barrel, 6.0 HR allowed</t>
         </is>
       </c>
       <c r="AM223" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN223" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>5.39</t>
         </is>
       </c>
       <c r="AO223" t="inlineStr">
         <is>
-          <t>32.08</t>
+          <t>40.51</t>
         </is>
       </c>
       <c r="AP223" t="inlineStr">
         <is>
-          <t>87.13</t>
+          <t>88.73</t>
         </is>
       </c>
       <c r="AQ223" t="inlineStr">
         <is>
-          <t>97.8652</t>
+          <t>100.2407</t>
         </is>
       </c>
       <c r="AR223" t="inlineStr">
         <is>
-          <t>0.3275</t>
+          <t>0.3352</t>
         </is>
       </c>
       <c r="AS223" t="inlineStr">
         <is>
-          <t>0.1043</t>
+          <t>0.0962</t>
         </is>
       </c>
       <c r="AT223" t="inlineStr">
         <is>
-          <t>0.2918</t>
+          <t>0.3136</t>
         </is>
       </c>
       <c r="AU223" t="inlineStr">
         <is>
-          <t>69.24</t>
+          <t>73.4</t>
         </is>
       </c>
       <c r="AV223" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>31.6</t>
         </is>
       </c>
       <c r="AW223" t="inlineStr">
         <is>
-          <t>34.55</t>
+          <t>42.78</t>
         </is>
       </c>
       <c r="AX223" t="inlineStr">
         <is>
-          <t>30.89</t>
+          <t>26.02</t>
         </is>
       </c>
       <c r="AY223" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>4.8</t>
         </is>
       </c>
       <c r="AZ223" t="inlineStr">
         <is>
-          <t>0.0555</t>
+          <t>0.1123</t>
         </is>
       </c>
       <c r="BA223" t="inlineStr">
         <is>
-          <t>8.39</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="BB223" t="inlineStr">
         <is>
-          <t>38.16</t>
+          <t>41.8</t>
         </is>
       </c>
       <c r="BC223" t="inlineStr">
         <is>
-          <t>88.1</t>
+          <t>90.1</t>
         </is>
       </c>
       <c r="BD223" t="inlineStr">
         <is>
-          <t>0.3854</t>
+          <t>0.413</t>
         </is>
       </c>
       <c r="BE223" t="inlineStr">
         <is>
-          <t>0.1522</t>
+          <t>0.166</t>
         </is>
       </c>
       <c r="BF223" t="inlineStr">
         <is>
-          <t>30.1</t>
-        </is>
-      </c>
-      <c r="BG223" t="inlineStr">
-        <is>
-          <t>In From LF</t>
-        </is>
-      </c>
-      <c r="BH223" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
+          <t>26.4</t>
+        </is>
+      </c>
+      <c r="BG223" t="inlineStr"/>
+      <c r="BH223" t="inlineStr"/>
       <c r="BI223" t="inlineStr">
         <is>
-          <t>Progressive Field</t>
+          <t>Kauffman Stadium</t>
         </is>
       </c>
       <c r="BJ223" t="inlineStr"/>
@@ -62375,47 +62375,47 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>686555</t>
+          <t>669701</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Isaac Collins</t>
+          <t>Josh Smith</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>2026-07-01T23:40:00Z</t>
+          <t>2026-07-01T17:10:00Z</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t>Shane McClanahan</t>
+          <t>Joey Cantillo</t>
         </is>
       </c>
       <c r="J224" t="inlineStr">
         <is>
-          <t>663556</t>
+          <t>676282</t>
         </is>
       </c>
       <c r="K224" t="inlineStr">
@@ -62424,7 +62424,7 @@
         </is>
       </c>
       <c r="L224" t="n">
-        <v>35.6</v>
+        <v>35.4</v>
       </c>
       <c r="M224" t="inlineStr">
         <is>
@@ -62438,65 +62438,57 @@
       </c>
       <c r="O224" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P224" t="n">
-        <v>23.7</v>
+        <v>16.5</v>
       </c>
       <c r="Q224" t="n">
-        <v>45.7</v>
+        <v>38.6</v>
       </c>
       <c r="R224" t="n">
-        <v>23.2</v>
+        <v>47.6</v>
       </c>
       <c r="S224" t="n">
-        <v>40.2</v>
+        <v>52.4</v>
       </c>
       <c r="T224" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U224" t="n">
-        <v>19.5</v>
+        <v>34.5</v>
       </c>
       <c r="V224" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W224" t="inlineStr"/>
+      <c r="X224" t="inlineStr"/>
+      <c r="Y224" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W224" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X224" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y224" t="inlineStr">
+      <c r="Z224" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z224" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA224" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AB224" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>not found on RotoWire</t>
         </is>
       </c>
       <c r="AC224" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD224" t="inlineStr"/>
@@ -62513,7 +62505,7 @@
       </c>
       <c r="AH224" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI224" t="inlineStr">
@@ -62528,119 +62520,127 @@
       </c>
       <c r="AK224" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/20, 0 HR</t>
+          <t>Contact streak: 7/20 over last 7 games</t>
         </is>
       </c>
       <c r="AL224" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 9.6% barrel, 6.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.4% barrel, 11.4 HR allowed</t>
         </is>
       </c>
       <c r="AM224" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN224" t="inlineStr">
         <is>
-          <t>5.39</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AO224" t="inlineStr">
         <is>
-          <t>40.51</t>
+          <t>32.08</t>
         </is>
       </c>
       <c r="AP224" t="inlineStr">
         <is>
-          <t>88.73</t>
+          <t>87.13</t>
         </is>
       </c>
       <c r="AQ224" t="inlineStr">
         <is>
-          <t>100.2407</t>
+          <t>97.8652</t>
         </is>
       </c>
       <c r="AR224" t="inlineStr">
         <is>
-          <t>0.3352</t>
+          <t>0.3275</t>
         </is>
       </c>
       <c r="AS224" t="inlineStr">
         <is>
-          <t>0.0962</t>
+          <t>0.1043</t>
         </is>
       </c>
       <c r="AT224" t="inlineStr">
         <is>
-          <t>0.3136</t>
+          <t>0.2918</t>
         </is>
       </c>
       <c r="AU224" t="inlineStr">
         <is>
-          <t>73.4</t>
+          <t>69.24</t>
         </is>
       </c>
       <c r="AV224" t="inlineStr">
         <is>
-          <t>31.6</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="AW224" t="inlineStr">
         <is>
-          <t>42.78</t>
+          <t>34.55</t>
         </is>
       </c>
       <c r="AX224" t="inlineStr">
         <is>
-          <t>26.02</t>
+          <t>30.89</t>
         </is>
       </c>
       <c r="AY224" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AZ224" t="inlineStr">
         <is>
-          <t>0.1123</t>
+          <t>0.0555</t>
         </is>
       </c>
       <c r="BA224" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>8.39</t>
         </is>
       </c>
       <c r="BB224" t="inlineStr">
         <is>
-          <t>41.8</t>
+          <t>38.16</t>
         </is>
       </c>
       <c r="BC224" t="inlineStr">
         <is>
-          <t>90.1</t>
+          <t>88.1</t>
         </is>
       </c>
       <c r="BD224" t="inlineStr">
         <is>
-          <t>0.413</t>
+          <t>0.3854</t>
         </is>
       </c>
       <c r="BE224" t="inlineStr">
         <is>
-          <t>0.166</t>
+          <t>0.1522</t>
         </is>
       </c>
       <c r="BF224" t="inlineStr">
         <is>
-          <t>26.4</t>
-        </is>
-      </c>
-      <c r="BG224" t="inlineStr"/>
-      <c r="BH224" t="inlineStr"/>
+          <t>30.1</t>
+        </is>
+      </c>
+      <c r="BG224" t="inlineStr">
+        <is>
+          <t>In From LF</t>
+        </is>
+      </c>
+      <c r="BH224" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
       <c r="BI224" t="inlineStr">
         <is>
-          <t>Kauffman Stadium</t>
+          <t>Progressive Field</t>
         </is>
       </c>
       <c r="BJ224" t="inlineStr"/>
@@ -72710,7 +72710,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>61.7</v>
+        <v>61.6</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -72743,7 +72743,7 @@
         <v>80</v>
       </c>
       <c r="U17" t="n">
-        <v>37.8</v>
+        <v>36.3</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
@@ -72800,7 +72800,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
@@ -72810,7 +72810,7 @@
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/24, 1 HR</t>
+          <t>Last 7 games: 6/25, 1 HR</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">

--- a/outputs/hr_rankings.xlsx
+++ b/outputs/hr_rankings.xlsx
@@ -7691,24 +7691,24 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>668804</t>
+          <t>607208</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Bryan Reynolds</t>
+          <t>Trea Turner</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
+          <t>PHI</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
           <t>PIT</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>PHI</t>
-        </is>
-      </c>
       <c r="F27" t="inlineStr">
         <is>
           <t>2026-07-02T16:35:00Z</t>
@@ -7721,17 +7721,17 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Alan Rangel</t>
+          <t>Jared Jones</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>660604</t>
+          <t>683003</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -7740,7 +7740,7 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>54.5</v>
+        <v>54.6</v>
       </c>
       <c r="M27" t="inlineStr">
         <is>
@@ -7754,26 +7754,26 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>Good Environment, Premium Lineup Spot, Platoon Edge</t>
+          <t>Good Environment, Premium Lineup Spot, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P27" t="n">
-        <v>46</v>
+        <v>26.6</v>
       </c>
       <c r="Q27" t="n">
-        <v>27.2</v>
+        <v>49.3</v>
       </c>
       <c r="R27" t="n">
         <v>80.8</v>
       </c>
       <c r="S27" t="n">
-        <v>96.59999999999999</v>
+        <v>93.2</v>
       </c>
       <c r="T27" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U27" t="n">
-        <v>8.800000000000001</v>
+        <v>87</v>
       </c>
       <c r="V27" t="inlineStr">
         <is>
@@ -7787,7 +7787,7 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr">
@@ -7808,7 +7808,7 @@
       <c r="AB27" t="inlineStr"/>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD27" t="inlineStr"/>
@@ -7825,127 +7825,127 @@
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/28, 0 HR</t>
+          <t>Hot streak: 3 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL27" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 6.9% barrel, 1.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 9.2% barrel, 5.0 HR allowed</t>
         </is>
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN27" t="inlineStr">
         <is>
-          <t>9.96</t>
+          <t>5.66</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>47.26</t>
+          <t>40.42</t>
         </is>
       </c>
       <c r="AP27" t="inlineStr">
         <is>
-          <t>91.34</t>
+          <t>88.95</t>
         </is>
       </c>
       <c r="AQ27" t="inlineStr">
         <is>
-          <t>102.1504</t>
+          <t>99.3035</t>
         </is>
       </c>
       <c r="AR27" t="inlineStr">
         <is>
-          <t>0.4498</t>
+          <t>0.3743</t>
         </is>
       </c>
       <c r="AS27" t="inlineStr">
         <is>
-          <t>0.1883</t>
+          <t>0.1253</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr">
         <is>
-          <t>0.359</t>
+          <t>0.2965</t>
         </is>
       </c>
       <c r="AU27" t="inlineStr">
         <is>
-          <t>72.76</t>
+          <t>71.48</t>
         </is>
       </c>
       <c r="AV27" t="inlineStr">
         <is>
-          <t>29.49</t>
+          <t>18.57</t>
         </is>
       </c>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>40.15</t>
+          <t>33.84</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>24.27</t>
+          <t>26.6</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
-          <t>12.5</t>
+          <t>11.5</t>
         </is>
       </c>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>0.1745</t>
+          <t>0.1362</t>
         </is>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
-          <t>6.86</t>
+          <t>9.2</t>
         </is>
       </c>
       <c r="BB27" t="inlineStr">
         <is>
-          <t>30.17</t>
+          <t>40.8</t>
         </is>
       </c>
       <c r="BC27" t="inlineStr">
         <is>
-          <t>87.1</t>
+          <t>90.3</t>
         </is>
       </c>
       <c r="BD27" t="inlineStr">
         <is>
-          <t>0.3892</t>
+          <t>0.457</t>
         </is>
       </c>
       <c r="BE27" t="inlineStr">
         <is>
-          <t>0.1569</t>
+          <t>0.198</t>
         </is>
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>30.41</t>
+          <t>26.3</t>
         </is>
       </c>
       <c r="BG27" t="inlineStr">
@@ -7971,24 +7971,24 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>607208</t>
+          <t>668804</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Trea Turner</t>
+          <t>Bryan Reynolds</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
+          <t>PIT</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
           <t>PHI</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>PIT</t>
-        </is>
-      </c>
       <c r="F28" t="inlineStr">
         <is>
           <t>2026-07-02T16:35:00Z</t>
@@ -8001,17 +8001,17 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Jared Jones</t>
+          <t>Alan Rangel</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>683003</t>
+          <t>660604</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -8034,26 +8034,26 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>Good Environment, Premium Lineup Spot, Hot Hitter/Streak</t>
+          <t>Good Environment, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P28" t="n">
-        <v>26.6</v>
+        <v>46</v>
       </c>
       <c r="Q28" t="n">
-        <v>49.3</v>
+        <v>27.2</v>
       </c>
       <c r="R28" t="n">
         <v>80.8</v>
       </c>
       <c r="S28" t="n">
-        <v>93.2</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T28" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="U28" t="n">
-        <v>83.59999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="V28" t="inlineStr">
         <is>
@@ -8067,7 +8067,7 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr">
@@ -8088,7 +8088,7 @@
       <c r="AB28" t="inlineStr"/>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD28" t="inlineStr"/>
@@ -8105,127 +8105,127 @@
       </c>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>Hot streak: 3 HR in last 7 games</t>
+          <t>Last 7 games: 5/28, 0 HR</t>
         </is>
       </c>
       <c r="AL28" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 9.2% barrel, 5.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 6.9% barrel, 1.0 HR allowed</t>
         </is>
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN28" t="inlineStr">
         <is>
-          <t>5.66</t>
+          <t>9.96</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>40.42</t>
+          <t>47.26</t>
         </is>
       </c>
       <c r="AP28" t="inlineStr">
         <is>
-          <t>88.95</t>
+          <t>91.34</t>
         </is>
       </c>
       <c r="AQ28" t="inlineStr">
         <is>
-          <t>99.3035</t>
+          <t>102.1504</t>
         </is>
       </c>
       <c r="AR28" t="inlineStr">
         <is>
-          <t>0.3743</t>
+          <t>0.4498</t>
         </is>
       </c>
       <c r="AS28" t="inlineStr">
         <is>
-          <t>0.1253</t>
+          <t>0.1883</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr">
         <is>
-          <t>0.2965</t>
+          <t>0.359</t>
         </is>
       </c>
       <c r="AU28" t="inlineStr">
         <is>
-          <t>71.48</t>
+          <t>72.76</t>
         </is>
       </c>
       <c r="AV28" t="inlineStr">
         <is>
-          <t>18.57</t>
+          <t>29.49</t>
         </is>
       </c>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>33.84</t>
+          <t>40.15</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>26.6</t>
+          <t>24.27</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
-          <t>11.5</t>
+          <t>12.5</t>
         </is>
       </c>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>0.1362</t>
+          <t>0.1745</t>
         </is>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
-          <t>9.2</t>
+          <t>6.86</t>
         </is>
       </c>
       <c r="BB28" t="inlineStr">
         <is>
-          <t>40.8</t>
+          <t>30.17</t>
         </is>
       </c>
       <c r="BC28" t="inlineStr">
         <is>
-          <t>90.3</t>
+          <t>87.1</t>
         </is>
       </c>
       <c r="BD28" t="inlineStr">
         <is>
-          <t>0.457</t>
+          <t>0.3892</t>
         </is>
       </c>
       <c r="BE28" t="inlineStr">
         <is>
-          <t>0.198</t>
+          <t>0.1569</t>
         </is>
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>26.3</t>
+          <t>30.41</t>
         </is>
       </c>
       <c r="BG28" t="inlineStr">
@@ -24396,7 +24396,7 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>44.9</v>
+        <v>45</v>
       </c>
       <c r="M87" t="inlineStr">
         <is>
@@ -24429,7 +24429,7 @@
         <v>80</v>
       </c>
       <c r="U87" t="n">
-        <v>4.5</v>
+        <v>5.7</v>
       </c>
       <c r="V87" t="inlineStr">
         <is>
@@ -24486,7 +24486,7 @@
       </c>
       <c r="AI87" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AJ87" t="inlineStr">
@@ -24496,7 +24496,7 @@
       </c>
       <c r="AK87" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/20, 0 HR</t>
+          <t>Last 7 games: 3/19, 0 HR</t>
         </is>
       </c>
       <c r="AL87" t="inlineStr">

--- a/outputs/hr_rankings.xlsx
+++ b/outputs/hr_rankings.xlsx
@@ -784,7 +784,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>74</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -817,7 +817,7 @@
         <v>80</v>
       </c>
       <c r="U2" t="n">
-        <v>31.6</v>
+        <v>30.3</v>
       </c>
       <c r="V2" t="inlineStr">
         <is>
@@ -874,7 +874,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
@@ -884,7 +884,7 @@
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/24, 1 HR</t>
+          <t>Last 7 games: 5/25, 1 HR</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
@@ -6027,47 +6027,47 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>694192</t>
+          <t>650489</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Jackson Chourio</t>
+          <t>Willi Castro</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-07-02T18:10:00Z</t>
+          <t>2026-07-02T19:10:00Z</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Chase Burns</t>
+          <t>Ryan Gusto</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>695505</t>
+          <t>687473</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -6076,7 +6076,7 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>55.6</v>
+        <v>55.5</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
@@ -6090,26 +6090,26 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot</t>
+          <t>Good Environment, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P21" t="n">
-        <v>53.4</v>
+        <v>28.3</v>
       </c>
       <c r="Q21" t="n">
-        <v>37.9</v>
+        <v>50.8</v>
       </c>
       <c r="R21" t="n">
-        <v>47.6</v>
+        <v>81.7</v>
       </c>
       <c r="S21" t="n">
-        <v>100</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T21" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="U21" t="n">
-        <v>65.2</v>
+        <v>34.2</v>
       </c>
       <c r="V21" t="inlineStr">
         <is>
@@ -6123,7 +6123,7 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
@@ -6161,27 +6161,27 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>31</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 7/31, 1 HR</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.7% barrel, 9.2 HR allowed</t>
+          <t>switch hitter; pitcher baseline 9.8% barrel, 6.5 HR allowed</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
@@ -6191,112 +6191,112 @@
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>12.78</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>45.66</t>
+          <t>40.31</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>91.47</t>
+          <t>87.96</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>102.3936</t>
+          <t>100.1044</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>0.4603</t>
+          <t>0.3687</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
         <is>
-          <t>0.2077</t>
+          <t>0.1316</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>0.3308</t>
+          <t>0.3039</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
         <is>
-          <t>74.67</t>
+          <t>72.51</t>
         </is>
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>48.47</t>
+          <t>24.81</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>32.9</t>
+          <t>43.44</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>28.99</t>
+          <t>30.69</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>14.7</t>
+          <t>7.5</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>0.2224</t>
+          <t>0.1253</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>8.66</t>
+          <t>9.85</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>38.91</t>
+          <t>46.68</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>89.22</t>
+          <t>90.04</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>0.3511</t>
+          <t>0.4446</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
-          <t>0.1439</t>
+          <t>0.1711</t>
         </is>
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>27.82</t>
+          <t>26.75</t>
         </is>
       </c>
       <c r="BG21" t="inlineStr">
         <is>
-          <t>In From RF</t>
+          <t>Out To LF</t>
         </is>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>90</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
         <is>
-          <t>American Family Field</t>
+          <t>Coors Field</t>
         </is>
       </c>
       <c r="BJ21" t="inlineStr"/>
@@ -6307,47 +6307,47 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>650489</t>
+          <t>691406</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Willi Castro</t>
+          <t>Junior Caminero</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-07-02T19:10:00Z</t>
+          <t>2026-07-02T23:40:00Z</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Ryan Gusto</t>
+          <t>Stephen Kolek</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>687473</t>
+          <t>663568</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -6370,58 +6370,62 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>Good Environment, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P22" t="n">
-        <v>28.3</v>
+        <v>65</v>
       </c>
       <c r="Q22" t="n">
-        <v>50.8</v>
+        <v>34.2</v>
       </c>
       <c r="R22" t="n">
-        <v>81.7</v>
+        <v>23.2</v>
       </c>
       <c r="S22" t="n">
-        <v>94.90000000000001</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="T22" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U22" t="n">
-        <v>34.2</v>
+        <v>100</v>
       </c>
       <c r="V22" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W22" t="inlineStr">
+      <c r="Z22" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y22" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC22" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -6441,142 +6445,134 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/31, 1 HR</t>
+          <t>Hot streak: 8 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 9.8% barrel, 6.5 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.9% barrel, 8.3 HR allowed</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>13.72</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>40.31</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>87.96</t>
+          <t>93.17</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>100.1044</t>
+          <t>105.5339</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>0.3687</t>
+          <t>0.5101</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
         <is>
-          <t>0.1316</t>
+          <t>0.2383</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>0.3039</t>
+          <t>0.3677</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
         <is>
-          <t>72.51</t>
+          <t>79.55</t>
         </is>
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>24.81</t>
+          <t>86.84</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>43.44</t>
+          <t>45.38</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>30.69</t>
+          <t>23.63</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>7.5</t>
+          <t>30.3</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>0.1253</t>
+          <t>0.2689</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>9.85</t>
+          <t>6.94</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>46.68</t>
+          <t>41.42</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>90.04</t>
+          <t>89.49</t>
         </is>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>0.4446</t>
+          <t>0.3899</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
-          <t>0.1711</t>
+          <t>0.1278</t>
         </is>
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>26.75</t>
-        </is>
-      </c>
-      <c r="BG22" t="inlineStr">
-        <is>
-          <t>Out To LF</t>
-        </is>
-      </c>
-      <c r="BH22" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
+          <t>21.88</t>
+        </is>
+      </c>
+      <c r="BG22" t="inlineStr"/>
+      <c r="BH22" t="inlineStr"/>
       <c r="BI22" t="inlineStr">
         <is>
-          <t>Coors Field</t>
+          <t>Kauffman Stadium</t>
         </is>
       </c>
       <c r="BJ22" t="inlineStr"/>
@@ -6587,47 +6583,47 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>691406</t>
+          <t>694192</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Junior Caminero</t>
+          <t>Jackson Chourio</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-07-02T23:40:00Z</t>
+          <t>2026-07-02T18:10:00Z</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Stephen Kolek</t>
+          <t>Chase Burns</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>663568</t>
+          <t>695505</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -6636,7 +6632,7 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>55.5</v>
+        <v>55.4</v>
       </c>
       <c r="M23" t="inlineStr">
         <is>
@@ -6650,62 +6646,58 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Hot Hitter/Streak</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P23" t="n">
-        <v>65</v>
+        <v>53.4</v>
       </c>
       <c r="Q23" t="n">
-        <v>34.2</v>
+        <v>37.9</v>
       </c>
       <c r="R23" t="n">
-        <v>23.2</v>
+        <v>47.6</v>
       </c>
       <c r="S23" t="n">
-        <v>92.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="T23" t="n">
         <v>50</v>
       </c>
       <c r="U23" t="n">
-        <v>100</v>
+        <v>60.7</v>
       </c>
       <c r="V23" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W23" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y23" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr"/>
       <c r="AC23" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -6725,134 +6717,142 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>Hot streak: 8 HR in last 7 games</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.9% barrel, 8.3 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.7% barrel, 9.2 HR allowed</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>EV profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>13.72</t>
+          <t>12.78</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>45.66</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>93.17</t>
+          <t>91.47</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>105.5339</t>
+          <t>102.3936</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>0.5101</t>
+          <t>0.4603</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
         <is>
-          <t>0.2383</t>
+          <t>0.2077</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>0.3677</t>
+          <t>0.3308</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
         <is>
-          <t>79.55</t>
+          <t>74.67</t>
         </is>
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>86.84</t>
+          <t>48.47</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>45.38</t>
+          <t>32.9</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>23.63</t>
+          <t>28.99</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>30.3</t>
+          <t>14.7</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>0.2689</t>
+          <t>0.2224</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>6.94</t>
+          <t>8.66</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>41.42</t>
+          <t>38.91</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>89.49</t>
+          <t>89.22</t>
         </is>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
-          <t>0.3899</t>
+          <t>0.3511</t>
         </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
-          <t>0.1278</t>
+          <t>0.1439</t>
         </is>
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>21.88</t>
-        </is>
-      </c>
-      <c r="BG23" t="inlineStr"/>
-      <c r="BH23" t="inlineStr"/>
+          <t>27.82</t>
+        </is>
+      </c>
+      <c r="BG23" t="inlineStr">
+        <is>
+          <t>In From RF</t>
+        </is>
+      </c>
+      <c r="BH23" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
       <c r="BI23" t="inlineStr">
         <is>
-          <t>Kauffman Stadium</t>
+          <t>American Family Field</t>
         </is>
       </c>
       <c r="BJ23" t="inlineStr"/>
@@ -19643,32 +19643,32 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>687263</t>
+          <t>592885</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Zach Neto</t>
+          <t>Christian Yelich</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-07-03T01:40:00Z</t>
+          <t>2026-07-02T18:10:00Z</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -19678,12 +19678,12 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Bryce Miller</t>
+          <t>Chase Burns</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>682243</t>
+          <t>695505</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -19692,7 +19692,7 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>47.9</v>
+        <v>48.1</v>
       </c>
       <c r="M70" t="inlineStr">
         <is>
@@ -19706,62 +19706,58 @@
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P70" t="n">
-        <v>50.8</v>
+        <v>33.4</v>
       </c>
       <c r="Q70" t="n">
-        <v>35.9</v>
+        <v>37.9</v>
       </c>
       <c r="R70" t="n">
-        <v>25.4</v>
+        <v>47.6</v>
       </c>
       <c r="S70" t="n">
-        <v>88.7</v>
+        <v>93.2</v>
       </c>
       <c r="T70" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U70" t="n">
-        <v>36.3</v>
+        <v>12</v>
       </c>
       <c r="V70" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z70" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W70" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X70" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y70" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z70" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB70" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr"/>
       <c r="AC70" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -19781,134 +19777,142 @@
       </c>
       <c r="AH70" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI70" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK70" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/25, 1 HR</t>
+          <t>Last 7 games: 4/20, 0 HR</t>
         </is>
       </c>
       <c r="AL70" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.3% barrel, 10.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.7% barrel, 9.2 HR allowed</t>
         </is>
       </c>
       <c r="AM70" t="inlineStr">
         <is>
-          <t>fly-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN70" t="inlineStr">
         <is>
-          <t>13.58</t>
+          <t>7.85</t>
         </is>
       </c>
       <c r="AO70" t="inlineStr">
         <is>
-          <t>41.42</t>
+          <t>42.62</t>
         </is>
       </c>
       <c r="AP70" t="inlineStr">
         <is>
-          <t>90.16</t>
+          <t>89.22</t>
         </is>
       </c>
       <c r="AQ70" t="inlineStr">
         <is>
-          <t>100.1597</t>
+          <t>100.7774</t>
         </is>
       </c>
       <c r="AR70" t="inlineStr">
         <is>
-          <t>0.4362</t>
+          <t>0.3844</t>
         </is>
       </c>
       <c r="AS70" t="inlineStr">
         <is>
-          <t>0.2202</t>
+          <t>0.1562</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr">
         <is>
-          <t>0.3223</t>
+          <t>0.3041</t>
         </is>
       </c>
       <c r="AU70" t="inlineStr">
         <is>
-          <t>70.98</t>
+          <t>73.19</t>
         </is>
       </c>
       <c r="AV70" t="inlineStr">
         <is>
-          <t>11.55</t>
+          <t>32.94</t>
         </is>
       </c>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>49.44</t>
+          <t>36.69</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>37.13</t>
+          <t>19.79</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr">
         <is>
-          <t>20.4</t>
+          <t>12.2</t>
         </is>
       </c>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>0.2233</t>
+          <t>0.1516</t>
         </is>
       </c>
       <c r="BA70" t="inlineStr">
         <is>
-          <t>8.28</t>
+          <t>8.66</t>
         </is>
       </c>
       <c r="BB70" t="inlineStr">
         <is>
-          <t>34.11</t>
+          <t>38.91</t>
         </is>
       </c>
       <c r="BC70" t="inlineStr">
         <is>
-          <t>87.92</t>
+          <t>89.22</t>
         </is>
       </c>
       <c r="BD70" t="inlineStr">
         <is>
-          <t>0.3755</t>
+          <t>0.3511</t>
         </is>
       </c>
       <c r="BE70" t="inlineStr">
         <is>
-          <t>0.1603</t>
+          <t>0.1439</t>
         </is>
       </c>
       <c r="BF70" t="inlineStr">
         <is>
-          <t>30.6</t>
-        </is>
-      </c>
-      <c r="BG70" t="inlineStr"/>
-      <c r="BH70" t="inlineStr"/>
+          <t>27.82</t>
+        </is>
+      </c>
+      <c r="BG70" t="inlineStr">
+        <is>
+          <t>In From RF</t>
+        </is>
+      </c>
+      <c r="BH70" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
       <c r="BI70" t="inlineStr">
         <is>
-          <t>T-Mobile Park</t>
+          <t>American Family Field</t>
         </is>
       </c>
       <c r="BJ70" t="inlineStr"/>
@@ -19919,32 +19923,32 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>592885</t>
+          <t>687263</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Christian Yelich</t>
+          <t>Zach Neto</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-07-02T18:10:00Z</t>
+          <t>2026-07-03T01:40:00Z</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -19954,12 +19958,12 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Chase Burns</t>
+          <t>Bryce Miller</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>695505</t>
+          <t>682243</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -19968,7 +19972,7 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>47.8</v>
+        <v>47.9</v>
       </c>
       <c r="M71" t="inlineStr">
         <is>
@@ -19982,58 +19986,62 @@
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P71" t="n">
-        <v>33.4</v>
+        <v>50.8</v>
       </c>
       <c r="Q71" t="n">
-        <v>37.9</v>
+        <v>35.9</v>
       </c>
       <c r="R71" t="n">
-        <v>47.6</v>
+        <v>25.4</v>
       </c>
       <c r="S71" t="n">
-        <v>93.2</v>
+        <v>88.7</v>
       </c>
       <c r="T71" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U71" t="n">
-        <v>7</v>
+        <v>36.3</v>
       </c>
       <c r="V71" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W71" t="inlineStr">
+      <c r="Z71" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X71" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y71" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB71" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC71" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -20053,142 +20061,134 @@
       </c>
       <c r="AH71" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI71" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/24, 0 HR</t>
+          <t>Last 7 games: 6/25, 1 HR</t>
         </is>
       </c>
       <c r="AL71" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.7% barrel, 9.2 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.3% barrel, 10.0 HR allowed</t>
         </is>
       </c>
       <c r="AM71" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>fly-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN71" t="inlineStr">
         <is>
-          <t>7.85</t>
+          <t>13.58</t>
         </is>
       </c>
       <c r="AO71" t="inlineStr">
         <is>
-          <t>42.62</t>
+          <t>41.42</t>
         </is>
       </c>
       <c r="AP71" t="inlineStr">
         <is>
-          <t>89.22</t>
+          <t>90.16</t>
         </is>
       </c>
       <c r="AQ71" t="inlineStr">
         <is>
-          <t>100.7774</t>
+          <t>100.1597</t>
         </is>
       </c>
       <c r="AR71" t="inlineStr">
         <is>
-          <t>0.3844</t>
+          <t>0.4362</t>
         </is>
       </c>
       <c r="AS71" t="inlineStr">
         <is>
-          <t>0.1562</t>
+          <t>0.2202</t>
         </is>
       </c>
       <c r="AT71" t="inlineStr">
         <is>
-          <t>0.3041</t>
+          <t>0.3223</t>
         </is>
       </c>
       <c r="AU71" t="inlineStr">
         <is>
-          <t>73.19</t>
+          <t>70.98</t>
         </is>
       </c>
       <c r="AV71" t="inlineStr">
         <is>
-          <t>32.94</t>
+          <t>11.55</t>
         </is>
       </c>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>36.69</t>
+          <t>49.44</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>19.79</t>
+          <t>37.13</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr">
         <is>
-          <t>12.2</t>
+          <t>20.4</t>
         </is>
       </c>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>0.1516</t>
+          <t>0.2233</t>
         </is>
       </c>
       <c r="BA71" t="inlineStr">
         <is>
-          <t>8.66</t>
+          <t>8.28</t>
         </is>
       </c>
       <c r="BB71" t="inlineStr">
         <is>
-          <t>38.91</t>
+          <t>34.11</t>
         </is>
       </c>
       <c r="BC71" t="inlineStr">
         <is>
-          <t>89.22</t>
+          <t>87.92</t>
         </is>
       </c>
       <c r="BD71" t="inlineStr">
         <is>
-          <t>0.3511</t>
+          <t>0.3755</t>
         </is>
       </c>
       <c r="BE71" t="inlineStr">
         <is>
-          <t>0.1439</t>
+          <t>0.1603</t>
         </is>
       </c>
       <c r="BF71" t="inlineStr">
         <is>
-          <t>27.82</t>
-        </is>
-      </c>
-      <c r="BG71" t="inlineStr">
-        <is>
-          <t>In From RF</t>
-        </is>
-      </c>
-      <c r="BH71" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
+          <t>30.6</t>
+        </is>
+      </c>
+      <c r="BG71" t="inlineStr"/>
+      <c r="BH71" t="inlineStr"/>
       <c r="BI71" t="inlineStr">
         <is>
-          <t>American Family Field</t>
+          <t>T-Mobile Park</t>
         </is>
       </c>
       <c r="BJ71" t="inlineStr"/>
@@ -26283,47 +26283,47 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>663586</t>
+          <t>663993</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Austin Riley</t>
+          <t>Nathaniel Lowe</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-07-02T23:15:00Z</t>
+          <t>2026-07-02T18:10:00Z</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>Dustin May</t>
+          <t>Jacob Misiorowski</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>669160</t>
+          <t>694819</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
@@ -26346,62 +26346,58 @@
       </c>
       <c r="O94" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P94" t="n">
-        <v>48.5</v>
+        <v>40.1</v>
       </c>
       <c r="Q94" t="n">
-        <v>43.2</v>
+        <v>14.1</v>
       </c>
       <c r="R94" t="n">
-        <v>30.9</v>
+        <v>47.6</v>
       </c>
       <c r="S94" t="n">
-        <v>59.8</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T94" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U94" t="n">
-        <v>0</v>
+        <v>16.6</v>
       </c>
       <c r="V94" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z94" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W94" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X94" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y94" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z94" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB94" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB94" t="inlineStr"/>
       <c r="AC94" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -26421,12 +26417,12 @@
       </c>
       <c r="AH94" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI94" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AJ94" t="inlineStr">
@@ -26436,12 +26432,12 @@
       </c>
       <c r="AK94" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/25, 0 HR</t>
+          <t>Last 7 games: 3/13, 0 HR</t>
         </is>
       </c>
       <c r="AL94" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.8% barrel, 11.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 4.2% barrel, 5.9 HR allowed</t>
         </is>
       </c>
       <c r="AM94" t="inlineStr">
@@ -26451,104 +26447,112 @@
       </c>
       <c r="AN94" t="inlineStr">
         <is>
-          <t>11.35</t>
+          <t>10.01</t>
         </is>
       </c>
       <c r="AO94" t="inlineStr">
         <is>
-          <t>45.51</t>
+          <t>40.66</t>
         </is>
       </c>
       <c r="AP94" t="inlineStr">
         <is>
-          <t>91.25</t>
+          <t>88.79</t>
         </is>
       </c>
       <c r="AQ94" t="inlineStr">
         <is>
-          <t>102.356</t>
+          <t>100.9038</t>
         </is>
       </c>
       <c r="AR94" t="inlineStr">
         <is>
-          <t>0.4013</t>
+          <t>0.4381</t>
         </is>
       </c>
       <c r="AS94" t="inlineStr">
         <is>
-          <t>0.1837</t>
+          <t>0.1828</t>
         </is>
       </c>
       <c r="AT94" t="inlineStr">
         <is>
-          <t>0.3027</t>
+          <t>0.3408</t>
         </is>
       </c>
       <c r="AU94" t="inlineStr">
         <is>
-          <t>75.69</t>
+          <t>73.96</t>
         </is>
       </c>
       <c r="AV94" t="inlineStr">
         <is>
-          <t>58.12</t>
+          <t>36.97</t>
         </is>
       </c>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>40.85</t>
+          <t>40.42</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>31.5</t>
+          <t>24.87</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr">
         <is>
-          <t>10.4</t>
+          <t>11.7</t>
         </is>
       </c>
       <c r="AZ94" t="inlineStr">
         <is>
-          <t>0.1379</t>
+          <t>0.1999</t>
         </is>
       </c>
       <c r="BA94" t="inlineStr">
         <is>
-          <t>7.8</t>
+          <t>4.19</t>
         </is>
       </c>
       <c r="BB94" t="inlineStr">
         <is>
-          <t>45.83</t>
+          <t>34.49</t>
         </is>
       </c>
       <c r="BC94" t="inlineStr">
         <is>
-          <t>90.18</t>
+          <t>87.67</t>
         </is>
       </c>
       <c r="BD94" t="inlineStr">
         <is>
-          <t>0.3999</t>
+          <t>0.274</t>
         </is>
       </c>
       <c r="BE94" t="inlineStr">
         <is>
-          <t>0.1539</t>
+          <t>0.0912</t>
         </is>
       </c>
       <c r="BF94" t="inlineStr">
         <is>
-          <t>24.1</t>
-        </is>
-      </c>
-      <c r="BG94" t="inlineStr"/>
-      <c r="BH94" t="inlineStr"/>
+          <t>23.82</t>
+        </is>
+      </c>
+      <c r="BG94" t="inlineStr">
+        <is>
+          <t>In From RF</t>
+        </is>
+      </c>
+      <c r="BH94" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
       <c r="BI94" t="inlineStr">
         <is>
-          <t>Truist Park</t>
+          <t>American Family Field</t>
         </is>
       </c>
       <c r="BJ94" t="inlineStr"/>
@@ -26559,47 +26563,47 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>663993</t>
+          <t>663586</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Nathaniel Lowe</t>
+          <t>Austin Riley</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-07-02T18:10:00Z</t>
+          <t>2026-07-02T23:15:00Z</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>Jacob Misiorowski</t>
+          <t>Dustin May</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>694819</t>
+          <t>669160</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
@@ -26608,7 +26612,7 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>43.6</v>
+        <v>43.9</v>
       </c>
       <c r="M95" t="inlineStr">
         <is>
@@ -26622,58 +26626,62 @@
       </c>
       <c r="O95" t="inlineStr">
         <is>
-          <t>Strong Barrel, Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel</t>
         </is>
       </c>
       <c r="P95" t="n">
-        <v>40.1</v>
+        <v>48.5</v>
       </c>
       <c r="Q95" t="n">
-        <v>14.1</v>
+        <v>43.2</v>
       </c>
       <c r="R95" t="n">
-        <v>47.6</v>
+        <v>30.9</v>
       </c>
       <c r="S95" t="n">
-        <v>86.40000000000001</v>
+        <v>59.8</v>
       </c>
       <c r="T95" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U95" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="V95" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W95" t="inlineStr">
+      <c r="Z95" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X95" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y95" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z95" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB95" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB95" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC95" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -26693,12 +26701,12 @@
       </c>
       <c r="AH95" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI95" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ95" t="inlineStr">
@@ -26708,12 +26716,12 @@
       </c>
       <c r="AK95" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/15, 0 HR</t>
+          <t>Last 7 games: 2/25, 0 HR</t>
         </is>
       </c>
       <c r="AL95" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 4.2% barrel, 5.9 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.8% barrel, 11.2 HR allowed</t>
         </is>
       </c>
       <c r="AM95" t="inlineStr">
@@ -26723,112 +26731,104 @@
       </c>
       <c r="AN95" t="inlineStr">
         <is>
-          <t>10.01</t>
+          <t>11.35</t>
         </is>
       </c>
       <c r="AO95" t="inlineStr">
         <is>
-          <t>40.66</t>
+          <t>45.51</t>
         </is>
       </c>
       <c r="AP95" t="inlineStr">
         <is>
-          <t>88.79</t>
+          <t>91.25</t>
         </is>
       </c>
       <c r="AQ95" t="inlineStr">
         <is>
-          <t>100.9038</t>
+          <t>102.356</t>
         </is>
       </c>
       <c r="AR95" t="inlineStr">
         <is>
-          <t>0.4381</t>
+          <t>0.4013</t>
         </is>
       </c>
       <c r="AS95" t="inlineStr">
         <is>
-          <t>0.1828</t>
+          <t>0.1837</t>
         </is>
       </c>
       <c r="AT95" t="inlineStr">
         <is>
-          <t>0.3408</t>
+          <t>0.3027</t>
         </is>
       </c>
       <c r="AU95" t="inlineStr">
         <is>
-          <t>73.96</t>
+          <t>75.69</t>
         </is>
       </c>
       <c r="AV95" t="inlineStr">
         <is>
-          <t>36.97</t>
+          <t>58.12</t>
         </is>
       </c>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>40.42</t>
+          <t>40.85</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>24.87</t>
+          <t>31.5</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr">
         <is>
-          <t>11.7</t>
+          <t>10.4</t>
         </is>
       </c>
       <c r="AZ95" t="inlineStr">
         <is>
-          <t>0.1999</t>
+          <t>0.1379</t>
         </is>
       </c>
       <c r="BA95" t="inlineStr">
         <is>
-          <t>4.19</t>
+          <t>7.8</t>
         </is>
       </c>
       <c r="BB95" t="inlineStr">
         <is>
-          <t>34.49</t>
+          <t>45.83</t>
         </is>
       </c>
       <c r="BC95" t="inlineStr">
         <is>
-          <t>87.67</t>
+          <t>90.18</t>
         </is>
       </c>
       <c r="BD95" t="inlineStr">
         <is>
-          <t>0.274</t>
+          <t>0.3999</t>
         </is>
       </c>
       <c r="BE95" t="inlineStr">
         <is>
-          <t>0.0912</t>
+          <t>0.1539</t>
         </is>
       </c>
       <c r="BF95" t="inlineStr">
         <is>
-          <t>23.82</t>
-        </is>
-      </c>
-      <c r="BG95" t="inlineStr">
-        <is>
-          <t>In From RF</t>
-        </is>
-      </c>
-      <c r="BH95" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
+          <t>24.1</t>
+        </is>
+      </c>
+      <c r="BG95" t="inlineStr"/>
+      <c r="BH95" t="inlineStr"/>
       <c r="BI95" t="inlineStr">
         <is>
-          <t>American Family Field</t>
+          <t>Truist Park</t>
         </is>
       </c>
       <c r="BJ95" t="inlineStr"/>
@@ -30163,27 +30163,27 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>553993</t>
+          <t>693304</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Eugenio Suárez</t>
+          <t>Nick Gonzales</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-07-02T18:10:00Z</t>
+          <t>2026-07-02T16:35:00Z</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -30193,17 +30193,17 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>Jacob Misiorowski</t>
+          <t>Alan Rangel</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>694819</t>
+          <t>660604</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
@@ -30212,7 +30212,7 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>40.7</v>
+        <v>40.8</v>
       </c>
       <c r="M108" t="inlineStr">
         <is>
@@ -30226,26 +30226,26 @@
       </c>
       <c r="O108" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot</t>
+          <t>Good Environment</t>
         </is>
       </c>
       <c r="P108" t="n">
-        <v>32</v>
+        <v>15.7</v>
       </c>
       <c r="Q108" t="n">
-        <v>14.1</v>
+        <v>27.3</v>
       </c>
       <c r="R108" t="n">
-        <v>47.6</v>
+        <v>80.8</v>
       </c>
       <c r="S108" t="n">
-        <v>94.90000000000001</v>
+        <v>76.2</v>
       </c>
       <c r="T108" t="n">
         <v>50</v>
       </c>
       <c r="U108" t="n">
-        <v>36</v>
+        <v>34.5</v>
       </c>
       <c r="V108" t="inlineStr">
         <is>
@@ -30259,7 +30259,7 @@
       </c>
       <c r="X108" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y108" t="inlineStr">
@@ -30297,142 +30297,142 @@
       </c>
       <c r="AH108" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI108" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK108" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/21, 1 HR</t>
+          <t>Contact streak: 7/20 over last 7 games</t>
         </is>
       </c>
       <c r="AL108" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 4.2% barrel, 5.9 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.9% barrel, 1.0 HR allowed</t>
         </is>
       </c>
       <c r="AM108" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN108" t="inlineStr">
         <is>
-          <t>9.82</t>
+          <t>3.38</t>
         </is>
       </c>
       <c r="AO108" t="inlineStr">
         <is>
-          <t>34.23</t>
+          <t>36.7</t>
         </is>
       </c>
       <c r="AP108" t="inlineStr">
         <is>
-          <t>88.03</t>
+          <t>86.63</t>
         </is>
       </c>
       <c r="AQ108" t="inlineStr">
         <is>
-          <t>99.1722</t>
+          <t>98.4206</t>
         </is>
       </c>
       <c r="AR108" t="inlineStr">
         <is>
-          <t>0.358</t>
+          <t>0.3806</t>
         </is>
       </c>
       <c r="AS108" t="inlineStr">
         <is>
-          <t>0.1603</t>
+          <t>0.1056</t>
         </is>
       </c>
       <c r="AT108" t="inlineStr">
         <is>
-          <t>0.2773</t>
+          <t>0.3141</t>
         </is>
       </c>
       <c r="AU108" t="inlineStr">
         <is>
-          <t>71.74</t>
+          <t>70.5</t>
         </is>
       </c>
       <c r="AV108" t="inlineStr">
         <is>
-          <t>19.85</t>
+          <t>12.45</t>
         </is>
       </c>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>47.61</t>
+          <t>40.72</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>30.61</t>
+          <t>20.56</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr">
         <is>
-          <t>20.3</t>
+          <t>3.6</t>
         </is>
       </c>
       <c r="AZ108" t="inlineStr">
         <is>
-          <t>0.2063</t>
+          <t>0.0817</t>
         </is>
       </c>
       <c r="BA108" t="inlineStr">
         <is>
-          <t>4.19</t>
+          <t>6.86</t>
         </is>
       </c>
       <c r="BB108" t="inlineStr">
         <is>
-          <t>34.49</t>
+          <t>30.17</t>
         </is>
       </c>
       <c r="BC108" t="inlineStr">
         <is>
-          <t>87.67</t>
+          <t>87.1</t>
         </is>
       </c>
       <c r="BD108" t="inlineStr">
         <is>
-          <t>0.274</t>
+          <t>0.3892</t>
         </is>
       </c>
       <c r="BE108" t="inlineStr">
         <is>
-          <t>0.0912</t>
+          <t>0.1569</t>
         </is>
       </c>
       <c r="BF108" t="inlineStr">
         <is>
-          <t>23.82</t>
+          <t>30.41</t>
         </is>
       </c>
       <c r="BG108" t="inlineStr">
         <is>
-          <t>In From RF</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BH108" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>98</t>
         </is>
       </c>
       <c r="BI108" t="inlineStr">
         <is>
-          <t>American Family Field</t>
+          <t>Citizens Bank Park</t>
         </is>
       </c>
       <c r="BJ108" t="inlineStr"/>
@@ -30443,47 +30443,47 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>683953</t>
+          <t>553993</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Travis Bazzana</t>
+          <t>Eugenio Suárez</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-07-02T22:40:00Z</t>
+          <t>2026-07-02T18:10:00Z</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>Davis Martin</t>
+          <t>Jacob Misiorowski</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>663436</t>
+          <t>694819</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
@@ -30506,65 +30506,61 @@
       </c>
       <c r="O109" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P109" t="n">
-        <v>21.9</v>
+        <v>32</v>
       </c>
       <c r="Q109" t="n">
-        <v>40.7</v>
+        <v>14.1</v>
       </c>
       <c r="R109" t="n">
-        <v>27.6</v>
+        <v>47.6</v>
       </c>
       <c r="S109" t="n">
-        <v>88.7</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T109" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U109" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="V109" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W109" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X109" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y109" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z109" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W109" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X109" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y109" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z109" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB109" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB109" t="inlineStr"/>
       <c r="AC109" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD109" t="inlineStr"/>
@@ -30581,27 +30577,27 @@
       </c>
       <c r="AH109" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI109" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/29, 0 HR</t>
+          <t>Last 7 games: 5/21, 1 HR</t>
         </is>
       </c>
       <c r="AL109" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.3% barrel, 10.2 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 4.2% barrel, 5.9 HR allowed</t>
         </is>
       </c>
       <c r="AM109" t="inlineStr">
@@ -30611,104 +30607,112 @@
       </c>
       <c r="AN109" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>9.82</t>
         </is>
       </c>
       <c r="AO109" t="inlineStr">
         <is>
-          <t>36.5</t>
+          <t>34.23</t>
         </is>
       </c>
       <c r="AP109" t="inlineStr">
         <is>
-          <t>88.4</t>
+          <t>88.03</t>
         </is>
       </c>
       <c r="AQ109" t="inlineStr">
         <is>
-          <t>98.6732</t>
+          <t>99.1722</t>
         </is>
       </c>
       <c r="AR109" t="inlineStr">
         <is>
-          <t>0.359</t>
+          <t>0.358</t>
         </is>
       </c>
       <c r="AS109" t="inlineStr">
         <is>
-          <t>0.129</t>
+          <t>0.1603</t>
         </is>
       </c>
       <c r="AT109" t="inlineStr">
         <is>
-          <t>0.306</t>
+          <t>0.2773</t>
         </is>
       </c>
       <c r="AU109" t="inlineStr">
         <is>
-          <t>69.5</t>
+          <t>71.74</t>
         </is>
       </c>
       <c r="AV109" t="inlineStr">
         <is>
-          <t>13.3</t>
+          <t>19.85</t>
         </is>
       </c>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>41.1</t>
+          <t>47.61</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>29.7</t>
+          <t>30.61</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>20.3</t>
         </is>
       </c>
       <c r="AZ109" t="inlineStr">
         <is>
-          <t>0.167</t>
+          <t>0.2063</t>
         </is>
       </c>
       <c r="BA109" t="inlineStr">
         <is>
-          <t>7.35</t>
+          <t>4.19</t>
         </is>
       </c>
       <c r="BB109" t="inlineStr">
         <is>
-          <t>45.09</t>
+          <t>34.49</t>
         </is>
       </c>
       <c r="BC109" t="inlineStr">
         <is>
-          <t>90.14</t>
+          <t>87.67</t>
         </is>
       </c>
       <c r="BD109" t="inlineStr">
         <is>
-          <t>0.4076</t>
+          <t>0.274</t>
         </is>
       </c>
       <c r="BE109" t="inlineStr">
         <is>
-          <t>0.1468</t>
+          <t>0.0912</t>
         </is>
       </c>
       <c r="BF109" t="inlineStr">
         <is>
-          <t>22.01</t>
-        </is>
-      </c>
-      <c r="BG109" t="inlineStr"/>
-      <c r="BH109" t="inlineStr"/>
+          <t>23.82</t>
+        </is>
+      </c>
+      <c r="BG109" t="inlineStr">
+        <is>
+          <t>In From RF</t>
+        </is>
+      </c>
+      <c r="BH109" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
       <c r="BI109" t="inlineStr">
         <is>
-          <t>Progressive Field</t>
+          <t>American Family Field</t>
         </is>
       </c>
       <c r="BJ109" t="inlineStr"/>
@@ -30719,47 +30723,47 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>693304</t>
+          <t>683953</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Nick Gonzales</t>
+          <t>Travis Bazzana</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-07-02T16:35:00Z</t>
+          <t>2026-07-02T22:40:00Z</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>Alan Rangel</t>
+          <t>Davis Martin</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>660604</t>
+          <t>663436</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
@@ -30768,7 +30772,7 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>40.5</v>
+        <v>40.7</v>
       </c>
       <c r="M110" t="inlineStr">
         <is>
@@ -30782,61 +30786,65 @@
       </c>
       <c r="O110" t="inlineStr">
         <is>
-          <t>Good Environment</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P110" t="n">
-        <v>15.7</v>
+        <v>21.9</v>
       </c>
       <c r="Q110" t="n">
-        <v>27.3</v>
+        <v>40.7</v>
       </c>
       <c r="R110" t="n">
-        <v>80.8</v>
+        <v>27.6</v>
       </c>
       <c r="S110" t="n">
-        <v>76.2</v>
+        <v>88.7</v>
       </c>
       <c r="T110" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U110" t="n">
-        <v>29.4</v>
+        <v>0</v>
       </c>
       <c r="V110" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W110" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X110" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y110" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W110" t="inlineStr">
+      <c r="Z110" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X110" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y110" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z110" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB110" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB110" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC110" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD110" t="inlineStr"/>
@@ -30853,12 +30861,12 @@
       </c>
       <c r="AH110" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI110" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ110" t="inlineStr">
@@ -30868,127 +30876,119 @@
       </c>
       <c r="AK110" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/19, 0 HR</t>
+          <t>Last 7 games: 2/29, 0 HR</t>
         </is>
       </c>
       <c r="AL110" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.9% barrel, 1.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.3% barrel, 10.2 HR allowed</t>
         </is>
       </c>
       <c r="AM110" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN110" t="inlineStr">
         <is>
-          <t>3.38</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AO110" t="inlineStr">
         <is>
-          <t>36.7</t>
+          <t>36.5</t>
         </is>
       </c>
       <c r="AP110" t="inlineStr">
         <is>
-          <t>86.63</t>
+          <t>88.4</t>
         </is>
       </c>
       <c r="AQ110" t="inlineStr">
         <is>
-          <t>98.4206</t>
+          <t>98.6732</t>
         </is>
       </c>
       <c r="AR110" t="inlineStr">
         <is>
-          <t>0.3806</t>
+          <t>0.359</t>
         </is>
       </c>
       <c r="AS110" t="inlineStr">
         <is>
-          <t>0.1056</t>
+          <t>0.129</t>
         </is>
       </c>
       <c r="AT110" t="inlineStr">
         <is>
-          <t>0.3141</t>
+          <t>0.306</t>
         </is>
       </c>
       <c r="AU110" t="inlineStr">
         <is>
-          <t>70.5</t>
+          <t>69.5</t>
         </is>
       </c>
       <c r="AV110" t="inlineStr">
         <is>
-          <t>12.45</t>
+          <t>13.3</t>
         </is>
       </c>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>40.72</t>
+          <t>41.1</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>20.56</t>
+          <t>29.7</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr">
         <is>
-          <t>3.6</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="AZ110" t="inlineStr">
         <is>
-          <t>0.0817</t>
+          <t>0.167</t>
         </is>
       </c>
       <c r="BA110" t="inlineStr">
         <is>
-          <t>6.86</t>
+          <t>7.35</t>
         </is>
       </c>
       <c r="BB110" t="inlineStr">
         <is>
-          <t>30.17</t>
+          <t>45.09</t>
         </is>
       </c>
       <c r="BC110" t="inlineStr">
         <is>
-          <t>87.1</t>
+          <t>90.14</t>
         </is>
       </c>
       <c r="BD110" t="inlineStr">
         <is>
-          <t>0.3892</t>
+          <t>0.4076</t>
         </is>
       </c>
       <c r="BE110" t="inlineStr">
         <is>
-          <t>0.1569</t>
+          <t>0.1468</t>
         </is>
       </c>
       <c r="BF110" t="inlineStr">
         <is>
-          <t>30.41</t>
-        </is>
-      </c>
-      <c r="BG110" t="inlineStr">
-        <is>
-          <t>Out To RF</t>
-        </is>
-      </c>
-      <c r="BH110" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
-      </c>
+          <t>22.01</t>
+        </is>
+      </c>
+      <c r="BG110" t="inlineStr"/>
+      <c r="BH110" t="inlineStr"/>
       <c r="BI110" t="inlineStr">
         <is>
-          <t>Citizens Bank Park</t>
+          <t>Progressive Field</t>
         </is>
       </c>
       <c r="BJ110" t="inlineStr"/>
@@ -45035,47 +45035,47 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>624431</t>
+          <t>691026</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Jose Trevino</t>
+          <t>Masyn Winn</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>2026-07-02T18:10:00Z</t>
+          <t>2026-07-02T23:15:00Z</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>Jacob Misiorowski</t>
+          <t>Hurston Waldrep</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>694819</t>
+          <t>694462</t>
         </is>
       </c>
       <c r="K162" t="inlineStr">
@@ -45098,58 +45098,62 @@
       </c>
       <c r="O162" t="inlineStr">
         <is>
-          <t>No major boost</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P162" t="n">
-        <v>9</v>
+        <v>12.9</v>
       </c>
       <c r="Q162" t="n">
-        <v>14.1</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="R162" t="n">
-        <v>47.6</v>
+        <v>30.9</v>
       </c>
       <c r="S162" t="n">
-        <v>52.4</v>
+        <v>71.7</v>
       </c>
       <c r="T162" t="n">
         <v>50</v>
       </c>
       <c r="U162" t="n">
-        <v>21.1</v>
+        <v>13.3</v>
       </c>
       <c r="V162" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W162" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X162" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y162" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W162" t="inlineStr">
+      <c r="Z162" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X162" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y162" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z162" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA162" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB162" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB162" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC162" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -45169,12 +45173,12 @@
       </c>
       <c r="AH162" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI162" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ162" t="inlineStr">
@@ -45184,12 +45188,12 @@
       </c>
       <c r="AK162" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/23, 0 HR</t>
+          <t>Last 7 games: 5/24, 0 HR</t>
         </is>
       </c>
       <c r="AL162" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 4.2% barrel, 5.9 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 1.3% barrel, 0.9 HR allowed</t>
         </is>
       </c>
       <c r="AM162" t="inlineStr">
@@ -45199,112 +45203,104 @@
       </c>
       <c r="AN162" t="inlineStr">
         <is>
-          <t>2.96</t>
+          <t>3.68</t>
         </is>
       </c>
       <c r="AO162" t="inlineStr">
         <is>
-          <t>32.02</t>
+          <t>33.06</t>
         </is>
       </c>
       <c r="AP162" t="inlineStr">
         <is>
-          <t>86.22</t>
+          <t>87.67</t>
         </is>
       </c>
       <c r="AQ162" t="inlineStr">
         <is>
-          <t>97.186</t>
+          <t>98.2909</t>
         </is>
       </c>
       <c r="AR162" t="inlineStr">
         <is>
-          <t>0.3284</t>
+          <t>0.3337</t>
         </is>
       </c>
       <c r="AS162" t="inlineStr">
         <is>
-          <t>0.0885</t>
+          <t>0.0818</t>
         </is>
       </c>
       <c r="AT162" t="inlineStr">
         <is>
-          <t>0.2584</t>
+          <t>0.2972</t>
         </is>
       </c>
       <c r="AU162" t="inlineStr">
         <is>
-          <t>69.18</t>
+          <t>70.75</t>
         </is>
       </c>
       <c r="AV162" t="inlineStr">
         <is>
-          <t>4.49</t>
+          <t>12.4</t>
         </is>
       </c>
       <c r="AW162" t="inlineStr">
         <is>
-          <t>33.97</t>
+          <t>32.18</t>
         </is>
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>18.84</t>
+          <t>19.29</t>
         </is>
       </c>
       <c r="AY162" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>4.8</t>
         </is>
       </c>
       <c r="AZ162" t="inlineStr">
         <is>
-          <t>0.0612</t>
+          <t>0.0939</t>
         </is>
       </c>
       <c r="BA162" t="inlineStr">
         <is>
-          <t>4.19</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="BB162" t="inlineStr">
         <is>
-          <t>34.49</t>
+          <t>40.09</t>
         </is>
       </c>
       <c r="BC162" t="inlineStr">
         <is>
-          <t>87.67</t>
+          <t>85.32</t>
         </is>
       </c>
       <c r="BD162" t="inlineStr">
         <is>
-          <t>0.274</t>
+          <t>0.2785</t>
         </is>
       </c>
       <c r="BE162" t="inlineStr">
         <is>
-          <t>0.0912</t>
+          <t>0.0436</t>
         </is>
       </c>
       <c r="BF162" t="inlineStr">
         <is>
-          <t>23.82</t>
-        </is>
-      </c>
-      <c r="BG162" t="inlineStr">
-        <is>
-          <t>In From RF</t>
-        </is>
-      </c>
-      <c r="BH162" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
+          <t>6.45</t>
+        </is>
+      </c>
+      <c r="BG162" t="inlineStr"/>
+      <c r="BH162" t="inlineStr"/>
       <c r="BI162" t="inlineStr">
         <is>
-          <t>American Family Field</t>
+          <t>Truist Park</t>
         </is>
       </c>
       <c r="BJ162" t="inlineStr"/>
@@ -45315,47 +45311,47 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>691026</t>
+          <t>624431</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Masyn Winn</t>
+          <t>Jose Trevino</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>2026-07-02T23:15:00Z</t>
+          <t>2026-07-02T18:10:00Z</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>Hurston Waldrep</t>
+          <t>Jacob Misiorowski</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>694462</t>
+          <t>694819</t>
         </is>
       </c>
       <c r="K163" t="inlineStr">
@@ -45364,7 +45360,7 @@
         </is>
       </c>
       <c r="L163" t="n">
-        <v>26.4</v>
+        <v>26.3</v>
       </c>
       <c r="M163" t="inlineStr">
         <is>
@@ -45378,62 +45374,58 @@
       </c>
       <c r="O163" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P163" t="n">
-        <v>12.9</v>
+        <v>9</v>
       </c>
       <c r="Q163" t="n">
-        <v>9.699999999999999</v>
+        <v>14.1</v>
       </c>
       <c r="R163" t="n">
-        <v>30.9</v>
+        <v>47.6</v>
       </c>
       <c r="S163" t="n">
-        <v>71.7</v>
+        <v>52.4</v>
       </c>
       <c r="T163" t="n">
         <v>50</v>
       </c>
       <c r="U163" t="n">
-        <v>13.3</v>
+        <v>19.5</v>
       </c>
       <c r="V163" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W163" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X163" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y163" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z163" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W163" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X163" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y163" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z163" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA163" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB163" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB163" t="inlineStr"/>
       <c r="AC163" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -45458,7 +45450,7 @@
       </c>
       <c r="AI163" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ163" t="inlineStr">
@@ -45468,12 +45460,12 @@
       </c>
       <c r="AK163" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/24, 0 HR</t>
+          <t>Last 7 games: 5/20, 0 HR</t>
         </is>
       </c>
       <c r="AL163" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 1.3% barrel, 0.9 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 4.2% barrel, 5.9 HR allowed</t>
         </is>
       </c>
       <c r="AM163" t="inlineStr">
@@ -45483,104 +45475,112 @@
       </c>
       <c r="AN163" t="inlineStr">
         <is>
-          <t>3.68</t>
+          <t>2.96</t>
         </is>
       </c>
       <c r="AO163" t="inlineStr">
         <is>
-          <t>33.06</t>
+          <t>32.02</t>
         </is>
       </c>
       <c r="AP163" t="inlineStr">
         <is>
+          <t>86.22</t>
+        </is>
+      </c>
+      <c r="AQ163" t="inlineStr">
+        <is>
+          <t>97.186</t>
+        </is>
+      </c>
+      <c r="AR163" t="inlineStr">
+        <is>
+          <t>0.3284</t>
+        </is>
+      </c>
+      <c r="AS163" t="inlineStr">
+        <is>
+          <t>0.0885</t>
+        </is>
+      </c>
+      <c r="AT163" t="inlineStr">
+        <is>
+          <t>0.2584</t>
+        </is>
+      </c>
+      <c r="AU163" t="inlineStr">
+        <is>
+          <t>69.18</t>
+        </is>
+      </c>
+      <c r="AV163" t="inlineStr">
+        <is>
+          <t>4.49</t>
+        </is>
+      </c>
+      <c r="AW163" t="inlineStr">
+        <is>
+          <t>33.97</t>
+        </is>
+      </c>
+      <c r="AX163" t="inlineStr">
+        <is>
+          <t>18.84</t>
+        </is>
+      </c>
+      <c r="AY163" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
+      <c r="AZ163" t="inlineStr">
+        <is>
+          <t>0.0612</t>
+        </is>
+      </c>
+      <c r="BA163" t="inlineStr">
+        <is>
+          <t>4.19</t>
+        </is>
+      </c>
+      <c r="BB163" t="inlineStr">
+        <is>
+          <t>34.49</t>
+        </is>
+      </c>
+      <c r="BC163" t="inlineStr">
+        <is>
           <t>87.67</t>
         </is>
       </c>
-      <c r="AQ163" t="inlineStr">
-        <is>
-          <t>98.2909</t>
-        </is>
-      </c>
-      <c r="AR163" t="inlineStr">
-        <is>
-          <t>0.3337</t>
-        </is>
-      </c>
-      <c r="AS163" t="inlineStr">
-        <is>
-          <t>0.0818</t>
-        </is>
-      </c>
-      <c r="AT163" t="inlineStr">
-        <is>
-          <t>0.2972</t>
-        </is>
-      </c>
-      <c r="AU163" t="inlineStr">
-        <is>
-          <t>70.75</t>
-        </is>
-      </c>
-      <c r="AV163" t="inlineStr">
-        <is>
-          <t>12.4</t>
-        </is>
-      </c>
-      <c r="AW163" t="inlineStr">
-        <is>
-          <t>32.18</t>
-        </is>
-      </c>
-      <c r="AX163" t="inlineStr">
-        <is>
-          <t>19.29</t>
-        </is>
-      </c>
-      <c r="AY163" t="inlineStr">
-        <is>
-          <t>4.8</t>
-        </is>
-      </c>
-      <c r="AZ163" t="inlineStr">
-        <is>
-          <t>0.0939</t>
-        </is>
-      </c>
-      <c r="BA163" t="inlineStr">
-        <is>
-          <t>1.26</t>
-        </is>
-      </c>
-      <c r="BB163" t="inlineStr">
-        <is>
-          <t>40.09</t>
-        </is>
-      </c>
-      <c r="BC163" t="inlineStr">
-        <is>
-          <t>85.32</t>
-        </is>
-      </c>
       <c r="BD163" t="inlineStr">
         <is>
-          <t>0.2785</t>
+          <t>0.274</t>
         </is>
       </c>
       <c r="BE163" t="inlineStr">
         <is>
-          <t>0.0436</t>
+          <t>0.0912</t>
         </is>
       </c>
       <c r="BF163" t="inlineStr">
         <is>
-          <t>6.45</t>
-        </is>
-      </c>
-      <c r="BG163" t="inlineStr"/>
-      <c r="BH163" t="inlineStr"/>
+          <t>23.82</t>
+        </is>
+      </c>
+      <c r="BG163" t="inlineStr">
+        <is>
+          <t>In From RF</t>
+        </is>
+      </c>
+      <c r="BH163" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
       <c r="BI163" t="inlineStr">
         <is>
-          <t>Truist Park</t>
+          <t>American Family Field</t>
         </is>
       </c>
       <c r="BJ163" t="inlineStr"/>
@@ -45966,7 +45966,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>74</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -45999,7 +45999,7 @@
         <v>80</v>
       </c>
       <c r="U2" t="n">
-        <v>31.6</v>
+        <v>30.3</v>
       </c>
       <c r="V2" t="inlineStr">
         <is>
@@ -46056,7 +46056,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
@@ -46066,7 +46066,7 @@
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/24, 1 HR</t>
+          <t>Last 7 games: 5/25, 1 HR</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
@@ -51209,47 +51209,47 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>694192</t>
+          <t>650489</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Jackson Chourio</t>
+          <t>Willi Castro</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-07-02T18:10:00Z</t>
+          <t>2026-07-02T19:10:00Z</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Chase Burns</t>
+          <t>Ryan Gusto</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>695505</t>
+          <t>687473</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -51258,7 +51258,7 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>55.6</v>
+        <v>55.5</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
@@ -51272,26 +51272,26 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot</t>
+          <t>Good Environment, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P21" t="n">
-        <v>53.4</v>
+        <v>28.3</v>
       </c>
       <c r="Q21" t="n">
-        <v>37.9</v>
+        <v>50.8</v>
       </c>
       <c r="R21" t="n">
-        <v>47.6</v>
+        <v>81.7</v>
       </c>
       <c r="S21" t="n">
-        <v>100</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T21" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="U21" t="n">
-        <v>65.2</v>
+        <v>34.2</v>
       </c>
       <c r="V21" t="inlineStr">
         <is>
@@ -51305,7 +51305,7 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
@@ -51343,27 +51343,27 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>31</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 7/31, 1 HR</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.7% barrel, 9.2 HR allowed</t>
+          <t>switch hitter; pitcher baseline 9.8% barrel, 6.5 HR allowed</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
@@ -51373,112 +51373,112 @@
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>12.78</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>45.66</t>
+          <t>40.31</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>91.47</t>
+          <t>87.96</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>102.3936</t>
+          <t>100.1044</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>0.4603</t>
+          <t>0.3687</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
         <is>
-          <t>0.2077</t>
+          <t>0.1316</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>0.3308</t>
+          <t>0.3039</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
         <is>
-          <t>74.67</t>
+          <t>72.51</t>
         </is>
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>48.47</t>
+          <t>24.81</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>32.9</t>
+          <t>43.44</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>28.99</t>
+          <t>30.69</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>14.7</t>
+          <t>7.5</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>0.2224</t>
+          <t>0.1253</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>8.66</t>
+          <t>9.85</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>38.91</t>
+          <t>46.68</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>89.22</t>
+          <t>90.04</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>0.3511</t>
+          <t>0.4446</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
-          <t>0.1439</t>
+          <t>0.1711</t>
         </is>
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>27.82</t>
+          <t>26.75</t>
         </is>
       </c>
       <c r="BG21" t="inlineStr">
         <is>
-          <t>In From RF</t>
+          <t>Out To LF</t>
         </is>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>90</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
         <is>
-          <t>American Family Field</t>
+          <t>Coors Field</t>
         </is>
       </c>
       <c r="BJ21" t="inlineStr"/>

--- a/outputs/hr_rankings.xlsx
+++ b/outputs/hr_rankings.xlsx
@@ -3255,32 +3255,32 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>678246</t>
+          <t>681624</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Miguel Vargas</t>
+          <t>Andy Pages</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-07-02T22:40:00Z</t>
+          <t>2026-07-03T02:10:00Z</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -3290,12 +3290,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Slade Cecconi</t>
+          <t>Randy Vásquez</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>677944</t>
+          <t>681190</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -3318,17 +3318,17 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot</t>
+          <t>Pitcher Vulnerable, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>55.6</v>
+        <v>39.8</v>
       </c>
       <c r="Q11" t="n">
-        <v>47.9</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="R11" t="n">
-        <v>58.6</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S11" t="n">
         <v>100</v>
@@ -3337,7 +3337,7 @@
         <v>50</v>
       </c>
       <c r="U11" t="n">
-        <v>66.90000000000001</v>
+        <v>43.2</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
@@ -3389,7 +3389,7 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
@@ -3399,132 +3399,132 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 8/28, 1 HR</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 9.1% barrel, 15.6 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 12.6% barrel, 13.9 HR allowed</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>12.97</t>
+          <t>8.82</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>44.35</t>
+          <t>42.59</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>90.05</t>
+          <t>89.02</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>100.5013</t>
+          <t>100.2865</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>0.5071</t>
+          <t>0.449</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>0.2417</t>
+          <t>0.1819</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>0.3778</t>
+          <t>0.3342</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>73.12</t>
+          <t>72.88</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>34.94</t>
+          <t>25.42</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>42.81</t>
+          <t>35.31</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>35.52</t>
+          <t>28.65</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>18.1</t>
+          <t>19.3</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>0.2188</t>
+          <t>0.2023</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>9.05</t>
+          <t>12.58</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>44.69</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>89.18</t>
+          <t>91.06</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>0.4463</t>
+          <t>0.5377</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
-          <t>0.1842</t>
+          <t>0.242</t>
         </is>
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>25.89</t>
+          <t>29.3</t>
         </is>
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>74</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>Progressive Field</t>
+          <t>UNIQLO Field at Dodger Stadium</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr"/>
@@ -3535,32 +3535,32 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>681624</t>
+          <t>678246</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Andy Pages</t>
+          <t>Miguel Vargas</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-07-03T02:10:00Z</t>
+          <t>2026-07-02T22:40:00Z</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -3570,12 +3570,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Randy Vásquez</t>
+          <t>Slade Cecconi</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>681190</t>
+          <t>677944</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -3584,7 +3584,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>60.5</v>
+        <v>60.2</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -3598,17 +3598,17 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Pitcher Vulnerable, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>39.8</v>
+        <v>55.6</v>
       </c>
       <c r="Q12" t="n">
-        <v>70.90000000000001</v>
+        <v>47.9</v>
       </c>
       <c r="R12" t="n">
-        <v>64.59999999999999</v>
+        <v>58.6</v>
       </c>
       <c r="S12" t="n">
         <v>100</v>
@@ -3617,7 +3617,7 @@
         <v>50</v>
       </c>
       <c r="U12" t="n">
-        <v>43.2</v>
+        <v>60.7</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
@@ -3669,142 +3669,142 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Last 7 games: 8/28, 1 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 12.6% barrel, 13.9 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 9.1% barrel, 15.6 HR allowed</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>8.82</t>
+          <t>12.97</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>42.59</t>
+          <t>44.35</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>89.02</t>
+          <t>90.05</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>100.2865</t>
+          <t>100.5013</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.449</t>
+          <t>0.5071</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>0.1819</t>
+          <t>0.2417</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>0.3342</t>
+          <t>0.3778</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>72.88</t>
+          <t>73.12</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>25.42</t>
+          <t>34.94</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>35.31</t>
+          <t>42.81</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>28.65</t>
+          <t>35.52</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>19.3</t>
+          <t>18.1</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>0.2023</t>
+          <t>0.2188</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>12.58</t>
+          <t>9.05</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>44.69</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>91.06</t>
+          <t>89.18</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>0.5377</t>
+          <t>0.4463</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
-          <t>0.242</t>
+          <t>0.1842</t>
         </is>
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>29.3</t>
+          <t>25.89</t>
         </is>
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>91</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>UNIQLO Field at Dodger Stadium</t>
+          <t>Progressive Field</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr"/>
@@ -5227,47 +5227,47 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>696135</t>
+          <t>701538</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Kahlil Watson</t>
+          <t>Jackson Merrill</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-07-02T22:40:00Z</t>
+          <t>2026-07-03T02:10:00Z</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Davis Martin</t>
+          <t>Roki Sasaki</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>663436</t>
+          <t>808963</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -5276,7 +5276,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>58.9</v>
+        <v>58.8</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -5290,61 +5290,65 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>54.7</v>
+        <v>44.6</v>
       </c>
       <c r="Q18" t="n">
-        <v>40.7</v>
+        <v>57.8</v>
       </c>
       <c r="R18" t="n">
-        <v>58.6</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S18" t="n">
-        <v>94.90000000000001</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="T18" t="n">
         <v>80</v>
       </c>
       <c r="U18" t="n">
-        <v>36</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
+      <c r="Z18" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD18" t="inlineStr"/>
@@ -5361,12 +5365,12 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
@@ -5376,127 +5380,127 @@
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Contact streak: 9/25 over last 7 games</t>
+          <t>Last 7 games: 5/28, 0 HR</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.3% barrel, 10.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 11.2% barrel, 11.6 HR allowed</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>EV profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>14.3</t>
+          <t>10.48</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>42.9</t>
+          <t>45.49</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>92.8</t>
+          <t>89.84</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>100.2169</t>
+          <t>100.5071</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>0.454</t>
+          <t>0.434</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>0.214</t>
+          <t>0.1899</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>0.303</t>
+          <t>0.3176</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>72.98</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>25.4</t>
+          <t>27.95</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>35.7</t>
+          <t>37.7</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>27.89</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>10.4</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>0.143</t>
+          <t>0.1489</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>7.35</t>
+          <t>11.24</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>45.09</t>
+          <t>45.19</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>90.14</t>
+          <t>90.32</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>0.4076</t>
+          <t>0.4377</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
-          <t>0.1468</t>
+          <t>0.1943</t>
         </is>
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>22.01</t>
+          <t>28.98</t>
         </is>
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>74</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
         <is>
-          <t>Progressive Field</t>
+          <t>UNIQLO Field at Dodger Stadium</t>
         </is>
       </c>
       <c r="BJ18" t="inlineStr"/>
@@ -5507,47 +5511,47 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>701538</t>
+          <t>696135</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Jackson Merrill</t>
+          <t>Kahlil Watson</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-07-03T02:10:00Z</t>
+          <t>2026-07-02T22:40:00Z</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Roki Sasaki</t>
+          <t>Davis Martin</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>808963</t>
+          <t>663436</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -5556,7 +5560,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>58.8</v>
+        <v>58.7</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -5570,65 +5574,61 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P19" t="n">
-        <v>44.6</v>
+        <v>54.7</v>
       </c>
       <c r="Q19" t="n">
-        <v>57.8</v>
+        <v>40.7</v>
       </c>
       <c r="R19" t="n">
-        <v>64.59999999999999</v>
+        <v>58.6</v>
       </c>
       <c r="S19" t="n">
-        <v>92.09999999999999</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T19" t="n">
         <v>80</v>
       </c>
       <c r="U19" t="n">
-        <v>8.800000000000001</v>
+        <v>32</v>
       </c>
       <c r="V19" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD19" t="inlineStr"/>
@@ -5645,12 +5645,12 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
@@ -5660,127 +5660,127 @@
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/28, 0 HR</t>
+          <t>Contact streak: 7/21 over last 7 games</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 11.2% barrel, 11.6 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.3% barrel, 10.2 HR allowed</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>10.48</t>
+          <t>14.3</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>45.49</t>
+          <t>42.9</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>89.84</t>
+          <t>92.8</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>100.5071</t>
+          <t>100.2169</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>0.434</t>
+          <t>0.454</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
         <is>
-          <t>0.1899</t>
+          <t>0.214</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>0.3176</t>
+          <t>0.303</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>72.98</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>27.95</t>
+          <t>25.4</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>37.7</t>
+          <t>35.7</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>27.89</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>10.4</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>0.1489</t>
+          <t>0.143</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>11.24</t>
+          <t>7.35</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>45.19</t>
+          <t>45.09</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>90.32</t>
+          <t>90.14</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>0.4377</t>
+          <t>0.4076</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
-          <t>0.1943</t>
+          <t>0.1468</t>
         </is>
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>28.98</t>
+          <t>22.01</t>
         </is>
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>91</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
         <is>
-          <t>UNIQLO Field at Dodger Stadium</t>
+          <t>Progressive Field</t>
         </is>
       </c>
       <c r="BJ19" t="inlineStr"/>
@@ -10275,47 +10275,47 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>669242</t>
+          <t>803011</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Tommy Edman</t>
+          <t>Sam Antonacci</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-07-03T02:10:00Z</t>
+          <t>2026-07-02T22:40:00Z</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Randy Vásquez</t>
+          <t>Slade Cecconi</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>681190</t>
+          <t>677944</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -10324,7 +10324,7 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>52.2</v>
+        <v>52.3</v>
       </c>
       <c r="M36" t="inlineStr">
         <is>
@@ -10338,57 +10338,61 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P36" t="n">
-        <v>31.4</v>
+        <v>26.9</v>
       </c>
       <c r="Q36" t="n">
-        <v>69.5</v>
+        <v>47.9</v>
       </c>
       <c r="R36" t="n">
-        <v>64.59999999999999</v>
+        <v>58.6</v>
       </c>
       <c r="S36" t="n">
-        <v>44.8</v>
+        <v>93.2</v>
       </c>
       <c r="T36" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="U36" t="n">
-        <v>50.3</v>
+        <v>58</v>
       </c>
       <c r="V36" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W36" t="inlineStr"/>
-      <c r="X36" t="inlineStr"/>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="Y36" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB36" t="inlineStr"/>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD36" t="inlineStr"/>
@@ -10405,12 +10409,12 @@
       </c>
       <c r="AH36" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AI36" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ36" t="inlineStr">
@@ -10420,12 +10424,12 @@
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>Contact streak: 8/24 over last 7 games</t>
+          <t>Contact streak: 10/26 over last 7 games</t>
         </is>
       </c>
       <c r="AL36" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 12.6% barrel, 13.9 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.1% barrel, 15.6 HR allowed</t>
         </is>
       </c>
       <c r="AM36" t="inlineStr">
@@ -10435,112 +10439,112 @@
       </c>
       <c r="AN36" t="inlineStr">
         <is>
-          <t>7.93</t>
+          <t>6.9</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>38.22</t>
+          <t>36.8</t>
         </is>
       </c>
       <c r="AP36" t="inlineStr">
         <is>
-          <t>89.35</t>
+          <t>87.9</t>
         </is>
       </c>
       <c r="AQ36" t="inlineStr">
         <is>
-          <t>100.1884</t>
+          <t>98.3656</t>
         </is>
       </c>
       <c r="AR36" t="inlineStr">
         <is>
-          <t>0.446</t>
+          <t>0.441</t>
         </is>
       </c>
       <c r="AS36" t="inlineStr">
         <is>
-          <t>0.1398</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr">
         <is>
-          <t>0.3588</t>
+          <t>0.374</t>
         </is>
       </c>
       <c r="AU36" t="inlineStr">
         <is>
-          <t>70.62</t>
+          <t>70.3</t>
         </is>
       </c>
       <c r="AV36" t="inlineStr">
         <is>
-          <t>12.91</t>
+          <t>9.4</t>
         </is>
       </c>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>43.44</t>
+          <t>33.5</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>22.65</t>
+          <t>21.5</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>0.1668</t>
+          <t>0.132</t>
         </is>
       </c>
       <c r="BA36" t="inlineStr">
         <is>
-          <t>12.58</t>
+          <t>9.05</t>
         </is>
       </c>
       <c r="BB36" t="inlineStr">
         <is>
-          <t>44.69</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="BC36" t="inlineStr">
         <is>
-          <t>91.06</t>
+          <t>89.18</t>
         </is>
       </c>
       <c r="BD36" t="inlineStr">
         <is>
-          <t>0.5377</t>
+          <t>0.4463</t>
         </is>
       </c>
       <c r="BE36" t="inlineStr">
         <is>
-          <t>0.242</t>
+          <t>0.1842</t>
         </is>
       </c>
       <c r="BF36" t="inlineStr">
         <is>
-          <t>29.3</t>
+          <t>25.89</t>
         </is>
       </c>
       <c r="BG36" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>91</t>
         </is>
       </c>
       <c r="BI36" t="inlineStr">
         <is>
-          <t>UNIQLO Field at Dodger Stadium</t>
+          <t>Progressive Field</t>
         </is>
       </c>
       <c r="BJ36" t="inlineStr"/>
@@ -10551,47 +10555,47 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>803011</t>
+          <t>669242</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Sam Antonacci</t>
+          <t>Tommy Edman</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-07-02T22:40:00Z</t>
+          <t>2026-07-03T02:10:00Z</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Slade Cecconi</t>
+          <t>Randy Vásquez</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>677944</t>
+          <t>681190</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -10600,7 +10604,7 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>51.8</v>
+        <v>52.2</v>
       </c>
       <c r="M37" t="inlineStr">
         <is>
@@ -10614,61 +10618,57 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P37" t="n">
-        <v>26.9</v>
+        <v>31.4</v>
       </c>
       <c r="Q37" t="n">
-        <v>47.9</v>
+        <v>69.5</v>
       </c>
       <c r="R37" t="n">
-        <v>58.6</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S37" t="n">
-        <v>93.2</v>
+        <v>44.8</v>
       </c>
       <c r="T37" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="U37" t="n">
-        <v>48.5</v>
+        <v>50.3</v>
       </c>
       <c r="V37" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W37" t="inlineStr">
+      <c r="W37" t="inlineStr"/>
+      <c r="X37" t="inlineStr"/>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y37" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB37" t="inlineStr"/>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>not found on RotoWire</t>
+        </is>
+      </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD37" t="inlineStr"/>
@@ -10685,12 +10685,12 @@
       </c>
       <c r="AH37" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI37" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ37" t="inlineStr">
@@ -10700,12 +10700,12 @@
       </c>
       <c r="AK37" t="inlineStr">
         <is>
-          <t>Contact streak: 9/28 over last 7 games</t>
+          <t>Contact streak: 8/24 over last 7 games</t>
         </is>
       </c>
       <c r="AL37" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 9.1% barrel, 15.6 HR allowed</t>
+          <t>switch hitter; pitcher baseline 12.6% barrel, 13.9 HR allowed</t>
         </is>
       </c>
       <c r="AM37" t="inlineStr">
@@ -10715,112 +10715,112 @@
       </c>
       <c r="AN37" t="inlineStr">
         <is>
-          <t>6.9</t>
+          <t>7.93</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>36.8</t>
+          <t>38.22</t>
         </is>
       </c>
       <c r="AP37" t="inlineStr">
         <is>
-          <t>87.9</t>
+          <t>89.35</t>
         </is>
       </c>
       <c r="AQ37" t="inlineStr">
         <is>
-          <t>98.3656</t>
+          <t>100.1884</t>
         </is>
       </c>
       <c r="AR37" t="inlineStr">
         <is>
-          <t>0.441</t>
+          <t>0.446</t>
         </is>
       </c>
       <c r="AS37" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>0.1398</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr">
         <is>
-          <t>0.374</t>
+          <t>0.3588</t>
         </is>
       </c>
       <c r="AU37" t="inlineStr">
         <is>
-          <t>70.3</t>
+          <t>70.62</t>
         </is>
       </c>
       <c r="AV37" t="inlineStr">
         <is>
-          <t>9.4</t>
+          <t>12.91</t>
         </is>
       </c>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>33.5</t>
+          <t>43.44</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>21.5</t>
+          <t>22.65</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>4.6</t>
         </is>
       </c>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>0.132</t>
+          <t>0.1668</t>
         </is>
       </c>
       <c r="BA37" t="inlineStr">
         <is>
-          <t>9.05</t>
+          <t>12.58</t>
         </is>
       </c>
       <c r="BB37" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>44.69</t>
         </is>
       </c>
       <c r="BC37" t="inlineStr">
         <is>
-          <t>89.18</t>
+          <t>91.06</t>
         </is>
       </c>
       <c r="BD37" t="inlineStr">
         <is>
-          <t>0.4463</t>
+          <t>0.5377</t>
         </is>
       </c>
       <c r="BE37" t="inlineStr">
         <is>
-          <t>0.1842</t>
+          <t>0.242</t>
         </is>
       </c>
       <c r="BF37" t="inlineStr">
         <is>
-          <t>25.89</t>
+          <t>29.3</t>
         </is>
       </c>
       <c r="BG37" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>74</t>
         </is>
       </c>
       <c r="BI37" t="inlineStr">
         <is>
-          <t>Progressive Field</t>
+          <t>UNIQLO Field at Dodger Stadium</t>
         </is>
       </c>
       <c r="BJ37" t="inlineStr"/>
@@ -11951,47 +11951,47 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>687263</t>
+          <t>691019</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Zach Neto</t>
+          <t>Kyle Teel</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-07-03T01:40:00Z</t>
+          <t>2026-07-02T22:40:00Z</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Bryce Miller</t>
+          <t>Slade Cecconi</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>682243</t>
+          <t>677944</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -12014,26 +12014,26 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P42" t="n">
-        <v>50.8</v>
+        <v>23.2</v>
       </c>
       <c r="Q42" t="n">
-        <v>35.9</v>
+        <v>47.9</v>
       </c>
       <c r="R42" t="n">
-        <v>38.9</v>
+        <v>58.6</v>
       </c>
       <c r="S42" t="n">
-        <v>93.2</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T42" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U42" t="n">
-        <v>36.3</v>
+        <v>39.5</v>
       </c>
       <c r="V42" t="inlineStr">
         <is>
@@ -12047,7 +12047,7 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y42" t="inlineStr">
@@ -12090,7 +12090,7 @@
       </c>
       <c r="AI42" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ42" t="inlineStr">
@@ -12100,127 +12100,127 @@
       </c>
       <c r="AK42" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/25, 1 HR</t>
+          <t>Last 7 games: 6/23, 1 HR</t>
         </is>
       </c>
       <c r="AL42" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.3% barrel, 10.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.1% barrel, 15.6 HR allowed</t>
         </is>
       </c>
       <c r="AM42" t="inlineStr">
         <is>
-          <t>fly-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN42" t="inlineStr">
         <is>
-          <t>13.58</t>
+          <t>7.85</t>
         </is>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>41.42</t>
+          <t>41.31</t>
         </is>
       </c>
       <c r="AP42" t="inlineStr">
         <is>
-          <t>90.16</t>
+          <t>84.59</t>
         </is>
       </c>
       <c r="AQ42" t="inlineStr">
         <is>
-          <t>100.1597</t>
+          <t>98.2797</t>
         </is>
       </c>
       <c r="AR42" t="inlineStr">
         <is>
-          <t>0.4362</t>
+          <t>0.3397</t>
         </is>
       </c>
       <c r="AS42" t="inlineStr">
         <is>
-          <t>0.2202</t>
+          <t>0.1202</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr">
         <is>
-          <t>0.3223</t>
+          <t>0.3027</t>
         </is>
       </c>
       <c r="AU42" t="inlineStr">
         <is>
-          <t>70.98</t>
+          <t>71.95</t>
         </is>
       </c>
       <c r="AV42" t="inlineStr">
         <is>
-          <t>11.55</t>
+          <t>28.96</t>
         </is>
       </c>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>49.44</t>
+          <t>32.14</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>37.13</t>
+          <t>23.92</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr">
         <is>
-          <t>20.4</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>0.2233</t>
+          <t>0.1219</t>
         </is>
       </c>
       <c r="BA42" t="inlineStr">
         <is>
-          <t>8.28</t>
+          <t>9.05</t>
         </is>
       </c>
       <c r="BB42" t="inlineStr">
         <is>
-          <t>34.11</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="BC42" t="inlineStr">
         <is>
-          <t>87.92</t>
+          <t>89.18</t>
         </is>
       </c>
       <c r="BD42" t="inlineStr">
         <is>
-          <t>0.3755</t>
+          <t>0.4463</t>
         </is>
       </c>
       <c r="BE42" t="inlineStr">
         <is>
-          <t>0.1603</t>
+          <t>0.1842</t>
         </is>
       </c>
       <c r="BF42" t="inlineStr">
         <is>
-          <t>30.6</t>
+          <t>25.89</t>
         </is>
       </c>
       <c r="BG42" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH42" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>91</t>
         </is>
       </c>
       <c r="BI42" t="inlineStr">
         <is>
-          <t>T-Mobile Park</t>
+          <t>Progressive Field</t>
         </is>
       </c>
       <c r="BJ42" t="inlineStr"/>
@@ -12231,47 +12231,47 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>691019</t>
+          <t>687263</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Kyle Teel</t>
+          <t>Zach Neto</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-07-02T22:40:00Z</t>
+          <t>2026-07-03T01:40:00Z</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Slade Cecconi</t>
+          <t>Bryce Miller</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>677944</t>
+          <t>682243</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -12280,7 +12280,7 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>50.4</v>
+        <v>50.6</v>
       </c>
       <c r="M43" t="inlineStr">
         <is>
@@ -12294,26 +12294,26 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P43" t="n">
-        <v>23.2</v>
+        <v>50.8</v>
       </c>
       <c r="Q43" t="n">
-        <v>47.9</v>
+        <v>35.9</v>
       </c>
       <c r="R43" t="n">
-        <v>58.6</v>
+        <v>38.9</v>
       </c>
       <c r="S43" t="n">
-        <v>96.59999999999999</v>
+        <v>93.2</v>
       </c>
       <c r="T43" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U43" t="n">
-        <v>34.9</v>
+        <v>36.3</v>
       </c>
       <c r="V43" t="inlineStr">
         <is>
@@ -12327,7 +12327,7 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y43" t="inlineStr">
@@ -12370,7 +12370,7 @@
       </c>
       <c r="AI43" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ43" t="inlineStr">
@@ -12380,127 +12380,127 @@
       </c>
       <c r="AK43" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/26, 1 HR</t>
+          <t>Last 7 games: 6/25, 1 HR</t>
         </is>
       </c>
       <c r="AL43" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 9.1% barrel, 15.6 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.3% barrel, 10.0 HR allowed</t>
         </is>
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>fly-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN43" t="inlineStr">
         <is>
-          <t>7.85</t>
+          <t>13.58</t>
         </is>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>41.31</t>
+          <t>41.42</t>
         </is>
       </c>
       <c r="AP43" t="inlineStr">
         <is>
-          <t>84.59</t>
+          <t>90.16</t>
         </is>
       </c>
       <c r="AQ43" t="inlineStr">
         <is>
-          <t>98.2797</t>
+          <t>100.1597</t>
         </is>
       </c>
       <c r="AR43" t="inlineStr">
         <is>
-          <t>0.3397</t>
+          <t>0.4362</t>
         </is>
       </c>
       <c r="AS43" t="inlineStr">
         <is>
-          <t>0.1202</t>
+          <t>0.2202</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr">
         <is>
-          <t>0.3027</t>
+          <t>0.3223</t>
         </is>
       </c>
       <c r="AU43" t="inlineStr">
         <is>
-          <t>71.95</t>
+          <t>70.98</t>
         </is>
       </c>
       <c r="AV43" t="inlineStr">
         <is>
-          <t>28.96</t>
+          <t>11.55</t>
         </is>
       </c>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>32.14</t>
+          <t>49.44</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>23.92</t>
+          <t>37.13</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>20.4</t>
         </is>
       </c>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>0.1219</t>
+          <t>0.2233</t>
         </is>
       </c>
       <c r="BA43" t="inlineStr">
         <is>
-          <t>9.05</t>
+          <t>8.28</t>
         </is>
       </c>
       <c r="BB43" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>34.11</t>
         </is>
       </c>
       <c r="BC43" t="inlineStr">
         <is>
-          <t>89.18</t>
+          <t>87.92</t>
         </is>
       </c>
       <c r="BD43" t="inlineStr">
         <is>
-          <t>0.4463</t>
+          <t>0.3755</t>
         </is>
       </c>
       <c r="BE43" t="inlineStr">
         <is>
-          <t>0.1842</t>
+          <t>0.1603</t>
         </is>
       </c>
       <c r="BF43" t="inlineStr">
         <is>
-          <t>25.89</t>
+          <t>30.6</t>
         </is>
       </c>
       <c r="BG43" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH43" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI43" t="inlineStr">
         <is>
-          <t>Progressive Field</t>
+          <t>T-Mobile Park</t>
         </is>
       </c>
       <c r="BJ43" t="inlineStr"/>
@@ -21763,47 +21763,47 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>671056</t>
+          <t>677587</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Iván Herrera</t>
+          <t>Brayan Rocchio</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-07-02T23:15:00Z</t>
+          <t>2026-07-02T22:40:00Z</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Hurston Waldrep</t>
+          <t>Davis Martin</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>694462</t>
+          <t>663436</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -21826,26 +21826,26 @@
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P77" t="n">
-        <v>37.3</v>
+        <v>12.8</v>
       </c>
       <c r="Q77" t="n">
-        <v>9.699999999999999</v>
+        <v>39.6</v>
       </c>
       <c r="R77" t="n">
-        <v>61.9</v>
+        <v>58.6</v>
       </c>
       <c r="S77" t="n">
-        <v>100</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T77" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="U77" t="n">
-        <v>0</v>
+        <v>22.9</v>
       </c>
       <c r="V77" t="inlineStr">
         <is>
@@ -21859,7 +21859,7 @@
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y77" t="inlineStr">
@@ -21897,12 +21897,12 @@
       </c>
       <c r="AH77" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI77" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ77" t="inlineStr">
@@ -21912,12 +21912,12 @@
       </c>
       <c r="AK77" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/24, 0 HR</t>
+          <t>Last 7 games: 6/22, 0 HR</t>
         </is>
       </c>
       <c r="AL77" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 1.3% barrel, 0.9 HR allowed</t>
+          <t>switch hitter; pitcher baseline 7.3% barrel, 10.2 HR allowed</t>
         </is>
       </c>
       <c r="AM77" t="inlineStr">
@@ -21927,97 +21927,97 @@
       </c>
       <c r="AN77" t="inlineStr">
         <is>
-          <t>7.95</t>
+          <t>2.74</t>
         </is>
       </c>
       <c r="AO77" t="inlineStr">
         <is>
-          <t>43.15</t>
+          <t>32.35</t>
         </is>
       </c>
       <c r="AP77" t="inlineStr">
         <is>
-          <t>89.94</t>
+          <t>86.81</t>
         </is>
       </c>
       <c r="AQ77" t="inlineStr">
         <is>
-          <t>101.3798</t>
+          <t>97.4049</t>
         </is>
       </c>
       <c r="AR77" t="inlineStr">
         <is>
-          <t>0.4294</t>
+          <t>0.3538</t>
         </is>
       </c>
       <c r="AS77" t="inlineStr">
         <is>
-          <t>0.167</t>
+          <t>0.1018</t>
         </is>
       </c>
       <c r="AT77" t="inlineStr">
         <is>
-          <t>0.3633</t>
+          <t>0.3027</t>
         </is>
       </c>
       <c r="AU77" t="inlineStr">
         <is>
-          <t>74.26</t>
+          <t>69.93</t>
         </is>
       </c>
       <c r="AV77" t="inlineStr">
         <is>
-          <t>45.18</t>
+          <t>7.08</t>
         </is>
       </c>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>37.03</t>
+          <t>43.57</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>19.66</t>
+          <t>23.48</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr">
         <is>
-          <t>12.7</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>0.1604</t>
+          <t>0.1112</t>
         </is>
       </c>
       <c r="BA77" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>7.35</t>
         </is>
       </c>
       <c r="BB77" t="inlineStr">
         <is>
-          <t>40.09</t>
+          <t>45.09</t>
         </is>
       </c>
       <c r="BC77" t="inlineStr">
         <is>
-          <t>85.32</t>
+          <t>90.14</t>
         </is>
       </c>
       <c r="BD77" t="inlineStr">
         <is>
-          <t>0.2785</t>
+          <t>0.4076</t>
         </is>
       </c>
       <c r="BE77" t="inlineStr">
         <is>
-          <t>0.0436</t>
+          <t>0.1468</t>
         </is>
       </c>
       <c r="BF77" t="inlineStr">
         <is>
-          <t>6.45</t>
+          <t>22.01</t>
         </is>
       </c>
       <c r="BG77" t="inlineStr">
@@ -22027,12 +22027,12 @@
       </c>
       <c r="BH77" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>91</t>
         </is>
       </c>
       <c r="BI77" t="inlineStr">
         <is>
-          <t>Truist Park</t>
+          <t>Progressive Field</t>
         </is>
       </c>
       <c r="BJ77" t="inlineStr"/>
@@ -22043,47 +22043,47 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>677587</t>
+          <t>671056</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Brayan Rocchio</t>
+          <t>Iván Herrera</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-07-02T22:40:00Z</t>
+          <t>2026-07-02T23:15:00Z</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Davis Martin</t>
+          <t>Hurston Waldrep</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>663436</t>
+          <t>694462</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -22092,7 +22092,7 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>42.4</v>
+        <v>42.5</v>
       </c>
       <c r="M78" t="inlineStr">
         <is>
@@ -22106,26 +22106,26 @@
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P78" t="n">
-        <v>12.8</v>
+        <v>37.3</v>
       </c>
       <c r="Q78" t="n">
-        <v>39.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="R78" t="n">
-        <v>58.6</v>
+        <v>61.9</v>
       </c>
       <c r="S78" t="n">
-        <v>86.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="T78" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U78" t="n">
-        <v>20.9</v>
+        <v>0</v>
       </c>
       <c r="V78" t="inlineStr">
         <is>
@@ -22139,7 +22139,7 @@
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y78" t="inlineStr">
@@ -22177,12 +22177,12 @@
       </c>
       <c r="AH78" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI78" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ78" t="inlineStr">
@@ -22192,12 +22192,12 @@
       </c>
       <c r="AK78" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/27, 0 HR</t>
+          <t>Last 7 games: 2/24, 0 HR</t>
         </is>
       </c>
       <c r="AL78" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 7.3% barrel, 10.2 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 1.3% barrel, 0.9 HR allowed</t>
         </is>
       </c>
       <c r="AM78" t="inlineStr">
@@ -22207,97 +22207,97 @@
       </c>
       <c r="AN78" t="inlineStr">
         <is>
-          <t>2.74</t>
+          <t>7.95</t>
         </is>
       </c>
       <c r="AO78" t="inlineStr">
         <is>
-          <t>32.35</t>
+          <t>43.15</t>
         </is>
       </c>
       <c r="AP78" t="inlineStr">
         <is>
-          <t>86.81</t>
+          <t>89.94</t>
         </is>
       </c>
       <c r="AQ78" t="inlineStr">
         <is>
-          <t>97.4049</t>
+          <t>101.3798</t>
         </is>
       </c>
       <c r="AR78" t="inlineStr">
         <is>
-          <t>0.3538</t>
+          <t>0.4294</t>
         </is>
       </c>
       <c r="AS78" t="inlineStr">
         <is>
-          <t>0.1018</t>
+          <t>0.167</t>
         </is>
       </c>
       <c r="AT78" t="inlineStr">
         <is>
-          <t>0.3027</t>
+          <t>0.3633</t>
         </is>
       </c>
       <c r="AU78" t="inlineStr">
         <is>
-          <t>69.93</t>
+          <t>74.26</t>
         </is>
       </c>
       <c r="AV78" t="inlineStr">
         <is>
-          <t>7.08</t>
+          <t>45.18</t>
         </is>
       </c>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>43.57</t>
+          <t>37.03</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>23.48</t>
+          <t>19.66</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>12.7</t>
         </is>
       </c>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>0.1112</t>
+          <t>0.1604</t>
         </is>
       </c>
       <c r="BA78" t="inlineStr">
         <is>
-          <t>7.35</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="BB78" t="inlineStr">
         <is>
-          <t>45.09</t>
+          <t>40.09</t>
         </is>
       </c>
       <c r="BC78" t="inlineStr">
         <is>
-          <t>90.14</t>
+          <t>85.32</t>
         </is>
       </c>
       <c r="BD78" t="inlineStr">
         <is>
-          <t>0.4076</t>
+          <t>0.2785</t>
         </is>
       </c>
       <c r="BE78" t="inlineStr">
         <is>
-          <t>0.1468</t>
+          <t>0.0436</t>
         </is>
       </c>
       <c r="BF78" t="inlineStr">
         <is>
-          <t>22.01</t>
+          <t>6.45</t>
         </is>
       </c>
       <c r="BG78" t="inlineStr">
@@ -22307,12 +22307,12 @@
       </c>
       <c r="BH78" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>95</t>
         </is>
       </c>
       <c r="BI78" t="inlineStr">
         <is>
-          <t>Progressive Field</t>
+          <t>Truist Park</t>
         </is>
       </c>
       <c r="BJ78" t="inlineStr"/>
@@ -23862,7 +23862,7 @@
       </c>
       <c r="AI84" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AJ84" t="inlineStr">
@@ -23872,7 +23872,7 @@
       </c>
       <c r="AK84" t="inlineStr">
         <is>
-          <t>Last 7 games: 1/15, 0 HR</t>
+          <t>Last 7 games: 1/14, 0 HR</t>
         </is>
       </c>
       <c r="AL84" t="inlineStr">
@@ -33849,32 +33849,32 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>678246</t>
+          <t>681624</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Miguel Vargas</t>
+          <t>Andy Pages</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-07-02T22:40:00Z</t>
+          <t>2026-07-03T02:10:00Z</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -33884,12 +33884,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Slade Cecconi</t>
+          <t>Randy Vásquez</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>677944</t>
+          <t>681190</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -33912,17 +33912,17 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot</t>
+          <t>Pitcher Vulnerable, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>55.6</v>
+        <v>39.8</v>
       </c>
       <c r="Q11" t="n">
-        <v>47.9</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="R11" t="n">
-        <v>58.6</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S11" t="n">
         <v>100</v>
@@ -33931,7 +33931,7 @@
         <v>50</v>
       </c>
       <c r="U11" t="n">
-        <v>66.90000000000001</v>
+        <v>43.2</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
@@ -33983,7 +33983,7 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
@@ -33993,132 +33993,132 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 8/28, 1 HR</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 9.1% barrel, 15.6 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 12.6% barrel, 13.9 HR allowed</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>12.97</t>
+          <t>8.82</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>44.35</t>
+          <t>42.59</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>90.05</t>
+          <t>89.02</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>100.5013</t>
+          <t>100.2865</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>0.5071</t>
+          <t>0.449</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>0.2417</t>
+          <t>0.1819</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>0.3778</t>
+          <t>0.3342</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>73.12</t>
+          <t>72.88</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>34.94</t>
+          <t>25.42</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>42.81</t>
+          <t>35.31</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>35.52</t>
+          <t>28.65</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>18.1</t>
+          <t>19.3</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>0.2188</t>
+          <t>0.2023</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>9.05</t>
+          <t>12.58</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>44.69</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>89.18</t>
+          <t>91.06</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>0.4463</t>
+          <t>0.5377</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
-          <t>0.1842</t>
+          <t>0.242</t>
         </is>
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>25.89</t>
+          <t>29.3</t>
         </is>
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>74</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>Progressive Field</t>
+          <t>UNIQLO Field at Dodger Stadium</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr"/>
@@ -34129,32 +34129,32 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>681624</t>
+          <t>678246</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Andy Pages</t>
+          <t>Miguel Vargas</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-07-03T02:10:00Z</t>
+          <t>2026-07-02T22:40:00Z</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -34164,12 +34164,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Randy Vásquez</t>
+          <t>Slade Cecconi</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>681190</t>
+          <t>677944</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -34178,7 +34178,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>60.5</v>
+        <v>60.2</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -34192,17 +34192,17 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Pitcher Vulnerable, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>39.8</v>
+        <v>55.6</v>
       </c>
       <c r="Q12" t="n">
-        <v>70.90000000000001</v>
+        <v>47.9</v>
       </c>
       <c r="R12" t="n">
-        <v>64.59999999999999</v>
+        <v>58.6</v>
       </c>
       <c r="S12" t="n">
         <v>100</v>
@@ -34211,7 +34211,7 @@
         <v>50</v>
       </c>
       <c r="U12" t="n">
-        <v>43.2</v>
+        <v>60.7</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
@@ -34263,142 +34263,142 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Last 7 games: 8/28, 1 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 12.6% barrel, 13.9 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 9.1% barrel, 15.6 HR allowed</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>8.82</t>
+          <t>12.97</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>42.59</t>
+          <t>44.35</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>89.02</t>
+          <t>90.05</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>100.2865</t>
+          <t>100.5013</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.449</t>
+          <t>0.5071</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>0.1819</t>
+          <t>0.2417</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>0.3342</t>
+          <t>0.3778</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>72.88</t>
+          <t>73.12</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>25.42</t>
+          <t>34.94</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>35.31</t>
+          <t>42.81</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>28.65</t>
+          <t>35.52</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>19.3</t>
+          <t>18.1</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>0.2023</t>
+          <t>0.2188</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>12.58</t>
+          <t>9.05</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>44.69</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>91.06</t>
+          <t>89.18</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>0.5377</t>
+          <t>0.4463</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
-          <t>0.242</t>
+          <t>0.1842</t>
         </is>
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>29.3</t>
+          <t>25.89</t>
         </is>
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>91</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>UNIQLO Field at Dodger Stadium</t>
+          <t>Progressive Field</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr"/>
@@ -35821,47 +35821,47 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>696135</t>
+          <t>701538</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Kahlil Watson</t>
+          <t>Jackson Merrill</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-07-02T22:40:00Z</t>
+          <t>2026-07-03T02:10:00Z</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Davis Martin</t>
+          <t>Roki Sasaki</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>663436</t>
+          <t>808963</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -35870,7 +35870,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>58.9</v>
+        <v>58.8</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -35884,61 +35884,65 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>54.7</v>
+        <v>44.6</v>
       </c>
       <c r="Q18" t="n">
-        <v>40.7</v>
+        <v>57.8</v>
       </c>
       <c r="R18" t="n">
-        <v>58.6</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S18" t="n">
-        <v>94.90000000000001</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="T18" t="n">
         <v>80</v>
       </c>
       <c r="U18" t="n">
-        <v>36</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
+      <c r="Z18" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD18" t="inlineStr"/>
@@ -35955,12 +35959,12 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
@@ -35970,127 +35974,127 @@
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Contact streak: 9/25 over last 7 games</t>
+          <t>Last 7 games: 5/28, 0 HR</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.3% barrel, 10.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 11.2% barrel, 11.6 HR allowed</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>EV profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>14.3</t>
+          <t>10.48</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>42.9</t>
+          <t>45.49</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>92.8</t>
+          <t>89.84</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>100.2169</t>
+          <t>100.5071</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>0.454</t>
+          <t>0.434</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>0.214</t>
+          <t>0.1899</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>0.303</t>
+          <t>0.3176</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>72.98</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>25.4</t>
+          <t>27.95</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>35.7</t>
+          <t>37.7</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>27.89</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>10.4</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>0.143</t>
+          <t>0.1489</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>7.35</t>
+          <t>11.24</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>45.09</t>
+          <t>45.19</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>90.14</t>
+          <t>90.32</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>0.4076</t>
+          <t>0.4377</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
-          <t>0.1468</t>
+          <t>0.1943</t>
         </is>
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>22.01</t>
+          <t>28.98</t>
         </is>
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>74</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
         <is>
-          <t>Progressive Field</t>
+          <t>UNIQLO Field at Dodger Stadium</t>
         </is>
       </c>
       <c r="BJ18" t="inlineStr"/>
@@ -36101,47 +36105,47 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>701538</t>
+          <t>696135</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Jackson Merrill</t>
+          <t>Kahlil Watson</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-07-03T02:10:00Z</t>
+          <t>2026-07-02T22:40:00Z</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Roki Sasaki</t>
+          <t>Davis Martin</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>808963</t>
+          <t>663436</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -36150,7 +36154,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>58.8</v>
+        <v>58.7</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -36164,65 +36168,61 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P19" t="n">
-        <v>44.6</v>
+        <v>54.7</v>
       </c>
       <c r="Q19" t="n">
-        <v>57.8</v>
+        <v>40.7</v>
       </c>
       <c r="R19" t="n">
-        <v>64.59999999999999</v>
+        <v>58.6</v>
       </c>
       <c r="S19" t="n">
-        <v>92.09999999999999</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T19" t="n">
         <v>80</v>
       </c>
       <c r="U19" t="n">
-        <v>8.800000000000001</v>
+        <v>32</v>
       </c>
       <c r="V19" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD19" t="inlineStr"/>
@@ -36239,12 +36239,12 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
@@ -36254,127 +36254,127 @@
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/28, 0 HR</t>
+          <t>Contact streak: 7/21 over last 7 games</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 11.2% barrel, 11.6 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.3% barrel, 10.2 HR allowed</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>10.48</t>
+          <t>14.3</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>45.49</t>
+          <t>42.9</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>89.84</t>
+          <t>92.8</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>100.5071</t>
+          <t>100.2169</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>0.434</t>
+          <t>0.454</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
         <is>
-          <t>0.1899</t>
+          <t>0.214</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>0.3176</t>
+          <t>0.303</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>72.98</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>27.95</t>
+          <t>25.4</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>37.7</t>
+          <t>35.7</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>27.89</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>10.4</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>0.1489</t>
+          <t>0.143</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>11.24</t>
+          <t>7.35</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>45.19</t>
+          <t>45.09</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>90.32</t>
+          <t>90.14</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>0.4377</t>
+          <t>0.4076</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
-          <t>0.1943</t>
+          <t>0.1468</t>
         </is>
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>28.98</t>
+          <t>22.01</t>
         </is>
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>91</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
         <is>
-          <t>UNIQLO Field at Dodger Stadium</t>
+          <t>Progressive Field</t>
         </is>
       </c>
       <c r="BJ19" t="inlineStr"/>

--- a/outputs/hr_rankings.xlsx
+++ b/outputs/hr_rankings.xlsx
@@ -3008,7 +3008,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>58.3</v>
+        <v>58.2</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -3041,7 +3041,7 @@
         <v>78</v>
       </c>
       <c r="U10" t="n">
-        <v>57.8</v>
+        <v>56.2</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
@@ -3098,7 +3098,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
@@ -6921,7 +6921,7 @@
         <v>50</v>
       </c>
       <c r="U24" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="V24" t="inlineStr">
         <is>
@@ -6978,7 +6978,7 @@
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ24" t="inlineStr">
@@ -6988,7 +6988,7 @@
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/24, 0 HR</t>
+          <t>Last 7 games: 3/25, 0 HR</t>
         </is>
       </c>
       <c r="AL24" t="inlineStr">
@@ -9891,47 +9891,47 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>605141</t>
+          <t>521692</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Mookie Betts</t>
+          <t>Salvador Perez</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-07-07T02:10:00Z</t>
+          <t>2026-07-06T18:10:00Z</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Kyle Freeland</t>
+          <t>Cristopher Sánchez</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>607536</t>
+          <t>650911</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -9940,7 +9940,7 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>51.2</v>
+        <v>51.4</v>
       </c>
       <c r="M35" t="inlineStr">
         <is>
@@ -9954,62 +9954,58 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P35" t="n">
-        <v>35</v>
+        <v>42.2</v>
       </c>
       <c r="Q35" t="n">
-        <v>59.9</v>
+        <v>32.7</v>
       </c>
       <c r="R35" t="n">
-        <v>27.6</v>
+        <v>47.2</v>
       </c>
       <c r="S35" t="n">
-        <v>90.40000000000001</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T35" t="n">
         <v>78</v>
       </c>
       <c r="U35" t="n">
-        <v>28.6</v>
+        <v>40.7</v>
       </c>
       <c r="V35" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W35" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y35" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr"/>
       <c r="AC35" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -10029,134 +10025,142 @@
       </c>
       <c r="AH35" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI35" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
         <is>
-          <t>Last 7 games: 9/29, 0 HR</t>
+          <t>Last 7 games: 7/26, 1 HR</t>
         </is>
       </c>
       <c r="AL35" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 10.2% barrel, 17.8 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.5% barrel, 9.2 HR allowed</t>
         </is>
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN35" t="inlineStr">
         <is>
-          <t>7.46</t>
+          <t>10.74</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>37.97</t>
+          <t>42.71</t>
         </is>
       </c>
       <c r="AP35" t="inlineStr">
         <is>
-          <t>90.22</t>
+          <t>89.09</t>
         </is>
       </c>
       <c r="AQ35" t="inlineStr">
         <is>
-          <t>98.6577</t>
+          <t>100.5081</t>
         </is>
       </c>
       <c r="AR35" t="inlineStr">
         <is>
-          <t>0.4388</t>
+          <t>0.4234</t>
         </is>
       </c>
       <c r="AS35" t="inlineStr">
         <is>
-          <t>0.1616</t>
+          <t>0.1883</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr">
         <is>
-          <t>0.337</t>
+          <t>0.3017</t>
         </is>
       </c>
       <c r="AU35" t="inlineStr">
         <is>
-          <t>69.42</t>
+          <t>72.06</t>
         </is>
       </c>
       <c r="AV35" t="inlineStr">
         <is>
-          <t>8.21</t>
+          <t>22.38</t>
         </is>
       </c>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>40.45</t>
+          <t>41.91</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>35.76</t>
+          <t>29.45</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
         <is>
-          <t>13.7</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>0.1809</t>
+          <t>0.1519</t>
         </is>
       </c>
       <c r="BA35" t="inlineStr">
         <is>
-          <t>10.24</t>
+          <t>7.52</t>
         </is>
       </c>
       <c r="BB35" t="inlineStr">
         <is>
-          <t>44.71</t>
+          <t>42.04</t>
         </is>
       </c>
       <c r="BC35" t="inlineStr">
         <is>
-          <t>90.89</t>
+          <t>89.07</t>
         </is>
       </c>
       <c r="BD35" t="inlineStr">
         <is>
-          <t>0.4856</t>
+          <t>0.3471</t>
         </is>
       </c>
       <c r="BE35" t="inlineStr">
         <is>
-          <t>0.1959</t>
+          <t>0.1263</t>
         </is>
       </c>
       <c r="BF35" t="inlineStr">
         <is>
-          <t>28.8</t>
-        </is>
-      </c>
-      <c r="BG35" t="inlineStr"/>
-      <c r="BH35" t="inlineStr"/>
+          <t>17.32</t>
+        </is>
+      </c>
+      <c r="BG35" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH35" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
       <c r="BI35" t="inlineStr">
         <is>
-          <t>UNIQLO Field at Dodger Stadium</t>
+          <t>Kauffman Stadium</t>
         </is>
       </c>
       <c r="BJ35" t="inlineStr"/>
@@ -10167,27 +10171,27 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>671218</t>
+          <t>605141</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Heliot Ramos</t>
+          <t>Mookie Betts</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-07-07T01:45:00Z</t>
+          <t>2026-07-07T02:10:00Z</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -10197,26 +10201,26 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Kevin Gausman</t>
+          <t>Kyle Freeland</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>592332</t>
+          <t>607536</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L36" t="n">
-        <v>51.1</v>
+        <v>51.2</v>
       </c>
       <c r="M36" t="inlineStr">
         <is>
@@ -10230,26 +10234,26 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P36" t="n">
-        <v>52.9</v>
+        <v>35</v>
       </c>
       <c r="Q36" t="n">
-        <v>43.6</v>
+        <v>59.9</v>
       </c>
       <c r="R36" t="n">
-        <v>19.3</v>
+        <v>27.6</v>
       </c>
       <c r="S36" t="n">
-        <v>92.09999999999999</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="T36" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U36" t="n">
-        <v>57.6</v>
+        <v>28.6</v>
       </c>
       <c r="V36" t="inlineStr">
         <is>
@@ -10263,7 +10267,7 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y36" t="inlineStr">
@@ -10305,134 +10309,134 @@
       </c>
       <c r="AH36" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI36" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 9/29, 0 HR</t>
         </is>
       </c>
       <c r="AL36" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.5% barrel, 16.8 HR allowed</t>
+          <t>platoon edge; pitcher baseline 10.2% barrel, 17.8 HR allowed</t>
         </is>
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>EV profile; pitcher fly-ball pressure modest</t>
+          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN36" t="inlineStr">
         <is>
-          <t>13.28</t>
+          <t>7.46</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>49.5</t>
+          <t>37.97</t>
         </is>
       </c>
       <c r="AP36" t="inlineStr">
         <is>
-          <t>92.01</t>
+          <t>90.22</t>
         </is>
       </c>
       <c r="AQ36" t="inlineStr">
         <is>
-          <t>103.3794</t>
+          <t>98.6577</t>
         </is>
       </c>
       <c r="AR36" t="inlineStr">
         <is>
-          <t>0.4583</t>
+          <t>0.4388</t>
         </is>
       </c>
       <c r="AS36" t="inlineStr">
         <is>
-          <t>0.1911</t>
+          <t>0.1616</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr">
         <is>
-          <t>0.3347</t>
+          <t>0.337</t>
         </is>
       </c>
       <c r="AU36" t="inlineStr">
         <is>
-          <t>72.67</t>
+          <t>69.42</t>
         </is>
       </c>
       <c r="AV36" t="inlineStr">
         <is>
-          <t>29.51</t>
+          <t>8.21</t>
         </is>
       </c>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>37.23</t>
+          <t>40.45</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>23.51</t>
+          <t>35.76</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">
         <is>
-          <t>10.5</t>
+          <t>13.7</t>
         </is>
       </c>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>0.1706</t>
+          <t>0.1809</t>
         </is>
       </c>
       <c r="BA36" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>10.24</t>
         </is>
       </c>
       <c r="BB36" t="inlineStr">
         <is>
-          <t>40.28</t>
+          <t>44.71</t>
         </is>
       </c>
       <c r="BC36" t="inlineStr">
         <is>
-          <t>89.09</t>
+          <t>90.89</t>
         </is>
       </c>
       <c r="BD36" t="inlineStr">
         <is>
-          <t>0.4049</t>
+          <t>0.4856</t>
         </is>
       </c>
       <c r="BE36" t="inlineStr">
         <is>
-          <t>0.1648</t>
+          <t>0.1959</t>
         </is>
       </c>
       <c r="BF36" t="inlineStr">
         <is>
-          <t>26.3</t>
+          <t>28.8</t>
         </is>
       </c>
       <c r="BG36" t="inlineStr"/>
       <c r="BH36" t="inlineStr"/>
       <c r="BI36" t="inlineStr">
         <is>
-          <t>Oracle Park</t>
+          <t>UNIQLO Field at Dodger Stadium</t>
         </is>
       </c>
       <c r="BJ36" t="inlineStr"/>
@@ -10443,56 +10447,56 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>669016</t>
+          <t>671218</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Brandon Marsh</t>
+          <t>Heliot Ramos</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-07-06T18:10:00Z</t>
+          <t>2026-07-07T01:45:00Z</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Noah Cameron</t>
+          <t>Kevin Gausman</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>702070</t>
+          <t>592332</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L37" t="n">
-        <v>50.6</v>
+        <v>51.1</v>
       </c>
       <c r="M37" t="inlineStr">
         <is>
@@ -10506,58 +10510,62 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>No major boost</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P37" t="n">
-        <v>41.7</v>
+        <v>52.9</v>
       </c>
       <c r="Q37" t="n">
-        <v>41.8</v>
+        <v>43.6</v>
       </c>
       <c r="R37" t="n">
-        <v>47.2</v>
+        <v>19.3</v>
       </c>
       <c r="S37" t="n">
-        <v>86.40000000000001</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="T37" t="n">
         <v>50</v>
       </c>
       <c r="U37" t="n">
-        <v>63.8</v>
+        <v>57.6</v>
       </c>
       <c r="V37" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W37" t="inlineStr">
+      <c r="Z37" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y37" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC37" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -10577,142 +10585,134 @@
       </c>
       <c r="AH37" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI37" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
         <is>
-          <t>Hot streak: 3 HR in last 7 games</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL37" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.9% barrel, 12.4 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.5% barrel, 16.8 HR allowed</t>
         </is>
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN37" t="inlineStr">
         <is>
-          <t>9.52</t>
+          <t>13.28</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>46.19</t>
+          <t>49.5</t>
         </is>
       </c>
       <c r="AP37" t="inlineStr">
         <is>
-          <t>90.12</t>
+          <t>92.01</t>
         </is>
       </c>
       <c r="AQ37" t="inlineStr">
         <is>
-          <t>100.4854</t>
+          <t>103.3794</t>
         </is>
       </c>
       <c r="AR37" t="inlineStr">
         <is>
-          <t>0.446</t>
+          <t>0.4583</t>
         </is>
       </c>
       <c r="AS37" t="inlineStr">
         <is>
-          <t>0.1739</t>
+          <t>0.1911</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr">
         <is>
-          <t>0.3279</t>
+          <t>0.3347</t>
         </is>
       </c>
       <c r="AU37" t="inlineStr">
         <is>
-          <t>71.47</t>
+          <t>72.67</t>
         </is>
       </c>
       <c r="AV37" t="inlineStr">
         <is>
-          <t>14.91</t>
+          <t>29.51</t>
         </is>
       </c>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>37.56</t>
+          <t>37.23</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>25.61</t>
+          <t>23.51</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr">
         <is>
-          <t>13.8</t>
+          <t>10.5</t>
         </is>
       </c>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>0.1903</t>
+          <t>0.1706</t>
         </is>
       </c>
       <c r="BA37" t="inlineStr">
         <is>
-          <t>7.91</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="BB37" t="inlineStr">
         <is>
-          <t>38.38</t>
+          <t>40.28</t>
         </is>
       </c>
       <c r="BC37" t="inlineStr">
         <is>
-          <t>88.67</t>
+          <t>89.09</t>
         </is>
       </c>
       <c r="BD37" t="inlineStr">
         <is>
-          <t>0.4436</t>
+          <t>0.4049</t>
         </is>
       </c>
       <c r="BE37" t="inlineStr">
         <is>
-          <t>0.1758</t>
+          <t>0.1648</t>
         </is>
       </c>
       <c r="BF37" t="inlineStr">
         <is>
-          <t>25.26</t>
-        </is>
-      </c>
-      <c r="BG37" t="inlineStr">
-        <is>
-          <t>L To R</t>
-        </is>
-      </c>
-      <c r="BH37" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
+          <t>26.3</t>
+        </is>
+      </c>
+      <c r="BG37" t="inlineStr"/>
+      <c r="BH37" t="inlineStr"/>
       <c r="BI37" t="inlineStr">
         <is>
-          <t>Kauffman Stadium</t>
+          <t>Oracle Park</t>
         </is>
       </c>
       <c r="BJ37" t="inlineStr"/>
@@ -10723,12 +10723,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>607208</t>
+          <t>669016</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Trea Turner</t>
+          <t>Brandon Marsh</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -10753,7 +10753,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -10772,7 +10772,7 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>50.3</v>
+        <v>50.6</v>
       </c>
       <c r="M38" t="inlineStr">
         <is>
@@ -10786,11 +10786,11 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P38" t="n">
-        <v>26.7</v>
+        <v>41.7</v>
       </c>
       <c r="Q38" t="n">
         <v>41.8</v>
@@ -10799,13 +10799,13 @@
         <v>47.2</v>
       </c>
       <c r="S38" t="n">
-        <v>93.2</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T38" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U38" t="n">
-        <v>87</v>
+        <v>62.9</v>
       </c>
       <c r="V38" t="inlineStr">
         <is>
@@ -10819,7 +10819,7 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y38" t="inlineStr">
@@ -10857,12 +10857,12 @@
       </c>
       <c r="AH38" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI38" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ38" t="inlineStr">
@@ -10877,7 +10877,7 @@
       </c>
       <c r="AL38" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.9% barrel, 12.4 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.9% barrel, 12.4 HR allowed</t>
         </is>
       </c>
       <c r="AM38" t="inlineStr">
@@ -10887,67 +10887,67 @@
       </c>
       <c r="AN38" t="inlineStr">
         <is>
-          <t>5.8</t>
+          <t>9.52</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>40.28</t>
+          <t>46.19</t>
         </is>
       </c>
       <c r="AP38" t="inlineStr">
         <is>
-          <t>88.95</t>
+          <t>90.12</t>
         </is>
       </c>
       <c r="AQ38" t="inlineStr">
         <is>
-          <t>99.2888</t>
+          <t>100.4854</t>
         </is>
       </c>
       <c r="AR38" t="inlineStr">
         <is>
-          <t>0.3715</t>
+          <t>0.446</t>
         </is>
       </c>
       <c r="AS38" t="inlineStr">
         <is>
-          <t>0.1246</t>
+          <t>0.1739</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr">
         <is>
-          <t>0.2937</t>
+          <t>0.3279</t>
         </is>
       </c>
       <c r="AU38" t="inlineStr">
         <is>
-          <t>71.48</t>
+          <t>71.47</t>
         </is>
       </c>
       <c r="AV38" t="inlineStr">
         <is>
-          <t>18.78</t>
+          <t>14.91</t>
         </is>
       </c>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>33.42</t>
+          <t>37.56</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>26.74</t>
+          <t>25.61</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr">
         <is>
-          <t>11.5</t>
+          <t>13.8</t>
         </is>
       </c>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>0.1327</t>
+          <t>0.1903</t>
         </is>
       </c>
       <c r="BA38" t="inlineStr">
@@ -11003,24 +11003,24 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>521692</t>
+          <t>607208</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Salvador Perez</t>
+          <t>Trea Turner</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
+          <t>PHI</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
           <t>KC</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>PHI</t>
-        </is>
-      </c>
       <c r="F39" t="inlineStr">
         <is>
           <t>2026-07-06T18:10:00Z</t>
@@ -11033,17 +11033,17 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Cristopher Sánchez</t>
+          <t>Noah Cameron</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>650911</t>
+          <t>702070</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -11066,26 +11066,26 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P39" t="n">
-        <v>42.2</v>
+        <v>26.7</v>
       </c>
       <c r="Q39" t="n">
-        <v>32.7</v>
+        <v>41.8</v>
       </c>
       <c r="R39" t="n">
         <v>47.2</v>
       </c>
       <c r="S39" t="n">
-        <v>96.59999999999999</v>
+        <v>93.2</v>
       </c>
       <c r="T39" t="n">
         <v>78</v>
       </c>
       <c r="U39" t="n">
-        <v>18</v>
+        <v>87</v>
       </c>
       <c r="V39" t="inlineStr">
         <is>
@@ -11099,7 +11099,7 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y39" t="inlineStr">
@@ -11137,27 +11137,27 @@
       </c>
       <c r="AH39" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AI39" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/25, 0 HR</t>
+          <t>Hot streak: 3 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL39" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.5% barrel, 9.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.9% barrel, 12.4 HR allowed</t>
         </is>
       </c>
       <c r="AM39" t="inlineStr">
@@ -11167,97 +11167,97 @@
       </c>
       <c r="AN39" t="inlineStr">
         <is>
-          <t>10.74</t>
+          <t>5.8</t>
         </is>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>42.71</t>
+          <t>40.28</t>
         </is>
       </c>
       <c r="AP39" t="inlineStr">
         <is>
-          <t>89.09</t>
+          <t>88.95</t>
         </is>
       </c>
       <c r="AQ39" t="inlineStr">
         <is>
-          <t>100.5081</t>
+          <t>99.2888</t>
         </is>
       </c>
       <c r="AR39" t="inlineStr">
         <is>
-          <t>0.4234</t>
+          <t>0.3715</t>
         </is>
       </c>
       <c r="AS39" t="inlineStr">
         <is>
-          <t>0.1883</t>
+          <t>0.1246</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr">
         <is>
-          <t>0.3017</t>
+          <t>0.2937</t>
         </is>
       </c>
       <c r="AU39" t="inlineStr">
         <is>
-          <t>72.06</t>
+          <t>71.48</t>
         </is>
       </c>
       <c r="AV39" t="inlineStr">
         <is>
-          <t>22.38</t>
+          <t>18.78</t>
         </is>
       </c>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>41.91</t>
+          <t>33.42</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>29.45</t>
+          <t>26.74</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr">
         <is>
-          <t>16.0</t>
+          <t>11.5</t>
         </is>
       </c>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>0.1519</t>
+          <t>0.1327</t>
         </is>
       </c>
       <c r="BA39" t="inlineStr">
         <is>
-          <t>7.52</t>
+          <t>7.91</t>
         </is>
       </c>
       <c r="BB39" t="inlineStr">
         <is>
-          <t>42.04</t>
+          <t>38.38</t>
         </is>
       </c>
       <c r="BC39" t="inlineStr">
         <is>
-          <t>89.07</t>
+          <t>88.67</t>
         </is>
       </c>
       <c r="BD39" t="inlineStr">
         <is>
-          <t>0.3471</t>
+          <t>0.4436</t>
         </is>
       </c>
       <c r="BE39" t="inlineStr">
         <is>
-          <t>0.1263</t>
+          <t>0.1758</t>
         </is>
       </c>
       <c r="BF39" t="inlineStr">
         <is>
-          <t>17.32</t>
+          <t>25.26</t>
         </is>
       </c>
       <c r="BG39" t="inlineStr">
@@ -17391,32 +17391,32 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>624641</t>
+          <t>676724</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Edmundo Sosa</t>
+          <t>Jared Young</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>NYM</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-07-06T18:10:00Z</t>
+          <t>2026-07-06T23:15:00Z</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -17426,17 +17426,17 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Noah Cameron</t>
+          <t>Reynaldo López</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>702070</t>
+          <t>625643</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L62" t="n">
@@ -17454,58 +17454,62 @@
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P62" t="n">
-        <v>31</v>
+        <v>47.2</v>
       </c>
       <c r="Q62" t="n">
-        <v>41.8</v>
+        <v>35.7</v>
       </c>
       <c r="R62" t="n">
-        <v>47.2</v>
+        <v>30.9</v>
       </c>
       <c r="S62" t="n">
-        <v>76.2</v>
+        <v>71.7</v>
       </c>
       <c r="T62" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U62" t="n">
-        <v>22.8</v>
+        <v>4.5</v>
       </c>
       <c r="V62" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W62" t="inlineStr">
+      <c r="Z62" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X62" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y62" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB62" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC62" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -17535,17 +17539,17 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK62" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/20, 1 HR</t>
+          <t>Last 7 games: 3/20, 0 HR</t>
         </is>
       </c>
       <c r="AL62" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.9% barrel, 12.4 HR allowed</t>
+          <t>platoon edge; pitcher baseline 5.6% barrel, 4.5 HR allowed</t>
         </is>
       </c>
       <c r="AM62" t="inlineStr">
@@ -17555,112 +17559,104 @@
       </c>
       <c r="AN62" t="inlineStr">
         <is>
-          <t>7.21</t>
+          <t>12.69</t>
         </is>
       </c>
       <c r="AO62" t="inlineStr">
         <is>
-          <t>39.4</t>
+          <t>45.25</t>
         </is>
       </c>
       <c r="AP62" t="inlineStr">
         <is>
-          <t>87.28</t>
+          <t>88.38</t>
         </is>
       </c>
       <c r="AQ62" t="inlineStr">
         <is>
-          <t>99.6935</t>
+          <t>101.1051</t>
         </is>
       </c>
       <c r="AR62" t="inlineStr">
         <is>
-          <t>0.447</t>
+          <t>0.4252</t>
         </is>
       </c>
       <c r="AS62" t="inlineStr">
         <is>
-          <t>0.1719</t>
+          <t>0.2053</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr">
         <is>
-          <t>0.3257</t>
+          <t>0.3114</t>
         </is>
       </c>
       <c r="AU62" t="inlineStr">
         <is>
-          <t>72.16</t>
+          <t>73.51</t>
         </is>
       </c>
       <c r="AV62" t="inlineStr">
         <is>
-          <t>24.94</t>
+          <t>35.42</t>
         </is>
       </c>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>39.63</t>
+          <t>39.93</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>18.84</t>
+          <t>28.21</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr">
         <is>
-          <t>6.8</t>
+          <t>5.4</t>
         </is>
       </c>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>0.172</t>
+          <t>0.218</t>
         </is>
       </c>
       <c r="BA62" t="inlineStr">
         <is>
-          <t>7.91</t>
+          <t>5.62</t>
         </is>
       </c>
       <c r="BB62" t="inlineStr">
         <is>
-          <t>38.38</t>
+          <t>39.92</t>
         </is>
       </c>
       <c r="BC62" t="inlineStr">
         <is>
-          <t>88.67</t>
+          <t>88.01</t>
         </is>
       </c>
       <c r="BD62" t="inlineStr">
         <is>
-          <t>0.4436</t>
+          <t>0.4761</t>
         </is>
       </c>
       <c r="BE62" t="inlineStr">
         <is>
-          <t>0.1758</t>
+          <t>0.1699</t>
         </is>
       </c>
       <c r="BF62" t="inlineStr">
         <is>
-          <t>25.26</t>
-        </is>
-      </c>
-      <c r="BG62" t="inlineStr">
-        <is>
-          <t>L To R</t>
-        </is>
-      </c>
-      <c r="BH62" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
+          <t>27.44</t>
+        </is>
+      </c>
+      <c r="BG62" t="inlineStr"/>
+      <c r="BH62" t="inlineStr"/>
       <c r="BI62" t="inlineStr">
         <is>
-          <t>Kauffman Stadium</t>
+          <t>Truist Park</t>
         </is>
       </c>
       <c r="BJ62" t="inlineStr"/>
@@ -17671,27 +17667,27 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>676724</t>
+          <t>630105</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Jared Young</t>
+          <t>Jake Cronenworth</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NYM</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-07-06T23:15:00Z</t>
+          <t>2026-07-07T01:40:00Z</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -17701,17 +17697,17 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Reynaldo López</t>
+          <t>Brandon Pfaadt</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>625643</t>
+          <t>694297</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -17734,26 +17730,26 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P63" t="n">
-        <v>47.2</v>
+        <v>20.4</v>
       </c>
       <c r="Q63" t="n">
-        <v>35.7</v>
+        <v>56.1</v>
       </c>
       <c r="R63" t="n">
-        <v>30.9</v>
+        <v>22.6</v>
       </c>
       <c r="S63" t="n">
-        <v>71.7</v>
+        <v>95.5</v>
       </c>
       <c r="T63" t="n">
         <v>80</v>
       </c>
       <c r="U63" t="n">
-        <v>4.5</v>
+        <v>41.2</v>
       </c>
       <c r="V63" t="inlineStr">
         <is>
@@ -17767,7 +17763,7 @@
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y63" t="inlineStr">
@@ -17809,27 +17805,27 @@
       </c>
       <c r="AH63" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI63" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/20, 0 HR</t>
+          <t>Last 7 games: 6/22, 1 HR</t>
         </is>
       </c>
       <c r="AL63" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 5.6% barrel, 4.5 HR allowed</t>
+          <t>platoon edge; pitcher baseline 11.5% barrel, 13.4 HR allowed</t>
         </is>
       </c>
       <c r="AM63" t="inlineStr">
@@ -17839,104 +17835,104 @@
       </c>
       <c r="AN63" t="inlineStr">
         <is>
-          <t>12.69</t>
+          <t>6.62</t>
         </is>
       </c>
       <c r="AO63" t="inlineStr">
         <is>
-          <t>45.25</t>
+          <t>32.91</t>
         </is>
       </c>
       <c r="AP63" t="inlineStr">
         <is>
-          <t>88.38</t>
+          <t>87.66</t>
         </is>
       </c>
       <c r="AQ63" t="inlineStr">
         <is>
-          <t>101.1051</t>
+          <t>97.821</t>
         </is>
       </c>
       <c r="AR63" t="inlineStr">
         <is>
-          <t>0.4252</t>
+          <t>0.3348</t>
         </is>
       </c>
       <c r="AS63" t="inlineStr">
         <is>
-          <t>0.2053</t>
+          <t>0.1147</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr">
         <is>
-          <t>0.3114</t>
+          <t>0.3029</t>
         </is>
       </c>
       <c r="AU63" t="inlineStr">
         <is>
-          <t>73.51</t>
+          <t>71.67</t>
         </is>
       </c>
       <c r="AV63" t="inlineStr">
         <is>
-          <t>35.42</t>
+          <t>18.16</t>
         </is>
       </c>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>39.93</t>
+          <t>32.73</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>28.21</t>
+          <t>21.6</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>4.7</t>
         </is>
       </c>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>0.218</t>
+          <t>0.0862</t>
         </is>
       </c>
       <c r="BA63" t="inlineStr">
         <is>
-          <t>5.62</t>
+          <t>11.53</t>
         </is>
       </c>
       <c r="BB63" t="inlineStr">
         <is>
-          <t>39.92</t>
+          <t>41.04</t>
         </is>
       </c>
       <c r="BC63" t="inlineStr">
         <is>
-          <t>88.01</t>
+          <t>89.89</t>
         </is>
       </c>
       <c r="BD63" t="inlineStr">
         <is>
-          <t>0.4761</t>
+          <t>0.4632</t>
         </is>
       </c>
       <c r="BE63" t="inlineStr">
         <is>
-          <t>0.1699</t>
+          <t>0.2044</t>
         </is>
       </c>
       <c r="BF63" t="inlineStr">
         <is>
-          <t>27.44</t>
+          <t>21.59</t>
         </is>
       </c>
       <c r="BG63" t="inlineStr"/>
       <c r="BH63" t="inlineStr"/>
       <c r="BI63" t="inlineStr">
         <is>
-          <t>Truist Park</t>
+          <t>Petco Park</t>
         </is>
       </c>
       <c r="BJ63" t="inlineStr"/>
@@ -17947,56 +17943,56 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>630105</t>
+          <t>624641</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Jake Cronenworth</t>
+          <t>Edmundo Sosa</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-07-07T01:40:00Z</t>
+          <t>2026-07-06T18:10:00Z</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Brandon Pfaadt</t>
+          <t>Noah Cameron</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>694297</t>
+          <t>702070</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L64" t="n">
-        <v>46.2</v>
+        <v>46.1</v>
       </c>
       <c r="M64" t="inlineStr">
         <is>
@@ -18010,62 +18006,58 @@
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P64" t="n">
-        <v>20.4</v>
+        <v>31</v>
       </c>
       <c r="Q64" t="n">
-        <v>56.1</v>
+        <v>41.8</v>
       </c>
       <c r="R64" t="n">
-        <v>22.6</v>
+        <v>47.2</v>
       </c>
       <c r="S64" t="n">
-        <v>95.5</v>
+        <v>76.2</v>
       </c>
       <c r="T64" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="U64" t="n">
-        <v>41.2</v>
+        <v>21.8</v>
       </c>
       <c r="V64" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W64" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X64" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y64" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr"/>
       <c r="AC64" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -18085,12 +18077,12 @@
       </c>
       <c r="AH64" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI64" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ64" t="inlineStr">
@@ -18100,12 +18092,12 @@
       </c>
       <c r="AK64" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/22, 1 HR</t>
+          <t>Last 7 games: 3/21, 1 HR</t>
         </is>
       </c>
       <c r="AL64" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 11.5% barrel, 13.4 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.9% barrel, 12.4 HR allowed</t>
         </is>
       </c>
       <c r="AM64" t="inlineStr">
@@ -18115,104 +18107,112 @@
       </c>
       <c r="AN64" t="inlineStr">
         <is>
-          <t>6.62</t>
+          <t>7.21</t>
         </is>
       </c>
       <c r="AO64" t="inlineStr">
         <is>
-          <t>32.91</t>
+          <t>39.4</t>
         </is>
       </c>
       <c r="AP64" t="inlineStr">
         <is>
-          <t>87.66</t>
+          <t>87.28</t>
         </is>
       </c>
       <c r="AQ64" t="inlineStr">
         <is>
-          <t>97.821</t>
+          <t>99.6935</t>
         </is>
       </c>
       <c r="AR64" t="inlineStr">
         <is>
-          <t>0.3348</t>
+          <t>0.447</t>
         </is>
       </c>
       <c r="AS64" t="inlineStr">
         <is>
-          <t>0.1147</t>
+          <t>0.1719</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr">
         <is>
-          <t>0.3029</t>
+          <t>0.3257</t>
         </is>
       </c>
       <c r="AU64" t="inlineStr">
         <is>
-          <t>71.67</t>
+          <t>72.16</t>
         </is>
       </c>
       <c r="AV64" t="inlineStr">
         <is>
-          <t>18.16</t>
+          <t>24.94</t>
         </is>
       </c>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>32.73</t>
+          <t>39.63</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>21.6</t>
+          <t>18.84</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>6.8</t>
         </is>
       </c>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>0.0862</t>
+          <t>0.172</t>
         </is>
       </c>
       <c r="BA64" t="inlineStr">
         <is>
-          <t>11.53</t>
+          <t>7.91</t>
         </is>
       </c>
       <c r="BB64" t="inlineStr">
         <is>
-          <t>41.04</t>
+          <t>38.38</t>
         </is>
       </c>
       <c r="BC64" t="inlineStr">
         <is>
-          <t>89.89</t>
+          <t>88.67</t>
         </is>
       </c>
       <c r="BD64" t="inlineStr">
         <is>
-          <t>0.4632</t>
+          <t>0.4436</t>
         </is>
       </c>
       <c r="BE64" t="inlineStr">
         <is>
-          <t>0.2044</t>
+          <t>0.1758</t>
         </is>
       </c>
       <c r="BF64" t="inlineStr">
         <is>
-          <t>21.59</t>
-        </is>
-      </c>
-      <c r="BG64" t="inlineStr"/>
-      <c r="BH64" t="inlineStr"/>
+          <t>25.26</t>
+        </is>
+      </c>
+      <c r="BG64" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH64" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
       <c r="BI64" t="inlineStr">
         <is>
-          <t>Petco Park</t>
+          <t>Kauffman Stadium</t>
         </is>
       </c>
       <c r="BJ64" t="inlineStr"/>
@@ -22091,12 +22091,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>656537</t>
+          <t>592663</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Derek Hill</t>
+          <t>J.T. Realmuto</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -22121,7 +22121,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -22154,11 +22154,11 @@
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>Strong Barrel, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P79" t="n">
-        <v>38</v>
+        <v>31.4</v>
       </c>
       <c r="Q79" t="n">
         <v>41.8</v>
@@ -22167,13 +22167,13 @@
         <v>47.2</v>
       </c>
       <c r="S79" t="n">
-        <v>44.8</v>
+        <v>52.4</v>
       </c>
       <c r="T79" t="n">
         <v>78</v>
       </c>
       <c r="U79" t="n">
-        <v>12</v>
+        <v>32.9</v>
       </c>
       <c r="V79" t="inlineStr">
         <is>
@@ -22187,7 +22187,7 @@
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y79" t="inlineStr">
@@ -22225,22 +22225,22 @@
       </c>
       <c r="AH79" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI79" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/10, 0 HR</t>
+          <t>Last 7 games: 5/23, 1 HR</t>
         </is>
       </c>
       <c r="AL79" t="inlineStr">
@@ -22255,67 +22255,67 @@
       </c>
       <c r="AN79" t="inlineStr">
         <is>
-          <t>11.27</t>
+          <t>6.49</t>
         </is>
       </c>
       <c r="AO79" t="inlineStr">
         <is>
-          <t>39.11</t>
+          <t>40.25</t>
         </is>
       </c>
       <c r="AP79" t="inlineStr">
         <is>
-          <t>90.15</t>
+          <t>89.44</t>
         </is>
       </c>
       <c r="AQ79" t="inlineStr">
         <is>
-          <t>100.2609</t>
+          <t>99.4091</t>
         </is>
       </c>
       <c r="AR79" t="inlineStr">
         <is>
-          <t>0.3866</t>
+          <t>0.3935</t>
         </is>
       </c>
       <c r="AS79" t="inlineStr">
         <is>
-          <t>0.1584</t>
+          <t>0.1447</t>
         </is>
       </c>
       <c r="AT79" t="inlineStr">
         <is>
-          <t>0.295</t>
+          <t>0.3167</t>
         </is>
       </c>
       <c r="AU79" t="inlineStr">
         <is>
-          <t>72.08</t>
+          <t>72.77</t>
         </is>
       </c>
       <c r="AV79" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>30.99</t>
         </is>
       </c>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>37.66</t>
+          <t>39.99</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>21.59</t>
+          <t>28.18</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>7.8</t>
         </is>
       </c>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>0.1575</t>
+          <t>0.1291</t>
         </is>
       </c>
       <c r="BA79" t="inlineStr">
@@ -22371,47 +22371,47 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>802139</t>
+          <t>656537</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>JJ Wetherholt</t>
+          <t>Derek Hill</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-07-06T23:45:00Z</t>
+          <t>2026-07-06T18:10:00Z</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Shane Drohan</t>
+          <t>Noah Cameron</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>675660</t>
+          <t>702070</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
@@ -22420,7 +22420,7 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>43.4</v>
+        <v>43.5</v>
       </c>
       <c r="M80" t="inlineStr">
         <is>
@@ -22434,65 +22434,61 @@
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P80" t="n">
-        <v>39.1</v>
+        <v>38</v>
       </c>
       <c r="Q80" t="n">
-        <v>32</v>
+        <v>41.8</v>
       </c>
       <c r="R80" t="n">
-        <v>22.1</v>
+        <v>47.2</v>
       </c>
       <c r="S80" t="n">
-        <v>88.7</v>
+        <v>44.8</v>
       </c>
       <c r="T80" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U80" t="n">
-        <v>52.1</v>
+        <v>12</v>
       </c>
       <c r="V80" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z80" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W80" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X80" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y80" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z80" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB80" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr"/>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>H:2026 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD80" t="inlineStr"/>
@@ -22509,27 +22505,27 @@
       </c>
       <c r="AH80" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI80" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="AI80" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK80" t="inlineStr">
         <is>
-          <t>Contact streak: 10/29 over last 7 games</t>
+          <t>Last 7 games: 2/10, 0 HR</t>
         </is>
       </c>
       <c r="AL80" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.7% barrel, 5.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.9% barrel, 12.4 HR allowed</t>
         </is>
       </c>
       <c r="AM80" t="inlineStr">
@@ -22539,104 +22535,112 @@
       </c>
       <c r="AN80" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>11.27</t>
         </is>
       </c>
       <c r="AO80" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>39.11</t>
         </is>
       </c>
       <c r="AP80" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>90.15</t>
         </is>
       </c>
       <c r="AQ80" t="inlineStr">
         <is>
-          <t>99.4588</t>
+          <t>100.2609</t>
         </is>
       </c>
       <c r="AR80" t="inlineStr">
         <is>
-          <t>0.442</t>
+          <t>0.3866</t>
         </is>
       </c>
       <c r="AS80" t="inlineStr">
         <is>
-          <t>0.176</t>
+          <t>0.1584</t>
         </is>
       </c>
       <c r="AT80" t="inlineStr">
         <is>
-          <t>0.355</t>
+          <t>0.295</t>
         </is>
       </c>
       <c r="AU80" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>72.08</t>
         </is>
       </c>
       <c r="AV80" t="inlineStr">
         <is>
-          <t>22.4</t>
+          <t>20.05</t>
         </is>
       </c>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>38.9</t>
+          <t>37.66</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>30.4</t>
+          <t>21.59</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>0.147</t>
+          <t>0.1575</t>
         </is>
       </c>
       <c r="BA80" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>7.91</t>
         </is>
       </c>
       <c r="BB80" t="inlineStr">
         <is>
-          <t>36.2</t>
+          <t>38.38</t>
         </is>
       </c>
       <c r="BC80" t="inlineStr">
         <is>
-          <t>87.7</t>
+          <t>88.67</t>
         </is>
       </c>
       <c r="BD80" t="inlineStr">
         <is>
-          <t>0.355</t>
+          <t>0.4436</t>
         </is>
       </c>
       <c r="BE80" t="inlineStr">
         <is>
-          <t>0.125</t>
+          <t>0.1758</t>
         </is>
       </c>
       <c r="BF80" t="inlineStr">
         <is>
-          <t>27.0</t>
-        </is>
-      </c>
-      <c r="BG80" t="inlineStr"/>
-      <c r="BH80" t="inlineStr"/>
+          <t>25.26</t>
+        </is>
+      </c>
+      <c r="BG80" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH80" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
       <c r="BI80" t="inlineStr">
         <is>
-          <t>Busch Stadium</t>
+          <t>Kauffman Stadium</t>
         </is>
       </c>
       <c r="BJ80" t="inlineStr"/>
@@ -22647,27 +22651,27 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>669242</t>
+          <t>802139</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Tommy Edman</t>
+          <t>JJ Wetherholt</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-07-07T02:10:00Z</t>
+          <t>2026-07-06T23:45:00Z</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -22677,17 +22681,17 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Kyle Freeland</t>
+          <t>Shane Drohan</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>607536</t>
+          <t>675660</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
@@ -22710,26 +22714,26 @@
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P81" t="n">
-        <v>29.2</v>
+        <v>39.1</v>
       </c>
       <c r="Q81" t="n">
-        <v>58</v>
+        <v>32</v>
       </c>
       <c r="R81" t="n">
-        <v>27.6</v>
+        <v>22.1</v>
       </c>
       <c r="S81" t="n">
-        <v>47.9</v>
+        <v>88.7</v>
       </c>
       <c r="T81" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U81" t="n">
-        <v>45.3</v>
+        <v>52.1</v>
       </c>
       <c r="V81" t="inlineStr">
         <is>
@@ -22743,7 +22747,7 @@
       </c>
       <c r="X81" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y81" t="inlineStr">
@@ -22768,7 +22772,7 @@
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026</t>
         </is>
       </c>
       <c r="AD81" t="inlineStr"/>
@@ -22785,12 +22789,12 @@
       </c>
       <c r="AH81" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AI81" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ81" t="inlineStr">
@@ -22800,12 +22804,12 @@
       </c>
       <c r="AK81" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/20, 1 HR</t>
+          <t>Contact streak: 10/29 over last 7 games</t>
         </is>
       </c>
       <c r="AL81" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 10.2% barrel, 17.8 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.7% barrel, 5.0 HR allowed</t>
         </is>
       </c>
       <c r="AM81" t="inlineStr">
@@ -22815,104 +22819,104 @@
       </c>
       <c r="AN81" t="inlineStr">
         <is>
-          <t>6.88</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="AO81" t="inlineStr">
         <is>
-          <t>39.62</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="AP81" t="inlineStr">
         <is>
-          <t>89.77</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AQ81" t="inlineStr">
         <is>
-          <t>100.2456</t>
+          <t>99.4588</t>
         </is>
       </c>
       <c r="AR81" t="inlineStr">
         <is>
-          <t>0.4292</t>
+          <t>0.442</t>
         </is>
       </c>
       <c r="AS81" t="inlineStr">
         <is>
-          <t>0.1293</t>
+          <t>0.176</t>
         </is>
       </c>
       <c r="AT81" t="inlineStr">
         <is>
-          <t>0.3588</t>
+          <t>0.355</t>
         </is>
       </c>
       <c r="AU81" t="inlineStr">
         <is>
-          <t>70.55</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="AV81" t="inlineStr">
         <is>
-          <t>11.3</t>
+          <t>22.4</t>
         </is>
       </c>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>42.25</t>
+          <t>38.9</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>20.2</t>
+          <t>30.4</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>0.1612</t>
+          <t>0.147</t>
         </is>
       </c>
       <c r="BA81" t="inlineStr">
         <is>
-          <t>10.24</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="BB81" t="inlineStr">
         <is>
-          <t>44.71</t>
+          <t>36.2</t>
         </is>
       </c>
       <c r="BC81" t="inlineStr">
         <is>
-          <t>90.89</t>
+          <t>87.7</t>
         </is>
       </c>
       <c r="BD81" t="inlineStr">
         <is>
-          <t>0.4856</t>
+          <t>0.355</t>
         </is>
       </c>
       <c r="BE81" t="inlineStr">
         <is>
-          <t>0.1959</t>
+          <t>0.125</t>
         </is>
       </c>
       <c r="BF81" t="inlineStr">
         <is>
-          <t>28.8</t>
+          <t>27.0</t>
         </is>
       </c>
       <c r="BG81" t="inlineStr"/>
       <c r="BH81" t="inlineStr"/>
       <c r="BI81" t="inlineStr">
         <is>
-          <t>UNIQLO Field at Dodger Stadium</t>
+          <t>Busch Stadium</t>
         </is>
       </c>
       <c r="BJ81" t="inlineStr"/>
@@ -22923,32 +22927,32 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>592663</t>
+          <t>669242</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>J.T. Realmuto</t>
+          <t>Tommy Edman</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-07-06T18:10:00Z</t>
+          <t>2026-07-07T02:10:00Z</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -22958,12 +22962,12 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Noah Cameron</t>
+          <t>Kyle Freeland</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>702070</t>
+          <t>607536</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
@@ -22972,7 +22976,7 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>43.2</v>
+        <v>43.4</v>
       </c>
       <c r="M82" t="inlineStr">
         <is>
@@ -22986,58 +22990,62 @@
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P82" t="n">
-        <v>31.4</v>
+        <v>29.2</v>
       </c>
       <c r="Q82" t="n">
-        <v>41.8</v>
+        <v>58</v>
       </c>
       <c r="R82" t="n">
-        <v>47.2</v>
+        <v>27.6</v>
       </c>
       <c r="S82" t="n">
-        <v>52.4</v>
+        <v>47.9</v>
       </c>
       <c r="T82" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="U82" t="n">
-        <v>27.6</v>
+        <v>45.3</v>
       </c>
       <c r="V82" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W82" t="inlineStr">
+      <c r="Z82" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X82" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y82" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z82" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB82" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC82" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -23057,12 +23065,12 @@
       </c>
       <c r="AH82" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI82" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ82" t="inlineStr">
@@ -23072,12 +23080,12 @@
       </c>
       <c r="AK82" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/22, 1 HR</t>
+          <t>Last 7 games: 6/20, 1 HR</t>
         </is>
       </c>
       <c r="AL82" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.9% barrel, 12.4 HR allowed</t>
+          <t>switch hitter; pitcher baseline 10.2% barrel, 17.8 HR allowed</t>
         </is>
       </c>
       <c r="AM82" t="inlineStr">
@@ -23087,112 +23095,104 @@
       </c>
       <c r="AN82" t="inlineStr">
         <is>
-          <t>6.49</t>
+          <t>6.88</t>
         </is>
       </c>
       <c r="AO82" t="inlineStr">
         <is>
-          <t>40.25</t>
+          <t>39.62</t>
         </is>
       </c>
       <c r="AP82" t="inlineStr">
         <is>
-          <t>89.44</t>
+          <t>89.77</t>
         </is>
       </c>
       <c r="AQ82" t="inlineStr">
         <is>
-          <t>99.4091</t>
+          <t>100.2456</t>
         </is>
       </c>
       <c r="AR82" t="inlineStr">
         <is>
-          <t>0.3935</t>
+          <t>0.4292</t>
         </is>
       </c>
       <c r="AS82" t="inlineStr">
         <is>
-          <t>0.1447</t>
+          <t>0.1293</t>
         </is>
       </c>
       <c r="AT82" t="inlineStr">
         <is>
-          <t>0.3167</t>
+          <t>0.3588</t>
         </is>
       </c>
       <c r="AU82" t="inlineStr">
         <is>
-          <t>72.77</t>
+          <t>70.55</t>
         </is>
       </c>
       <c r="AV82" t="inlineStr">
         <is>
-          <t>30.99</t>
+          <t>11.3</t>
         </is>
       </c>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>39.99</t>
+          <t>42.25</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>28.18</t>
+          <t>20.2</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr">
         <is>
-          <t>7.8</t>
+          <t>4.6</t>
         </is>
       </c>
       <c r="AZ82" t="inlineStr">
         <is>
-          <t>0.1291</t>
+          <t>0.1612</t>
         </is>
       </c>
       <c r="BA82" t="inlineStr">
         <is>
-          <t>7.91</t>
+          <t>10.24</t>
         </is>
       </c>
       <c r="BB82" t="inlineStr">
         <is>
-          <t>38.38</t>
+          <t>44.71</t>
         </is>
       </c>
       <c r="BC82" t="inlineStr">
         <is>
-          <t>88.67</t>
+          <t>90.89</t>
         </is>
       </c>
       <c r="BD82" t="inlineStr">
         <is>
-          <t>0.4436</t>
+          <t>0.4856</t>
         </is>
       </c>
       <c r="BE82" t="inlineStr">
         <is>
-          <t>0.1758</t>
+          <t>0.1959</t>
         </is>
       </c>
       <c r="BF82" t="inlineStr">
         <is>
-          <t>25.26</t>
-        </is>
-      </c>
-      <c r="BG82" t="inlineStr">
-        <is>
-          <t>L To R</t>
-        </is>
-      </c>
-      <c r="BH82" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
+          <t>28.8</t>
+        </is>
+      </c>
+      <c r="BG82" t="inlineStr"/>
+      <c r="BH82" t="inlineStr"/>
       <c r="BI82" t="inlineStr">
         <is>
-          <t>Kauffman Stadium</t>
+          <t>UNIQLO Field at Dodger Stadium</t>
         </is>
       </c>
       <c r="BJ82" t="inlineStr"/>
@@ -25159,47 +25159,47 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>678662</t>
+          <t>681082</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Ezequiel Tovar</t>
+          <t>Bryson Stott</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-07-07T02:10:00Z</t>
+          <t>2026-07-06T18:10:00Z</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>Eric Lauer</t>
+          <t>Noah Cameron</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>641778</t>
+          <t>702070</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
@@ -25208,7 +25208,7 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>41.5</v>
+        <v>41.6</v>
       </c>
       <c r="M90" t="inlineStr">
         <is>
@@ -25222,62 +25222,58 @@
       </c>
       <c r="O90" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P90" t="n">
-        <v>29.8</v>
+        <v>27.2</v>
       </c>
       <c r="Q90" t="n">
-        <v>55.8</v>
+        <v>41.8</v>
       </c>
       <c r="R90" t="n">
-        <v>27.6</v>
+        <v>47.2</v>
       </c>
       <c r="S90" t="n">
-        <v>40.2</v>
+        <v>64.3</v>
       </c>
       <c r="T90" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U90" t="n">
-        <v>30.3</v>
+        <v>39.7</v>
       </c>
       <c r="V90" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z90" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W90" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X90" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y90" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z90" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB90" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB90" t="inlineStr"/>
       <c r="AC90" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -25297,134 +25293,142 @@
       </c>
       <c r="AH90" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AI90" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK90" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/20, 1 HR</t>
+          <t>Contact streak: 10/26 over last 7 games</t>
         </is>
       </c>
       <c r="AL90" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 10.4% barrel, 16.4 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.9% barrel, 12.4 HR allowed</t>
         </is>
       </c>
       <c r="AM90" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN90" t="inlineStr">
         <is>
-          <t>7.69</t>
+          <t>6.43</t>
         </is>
       </c>
       <c r="AO90" t="inlineStr">
         <is>
-          <t>34.56</t>
+          <t>36.01</t>
         </is>
       </c>
       <c r="AP90" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>88.65</t>
         </is>
       </c>
       <c r="AQ90" t="inlineStr">
         <is>
-          <t>98.8959</t>
+          <t>98.6212</t>
         </is>
       </c>
       <c r="AR90" t="inlineStr">
         <is>
-          <t>0.3878</t>
+          <t>0.4028</t>
         </is>
       </c>
       <c r="AS90" t="inlineStr">
         <is>
-          <t>0.1569</t>
+          <t>0.1453</t>
         </is>
       </c>
       <c r="AT90" t="inlineStr">
         <is>
-          <t>0.2868</t>
+          <t>0.3172</t>
         </is>
       </c>
       <c r="AU90" t="inlineStr">
         <is>
-          <t>71.81</t>
+          <t>69.75</t>
         </is>
       </c>
       <c r="AV90" t="inlineStr">
         <is>
-          <t>19.94</t>
+          <t>5.91</t>
         </is>
       </c>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>38.24</t>
+          <t>35.36</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>31.46</t>
+          <t>28.71</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr">
         <is>
-          <t>7.6</t>
+          <t>8.8</t>
         </is>
       </c>
       <c r="AZ90" t="inlineStr">
         <is>
-          <t>0.1323</t>
+          <t>0.1452</t>
         </is>
       </c>
       <c r="BA90" t="inlineStr">
         <is>
-          <t>10.41</t>
+          <t>7.91</t>
         </is>
       </c>
       <c r="BB90" t="inlineStr">
         <is>
-          <t>37.77</t>
+          <t>38.38</t>
         </is>
       </c>
       <c r="BC90" t="inlineStr">
         <is>
-          <t>88.92</t>
+          <t>88.67</t>
         </is>
       </c>
       <c r="BD90" t="inlineStr">
         <is>
-          <t>0.461</t>
+          <t>0.4436</t>
         </is>
       </c>
       <c r="BE90" t="inlineStr">
         <is>
-          <t>0.2077</t>
+          <t>0.1758</t>
         </is>
       </c>
       <c r="BF90" t="inlineStr">
         <is>
-          <t>38.09</t>
-        </is>
-      </c>
-      <c r="BG90" t="inlineStr"/>
-      <c r="BH90" t="inlineStr"/>
+          <t>25.26</t>
+        </is>
+      </c>
+      <c r="BG90" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH90" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
       <c r="BI90" t="inlineStr">
         <is>
-          <t>UNIQLO Field at Dodger Stadium</t>
+          <t>Kauffman Stadium</t>
         </is>
       </c>
       <c r="BJ90" t="inlineStr"/>
@@ -25435,47 +25439,47 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>681082</t>
+          <t>678662</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Bryson Stott</t>
+          <t>Ezequiel Tovar</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-07-06T18:10:00Z</t>
+          <t>2026-07-07T02:10:00Z</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>Noah Cameron</t>
+          <t>Eric Lauer</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>702070</t>
+          <t>641778</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -25484,7 +25488,7 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>41.4</v>
+        <v>41.5</v>
       </c>
       <c r="M91" t="inlineStr">
         <is>
@@ -25498,58 +25502,62 @@
       </c>
       <c r="O91" t="inlineStr">
         <is>
-          <t>No major boost</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P91" t="n">
-        <v>27.2</v>
+        <v>29.8</v>
       </c>
       <c r="Q91" t="n">
-        <v>41.8</v>
+        <v>55.8</v>
       </c>
       <c r="R91" t="n">
-        <v>47.2</v>
+        <v>27.6</v>
       </c>
       <c r="S91" t="n">
-        <v>64.3</v>
+        <v>40.2</v>
       </c>
       <c r="T91" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U91" t="n">
-        <v>36</v>
+        <v>30.3</v>
       </c>
       <c r="V91" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W91" t="inlineStr">
+      <c r="Z91" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X91" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y91" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z91" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB91" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB91" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC91" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -25569,142 +25577,134 @@
       </c>
       <c r="AH91" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI91" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
         <is>
-          <t>Contact streak: 9/25 over last 7 games</t>
+          <t>Last 7 games: 4/20, 1 HR</t>
         </is>
       </c>
       <c r="AL91" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.9% barrel, 12.4 HR allowed</t>
+          <t>platoon edge; pitcher baseline 10.4% barrel, 16.4 HR allowed</t>
         </is>
       </c>
       <c r="AM91" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN91" t="inlineStr">
         <is>
-          <t>6.43</t>
+          <t>7.69</t>
         </is>
       </c>
       <c r="AO91" t="inlineStr">
         <is>
-          <t>36.01</t>
+          <t>34.56</t>
         </is>
       </c>
       <c r="AP91" t="inlineStr">
         <is>
-          <t>88.65</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AQ91" t="inlineStr">
         <is>
-          <t>98.6212</t>
+          <t>98.8959</t>
         </is>
       </c>
       <c r="AR91" t="inlineStr">
         <is>
-          <t>0.4028</t>
+          <t>0.3878</t>
         </is>
       </c>
       <c r="AS91" t="inlineStr">
         <is>
-          <t>0.1453</t>
+          <t>0.1569</t>
         </is>
       </c>
       <c r="AT91" t="inlineStr">
         <is>
-          <t>0.3172</t>
+          <t>0.2868</t>
         </is>
       </c>
       <c r="AU91" t="inlineStr">
         <is>
-          <t>69.75</t>
+          <t>71.81</t>
         </is>
       </c>
       <c r="AV91" t="inlineStr">
         <is>
-          <t>5.91</t>
+          <t>19.94</t>
         </is>
       </c>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>35.36</t>
+          <t>38.24</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>28.71</t>
+          <t>31.46</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr">
         <is>
-          <t>8.8</t>
+          <t>7.6</t>
         </is>
       </c>
       <c r="AZ91" t="inlineStr">
         <is>
-          <t>0.1452</t>
+          <t>0.1323</t>
         </is>
       </c>
       <c r="BA91" t="inlineStr">
         <is>
-          <t>7.91</t>
+          <t>10.41</t>
         </is>
       </c>
       <c r="BB91" t="inlineStr">
         <is>
-          <t>38.38</t>
+          <t>37.77</t>
         </is>
       </c>
       <c r="BC91" t="inlineStr">
         <is>
-          <t>88.67</t>
+          <t>88.92</t>
         </is>
       </c>
       <c r="BD91" t="inlineStr">
         <is>
-          <t>0.4436</t>
+          <t>0.461</t>
         </is>
       </c>
       <c r="BE91" t="inlineStr">
         <is>
-          <t>0.1758</t>
+          <t>0.2077</t>
         </is>
       </c>
       <c r="BF91" t="inlineStr">
         <is>
-          <t>25.26</t>
-        </is>
-      </c>
-      <c r="BG91" t="inlineStr">
-        <is>
-          <t>L To R</t>
-        </is>
-      </c>
-      <c r="BH91" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
+          <t>38.09</t>
+        </is>
+      </c>
+      <c r="BG91" t="inlineStr"/>
+      <c r="BH91" t="inlineStr"/>
       <c r="BI91" t="inlineStr">
         <is>
-          <t>Kauffman Stadium</t>
+          <t>UNIQLO Field at Dodger Stadium</t>
         </is>
       </c>
       <c r="BJ91" t="inlineStr"/>
@@ -40774,7 +40774,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>58.3</v>
+        <v>58.2</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -40807,7 +40807,7 @@
         <v>78</v>
       </c>
       <c r="U10" t="n">
-        <v>57.8</v>
+        <v>56.2</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
@@ -40864,7 +40864,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">

--- a/outputs/hr_rankings.xlsx
+++ b/outputs/hr_rankings.xlsx
@@ -760,7 +760,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Player challenge</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -784,7 +784,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>77.40000000000001</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -817,7 +817,7 @@
         <v>80</v>
       </c>
       <c r="U2" t="n">
-        <v>94.7</v>
+        <v>99.5</v>
       </c>
       <c r="V2" t="inlineStr">
         <is>
@@ -874,7 +874,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Player challenge</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Player challenge</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -3280,7 +3280,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -5771,47 +5771,47 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>572233</t>
+          <t>665487</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Christian Walker</t>
+          <t>Fernando Tatis Jr.</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>WSH</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-07-06T22:45:00Z</t>
+          <t>2026-07-07T01:40:00Z</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Miles Mikolas</t>
+          <t>Brandon Pfaadt</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>571945</t>
+          <t>694297</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -5820,7 +5820,7 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>57.7</v>
+        <v>57.6</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
@@ -5838,22 +5838,22 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>44.4</v>
+        <v>50.2</v>
       </c>
       <c r="Q20" t="n">
-        <v>57.9</v>
+        <v>56.1</v>
       </c>
       <c r="R20" t="n">
-        <v>61.2</v>
+        <v>46.1</v>
       </c>
       <c r="S20" t="n">
-        <v>94.90000000000001</v>
+        <v>93.2</v>
       </c>
       <c r="T20" t="n">
         <v>50</v>
       </c>
       <c r="U20" t="n">
-        <v>44.8</v>
+        <v>62.2</v>
       </c>
       <c r="V20" t="inlineStr">
         <is>
@@ -5867,7 +5867,7 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
@@ -5905,12 +5905,12 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>31</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
@@ -5925,122 +5925,122 @@
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 10.1% barrel, 21.3 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 11.5% barrel, 13.4 HR allowed</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>11.08</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>44.42</t>
+          <t>52.57</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>90.13</t>
+          <t>92.25</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>101.7846</t>
+          <t>104.1997</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>0.4042</t>
+          <t>0.4495</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
         <is>
-          <t>0.1764</t>
+          <t>0.168</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>0.3056</t>
+          <t>0.3574</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
         <is>
-          <t>74.17</t>
+          <t>75.19</t>
         </is>
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>42.32</t>
+          <t>56.14</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>43.74</t>
+          <t>31.44</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>28.56</t>
+          <t>21.52</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>22.1</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>0.2173</t>
+          <t>0.1248</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>10.11</t>
+          <t>11.53</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>40.75</t>
+          <t>41.04</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>89.65</t>
+          <t>89.89</t>
         </is>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>0.4899</t>
+          <t>0.4632</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
-          <t>0.2172</t>
+          <t>0.2044</t>
         </is>
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>28.35</t>
+          <t>21.59</t>
         </is>
       </c>
       <c r="BG20" t="inlineStr">
         <is>
-          <t>Out To LF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
         <is>
-          <t>Nationals Park</t>
+          <t>Petco Park</t>
         </is>
       </c>
       <c r="BJ20" t="inlineStr"/>
@@ -6051,27 +6051,27 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>665487</t>
+          <t>606192</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Fernando Tatis Jr.</t>
+          <t>Teoscar Hernández</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-07-07T01:40:00Z</t>
+          <t>2026-07-07T02:10:00Z</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -6081,22 +6081,22 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Brandon Pfaadt</t>
+          <t>Kyle Freeland</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>694297</t>
+          <t>607536</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L21" t="n">
@@ -6114,26 +6114,26 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P21" t="n">
-        <v>50.2</v>
+        <v>45.8</v>
       </c>
       <c r="Q21" t="n">
-        <v>56.1</v>
+        <v>59.9</v>
       </c>
       <c r="R21" t="n">
-        <v>46.1</v>
+        <v>62.6</v>
       </c>
       <c r="S21" t="n">
-        <v>93.2</v>
+        <v>76.2</v>
       </c>
       <c r="T21" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U21" t="n">
-        <v>62.2</v>
+        <v>19.9</v>
       </c>
       <c r="V21" t="inlineStr">
         <is>
@@ -6147,7 +6147,7 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
@@ -6185,142 +6185,142 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 3/23, 1 HR</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 11.5% barrel, 13.4 HR allowed</t>
+          <t>platoon edge; pitcher baseline 10.2% barrel, 17.8 HR allowed</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>EV profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>11.0</t>
+          <t>10.87</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>52.57</t>
+          <t>45.89</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>92.25</t>
+          <t>90.27</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>104.1997</t>
+          <t>101.01</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>0.4495</t>
+          <t>0.4361</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
         <is>
-          <t>0.168</t>
+          <t>0.1871</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>0.3574</t>
+          <t>0.3286</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
         <is>
-          <t>75.19</t>
+          <t>72.41</t>
         </is>
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>56.14</t>
+          <t>25.12</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>31.44</t>
+          <t>33.94</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>21.52</t>
+          <t>29.52</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>11.0</t>
+          <t>13.1</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>0.1248</t>
+          <t>0.1727</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>11.53</t>
+          <t>10.24</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>41.04</t>
+          <t>44.71</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>89.89</t>
+          <t>90.89</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>0.4632</t>
+          <t>0.4856</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
-          <t>0.2044</t>
+          <t>0.1959</t>
         </is>
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>21.59</t>
+          <t>28.8</t>
         </is>
       </c>
       <c r="BG21" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>70</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
         <is>
-          <t>Petco Park</t>
+          <t>UNIQLO Field at Dodger Stadium</t>
         </is>
       </c>
       <c r="BJ21" t="inlineStr"/>
@@ -6331,27 +6331,27 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>606192</t>
+          <t>691023</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Teoscar Hernández</t>
+          <t>Jordan Walker</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-07-07T02:10:00Z</t>
+          <t>2026-07-06T23:45:00Z</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -6361,17 +6361,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Kyle Freeland</t>
+          <t>Shane Drohan</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>607536</t>
+          <t>675660</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -6380,7 +6380,7 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>57.6</v>
+        <v>57.5</v>
       </c>
       <c r="M22" t="inlineStr">
         <is>
@@ -6394,26 +6394,26 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>Strong Barrel, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P22" t="n">
-        <v>45.8</v>
+        <v>60.1</v>
       </c>
       <c r="Q22" t="n">
-        <v>59.9</v>
+        <v>32</v>
       </c>
       <c r="R22" t="n">
-        <v>62.6</v>
+        <v>41.1</v>
       </c>
       <c r="S22" t="n">
-        <v>76.2</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T22" t="n">
         <v>78</v>
       </c>
       <c r="U22" t="n">
-        <v>19.9</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="V22" t="inlineStr">
         <is>
@@ -6427,7 +6427,7 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
@@ -6448,7 +6448,7 @@
       <c r="AB22" t="inlineStr"/>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD22" t="inlineStr"/>
@@ -6465,142 +6465,142 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/23, 1 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 10.2% barrel, 17.8 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.7% barrel, 5.0 HR allowed</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>10.87</t>
+          <t>13.21</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>45.89</t>
+          <t>50.7</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>90.27</t>
+          <t>93.42</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>101.01</t>
+          <t>105.0535</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>0.4361</t>
+          <t>0.4652</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
         <is>
-          <t>0.1871</t>
+          <t>0.2061</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>0.3286</t>
+          <t>0.341</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
         <is>
-          <t>72.41</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>25.12</t>
+          <t>83.33</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>33.94</t>
+          <t>37.54</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>29.52</t>
+          <t>24.54</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>13.1</t>
+          <t>15.8</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>0.1727</t>
+          <t>0.1932</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>10.24</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>44.71</t>
+          <t>36.2</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>90.89</t>
+          <t>87.7</t>
         </is>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>0.4856</t>
+          <t>0.355</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
-          <t>0.1959</t>
+          <t>0.125</t>
         </is>
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>28.8</t>
+          <t>27.0</t>
         </is>
       </c>
       <c r="BG22" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>In From LF</t>
         </is>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>86</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
         <is>
-          <t>UNIQLO Field at Dodger Stadium</t>
+          <t>Busch Stadium</t>
         </is>
       </c>
       <c r="BJ22" t="inlineStr"/>
@@ -6611,56 +6611,56 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>691023</t>
+          <t>663757</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Jordan Walker</t>
+          <t>Trent Grisham</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-07-06T23:45:00Z</t>
+          <t>2026-07-06T22:40:00Z</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Shane Drohan</t>
+          <t>Griffin Jax</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>675660</t>
+          <t>643377</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L23" t="n">
-        <v>57.5</v>
+        <v>57.3</v>
       </c>
       <c r="M23" t="inlineStr">
         <is>
@@ -6678,22 +6678,22 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>60.1</v>
+        <v>50.7</v>
       </c>
       <c r="Q23" t="n">
-        <v>32</v>
+        <v>49.4</v>
       </c>
       <c r="R23" t="n">
         <v>41.1</v>
       </c>
       <c r="S23" t="n">
-        <v>96.59999999999999</v>
+        <v>93.2</v>
       </c>
       <c r="T23" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U23" t="n">
-        <v>66.40000000000001</v>
+        <v>46</v>
       </c>
       <c r="V23" t="inlineStr">
         <is>
@@ -6707,7 +6707,7 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
@@ -6728,7 +6728,7 @@
       <c r="AB23" t="inlineStr"/>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD23" t="inlineStr"/>
@@ -6750,137 +6750,137 @@
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 7/23, 1 HR</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.7% barrel, 5.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 10.3% barrel, 9.8 HR allowed</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>EV profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>13.21</t>
+          <t>12.38</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>50.7</t>
+          <t>46.33</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>93.42</t>
+          <t>90.96</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>105.0535</t>
+          <t>100.9153</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>0.4652</t>
+          <t>0.463</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
         <is>
-          <t>0.2061</t>
+          <t>0.2115</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>0.341</t>
+          <t>0.3581</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>70.23</t>
         </is>
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>83.33</t>
+          <t>7.58</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>37.54</t>
+          <t>43.81</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>24.54</t>
+          <t>31.4</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>15.8</t>
+          <t>16.5</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>0.1932</t>
+          <t>0.1982</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>10.31</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>36.2</t>
+          <t>42.21</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>87.7</t>
+          <t>88.99</t>
         </is>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
-          <t>0.355</t>
+          <t>0.4458</t>
         </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
-          <t>0.125</t>
+          <t>0.1828</t>
         </is>
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>27.0</t>
+          <t>22.74</t>
         </is>
       </c>
       <c r="BG23" t="inlineStr">
         <is>
-          <t>In From LF</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
         <is>
-          <t>Busch Stadium</t>
+          <t>Tropicana Field</t>
         </is>
       </c>
       <c r="BJ23" t="inlineStr"/>
@@ -6891,32 +6891,32 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>663757</t>
+          <t>671739</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Trent Grisham</t>
+          <t>Michael Harris II</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>NYM</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-07-06T22:40:00Z</t>
+          <t>2026-07-06T23:15:00Z</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -6926,12 +6926,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Griffin Jax</t>
+          <t>Freddy Peralta</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>643377</t>
+          <t>642547</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -6958,13 +6958,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>50.7</v>
+        <v>54.1</v>
       </c>
       <c r="Q24" t="n">
-        <v>49.4</v>
+        <v>30.2</v>
       </c>
       <c r="R24" t="n">
-        <v>41.1</v>
+        <v>57.4</v>
       </c>
       <c r="S24" t="n">
         <v>93.2</v>
@@ -6973,7 +6973,7 @@
         <v>80</v>
       </c>
       <c r="U24" t="n">
-        <v>46</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="V24" t="inlineStr">
         <is>
@@ -7025,27 +7025,27 @@
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/23, 1 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL24" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 10.3% barrel, 9.8 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.2% barrel, 15.4 HR allowed</t>
         </is>
       </c>
       <c r="AM24" t="inlineStr">
@@ -7055,112 +7055,112 @@
       </c>
       <c r="AN24" t="inlineStr">
         <is>
-          <t>12.38</t>
+          <t>12.46</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>46.33</t>
+          <t>48.44</t>
         </is>
       </c>
       <c r="AP24" t="inlineStr">
         <is>
-          <t>90.96</t>
+          <t>91.39</t>
         </is>
       </c>
       <c r="AQ24" t="inlineStr">
         <is>
-          <t>100.9153</t>
+          <t>103.9802</t>
         </is>
       </c>
       <c r="AR24" t="inlineStr">
         <is>
-          <t>0.463</t>
+          <t>0.5024</t>
         </is>
       </c>
       <c r="AS24" t="inlineStr">
         <is>
-          <t>0.2115</t>
+          <t>0.2082</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr">
         <is>
-          <t>0.3581</t>
+          <t>0.3563</t>
         </is>
       </c>
       <c r="AU24" t="inlineStr">
         <is>
-          <t>70.23</t>
+          <t>74.72</t>
         </is>
       </c>
       <c r="AV24" t="inlineStr">
         <is>
-          <t>7.58</t>
+          <t>46.37</t>
         </is>
       </c>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>43.81</t>
+          <t>33.91</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>31.4</t>
+          <t>23.4</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
-          <t>16.5</t>
+          <t>17.2</t>
         </is>
       </c>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>0.1982</t>
+          <t>0.1901</t>
         </is>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
-          <t>10.31</t>
+          <t>6.22</t>
         </is>
       </c>
       <c r="BB24" t="inlineStr">
         <is>
-          <t>42.21</t>
+          <t>37.79</t>
         </is>
       </c>
       <c r="BC24" t="inlineStr">
         <is>
-          <t>88.99</t>
+          <t>87.86</t>
         </is>
       </c>
       <c r="BD24" t="inlineStr">
         <is>
-          <t>0.4458</t>
+          <t>0.3617</t>
         </is>
       </c>
       <c r="BE24" t="inlineStr">
         <is>
-          <t>0.1828</t>
+          <t>0.1347</t>
         </is>
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>22.74</t>
+          <t>26.17</t>
         </is>
       </c>
       <c r="BG24" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>R To L</t>
         </is>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>84</t>
         </is>
       </c>
       <c r="BI24" t="inlineStr">
         <is>
-          <t>Tropicana Field</t>
+          <t>Truist Park</t>
         </is>
       </c>
       <c r="BJ24" t="inlineStr"/>
@@ -7171,12 +7171,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>671739</t>
+          <t>686948</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Michael Harris II</t>
+          <t>Drake Baldwin</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -7196,12 +7196,12 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -7220,7 +7220,7 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>57.3</v>
+        <v>57.1</v>
       </c>
       <c r="M25" t="inlineStr">
         <is>
@@ -7238,7 +7238,7 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>54.1</v>
+        <v>58.9</v>
       </c>
       <c r="Q25" t="n">
         <v>30.2</v>
@@ -7247,13 +7247,13 @@
         <v>57.4</v>
       </c>
       <c r="S25" t="n">
-        <v>93.2</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T25" t="n">
         <v>80</v>
       </c>
       <c r="U25" t="n">
-        <v>66.90000000000001</v>
+        <v>27.1</v>
       </c>
       <c r="V25" t="inlineStr">
         <is>
@@ -7267,7 +7267,7 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
@@ -7305,7 +7305,7 @@
       </c>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI25" t="inlineStr">
@@ -7315,12 +7315,12 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 5/28, 1 HR</t>
         </is>
       </c>
       <c r="AL25" t="inlineStr">
@@ -7335,67 +7335,67 @@
       </c>
       <c r="AN25" t="inlineStr">
         <is>
-          <t>12.46</t>
+          <t>14.5</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>48.44</t>
+          <t>48.76</t>
         </is>
       </c>
       <c r="AP25" t="inlineStr">
         <is>
-          <t>91.39</t>
+          <t>91.21</t>
         </is>
       </c>
       <c r="AQ25" t="inlineStr">
         <is>
-          <t>103.9802</t>
+          <t>102.4409</t>
         </is>
       </c>
       <c r="AR25" t="inlineStr">
         <is>
-          <t>0.5024</t>
+          <t>0.501</t>
         </is>
       </c>
       <c r="AS25" t="inlineStr">
         <is>
-          <t>0.2082</t>
+          <t>0.2304</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr">
         <is>
-          <t>0.3563</t>
+          <t>0.367</t>
         </is>
       </c>
       <c r="AU25" t="inlineStr">
         <is>
-          <t>74.72</t>
+          <t>75.09</t>
         </is>
       </c>
       <c r="AV25" t="inlineStr">
         <is>
-          <t>46.37</t>
+          <t>54.02</t>
         </is>
       </c>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>33.91</t>
+          <t>32.22</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>23.4</t>
+          <t>23.5</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
-          <t>17.2</t>
+          <t>16.2</t>
         </is>
       </c>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>0.1901</t>
+          <t>0.1985</t>
         </is>
       </c>
       <c r="BA25" t="inlineStr">
@@ -7451,27 +7451,27 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>686948</t>
+          <t>605141</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Drake Baldwin</t>
+          <t>Mookie Betts</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>NYM</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-07-06T23:15:00Z</t>
+          <t>2026-07-07T02:10:00Z</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -7486,17 +7486,17 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Freddy Peralta</t>
+          <t>Kyle Freeland</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>642547</t>
+          <t>607536</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L26" t="n">
@@ -7514,26 +7514,26 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P26" t="n">
-        <v>58.9</v>
+        <v>35</v>
       </c>
       <c r="Q26" t="n">
-        <v>30.2</v>
+        <v>59.9</v>
       </c>
       <c r="R26" t="n">
-        <v>57.4</v>
+        <v>62.6</v>
       </c>
       <c r="S26" t="n">
         <v>94.90000000000001</v>
       </c>
       <c r="T26" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="U26" t="n">
-        <v>27.1</v>
+        <v>28.6</v>
       </c>
       <c r="V26" t="inlineStr">
         <is>
@@ -7585,142 +7585,142 @@
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/28, 1 HR</t>
+          <t>Last 7 games: 9/29, 0 HR</t>
         </is>
       </c>
       <c r="AL26" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.2% barrel, 15.4 HR allowed</t>
+          <t>platoon edge; pitcher baseline 10.2% barrel, 17.8 HR allowed</t>
         </is>
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN26" t="inlineStr">
         <is>
-          <t>14.5</t>
+          <t>7.46</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>48.76</t>
+          <t>37.97</t>
         </is>
       </c>
       <c r="AP26" t="inlineStr">
         <is>
-          <t>91.21</t>
+          <t>90.22</t>
         </is>
       </c>
       <c r="AQ26" t="inlineStr">
         <is>
-          <t>102.4409</t>
+          <t>98.6577</t>
         </is>
       </c>
       <c r="AR26" t="inlineStr">
         <is>
-          <t>0.501</t>
+          <t>0.4388</t>
         </is>
       </c>
       <c r="AS26" t="inlineStr">
         <is>
-          <t>0.2304</t>
+          <t>0.1616</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr">
         <is>
-          <t>0.367</t>
+          <t>0.337</t>
         </is>
       </c>
       <c r="AU26" t="inlineStr">
         <is>
-          <t>75.09</t>
+          <t>69.42</t>
         </is>
       </c>
       <c r="AV26" t="inlineStr">
         <is>
-          <t>54.02</t>
+          <t>8.21</t>
         </is>
       </c>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>32.22</t>
+          <t>40.45</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>23.5</t>
+          <t>35.76</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
-          <t>16.2</t>
+          <t>13.7</t>
         </is>
       </c>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>0.1985</t>
+          <t>0.1809</t>
         </is>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
-          <t>6.22</t>
+          <t>10.24</t>
         </is>
       </c>
       <c r="BB26" t="inlineStr">
         <is>
-          <t>37.79</t>
+          <t>44.71</t>
         </is>
       </c>
       <c r="BC26" t="inlineStr">
         <is>
-          <t>87.86</t>
+          <t>90.89</t>
         </is>
       </c>
       <c r="BD26" t="inlineStr">
         <is>
-          <t>0.3617</t>
+          <t>0.4856</t>
         </is>
       </c>
       <c r="BE26" t="inlineStr">
         <is>
-          <t>0.1347</t>
+          <t>0.1959</t>
         </is>
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>26.17</t>
+          <t>28.8</t>
         </is>
       </c>
       <c r="BG26" t="inlineStr">
         <is>
-          <t>R To L</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>70</t>
         </is>
       </c>
       <c r="BI26" t="inlineStr">
         <is>
-          <t>Truist Park</t>
+          <t>UNIQLO Field at Dodger Stadium</t>
         </is>
       </c>
       <c r="BJ26" t="inlineStr"/>
@@ -7731,27 +7731,27 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>605141</t>
+          <t>682998</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Mookie Betts</t>
+          <t>Corbin Carroll</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-07-07T02:10:00Z</t>
+          <t>2026-07-07T01:40:00Z</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -7761,26 +7761,26 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Kyle Freeland</t>
+          <t>Walker Buehler</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>607536</t>
+          <t>621111</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L27" t="n">
-        <v>57.1</v>
+        <v>56.8</v>
       </c>
       <c r="M27" t="inlineStr">
         <is>
@@ -7794,50 +7794,42 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P27" t="n">
-        <v>35</v>
+        <v>56.3</v>
       </c>
       <c r="Q27" t="n">
-        <v>59.9</v>
+        <v>44.2</v>
       </c>
       <c r="R27" t="n">
-        <v>62.6</v>
+        <v>46.1</v>
       </c>
       <c r="S27" t="n">
-        <v>94.90000000000001</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T27" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U27" t="n">
-        <v>28.6</v>
+        <v>0</v>
       </c>
       <c r="V27" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W27" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="X27" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+      <c r="W27" t="inlineStr"/>
+      <c r="X27" t="inlineStr"/>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -7845,7 +7837,11 @@
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB27" t="inlineStr"/>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>not found on RotoWire</t>
+        </is>
+      </c>
       <c r="AC27" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -7865,12 +7861,12 @@
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ27" t="inlineStr">
@@ -7880,127 +7876,127 @@
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>Last 7 games: 9/29, 0 HR</t>
+          <t>Last 7 games: 2/25, 0 HR</t>
         </is>
       </c>
       <c r="AL27" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 10.2% barrel, 17.8 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.9% barrel, 12.9 HR allowed</t>
         </is>
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN27" t="inlineStr">
         <is>
-          <t>7.46</t>
+          <t>12.68</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>37.97</t>
+          <t>48.08</t>
         </is>
       </c>
       <c r="AP27" t="inlineStr">
         <is>
-          <t>90.22</t>
+          <t>91.68</t>
         </is>
       </c>
       <c r="AQ27" t="inlineStr">
         <is>
-          <t>98.6577</t>
+          <t>102.5754</t>
         </is>
       </c>
       <c r="AR27" t="inlineStr">
         <is>
-          <t>0.4388</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AS27" t="inlineStr">
         <is>
-          <t>0.1616</t>
+          <t>0.2194</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr">
         <is>
-          <t>0.337</t>
+          <t>0.3587</t>
         </is>
       </c>
       <c r="AU27" t="inlineStr">
         <is>
-          <t>69.42</t>
+          <t>75.26</t>
         </is>
       </c>
       <c r="AV27" t="inlineStr">
         <is>
-          <t>8.21</t>
+          <t>55.68</t>
         </is>
       </c>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>40.45</t>
+          <t>45.69</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>35.76</t>
+          <t>28.85</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
-          <t>13.7</t>
+          <t>18.4</t>
         </is>
       </c>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>0.1809</t>
+          <t>0.2526</t>
         </is>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
-          <t>10.24</t>
+          <t>8.94</t>
         </is>
       </c>
       <c r="BB27" t="inlineStr">
         <is>
-          <t>44.71</t>
+          <t>40.53</t>
         </is>
       </c>
       <c r="BC27" t="inlineStr">
         <is>
-          <t>90.89</t>
+          <t>89.72</t>
         </is>
       </c>
       <c r="BD27" t="inlineStr">
         <is>
-          <t>0.4856</t>
+          <t>0.4248</t>
         </is>
       </c>
       <c r="BE27" t="inlineStr">
         <is>
-          <t>0.1959</t>
+          <t>0.161</t>
         </is>
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>28.8</t>
+          <t>21.97</t>
         </is>
       </c>
       <c r="BG27" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI27" t="inlineStr">
         <is>
-          <t>UNIQLO Field at Dodger Stadium</t>
+          <t>Petco Park</t>
         </is>
       </c>
       <c r="BJ27" t="inlineStr"/>
@@ -8011,47 +8007,47 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>682998</t>
+          <t>572233</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Corbin Carroll</t>
+          <t>Christian Walker</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>WSH</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-07-07T01:40:00Z</t>
+          <t>2026-07-06T22:45:00Z</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Player challenge</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Walker Buehler</t>
+          <t>Miles Mikolas</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>621111</t>
+          <t>571945</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -8060,7 +8056,7 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>56.8</v>
+        <v>56.7</v>
       </c>
       <c r="M28" t="inlineStr">
         <is>
@@ -8074,54 +8070,58 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P28" t="n">
-        <v>56.3</v>
+        <v>44.4</v>
       </c>
       <c r="Q28" t="n">
-        <v>44.2</v>
+        <v>57.9</v>
       </c>
       <c r="R28" t="n">
-        <v>46.1</v>
+        <v>61.2</v>
       </c>
       <c r="S28" t="n">
-        <v>96.59999999999999</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T28" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="V28" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W28" t="inlineStr"/>
-      <c r="X28" t="inlineStr"/>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="Y28" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB28" t="inlineStr"/>
       <c r="AC28" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8141,27 +8141,27 @@
       </c>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/25, 0 HR</t>
+          <t>Last 7 games: 3/19, 1 HR</t>
         </is>
       </c>
       <c r="AL28" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.9% barrel, 12.9 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 10.1% barrel, 21.3 HR allowed</t>
         </is>
       </c>
       <c r="AM28" t="inlineStr">
@@ -8171,112 +8171,112 @@
       </c>
       <c r="AN28" t="inlineStr">
         <is>
-          <t>12.68</t>
+          <t>11.08</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>48.08</t>
+          <t>44.42</t>
         </is>
       </c>
       <c r="AP28" t="inlineStr">
         <is>
-          <t>91.68</t>
+          <t>90.13</t>
         </is>
       </c>
       <c r="AQ28" t="inlineStr">
         <is>
-          <t>102.5754</t>
+          <t>101.7846</t>
         </is>
       </c>
       <c r="AR28" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.4042</t>
         </is>
       </c>
       <c r="AS28" t="inlineStr">
         <is>
-          <t>0.2194</t>
+          <t>0.1764</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr">
         <is>
-          <t>0.3587</t>
+          <t>0.3056</t>
         </is>
       </c>
       <c r="AU28" t="inlineStr">
         <is>
-          <t>75.26</t>
+          <t>74.17</t>
         </is>
       </c>
       <c r="AV28" t="inlineStr">
         <is>
-          <t>55.68</t>
+          <t>42.32</t>
         </is>
       </c>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>45.69</t>
+          <t>43.74</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>28.85</t>
+          <t>28.56</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
-          <t>18.4</t>
+          <t>22.1</t>
         </is>
       </c>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>0.2526</t>
+          <t>0.2173</t>
         </is>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
-          <t>8.94</t>
+          <t>10.11</t>
         </is>
       </c>
       <c r="BB28" t="inlineStr">
         <is>
-          <t>40.53</t>
+          <t>40.75</t>
         </is>
       </c>
       <c r="BC28" t="inlineStr">
         <is>
-          <t>89.72</t>
+          <t>89.65</t>
         </is>
       </c>
       <c r="BD28" t="inlineStr">
         <is>
-          <t>0.4248</t>
+          <t>0.4899</t>
         </is>
       </c>
       <c r="BE28" t="inlineStr">
         <is>
-          <t>0.161</t>
+          <t>0.2172</t>
         </is>
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>21.97</t>
+          <t>28.35</t>
         </is>
       </c>
       <c r="BG28" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>Out To LF</t>
         </is>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>80</t>
         </is>
       </c>
       <c r="BI28" t="inlineStr">
         <is>
-          <t>Petco Park</t>
+          <t>Nationals Park</t>
         </is>
       </c>
       <c r="BJ28" t="inlineStr"/>
@@ -9992,7 +9992,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Player challenge</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -10016,7 +10016,7 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>55.5</v>
+        <v>55.7</v>
       </c>
       <c r="M35" t="inlineStr">
         <is>
@@ -10049,7 +10049,7 @@
         <v>50</v>
       </c>
       <c r="U35" t="n">
-        <v>53.3</v>
+        <v>57.8</v>
       </c>
       <c r="V35" t="inlineStr">
         <is>
@@ -10106,7 +10106,7 @@
       </c>
       <c r="AI35" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ35" t="inlineStr">
@@ -10272,7 +10272,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -10552,7 +10552,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Player challenge</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -12508,7 +12508,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Player challenge</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -13348,7 +13348,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Player challenge</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -13628,7 +13628,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Player challenge</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -13652,7 +13652,7 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>51.6</v>
+        <v>51.8</v>
       </c>
       <c r="M48" t="inlineStr">
         <is>
@@ -13685,7 +13685,7 @@
         <v>50</v>
       </c>
       <c r="U48" t="n">
-        <v>26.4</v>
+        <v>30</v>
       </c>
       <c r="V48" t="inlineStr">
         <is>
@@ -13742,7 +13742,7 @@
       </c>
       <c r="AI48" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ48" t="inlineStr">
@@ -13752,7 +13752,7 @@
       </c>
       <c r="AK48" t="inlineStr">
         <is>
-          <t>Last 7 games: 8/27, 0 HR</t>
+          <t>Contact streak: 8/25 over last 7 games</t>
         </is>
       </c>
       <c r="AL48" t="inlineStr">
@@ -14468,7 +14468,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -14748,7 +14748,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -15028,7 +15028,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Player challenge</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -15308,7 +15308,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -15588,7 +15588,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Player challenge</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -16708,7 +16708,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -18944,7 +18944,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -19504,7 +19504,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Player challenge</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -20904,7 +20904,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -21184,7 +21184,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Player challenge</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -22304,7 +22304,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Player challenge</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -22864,7 +22864,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Player challenge</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -23704,7 +23704,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -23984,7 +23984,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -25660,7 +25660,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -26220,7 +26220,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -27056,7 +27056,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -27336,7 +27336,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Player challenge</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -28456,7 +28456,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -31804,7 +31804,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Player challenge</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -33459,47 +33459,47 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>686452</t>
+          <t>805347</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Drew Millas</t>
+          <t>Jim Jarvis</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>WSH</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>NYM</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>2026-07-06T22:45:00Z</t>
+          <t>2026-07-06T23:15:00Z</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>Mike Burrows</t>
+          <t>Freddy Peralta</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>681347</t>
+          <t>642547</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
@@ -33508,7 +33508,7 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>34.9</v>
+        <v>34.7</v>
       </c>
       <c r="M119" t="inlineStr">
         <is>
@@ -33526,22 +33526,22 @@
         </is>
       </c>
       <c r="P119" t="n">
-        <v>1.1</v>
+        <v>15</v>
       </c>
       <c r="Q119" t="n">
-        <v>43.7</v>
+        <v>30.2</v>
       </c>
       <c r="R119" t="n">
-        <v>61.2</v>
+        <v>57.4</v>
       </c>
       <c r="S119" t="n">
-        <v>52.4</v>
+        <v>44.8</v>
       </c>
       <c r="T119" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="U119" t="n">
-        <v>16.1</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="V119" t="inlineStr">
         <is>
@@ -33555,7 +33555,7 @@
       </c>
       <c r="X119" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y119" t="inlineStr">
@@ -33576,7 +33576,7 @@
       <c r="AB119" t="inlineStr"/>
       <c r="AC119" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD119" t="inlineStr"/>
@@ -33588,17 +33588,17 @@
       </c>
       <c r="AG119" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AH119" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI119" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AJ119" t="inlineStr">
@@ -33608,12 +33608,12 @@
       </c>
       <c r="AK119" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/22, 0 HR</t>
+          <t>Last 4 games: 2/11, 0 HR</t>
         </is>
       </c>
       <c r="AL119" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 9.1% barrel, 17.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.2% barrel, 15.4 HR allowed</t>
         </is>
       </c>
       <c r="AM119" t="inlineStr">
@@ -33623,112 +33623,112 @@
       </c>
       <c r="AN119" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AO119" t="inlineStr">
         <is>
-          <t>22.04</t>
+          <t>37.5</t>
         </is>
       </c>
       <c r="AP119" t="inlineStr">
         <is>
-          <t>83.89</t>
+          <t>89.5</t>
         </is>
       </c>
       <c r="AQ119" t="inlineStr">
         <is>
-          <t>94.7821</t>
+          <t>97.3227</t>
         </is>
       </c>
       <c r="AR119" t="inlineStr">
         <is>
-          <t>0.3044</t>
+          <t>0.239</t>
         </is>
       </c>
       <c r="AS119" t="inlineStr">
         <is>
-          <t>0.0786</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AT119" t="inlineStr">
         <is>
-          <t>0.2784</t>
+          <t>0.197</t>
         </is>
       </c>
       <c r="AU119" t="inlineStr">
         <is>
-          <t>67.68</t>
+          <t>70.9</t>
         </is>
       </c>
       <c r="AV119" t="inlineStr">
         <is>
-          <t>4.2</t>
+          <t>13.6</t>
         </is>
       </c>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>36.78</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>18.47</t>
+          <t>12.5</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ119" t="inlineStr">
         <is>
-          <t>0.0989</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="BA119" t="inlineStr">
         <is>
-          <t>9.05</t>
+          <t>6.22</t>
         </is>
       </c>
       <c r="BB119" t="inlineStr">
         <is>
-          <t>38.99</t>
+          <t>37.79</t>
         </is>
       </c>
       <c r="BC119" t="inlineStr">
         <is>
-          <t>88.36</t>
+          <t>87.86</t>
         </is>
       </c>
       <c r="BD119" t="inlineStr">
         <is>
-          <t>0.4292</t>
+          <t>0.3617</t>
         </is>
       </c>
       <c r="BE119" t="inlineStr">
         <is>
-          <t>0.1738</t>
+          <t>0.1347</t>
         </is>
       </c>
       <c r="BF119" t="inlineStr">
         <is>
-          <t>27.68</t>
+          <t>26.17</t>
         </is>
       </c>
       <c r="BG119" t="inlineStr">
         <is>
-          <t>Out To LF</t>
+          <t>R To L</t>
         </is>
       </c>
       <c r="BH119" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>84</t>
         </is>
       </c>
       <c r="BI119" t="inlineStr">
         <is>
-          <t>Nationals Park</t>
+          <t>Truist Park</t>
         </is>
       </c>
       <c r="BJ119" t="inlineStr"/>
@@ -33739,27 +33739,27 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>805347</t>
+          <t>666152</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Jim Jarvis</t>
+          <t>David Hamilton</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>NYM</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>2026-07-06T23:15:00Z</t>
+          <t>2026-07-06T23:45:00Z</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
@@ -33774,12 +33774,12 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>Freddy Peralta</t>
+          <t>Dustin May</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>642547</t>
+          <t>669160</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
@@ -33788,7 +33788,7 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>34.7</v>
+        <v>34.5</v>
       </c>
       <c r="M120" t="inlineStr">
         <is>
@@ -33806,13 +33806,13 @@
         </is>
       </c>
       <c r="P120" t="n">
-        <v>15</v>
+        <v>11.2</v>
       </c>
       <c r="Q120" t="n">
-        <v>30.2</v>
+        <v>42.9</v>
       </c>
       <c r="R120" t="n">
-        <v>57.4</v>
+        <v>41.1</v>
       </c>
       <c r="S120" t="n">
         <v>44.8</v>
@@ -33821,7 +33821,7 @@
         <v>80</v>
       </c>
       <c r="U120" t="n">
-        <v>9.300000000000001</v>
+        <v>16.6</v>
       </c>
       <c r="V120" t="inlineStr">
         <is>
@@ -33856,7 +33856,7 @@
       <c r="AB120" t="inlineStr"/>
       <c r="AC120" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD120" t="inlineStr"/>
@@ -33868,17 +33868,17 @@
       </c>
       <c r="AG120" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AH120" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI120" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AJ120" t="inlineStr">
@@ -33888,12 +33888,12 @@
       </c>
       <c r="AK120" t="inlineStr">
         <is>
-          <t>Last 4 games: 2/11, 0 HR</t>
+          <t>Last 7 games: 3/13, 0 HR</t>
         </is>
       </c>
       <c r="AL120" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.2% barrel, 15.4 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.7% barrel, 11.2 HR allowed</t>
         </is>
       </c>
       <c r="AM120" t="inlineStr">
@@ -33903,112 +33903,112 @@
       </c>
       <c r="AN120" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.46</t>
         </is>
       </c>
       <c r="AO120" t="inlineStr">
         <is>
-          <t>37.5</t>
+          <t>27.1</t>
         </is>
       </c>
       <c r="AP120" t="inlineStr">
         <is>
-          <t>89.5</t>
+          <t>86.6</t>
         </is>
       </c>
       <c r="AQ120" t="inlineStr">
         <is>
-          <t>97.3227</t>
+          <t>96.8572</t>
         </is>
       </c>
       <c r="AR120" t="inlineStr">
         <is>
-          <t>0.239</t>
+          <t>0.3008</t>
         </is>
       </c>
       <c r="AS120" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.0967</t>
         </is>
       </c>
       <c r="AT120" t="inlineStr">
         <is>
-          <t>0.197</t>
+          <t>0.2628</t>
         </is>
       </c>
       <c r="AU120" t="inlineStr">
         <is>
-          <t>70.9</t>
+          <t>69.94</t>
         </is>
       </c>
       <c r="AV120" t="inlineStr">
         <is>
-          <t>13.6</t>
+          <t>7.95</t>
         </is>
       </c>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>34.06</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>12.5</t>
+          <t>26.93</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.9</t>
         </is>
       </c>
       <c r="AZ120" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1028</t>
         </is>
       </c>
       <c r="BA120" t="inlineStr">
         <is>
-          <t>6.22</t>
+          <t>7.73</t>
         </is>
       </c>
       <c r="BB120" t="inlineStr">
         <is>
-          <t>37.79</t>
+          <t>45.9</t>
         </is>
       </c>
       <c r="BC120" t="inlineStr">
         <is>
-          <t>87.86</t>
+          <t>90.18</t>
         </is>
       </c>
       <c r="BD120" t="inlineStr">
         <is>
-          <t>0.3617</t>
+          <t>0.4006</t>
         </is>
       </c>
       <c r="BE120" t="inlineStr">
         <is>
-          <t>0.1347</t>
+          <t>0.1525</t>
         </is>
       </c>
       <c r="BF120" t="inlineStr">
         <is>
-          <t>26.17</t>
+          <t>23.96</t>
         </is>
       </c>
       <c r="BG120" t="inlineStr">
         <is>
-          <t>R To L</t>
+          <t>In From LF</t>
         </is>
       </c>
       <c r="BH120" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>86</t>
         </is>
       </c>
       <c r="BI120" t="inlineStr">
         <is>
-          <t>Truist Park</t>
+          <t>Busch Stadium</t>
         </is>
       </c>
       <c r="BJ120" t="inlineStr"/>
@@ -34019,47 +34019,47 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>666152</t>
+          <t>686452</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>David Hamilton</t>
+          <t>Drew Millas</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>WSH</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>2026-07-06T23:45:00Z</t>
+          <t>2026-07-06T22:45:00Z</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Player challenge</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>Dustin May</t>
+          <t>Mike Burrows</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>669160</t>
+          <t>681347</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
@@ -34068,7 +34068,7 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>34.5</v>
+        <v>34.4</v>
       </c>
       <c r="M121" t="inlineStr">
         <is>
@@ -34086,22 +34086,22 @@
         </is>
       </c>
       <c r="P121" t="n">
-        <v>11.2</v>
+        <v>1.1</v>
       </c>
       <c r="Q121" t="n">
-        <v>42.9</v>
+        <v>43.7</v>
       </c>
       <c r="R121" t="n">
-        <v>41.1</v>
+        <v>61.2</v>
       </c>
       <c r="S121" t="n">
-        <v>44.8</v>
+        <v>52.4</v>
       </c>
       <c r="T121" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="U121" t="n">
-        <v>16.6</v>
+        <v>7</v>
       </c>
       <c r="V121" t="inlineStr">
         <is>
@@ -34115,7 +34115,7 @@
       </c>
       <c r="X121" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y121" t="inlineStr">
@@ -34158,7 +34158,7 @@
       </c>
       <c r="AI121" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AJ121" t="inlineStr">
@@ -34168,12 +34168,12 @@
       </c>
       <c r="AK121" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/13, 0 HR</t>
+          <t>Last 7 games: 3/18, 0 HR</t>
         </is>
       </c>
       <c r="AL121" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.7% barrel, 11.2 HR allowed</t>
+          <t>switch hitter; pitcher baseline 9.1% barrel, 17.2 HR allowed</t>
         </is>
       </c>
       <c r="AM121" t="inlineStr">
@@ -34183,112 +34183,112 @@
       </c>
       <c r="AN121" t="inlineStr">
         <is>
-          <t>4.46</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AO121" t="inlineStr">
         <is>
-          <t>27.1</t>
+          <t>22.04</t>
         </is>
       </c>
       <c r="AP121" t="inlineStr">
         <is>
-          <t>86.6</t>
+          <t>83.89</t>
         </is>
       </c>
       <c r="AQ121" t="inlineStr">
         <is>
-          <t>96.8572</t>
+          <t>94.7821</t>
         </is>
       </c>
       <c r="AR121" t="inlineStr">
         <is>
-          <t>0.3008</t>
+          <t>0.3044</t>
         </is>
       </c>
       <c r="AS121" t="inlineStr">
         <is>
-          <t>0.0967</t>
+          <t>0.0786</t>
         </is>
       </c>
       <c r="AT121" t="inlineStr">
         <is>
-          <t>0.2628</t>
+          <t>0.2784</t>
         </is>
       </c>
       <c r="AU121" t="inlineStr">
         <is>
-          <t>69.94</t>
+          <t>67.68</t>
         </is>
       </c>
       <c r="AV121" t="inlineStr">
         <is>
-          <t>7.95</t>
+          <t>4.2</t>
         </is>
       </c>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>34.06</t>
+          <t>36.78</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>26.93</t>
+          <t>18.47</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr">
         <is>
-          <t>3.9</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="AZ121" t="inlineStr">
         <is>
-          <t>0.1028</t>
+          <t>0.0989</t>
         </is>
       </c>
       <c r="BA121" t="inlineStr">
         <is>
-          <t>7.73</t>
+          <t>9.05</t>
         </is>
       </c>
       <c r="BB121" t="inlineStr">
         <is>
-          <t>45.9</t>
+          <t>38.99</t>
         </is>
       </c>
       <c r="BC121" t="inlineStr">
         <is>
-          <t>90.18</t>
+          <t>88.36</t>
         </is>
       </c>
       <c r="BD121" t="inlineStr">
         <is>
-          <t>0.4006</t>
+          <t>0.4292</t>
         </is>
       </c>
       <c r="BE121" t="inlineStr">
         <is>
-          <t>0.1525</t>
+          <t>0.1738</t>
         </is>
       </c>
       <c r="BF121" t="inlineStr">
         <is>
-          <t>23.96</t>
+          <t>27.68</t>
         </is>
       </c>
       <c r="BG121" t="inlineStr">
         <is>
-          <t>In From LF</t>
+          <t>Out To LF</t>
         </is>
       </c>
       <c r="BH121" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>80</t>
         </is>
       </c>
       <c r="BI121" t="inlineStr">
         <is>
-          <t>Busch Stadium</t>
+          <t>Nationals Park</t>
         </is>
       </c>
       <c r="BJ121" t="inlineStr"/>
@@ -36330,7 +36330,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Player challenge</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -36354,7 +36354,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>77.40000000000001</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -36387,7 +36387,7 @@
         <v>80</v>
       </c>
       <c r="U2" t="n">
-        <v>94.7</v>
+        <v>99.5</v>
       </c>
       <c r="V2" t="inlineStr">
         <is>
@@ -36444,7 +36444,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
@@ -36610,7 +36610,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Player challenge</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -37450,7 +37450,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -38010,7 +38010,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Player challenge</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -38850,7 +38850,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -41341,47 +41341,47 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>572233</t>
+          <t>665487</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Christian Walker</t>
+          <t>Fernando Tatis Jr.</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>WSH</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-07-06T22:45:00Z</t>
+          <t>2026-07-07T01:40:00Z</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Miles Mikolas</t>
+          <t>Brandon Pfaadt</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>571945</t>
+          <t>694297</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -41390,7 +41390,7 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>57.7</v>
+        <v>57.6</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
@@ -41408,22 +41408,22 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>44.4</v>
+        <v>50.2</v>
       </c>
       <c r="Q20" t="n">
-        <v>57.9</v>
+        <v>56.1</v>
       </c>
       <c r="R20" t="n">
-        <v>61.2</v>
+        <v>46.1</v>
       </c>
       <c r="S20" t="n">
-        <v>94.90000000000001</v>
+        <v>93.2</v>
       </c>
       <c r="T20" t="n">
         <v>50</v>
       </c>
       <c r="U20" t="n">
-        <v>44.8</v>
+        <v>62.2</v>
       </c>
       <c r="V20" t="inlineStr">
         <is>
@@ -41437,7 +41437,7 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
@@ -41475,12 +41475,12 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>31</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
@@ -41495,122 +41495,122 @@
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 10.1% barrel, 21.3 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 11.5% barrel, 13.4 HR allowed</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>11.08</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>44.42</t>
+          <t>52.57</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>90.13</t>
+          <t>92.25</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>101.7846</t>
+          <t>104.1997</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>0.4042</t>
+          <t>0.4495</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
         <is>
-          <t>0.1764</t>
+          <t>0.168</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>0.3056</t>
+          <t>0.3574</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
         <is>
-          <t>74.17</t>
+          <t>75.19</t>
         </is>
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>42.32</t>
+          <t>56.14</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>43.74</t>
+          <t>31.44</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>28.56</t>
+          <t>21.52</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>22.1</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>0.2173</t>
+          <t>0.1248</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>10.11</t>
+          <t>11.53</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>40.75</t>
+          <t>41.04</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>89.65</t>
+          <t>89.89</t>
         </is>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>0.4899</t>
+          <t>0.4632</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
-          <t>0.2172</t>
+          <t>0.2044</t>
         </is>
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>28.35</t>
+          <t>21.59</t>
         </is>
       </c>
       <c r="BG20" t="inlineStr">
         <is>
-          <t>Out To LF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
         <is>
-          <t>Nationals Park</t>
+          <t>Petco Park</t>
         </is>
       </c>
       <c r="BJ20" t="inlineStr"/>
@@ -41621,27 +41621,27 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>665487</t>
+          <t>606192</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Fernando Tatis Jr.</t>
+          <t>Teoscar Hernández</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-07-07T01:40:00Z</t>
+          <t>2026-07-07T02:10:00Z</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -41651,22 +41651,22 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Brandon Pfaadt</t>
+          <t>Kyle Freeland</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>694297</t>
+          <t>607536</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L21" t="n">
@@ -41684,26 +41684,26 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P21" t="n">
-        <v>50.2</v>
+        <v>45.8</v>
       </c>
       <c r="Q21" t="n">
-        <v>56.1</v>
+        <v>59.9</v>
       </c>
       <c r="R21" t="n">
-        <v>46.1</v>
+        <v>62.6</v>
       </c>
       <c r="S21" t="n">
-        <v>93.2</v>
+        <v>76.2</v>
       </c>
       <c r="T21" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U21" t="n">
-        <v>62.2</v>
+        <v>19.9</v>
       </c>
       <c r="V21" t="inlineStr">
         <is>
@@ -41717,7 +41717,7 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
@@ -41755,142 +41755,142 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 3/23, 1 HR</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 11.5% barrel, 13.4 HR allowed</t>
+          <t>platoon edge; pitcher baseline 10.2% barrel, 17.8 HR allowed</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>EV profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>11.0</t>
+          <t>10.87</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>52.57</t>
+          <t>45.89</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>92.25</t>
+          <t>90.27</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>104.1997</t>
+          <t>101.01</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>0.4495</t>
+          <t>0.4361</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
         <is>
-          <t>0.168</t>
+          <t>0.1871</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>0.3574</t>
+          <t>0.3286</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
         <is>
-          <t>75.19</t>
+          <t>72.41</t>
         </is>
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>56.14</t>
+          <t>25.12</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>31.44</t>
+          <t>33.94</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>21.52</t>
+          <t>29.52</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>11.0</t>
+          <t>13.1</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>0.1248</t>
+          <t>0.1727</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>11.53</t>
+          <t>10.24</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>41.04</t>
+          <t>44.71</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>89.89</t>
+          <t>90.89</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>0.4632</t>
+          <t>0.4856</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
-          <t>0.2044</t>
+          <t>0.1959</t>
         </is>
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>21.59</t>
+          <t>28.8</t>
         </is>
       </c>
       <c r="BG21" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>70</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
         <is>
-          <t>Petco Park</t>
+          <t>UNIQLO Field at Dodger Stadium</t>
         </is>
       </c>
       <c r="BJ21" t="inlineStr"/>

--- a/outputs/hr_rankings.xlsx
+++ b/outputs/hr_rankings.xlsx
@@ -1044,7 +1044,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Delayed</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -1628,7 +1628,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>64.3</v>
+        <v>64.5</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
         <v>80</v>
       </c>
       <c r="U5" t="n">
-        <v>82.7</v>
+        <v>87</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
@@ -1713,22 +1713,22 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Hot streak: 3 HR in last 7 games</t>
+          <t>Hot streak: 4 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
@@ -2448,7 +2448,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Delayed</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Delayed</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -3288,7 +3288,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Delayed</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -3568,7 +3568,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Delayed</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -6040,7 +6040,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Delayed</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -9060,7 +9060,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Delayed</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -11604,7 +11604,7 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>54.4</v>
+        <v>54.3</v>
       </c>
       <c r="M41" t="inlineStr">
         <is>
@@ -11637,7 +11637,7 @@
         <v>78</v>
       </c>
       <c r="U41" t="n">
-        <v>79.90000000000001</v>
+        <v>77</v>
       </c>
       <c r="V41" t="inlineStr">
         <is>
@@ -11694,7 +11694,7 @@
       </c>
       <c r="AI41" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AJ41" t="inlineStr">
@@ -13828,7 +13828,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Delayed</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -18040,7 +18040,7 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>52.1</v>
+        <v>52</v>
       </c>
       <c r="M64" t="inlineStr">
         <is>
@@ -18073,7 +18073,7 @@
         <v>50</v>
       </c>
       <c r="U64" t="n">
-        <v>42.3</v>
+        <v>40.7</v>
       </c>
       <c r="V64" t="inlineStr">
         <is>
@@ -18130,7 +18130,7 @@
       </c>
       <c r="AI64" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ64" t="inlineStr">
@@ -18140,7 +18140,7 @@
       </c>
       <c r="AK64" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/25, 1 HR</t>
+          <t>Last 7 games: 7/26, 1 HR</t>
         </is>
       </c>
       <c r="AL64" t="inlineStr">
@@ -18271,27 +18271,27 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>663616</t>
+          <t>663757</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Trevor Larnach</t>
+          <t>Trent Grisham</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-07-09T17:40:00Z</t>
+          <t>2026-07-09T17:10:00Z</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -18306,12 +18306,12 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Gavin Williams</t>
+          <t>Drew Rasmussen</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>668909</t>
+          <t>656876</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -18320,7 +18320,7 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>52.1</v>
+        <v>52</v>
       </c>
       <c r="M65" t="inlineStr">
         <is>
@@ -18334,17 +18334,17 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P65" t="n">
-        <v>29.4</v>
+        <v>50.3</v>
       </c>
       <c r="Q65" t="n">
-        <v>59.5</v>
+        <v>30.2</v>
       </c>
       <c r="R65" t="n">
-        <v>39.6</v>
+        <v>41.1</v>
       </c>
       <c r="S65" t="n">
         <v>93.2</v>
@@ -18353,7 +18353,7 @@
         <v>80</v>
       </c>
       <c r="U65" t="n">
-        <v>37.8</v>
+        <v>34.4</v>
       </c>
       <c r="V65" t="inlineStr">
         <is>
@@ -18410,7 +18410,7 @@
       </c>
       <c r="AI65" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ65" t="inlineStr">
@@ -18420,12 +18420,12 @@
       </c>
       <c r="AK65" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/20, 1 HR</t>
+          <t>Last 7 games: 5/22, 1 HR</t>
         </is>
       </c>
       <c r="AL65" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 11.4% barrel, 18.1 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.7% barrel, 13.1 HR allowed</t>
         </is>
       </c>
       <c r="AM65" t="inlineStr">
@@ -18435,112 +18435,112 @@
       </c>
       <c r="AN65" t="inlineStr">
         <is>
-          <t>7.27</t>
+          <t>12.1</t>
         </is>
       </c>
       <c r="AO65" t="inlineStr">
         <is>
-          <t>37.93</t>
+          <t>46.26</t>
         </is>
       </c>
       <c r="AP65" t="inlineStr">
         <is>
-          <t>88.31</t>
+          <t>90.89</t>
         </is>
       </c>
       <c r="AQ65" t="inlineStr">
         <is>
-          <t>99.2939</t>
+          <t>100.8754</t>
         </is>
       </c>
       <c r="AR65" t="inlineStr">
         <is>
-          <t>0.4037</t>
+          <t>0.4609</t>
         </is>
       </c>
       <c r="AS65" t="inlineStr">
         <is>
-          <t>0.1439</t>
+          <t>0.2101</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr">
         <is>
-          <t>0.3334</t>
+          <t>0.356</t>
         </is>
       </c>
       <c r="AU65" t="inlineStr">
         <is>
-          <t>71.99</t>
+          <t>70.37</t>
         </is>
       </c>
       <c r="AV65" t="inlineStr">
         <is>
-          <t>20.96</t>
+          <t>8.14</t>
         </is>
       </c>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>41.36</t>
+          <t>43.81</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>25.31</t>
+          <t>32.1</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr">
         <is>
-          <t>9.3</t>
+          <t>16.5</t>
         </is>
       </c>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>0.1519</t>
+          <t>0.1961</t>
         </is>
       </c>
       <c r="BA65" t="inlineStr">
         <is>
-          <t>11.38</t>
+          <t>6.72</t>
         </is>
       </c>
       <c r="BB65" t="inlineStr">
         <is>
-          <t>47.1</t>
+          <t>36.44</t>
         </is>
       </c>
       <c r="BC65" t="inlineStr">
         <is>
-          <t>90.89</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="BD65" t="inlineStr">
         <is>
-          <t>0.4316</t>
+          <t>0.3652</t>
         </is>
       </c>
       <c r="BE65" t="inlineStr">
         <is>
-          <t>0.1894</t>
+          <t>0.1334</t>
         </is>
       </c>
       <c r="BF65" t="inlineStr">
         <is>
-          <t>23.9</t>
+          <t>22.54</t>
         </is>
       </c>
       <c r="BG65" t="inlineStr">
         <is>
-          <t>In From LF</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH65" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI65" t="inlineStr">
         <is>
-          <t>Target Field</t>
+          <t>Tropicana Field</t>
         </is>
       </c>
       <c r="BJ65" t="inlineStr"/>
@@ -18551,27 +18551,27 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>663757</t>
+          <t>800050</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Trent Grisham</t>
+          <t>Chase DeLauter</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-07-09T17:10:00Z</t>
+          <t>2026-07-09T17:40:00Z</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -18581,17 +18581,17 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Drew Rasmussen</t>
+          <t>Bailey Ober</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>656876</t>
+          <t>641927</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -18614,26 +18614,26 @@
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P66" t="n">
-        <v>50.3</v>
+        <v>29.9</v>
       </c>
       <c r="Q66" t="n">
-        <v>30.2</v>
+        <v>50.6</v>
       </c>
       <c r="R66" t="n">
-        <v>41.1</v>
+        <v>39.6</v>
       </c>
       <c r="S66" t="n">
-        <v>93.2</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T66" t="n">
         <v>80</v>
       </c>
       <c r="U66" t="n">
-        <v>34.4</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="V66" t="inlineStr">
         <is>
@@ -18647,7 +18647,7 @@
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y66" t="inlineStr">
@@ -18668,7 +18668,7 @@
       <c r="AB66" t="inlineStr"/>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD66" t="inlineStr"/>
@@ -18685,142 +18685,142 @@
       </c>
       <c r="AH66" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI66" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK66" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/22, 1 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL66" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.7% barrel, 13.1 HR allowed</t>
+          <t>platoon edge; pitcher baseline 10.1% barrel, 17.4 HR allowed</t>
         </is>
       </c>
       <c r="AM66" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN66" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>5.4</t>
         </is>
       </c>
       <c r="AO66" t="inlineStr">
         <is>
-          <t>46.26</t>
+          <t>43.6</t>
         </is>
       </c>
       <c r="AP66" t="inlineStr">
         <is>
-          <t>90.89</t>
+          <t>90.6</t>
         </is>
       </c>
       <c r="AQ66" t="inlineStr">
         <is>
-          <t>100.8754</t>
+          <t>101.3496</t>
         </is>
       </c>
       <c r="AR66" t="inlineStr">
         <is>
-          <t>0.4609</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="AS66" t="inlineStr">
         <is>
-          <t>0.2101</t>
+          <t>0.132</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr">
         <is>
-          <t>0.356</t>
+          <t>0.337</t>
         </is>
       </c>
       <c r="AU66" t="inlineStr">
         <is>
-          <t>70.37</t>
+          <t>71.5</t>
         </is>
       </c>
       <c r="AV66" t="inlineStr">
         <is>
-          <t>8.14</t>
+          <t>18.7</t>
         </is>
       </c>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>43.81</t>
+          <t>39.3</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>32.1</t>
+          <t>19.4</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr">
         <is>
-          <t>16.5</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>0.1961</t>
+          <t>0.149</t>
         </is>
       </c>
       <c r="BA66" t="inlineStr">
         <is>
-          <t>6.72</t>
+          <t>10.13</t>
         </is>
       </c>
       <c r="BB66" t="inlineStr">
         <is>
-          <t>36.44</t>
+          <t>34.62</t>
         </is>
       </c>
       <c r="BC66" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>88.41</t>
         </is>
       </c>
       <c r="BD66" t="inlineStr">
         <is>
-          <t>0.3652</t>
+          <t>0.4508</t>
         </is>
       </c>
       <c r="BE66" t="inlineStr">
         <is>
-          <t>0.1334</t>
+          <t>0.2049</t>
         </is>
       </c>
       <c r="BF66" t="inlineStr">
         <is>
-          <t>22.54</t>
+          <t>32.11</t>
         </is>
       </c>
       <c r="BG66" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>In From LF</t>
         </is>
       </c>
       <c r="BH66" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>79</t>
         </is>
       </c>
       <c r="BI66" t="inlineStr">
         <is>
-          <t>Tropicana Field</t>
+          <t>Target Field</t>
         </is>
       </c>
       <c r="BJ66" t="inlineStr"/>
@@ -18831,24 +18831,24 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>700932</t>
+          <t>663616</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Kyle Manzardo</t>
+          <t>Trevor Larnach</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
+          <t>MIN</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>MIN</t>
-        </is>
-      </c>
       <c r="F67" t="inlineStr">
         <is>
           <t>2026-07-09T17:40:00Z</t>
@@ -18861,17 +18861,17 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Bailey Ober</t>
+          <t>Gavin Williams</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>641927</t>
+          <t>668909</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -18880,7 +18880,7 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>51.9</v>
+        <v>52</v>
       </c>
       <c r="M67" t="inlineStr">
         <is>
@@ -18894,26 +18894,26 @@
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P67" t="n">
-        <v>40.4</v>
+        <v>29.4</v>
       </c>
       <c r="Q67" t="n">
-        <v>50.6</v>
+        <v>59.5</v>
       </c>
       <c r="R67" t="n">
         <v>39.6</v>
       </c>
       <c r="S67" t="n">
-        <v>94.90000000000001</v>
+        <v>93.2</v>
       </c>
       <c r="T67" t="n">
         <v>80</v>
       </c>
       <c r="U67" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="V67" t="inlineStr">
         <is>
@@ -18927,7 +18927,7 @@
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y67" t="inlineStr">
@@ -18965,127 +18965,127 @@
       </c>
       <c r="AH67" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AI67" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="AJ67" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AI67" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="AJ67" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AK67" t="inlineStr">
         <is>
-          <t>Last 7 games: 1/20, 0 HR</t>
+          <t>Last 7 games: 5/21, 1 HR</t>
         </is>
       </c>
       <c r="AL67" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 10.1% barrel, 17.4 HR allowed</t>
+          <t>platoon edge; pitcher baseline 11.4% barrel, 18.1 HR allowed</t>
         </is>
       </c>
       <c r="AM67" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN67" t="inlineStr">
         <is>
-          <t>11.24</t>
+          <t>7.27</t>
         </is>
       </c>
       <c r="AO67" t="inlineStr">
         <is>
-          <t>41.28</t>
+          <t>37.93</t>
         </is>
       </c>
       <c r="AP67" t="inlineStr">
         <is>
-          <t>89.32</t>
+          <t>88.31</t>
         </is>
       </c>
       <c r="AQ67" t="inlineStr">
         <is>
-          <t>99.1104</t>
+          <t>99.2939</t>
         </is>
       </c>
       <c r="AR67" t="inlineStr">
         <is>
-          <t>0.3947</t>
+          <t>0.4037</t>
         </is>
       </c>
       <c r="AS67" t="inlineStr">
         <is>
-          <t>0.1745</t>
+          <t>0.1439</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr">
         <is>
-          <t>0.3101</t>
+          <t>0.3334</t>
         </is>
       </c>
       <c r="AU67" t="inlineStr">
         <is>
-          <t>70.11</t>
+          <t>71.99</t>
         </is>
       </c>
       <c r="AV67" t="inlineStr">
         <is>
-          <t>7.58</t>
+          <t>20.96</t>
         </is>
       </c>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>42.22</t>
+          <t>41.36</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>33.2</t>
+          <t>25.31</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr">
         <is>
-          <t>15.1</t>
+          <t>9.3</t>
         </is>
       </c>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>0.1727</t>
+          <t>0.1519</t>
         </is>
       </c>
       <c r="BA67" t="inlineStr">
         <is>
-          <t>10.13</t>
+          <t>11.38</t>
         </is>
       </c>
       <c r="BB67" t="inlineStr">
         <is>
-          <t>34.62</t>
+          <t>47.1</t>
         </is>
       </c>
       <c r="BC67" t="inlineStr">
         <is>
-          <t>88.41</t>
+          <t>90.89</t>
         </is>
       </c>
       <c r="BD67" t="inlineStr">
         <is>
-          <t>0.4508</t>
+          <t>0.4316</t>
         </is>
       </c>
       <c r="BE67" t="inlineStr">
         <is>
-          <t>0.2049</t>
+          <t>0.1894</t>
         </is>
       </c>
       <c r="BF67" t="inlineStr">
         <is>
-          <t>32.11</t>
+          <t>23.9</t>
         </is>
       </c>
       <c r="BG67" t="inlineStr">
@@ -19111,12 +19111,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>672356</t>
+          <t>700932</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Gabriel Arias</t>
+          <t>Kyle Manzardo</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -19141,7 +19141,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -19160,7 +19160,7 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>51.5</v>
+        <v>51.9</v>
       </c>
       <c r="M68" t="inlineStr">
         <is>
@@ -19174,11 +19174,11 @@
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>Strong Barrel</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P68" t="n">
-        <v>46.5</v>
+        <v>40.4</v>
       </c>
       <c r="Q68" t="n">
         <v>50.6</v>
@@ -19187,13 +19187,13 @@
         <v>39.6</v>
       </c>
       <c r="S68" t="n">
-        <v>76.2</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T68" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U68" t="n">
-        <v>58.7</v>
+        <v>0</v>
       </c>
       <c r="V68" t="inlineStr">
         <is>
@@ -19207,7 +19207,7 @@
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y68" t="inlineStr">
@@ -19245,27 +19245,27 @@
       </c>
       <c r="AH68" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AI68" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK68" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 1/20, 0 HR</t>
         </is>
       </c>
       <c r="AL68" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 10.1% barrel, 17.4 HR allowed</t>
+          <t>platoon edge; pitcher baseline 10.1% barrel, 17.4 HR allowed</t>
         </is>
       </c>
       <c r="AM68" t="inlineStr">
@@ -19275,67 +19275,67 @@
       </c>
       <c r="AN68" t="inlineStr">
         <is>
-          <t>11.16</t>
+          <t>11.24</t>
         </is>
       </c>
       <c r="AO68" t="inlineStr">
         <is>
-          <t>48.76</t>
+          <t>41.28</t>
         </is>
       </c>
       <c r="AP68" t="inlineStr">
         <is>
-          <t>91.67</t>
+          <t>89.32</t>
         </is>
       </c>
       <c r="AQ68" t="inlineStr">
         <is>
-          <t>103.0682</t>
+          <t>99.1104</t>
         </is>
       </c>
       <c r="AR68" t="inlineStr">
         <is>
-          <t>0.3927</t>
+          <t>0.3947</t>
         </is>
       </c>
       <c r="AS68" t="inlineStr">
         <is>
-          <t>0.1752</t>
+          <t>0.1745</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr">
         <is>
-          <t>0.2839</t>
+          <t>0.3101</t>
         </is>
       </c>
       <c r="AU68" t="inlineStr">
         <is>
-          <t>74.61</t>
+          <t>70.11</t>
         </is>
       </c>
       <c r="AV68" t="inlineStr">
         <is>
-          <t>46.05</t>
+          <t>7.58</t>
         </is>
       </c>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>37.92</t>
+          <t>42.22</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>20.45</t>
+          <t>33.2</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>15.1</t>
         </is>
       </c>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>0.1661</t>
+          <t>0.1727</t>
         </is>
       </c>
       <c r="BA68" t="inlineStr">
@@ -19391,47 +19391,47 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>592663</t>
+          <t>672356</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>J.T. Realmuto</t>
+          <t>Gabriel Arias</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-07-09T23:10:00Z</t>
+          <t>2026-07-09T17:40:00Z</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Brady Singer</t>
+          <t>Bailey Ober</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>663903</t>
+          <t>641927</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -19440,7 +19440,7 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>51.3</v>
+        <v>51.5</v>
       </c>
       <c r="M69" t="inlineStr">
         <is>
@@ -19454,62 +19454,58 @@
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>Projected Lineup, Good Environment</t>
+          <t>Strong Barrel</t>
         </is>
       </c>
       <c r="P69" t="n">
-        <v>30.9</v>
+        <v>46.5</v>
       </c>
       <c r="Q69" t="n">
-        <v>58.6</v>
+        <v>50.6</v>
       </c>
       <c r="R69" t="n">
-        <v>79.8</v>
+        <v>39.6</v>
       </c>
       <c r="S69" t="n">
-        <v>59.8</v>
+        <v>76.2</v>
       </c>
       <c r="T69" t="n">
         <v>50</v>
       </c>
       <c r="U69" t="n">
-        <v>44.8</v>
+        <v>58.7</v>
       </c>
       <c r="V69" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z69" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W69" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X69" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y69" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z69" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB69" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr"/>
       <c r="AC69" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -19534,7 +19530,7 @@
       </c>
       <c r="AI69" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AJ69" t="inlineStr">
@@ -19549,122 +19545,122 @@
       </c>
       <c r="AL69" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 10.7% barrel, 19.7 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 10.1% barrel, 17.4 HR allowed</t>
         </is>
       </c>
       <c r="AM69" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN69" t="inlineStr">
         <is>
-          <t>6.42</t>
+          <t>11.16</t>
         </is>
       </c>
       <c r="AO69" t="inlineStr">
         <is>
-          <t>40.18</t>
+          <t>48.76</t>
         </is>
       </c>
       <c r="AP69" t="inlineStr">
         <is>
-          <t>89.37</t>
+          <t>91.67</t>
         </is>
       </c>
       <c r="AQ69" t="inlineStr">
         <is>
-          <t>99.4447</t>
+          <t>103.0682</t>
         </is>
       </c>
       <c r="AR69" t="inlineStr">
         <is>
-          <t>0.3865</t>
+          <t>0.3927</t>
         </is>
       </c>
       <c r="AS69" t="inlineStr">
         <is>
-          <t>0.1426</t>
+          <t>0.1752</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr">
         <is>
-          <t>0.3125</t>
+          <t>0.2839</t>
         </is>
       </c>
       <c r="AU69" t="inlineStr">
         <is>
-          <t>72.77</t>
+          <t>74.61</t>
         </is>
       </c>
       <c r="AV69" t="inlineStr">
         <is>
-          <t>30.71</t>
+          <t>46.05</t>
         </is>
       </c>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>39.78</t>
+          <t>37.92</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>28.25</t>
+          <t>20.45</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>0.134</t>
+          <t>0.1661</t>
         </is>
       </c>
       <c r="BA69" t="inlineStr">
         <is>
-          <t>10.73</t>
+          <t>10.13</t>
         </is>
       </c>
       <c r="BB69" t="inlineStr">
         <is>
-          <t>40.77</t>
+          <t>34.62</t>
         </is>
       </c>
       <c r="BC69" t="inlineStr">
         <is>
-          <t>90.86</t>
+          <t>88.41</t>
         </is>
       </c>
       <c r="BD69" t="inlineStr">
         <is>
-          <t>0.4608</t>
+          <t>0.4508</t>
         </is>
       </c>
       <c r="BE69" t="inlineStr">
         <is>
-          <t>0.1982</t>
+          <t>0.2049</t>
         </is>
       </c>
       <c r="BF69" t="inlineStr">
         <is>
-          <t>28.96</t>
+          <t>32.11</t>
         </is>
       </c>
       <c r="BG69" t="inlineStr">
         <is>
-          <t>Out To LF</t>
+          <t>In From LF</t>
         </is>
       </c>
       <c r="BH69" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>79</t>
         </is>
       </c>
       <c r="BI69" t="inlineStr">
         <is>
-          <t>Great American Ball Park</t>
+          <t>Target Field</t>
         </is>
       </c>
       <c r="BJ69" t="inlineStr"/>
@@ -19675,27 +19671,27 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>670042</t>
+          <t>592663</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Luke Raley</t>
+          <t>J.T. Realmuto</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-07-09T22:40:00Z</t>
+          <t>2026-07-09T23:10:00Z</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -19705,17 +19701,17 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Janson Junk</t>
+          <t>Brady Singer</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>676083</t>
+          <t>663903</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -19724,7 +19720,7 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>51.1</v>
+        <v>51.3</v>
       </c>
       <c r="M70" t="inlineStr">
         <is>
@@ -19738,58 +19734,62 @@
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>Strong Barrel, Platoon Edge</t>
+          <t>Projected Lineup, Good Environment</t>
         </is>
       </c>
       <c r="P70" t="n">
-        <v>54.2</v>
+        <v>30.9</v>
       </c>
       <c r="Q70" t="n">
-        <v>41.6</v>
+        <v>58.6</v>
       </c>
       <c r="R70" t="n">
-        <v>35</v>
+        <v>79.8</v>
       </c>
       <c r="S70" t="n">
-        <v>76.2</v>
+        <v>59.8</v>
       </c>
       <c r="T70" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U70" t="n">
-        <v>1.6</v>
+        <v>44.8</v>
       </c>
       <c r="V70" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W70" t="inlineStr">
+      <c r="Z70" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X70" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y70" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z70" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB70" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC70" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -19809,7 +19809,7 @@
       </c>
       <c r="AH70" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI70" t="inlineStr">
@@ -19819,17 +19819,17 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK70" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/23, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL70" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.2% barrel, 8.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 10.7% barrel, 19.7 HR allowed</t>
         </is>
       </c>
       <c r="AM70" t="inlineStr">
@@ -19839,112 +19839,112 @@
       </c>
       <c r="AN70" t="inlineStr">
         <is>
-          <t>14.52</t>
+          <t>6.42</t>
         </is>
       </c>
       <c r="AO70" t="inlineStr">
         <is>
-          <t>45.31</t>
+          <t>40.18</t>
         </is>
       </c>
       <c r="AP70" t="inlineStr">
         <is>
-          <t>90.27</t>
+          <t>89.37</t>
         </is>
       </c>
       <c r="AQ70" t="inlineStr">
         <is>
-          <t>101.9314</t>
+          <t>99.4447</t>
         </is>
       </c>
       <c r="AR70" t="inlineStr">
         <is>
-          <t>0.4504</t>
+          <t>0.3865</t>
         </is>
       </c>
       <c r="AS70" t="inlineStr">
         <is>
-          <t>0.2134</t>
+          <t>0.1426</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr">
         <is>
-          <t>0.3344</t>
+          <t>0.3125</t>
         </is>
       </c>
       <c r="AU70" t="inlineStr">
         <is>
-          <t>74.78</t>
+          <t>72.77</t>
         </is>
       </c>
       <c r="AV70" t="inlineStr">
         <is>
-          <t>50.34</t>
+          <t>30.71</t>
         </is>
       </c>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>47.27</t>
+          <t>39.78</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>27.63</t>
+          <t>28.25</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr">
         <is>
-          <t>11.0</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>0.1972</t>
+          <t>0.134</t>
         </is>
       </c>
       <c r="BA70" t="inlineStr">
         <is>
-          <t>7.17</t>
+          <t>10.73</t>
         </is>
       </c>
       <c r="BB70" t="inlineStr">
         <is>
-          <t>43.31</t>
+          <t>40.77</t>
         </is>
       </c>
       <c r="BC70" t="inlineStr">
         <is>
-          <t>90.41</t>
+          <t>90.86</t>
         </is>
       </c>
       <c r="BD70" t="inlineStr">
         <is>
-          <t>0.4236</t>
+          <t>0.4608</t>
         </is>
       </c>
       <c r="BE70" t="inlineStr">
         <is>
-          <t>0.1606</t>
+          <t>0.1982</t>
         </is>
       </c>
       <c r="BF70" t="inlineStr">
         <is>
-          <t>24.2</t>
+          <t>28.96</t>
         </is>
       </c>
       <c r="BG70" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Out To LF</t>
         </is>
       </c>
       <c r="BH70" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>87</t>
         </is>
       </c>
       <c r="BI70" t="inlineStr">
         <is>
-          <t>loanDepot park</t>
+          <t>Great American Ball Park</t>
         </is>
       </c>
       <c r="BJ70" t="inlineStr"/>
@@ -19955,47 +19955,47 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>663586</t>
+          <t>670042</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Austin Riley</t>
+          <t>Luke Raley</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-07-09T16:35:00Z</t>
+          <t>2026-07-09T22:40:00Z</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Delayed</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Mitch Keller</t>
+          <t>Janson Junk</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>656605</t>
+          <t>676083</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -20004,7 +20004,7 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>51</v>
+        <v>51.1</v>
       </c>
       <c r="M71" t="inlineStr">
         <is>
@@ -20018,26 +20018,26 @@
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>Strong Barrel</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P71" t="n">
-        <v>48.3</v>
+        <v>54.2</v>
       </c>
       <c r="Q71" t="n">
-        <v>43.5</v>
+        <v>41.6</v>
       </c>
       <c r="R71" t="n">
-        <v>63.3</v>
+        <v>35</v>
       </c>
       <c r="S71" t="n">
-        <v>64.3</v>
+        <v>76.2</v>
       </c>
       <c r="T71" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U71" t="n">
-        <v>31.6</v>
+        <v>1.6</v>
       </c>
       <c r="V71" t="inlineStr">
         <is>
@@ -20051,7 +20051,7 @@
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y71" t="inlineStr">
@@ -20089,27 +20089,27 @@
       </c>
       <c r="AH71" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI71" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/24, 1 HR</t>
+          <t>Last 7 games: 3/23, 0 HR</t>
         </is>
       </c>
       <c r="AL71" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.5% barrel, 14.7 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.2% barrel, 8.0 HR allowed</t>
         </is>
       </c>
       <c r="AM71" t="inlineStr">
@@ -20119,112 +20119,112 @@
       </c>
       <c r="AN71" t="inlineStr">
         <is>
-          <t>11.77</t>
+          <t>14.52</t>
         </is>
       </c>
       <c r="AO71" t="inlineStr">
         <is>
-          <t>44.74</t>
+          <t>45.31</t>
         </is>
       </c>
       <c r="AP71" t="inlineStr">
         <is>
-          <t>90.97</t>
+          <t>90.27</t>
         </is>
       </c>
       <c r="AQ71" t="inlineStr">
         <is>
-          <t>102.2808</t>
+          <t>101.9314</t>
         </is>
       </c>
       <c r="AR71" t="inlineStr">
         <is>
-          <t>0.3992</t>
+          <t>0.4504</t>
         </is>
       </c>
       <c r="AS71" t="inlineStr">
         <is>
-          <t>0.1823</t>
+          <t>0.2134</t>
         </is>
       </c>
       <c r="AT71" t="inlineStr">
         <is>
-          <t>0.302</t>
+          <t>0.3344</t>
         </is>
       </c>
       <c r="AU71" t="inlineStr">
         <is>
-          <t>75.76</t>
+          <t>74.78</t>
         </is>
       </c>
       <c r="AV71" t="inlineStr">
         <is>
-          <t>58.47</t>
+          <t>50.34</t>
         </is>
       </c>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>40.57</t>
+          <t>47.27</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>31.43</t>
+          <t>27.63</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr">
         <is>
-          <t>11.1</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>0.1393</t>
+          <t>0.1972</t>
         </is>
       </c>
       <c r="BA71" t="inlineStr">
         <is>
-          <t>7.45</t>
+          <t>7.17</t>
         </is>
       </c>
       <c r="BB71" t="inlineStr">
         <is>
-          <t>42.54</t>
+          <t>43.31</t>
         </is>
       </c>
       <c r="BC71" t="inlineStr">
         <is>
-          <t>89.47</t>
+          <t>90.41</t>
         </is>
       </c>
       <c r="BD71" t="inlineStr">
         <is>
-          <t>0.4461</t>
+          <t>0.4236</t>
         </is>
       </c>
       <c r="BE71" t="inlineStr">
         <is>
-          <t>0.164</t>
+          <t>0.1606</t>
         </is>
       </c>
       <c r="BF71" t="inlineStr">
         <is>
-          <t>24.26</t>
+          <t>24.2</t>
         </is>
       </c>
       <c r="BG71" t="inlineStr">
         <is>
-          <t>Out To LF</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH71" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI71" t="inlineStr">
         <is>
-          <t>PNC Park</t>
+          <t>loanDepot park</t>
         </is>
       </c>
       <c r="BJ71" t="inlineStr"/>
@@ -20235,47 +20235,47 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>668930</t>
+          <t>663586</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Brice Turang</t>
+          <t>Austin Riley</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-07-09T23:45:00Z</t>
+          <t>2026-07-09T16:35:00Z</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>Andre Pallante</t>
+          <t>Mitch Keller</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>669467</t>
+          <t>656605</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -20298,62 +20298,58 @@
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel</t>
         </is>
       </c>
       <c r="P72" t="n">
-        <v>38.1</v>
+        <v>48.3</v>
       </c>
       <c r="Q72" t="n">
-        <v>28.5</v>
+        <v>43.5</v>
       </c>
       <c r="R72" t="n">
-        <v>65.59999999999999</v>
+        <v>63.3</v>
       </c>
       <c r="S72" t="n">
-        <v>92.09999999999999</v>
+        <v>64.3</v>
       </c>
       <c r="T72" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U72" t="n">
-        <v>33.6</v>
+        <v>31.6</v>
       </c>
       <c r="V72" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z72" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W72" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X72" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y72" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z72" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB72" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr"/>
       <c r="AC72" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -20373,27 +20369,27 @@
       </c>
       <c r="AH72" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI72" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK72" t="inlineStr">
         <is>
-          <t>Contact streak: 11/32 over last 7 games</t>
+          <t>Last 7 games: 5/24, 1 HR</t>
         </is>
       </c>
       <c r="AL72" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.3% barrel, 12.6 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.5% barrel, 14.7 HR allowed</t>
         </is>
       </c>
       <c r="AM72" t="inlineStr">
@@ -20403,112 +20399,112 @@
       </c>
       <c r="AN72" t="inlineStr">
         <is>
-          <t>7.86</t>
+          <t>11.77</t>
         </is>
       </c>
       <c r="AO72" t="inlineStr">
         <is>
-          <t>44.53</t>
+          <t>44.74</t>
         </is>
       </c>
       <c r="AP72" t="inlineStr">
         <is>
-          <t>90.82</t>
+          <t>90.97</t>
         </is>
       </c>
       <c r="AQ72" t="inlineStr">
         <is>
-          <t>100.6447</t>
+          <t>102.2808</t>
         </is>
       </c>
       <c r="AR72" t="inlineStr">
         <is>
-          <t>0.4339</t>
+          <t>0.3992</t>
         </is>
       </c>
       <c r="AS72" t="inlineStr">
         <is>
-          <t>0.1768</t>
+          <t>0.1823</t>
         </is>
       </c>
       <c r="AT72" t="inlineStr">
         <is>
-          <t>0.3413</t>
+          <t>0.302</t>
         </is>
       </c>
       <c r="AU72" t="inlineStr">
         <is>
-          <t>70.25</t>
+          <t>75.76</t>
         </is>
       </c>
       <c r="AV72" t="inlineStr">
         <is>
-          <t>12.36</t>
+          <t>58.47</t>
         </is>
       </c>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>27.23</t>
+          <t>40.57</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>23.08</t>
+          <t>31.43</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr">
         <is>
-          <t>13.8</t>
+          <t>11.1</t>
         </is>
       </c>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>0.1757</t>
+          <t>0.1393</t>
         </is>
       </c>
       <c r="BA72" t="inlineStr">
         <is>
-          <t>6.32</t>
+          <t>7.45</t>
         </is>
       </c>
       <c r="BB72" t="inlineStr">
         <is>
-          <t>36.19</t>
+          <t>42.54</t>
         </is>
       </c>
       <c r="BC72" t="inlineStr">
         <is>
-          <t>87.87</t>
+          <t>89.47</t>
         </is>
       </c>
       <c r="BD72" t="inlineStr">
         <is>
-          <t>0.3824</t>
+          <t>0.4461</t>
         </is>
       </c>
       <c r="BE72" t="inlineStr">
         <is>
-          <t>0.1384</t>
+          <t>0.164</t>
         </is>
       </c>
       <c r="BF72" t="inlineStr">
         <is>
-          <t>18.73</t>
+          <t>24.26</t>
         </is>
       </c>
       <c r="BG72" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>Out To LF</t>
         </is>
       </c>
       <c r="BH72" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>82</t>
         </is>
       </c>
       <c r="BI72" t="inlineStr">
         <is>
-          <t>Busch Stadium</t>
+          <t>PNC Park</t>
         </is>
       </c>
       <c r="BJ72" t="inlineStr"/>
@@ -20519,32 +20515,32 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>800050</t>
+          <t>668930</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Chase DeLauter</t>
+          <t>Brice Turang</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-07-09T17:40:00Z</t>
+          <t>2026-07-09T23:45:00Z</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -20554,12 +20550,12 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Bailey Ober</t>
+          <t>Andre Pallante</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>641927</t>
+          <t>669467</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -20568,7 +20564,7 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>50.9</v>
+        <v>51</v>
       </c>
       <c r="M73" t="inlineStr">
         <is>
@@ -20582,61 +20578,65 @@
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P73" t="n">
-        <v>29.9</v>
+        <v>38.1</v>
       </c>
       <c r="Q73" t="n">
-        <v>50.6</v>
+        <v>28.5</v>
       </c>
       <c r="R73" t="n">
-        <v>39.6</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="S73" t="n">
-        <v>96.59999999999999</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="T73" t="n">
         <v>80</v>
       </c>
       <c r="U73" t="n">
-        <v>44.8</v>
+        <v>33.6</v>
       </c>
       <c r="V73" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W73" t="inlineStr">
+      <c r="Z73" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X73" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y73" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z73" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB73" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD73" t="inlineStr"/>
@@ -20653,142 +20653,142 @@
       </c>
       <c r="AH73" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AI73" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>32</t>
         </is>
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
         <is>
-          <t>Last 7 games: 8/27, 1 HR</t>
+          <t>Contact streak: 11/32 over last 7 games</t>
         </is>
       </c>
       <c r="AL73" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 10.1% barrel, 17.4 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.3% barrel, 12.6 HR allowed</t>
         </is>
       </c>
       <c r="AM73" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN73" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>7.86</t>
         </is>
       </c>
       <c r="AO73" t="inlineStr">
         <is>
-          <t>43.6</t>
+          <t>44.53</t>
         </is>
       </c>
       <c r="AP73" t="inlineStr">
         <is>
-          <t>90.6</t>
+          <t>90.82</t>
         </is>
       </c>
       <c r="AQ73" t="inlineStr">
         <is>
-          <t>101.3496</t>
+          <t>100.6447</t>
         </is>
       </c>
       <c r="AR73" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>0.4339</t>
         </is>
       </c>
       <c r="AS73" t="inlineStr">
         <is>
-          <t>0.132</t>
+          <t>0.1768</t>
         </is>
       </c>
       <c r="AT73" t="inlineStr">
         <is>
-          <t>0.337</t>
+          <t>0.3413</t>
         </is>
       </c>
       <c r="AU73" t="inlineStr">
         <is>
-          <t>71.5</t>
+          <t>70.25</t>
         </is>
       </c>
       <c r="AV73" t="inlineStr">
         <is>
-          <t>18.7</t>
+          <t>12.36</t>
         </is>
       </c>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>39.3</t>
+          <t>27.23</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>19.4</t>
+          <t>23.08</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>13.8</t>
         </is>
       </c>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>0.149</t>
+          <t>0.1757</t>
         </is>
       </c>
       <c r="BA73" t="inlineStr">
         <is>
-          <t>10.13</t>
+          <t>6.32</t>
         </is>
       </c>
       <c r="BB73" t="inlineStr">
         <is>
-          <t>34.62</t>
+          <t>36.19</t>
         </is>
       </c>
       <c r="BC73" t="inlineStr">
         <is>
-          <t>88.41</t>
+          <t>87.87</t>
         </is>
       </c>
       <c r="BD73" t="inlineStr">
         <is>
-          <t>0.4508</t>
+          <t>0.3824</t>
         </is>
       </c>
       <c r="BE73" t="inlineStr">
         <is>
-          <t>0.2049</t>
+          <t>0.1384</t>
         </is>
       </c>
       <c r="BF73" t="inlineStr">
         <is>
-          <t>32.11</t>
+          <t>18.73</t>
         </is>
       </c>
       <c r="BG73" t="inlineStr">
         <is>
-          <t>In From LF</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BH73" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>91</t>
         </is>
       </c>
       <c r="BI73" t="inlineStr">
         <is>
-          <t>Target Field</t>
+          <t>Busch Stadium</t>
         </is>
       </c>
       <c r="BJ73" t="inlineStr"/>
@@ -21079,27 +21079,27 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>678882</t>
+          <t>701807</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Ceddanne Rafaela</t>
+          <t>Carson Benge</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>NYM</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-07-09T18:10:00Z</t>
+          <t>2026-07-09T17:10:00Z</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -21109,22 +21109,22 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Anthony Kay</t>
+          <t>Michael Wacha</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>641743</t>
+          <t>608379</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L75" t="n">
@@ -21146,22 +21146,22 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>21.8</v>
+        <v>36.8</v>
       </c>
       <c r="Q75" t="n">
-        <v>40.3</v>
+        <v>34.3</v>
       </c>
       <c r="R75" t="n">
-        <v>66.59999999999999</v>
+        <v>44.3</v>
       </c>
       <c r="S75" t="n">
-        <v>100</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T75" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U75" t="n">
-        <v>50.3</v>
+        <v>58</v>
       </c>
       <c r="V75" t="inlineStr">
         <is>
@@ -21175,7 +21175,7 @@
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y75" t="inlineStr">
@@ -21196,7 +21196,7 @@
       <c r="AB75" t="inlineStr"/>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD75" t="inlineStr"/>
@@ -21218,7 +21218,7 @@
       </c>
       <c r="AI75" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ75" t="inlineStr">
@@ -21228,12 +21228,12 @@
       </c>
       <c r="AK75" t="inlineStr">
         <is>
-          <t>Contact streak: 10/30 over last 7 games</t>
+          <t>Contact streak: 10/26 over last 7 games</t>
         </is>
       </c>
       <c r="AL75" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.8% barrel, 11.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.6% barrel, 13.6 HR allowed</t>
         </is>
       </c>
       <c r="AM75" t="inlineStr">
@@ -21243,112 +21243,112 @@
       </c>
       <c r="AN75" t="inlineStr">
         <is>
-          <t>6.33</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="AO75" t="inlineStr">
         <is>
-          <t>34.78</t>
+          <t>41.8</t>
         </is>
       </c>
       <c r="AP75" t="inlineStr">
         <is>
-          <t>86.83</t>
+          <t>89.6</t>
         </is>
       </c>
       <c r="AQ75" t="inlineStr">
         <is>
-          <t>97.877</t>
+          <t>100.1929</t>
         </is>
       </c>
       <c r="AR75" t="inlineStr">
         <is>
-          <t>0.3747</t>
+          <t>0.458</t>
         </is>
       </c>
       <c r="AS75" t="inlineStr">
         <is>
-          <t>0.1299</t>
+          <t>0.167</t>
         </is>
       </c>
       <c r="AT75" t="inlineStr">
         <is>
-          <t>0.2938</t>
+          <t>0.353</t>
         </is>
       </c>
       <c r="AU75" t="inlineStr">
         <is>
-          <t>70.23</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="AV75" t="inlineStr">
         <is>
-          <t>9.11</t>
+          <t>18.2</t>
         </is>
       </c>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>36.06</t>
+          <t>31.0</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>24.67</t>
+          <t>26.1</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr">
         <is>
-          <t>10.4</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>0.1594</t>
+          <t>0.145</t>
         </is>
       </c>
       <c r="BA75" t="inlineStr">
         <is>
-          <t>8.8</t>
+          <t>6.56</t>
         </is>
       </c>
       <c r="BB75" t="inlineStr">
         <is>
-          <t>39.1</t>
+          <t>35.86</t>
         </is>
       </c>
       <c r="BC75" t="inlineStr">
         <is>
-          <t>88.8</t>
+          <t>87.99</t>
         </is>
       </c>
       <c r="BD75" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.4123</t>
         </is>
       </c>
       <c r="BE75" t="inlineStr">
         <is>
-          <t>0.152</t>
+          <t>0.1612</t>
         </is>
       </c>
       <c r="BF75" t="inlineStr">
         <is>
-          <t>21.4</t>
+          <t>26.78</t>
         </is>
       </c>
       <c r="BG75" t="inlineStr">
         <is>
-          <t>Out To LF</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BH75" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>83</t>
         </is>
       </c>
       <c r="BI75" t="inlineStr">
         <is>
-          <t>Rate Field</t>
+          <t>Citi Field</t>
         </is>
       </c>
       <c r="BJ75" t="inlineStr"/>
@@ -21359,47 +21359,47 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>679822</t>
+          <t>678882</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Justin Foscue</t>
+          <t>Ceddanne Rafaela</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-07-10T00:05:00Z</t>
+          <t>2026-07-09T18:10:00Z</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Reid Detmers</t>
+          <t>Anthony Kay</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>672282</t>
+          <t>641743</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -21422,65 +21422,61 @@
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P76" t="n">
-        <v>45.8</v>
+        <v>21.8</v>
       </c>
       <c r="Q76" t="n">
-        <v>33.3</v>
+        <v>40.3</v>
       </c>
       <c r="R76" t="n">
-        <v>27.6</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="S76" t="n">
-        <v>88.7</v>
+        <v>100</v>
       </c>
       <c r="T76" t="n">
         <v>78</v>
       </c>
       <c r="U76" t="n">
-        <v>73.90000000000001</v>
+        <v>50.3</v>
       </c>
       <c r="V76" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z76" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W76" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X76" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y76" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z76" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB76" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr"/>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD76" t="inlineStr"/>
@@ -21497,27 +21493,27 @@
       </c>
       <c r="AH76" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AI76" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK76" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Contact streak: 10/30 over last 7 games</t>
         </is>
       </c>
       <c r="AL76" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.3% barrel, 8.1 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.8% barrel, 11.0 HR allowed</t>
         </is>
       </c>
       <c r="AM76" t="inlineStr">
@@ -21527,104 +21523,112 @@
       </c>
       <c r="AN76" t="inlineStr">
         <is>
-          <t>8.75</t>
+          <t>6.33</t>
         </is>
       </c>
       <c r="AO76" t="inlineStr">
         <is>
-          <t>52.07</t>
+          <t>34.78</t>
         </is>
       </c>
       <c r="AP76" t="inlineStr">
         <is>
-          <t>90.55</t>
+          <t>86.83</t>
         </is>
       </c>
       <c r="AQ76" t="inlineStr">
         <is>
-          <t>100.0572</t>
+          <t>97.877</t>
         </is>
       </c>
       <c r="AR76" t="inlineStr">
         <is>
-          <t>0.4295</t>
+          <t>0.3747</t>
         </is>
       </c>
       <c r="AS76" t="inlineStr">
         <is>
-          <t>0.1929</t>
+          <t>0.1299</t>
         </is>
       </c>
       <c r="AT76" t="inlineStr">
         <is>
-          <t>0.3108</t>
+          <t>0.2938</t>
         </is>
       </c>
       <c r="AU76" t="inlineStr">
         <is>
-          <t>70.89</t>
+          <t>70.23</t>
         </is>
       </c>
       <c r="AV76" t="inlineStr">
         <is>
-          <t>9.45</t>
+          <t>9.11</t>
         </is>
       </c>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>43.21</t>
+          <t>36.06</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>33.48</t>
+          <t>24.67</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr">
         <is>
-          <t>4.2</t>
+          <t>10.4</t>
         </is>
       </c>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>0.2069</t>
+          <t>0.1594</t>
         </is>
       </c>
       <c r="BA76" t="inlineStr">
         <is>
-          <t>7.29</t>
+          <t>8.8</t>
         </is>
       </c>
       <c r="BB76" t="inlineStr">
         <is>
-          <t>38.74</t>
+          <t>39.1</t>
         </is>
       </c>
       <c r="BC76" t="inlineStr">
         <is>
-          <t>89.68</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="BD76" t="inlineStr">
         <is>
-          <t>0.3469</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="BE76" t="inlineStr">
         <is>
-          <t>0.1271</t>
+          <t>0.152</t>
         </is>
       </c>
       <c r="BF76" t="inlineStr">
         <is>
-          <t>27.29</t>
-        </is>
-      </c>
-      <c r="BG76" t="inlineStr"/>
-      <c r="BH76" t="inlineStr"/>
+          <t>21.4</t>
+        </is>
+      </c>
+      <c r="BG76" t="inlineStr">
+        <is>
+          <t>Out To LF</t>
+        </is>
+      </c>
+      <c r="BH76" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
       <c r="BI76" t="inlineStr">
         <is>
-          <t>Globe Life Field</t>
+          <t>Rate Field</t>
         </is>
       </c>
       <c r="BJ76" t="inlineStr"/>
@@ -21635,56 +21639,56 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>701807</t>
+          <t>679822</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Carson Benge</t>
+          <t>Justin Foscue</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NYM</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-07-09T17:10:00Z</t>
+          <t>2026-07-10T00:05:00Z</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Michael Wacha</t>
+          <t>Reid Detmers</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>608379</t>
+          <t>672282</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L77" t="n">
-        <v>50.2</v>
+        <v>50.4</v>
       </c>
       <c r="M77" t="inlineStr">
         <is>
@@ -21698,61 +21702,65 @@
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P77" t="n">
-        <v>36.8</v>
+        <v>45.8</v>
       </c>
       <c r="Q77" t="n">
-        <v>34.3</v>
+        <v>33.3</v>
       </c>
       <c r="R77" t="n">
-        <v>44.3</v>
+        <v>27.6</v>
       </c>
       <c r="S77" t="n">
-        <v>94.90000000000001</v>
+        <v>88.7</v>
       </c>
       <c r="T77" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="U77" t="n">
-        <v>54.3</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="V77" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W77" t="inlineStr">
+      <c r="Z77" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X77" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y77" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z77" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB77" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD77" t="inlineStr"/>
@@ -21769,27 +21777,27 @@
       </c>
       <c r="AH77" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI77" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
         <is>
-          <t>Contact streak: 9/25 over last 7 games</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL77" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.6% barrel, 13.6 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.3% barrel, 8.1 HR allowed</t>
         </is>
       </c>
       <c r="AM77" t="inlineStr">
@@ -21799,112 +21807,104 @@
       </c>
       <c r="AN77" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.75</t>
         </is>
       </c>
       <c r="AO77" t="inlineStr">
         <is>
-          <t>41.8</t>
+          <t>52.07</t>
         </is>
       </c>
       <c r="AP77" t="inlineStr">
         <is>
-          <t>89.6</t>
+          <t>90.55</t>
         </is>
       </c>
       <c r="AQ77" t="inlineStr">
         <is>
-          <t>100.1929</t>
+          <t>100.0572</t>
         </is>
       </c>
       <c r="AR77" t="inlineStr">
         <is>
-          <t>0.458</t>
+          <t>0.4295</t>
         </is>
       </c>
       <c r="AS77" t="inlineStr">
         <is>
-          <t>0.167</t>
+          <t>0.1929</t>
         </is>
       </c>
       <c r="AT77" t="inlineStr">
         <is>
-          <t>0.353</t>
+          <t>0.3108</t>
         </is>
       </c>
       <c r="AU77" t="inlineStr">
         <is>
-          <t>71.1</t>
+          <t>70.89</t>
         </is>
       </c>
       <c r="AV77" t="inlineStr">
         <is>
-          <t>18.2</t>
+          <t>9.45</t>
         </is>
       </c>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>31.0</t>
+          <t>43.21</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>26.1</t>
+          <t>33.48</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr">
         <is>
-          <t>11.0</t>
+          <t>4.2</t>
         </is>
       </c>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>0.145</t>
+          <t>0.2069</t>
         </is>
       </c>
       <c r="BA77" t="inlineStr">
         <is>
-          <t>6.56</t>
+          <t>7.29</t>
         </is>
       </c>
       <c r="BB77" t="inlineStr">
         <is>
-          <t>35.86</t>
+          <t>38.74</t>
         </is>
       </c>
       <c r="BC77" t="inlineStr">
         <is>
-          <t>87.99</t>
+          <t>89.68</t>
         </is>
       </c>
       <c r="BD77" t="inlineStr">
         <is>
-          <t>0.4123</t>
+          <t>0.3469</t>
         </is>
       </c>
       <c r="BE77" t="inlineStr">
         <is>
-          <t>0.1612</t>
+          <t>0.1271</t>
         </is>
       </c>
       <c r="BF77" t="inlineStr">
         <is>
-          <t>26.78</t>
-        </is>
-      </c>
-      <c r="BG77" t="inlineStr">
-        <is>
-          <t>In From CF</t>
-        </is>
-      </c>
-      <c r="BH77" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
+          <t>27.29</t>
+        </is>
+      </c>
+      <c r="BG77" t="inlineStr"/>
+      <c r="BH77" t="inlineStr"/>
       <c r="BI77" t="inlineStr">
         <is>
-          <t>Citi Field</t>
+          <t>Globe Life Field</t>
         </is>
       </c>
       <c r="BJ77" t="inlineStr"/>
@@ -26189,7 +26189,7 @@
         <v>78</v>
       </c>
       <c r="U93" t="n">
-        <v>34.4</v>
+        <v>32.9</v>
       </c>
       <c r="V93" t="inlineStr">
         <is>
@@ -26246,7 +26246,7 @@
       </c>
       <c r="AI93" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ93" t="inlineStr">
@@ -26256,7 +26256,7 @@
       </c>
       <c r="AK93" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/22, 1 HR</t>
+          <t>Last 7 games: 5/23, 1 HR</t>
         </is>
       </c>
       <c r="AL93" t="inlineStr">
@@ -26688,7 +26688,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Delayed</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -31424,7 +31424,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Delayed</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -32795,22 +32795,22 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>666182</t>
+          <t>665862</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Bo Bichette</t>
+          <t>Jazz Chisholm Jr.</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NYM</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -32825,17 +32825,17 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>Michael Wacha</t>
+          <t>Drew Rasmussen</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>608379</t>
+          <t>656876</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
@@ -32858,26 +32858,26 @@
       </c>
       <c r="O117" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P117" t="n">
-        <v>35.8</v>
+        <v>42.7</v>
       </c>
       <c r="Q117" t="n">
-        <v>34.3</v>
+        <v>30.2</v>
       </c>
       <c r="R117" t="n">
-        <v>44.3</v>
+        <v>41.1</v>
       </c>
       <c r="S117" t="n">
-        <v>96.59999999999999</v>
+        <v>76.2</v>
       </c>
       <c r="T117" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U117" t="n">
-        <v>32</v>
+        <v>17.7</v>
       </c>
       <c r="V117" t="inlineStr">
         <is>
@@ -32891,7 +32891,7 @@
       </c>
       <c r="X117" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y117" t="inlineStr">
@@ -32929,12 +32929,12 @@
       </c>
       <c r="AH117" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI117" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ117" t="inlineStr">
@@ -32944,12 +32944,12 @@
       </c>
       <c r="AK117" t="inlineStr">
         <is>
-          <t>Contact streak: 10/30 over last 7 games</t>
+          <t>Last 7 games: 5/21, 0 HR</t>
         </is>
       </c>
       <c r="AL117" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.6% barrel, 13.6 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.7% barrel, 13.1 HR allowed</t>
         </is>
       </c>
       <c r="AM117" t="inlineStr">
@@ -32959,112 +32959,112 @@
       </c>
       <c r="AN117" t="inlineStr">
         <is>
-          <t>7.41</t>
+          <t>10.66</t>
         </is>
       </c>
       <c r="AO117" t="inlineStr">
         <is>
-          <t>45.3</t>
+          <t>41.69</t>
         </is>
       </c>
       <c r="AP117" t="inlineStr">
         <is>
-          <t>90.51</t>
+          <t>90.19</t>
         </is>
       </c>
       <c r="AQ117" t="inlineStr">
         <is>
-          <t>101.4865</t>
+          <t>100.405</t>
         </is>
       </c>
       <c r="AR117" t="inlineStr">
         <is>
-          <t>0.4429</t>
+          <t>0.3977</t>
         </is>
       </c>
       <c r="AS117" t="inlineStr">
         <is>
-          <t>0.1552</t>
+          <t>0.1826</t>
         </is>
       </c>
       <c r="AT117" t="inlineStr">
         <is>
-          <t>0.3376</t>
+          <t>0.3082</t>
         </is>
       </c>
       <c r="AU117" t="inlineStr">
         <is>
-          <t>69.8</t>
+          <t>73.34</t>
         </is>
       </c>
       <c r="AV117" t="inlineStr">
         <is>
-          <t>13.6</t>
+          <t>34.48</t>
         </is>
       </c>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>26.42</t>
+          <t>53.24</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>23.23</t>
+          <t>29.77</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr">
         <is>
-          <t>12.4</t>
+          <t>17.7</t>
         </is>
       </c>
       <c r="AZ117" t="inlineStr">
         <is>
-          <t>0.137</t>
+          <t>0.1886</t>
         </is>
       </c>
       <c r="BA117" t="inlineStr">
         <is>
-          <t>6.56</t>
+          <t>6.72</t>
         </is>
       </c>
       <c r="BB117" t="inlineStr">
         <is>
-          <t>35.86</t>
+          <t>36.44</t>
         </is>
       </c>
       <c r="BC117" t="inlineStr">
         <is>
-          <t>87.99</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="BD117" t="inlineStr">
         <is>
-          <t>0.4123</t>
+          <t>0.3652</t>
         </is>
       </c>
       <c r="BE117" t="inlineStr">
         <is>
-          <t>0.1612</t>
+          <t>0.1334</t>
         </is>
       </c>
       <c r="BF117" t="inlineStr">
         <is>
-          <t>26.78</t>
+          <t>22.54</t>
         </is>
       </c>
       <c r="BG117" t="inlineStr">
         <is>
-          <t>In From CF</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH117" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI117" t="inlineStr">
         <is>
-          <t>Citi Field</t>
+          <t>Tropicana Field</t>
         </is>
       </c>
       <c r="BJ117" t="inlineStr"/>
@@ -33075,27 +33075,27 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>665862</t>
+          <t>642086</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Jazz Chisholm Jr.</t>
+          <t>Dominic Smith</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2026-07-09T17:10:00Z</t>
+          <t>2026-07-09T16:35:00Z</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
@@ -33110,12 +33110,12 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>Drew Rasmussen</t>
+          <t>Mitch Keller</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>656876</t>
+          <t>656605</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
@@ -33124,7 +33124,7 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>46.3</v>
+        <v>46.2</v>
       </c>
       <c r="M118" t="inlineStr">
         <is>
@@ -33138,17 +33138,17 @@
       </c>
       <c r="O118" t="inlineStr">
         <is>
-          <t>Strong Barrel, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P118" t="n">
-        <v>42.7</v>
+        <v>23.6</v>
       </c>
       <c r="Q118" t="n">
-        <v>30.2</v>
+        <v>43.5</v>
       </c>
       <c r="R118" t="n">
-        <v>41.1</v>
+        <v>63.3</v>
       </c>
       <c r="S118" t="n">
         <v>76.2</v>
@@ -33157,7 +33157,7 @@
         <v>80</v>
       </c>
       <c r="U118" t="n">
-        <v>17.7</v>
+        <v>12</v>
       </c>
       <c r="V118" t="inlineStr">
         <is>
@@ -33214,7 +33214,7 @@
       </c>
       <c r="AI118" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ118" t="inlineStr">
@@ -33224,12 +33224,12 @@
       </c>
       <c r="AK118" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/21, 0 HR</t>
+          <t>Last 7 games: 5/25, 0 HR</t>
         </is>
       </c>
       <c r="AL118" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.7% barrel, 13.1 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.5% barrel, 14.7 HR allowed</t>
         </is>
       </c>
       <c r="AM118" t="inlineStr">
@@ -33239,112 +33239,112 @@
       </c>
       <c r="AN118" t="inlineStr">
         <is>
-          <t>10.66</t>
+          <t>5.67</t>
         </is>
       </c>
       <c r="AO118" t="inlineStr">
         <is>
-          <t>41.69</t>
+          <t>35.15</t>
         </is>
       </c>
       <c r="AP118" t="inlineStr">
         <is>
-          <t>90.19</t>
+          <t>87.63</t>
         </is>
       </c>
       <c r="AQ118" t="inlineStr">
         <is>
-          <t>100.405</t>
+          <t>98.233</t>
         </is>
       </c>
       <c r="AR118" t="inlineStr">
         <is>
-          <t>0.3977</t>
+          <t>0.4036</t>
         </is>
       </c>
       <c r="AS118" t="inlineStr">
         <is>
-          <t>0.1826</t>
+          <t>0.1443</t>
         </is>
       </c>
       <c r="AT118" t="inlineStr">
         <is>
-          <t>0.3082</t>
+          <t>0.3116</t>
         </is>
       </c>
       <c r="AU118" t="inlineStr">
         <is>
-          <t>73.34</t>
+          <t>68.4</t>
         </is>
       </c>
       <c r="AV118" t="inlineStr">
         <is>
-          <t>34.48</t>
+          <t>4.87</t>
         </is>
       </c>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>53.24</t>
+          <t>35.67</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>29.77</t>
+          <t>28.47</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>5.7</t>
         </is>
       </c>
       <c r="AZ118" t="inlineStr">
         <is>
-          <t>0.1886</t>
+          <t>0.1302</t>
         </is>
       </c>
       <c r="BA118" t="inlineStr">
         <is>
-          <t>6.72</t>
+          <t>7.45</t>
         </is>
       </c>
       <c r="BB118" t="inlineStr">
         <is>
-          <t>36.44</t>
+          <t>42.54</t>
         </is>
       </c>
       <c r="BC118" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>89.47</t>
         </is>
       </c>
       <c r="BD118" t="inlineStr">
         <is>
-          <t>0.3652</t>
+          <t>0.4461</t>
         </is>
       </c>
       <c r="BE118" t="inlineStr">
         <is>
-          <t>0.1334</t>
+          <t>0.164</t>
         </is>
       </c>
       <c r="BF118" t="inlineStr">
         <is>
-          <t>22.54</t>
+          <t>24.26</t>
         </is>
       </c>
       <c r="BG118" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Out To LF</t>
         </is>
       </c>
       <c r="BH118" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>82</t>
         </is>
       </c>
       <c r="BI118" t="inlineStr">
         <is>
-          <t>Tropicana Field</t>
+          <t>PNC Park</t>
         </is>
       </c>
       <c r="BJ118" t="inlineStr"/>
@@ -33355,47 +33355,47 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>642086</t>
+          <t>666182</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Dominic Smith</t>
+          <t>Bo Bichette</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>NYM</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>2026-07-09T16:35:00Z</t>
+          <t>2026-07-09T17:10:00Z</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Delayed</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>Mitch Keller</t>
+          <t>Michael Wacha</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>656605</t>
+          <t>608379</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
@@ -33418,26 +33418,26 @@
       </c>
       <c r="O119" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P119" t="n">
-        <v>23.6</v>
+        <v>35.8</v>
       </c>
       <c r="Q119" t="n">
-        <v>43.5</v>
+        <v>34.3</v>
       </c>
       <c r="R119" t="n">
-        <v>63.3</v>
+        <v>44.3</v>
       </c>
       <c r="S119" t="n">
-        <v>76.2</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T119" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U119" t="n">
-        <v>12</v>
+        <v>30.4</v>
       </c>
       <c r="V119" t="inlineStr">
         <is>
@@ -33451,7 +33451,7 @@
       </c>
       <c r="X119" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y119" t="inlineStr">
@@ -33489,12 +33489,12 @@
       </c>
       <c r="AH119" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AI119" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>31</t>
         </is>
       </c>
       <c r="AJ119" t="inlineStr">
@@ -33504,12 +33504,12 @@
       </c>
       <c r="AK119" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/25, 0 HR</t>
+          <t>Contact streak: 10/31 over last 7 games</t>
         </is>
       </c>
       <c r="AL119" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.5% barrel, 14.7 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.6% barrel, 13.6 HR allowed</t>
         </is>
       </c>
       <c r="AM119" t="inlineStr">
@@ -33519,112 +33519,112 @@
       </c>
       <c r="AN119" t="inlineStr">
         <is>
-          <t>5.67</t>
+          <t>7.41</t>
         </is>
       </c>
       <c r="AO119" t="inlineStr">
         <is>
-          <t>35.15</t>
+          <t>45.3</t>
         </is>
       </c>
       <c r="AP119" t="inlineStr">
         <is>
-          <t>87.63</t>
+          <t>90.51</t>
         </is>
       </c>
       <c r="AQ119" t="inlineStr">
         <is>
-          <t>98.233</t>
+          <t>101.4865</t>
         </is>
       </c>
       <c r="AR119" t="inlineStr">
         <is>
-          <t>0.4036</t>
+          <t>0.4429</t>
         </is>
       </c>
       <c r="AS119" t="inlineStr">
         <is>
-          <t>0.1443</t>
+          <t>0.1552</t>
         </is>
       </c>
       <c r="AT119" t="inlineStr">
         <is>
-          <t>0.3116</t>
+          <t>0.3376</t>
         </is>
       </c>
       <c r="AU119" t="inlineStr">
         <is>
-          <t>68.4</t>
+          <t>69.8</t>
         </is>
       </c>
       <c r="AV119" t="inlineStr">
         <is>
-          <t>4.87</t>
+          <t>13.6</t>
         </is>
       </c>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>35.67</t>
+          <t>26.42</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>28.47</t>
+          <t>23.23</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr">
         <is>
-          <t>5.7</t>
+          <t>12.4</t>
         </is>
       </c>
       <c r="AZ119" t="inlineStr">
         <is>
-          <t>0.1302</t>
+          <t>0.137</t>
         </is>
       </c>
       <c r="BA119" t="inlineStr">
         <is>
-          <t>7.45</t>
+          <t>6.56</t>
         </is>
       </c>
       <c r="BB119" t="inlineStr">
         <is>
-          <t>42.54</t>
+          <t>35.86</t>
         </is>
       </c>
       <c r="BC119" t="inlineStr">
         <is>
-          <t>89.47</t>
+          <t>87.99</t>
         </is>
       </c>
       <c r="BD119" t="inlineStr">
         <is>
-          <t>0.4461</t>
+          <t>0.4123</t>
         </is>
       </c>
       <c r="BE119" t="inlineStr">
         <is>
-          <t>0.164</t>
+          <t>0.1612</t>
         </is>
       </c>
       <c r="BF119" t="inlineStr">
         <is>
-          <t>24.26</t>
+          <t>26.78</t>
         </is>
       </c>
       <c r="BG119" t="inlineStr">
         <is>
-          <t>Out To LF</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BH119" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>83</t>
         </is>
       </c>
       <c r="BI119" t="inlineStr">
         <is>
-          <t>PNC Park</t>
+          <t>Citi Field</t>
         </is>
       </c>
       <c r="BJ119" t="inlineStr"/>
@@ -34326,7 +34326,7 @@
       </c>
       <c r="AI122" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ122" t="inlineStr">
@@ -34336,7 +34336,7 @@
       </c>
       <c r="AK122" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/26, 0 HR</t>
+          <t>Last 7 games: 3/27, 0 HR</t>
         </is>
       </c>
       <c r="AL122" t="inlineStr">
@@ -34829,7 +34829,7 @@
         <v>75</v>
       </c>
       <c r="U124" t="n">
-        <v>61.5</v>
+        <v>59.6</v>
       </c>
       <c r="V124" t="inlineStr">
         <is>
@@ -34886,7 +34886,7 @@
       </c>
       <c r="AI124" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ124" t="inlineStr">
@@ -40304,7 +40304,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Delayed</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -41955,52 +41955,52 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>702222</t>
+          <t>702332</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Justin Crawford</t>
+          <t>Caleb Durbin</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>2026-07-09T23:10:00Z</t>
+          <t>2026-07-09T18:10:00Z</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>Brady Singer</t>
+          <t>Anthony Kay</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>663903</t>
+          <t>641743</t>
         </is>
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L150" t="n">
@@ -42018,65 +42018,61 @@
       </c>
       <c r="O150" t="inlineStr">
         <is>
-          <t>Projected Lineup, Good Environment, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P150" t="n">
-        <v>8.9</v>
+        <v>7.3</v>
       </c>
       <c r="Q150" t="n">
-        <v>58.6</v>
+        <v>40.3</v>
       </c>
       <c r="R150" t="n">
-        <v>79.8</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="S150" t="n">
-        <v>40.2</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T150" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="U150" t="n">
-        <v>32</v>
+        <v>44.8</v>
       </c>
       <c r="V150" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W150" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X150" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y150" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z150" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W150" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X150" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y150" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z150" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA150" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB150" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB150" t="inlineStr"/>
       <c r="AC150" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD150" t="inlineStr"/>
@@ -42093,27 +42089,27 @@
       </c>
       <c r="AH150" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI150" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK150" t="inlineStr">
         <is>
-          <t>Contact streak: 7/21 over last 7 games</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL150" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 10.7% barrel, 19.7 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.8% barrel, 11.0 HR allowed</t>
         </is>
       </c>
       <c r="AM150" t="inlineStr">
@@ -42123,97 +42119,97 @@
       </c>
       <c r="AN150" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>3.3</t>
         </is>
       </c>
       <c r="AO150" t="inlineStr">
         <is>
-          <t>33.0</t>
+          <t>28.51</t>
         </is>
       </c>
       <c r="AP150" t="inlineStr">
         <is>
-          <t>86.7</t>
+          <t>84.92</t>
         </is>
       </c>
       <c r="AQ150" t="inlineStr">
         <is>
-          <t>97.5538</t>
+          <t>96.3013</t>
         </is>
       </c>
       <c r="AR150" t="inlineStr">
         <is>
-          <t>0.317</t>
+          <t>0.3424</t>
         </is>
       </c>
       <c r="AS150" t="inlineStr">
         <is>
-          <t>0.063</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="AT150" t="inlineStr">
         <is>
-          <t>0.279</t>
+          <t>0.2938</t>
         </is>
       </c>
       <c r="AU150" t="inlineStr">
         <is>
-          <t>68.8</t>
+          <t>68.67</t>
         </is>
       </c>
       <c r="AV150" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>5.12</t>
         </is>
       </c>
       <c r="AW150" t="inlineStr">
         <is>
-          <t>27.2</t>
+          <t>42.42</t>
         </is>
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>16.0</t>
+          <t>18.56</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>8.9</t>
         </is>
       </c>
       <c r="AZ150" t="inlineStr">
         <is>
-          <t>0.092</t>
+          <t>0.1527</t>
         </is>
       </c>
       <c r="BA150" t="inlineStr">
         <is>
-          <t>10.73</t>
+          <t>8.8</t>
         </is>
       </c>
       <c r="BB150" t="inlineStr">
         <is>
-          <t>40.77</t>
+          <t>39.1</t>
         </is>
       </c>
       <c r="BC150" t="inlineStr">
         <is>
-          <t>90.86</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="BD150" t="inlineStr">
         <is>
-          <t>0.4608</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="BE150" t="inlineStr">
         <is>
-          <t>0.1982</t>
+          <t>0.152</t>
         </is>
       </c>
       <c r="BF150" t="inlineStr">
         <is>
-          <t>28.96</t>
+          <t>21.4</t>
         </is>
       </c>
       <c r="BG150" t="inlineStr">
@@ -42223,12 +42219,12 @@
       </c>
       <c r="BH150" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>80</t>
         </is>
       </c>
       <c r="BI150" t="inlineStr">
         <is>
-          <t>Great American Ball Park</t>
+          <t>Rate Field</t>
         </is>
       </c>
       <c r="BJ150" t="inlineStr"/>
@@ -42239,56 +42235,56 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>695731</t>
+          <t>702222</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Braden Montgomery</t>
+          <t>Justin Crawford</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>2026-07-09T18:10:00Z</t>
+          <t>2026-07-09T23:10:00Z</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>Patrick Sandoval</t>
+          <t>Brady Singer</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>663776</t>
+          <t>663903</t>
         </is>
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L151" t="n">
-        <v>43.2</v>
+        <v>43.4</v>
       </c>
       <c r="M151" t="inlineStr">
         <is>
@@ -42302,61 +42298,65 @@
       </c>
       <c r="O151" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Projected Lineup, Good Environment, Platoon Edge</t>
         </is>
       </c>
       <c r="P151" t="n">
-        <v>21.5</v>
+        <v>8.9</v>
       </c>
       <c r="Q151" t="n">
+        <v>58.6</v>
+      </c>
+      <c r="R151" t="n">
+        <v>79.8</v>
+      </c>
+      <c r="S151" t="n">
         <v>40.2</v>
       </c>
-      <c r="R151" t="n">
-        <v>66.59999999999999</v>
-      </c>
-      <c r="S151" t="n">
-        <v>64.3</v>
-      </c>
       <c r="T151" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="U151" t="n">
-        <v>14.6</v>
+        <v>32</v>
       </c>
       <c r="V151" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W151" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X151" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y151" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W151" t="inlineStr">
+      <c r="Z151" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X151" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y151" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z151" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA151" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB151" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB151" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC151" t="inlineStr">
         <is>
-          <t>H:2026 P:</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD151" t="inlineStr"/>
@@ -42373,12 +42373,12 @@
       </c>
       <c r="AH151" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI151" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ151" t="inlineStr">
@@ -42388,12 +42388,12 @@
       </c>
       <c r="AK151" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/23, 0 HR</t>
+          <t>Contact streak: 7/21 over last 7 games</t>
         </is>
       </c>
       <c r="AL151" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 10.7% barrel, 19.7 HR allowed</t>
         </is>
       </c>
       <c r="AM151" t="inlineStr">
@@ -42403,57 +42403,57 @@
       </c>
       <c r="AN151" t="inlineStr">
         <is>
-          <t>4.4</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AO151" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>33.0</t>
         </is>
       </c>
       <c r="AP151" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>86.7</t>
         </is>
       </c>
       <c r="AQ151" t="inlineStr">
         <is>
-          <t>100.2588</t>
+          <t>97.5538</t>
         </is>
       </c>
       <c r="AR151" t="inlineStr">
         <is>
-          <t>0.351</t>
+          <t>0.317</t>
         </is>
       </c>
       <c r="AS151" t="inlineStr">
         <is>
-          <t>0.114</t>
+          <t>0.063</t>
         </is>
       </c>
       <c r="AT151" t="inlineStr">
         <is>
-          <t>0.297</t>
+          <t>0.279</t>
         </is>
       </c>
       <c r="AU151" t="inlineStr">
         <is>
-          <t>69.9</t>
+          <t>68.8</t>
         </is>
       </c>
       <c r="AV151" t="inlineStr">
         <is>
-          <t>9.8</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AW151" t="inlineStr">
         <is>
-          <t>36.8</t>
+          <t>27.2</t>
         </is>
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>19.1</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="AY151" t="inlineStr">
@@ -42463,15 +42463,39 @@
       </c>
       <c r="AZ151" t="inlineStr">
         <is>
-          <t>0.157</t>
-        </is>
-      </c>
-      <c r="BA151" t="inlineStr"/>
-      <c r="BB151" t="inlineStr"/>
-      <c r="BC151" t="inlineStr"/>
-      <c r="BD151" t="inlineStr"/>
-      <c r="BE151" t="inlineStr"/>
-      <c r="BF151" t="inlineStr"/>
+          <t>0.092</t>
+        </is>
+      </c>
+      <c r="BA151" t="inlineStr">
+        <is>
+          <t>10.73</t>
+        </is>
+      </c>
+      <c r="BB151" t="inlineStr">
+        <is>
+          <t>40.77</t>
+        </is>
+      </c>
+      <c r="BC151" t="inlineStr">
+        <is>
+          <t>90.86</t>
+        </is>
+      </c>
+      <c r="BD151" t="inlineStr">
+        <is>
+          <t>0.4608</t>
+        </is>
+      </c>
+      <c r="BE151" t="inlineStr">
+        <is>
+          <t>0.1982</t>
+        </is>
+      </c>
+      <c r="BF151" t="inlineStr">
+        <is>
+          <t>28.96</t>
+        </is>
+      </c>
       <c r="BG151" t="inlineStr">
         <is>
           <t>Out To LF</t>
@@ -42479,12 +42503,12 @@
       </c>
       <c r="BH151" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>87</t>
         </is>
       </c>
       <c r="BI151" t="inlineStr">
         <is>
-          <t>Rate Field</t>
+          <t>Great American Ball Park</t>
         </is>
       </c>
       <c r="BJ151" t="inlineStr"/>
@@ -42495,56 +42519,56 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>643289</t>
+          <t>695731</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Mauricio Dubón</t>
+          <t>Braden Montgomery</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>2026-07-09T16:35:00Z</t>
+          <t>2026-07-09T18:10:00Z</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Delayed</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>Mitch Keller</t>
+          <t>Patrick Sandoval</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>656605</t>
+          <t>663776</t>
         </is>
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L152" t="n">
-        <v>42.8</v>
+        <v>43.2</v>
       </c>
       <c r="M152" t="inlineStr">
         <is>
@@ -42558,26 +42582,26 @@
       </c>
       <c r="O152" t="inlineStr">
         <is>
-          <t>No major boost</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P152" t="n">
-        <v>12.1</v>
+        <v>21.5</v>
       </c>
       <c r="Q152" t="n">
-        <v>43.5</v>
+        <v>40.2</v>
       </c>
       <c r="R152" t="n">
-        <v>63.3</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="S152" t="n">
-        <v>86.40000000000001</v>
+        <v>64.3</v>
       </c>
       <c r="T152" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="U152" t="n">
-        <v>44.8</v>
+        <v>14.6</v>
       </c>
       <c r="V152" t="inlineStr">
         <is>
@@ -42591,7 +42615,7 @@
       </c>
       <c r="X152" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y152" t="inlineStr">
@@ -42612,7 +42636,7 @@
       <c r="AB152" t="inlineStr"/>
       <c r="AC152" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:</t>
         </is>
       </c>
       <c r="AD152" t="inlineStr"/>
@@ -42629,27 +42653,27 @@
       </c>
       <c r="AH152" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI152" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ152" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK152" t="inlineStr">
         <is>
-          <t>Last 7 games: 8/27, 1 HR</t>
+          <t>Last 7 games: 5/23, 0 HR</t>
         </is>
       </c>
       <c r="AL152" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.5% barrel, 14.7 HR allowed</t>
+          <t>switch hitter; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
         </is>
       </c>
       <c r="AM152" t="inlineStr">
@@ -42659,99 +42683,75 @@
       </c>
       <c r="AN152" t="inlineStr">
         <is>
-          <t>3.65</t>
+          <t>4.4</t>
         </is>
       </c>
       <c r="AO152" t="inlineStr">
         <is>
-          <t>29.73</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="AP152" t="inlineStr">
         <is>
-          <t>85.76</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AQ152" t="inlineStr">
         <is>
-          <t>96.464</t>
+          <t>100.2588</t>
         </is>
       </c>
       <c r="AR152" t="inlineStr">
         <is>
-          <t>0.3765</t>
+          <t>0.351</t>
         </is>
       </c>
       <c r="AS152" t="inlineStr">
         <is>
-          <t>0.1106</t>
+          <t>0.114</t>
         </is>
       </c>
       <c r="AT152" t="inlineStr">
         <is>
-          <t>0.3074</t>
+          <t>0.297</t>
         </is>
       </c>
       <c r="AU152" t="inlineStr">
         <is>
-          <t>68.69</t>
+          <t>69.9</t>
         </is>
       </c>
       <c r="AV152" t="inlineStr">
         <is>
-          <t>2.84</t>
+          <t>9.8</t>
         </is>
       </c>
       <c r="AW152" t="inlineStr">
         <is>
-          <t>32.1</t>
+          <t>36.8</t>
         </is>
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>24.53</t>
+          <t>19.1</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AZ152" t="inlineStr">
         <is>
-          <t>0.1413</t>
-        </is>
-      </c>
-      <c r="BA152" t="inlineStr">
-        <is>
-          <t>7.45</t>
-        </is>
-      </c>
-      <c r="BB152" t="inlineStr">
-        <is>
-          <t>42.54</t>
-        </is>
-      </c>
-      <c r="BC152" t="inlineStr">
-        <is>
-          <t>89.47</t>
-        </is>
-      </c>
-      <c r="BD152" t="inlineStr">
-        <is>
-          <t>0.4461</t>
-        </is>
-      </c>
-      <c r="BE152" t="inlineStr">
-        <is>
-          <t>0.164</t>
-        </is>
-      </c>
-      <c r="BF152" t="inlineStr">
-        <is>
-          <t>24.26</t>
-        </is>
-      </c>
+          <t>0.157</t>
+        </is>
+      </c>
+      <c r="BA152" t="inlineStr"/>
+      <c r="BB152" t="inlineStr"/>
+      <c r="BC152" t="inlineStr"/>
+      <c r="BD152" t="inlineStr"/>
+      <c r="BE152" t="inlineStr"/>
+      <c r="BF152" t="inlineStr"/>
       <c r="BG152" t="inlineStr">
         <is>
           <t>Out To LF</t>
@@ -42759,12 +42759,12 @@
       </c>
       <c r="BH152" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>80</t>
         </is>
       </c>
       <c r="BI152" t="inlineStr">
         <is>
-          <t>PNC Park</t>
+          <t>Rate Field</t>
         </is>
       </c>
       <c r="BJ152" t="inlineStr"/>
@@ -42775,56 +42775,56 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>691720</t>
+          <t>643289</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Kyle Karros</t>
+          <t>Mauricio Dubón</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>2026-07-10T01:45:00Z</t>
+          <t>2026-07-09T16:35:00Z</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>Carson Whisenhunt</t>
+          <t>Mitch Keller</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>687931</t>
+          <t>656605</t>
         </is>
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L153" t="n">
-        <v>42.7</v>
+        <v>42.8</v>
       </c>
       <c r="M153" t="inlineStr">
         <is>
@@ -42838,62 +42838,58 @@
       </c>
       <c r="O153" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P153" t="n">
-        <v>25.9</v>
+        <v>12.1</v>
       </c>
       <c r="Q153" t="n">
-        <v>31.9</v>
+        <v>43.5</v>
       </c>
       <c r="R153" t="n">
-        <v>19.3</v>
+        <v>63.3</v>
       </c>
       <c r="S153" t="n">
-        <v>95.5</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T153" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U153" t="n">
-        <v>64.8</v>
+        <v>44.8</v>
       </c>
       <c r="V153" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W153" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X153" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y153" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z153" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W153" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X153" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y153" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z153" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA153" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB153" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB153" t="inlineStr"/>
       <c r="AC153" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -42918,129 +42914,137 @@
       </c>
       <c r="AI153" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 8/27, 1 HR</t>
         </is>
       </c>
       <c r="AL153" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 3.8% barrel, 1.8 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.5% barrel, 14.7 HR allowed</t>
         </is>
       </c>
       <c r="AM153" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN153" t="inlineStr">
         <is>
-          <t>6.32</t>
+          <t>3.65</t>
         </is>
       </c>
       <c r="AO153" t="inlineStr">
         <is>
-          <t>40.7</t>
+          <t>29.73</t>
         </is>
       </c>
       <c r="AP153" t="inlineStr">
         <is>
-          <t>89.02</t>
+          <t>85.76</t>
         </is>
       </c>
       <c r="AQ153" t="inlineStr">
         <is>
-          <t>99.7297</t>
+          <t>96.464</t>
         </is>
       </c>
       <c r="AR153" t="inlineStr">
         <is>
-          <t>0.3649</t>
+          <t>0.3765</t>
         </is>
       </c>
       <c r="AS153" t="inlineStr">
         <is>
-          <t>0.1229</t>
+          <t>0.1106</t>
         </is>
       </c>
       <c r="AT153" t="inlineStr">
         <is>
-          <t>0.3168</t>
+          <t>0.3074</t>
         </is>
       </c>
       <c r="AU153" t="inlineStr">
         <is>
-          <t>70.01</t>
+          <t>68.69</t>
         </is>
       </c>
       <c r="AV153" t="inlineStr">
         <is>
-          <t>5.93</t>
+          <t>2.84</t>
         </is>
       </c>
       <c r="AW153" t="inlineStr">
         <is>
-          <t>39.15</t>
+          <t>32.1</t>
         </is>
       </c>
       <c r="AX153" t="inlineStr">
         <is>
-          <t>23.22</t>
+          <t>24.53</t>
         </is>
       </c>
       <c r="AY153" t="inlineStr">
         <is>
-          <t>5.9</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="AZ153" t="inlineStr">
         <is>
-          <t>0.1385</t>
+          <t>0.1413</t>
         </is>
       </c>
       <c r="BA153" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>7.45</t>
         </is>
       </c>
       <c r="BB153" t="inlineStr">
         <is>
-          <t>40.34</t>
+          <t>42.54</t>
         </is>
       </c>
       <c r="BC153" t="inlineStr">
         <is>
-          <t>89.74</t>
+          <t>89.47</t>
         </is>
       </c>
       <c r="BD153" t="inlineStr">
         <is>
-          <t>0.4295</t>
+          <t>0.4461</t>
         </is>
       </c>
       <c r="BE153" t="inlineStr">
         <is>
-          <t>0.1486</t>
+          <t>0.164</t>
         </is>
       </c>
       <c r="BF153" t="inlineStr">
         <is>
-          <t>34.1</t>
-        </is>
-      </c>
-      <c r="BG153" t="inlineStr"/>
-      <c r="BH153" t="inlineStr"/>
+          <t>24.26</t>
+        </is>
+      </c>
+      <c r="BG153" t="inlineStr">
+        <is>
+          <t>Out To LF</t>
+        </is>
+      </c>
+      <c r="BH153" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
       <c r="BI153" t="inlineStr">
         <is>
-          <t>Oracle Park</t>
+          <t>PNC Park</t>
         </is>
       </c>
       <c r="BJ153" t="inlineStr"/>
@@ -43051,27 +43055,27 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>641680</t>
+          <t>691720</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Jonah Heim</t>
+          <t>Kyle Karros</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>2026-07-09T22:40:00Z</t>
+          <t>2026-07-10T01:45:00Z</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
@@ -43081,17 +43085,17 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>Framber Valdez</t>
+          <t>Carson Whisenhunt</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>664285</t>
+          <t>687931</t>
         </is>
       </c>
       <c r="K154" t="inlineStr">
@@ -43100,7 +43104,7 @@
         </is>
       </c>
       <c r="L154" t="n">
-        <v>42.5</v>
+        <v>42.7</v>
       </c>
       <c r="M154" t="inlineStr">
         <is>
@@ -43114,26 +43118,26 @@
       </c>
       <c r="O154" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P154" t="n">
-        <v>25.4</v>
+        <v>25.9</v>
       </c>
       <c r="Q154" t="n">
-        <v>36.7</v>
+        <v>31.9</v>
       </c>
       <c r="R154" t="n">
-        <v>27.6</v>
+        <v>19.3</v>
       </c>
       <c r="S154" t="n">
-        <v>81.90000000000001</v>
+        <v>95.5</v>
       </c>
       <c r="T154" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="U154" t="n">
-        <v>59.1</v>
+        <v>64.8</v>
       </c>
       <c r="V154" t="inlineStr">
         <is>
@@ -43147,7 +43151,7 @@
       </c>
       <c r="X154" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y154" t="inlineStr">
@@ -43189,7 +43193,7 @@
       </c>
       <c r="AH154" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI154" t="inlineStr">
@@ -43209,114 +43213,114 @@
       </c>
       <c r="AL154" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 6.8% barrel, 12.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 3.8% barrel, 1.8 HR allowed</t>
         </is>
       </c>
       <c r="AM154" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN154" t="inlineStr">
         <is>
-          <t>7.01</t>
+          <t>6.32</t>
         </is>
       </c>
       <c r="AO154" t="inlineStr">
         <is>
-          <t>31.63</t>
+          <t>40.7</t>
         </is>
       </c>
       <c r="AP154" t="inlineStr">
         <is>
-          <t>87.54</t>
+          <t>89.02</t>
         </is>
       </c>
       <c r="AQ154" t="inlineStr">
         <is>
-          <t>97.9399</t>
+          <t>99.7297</t>
         </is>
       </c>
       <c r="AR154" t="inlineStr">
         <is>
-          <t>0.3866</t>
+          <t>0.3649</t>
         </is>
       </c>
       <c r="AS154" t="inlineStr">
         <is>
-          <t>0.1571</t>
+          <t>0.1229</t>
         </is>
       </c>
       <c r="AT154" t="inlineStr">
         <is>
-          <t>0.2963</t>
+          <t>0.3168</t>
         </is>
       </c>
       <c r="AU154" t="inlineStr">
         <is>
-          <t>69.77</t>
+          <t>70.01</t>
         </is>
       </c>
       <c r="AV154" t="inlineStr">
         <is>
-          <t>9.8</t>
+          <t>5.93</t>
         </is>
       </c>
       <c r="AW154" t="inlineStr">
         <is>
-          <t>38.81</t>
+          <t>39.15</t>
         </is>
       </c>
       <c r="AX154" t="inlineStr">
         <is>
-          <t>29.58</t>
+          <t>23.22</t>
         </is>
       </c>
       <c r="AY154" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>5.9</t>
         </is>
       </c>
       <c r="AZ154" t="inlineStr">
         <is>
-          <t>0.2058</t>
+          <t>0.1385</t>
         </is>
       </c>
       <c r="BA154" t="inlineStr">
         <is>
-          <t>6.84</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="BB154" t="inlineStr">
         <is>
-          <t>43.36</t>
+          <t>40.34</t>
         </is>
       </c>
       <c r="BC154" t="inlineStr">
         <is>
-          <t>90.17</t>
+          <t>89.74</t>
         </is>
       </c>
       <c r="BD154" t="inlineStr">
         <is>
-          <t>0.3952</t>
+          <t>0.4295</t>
         </is>
       </c>
       <c r="BE154" t="inlineStr">
         <is>
-          <t>0.1444</t>
+          <t>0.1486</t>
         </is>
       </c>
       <c r="BF154" t="inlineStr">
         <is>
-          <t>20.84</t>
+          <t>34.1</t>
         </is>
       </c>
       <c r="BG154" t="inlineStr"/>
       <c r="BH154" t="inlineStr"/>
       <c r="BI154" t="inlineStr">
         <is>
-          <t>Comerica Park</t>
+          <t>Oracle Park</t>
         </is>
       </c>
       <c r="BJ154" t="inlineStr"/>
@@ -43327,56 +43331,56 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>668723</t>
+          <t>641680</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Ryan Vilade</t>
+          <t>Jonah Heim</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>2026-07-09T17:10:00Z</t>
+          <t>2026-07-09T22:40:00Z</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>Paul Blackburn</t>
+          <t>Framber Valdez</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>621112</t>
+          <t>664285</t>
         </is>
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L155" t="n">
-        <v>42.2</v>
+        <v>42.5</v>
       </c>
       <c r="M155" t="inlineStr">
         <is>
@@ -43390,60 +43394,60 @@
       </c>
       <c r="O155" t="inlineStr">
         <is>
-          <t>No major boost</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P155" t="n">
-        <v>41.1</v>
+        <v>25.4</v>
       </c>
       <c r="Q155" t="n">
-        <v>22.4</v>
+        <v>36.7</v>
       </c>
       <c r="R155" t="n">
-        <v>41.1</v>
+        <v>27.6</v>
       </c>
       <c r="S155" t="n">
-        <v>76.2</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T155" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="U155" t="n">
-        <v>37.4</v>
+        <v>59.1</v>
       </c>
       <c r="V155" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W155" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X155" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y155" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W155" t="inlineStr">
+      <c r="Z155" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X155" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y155" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z155" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA155" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
         </is>
       </c>
       <c r="AB155" t="inlineStr">
         <is>
-          <t>order MLB 6 vs RotoWire 5</t>
+          <t>lineup projected / unconfirmed</t>
         </is>
       </c>
       <c r="AC155" t="inlineStr">
@@ -43465,12 +43469,12 @@
       </c>
       <c r="AH155" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI155" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ155" t="inlineStr">
@@ -43485,7 +43489,7 @@
       </c>
       <c r="AL155" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.6% barrel, 3.9 HR allowed</t>
+          <t>switch hitter; pitcher baseline 6.8% barrel, 12.2 HR allowed</t>
         </is>
       </c>
       <c r="AM155" t="inlineStr">
@@ -43495,112 +43499,104 @@
       </c>
       <c r="AN155" t="inlineStr">
         <is>
-          <t>7.74</t>
+          <t>7.01</t>
         </is>
       </c>
       <c r="AO155" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>31.63</t>
         </is>
       </c>
       <c r="AP155" t="inlineStr">
         <is>
-          <t>91.35</t>
+          <t>87.54</t>
         </is>
       </c>
       <c r="AQ155" t="inlineStr">
         <is>
-          <t>102.2367</t>
+          <t>97.9399</t>
         </is>
       </c>
       <c r="AR155" t="inlineStr">
         <is>
-          <t>0.3851</t>
+          <t>0.3866</t>
         </is>
       </c>
       <c r="AS155" t="inlineStr">
         <is>
-          <t>0.1527</t>
+          <t>0.1571</t>
         </is>
       </c>
       <c r="AT155" t="inlineStr">
         <is>
-          <t>0.3069</t>
+          <t>0.2963</t>
         </is>
       </c>
       <c r="AU155" t="inlineStr">
         <is>
-          <t>75.66</t>
+          <t>69.77</t>
         </is>
       </c>
       <c r="AV155" t="inlineStr">
         <is>
-          <t>55.72</t>
+          <t>9.8</t>
         </is>
       </c>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>22.47</t>
+          <t>38.81</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>24.89</t>
+          <t>29.58</t>
         </is>
       </c>
       <c r="AY155" t="inlineStr">
         <is>
-          <t>4.2</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="AZ155" t="inlineStr">
         <is>
-          <t>0.1372</t>
+          <t>0.2058</t>
         </is>
       </c>
       <c r="BA155" t="inlineStr">
         <is>
-          <t>6.64</t>
+          <t>6.84</t>
         </is>
       </c>
       <c r="BB155" t="inlineStr">
         <is>
-          <t>33.52</t>
+          <t>43.36</t>
         </is>
       </c>
       <c r="BC155" t="inlineStr">
         <is>
-          <t>86.61</t>
+          <t>90.17</t>
         </is>
       </c>
       <c r="BD155" t="inlineStr">
         <is>
-          <t>0.3633</t>
+          <t>0.3952</t>
         </is>
       </c>
       <c r="BE155" t="inlineStr">
         <is>
-          <t>0.1242</t>
+          <t>0.1444</t>
         </is>
       </c>
       <c r="BF155" t="inlineStr">
         <is>
-          <t>21.79</t>
-        </is>
-      </c>
-      <c r="BG155" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="BH155" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
+          <t>20.84</t>
+        </is>
+      </c>
+      <c r="BG155" t="inlineStr"/>
+      <c r="BH155" t="inlineStr"/>
       <c r="BI155" t="inlineStr">
         <is>
-          <t>Tropicana Field</t>
+          <t>Comerica Park</t>
         </is>
       </c>
       <c r="BJ155" t="inlineStr"/>
@@ -43611,27 +43607,27 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>702332</t>
+          <t>683146</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Caleb Durbin</t>
+          <t>Brett Baty</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>NYM</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>2026-07-09T18:10:00Z</t>
+          <t>2026-07-09T17:10:00Z</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
@@ -43641,26 +43637,26 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>Anthony Kay</t>
+          <t>Michael Wacha</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>641743</t>
+          <t>608379</t>
         </is>
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L156" t="n">
-        <v>42.2</v>
+        <v>42.1</v>
       </c>
       <c r="M156" t="inlineStr">
         <is>
@@ -43678,22 +43674,22 @@
         </is>
       </c>
       <c r="P156" t="n">
-        <v>7.3</v>
+        <v>37.6</v>
       </c>
       <c r="Q156" t="n">
-        <v>40.3</v>
+        <v>34.3</v>
       </c>
       <c r="R156" t="n">
-        <v>66.59999999999999</v>
+        <v>44.3</v>
       </c>
       <c r="S156" t="n">
-        <v>86.40000000000001</v>
+        <v>44.8</v>
       </c>
       <c r="T156" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U156" t="n">
-        <v>20.8</v>
+        <v>26.4</v>
       </c>
       <c r="V156" t="inlineStr">
         <is>
@@ -43707,7 +43703,7 @@
       </c>
       <c r="X156" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y156" t="inlineStr">
@@ -43717,7 +43713,7 @@
       </c>
       <c r="Z156" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
@@ -43725,10 +43721,14 @@
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB156" t="inlineStr"/>
+      <c r="AB156" t="inlineStr">
+        <is>
+          <t>order MLB 9 vs RotoWire 8</t>
+        </is>
+      </c>
       <c r="AC156" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD156" t="inlineStr"/>
@@ -43745,27 +43745,27 @@
       </c>
       <c r="AH156" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI156" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK156" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/22, 1 HR</t>
+          <t>Last 7 games: 8/27, 0 HR</t>
         </is>
       </c>
       <c r="AL156" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.8% barrel, 11.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.6% barrel, 13.6 HR allowed</t>
         </is>
       </c>
       <c r="AM156" t="inlineStr">
@@ -43775,112 +43775,112 @@
       </c>
       <c r="AN156" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>9.61</t>
         </is>
       </c>
       <c r="AO156" t="inlineStr">
         <is>
-          <t>28.51</t>
+          <t>41.16</t>
         </is>
       </c>
       <c r="AP156" t="inlineStr">
         <is>
-          <t>84.92</t>
+          <t>89.72</t>
         </is>
       </c>
       <c r="AQ156" t="inlineStr">
         <is>
-          <t>96.3013</t>
+          <t>101.0475</t>
         </is>
       </c>
       <c r="AR156" t="inlineStr">
         <is>
-          <t>0.3424</t>
+          <t>0.3912</t>
         </is>
       </c>
       <c r="AS156" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.1539</t>
         </is>
       </c>
       <c r="AT156" t="inlineStr">
         <is>
-          <t>0.2938</t>
+          <t>0.3116</t>
         </is>
       </c>
       <c r="AU156" t="inlineStr">
         <is>
-          <t>68.67</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="AV156" t="inlineStr">
         <is>
-          <t>5.12</t>
+          <t>51.16</t>
         </is>
       </c>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>42.42</t>
+          <t>36.24</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>18.56</t>
+          <t>23.3</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr">
         <is>
-          <t>8.9</t>
+          <t>7.5</t>
         </is>
       </c>
       <c r="AZ156" t="inlineStr">
         <is>
-          <t>0.1527</t>
+          <t>0.1152</t>
         </is>
       </c>
       <c r="BA156" t="inlineStr">
         <is>
-          <t>8.8</t>
+          <t>6.56</t>
         </is>
       </c>
       <c r="BB156" t="inlineStr">
         <is>
-          <t>39.1</t>
+          <t>35.86</t>
         </is>
       </c>
       <c r="BC156" t="inlineStr">
         <is>
-          <t>88.8</t>
+          <t>87.99</t>
         </is>
       </c>
       <c r="BD156" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.4123</t>
         </is>
       </c>
       <c r="BE156" t="inlineStr">
         <is>
-          <t>0.152</t>
+          <t>0.1612</t>
         </is>
       </c>
       <c r="BF156" t="inlineStr">
         <is>
-          <t>21.4</t>
+          <t>26.78</t>
         </is>
       </c>
       <c r="BG156" t="inlineStr">
         <is>
-          <t>Out To LF</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BH156" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>83</t>
         </is>
       </c>
       <c r="BI156" t="inlineStr">
         <is>
-          <t>Rate Field</t>
+          <t>Citi Field</t>
         </is>
       </c>
       <c r="BJ156" t="inlineStr"/>
@@ -43891,22 +43891,22 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>683146</t>
+          <t>668723</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Brett Baty</t>
+          <t>Ryan Vilade</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>NYM</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -43921,17 +43921,17 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>Michael Wacha</t>
+          <t>Paul Blackburn</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>608379</t>
+          <t>621112</t>
         </is>
       </c>
       <c r="K157" t="inlineStr">
@@ -43954,26 +43954,26 @@
       </c>
       <c r="O157" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P157" t="n">
-        <v>37.6</v>
+        <v>41.1</v>
       </c>
       <c r="Q157" t="n">
-        <v>34.3</v>
+        <v>22.4</v>
       </c>
       <c r="R157" t="n">
-        <v>44.3</v>
+        <v>41.1</v>
       </c>
       <c r="S157" t="n">
-        <v>44.8</v>
+        <v>76.2</v>
       </c>
       <c r="T157" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U157" t="n">
-        <v>26.4</v>
+        <v>36.7</v>
       </c>
       <c r="V157" t="inlineStr">
         <is>
@@ -43987,7 +43987,7 @@
       </c>
       <c r="X157" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y157" t="inlineStr">
@@ -44007,7 +44007,7 @@
       </c>
       <c r="AB157" t="inlineStr">
         <is>
-          <t>order MLB 9 vs RotoWire 8</t>
+          <t>order MLB 6 vs RotoWire 5</t>
         </is>
       </c>
       <c r="AC157" t="inlineStr">
@@ -44029,27 +44029,27 @@
       </c>
       <c r="AH157" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI157" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK157" t="inlineStr">
         <is>
-          <t>Last 7 games: 8/27, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL157" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.6% barrel, 13.6 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.6% barrel, 3.9 HR allowed</t>
         </is>
       </c>
       <c r="AM157" t="inlineStr">
@@ -44059,112 +44059,112 @@
       </c>
       <c r="AN157" t="inlineStr">
         <is>
-          <t>9.61</t>
+          <t>7.74</t>
         </is>
       </c>
       <c r="AO157" t="inlineStr">
         <is>
-          <t>41.16</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="AP157" t="inlineStr">
         <is>
-          <t>89.72</t>
+          <t>91.35</t>
         </is>
       </c>
       <c r="AQ157" t="inlineStr">
         <is>
-          <t>101.0475</t>
+          <t>102.2367</t>
         </is>
       </c>
       <c r="AR157" t="inlineStr">
         <is>
-          <t>0.3912</t>
+          <t>0.3851</t>
         </is>
       </c>
       <c r="AS157" t="inlineStr">
         <is>
-          <t>0.1539</t>
+          <t>0.1527</t>
         </is>
       </c>
       <c r="AT157" t="inlineStr">
         <is>
-          <t>0.3116</t>
+          <t>0.3069</t>
         </is>
       </c>
       <c r="AU157" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>75.66</t>
         </is>
       </c>
       <c r="AV157" t="inlineStr">
         <is>
-          <t>51.16</t>
+          <t>55.72</t>
         </is>
       </c>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>36.24</t>
+          <t>22.47</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>23.3</t>
+          <t>24.89</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr">
         <is>
-          <t>7.5</t>
+          <t>4.2</t>
         </is>
       </c>
       <c r="AZ157" t="inlineStr">
         <is>
-          <t>0.1152</t>
+          <t>0.1372</t>
         </is>
       </c>
       <c r="BA157" t="inlineStr">
         <is>
-          <t>6.56</t>
+          <t>6.64</t>
         </is>
       </c>
       <c r="BB157" t="inlineStr">
         <is>
-          <t>35.86</t>
+          <t>33.52</t>
         </is>
       </c>
       <c r="BC157" t="inlineStr">
         <is>
-          <t>87.99</t>
+          <t>86.61</t>
         </is>
       </c>
       <c r="BD157" t="inlineStr">
         <is>
-          <t>0.4123</t>
+          <t>0.3633</t>
         </is>
       </c>
       <c r="BE157" t="inlineStr">
         <is>
-          <t>0.1612</t>
+          <t>0.1242</t>
         </is>
       </c>
       <c r="BF157" t="inlineStr">
         <is>
-          <t>26.78</t>
+          <t>21.79</t>
         </is>
       </c>
       <c r="BG157" t="inlineStr">
         <is>
-          <t>In From CF</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH157" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI157" t="inlineStr">
         <is>
-          <t>Citi Field</t>
+          <t>Tropicana Field</t>
         </is>
       </c>
       <c r="BJ157" t="inlineStr"/>
@@ -44480,7 +44480,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Delayed</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -45320,7 +45320,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Delayed</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -51802,7 +51802,7 @@
       </c>
       <c r="AI185" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ185" t="inlineStr">
@@ -53904,7 +53904,7 @@
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Delayed</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
@@ -56404,7 +56404,7 @@
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Delayed</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
@@ -57272,7 +57272,7 @@
         </is>
       </c>
       <c r="L205" t="n">
-        <v>34.2</v>
+        <v>34.1</v>
       </c>
       <c r="M205" t="inlineStr">
         <is>
@@ -57305,7 +57305,7 @@
         <v>50</v>
       </c>
       <c r="U205" t="n">
-        <v>40.3</v>
+        <v>37.8</v>
       </c>
       <c r="V205" t="inlineStr">
         <is>
@@ -57358,7 +57358,7 @@
       </c>
       <c r="AI205" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AJ205" t="inlineStr">
@@ -57368,7 +57368,7 @@
       </c>
       <c r="AK205" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/15, 1 HR</t>
+          <t>Last 7 games: 4/16, 1 HR</t>
         </is>
       </c>
       <c r="AL205" t="inlineStr">
@@ -63914,7 +63914,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Delayed</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -64498,7 +64498,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>64.3</v>
+        <v>64.5</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -64531,7 +64531,7 @@
         <v>80</v>
       </c>
       <c r="U5" t="n">
-        <v>82.7</v>
+        <v>87</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
@@ -64583,22 +64583,22 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Hot streak: 3 HR in last 7 games</t>
+          <t>Hot streak: 4 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
@@ -65318,7 +65318,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Delayed</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -65878,7 +65878,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Delayed</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -66158,7 +66158,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Delayed</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -66438,7 +66438,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Delayed</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -68910,7 +68910,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Delayed</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">

--- a/outputs/hr_rankings.xlsx
+++ b/outputs/hr_rankings.xlsx
@@ -826,34 +826,30 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2226,34 +2222,30 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 6 vs RotoWire 8</t>
-        </is>
-      </c>
+      <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -8587,56 +8579,56 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>666176</t>
+          <t>804668</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Jo Adell</t>
+          <t>Rafael Flores Jr.</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-07-11T18:10:00Z</t>
+          <t>2026-07-11T20:05:00Z</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Joe Ryan</t>
+          <t>Shane Drohan</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>657746</t>
+          <t>675660</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L30" t="n">
-        <v>58.3</v>
+        <v>58.2</v>
       </c>
       <c r="M30" t="inlineStr">
         <is>
@@ -8650,26 +8642,26 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>Strong Barrel, Hot Hitter/Streak</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P30" t="n">
-        <v>51.5</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="Q30" t="n">
-        <v>51.2</v>
+        <v>32.8</v>
       </c>
       <c r="R30" t="n">
-        <v>68.09999999999999</v>
+        <v>47.8</v>
       </c>
       <c r="S30" t="n">
-        <v>76.2</v>
+        <v>64.3</v>
       </c>
       <c r="T30" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U30" t="n">
-        <v>73.2</v>
+        <v>63.3</v>
       </c>
       <c r="V30" t="inlineStr">
         <is>
@@ -8683,7 +8675,7 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
@@ -8704,7 +8696,7 @@
       <c r="AB30" t="inlineStr"/>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD30" t="inlineStr"/>
@@ -8716,32 +8708,32 @@
       </c>
       <c r="AG30" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AH30" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AI30" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Contact streak: 3/7 over last 3 games</t>
         </is>
       </c>
       <c r="AL30" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 11.1% barrel, 14.8 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.2% barrel, 5.0 HR allowed</t>
         </is>
       </c>
       <c r="AM30" t="inlineStr">
@@ -8751,112 +8743,112 @@
       </c>
       <c r="AN30" t="inlineStr">
         <is>
-          <t>11.21</t>
+          <t>15.44</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>45.73</t>
+          <t>42.06</t>
         </is>
       </c>
       <c r="AP30" t="inlineStr">
         <is>
-          <t>90.37</t>
+          <t>91.58</t>
         </is>
       </c>
       <c r="AQ30" t="inlineStr">
         <is>
-          <t>102.6264</t>
+          <t>102.6343</t>
         </is>
       </c>
       <c r="AR30" t="inlineStr">
         <is>
-          <t>0.4734</t>
+          <t>0.7821</t>
         </is>
       </c>
       <c r="AS30" t="inlineStr">
         <is>
-          <t>0.212</t>
+          <t>0.3984</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr">
         <is>
-          <t>0.3377</t>
+          <t>0.522</t>
         </is>
       </c>
       <c r="AU30" t="inlineStr">
         <is>
-          <t>77.32</t>
+          <t>74.1</t>
         </is>
       </c>
       <c r="AV30" t="inlineStr">
         <is>
-          <t>71.44</t>
+          <t>53.88</t>
         </is>
       </c>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>37.79</t>
+          <t>30.81</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>26.86</t>
+          <t>34.56</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
-          <t>20.2</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>0.1825</t>
+          <t>0.4396</t>
         </is>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
-          <t>11.08</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="BB30" t="inlineStr">
         <is>
-          <t>42.74</t>
+          <t>38.9</t>
         </is>
       </c>
       <c r="BC30" t="inlineStr">
         <is>
-          <t>89.99</t>
+          <t>88.1</t>
         </is>
       </c>
       <c r="BD30" t="inlineStr">
         <is>
-          <t>0.3711</t>
+          <t>0.364</t>
         </is>
       </c>
       <c r="BE30" t="inlineStr">
         <is>
-          <t>0.1621</t>
+          <t>0.127</t>
         </is>
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>29.82</t>
+          <t>25.4</t>
         </is>
       </c>
       <c r="BG30" t="inlineStr">
         <is>
-          <t>Out To LF</t>
+          <t>R To L</t>
         </is>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>82</t>
         </is>
       </c>
       <c r="BI30" t="inlineStr">
         <is>
-          <t>Target Field</t>
+          <t>PNC Park</t>
         </is>
       </c>
       <c r="BJ30" t="inlineStr"/>
@@ -8867,52 +8859,52 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>804668</t>
+          <t>666176</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Rafael Flores Jr.</t>
+          <t>Jo Adell</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-07-11T20:05:00Z</t>
+          <t>2026-07-11T18:10:00Z</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Shane Drohan</t>
+          <t>Joe Ryan</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>675660</t>
+          <t>657746</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L31" t="n">
@@ -8930,26 +8922,26 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>Strong Barrel, Platoon Edge</t>
+          <t>Strong Barrel, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P31" t="n">
-        <v>72.59999999999999</v>
+        <v>51.5</v>
       </c>
       <c r="Q31" t="n">
-        <v>32.8</v>
+        <v>51.2</v>
       </c>
       <c r="R31" t="n">
-        <v>47.8</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="S31" t="n">
-        <v>64.3</v>
+        <v>76.2</v>
       </c>
       <c r="T31" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U31" t="n">
-        <v>63.3</v>
+        <v>70.8</v>
       </c>
       <c r="V31" t="inlineStr">
         <is>
@@ -8963,7 +8955,7 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
@@ -8984,7 +8976,7 @@
       <c r="AB31" t="inlineStr"/>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD31" t="inlineStr"/>
@@ -8996,32 +8988,32 @@
       </c>
       <c r="AG31" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>Contact streak: 3/7 over last 3 games</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL31" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.2% barrel, 5.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 11.1% barrel, 14.8 HR allowed</t>
         </is>
       </c>
       <c r="AM31" t="inlineStr">
@@ -9031,112 +9023,112 @@
       </c>
       <c r="AN31" t="inlineStr">
         <is>
-          <t>15.44</t>
+          <t>11.21</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>42.06</t>
+          <t>45.73</t>
         </is>
       </c>
       <c r="AP31" t="inlineStr">
         <is>
-          <t>91.58</t>
+          <t>90.37</t>
         </is>
       </c>
       <c r="AQ31" t="inlineStr">
         <is>
-          <t>102.6343</t>
+          <t>102.6264</t>
         </is>
       </c>
       <c r="AR31" t="inlineStr">
         <is>
-          <t>0.7821</t>
+          <t>0.4734</t>
         </is>
       </c>
       <c r="AS31" t="inlineStr">
         <is>
-          <t>0.3984</t>
+          <t>0.212</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr">
         <is>
-          <t>0.522</t>
+          <t>0.3377</t>
         </is>
       </c>
       <c r="AU31" t="inlineStr">
         <is>
-          <t>74.1</t>
+          <t>77.32</t>
         </is>
       </c>
       <c r="AV31" t="inlineStr">
         <is>
-          <t>53.88</t>
+          <t>71.44</t>
         </is>
       </c>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>30.81</t>
+          <t>37.79</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>34.56</t>
+          <t>26.86</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>20.2</t>
         </is>
       </c>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>0.4396</t>
+          <t>0.1825</t>
         </is>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>11.08</t>
         </is>
       </c>
       <c r="BB31" t="inlineStr">
         <is>
-          <t>38.9</t>
+          <t>42.74</t>
         </is>
       </c>
       <c r="BC31" t="inlineStr">
         <is>
-          <t>88.1</t>
+          <t>89.99</t>
         </is>
       </c>
       <c r="BD31" t="inlineStr">
         <is>
-          <t>0.364</t>
+          <t>0.3711</t>
         </is>
       </c>
       <c r="BE31" t="inlineStr">
         <is>
-          <t>0.127</t>
+          <t>0.1621</t>
         </is>
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>25.4</t>
+          <t>29.82</t>
         </is>
       </c>
       <c r="BG31" t="inlineStr">
         <is>
-          <t>R To L</t>
+          <t>Out To LF</t>
         </is>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>86</t>
         </is>
       </c>
       <c r="BI31" t="inlineStr">
         <is>
-          <t>PNC Park</t>
+          <t>Target Field</t>
         </is>
       </c>
       <c r="BJ31" t="inlineStr"/>
@@ -11482,34 +11474,30 @@
       </c>
       <c r="W40" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X40" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y40" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 5 vs RotoWire 4</t>
-        </is>
-      </c>
+      <c r="AB40" t="inlineStr"/>
       <c r="AC40" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -12050,34 +12038,30 @@
       </c>
       <c r="W42" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X42" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y42" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 4 vs RotoWire 3</t>
-        </is>
-      </c>
+      <c r="AB42" t="inlineStr"/>
       <c r="AC42" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -16248,28 +16232,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W57" t="inlineStr"/>
-      <c r="X57" t="inlineStr"/>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="Y57" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB57" t="inlineStr"/>
       <c r="AC57" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -19515,22 +19503,22 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>687093</t>
+          <t>545341</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Vaughn Grissom</t>
+          <t>Randal Grichuk</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -19545,22 +19533,22 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Joe Ryan</t>
+          <t>Gage Jump</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>657746</t>
+          <t>695611</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L69" t="n">
@@ -19578,26 +19566,26 @@
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>No major boost</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P69" t="n">
-        <v>33.6</v>
+        <v>57</v>
       </c>
       <c r="Q69" t="n">
-        <v>51.2</v>
+        <v>31.6</v>
       </c>
       <c r="R69" t="n">
-        <v>68.09999999999999</v>
+        <v>40.1</v>
       </c>
       <c r="S69" t="n">
-        <v>86.40000000000001</v>
+        <v>93.2</v>
       </c>
       <c r="T69" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U69" t="n">
-        <v>52.3</v>
+        <v>7</v>
       </c>
       <c r="V69" t="inlineStr">
         <is>
@@ -19611,7 +19599,7 @@
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y69" t="inlineStr">
@@ -19632,7 +19620,7 @@
       <c r="AB69" t="inlineStr"/>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD69" t="inlineStr"/>
@@ -19649,27 +19637,27 @@
       </c>
       <c r="AH69" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI69" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
         <is>
-          <t>Contact streak: 9/26 over last 7 games</t>
+          <t>Last 7 games: 3/18, 0 HR</t>
         </is>
       </c>
       <c r="AL69" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 11.1% barrel, 14.8 HR allowed</t>
+          <t>platoon edge; pitcher baseline 5.6% barrel, 4.0 HR allowed</t>
         </is>
       </c>
       <c r="AM69" t="inlineStr">
@@ -19679,112 +19667,112 @@
       </c>
       <c r="AN69" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>13.1</t>
         </is>
       </c>
       <c r="AO69" t="inlineStr">
         <is>
-          <t>42.6</t>
+          <t>47.82</t>
         </is>
       </c>
       <c r="AP69" t="inlineStr">
         <is>
-          <t>89.7</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AQ69" t="inlineStr">
         <is>
-          <t>100.1077</t>
+          <t>102.7141</t>
         </is>
       </c>
       <c r="AR69" t="inlineStr">
         <is>
-          <t>0.416</t>
+          <t>0.5116</t>
         </is>
       </c>
       <c r="AS69" t="inlineStr">
         <is>
-          <t>0.155</t>
+          <t>0.2285</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr">
         <is>
-          <t>0.336</t>
+          <t>0.3547</t>
         </is>
       </c>
       <c r="AU69" t="inlineStr">
         <is>
-          <t>71.6</t>
+          <t>73.9</t>
         </is>
       </c>
       <c r="AV69" t="inlineStr">
         <is>
-          <t>19.1</t>
+          <t>39.42</t>
         </is>
       </c>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>40.6</t>
+          <t>46.29</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>28.4</t>
+          <t>30.11</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>0.144</t>
+          <t>0.2416</t>
         </is>
       </c>
       <c r="BA69" t="inlineStr">
         <is>
-          <t>11.08</t>
+          <t>5.6</t>
         </is>
       </c>
       <c r="BB69" t="inlineStr">
         <is>
-          <t>42.74</t>
+          <t>38.7</t>
         </is>
       </c>
       <c r="BC69" t="inlineStr">
         <is>
-          <t>89.99</t>
+          <t>89.5</t>
         </is>
       </c>
       <c r="BD69" t="inlineStr">
         <is>
-          <t>0.3711</t>
+          <t>0.399</t>
         </is>
       </c>
       <c r="BE69" t="inlineStr">
         <is>
-          <t>0.1621</t>
+          <t>0.142</t>
         </is>
       </c>
       <c r="BF69" t="inlineStr">
         <is>
-          <t>29.82</t>
+          <t>28.2</t>
         </is>
       </c>
       <c r="BG69" t="inlineStr">
         <is>
-          <t>Out To LF</t>
+          <t>In From LF</t>
         </is>
       </c>
       <c r="BH69" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>79</t>
         </is>
       </c>
       <c r="BI69" t="inlineStr">
         <is>
-          <t>Target Field</t>
+          <t>Rate Field</t>
         </is>
       </c>
       <c r="BJ69" t="inlineStr"/>
@@ -19795,47 +19783,47 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>545341</t>
+          <t>694212</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Randal Grichuk</t>
+          <t>Samuel Basallo</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-07-11T18:10:00Z</t>
+          <t>2026-07-11T23:05:00Z</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Gage Jump</t>
+          <t>Noah Cameron</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>695611</t>
+          <t>702070</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -19858,61 +19846,65 @@
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel</t>
         </is>
       </c>
       <c r="P70" t="n">
-        <v>57</v>
+        <v>49.6</v>
       </c>
       <c r="Q70" t="n">
-        <v>31.6</v>
+        <v>42.9</v>
       </c>
       <c r="R70" t="n">
-        <v>40.1</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="S70" t="n">
-        <v>93.2</v>
+        <v>59.8</v>
       </c>
       <c r="T70" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U70" t="n">
-        <v>7</v>
+        <v>62</v>
       </c>
       <c r="V70" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W70" t="inlineStr">
+      <c r="Z70" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X70" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y70" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z70" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB70" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD70" t="inlineStr"/>
@@ -19929,27 +19921,27 @@
       </c>
       <c r="AH70" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AI70" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="AJ70" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AI70" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="AJ70" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AK70" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/18, 0 HR</t>
+          <t>Hot streak: 3 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL70" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 5.6% barrel, 4.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.4% barrel, 12.4 HR allowed</t>
         </is>
       </c>
       <c r="AM70" t="inlineStr">
@@ -19959,112 +19951,112 @@
       </c>
       <c r="AN70" t="inlineStr">
         <is>
-          <t>13.1</t>
+          <t>11.42</t>
         </is>
       </c>
       <c r="AO70" t="inlineStr">
         <is>
-          <t>47.82</t>
+          <t>44.82</t>
         </is>
       </c>
       <c r="AP70" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>90.64</t>
         </is>
       </c>
       <c r="AQ70" t="inlineStr">
         <is>
-          <t>102.7141</t>
+          <t>102.5598</t>
         </is>
       </c>
       <c r="AR70" t="inlineStr">
         <is>
-          <t>0.5116</t>
+          <t>0.4464</t>
         </is>
       </c>
       <c r="AS70" t="inlineStr">
         <is>
-          <t>0.2285</t>
+          <t>0.2043</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr">
         <is>
-          <t>0.3547</t>
+          <t>0.3232</t>
         </is>
       </c>
       <c r="AU70" t="inlineStr">
         <is>
-          <t>73.9</t>
+          <t>74.94</t>
         </is>
       </c>
       <c r="AV70" t="inlineStr">
         <is>
-          <t>39.42</t>
+          <t>49.93</t>
         </is>
       </c>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>46.29</t>
+          <t>42.25</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>30.11</t>
+          <t>29.47</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>11.7</t>
         </is>
       </c>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>0.2416</t>
+          <t>0.1972</t>
         </is>
       </c>
       <c r="BA70" t="inlineStr">
         <is>
-          <t>5.6</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="BB70" t="inlineStr">
         <is>
-          <t>38.7</t>
+          <t>38.31</t>
         </is>
       </c>
       <c r="BC70" t="inlineStr">
         <is>
-          <t>89.5</t>
+          <t>88.74</t>
         </is>
       </c>
       <c r="BD70" t="inlineStr">
         <is>
-          <t>0.399</t>
+          <t>0.4408</t>
         </is>
       </c>
       <c r="BE70" t="inlineStr">
         <is>
-          <t>0.142</t>
+          <t>0.1751</t>
         </is>
       </c>
       <c r="BF70" t="inlineStr">
         <is>
-          <t>28.2</t>
+          <t>25.4</t>
         </is>
       </c>
       <c r="BG70" t="inlineStr">
         <is>
-          <t>In From LF</t>
+          <t>Out To LF</t>
         </is>
       </c>
       <c r="BH70" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>82</t>
         </is>
       </c>
       <c r="BI70" t="inlineStr">
         <is>
-          <t>Rate Field</t>
+          <t>Oriole Park at Camden Yards</t>
         </is>
       </c>
       <c r="BJ70" t="inlineStr"/>
@@ -20075,56 +20067,56 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>694212</t>
+          <t>687093</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Samuel Basallo</t>
+          <t>Vaughn Grissom</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-07-11T23:05:00Z</t>
+          <t>2026-07-11T18:10:00Z</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Noah Cameron</t>
+          <t>Joe Ryan</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>702070</t>
+          <t>657746</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L71" t="n">
-        <v>52.8</v>
+        <v>52.7</v>
       </c>
       <c r="M71" t="inlineStr">
         <is>
@@ -20138,65 +20130,61 @@
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P71" t="n">
-        <v>49.6</v>
+        <v>33.6</v>
       </c>
       <c r="Q71" t="n">
-        <v>42.9</v>
+        <v>51.2</v>
       </c>
       <c r="R71" t="n">
         <v>68.09999999999999</v>
       </c>
       <c r="S71" t="n">
-        <v>59.8</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T71" t="n">
         <v>50</v>
       </c>
       <c r="U71" t="n">
-        <v>62</v>
+        <v>50.3</v>
       </c>
       <c r="V71" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W71" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X71" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y71" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB71" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr"/>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD71" t="inlineStr"/>
@@ -20213,27 +20201,27 @@
       </c>
       <c r="AH71" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI71" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
         <is>
-          <t>Hot streak: 3 HR in last 7 games</t>
+          <t>Contact streak: 9/27 over last 7 games</t>
         </is>
       </c>
       <c r="AL71" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.4% barrel, 12.4 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 11.1% barrel, 14.8 HR allowed</t>
         </is>
       </c>
       <c r="AM71" t="inlineStr">
@@ -20243,97 +20231,97 @@
       </c>
       <c r="AN71" t="inlineStr">
         <is>
-          <t>11.42</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AO71" t="inlineStr">
         <is>
-          <t>44.82</t>
+          <t>42.6</t>
         </is>
       </c>
       <c r="AP71" t="inlineStr">
         <is>
-          <t>90.64</t>
+          <t>89.7</t>
         </is>
       </c>
       <c r="AQ71" t="inlineStr">
         <is>
-          <t>102.5598</t>
+          <t>100.1077</t>
         </is>
       </c>
       <c r="AR71" t="inlineStr">
         <is>
-          <t>0.4464</t>
+          <t>0.416</t>
         </is>
       </c>
       <c r="AS71" t="inlineStr">
         <is>
-          <t>0.2043</t>
+          <t>0.155</t>
         </is>
       </c>
       <c r="AT71" t="inlineStr">
         <is>
-          <t>0.3232</t>
+          <t>0.336</t>
         </is>
       </c>
       <c r="AU71" t="inlineStr">
         <is>
-          <t>74.94</t>
+          <t>71.6</t>
         </is>
       </c>
       <c r="AV71" t="inlineStr">
         <is>
-          <t>49.93</t>
+          <t>19.1</t>
         </is>
       </c>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>42.25</t>
+          <t>40.6</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>29.47</t>
+          <t>28.4</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr">
         <is>
-          <t>11.7</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>0.1972</t>
+          <t>0.144</t>
         </is>
       </c>
       <c r="BA71" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>11.08</t>
         </is>
       </c>
       <c r="BB71" t="inlineStr">
         <is>
-          <t>38.31</t>
+          <t>42.74</t>
         </is>
       </c>
       <c r="BC71" t="inlineStr">
         <is>
-          <t>88.74</t>
+          <t>89.99</t>
         </is>
       </c>
       <c r="BD71" t="inlineStr">
         <is>
-          <t>0.4408</t>
+          <t>0.3711</t>
         </is>
       </c>
       <c r="BE71" t="inlineStr">
         <is>
-          <t>0.1751</t>
+          <t>0.1621</t>
         </is>
       </c>
       <c r="BF71" t="inlineStr">
         <is>
-          <t>25.4</t>
+          <t>29.82</t>
         </is>
       </c>
       <c r="BG71" t="inlineStr">
@@ -20343,12 +20331,12 @@
       </c>
       <c r="BH71" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>86</t>
         </is>
       </c>
       <c r="BI71" t="inlineStr">
         <is>
-          <t>Oriole Park at Camden Yards</t>
+          <t>Target Field</t>
         </is>
       </c>
       <c r="BJ71" t="inlineStr"/>
@@ -22978,34 +22966,30 @@
       </c>
       <c r="W81" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z81" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X81" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y81" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z81" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB81" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB81" t="inlineStr"/>
       <c r="AC81" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -30554,34 +30538,30 @@
       </c>
       <c r="W108" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X108" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y108" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z108" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X108" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y108" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z108" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA108" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB108" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 2 vs RotoWire 1</t>
-        </is>
-      </c>
+      <c r="AB108" t="inlineStr"/>
       <c r="AC108" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -35763,47 +35743,47 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>656484</t>
+          <t>695734</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Tristan Gray</t>
+          <t>Daylen Lile</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>WSH</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>2026-07-11T18:10:00Z</t>
+          <t>2026-07-11T20:05:00Z</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>Ryan Johnson</t>
+          <t>Cam Schlittler</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>696270</t>
+          <t>693645</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
@@ -35830,22 +35810,22 @@
         </is>
       </c>
       <c r="P127" t="n">
-        <v>32.7</v>
+        <v>29.3</v>
       </c>
       <c r="Q127" t="n">
-        <v>43.8</v>
+        <v>34.9</v>
       </c>
       <c r="R127" t="n">
-        <v>68.09999999999999</v>
+        <v>40.2</v>
       </c>
       <c r="S127" t="n">
-        <v>52.4</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T127" t="n">
         <v>80</v>
       </c>
       <c r="U127" t="n">
-        <v>4.5</v>
+        <v>59.1</v>
       </c>
       <c r="V127" t="inlineStr">
         <is>
@@ -35859,7 +35839,7 @@
       </c>
       <c r="X127" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y127" t="inlineStr">
@@ -35897,132 +35877,132 @@
       </c>
       <c r="AH127" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI127" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK127" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/20, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL127" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.2% barrel, 6.8 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.1% barrel, 9.4 HR allowed</t>
         </is>
       </c>
       <c r="AM127" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN127" t="inlineStr">
         <is>
-          <t>8.34</t>
+          <t>6.74</t>
         </is>
       </c>
       <c r="AO127" t="inlineStr">
         <is>
-          <t>40.17</t>
+          <t>36.6</t>
         </is>
       </c>
       <c r="AP127" t="inlineStr">
         <is>
-          <t>89.51</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="AQ127" t="inlineStr">
         <is>
-          <t>100.6168</t>
+          <t>98.614</t>
         </is>
       </c>
       <c r="AR127" t="inlineStr">
         <is>
-          <t>0.375</t>
+          <t>0.4224</t>
         </is>
       </c>
       <c r="AS127" t="inlineStr">
         <is>
-          <t>0.1404</t>
+          <t>0.1516</t>
         </is>
       </c>
       <c r="AT127" t="inlineStr">
         <is>
-          <t>0.2937</t>
+          <t>0.3256</t>
         </is>
       </c>
       <c r="AU127" t="inlineStr">
         <is>
-          <t>73.14</t>
+          <t>70.32</t>
         </is>
       </c>
       <c r="AV127" t="inlineStr">
         <is>
-          <t>35.95</t>
+          <t>7.12</t>
         </is>
       </c>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>42.06</t>
+          <t>41.08</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>23.98</t>
+          <t>31.36</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>9.7</t>
         </is>
       </c>
       <c r="AZ127" t="inlineStr">
         <is>
-          <t>0.1258</t>
+          <t>0.1703</t>
         </is>
       </c>
       <c r="BA127" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.06</t>
         </is>
       </c>
       <c r="BB127" t="inlineStr">
         <is>
-          <t>39.01</t>
+          <t>39.22</t>
         </is>
       </c>
       <c r="BC127" t="inlineStr">
         <is>
-          <t>88.66</t>
+          <t>88.09</t>
         </is>
       </c>
       <c r="BD127" t="inlineStr">
         <is>
-          <t>0.4332</t>
+          <t>0.3609</t>
         </is>
       </c>
       <c r="BE127" t="inlineStr">
         <is>
-          <t>0.1791</t>
+          <t>0.1407</t>
         </is>
       </c>
       <c r="BF127" t="inlineStr">
         <is>
-          <t>35.07</t>
+          <t>26.81</t>
         </is>
       </c>
       <c r="BG127" t="inlineStr">
         <is>
-          <t>Out To LF</t>
+          <t>In From LF</t>
         </is>
       </c>
       <c r="BH127" t="inlineStr">
@@ -36032,7 +36012,7 @@
       </c>
       <c r="BI127" t="inlineStr">
         <is>
-          <t>Target Field</t>
+          <t>Nationals Park</t>
         </is>
       </c>
       <c r="BJ127" t="inlineStr"/>
@@ -36043,32 +36023,32 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>695734</t>
+          <t>647304</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Daylen Lile</t>
+          <t>Josh Naylor</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>WSH</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>2026-07-11T20:05:00Z</t>
+          <t>2026-07-11T20:10:00Z</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -36078,12 +36058,12 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>Cam Schlittler</t>
+          <t>Griffin Jax</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>693645</t>
+          <t>643377</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
@@ -36110,13 +36090,13 @@
         </is>
       </c>
       <c r="P128" t="n">
-        <v>29.3</v>
+        <v>24.8</v>
       </c>
       <c r="Q128" t="n">
-        <v>34.9</v>
+        <v>49.5</v>
       </c>
       <c r="R128" t="n">
-        <v>40.2</v>
+        <v>41.1</v>
       </c>
       <c r="S128" t="n">
         <v>86.40000000000001</v>
@@ -36125,7 +36105,7 @@
         <v>80</v>
       </c>
       <c r="U128" t="n">
-        <v>59.1</v>
+        <v>15.3</v>
       </c>
       <c r="V128" t="inlineStr">
         <is>
@@ -36177,27 +36157,27 @@
       </c>
       <c r="AH128" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI128" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ128" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK128" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 6/27, 0 HR</t>
         </is>
       </c>
       <c r="AL128" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.1% barrel, 9.4 HR allowed</t>
+          <t>platoon edge; pitcher baseline 10.4% barrel, 10.5 HR allowed</t>
         </is>
       </c>
       <c r="AM128" t="inlineStr">
@@ -36207,112 +36187,112 @@
       </c>
       <c r="AN128" t="inlineStr">
         <is>
-          <t>6.74</t>
+          <t>5.3</t>
         </is>
       </c>
       <c r="AO128" t="inlineStr">
         <is>
-          <t>36.6</t>
+          <t>38.68</t>
         </is>
       </c>
       <c r="AP128" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>88.01</t>
         </is>
       </c>
       <c r="AQ128" t="inlineStr">
         <is>
-          <t>98.614</t>
+          <t>99.2618</t>
         </is>
       </c>
       <c r="AR128" t="inlineStr">
         <is>
-          <t>0.4224</t>
+          <t>0.4073</t>
         </is>
       </c>
       <c r="AS128" t="inlineStr">
         <is>
-          <t>0.1516</t>
+          <t>0.1373</t>
         </is>
       </c>
       <c r="AT128" t="inlineStr">
         <is>
-          <t>0.3256</t>
+          <t>0.3238</t>
         </is>
       </c>
       <c r="AU128" t="inlineStr">
         <is>
-          <t>70.32</t>
+          <t>70.44</t>
         </is>
       </c>
       <c r="AV128" t="inlineStr">
         <is>
-          <t>7.12</t>
+          <t>11.18</t>
         </is>
       </c>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>41.08</t>
+          <t>41.57</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>31.36</t>
+          <t>23.69</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr">
         <is>
-          <t>9.7</t>
+          <t>11.6</t>
         </is>
       </c>
       <c r="AZ128" t="inlineStr">
         <is>
-          <t>0.1703</t>
+          <t>0.1215</t>
         </is>
       </c>
       <c r="BA128" t="inlineStr">
         <is>
-          <t>8.06</t>
+          <t>10.45</t>
         </is>
       </c>
       <c r="BB128" t="inlineStr">
         <is>
-          <t>39.22</t>
+          <t>42.42</t>
         </is>
       </c>
       <c r="BC128" t="inlineStr">
         <is>
-          <t>88.09</t>
+          <t>89.06</t>
         </is>
       </c>
       <c r="BD128" t="inlineStr">
         <is>
-          <t>0.3609</t>
+          <t>0.4374</t>
         </is>
       </c>
       <c r="BE128" t="inlineStr">
         <is>
-          <t>0.1407</t>
+          <t>0.1807</t>
         </is>
       </c>
       <c r="BF128" t="inlineStr">
         <is>
-          <t>26.81</t>
+          <t>22.53</t>
         </is>
       </c>
       <c r="BG128" t="inlineStr">
         <is>
-          <t>In From LF</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH128" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI128" t="inlineStr">
         <is>
-          <t>Nationals Park</t>
+          <t>Tropicana Field</t>
         </is>
       </c>
       <c r="BJ128" t="inlineStr"/>
@@ -36323,47 +36303,47 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>647304</t>
+          <t>656484</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Josh Naylor</t>
+          <t>Tristan Gray</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>2026-07-11T20:10:00Z</t>
+          <t>2026-07-11T18:10:00Z</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>Griffin Jax</t>
+          <t>Ryan Johnson</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>643377</t>
+          <t>696270</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
@@ -36372,7 +36352,7 @@
         </is>
       </c>
       <c r="L129" t="n">
-        <v>46.3</v>
+        <v>46.2</v>
       </c>
       <c r="M129" t="inlineStr">
         <is>
@@ -36390,22 +36370,22 @@
         </is>
       </c>
       <c r="P129" t="n">
-        <v>24.8</v>
+        <v>32.7</v>
       </c>
       <c r="Q129" t="n">
-        <v>49.5</v>
+        <v>43.8</v>
       </c>
       <c r="R129" t="n">
-        <v>41.1</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="S129" t="n">
-        <v>86.40000000000001</v>
+        <v>52.4</v>
       </c>
       <c r="T129" t="n">
         <v>80</v>
       </c>
       <c r="U129" t="n">
-        <v>15.3</v>
+        <v>3.4</v>
       </c>
       <c r="V129" t="inlineStr">
         <is>
@@ -36419,7 +36399,7 @@
       </c>
       <c r="X129" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y129" t="inlineStr">
@@ -36457,12 +36437,12 @@
       </c>
       <c r="AH129" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI129" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ129" t="inlineStr">
@@ -36472,127 +36452,127 @@
       </c>
       <c r="AK129" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/27, 0 HR</t>
+          <t>Last 7 games: 3/21, 0 HR</t>
         </is>
       </c>
       <c r="AL129" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 10.4% barrel, 10.5 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.2% barrel, 6.8 HR allowed</t>
         </is>
       </c>
       <c r="AM129" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN129" t="inlineStr">
         <is>
-          <t>5.3</t>
+          <t>8.34</t>
         </is>
       </c>
       <c r="AO129" t="inlineStr">
         <is>
-          <t>38.68</t>
+          <t>40.17</t>
         </is>
       </c>
       <c r="AP129" t="inlineStr">
         <is>
-          <t>88.01</t>
+          <t>89.51</t>
         </is>
       </c>
       <c r="AQ129" t="inlineStr">
         <is>
-          <t>99.2618</t>
+          <t>100.6168</t>
         </is>
       </c>
       <c r="AR129" t="inlineStr">
         <is>
-          <t>0.4073</t>
+          <t>0.375</t>
         </is>
       </c>
       <c r="AS129" t="inlineStr">
         <is>
-          <t>0.1373</t>
+          <t>0.1404</t>
         </is>
       </c>
       <c r="AT129" t="inlineStr">
         <is>
-          <t>0.3238</t>
+          <t>0.2937</t>
         </is>
       </c>
       <c r="AU129" t="inlineStr">
         <is>
-          <t>70.44</t>
+          <t>73.14</t>
         </is>
       </c>
       <c r="AV129" t="inlineStr">
         <is>
-          <t>11.18</t>
+          <t>35.95</t>
         </is>
       </c>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>41.57</t>
+          <t>42.06</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>23.69</t>
+          <t>23.98</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr">
         <is>
-          <t>11.6</t>
+          <t>3.7</t>
         </is>
       </c>
       <c r="AZ129" t="inlineStr">
         <is>
-          <t>0.1215</t>
+          <t>0.1258</t>
         </is>
       </c>
       <c r="BA129" t="inlineStr">
         <is>
-          <t>10.45</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="BB129" t="inlineStr">
         <is>
-          <t>42.42</t>
+          <t>39.01</t>
         </is>
       </c>
       <c r="BC129" t="inlineStr">
         <is>
-          <t>89.06</t>
+          <t>88.66</t>
         </is>
       </c>
       <c r="BD129" t="inlineStr">
         <is>
-          <t>0.4374</t>
+          <t>0.4332</t>
         </is>
       </c>
       <c r="BE129" t="inlineStr">
         <is>
-          <t>0.1807</t>
+          <t>0.1791</t>
         </is>
       </c>
       <c r="BF129" t="inlineStr">
         <is>
-          <t>22.53</t>
+          <t>35.07</t>
         </is>
       </c>
       <c r="BG129" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Out To LF</t>
         </is>
       </c>
       <c r="BH129" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>86</t>
         </is>
       </c>
       <c r="BI129" t="inlineStr">
         <is>
-          <t>Tropicana Field</t>
+          <t>Target Field</t>
         </is>
       </c>
       <c r="BJ129" t="inlineStr"/>
@@ -39766,34 +39746,30 @@
       </c>
       <c r="W141" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X141" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y141" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z141" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X141" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y141" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z141" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA141" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB141" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 1 vs RotoWire 2</t>
-        </is>
-      </c>
+      <c r="AB141" t="inlineStr"/>
       <c r="AC141" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -41166,34 +41142,30 @@
       </c>
       <c r="W146" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X146" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y146" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z146" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X146" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y146" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z146" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA146" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB146" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 8 vs RotoWire 9</t>
-        </is>
-      </c>
+      <c r="AB146" t="inlineStr"/>
       <c r="AC146" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -41730,34 +41702,30 @@
       </c>
       <c r="W148" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X148" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y148" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z148" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X148" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y148" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z148" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA148" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB148" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB148" t="inlineStr"/>
       <c r="AC148" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -44522,34 +44490,30 @@
       </c>
       <c r="W158" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X158" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y158" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z158" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X158" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y158" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z158" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA158" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB158" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB158" t="inlineStr"/>
       <c r="AC158" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -45086,34 +45050,30 @@
       </c>
       <c r="W160" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X160" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y160" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z160" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X160" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y160" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z160" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA160" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB160" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 7 vs RotoWire 8</t>
-        </is>
-      </c>
+      <c r="AB160" t="inlineStr"/>
       <c r="AC160" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -46490,34 +46450,30 @@
       </c>
       <c r="W165" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X165" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y165" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z165" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X165" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y165" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z165" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA165" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB165" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB165" t="inlineStr"/>
       <c r="AC165" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -50962,34 +50918,30 @@
       </c>
       <c r="W181" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X181" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y181" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z181" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X181" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y181" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z181" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA181" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB181" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB181" t="inlineStr"/>
       <c r="AC181" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -52918,34 +52870,30 @@
       </c>
       <c r="W188" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X188" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y188" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z188" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X188" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y188" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z188" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA188" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB188" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 7 vs RotoWire 5</t>
-        </is>
-      </c>
+      <c r="AB188" t="inlineStr"/>
       <c r="AC188" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -54362,7 +54310,7 @@
       </c>
       <c r="AI193" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AJ193" t="inlineStr">
@@ -54372,7 +54320,7 @@
       </c>
       <c r="AK193" t="inlineStr">
         <is>
-          <t>Last 7 games: 1/14, 0 HR</t>
+          <t>Last 7 games: 1/15, 0 HR</t>
         </is>
       </c>
       <c r="AL193" t="inlineStr">
@@ -62392,7 +62340,7 @@
         </is>
       </c>
       <c r="L222" t="n">
-        <v>37</v>
+        <v>36.8</v>
       </c>
       <c r="M222" t="inlineStr">
         <is>
@@ -62425,7 +62373,7 @@
         <v>50</v>
       </c>
       <c r="U222" t="n">
-        <v>42</v>
+        <v>39.8</v>
       </c>
       <c r="V222" t="inlineStr">
         <is>
@@ -62482,7 +62430,7 @@
       </c>
       <c r="AI222" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AJ222" t="inlineStr">
@@ -62492,7 +62440,7 @@
       </c>
       <c r="AK222" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/18, 1 HR</t>
+          <t>Last 7 games: 5/19, 1 HR</t>
         </is>
       </c>
       <c r="AL222" t="inlineStr">
@@ -64670,34 +64618,30 @@
       </c>
       <c r="W230" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X230" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y230" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z230" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X230" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y230" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z230" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA230" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB230" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 8 vs RotoWire 7</t>
-        </is>
-      </c>
+      <c r="AB230" t="inlineStr"/>
       <c r="AC230" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -69339,56 +69283,56 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>645302</t>
+          <t>671976</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Victor Robles</t>
+          <t>Tristan Peters</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>2026-07-11T20:10:00Z</t>
+          <t>2026-07-11T18:10:00Z</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I247" t="inlineStr">
         <is>
-          <t>Griffin Jax</t>
+          <t>Gage Jump</t>
         </is>
       </c>
       <c r="J247" t="inlineStr">
         <is>
-          <t>643377</t>
+          <t>695611</t>
         </is>
       </c>
       <c r="K247" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L247" t="n">
-        <v>32.3</v>
+        <v>32.4</v>
       </c>
       <c r="M247" t="inlineStr">
         <is>
@@ -69402,61 +69346,57 @@
       </c>
       <c r="O247" t="inlineStr">
         <is>
-          <t>No major boost</t>
+          <t>Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P247" t="n">
-        <v>6.4</v>
+        <v>12</v>
       </c>
       <c r="Q247" t="n">
-        <v>49.5</v>
+        <v>31.6</v>
       </c>
       <c r="R247" t="n">
-        <v>41.1</v>
+        <v>40.1</v>
       </c>
       <c r="S247" t="n">
-        <v>52.4</v>
+        <v>44.8</v>
       </c>
       <c r="T247" t="n">
         <v>50</v>
       </c>
       <c r="U247" t="n">
-        <v>5.7</v>
+        <v>81.7</v>
       </c>
       <c r="V247" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W247" t="inlineStr">
+      <c r="W247" t="inlineStr"/>
+      <c r="X247" t="inlineStr"/>
+      <c r="Y247" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z247" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X247" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y247" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z247" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA247" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB247" t="inlineStr"/>
+      <c r="AB247" t="inlineStr">
+        <is>
+          <t>not found on RotoWire</t>
+        </is>
+      </c>
       <c r="AC247" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD247" t="inlineStr"/>
@@ -69473,27 +69413,27 @@
       </c>
       <c r="AH247" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI247" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AJ247" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK247" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/19, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL247" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 10.4% barrel, 10.5 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 5.6% barrel, 4.0 HR allowed</t>
         </is>
       </c>
       <c r="AM247" t="inlineStr">
@@ -69503,112 +69443,112 @@
       </c>
       <c r="AN247" t="inlineStr">
         <is>
-          <t>3.36</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="AO247" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>33.49</t>
         </is>
       </c>
       <c r="AP247" t="inlineStr">
         <is>
-          <t>85.19</t>
+          <t>87.01</t>
         </is>
       </c>
       <c r="AQ247" t="inlineStr">
         <is>
-          <t>94.7182</t>
+          <t>97.9126</t>
         </is>
       </c>
       <c r="AR247" t="inlineStr">
         <is>
-          <t>0.3109</t>
+          <t>0.3243</t>
         </is>
       </c>
       <c r="AS247" t="inlineStr">
         <is>
-          <t>0.0939</t>
+          <t>0.0973</t>
         </is>
       </c>
       <c r="AT247" t="inlineStr">
         <is>
-          <t>0.258</t>
+          <t>0.2614</t>
         </is>
       </c>
       <c r="AU247" t="inlineStr">
         <is>
-          <t>67.98</t>
+          <t>69.28</t>
         </is>
       </c>
       <c r="AV247" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>4.97</t>
         </is>
       </c>
       <c r="AW247" t="inlineStr">
         <is>
-          <t>48.85</t>
+          <t>42.05</t>
         </is>
       </c>
       <c r="AX247" t="inlineStr">
         <is>
-          <t>29.53</t>
+          <t>16.8</t>
         </is>
       </c>
       <c r="AY247" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>4.2</t>
         </is>
       </c>
       <c r="AZ247" t="inlineStr">
         <is>
-          <t>0.0409</t>
+          <t>0.1267</t>
         </is>
       </c>
       <c r="BA247" t="inlineStr">
         <is>
-          <t>10.45</t>
+          <t>5.6</t>
         </is>
       </c>
       <c r="BB247" t="inlineStr">
         <is>
-          <t>42.42</t>
+          <t>38.7</t>
         </is>
       </c>
       <c r="BC247" t="inlineStr">
         <is>
-          <t>89.06</t>
+          <t>89.5</t>
         </is>
       </c>
       <c r="BD247" t="inlineStr">
         <is>
-          <t>0.4374</t>
+          <t>0.399</t>
         </is>
       </c>
       <c r="BE247" t="inlineStr">
         <is>
-          <t>0.1807</t>
+          <t>0.142</t>
         </is>
       </c>
       <c r="BF247" t="inlineStr">
         <is>
-          <t>22.53</t>
+          <t>28.2</t>
         </is>
       </c>
       <c r="BG247" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>In From LF</t>
         </is>
       </c>
       <c r="BH247" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>79</t>
         </is>
       </c>
       <c r="BI247" t="inlineStr">
         <is>
-          <t>Tropicana Field</t>
+          <t>Rate Field</t>
         </is>
       </c>
       <c r="BJ247" t="inlineStr"/>
@@ -69619,22 +69559,22 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>691594</t>
+          <t>645302</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Javier Sanoja</t>
+          <t>Victor Robles</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
@@ -69644,22 +69584,22 @@
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I248" t="inlineStr">
         <is>
-          <t>Tanner Bibee</t>
+          <t>Griffin Jax</t>
         </is>
       </c>
       <c r="J248" t="inlineStr">
         <is>
-          <t>676440</t>
+          <t>643377</t>
         </is>
       </c>
       <c r="K248" t="inlineStr">
@@ -69668,7 +69608,7 @@
         </is>
       </c>
       <c r="L248" t="n">
-        <v>32.1</v>
+        <v>32.3</v>
       </c>
       <c r="M248" t="inlineStr">
         <is>
@@ -69686,22 +69626,22 @@
         </is>
       </c>
       <c r="P248" t="n">
-        <v>10.7</v>
+        <v>6.4</v>
       </c>
       <c r="Q248" t="n">
-        <v>50.2</v>
+        <v>49.5</v>
       </c>
       <c r="R248" t="n">
-        <v>35</v>
+        <v>41.1</v>
       </c>
       <c r="S248" t="n">
-        <v>44.8</v>
+        <v>52.4</v>
       </c>
       <c r="T248" t="n">
         <v>50</v>
       </c>
       <c r="U248" t="n">
-        <v>10.6</v>
+        <v>5.7</v>
       </c>
       <c r="V248" t="inlineStr">
         <is>
@@ -69715,7 +69655,7 @@
       </c>
       <c r="X248" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y248" t="inlineStr">
@@ -69753,12 +69693,12 @@
       </c>
       <c r="AH248" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI248" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AJ248" t="inlineStr">
@@ -69768,12 +69708,12 @@
       </c>
       <c r="AK248" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/21, 0 HR</t>
+          <t>Last 7 games: 3/19, 0 HR</t>
         </is>
       </c>
       <c r="AL248" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 9.4% barrel, 22.1 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 10.4% barrel, 10.5 HR allowed</t>
         </is>
       </c>
       <c r="AM248" t="inlineStr">
@@ -69783,87 +69723,87 @@
       </c>
       <c r="AN248" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>3.36</t>
         </is>
       </c>
       <c r="AO248" t="inlineStr">
         <is>
-          <t>32.76</t>
+          <t>20.05</t>
         </is>
       </c>
       <c r="AP248" t="inlineStr">
         <is>
-          <t>87.8</t>
+          <t>85.19</t>
         </is>
       </c>
       <c r="AQ248" t="inlineStr">
         <is>
-          <t>97.6261</t>
+          <t>94.7182</t>
         </is>
       </c>
       <c r="AR248" t="inlineStr">
         <is>
-          <t>0.3301</t>
+          <t>0.3109</t>
         </is>
       </c>
       <c r="AS248" t="inlineStr">
         <is>
-          <t>0.0739</t>
+          <t>0.0939</t>
         </is>
       </c>
       <c r="AT248" t="inlineStr">
         <is>
-          <t>0.2799</t>
+          <t>0.258</t>
         </is>
       </c>
       <c r="AU248" t="inlineStr">
         <is>
-          <t>69.14</t>
+          <t>67.98</t>
         </is>
       </c>
       <c r="AV248" t="inlineStr">
         <is>
-          <t>6.74</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="AW248" t="inlineStr">
         <is>
-          <t>41.51</t>
+          <t>48.85</t>
         </is>
       </c>
       <c r="AX248" t="inlineStr">
         <is>
-          <t>16.8</t>
+          <t>29.53</t>
         </is>
       </c>
       <c r="AY248" t="inlineStr">
         <is>
-          <t>3.9</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="AZ248" t="inlineStr">
         <is>
-          <t>0.1411</t>
+          <t>0.0409</t>
         </is>
       </c>
       <c r="BA248" t="inlineStr">
         <is>
-          <t>9.36</t>
+          <t>10.45</t>
         </is>
       </c>
       <c r="BB248" t="inlineStr">
         <is>
-          <t>40.87</t>
+          <t>42.42</t>
         </is>
       </c>
       <c r="BC248" t="inlineStr">
         <is>
-          <t>89.48</t>
+          <t>89.06</t>
         </is>
       </c>
       <c r="BD248" t="inlineStr">
         <is>
-          <t>0.434</t>
+          <t>0.4374</t>
         </is>
       </c>
       <c r="BE248" t="inlineStr">
@@ -69873,7 +69813,7 @@
       </c>
       <c r="BF248" t="inlineStr">
         <is>
-          <t>27.34</t>
+          <t>22.53</t>
         </is>
       </c>
       <c r="BG248" t="inlineStr">
@@ -69888,7 +69828,7 @@
       </c>
       <c r="BI248" t="inlineStr">
         <is>
-          <t>loanDepot park</t>
+          <t>Tropicana Field</t>
         </is>
       </c>
       <c r="BJ248" t="inlineStr"/>
@@ -69899,47 +69839,47 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>670032</t>
+          <t>691594</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Nicky Lopez</t>
+          <t>Javier Sanoja</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>2026-07-11T23:05:00Z</t>
+          <t>2026-07-11T20:10:00Z</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I249" t="inlineStr">
         <is>
-          <t>Peter Lambert</t>
+          <t>Tanner Bibee</t>
         </is>
       </c>
       <c r="J249" t="inlineStr">
         <is>
-          <t>663567</t>
+          <t>676440</t>
         </is>
       </c>
       <c r="K249" t="inlineStr">
@@ -69948,7 +69888,7 @@
         </is>
       </c>
       <c r="L249" t="n">
-        <v>32</v>
+        <v>32.1</v>
       </c>
       <c r="M249" t="inlineStr">
         <is>
@@ -69962,26 +69902,26 @@
       </c>
       <c r="O249" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P249" t="n">
-        <v>2.8</v>
+        <v>10.7</v>
       </c>
       <c r="Q249" t="n">
-        <v>35.1</v>
+        <v>50.2</v>
       </c>
       <c r="R249" t="n">
-        <v>41.1</v>
+        <v>35</v>
       </c>
       <c r="S249" t="n">
-        <v>52.4</v>
+        <v>44.8</v>
       </c>
       <c r="T249" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U249" t="n">
-        <v>38.3</v>
+        <v>10.6</v>
       </c>
       <c r="V249" t="inlineStr">
         <is>
@@ -69995,7 +69935,7 @@
       </c>
       <c r="X249" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y249" t="inlineStr">
@@ -70016,7 +69956,7 @@
       <c r="AB249" t="inlineStr"/>
       <c r="AC249" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD249" t="inlineStr"/>
@@ -70033,12 +69973,12 @@
       </c>
       <c r="AH249" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI249" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ249" t="inlineStr">
@@ -70048,112 +69988,112 @@
       </c>
       <c r="AK249" t="inlineStr">
         <is>
-          <t>Contact streak: 6/16 over last 7 games</t>
+          <t>Last 7 games: 4/21, 0 HR</t>
         </is>
       </c>
       <c r="AL249" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.8% barrel, 10.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 9.4% barrel, 22.1 HR allowed</t>
         </is>
       </c>
       <c r="AM249" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN249" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="AO249" t="inlineStr">
         <is>
-          <t>27.33</t>
+          <t>32.76</t>
         </is>
       </c>
       <c r="AP249" t="inlineStr">
         <is>
-          <t>85.01</t>
+          <t>87.8</t>
         </is>
       </c>
       <c r="AQ249" t="inlineStr">
         <is>
-          <t>95.4416</t>
+          <t>97.6261</t>
         </is>
       </c>
       <c r="AR249" t="inlineStr">
         <is>
-          <t>0.2683</t>
+          <t>0.3301</t>
         </is>
       </c>
       <c r="AS249" t="inlineStr">
         <is>
-          <t>0.0412</t>
+          <t>0.0739</t>
         </is>
       </c>
       <c r="AT249" t="inlineStr">
         <is>
-          <t>0.2561</t>
+          <t>0.2799</t>
         </is>
       </c>
       <c r="AU249" t="inlineStr">
         <is>
-          <t>66.86</t>
+          <t>69.14</t>
         </is>
       </c>
       <c r="AV249" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>6.74</t>
         </is>
       </c>
       <c r="AW249" t="inlineStr">
         <is>
-          <t>35.41</t>
+          <t>41.51</t>
         </is>
       </c>
       <c r="AX249" t="inlineStr">
         <is>
-          <t>10.95</t>
+          <t>16.8</t>
         </is>
       </c>
       <c r="AY249" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>3.9</t>
         </is>
       </c>
       <c r="AZ249" t="inlineStr">
         <is>
-          <t>0.0385</t>
+          <t>0.1411</t>
         </is>
       </c>
       <c r="BA249" t="inlineStr">
         <is>
-          <t>6.8</t>
+          <t>9.36</t>
         </is>
       </c>
       <c r="BB249" t="inlineStr">
         <is>
-          <t>38.2</t>
+          <t>40.87</t>
         </is>
       </c>
       <c r="BC249" t="inlineStr">
         <is>
-          <t>89.1</t>
+          <t>89.48</t>
         </is>
       </c>
       <c r="BD249" t="inlineStr">
         <is>
-          <t>0.357</t>
+          <t>0.434</t>
         </is>
       </c>
       <c r="BE249" t="inlineStr">
         <is>
-          <t>0.148</t>
+          <t>0.1807</t>
         </is>
       </c>
       <c r="BF249" t="inlineStr">
         <is>
-          <t>33.6</t>
+          <t>27.34</t>
         </is>
       </c>
       <c r="BG249" t="inlineStr">
@@ -70168,7 +70108,7 @@
       </c>
       <c r="BI249" t="inlineStr">
         <is>
-          <t>Globe Life Field</t>
+          <t>loanDepot park</t>
         </is>
       </c>
       <c r="BJ249" t="inlineStr"/>
@@ -70179,32 +70119,32 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>682729</t>
+          <t>670032</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Jonatan Clase</t>
+          <t>Nicky Lopez</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>2026-07-12T00:40:00Z</t>
+          <t>2026-07-11T23:05:00Z</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
@@ -70214,12 +70154,12 @@
       </c>
       <c r="I250" t="inlineStr">
         <is>
-          <t>Walker Buehler</t>
+          <t>Peter Lambert</t>
         </is>
       </c>
       <c r="J250" t="inlineStr">
         <is>
-          <t>621111</t>
+          <t>663567</t>
         </is>
       </c>
       <c r="K250" t="inlineStr">
@@ -70242,65 +70182,61 @@
       </c>
       <c r="O250" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P250" t="n">
-        <v>7.3</v>
+        <v>2.8</v>
       </c>
       <c r="Q250" t="n">
-        <v>44.5</v>
+        <v>35.1</v>
       </c>
       <c r="R250" t="n">
-        <v>22.6</v>
+        <v>41.1</v>
       </c>
       <c r="S250" t="n">
-        <v>47.9</v>
+        <v>52.4</v>
       </c>
       <c r="T250" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="U250" t="n">
-        <v>41.2</v>
+        <v>38.3</v>
       </c>
       <c r="V250" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W250" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X250" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y250" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z250" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W250" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X250" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y250" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z250" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA250" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB250" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB250" t="inlineStr"/>
       <c r="AC250" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD250" t="inlineStr"/>
@@ -70312,139 +70248,147 @@
       </c>
       <c r="AG250" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AH250" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI250" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AJ250" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK250" t="inlineStr">
         <is>
-          <t>Last 4 games: 3/11, 1 HR</t>
+          <t>Contact streak: 6/16 over last 7 games</t>
         </is>
       </c>
       <c r="AL250" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 9.3% barrel, 14.3 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.8% barrel, 10.0 HR allowed</t>
         </is>
       </c>
       <c r="AM250" t="inlineStr">
         <is>
-          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN250" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AO250" t="inlineStr">
         <is>
-          <t>19.43</t>
+          <t>27.33</t>
         </is>
       </c>
       <c r="AP250" t="inlineStr">
         <is>
-          <t>85.09</t>
+          <t>85.01</t>
         </is>
       </c>
       <c r="AQ250" t="inlineStr">
         <is>
-          <t>93.3128</t>
+          <t>95.4416</t>
         </is>
       </c>
       <c r="AR250" t="inlineStr">
         <is>
-          <t>0.2528</t>
+          <t>0.2683</t>
         </is>
       </c>
       <c r="AS250" t="inlineStr">
         <is>
-          <t>0.0876</t>
+          <t>0.0412</t>
         </is>
       </c>
       <c r="AT250" t="inlineStr">
         <is>
-          <t>0.1909</t>
+          <t>0.2561</t>
         </is>
       </c>
       <c r="AU250" t="inlineStr">
         <is>
-          <t>69.35</t>
+          <t>66.86</t>
         </is>
       </c>
       <c r="AV250" t="inlineStr">
         <is>
-          <t>10.98</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="AW250" t="inlineStr">
         <is>
-          <t>64.83</t>
+          <t>35.41</t>
         </is>
       </c>
       <c r="AX250" t="inlineStr">
         <is>
-          <t>37.35</t>
+          <t>10.95</t>
         </is>
       </c>
       <c r="AY250" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="AZ250" t="inlineStr">
         <is>
-          <t>0.2174</t>
+          <t>0.0385</t>
         </is>
       </c>
       <c r="BA250" t="inlineStr">
         <is>
-          <t>9.29</t>
+          <t>6.8</t>
         </is>
       </c>
       <c r="BB250" t="inlineStr">
         <is>
-          <t>40.95</t>
+          <t>38.2</t>
         </is>
       </c>
       <c r="BC250" t="inlineStr">
         <is>
-          <t>89.72</t>
+          <t>89.1</t>
         </is>
       </c>
       <c r="BD250" t="inlineStr">
         <is>
-          <t>0.4262</t>
+          <t>0.357</t>
         </is>
       </c>
       <c r="BE250" t="inlineStr">
         <is>
-          <t>0.1638</t>
+          <t>0.148</t>
         </is>
       </c>
       <c r="BF250" t="inlineStr">
         <is>
-          <t>22.25</t>
-        </is>
-      </c>
-      <c r="BG250" t="inlineStr"/>
-      <c r="BH250" t="inlineStr"/>
+          <t>33.6</t>
+        </is>
+      </c>
+      <c r="BG250" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH250" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
       <c r="BI250" t="inlineStr">
         <is>
-          <t>Petco Park</t>
+          <t>Globe Life Field</t>
         </is>
       </c>
       <c r="BJ250" t="inlineStr"/>
@@ -70455,47 +70399,47 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>683083</t>
+          <t>682729</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Nasim Nuñez</t>
+          <t>Jonatan Clase</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>WSH</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>2026-07-11T20:05:00Z</t>
+          <t>2026-07-12T00:40:00Z</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I251" t="inlineStr">
         <is>
-          <t>Cam Schlittler</t>
+          <t>Walker Buehler</t>
         </is>
       </c>
       <c r="J251" t="inlineStr">
         <is>
-          <t>693645</t>
+          <t>621111</t>
         </is>
       </c>
       <c r="K251" t="inlineStr">
@@ -70504,7 +70448,7 @@
         </is>
       </c>
       <c r="L251" t="n">
-        <v>31.6</v>
+        <v>32</v>
       </c>
       <c r="M251" t="inlineStr">
         <is>
@@ -70518,58 +70462,62 @@
       </c>
       <c r="O251" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P251" t="n">
-        <v>5</v>
+        <v>7.3</v>
       </c>
       <c r="Q251" t="n">
-        <v>33.9</v>
+        <v>44.5</v>
       </c>
       <c r="R251" t="n">
-        <v>40.2</v>
+        <v>22.6</v>
       </c>
       <c r="S251" t="n">
-        <v>44.8</v>
+        <v>47.9</v>
       </c>
       <c r="T251" t="n">
         <v>75</v>
       </c>
       <c r="U251" t="n">
-        <v>54.9</v>
+        <v>41.2</v>
       </c>
       <c r="V251" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W251" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X251" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y251" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W251" t="inlineStr">
+      <c r="Z251" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X251" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y251" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z251" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA251" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB251" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB251" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC251" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -70584,17 +70532,17 @@
       </c>
       <c r="AG251" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AH251" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI251" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AJ251" t="inlineStr">
@@ -70604,127 +70552,119 @@
       </c>
       <c r="AK251" t="inlineStr">
         <is>
-          <t>Contact streak: 8/22 over last 7 games</t>
+          <t>Last 4 games: 3/11, 1 HR</t>
         </is>
       </c>
       <c r="AL251" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 8.1% barrel, 9.4 HR allowed</t>
+          <t>switch hitter; pitcher baseline 9.3% barrel, 14.3 HR allowed</t>
         </is>
       </c>
       <c r="AM251" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN251" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="AO251" t="inlineStr">
         <is>
-          <t>27.22</t>
+          <t>19.43</t>
         </is>
       </c>
       <c r="AP251" t="inlineStr">
         <is>
-          <t>86.01</t>
+          <t>85.09</t>
         </is>
       </c>
       <c r="AQ251" t="inlineStr">
         <is>
-          <t>96.0075</t>
+          <t>93.3128</t>
         </is>
       </c>
       <c r="AR251" t="inlineStr">
         <is>
-          <t>0.2984</t>
+          <t>0.2528</t>
         </is>
       </c>
       <c r="AS251" t="inlineStr">
         <is>
-          <t>0.0741</t>
+          <t>0.0876</t>
         </is>
       </c>
       <c r="AT251" t="inlineStr">
         <is>
-          <t>0.2771</t>
+          <t>0.1909</t>
         </is>
       </c>
       <c r="AU251" t="inlineStr">
         <is>
-          <t>68.77</t>
+          <t>69.35</t>
         </is>
       </c>
       <c r="AV251" t="inlineStr">
         <is>
-          <t>5.15</t>
+          <t>10.98</t>
         </is>
       </c>
       <c r="AW251" t="inlineStr">
         <is>
-          <t>32.83</t>
+          <t>64.83</t>
         </is>
       </c>
       <c r="AX251" t="inlineStr">
         <is>
-          <t>18.68</t>
+          <t>37.35</t>
         </is>
       </c>
       <c r="AY251" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="AZ251" t="inlineStr">
         <is>
-          <t>0.086</t>
+          <t>0.2174</t>
         </is>
       </c>
       <c r="BA251" t="inlineStr">
         <is>
-          <t>8.06</t>
+          <t>9.29</t>
         </is>
       </c>
       <c r="BB251" t="inlineStr">
         <is>
-          <t>39.22</t>
+          <t>40.95</t>
         </is>
       </c>
       <c r="BC251" t="inlineStr">
         <is>
-          <t>88.09</t>
+          <t>89.72</t>
         </is>
       </c>
       <c r="BD251" t="inlineStr">
         <is>
-          <t>0.3609</t>
+          <t>0.4262</t>
         </is>
       </c>
       <c r="BE251" t="inlineStr">
         <is>
-          <t>0.1407</t>
+          <t>0.1638</t>
         </is>
       </c>
       <c r="BF251" t="inlineStr">
         <is>
-          <t>26.81</t>
-        </is>
-      </c>
-      <c r="BG251" t="inlineStr">
-        <is>
-          <t>In From LF</t>
-        </is>
-      </c>
-      <c r="BH251" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
+          <t>22.25</t>
+        </is>
+      </c>
+      <c r="BG251" t="inlineStr"/>
+      <c r="BH251" t="inlineStr"/>
       <c r="BI251" t="inlineStr">
         <is>
-          <t>Nationals Park</t>
+          <t>Petco Park</t>
         </is>
       </c>
       <c r="BJ251" t="inlineStr"/>
@@ -70735,47 +70675,47 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>691026</t>
+          <t>683083</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Masyn Winn</t>
+          <t>Nasim Nuñez</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>WSH</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>2026-07-11T23:15:00Z</t>
+          <t>2026-07-11T20:05:00Z</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I252" t="inlineStr">
         <is>
-          <t>Reynaldo López</t>
+          <t>Cam Schlittler</t>
         </is>
       </c>
       <c r="J252" t="inlineStr">
         <is>
-          <t>625643</t>
+          <t>693645</t>
         </is>
       </c>
       <c r="K252" t="inlineStr">
@@ -70798,62 +70738,58 @@
       </c>
       <c r="O252" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P252" t="n">
-        <v>14.3</v>
+        <v>5</v>
       </c>
       <c r="Q252" t="n">
-        <v>35.4</v>
+        <v>33.9</v>
       </c>
       <c r="R252" t="n">
-        <v>22.1</v>
+        <v>40.2</v>
       </c>
       <c r="S252" t="n">
-        <v>71.7</v>
+        <v>44.8</v>
       </c>
       <c r="T252" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="U252" t="n">
-        <v>10.6</v>
+        <v>54.9</v>
       </c>
       <c r="V252" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W252" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X252" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y252" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z252" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W252" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X252" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y252" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z252" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA252" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB252" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB252" t="inlineStr"/>
       <c r="AC252" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -70873,27 +70809,27 @@
       </c>
       <c r="AH252" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI252" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ252" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK252" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/21, 0 HR</t>
+          <t>Contact streak: 8/22 over last 7 games</t>
         </is>
       </c>
       <c r="AL252" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 5.7% barrel, 5.2 HR allowed</t>
+          <t>switch hitter; pitcher baseline 8.1% barrel, 9.4 HR allowed</t>
         </is>
       </c>
       <c r="AM252" t="inlineStr">
@@ -70903,72 +70839,72 @@
       </c>
       <c r="AN252" t="inlineStr">
         <is>
-          <t>3.68</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="AO252" t="inlineStr">
         <is>
-          <t>34.67</t>
+          <t>27.22</t>
         </is>
       </c>
       <c r="AP252" t="inlineStr">
         <is>
-          <t>87.95</t>
+          <t>86.01</t>
         </is>
       </c>
       <c r="AQ252" t="inlineStr">
         <is>
-          <t>98.5487</t>
+          <t>96.0075</t>
         </is>
       </c>
       <c r="AR252" t="inlineStr">
         <is>
-          <t>0.3344</t>
+          <t>0.2984</t>
         </is>
       </c>
       <c r="AS252" t="inlineStr">
         <is>
+          <t>0.0741</t>
+        </is>
+      </c>
+      <c r="AT252" t="inlineStr">
+        <is>
+          <t>0.2771</t>
+        </is>
+      </c>
+      <c r="AU252" t="inlineStr">
+        <is>
+          <t>68.77</t>
+        </is>
+      </c>
+      <c r="AV252" t="inlineStr">
+        <is>
+          <t>5.15</t>
+        </is>
+      </c>
+      <c r="AW252" t="inlineStr">
+        <is>
+          <t>32.83</t>
+        </is>
+      </c>
+      <c r="AX252" t="inlineStr">
+        <is>
+          <t>18.68</t>
+        </is>
+      </c>
+      <c r="AY252" t="inlineStr">
+        <is>
+          <t>1.9</t>
+        </is>
+      </c>
+      <c r="AZ252" t="inlineStr">
+        <is>
           <t>0.086</t>
         </is>
       </c>
-      <c r="AT252" t="inlineStr">
-        <is>
-          <t>0.2951</t>
-        </is>
-      </c>
-      <c r="AU252" t="inlineStr">
-        <is>
-          <t>70.96</t>
-        </is>
-      </c>
-      <c r="AV252" t="inlineStr">
-        <is>
-          <t>14.5</t>
-        </is>
-      </c>
-      <c r="AW252" t="inlineStr">
-        <is>
-          <t>33.09</t>
-        </is>
-      </c>
-      <c r="AX252" t="inlineStr">
-        <is>
-          <t>19.99</t>
-        </is>
-      </c>
-      <c r="AY252" t="inlineStr">
-        <is>
-          <t>5.5</t>
-        </is>
-      </c>
-      <c r="AZ252" t="inlineStr">
-        <is>
-          <t>0.096</t>
-        </is>
-      </c>
       <c r="BA252" t="inlineStr">
         <is>
-          <t>5.69</t>
+          <t>8.06</t>
         </is>
       </c>
       <c r="BB252" t="inlineStr">
@@ -70978,29 +70914,37 @@
       </c>
       <c r="BC252" t="inlineStr">
         <is>
-          <t>87.94</t>
+          <t>88.09</t>
         </is>
       </c>
       <c r="BD252" t="inlineStr">
         <is>
-          <t>0.4726</t>
+          <t>0.3609</t>
         </is>
       </c>
       <c r="BE252" t="inlineStr">
         <is>
-          <t>0.1699</t>
+          <t>0.1407</t>
         </is>
       </c>
       <c r="BF252" t="inlineStr">
         <is>
-          <t>27.23</t>
-        </is>
-      </c>
-      <c r="BG252" t="inlineStr"/>
-      <c r="BH252" t="inlineStr"/>
+          <t>26.81</t>
+        </is>
+      </c>
+      <c r="BG252" t="inlineStr">
+        <is>
+          <t>In From LF</t>
+        </is>
+      </c>
+      <c r="BH252" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
       <c r="BI252" t="inlineStr">
         <is>
-          <t>Busch Stadium</t>
+          <t>Nationals Park</t>
         </is>
       </c>
       <c r="BJ252" t="inlineStr"/>
@@ -71011,56 +70955,56 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>691011</t>
+          <t>691026</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Drew Romo</t>
+          <t>Masyn Winn</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>2026-07-11T18:10:00Z</t>
+          <t>2026-07-11T23:15:00Z</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I253" t="inlineStr">
         <is>
-          <t>Gage Jump</t>
+          <t>Reynaldo López</t>
         </is>
       </c>
       <c r="J253" t="inlineStr">
         <is>
-          <t>695611</t>
+          <t>625643</t>
         </is>
       </c>
       <c r="K253" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L253" t="n">
-        <v>31.3</v>
+        <v>31.6</v>
       </c>
       <c r="M253" t="inlineStr">
         <is>
@@ -71074,61 +71018,65 @@
       </c>
       <c r="O253" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P253" t="n">
-        <v>14.6</v>
+        <v>14.3</v>
       </c>
       <c r="Q253" t="n">
-        <v>31.2</v>
+        <v>35.4</v>
       </c>
       <c r="R253" t="n">
-        <v>40.1</v>
+        <v>22.1</v>
       </c>
       <c r="S253" t="n">
-        <v>44.8</v>
+        <v>71.7</v>
       </c>
       <c r="T253" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U253" t="n">
-        <v>0</v>
+        <v>10.6</v>
       </c>
       <c r="V253" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W253" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X253" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y253" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W253" t="inlineStr">
+      <c r="Z253" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X253" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y253" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z253" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA253" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB253" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB253" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC253" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD253" t="inlineStr"/>
@@ -71145,12 +71093,12 @@
       </c>
       <c r="AH253" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI253" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ253" t="inlineStr">
@@ -71160,127 +71108,119 @@
       </c>
       <c r="AK253" t="inlineStr">
         <is>
-          <t>Last 7 games: 1/18, 0 HR</t>
+          <t>Last 7 games: 4/21, 0 HR</t>
         </is>
       </c>
       <c r="AL253" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 5.6% barrel, 4.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 5.7% barrel, 5.2 HR allowed</t>
         </is>
       </c>
       <c r="AM253" t="inlineStr">
         <is>
-          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN253" t="inlineStr">
         <is>
-          <t>7.9</t>
+          <t>3.68</t>
         </is>
       </c>
       <c r="AO253" t="inlineStr">
         <is>
-          <t>28.9</t>
+          <t>34.67</t>
         </is>
       </c>
       <c r="AP253" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>87.95</t>
         </is>
       </c>
       <c r="AQ253" t="inlineStr">
         <is>
-          <t>96.0986</t>
+          <t>98.5487</t>
         </is>
       </c>
       <c r="AR253" t="inlineStr">
         <is>
-          <t>0.2114</t>
+          <t>0.3344</t>
         </is>
       </c>
       <c r="AS253" t="inlineStr">
         <is>
-          <t>0.0875</t>
+          <t>0.086</t>
         </is>
       </c>
       <c r="AT253" t="inlineStr">
         <is>
-          <t>0.1813</t>
+          <t>0.2951</t>
         </is>
       </c>
       <c r="AU253" t="inlineStr">
         <is>
-          <t>68.49</t>
+          <t>70.96</t>
         </is>
       </c>
       <c r="AV253" t="inlineStr">
         <is>
-          <t>3.92</t>
+          <t>14.5</t>
         </is>
       </c>
       <c r="AW253" t="inlineStr">
         <is>
-          <t>39.5</t>
+          <t>33.09</t>
         </is>
       </c>
       <c r="AX253" t="inlineStr">
         <is>
-          <t>35.5</t>
+          <t>19.99</t>
         </is>
       </c>
       <c r="AY253" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AZ253" t="inlineStr">
         <is>
-          <t>0.1309</t>
+          <t>0.096</t>
         </is>
       </c>
       <c r="BA253" t="inlineStr">
         <is>
-          <t>5.6</t>
+          <t>5.69</t>
         </is>
       </c>
       <c r="BB253" t="inlineStr">
         <is>
-          <t>38.7</t>
+          <t>39.22</t>
         </is>
       </c>
       <c r="BC253" t="inlineStr">
         <is>
-          <t>89.5</t>
+          <t>87.94</t>
         </is>
       </c>
       <c r="BD253" t="inlineStr">
         <is>
-          <t>0.399</t>
+          <t>0.4726</t>
         </is>
       </c>
       <c r="BE253" t="inlineStr">
         <is>
-          <t>0.142</t>
+          <t>0.1699</t>
         </is>
       </c>
       <c r="BF253" t="inlineStr">
         <is>
-          <t>28.2</t>
-        </is>
-      </c>
-      <c r="BG253" t="inlineStr">
-        <is>
-          <t>In From LF</t>
-        </is>
-      </c>
-      <c r="BH253" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
+          <t>27.23</t>
+        </is>
+      </c>
+      <c r="BG253" t="inlineStr"/>
+      <c r="BH253" t="inlineStr"/>
       <c r="BI253" t="inlineStr">
         <is>
-          <t>Rate Field</t>
+          <t>Busch Stadium</t>
         </is>
       </c>
       <c r="BJ253" t="inlineStr"/>
@@ -71662,34 +71602,30 @@
       </c>
       <c r="W255" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X255" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y255" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z255" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X255" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y255" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z255" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA255" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB255" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB255" t="inlineStr"/>
       <c r="AC255" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -71944,28 +71880,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W256" t="inlineStr"/>
-      <c r="X256" t="inlineStr"/>
+      <c r="W256" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X256" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="Y256" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z256" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z256" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA256" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB256" t="inlineStr">
-        <is>
-          <t>not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB256" t="inlineStr"/>
       <c r="AC256" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -74216,34 +74156,30 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -75616,34 +75552,30 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 6 vs RotoWire 8</t>
-        </is>
-      </c>
+      <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>

--- a/outputs/hr_rankings.xlsx
+++ b/outputs/hr_rankings.xlsx
@@ -1320,7 +1320,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1600,7 +1600,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1904,7 +1904,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>65.59999999999999</v>
+        <v>65.8</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         <v>42.9</v>
       </c>
       <c r="R6" t="n">
-        <v>68.09999999999999</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="S6" t="n">
         <v>94.90000000000001</v>
@@ -2119,7 +2119,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>85</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2464,7 +2464,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>61.3</v>
+        <v>61.5</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -2488,7 +2488,7 @@
         <v>35.2</v>
       </c>
       <c r="R8" t="n">
-        <v>68.09999999999999</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="S8" t="n">
         <v>96.59999999999999</v>
@@ -2679,7 +2679,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>85</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3584,7 +3584,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>58.8</v>
+        <v>59</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -3608,7 +3608,7 @@
         <v>42.9</v>
       </c>
       <c r="R12" t="n">
-        <v>68.09999999999999</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="S12" t="n">
         <v>76.2</v>
@@ -3799,7 +3799,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>85</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -3864,7 +3864,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>58.7</v>
+        <v>58.9</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -3888,7 +3888,7 @@
         <v>35.2</v>
       </c>
       <c r="R13" t="n">
-        <v>68.09999999999999</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="S13" t="n">
         <v>100</v>
@@ -4079,7 +4079,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>85</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -4935,27 +4935,27 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>691023</t>
+          <t>695600</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Jordan Walker</t>
+          <t>Carter Jensen</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-07-11T23:15:00Z</t>
+          <t>2026-07-11T23:05:00Z</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -4965,17 +4965,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Reynaldo López</t>
+          <t>Kyle Bradish</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>625643</t>
+          <t>680694</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -4998,26 +4998,26 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot, Hot Hitter/Streak</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>61.5</v>
+        <v>53.7</v>
       </c>
       <c r="Q17" t="n">
-        <v>35.4</v>
+        <v>35.2</v>
       </c>
       <c r="R17" t="n">
-        <v>49.1</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="S17" t="n">
-        <v>94.90000000000001</v>
+        <v>93.2</v>
       </c>
       <c r="T17" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U17" t="n">
-        <v>87</v>
+        <v>29.2</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
@@ -5069,27 +5069,27 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Hot streak: 3 HR in last 7 games</t>
+          <t>Last 7 games: 5/26, 1 HR</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 5.7% barrel, 5.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.8% barrel, 9.3 HR allowed</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
@@ -5099,112 +5099,112 @@
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>13.42</t>
+          <t>12.54</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>51.4</t>
+          <t>48.01</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>93.63</t>
+          <t>92.18</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>105.2795</t>
+          <t>102.93</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>0.4736</t>
+          <t>0.4489</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>0.211</t>
+          <t>0.1976</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>0.3452</t>
+          <t>0.3364</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>78.87</t>
+          <t>74.27</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>83.54</t>
+          <t>40.5</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>38.24</t>
+          <t>39.04</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>24.19</t>
+          <t>29.23</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>17.2</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>0.1974</t>
+          <t>0.2073</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>5.69</t>
+          <t>8.8</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>39.22</t>
+          <t>37.08</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>87.94</t>
+          <t>88.61</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>0.4726</t>
+          <t>0.3627</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
-          <t>0.1699</t>
+          <t>0.1408</t>
         </is>
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>27.23</t>
+          <t>22.1</t>
         </is>
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>R To L</t>
+          <t>Out To LF</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>85</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
         <is>
-          <t>Busch Stadium</t>
+          <t>Oriole Park at Camden Yards</t>
         </is>
       </c>
       <c r="BJ17" t="inlineStr"/>
@@ -5215,27 +5215,27 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>695600</t>
+          <t>691023</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Carter Jensen</t>
+          <t>Jordan Walker</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-07-11T23:05:00Z</t>
+          <t>2026-07-11T23:15:00Z</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -5245,17 +5245,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Kyle Bradish</t>
+          <t>Reynaldo López</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>680694</t>
+          <t>625643</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -5264,7 +5264,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>58.1</v>
+        <v>58.3</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -5278,26 +5278,26 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>53.7</v>
+        <v>61.5</v>
       </c>
       <c r="Q18" t="n">
-        <v>35.2</v>
+        <v>35.4</v>
       </c>
       <c r="R18" t="n">
-        <v>68.09999999999999</v>
+        <v>49.1</v>
       </c>
       <c r="S18" t="n">
-        <v>93.2</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T18" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U18" t="n">
-        <v>29.2</v>
+        <v>87</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
@@ -5311,7 +5311,7 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
@@ -5349,27 +5349,27 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/26, 1 HR</t>
+          <t>Hot streak: 3 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.8% barrel, 9.3 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 5.7% barrel, 5.2 HR allowed</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
@@ -5379,112 +5379,112 @@
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>12.54</t>
+          <t>13.42</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>48.01</t>
+          <t>51.4</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>92.18</t>
+          <t>93.63</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>102.93</t>
+          <t>105.2795</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>0.4489</t>
+          <t>0.4736</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>0.1976</t>
+          <t>0.211</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>0.3364</t>
+          <t>0.3452</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>74.27</t>
+          <t>78.87</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>40.5</t>
+          <t>83.54</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>39.04</t>
+          <t>38.24</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>29.23</t>
+          <t>24.19</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>17.2</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>0.2073</t>
+          <t>0.1974</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>8.8</t>
+          <t>5.69</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>37.08</t>
+          <t>39.22</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>88.61</t>
+          <t>87.94</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>0.3627</t>
+          <t>0.4726</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
-          <t>0.1408</t>
+          <t>0.1699</t>
         </is>
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>22.1</t>
+          <t>27.23</t>
         </is>
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>Out To LF</t>
+          <t>R To L</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>81</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
         <is>
-          <t>Oriole Park at Camden Yards</t>
+          <t>Busch Stadium</t>
         </is>
       </c>
       <c r="BJ18" t="inlineStr"/>
@@ -6104,7 +6104,7 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>56.6</v>
+        <v>56.8</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
@@ -6128,7 +6128,7 @@
         <v>42.9</v>
       </c>
       <c r="R21" t="n">
-        <v>68.09999999999999</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="S21" t="n">
         <v>86.40000000000001</v>
@@ -6319,7 +6319,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>85</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -6920,7 +6920,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -7200,7 +7200,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -8295,27 +8295,27 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>693307</t>
+          <t>668939</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Dillon Dingler</t>
+          <t>Adley Rutschman</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-07-11T22:10:00Z</t>
+          <t>2026-07-11T23:05:00Z</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -8325,17 +8325,17 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Cristopher Sánchez</t>
+          <t>Noah Cameron</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>650911</t>
+          <t>702070</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -8344,7 +8344,7 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>53.9</v>
+        <v>54</v>
       </c>
       <c r="M29" t="inlineStr">
         <is>
@@ -8358,26 +8358,26 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P29" t="n">
-        <v>50.9</v>
+        <v>34.8</v>
       </c>
       <c r="Q29" t="n">
-        <v>36.1</v>
+        <v>41.6</v>
       </c>
       <c r="R29" t="n">
-        <v>44.6</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="S29" t="n">
-        <v>96.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="T29" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="U29" t="n">
-        <v>24.9</v>
+        <v>26.4</v>
       </c>
       <c r="V29" t="inlineStr">
         <is>
@@ -8391,7 +8391,7 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
@@ -8434,7 +8434,7 @@
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ29" t="inlineStr">
@@ -8444,12 +8444,12 @@
       </c>
       <c r="AK29" t="inlineStr">
         <is>
-          <t>Last 7 games: 8/28, 0 HR</t>
+          <t>Last 7 games: 8/27, 0 HR</t>
         </is>
       </c>
       <c r="AL29" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.0% barrel, 11.3 HR allowed</t>
+          <t>switch hitter; pitcher baseline 8.4% barrel, 12.4 HR allowed</t>
         </is>
       </c>
       <c r="AM29" t="inlineStr">
@@ -8459,112 +8459,112 @@
       </c>
       <c r="AN29" t="inlineStr">
         <is>
-          <t>11.02</t>
+          <t>7.43</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>47.17</t>
+          <t>41.61</t>
         </is>
       </c>
       <c r="AP29" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>89.47</t>
         </is>
       </c>
       <c r="AQ29" t="inlineStr">
         <is>
-          <t>101.2298</t>
+          <t>99.7403</t>
         </is>
       </c>
       <c r="AR29" t="inlineStr">
         <is>
-          <t>0.5142</t>
+          <t>0.4296</t>
         </is>
       </c>
       <c r="AS29" t="inlineStr">
         <is>
-          <t>0.2235</t>
+          <t>0.1641</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr">
         <is>
-          <t>0.3713</t>
+          <t>0.3418</t>
         </is>
       </c>
       <c r="AU29" t="inlineStr">
         <is>
-          <t>71.91</t>
+          <t>70.66</t>
         </is>
       </c>
       <c r="AV29" t="inlineStr">
         <is>
-          <t>16.7</t>
+          <t>13.18</t>
         </is>
       </c>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>41.36</t>
+          <t>37.77</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>29.76</t>
+          <t>28.8</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
-          <t>17.2</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>0.2205</t>
+          <t>0.174</t>
         </is>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
-          <t>8.01</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="BB29" t="inlineStr">
         <is>
-          <t>42.81</t>
+          <t>38.31</t>
         </is>
       </c>
       <c r="BC29" t="inlineStr">
         <is>
-          <t>89.21</t>
+          <t>88.74</t>
         </is>
       </c>
       <c r="BD29" t="inlineStr">
         <is>
-          <t>0.3604</t>
+          <t>0.4408</t>
         </is>
       </c>
       <c r="BE29" t="inlineStr">
         <is>
-          <t>0.1319</t>
+          <t>0.1751</t>
         </is>
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>17.67</t>
+          <t>25.4</t>
         </is>
       </c>
       <c r="BG29" t="inlineStr">
         <is>
-          <t>In From CF</t>
+          <t>Out To LF</t>
         </is>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>85</t>
         </is>
       </c>
       <c r="BI29" t="inlineStr">
         <is>
-          <t>Comerica Park</t>
+          <t>Oriole Park at Camden Yards</t>
         </is>
       </c>
       <c r="BJ29" t="inlineStr"/>
@@ -8575,47 +8575,47 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>668939</t>
+          <t>693307</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Adley Rutschman</t>
+          <t>Dillon Dingler</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-07-11T23:05:00Z</t>
+          <t>2026-07-11T22:10:00Z</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Noah Cameron</t>
+          <t>Cristopher Sánchez</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>702070</t>
+          <t>650911</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -8624,7 +8624,7 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>53.8</v>
+        <v>53.9</v>
       </c>
       <c r="M30" t="inlineStr">
         <is>
@@ -8638,26 +8638,26 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P30" t="n">
-        <v>34.8</v>
+        <v>50.9</v>
       </c>
       <c r="Q30" t="n">
-        <v>41.6</v>
+        <v>36.1</v>
       </c>
       <c r="R30" t="n">
-        <v>68.09999999999999</v>
+        <v>44.6</v>
       </c>
       <c r="S30" t="n">
-        <v>100</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T30" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="U30" t="n">
-        <v>26.4</v>
+        <v>24.9</v>
       </c>
       <c r="V30" t="inlineStr">
         <is>
@@ -8671,7 +8671,7 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
@@ -8714,7 +8714,7 @@
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ30" t="inlineStr">
@@ -8724,12 +8724,12 @@
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>Last 7 games: 8/27, 0 HR</t>
+          <t>Last 7 games: 8/28, 0 HR</t>
         </is>
       </c>
       <c r="AL30" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 8.4% barrel, 12.4 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.0% barrel, 11.3 HR allowed</t>
         </is>
       </c>
       <c r="AM30" t="inlineStr">
@@ -8739,102 +8739,102 @@
       </c>
       <c r="AN30" t="inlineStr">
         <is>
-          <t>7.43</t>
+          <t>11.02</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>41.61</t>
+          <t>47.17</t>
         </is>
       </c>
       <c r="AP30" t="inlineStr">
         <is>
-          <t>89.47</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AQ30" t="inlineStr">
         <is>
-          <t>99.7403</t>
+          <t>101.2298</t>
         </is>
       </c>
       <c r="AR30" t="inlineStr">
         <is>
-          <t>0.4296</t>
+          <t>0.5142</t>
         </is>
       </c>
       <c r="AS30" t="inlineStr">
         <is>
-          <t>0.1641</t>
+          <t>0.2235</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr">
         <is>
-          <t>0.3418</t>
+          <t>0.3713</t>
         </is>
       </c>
       <c r="AU30" t="inlineStr">
         <is>
-          <t>70.66</t>
+          <t>71.91</t>
         </is>
       </c>
       <c r="AV30" t="inlineStr">
         <is>
-          <t>13.18</t>
+          <t>16.7</t>
         </is>
       </c>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>37.77</t>
+          <t>41.36</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>28.8</t>
+          <t>29.76</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>17.2</t>
         </is>
       </c>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>0.174</t>
+          <t>0.2205</t>
         </is>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.01</t>
         </is>
       </c>
       <c r="BB30" t="inlineStr">
         <is>
-          <t>38.31</t>
+          <t>42.81</t>
         </is>
       </c>
       <c r="BC30" t="inlineStr">
         <is>
-          <t>88.74</t>
+          <t>89.21</t>
         </is>
       </c>
       <c r="BD30" t="inlineStr">
         <is>
-          <t>0.4408</t>
+          <t>0.3604</t>
         </is>
       </c>
       <c r="BE30" t="inlineStr">
         <is>
-          <t>0.1751</t>
+          <t>0.1319</t>
         </is>
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>25.4</t>
+          <t>17.67</t>
         </is>
       </c>
       <c r="BG30" t="inlineStr">
         <is>
-          <t>Out To LF</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BH30" t="inlineStr">
@@ -8844,7 +8844,7 @@
       </c>
       <c r="BI30" t="inlineStr">
         <is>
-          <t>Oriole Park at Camden Yards</t>
+          <t>Comerica Park</t>
         </is>
       </c>
       <c r="BJ30" t="inlineStr"/>
@@ -8855,27 +8855,27 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>547180</t>
+          <t>621493</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Bryce Harper</t>
+          <t>Taylor Ward</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-07-11T22:10:00Z</t>
+          <t>2026-07-11T23:05:00Z</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -8890,21 +8890,21 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Casey Mize</t>
+          <t>Noah Cameron</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>663554</t>
+          <t>702070</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L31" t="n">
-        <v>53.6</v>
+        <v>53.7</v>
       </c>
       <c r="M31" t="inlineStr">
         <is>
@@ -8918,26 +8918,26 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P31" t="n">
-        <v>54.3</v>
+        <v>32.9</v>
       </c>
       <c r="Q31" t="n">
-        <v>34.5</v>
+        <v>42.9</v>
       </c>
       <c r="R31" t="n">
-        <v>44.6</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="S31" t="n">
         <v>96.59999999999999</v>
       </c>
       <c r="T31" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="V31" t="inlineStr">
         <is>
@@ -8989,12 +8989,12 @@
       </c>
       <c r="AH31" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ31" t="inlineStr">
@@ -9004,12 +9004,12 @@
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>Last 7 games: 1/23, 0 HR</t>
+          <t>Contact streak: 8/24 over last 7 games</t>
         </is>
       </c>
       <c r="AL31" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.5% barrel, 9.8 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.4% barrel, 12.4 HR allowed</t>
         </is>
       </c>
       <c r="AM31" t="inlineStr">
@@ -9019,112 +9019,112 @@
       </c>
       <c r="AN31" t="inlineStr">
         <is>
-          <t>11.81</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>46.52</t>
+          <t>40.25</t>
         </is>
       </c>
       <c r="AP31" t="inlineStr">
         <is>
-          <t>90.53</t>
+          <t>89.54</t>
         </is>
       </c>
       <c r="AQ31" t="inlineStr">
         <is>
-          <t>102.1064</t>
+          <t>99.6112</t>
         </is>
       </c>
       <c r="AR31" t="inlineStr">
         <is>
-          <t>0.5116</t>
+          <t>0.4031</t>
         </is>
       </c>
       <c r="AS31" t="inlineStr">
         <is>
-          <t>0.2366</t>
+          <t>0.156</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr">
         <is>
-          <t>0.3862</t>
+          <t>0.3428</t>
         </is>
       </c>
       <c r="AU31" t="inlineStr">
         <is>
-          <t>74.34</t>
+          <t>68.59</t>
         </is>
       </c>
       <c r="AV31" t="inlineStr">
         <is>
-          <t>47.31</t>
+          <t>4.26</t>
         </is>
       </c>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>38.26</t>
+          <t>32.89</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>27.8</t>
+          <t>29.59</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
-          <t>22.1</t>
+          <t>14.3</t>
         </is>
       </c>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>0.2358</t>
+          <t>0.1413</t>
         </is>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
-          <t>7.52</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="BB31" t="inlineStr">
         <is>
-          <t>36.97</t>
+          <t>38.31</t>
         </is>
       </c>
       <c r="BC31" t="inlineStr">
         <is>
-          <t>88.67</t>
+          <t>88.74</t>
         </is>
       </c>
       <c r="BD31" t="inlineStr">
         <is>
-          <t>0.3665</t>
+          <t>0.4408</t>
         </is>
       </c>
       <c r="BE31" t="inlineStr">
         <is>
-          <t>0.1427</t>
+          <t>0.1751</t>
         </is>
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>29.27</t>
+          <t>25.4</t>
         </is>
       </c>
       <c r="BG31" t="inlineStr">
         <is>
-          <t>In From CF</t>
+          <t>Out To LF</t>
         </is>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>85</t>
         </is>
       </c>
       <c r="BI31" t="inlineStr">
         <is>
-          <t>Comerica Park</t>
+          <t>Oriole Park at Camden Yards</t>
         </is>
       </c>
       <c r="BJ31" t="inlineStr"/>
@@ -9135,32 +9135,32 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>621493</t>
+          <t>547180</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Taylor Ward</t>
+          <t>Bryce Harper</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-07-11T23:05:00Z</t>
+          <t>2026-07-11T22:10:00Z</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -9170,21 +9170,21 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Noah Cameron</t>
+          <t>Casey Mize</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>702070</t>
+          <t>663554</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L32" t="n">
-        <v>53.5</v>
+        <v>53.6</v>
       </c>
       <c r="M32" t="inlineStr">
         <is>
@@ -9198,26 +9198,26 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P32" t="n">
-        <v>32.9</v>
+        <v>54.3</v>
       </c>
       <c r="Q32" t="n">
-        <v>42.9</v>
+        <v>34.5</v>
       </c>
       <c r="R32" t="n">
-        <v>68.09999999999999</v>
+        <v>44.6</v>
       </c>
       <c r="S32" t="n">
         <v>96.59999999999999</v>
       </c>
       <c r="T32" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U32" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="V32" t="inlineStr">
         <is>
@@ -9269,12 +9269,12 @@
       </c>
       <c r="AH32" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ32" t="inlineStr">
@@ -9284,12 +9284,12 @@
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>Contact streak: 8/24 over last 7 games</t>
+          <t>Last 7 games: 1/23, 0 HR</t>
         </is>
       </c>
       <c r="AL32" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.4% barrel, 12.4 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.5% barrel, 9.8 HR allowed</t>
         </is>
       </c>
       <c r="AM32" t="inlineStr">
@@ -9299,102 +9299,102 @@
       </c>
       <c r="AN32" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>11.81</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>40.25</t>
+          <t>46.52</t>
         </is>
       </c>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>89.54</t>
+          <t>90.53</t>
         </is>
       </c>
       <c r="AQ32" t="inlineStr">
         <is>
-          <t>99.6112</t>
+          <t>102.1064</t>
         </is>
       </c>
       <c r="AR32" t="inlineStr">
         <is>
-          <t>0.4031</t>
+          <t>0.5116</t>
         </is>
       </c>
       <c r="AS32" t="inlineStr">
         <is>
-          <t>0.156</t>
+          <t>0.2366</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr">
         <is>
-          <t>0.3428</t>
+          <t>0.3862</t>
         </is>
       </c>
       <c r="AU32" t="inlineStr">
         <is>
-          <t>68.59</t>
+          <t>74.34</t>
         </is>
       </c>
       <c r="AV32" t="inlineStr">
         <is>
-          <t>4.26</t>
+          <t>47.31</t>
         </is>
       </c>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>32.89</t>
+          <t>38.26</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>29.59</t>
+          <t>27.8</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
-          <t>14.3</t>
+          <t>22.1</t>
         </is>
       </c>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>0.1413</t>
+          <t>0.2358</t>
         </is>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>7.52</t>
         </is>
       </c>
       <c r="BB32" t="inlineStr">
         <is>
-          <t>38.31</t>
+          <t>36.97</t>
         </is>
       </c>
       <c r="BC32" t="inlineStr">
         <is>
-          <t>88.74</t>
+          <t>88.67</t>
         </is>
       </c>
       <c r="BD32" t="inlineStr">
         <is>
-          <t>0.4408</t>
+          <t>0.3665</t>
         </is>
       </c>
       <c r="BE32" t="inlineStr">
         <is>
-          <t>0.1751</t>
+          <t>0.1427</t>
         </is>
       </c>
       <c r="BF32" t="inlineStr">
         <is>
-          <t>25.4</t>
+          <t>29.27</t>
         </is>
       </c>
       <c r="BG32" t="inlineStr">
         <is>
-          <t>Out To LF</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BH32" t="inlineStr">
@@ -9404,7 +9404,7 @@
       </c>
       <c r="BI32" t="inlineStr">
         <is>
-          <t>Oriole Park at Camden Yards</t>
+          <t>Comerica Park</t>
         </is>
       </c>
       <c r="BJ32" t="inlineStr"/>
@@ -9975,22 +9975,22 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>592626</t>
+          <t>691723</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Joc Pederson</t>
+          <t>Coby Mayo</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -10005,26 +10005,26 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Peter Lambert</t>
+          <t>Noah Cameron</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>663567</t>
+          <t>702070</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L35" t="n">
-        <v>52.1</v>
+        <v>52.2</v>
       </c>
       <c r="M35" t="inlineStr">
         <is>
@@ -10038,26 +10038,26 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P35" t="n">
-        <v>48.3</v>
+        <v>43.6</v>
       </c>
       <c r="Q35" t="n">
-        <v>35.1</v>
+        <v>42.9</v>
       </c>
       <c r="R35" t="n">
-        <v>41.1</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="S35" t="n">
-        <v>93.2</v>
+        <v>64.3</v>
       </c>
       <c r="T35" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="U35" t="n">
-        <v>26.8</v>
+        <v>20.3</v>
       </c>
       <c r="V35" t="inlineStr">
         <is>
@@ -10071,7 +10071,7 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y35" t="inlineStr">
@@ -10092,7 +10092,7 @@
       <c r="AB35" t="inlineStr"/>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD35" t="inlineStr"/>
@@ -10109,12 +10109,12 @@
       </c>
       <c r="AH35" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI35" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AJ35" t="inlineStr">
@@ -10124,127 +10124,127 @@
       </c>
       <c r="AK35" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/17, 1 HR</t>
+          <t>Last 7 games: 2/15, 1 HR</t>
         </is>
       </c>
       <c r="AL35" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.8% barrel, 10.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.4% barrel, 12.4 HR allowed</t>
         </is>
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN35" t="inlineStr">
         <is>
-          <t>10.9</t>
+          <t>9.96</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>48.23</t>
+          <t>45.31</t>
         </is>
       </c>
       <c r="AP35" t="inlineStr">
         <is>
-          <t>91.76</t>
+          <t>90.59</t>
         </is>
       </c>
       <c r="AQ35" t="inlineStr">
         <is>
-          <t>101.8965</t>
+          <t>102.884</t>
         </is>
       </c>
       <c r="AR35" t="inlineStr">
         <is>
-          <t>0.4322</t>
+          <t>0.3721</t>
         </is>
       </c>
       <c r="AS35" t="inlineStr">
         <is>
-          <t>0.1887</t>
+          <t>0.1663</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr">
         <is>
-          <t>0.3423</t>
+          <t>0.289</t>
         </is>
       </c>
       <c r="AU35" t="inlineStr">
         <is>
-          <t>72.42</t>
+          <t>75.33</t>
         </is>
       </c>
       <c r="AV35" t="inlineStr">
         <is>
-          <t>23.47</t>
+          <t>54.03</t>
         </is>
       </c>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>40.8</t>
+          <t>50.39</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>27.58</t>
+          <t>33.2</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
         <is>
-          <t>13.2</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>0.2037</t>
+          <t>0.185</t>
         </is>
       </c>
       <c r="BA35" t="inlineStr">
         <is>
-          <t>6.8</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="BB35" t="inlineStr">
         <is>
-          <t>38.2</t>
+          <t>38.31</t>
         </is>
       </c>
       <c r="BC35" t="inlineStr">
         <is>
-          <t>89.1</t>
+          <t>88.74</t>
         </is>
       </c>
       <c r="BD35" t="inlineStr">
         <is>
-          <t>0.357</t>
+          <t>0.4408</t>
         </is>
       </c>
       <c r="BE35" t="inlineStr">
         <is>
-          <t>0.148</t>
+          <t>0.1751</t>
         </is>
       </c>
       <c r="BF35" t="inlineStr">
         <is>
-          <t>33.6</t>
+          <t>25.4</t>
         </is>
       </c>
       <c r="BG35" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Out To LF</t>
         </is>
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>85</t>
         </is>
       </c>
       <c r="BI35" t="inlineStr">
         <is>
-          <t>Globe Life Field</t>
+          <t>Oriole Park at Camden Yards</t>
         </is>
       </c>
       <c r="BJ35" t="inlineStr"/>
@@ -10255,22 +10255,22 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>691723</t>
+          <t>592626</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Coby Mayo</t>
+          <t>Joc Pederson</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -10285,26 +10285,26 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Noah Cameron</t>
+          <t>Peter Lambert</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>702070</t>
+          <t>663567</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L36" t="n">
-        <v>51.9</v>
+        <v>52.1</v>
       </c>
       <c r="M36" t="inlineStr">
         <is>
@@ -10318,26 +10318,26 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P36" t="n">
-        <v>43.6</v>
+        <v>48.3</v>
       </c>
       <c r="Q36" t="n">
-        <v>42.9</v>
+        <v>35.1</v>
       </c>
       <c r="R36" t="n">
-        <v>68.09999999999999</v>
+        <v>41.1</v>
       </c>
       <c r="S36" t="n">
-        <v>64.3</v>
+        <v>93.2</v>
       </c>
       <c r="T36" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U36" t="n">
-        <v>20.3</v>
+        <v>26.8</v>
       </c>
       <c r="V36" t="inlineStr">
         <is>
@@ -10351,7 +10351,7 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y36" t="inlineStr">
@@ -10372,7 +10372,7 @@
       <c r="AB36" t="inlineStr"/>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD36" t="inlineStr"/>
@@ -10389,12 +10389,12 @@
       </c>
       <c r="AH36" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI36" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AJ36" t="inlineStr">
@@ -10404,127 +10404,127 @@
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/15, 1 HR</t>
+          <t>Last 7 games: 3/17, 1 HR</t>
         </is>
       </c>
       <c r="AL36" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.4% barrel, 12.4 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.8% barrel, 10.0 HR allowed</t>
         </is>
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN36" t="inlineStr">
         <is>
-          <t>9.96</t>
+          <t>10.9</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>45.31</t>
+          <t>48.23</t>
         </is>
       </c>
       <c r="AP36" t="inlineStr">
         <is>
-          <t>90.59</t>
+          <t>91.76</t>
         </is>
       </c>
       <c r="AQ36" t="inlineStr">
         <is>
-          <t>102.884</t>
+          <t>101.8965</t>
         </is>
       </c>
       <c r="AR36" t="inlineStr">
         <is>
-          <t>0.3721</t>
+          <t>0.4322</t>
         </is>
       </c>
       <c r="AS36" t="inlineStr">
         <is>
-          <t>0.1663</t>
+          <t>0.1887</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr">
         <is>
-          <t>0.289</t>
+          <t>0.3423</t>
         </is>
       </c>
       <c r="AU36" t="inlineStr">
         <is>
-          <t>75.33</t>
+          <t>72.42</t>
         </is>
       </c>
       <c r="AV36" t="inlineStr">
         <is>
-          <t>54.03</t>
+          <t>23.47</t>
         </is>
       </c>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>50.39</t>
+          <t>40.8</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>33.2</t>
+          <t>27.58</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">
         <is>
-          <t>11.0</t>
+          <t>13.2</t>
         </is>
       </c>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>0.185</t>
+          <t>0.2037</t>
         </is>
       </c>
       <c r="BA36" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>6.8</t>
         </is>
       </c>
       <c r="BB36" t="inlineStr">
         <is>
-          <t>38.31</t>
+          <t>38.2</t>
         </is>
       </c>
       <c r="BC36" t="inlineStr">
         <is>
-          <t>88.74</t>
+          <t>89.1</t>
         </is>
       </c>
       <c r="BD36" t="inlineStr">
         <is>
-          <t>0.4408</t>
+          <t>0.357</t>
         </is>
       </c>
       <c r="BE36" t="inlineStr">
         <is>
-          <t>0.1751</t>
+          <t>0.148</t>
         </is>
       </c>
       <c r="BF36" t="inlineStr">
         <is>
-          <t>25.4</t>
+          <t>33.6</t>
         </is>
       </c>
       <c r="BG36" t="inlineStr">
         <is>
-          <t>Out To LF</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI36" t="inlineStr">
         <is>
-          <t>Oriole Park at Camden Yards</t>
+          <t>Globe Life Field</t>
         </is>
       </c>
       <c r="BJ36" t="inlineStr"/>
@@ -12260,7 +12260,7 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>51</v>
+        <v>51.2</v>
       </c>
       <c r="M43" t="inlineStr">
         <is>
@@ -12284,7 +12284,7 @@
         <v>35.2</v>
       </c>
       <c r="R43" t="n">
-        <v>68.09999999999999</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="S43" t="n">
         <v>86.40000000000001</v>
@@ -12475,7 +12475,7 @@
       </c>
       <c r="BH43" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>85</t>
         </is>
       </c>
       <c r="BI43" t="inlineStr">
@@ -12491,22 +12491,22 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>694671</t>
+          <t>521692</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Wyatt Langford</t>
+          <t>Salvador Perez</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -12521,17 +12521,17 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Peter Lambert</t>
+          <t>Kyle Bradish</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>663567</t>
+          <t>680694</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -12540,7 +12540,7 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>51</v>
+        <v>51.1</v>
       </c>
       <c r="M44" t="inlineStr">
         <is>
@@ -12554,26 +12554,26 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot, Hot Hitter/Streak</t>
+          <t>Strong Barrel</t>
         </is>
       </c>
       <c r="P44" t="n">
-        <v>41.8</v>
+        <v>44.5</v>
       </c>
       <c r="Q44" t="n">
-        <v>35.1</v>
+        <v>35.2</v>
       </c>
       <c r="R44" t="n">
-        <v>41.1</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="S44" t="n">
-        <v>100</v>
+        <v>76.2</v>
       </c>
       <c r="T44" t="n">
         <v>50</v>
       </c>
       <c r="U44" t="n">
-        <v>82</v>
+        <v>46.9</v>
       </c>
       <c r="V44" t="inlineStr">
         <is>
@@ -12587,7 +12587,7 @@
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y44" t="inlineStr">
@@ -12608,7 +12608,7 @@
       <c r="AB44" t="inlineStr"/>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD44" t="inlineStr"/>
@@ -12630,137 +12630,137 @@
       </c>
       <c r="AI44" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK44" t="inlineStr">
         <is>
-          <t>Hot streak: 3 HR in last 7 games</t>
+          <t>Last 7 games: 9/29, 1 HR</t>
         </is>
       </c>
       <c r="AL44" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.8% barrel, 10.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.8% barrel, 9.3 HR allowed</t>
         </is>
       </c>
       <c r="AM44" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN44" t="inlineStr">
         <is>
-          <t>10.15</t>
+          <t>11.09</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>40.56</t>
+          <t>44.04</t>
         </is>
       </c>
       <c r="AP44" t="inlineStr">
         <is>
-          <t>89.72</t>
+          <t>89.37</t>
         </is>
       </c>
       <c r="AQ44" t="inlineStr">
         <is>
-          <t>100.9352</t>
+          <t>100.7366</t>
         </is>
       </c>
       <c r="AR44" t="inlineStr">
         <is>
-          <t>0.427</t>
+          <t>0.4346</t>
         </is>
       </c>
       <c r="AS44" t="inlineStr">
         <is>
-          <t>0.1883</t>
+          <t>0.1939</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr">
         <is>
-          <t>0.3194</t>
+          <t>0.3087</t>
         </is>
       </c>
       <c r="AU44" t="inlineStr">
         <is>
-          <t>72.96</t>
+          <t>72.13</t>
         </is>
       </c>
       <c r="AV44" t="inlineStr">
         <is>
-          <t>26.97</t>
+          <t>22.73</t>
         </is>
       </c>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>40.58</t>
+          <t>42.05</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>29.27</t>
+          <t>29.87</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">
         <is>
-          <t>12.9</t>
+          <t>16.7</t>
         </is>
       </c>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>0.218</t>
+          <t>0.1568</t>
         </is>
       </c>
       <c r="BA44" t="inlineStr">
         <is>
-          <t>6.8</t>
+          <t>8.8</t>
         </is>
       </c>
       <c r="BB44" t="inlineStr">
         <is>
-          <t>38.2</t>
+          <t>37.08</t>
         </is>
       </c>
       <c r="BC44" t="inlineStr">
         <is>
-          <t>89.1</t>
+          <t>88.61</t>
         </is>
       </c>
       <c r="BD44" t="inlineStr">
         <is>
-          <t>0.357</t>
+          <t>0.3627</t>
         </is>
       </c>
       <c r="BE44" t="inlineStr">
         <is>
-          <t>0.148</t>
+          <t>0.1408</t>
         </is>
       </c>
       <c r="BF44" t="inlineStr">
         <is>
-          <t>33.6</t>
+          <t>22.1</t>
         </is>
       </c>
       <c r="BG44" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Out To LF</t>
         </is>
       </c>
       <c r="BH44" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>85</t>
         </is>
       </c>
       <c r="BI44" t="inlineStr">
         <is>
-          <t>Globe Life Field</t>
+          <t>Oriole Park at Camden Yards</t>
         </is>
       </c>
       <c r="BJ44" t="inlineStr"/>
@@ -12771,27 +12771,27 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>682998</t>
+          <t>694671</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Corbin Carroll</t>
+          <t>Wyatt Langford</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-07-12T01:10:00Z</t>
+          <t>2026-07-11T23:05:00Z</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -12801,17 +12801,17 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Yoshinobu Yamamoto</t>
+          <t>Peter Lambert</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>808967</t>
+          <t>663567</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -12834,57 +12834,61 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P45" t="n">
-        <v>54.5</v>
+        <v>41.8</v>
       </c>
       <c r="Q45" t="n">
-        <v>27.3</v>
+        <v>35.1</v>
       </c>
       <c r="R45" t="n">
-        <v>38.1</v>
+        <v>41.1</v>
       </c>
       <c r="S45" t="n">
-        <v>96.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="T45" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U45" t="n">
-        <v>0.8</v>
+        <v>82</v>
       </c>
       <c r="V45" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W45" t="inlineStr"/>
-      <c r="X45" t="inlineStr"/>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="Y45" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB45" t="inlineStr"/>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD45" t="inlineStr"/>
@@ -12901,142 +12905,142 @@
       </c>
       <c r="AH45" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AI45" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AI45" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AK45" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/24, 0 HR</t>
+          <t>Hot streak: 3 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL45" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.3% barrel, 11.9 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.8% barrel, 10.0 HR allowed</t>
         </is>
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN45" t="inlineStr">
         <is>
-          <t>12.26</t>
+          <t>10.15</t>
         </is>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>47.45</t>
+          <t>40.56</t>
         </is>
       </c>
       <c r="AP45" t="inlineStr">
         <is>
-          <t>91.54</t>
+          <t>89.72</t>
         </is>
       </c>
       <c r="AQ45" t="inlineStr">
         <is>
-          <t>102.4703</t>
+          <t>100.9352</t>
         </is>
       </c>
       <c r="AR45" t="inlineStr">
         <is>
-          <t>0.4695</t>
+          <t>0.427</t>
         </is>
       </c>
       <c r="AS45" t="inlineStr">
         <is>
-          <t>0.2138</t>
+          <t>0.1883</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr">
         <is>
-          <t>0.3538</t>
+          <t>0.3194</t>
         </is>
       </c>
       <c r="AU45" t="inlineStr">
         <is>
-          <t>75.33</t>
+          <t>72.96</t>
         </is>
       </c>
       <c r="AV45" t="inlineStr">
         <is>
-          <t>55.82</t>
+          <t>26.97</t>
         </is>
       </c>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>46.18</t>
+          <t>40.58</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>28.57</t>
+          <t>29.27</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr">
         <is>
-          <t>18.4</t>
+          <t>12.9</t>
         </is>
       </c>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>0.247</t>
+          <t>0.218</t>
         </is>
       </c>
       <c r="BA45" t="inlineStr">
         <is>
-          <t>6.33</t>
+          <t>6.8</t>
         </is>
       </c>
       <c r="BB45" t="inlineStr">
         <is>
-          <t>36.97</t>
+          <t>38.2</t>
         </is>
       </c>
       <c r="BC45" t="inlineStr">
         <is>
-          <t>88.09</t>
+          <t>89.1</t>
         </is>
       </c>
       <c r="BD45" t="inlineStr">
         <is>
-          <t>0.3502</t>
+          <t>0.357</t>
         </is>
       </c>
       <c r="BE45" t="inlineStr">
         <is>
-          <t>0.127</t>
+          <t>0.148</t>
         </is>
       </c>
       <c r="BF45" t="inlineStr">
         <is>
-          <t>22.45</t>
+          <t>33.6</t>
         </is>
       </c>
       <c r="BG45" t="inlineStr">
         <is>
-          <t>In From CF</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH45" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI45" t="inlineStr">
         <is>
-          <t>UNIQLO Field at Dodger Stadium</t>
+          <t>Globe Life Field</t>
         </is>
       </c>
       <c r="BJ45" t="inlineStr"/>
@@ -13047,27 +13051,27 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>521692</t>
+          <t>682998</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Salvador Perez</t>
+          <t>Corbin Carroll</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-07-11T23:05:00Z</t>
+          <t>2026-07-12T01:10:00Z</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -13077,17 +13081,17 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Kyle Bradish</t>
+          <t>Yoshinobu Yamamoto</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>680694</t>
+          <t>808967</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -13096,7 +13100,7 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>50.9</v>
+        <v>51</v>
       </c>
       <c r="M46" t="inlineStr">
         <is>
@@ -13110,50 +13114,42 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>Strong Barrel</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P46" t="n">
-        <v>44.5</v>
+        <v>54.5</v>
       </c>
       <c r="Q46" t="n">
-        <v>35.2</v>
+        <v>27.3</v>
       </c>
       <c r="R46" t="n">
-        <v>68.09999999999999</v>
+        <v>38.1</v>
       </c>
       <c r="S46" t="n">
-        <v>76.2</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T46" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U46" t="n">
-        <v>46.9</v>
+        <v>0.8</v>
       </c>
       <c r="V46" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W46" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="X46" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+      <c r="W46" t="inlineStr"/>
+      <c r="X46" t="inlineStr"/>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -13161,7 +13157,11 @@
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB46" t="inlineStr"/>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>not found on RotoWire</t>
+        </is>
+      </c>
       <c r="AC46" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -13181,27 +13181,27 @@
       </c>
       <c r="AH46" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI46" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
         <is>
-          <t>Last 7 games: 9/29, 1 HR</t>
+          <t>Last 7 games: 3/24, 0 HR</t>
         </is>
       </c>
       <c r="AL46" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.8% barrel, 9.3 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.3% barrel, 11.9 HR allowed</t>
         </is>
       </c>
       <c r="AM46" t="inlineStr">
@@ -13211,112 +13211,112 @@
       </c>
       <c r="AN46" t="inlineStr">
         <is>
-          <t>11.09</t>
+          <t>12.26</t>
         </is>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>44.04</t>
+          <t>47.45</t>
         </is>
       </c>
       <c r="AP46" t="inlineStr">
         <is>
-          <t>89.37</t>
+          <t>91.54</t>
         </is>
       </c>
       <c r="AQ46" t="inlineStr">
         <is>
-          <t>100.7366</t>
+          <t>102.4703</t>
         </is>
       </c>
       <c r="AR46" t="inlineStr">
         <is>
-          <t>0.4346</t>
+          <t>0.4695</t>
         </is>
       </c>
       <c r="AS46" t="inlineStr">
         <is>
-          <t>0.1939</t>
+          <t>0.2138</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr">
         <is>
-          <t>0.3087</t>
+          <t>0.3538</t>
         </is>
       </c>
       <c r="AU46" t="inlineStr">
         <is>
-          <t>72.13</t>
+          <t>75.33</t>
         </is>
       </c>
       <c r="AV46" t="inlineStr">
         <is>
-          <t>22.73</t>
+          <t>55.82</t>
         </is>
       </c>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>42.05</t>
+          <t>46.18</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>29.87</t>
+          <t>28.57</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">
         <is>
-          <t>16.7</t>
+          <t>18.4</t>
         </is>
       </c>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>0.1568</t>
+          <t>0.247</t>
         </is>
       </c>
       <c r="BA46" t="inlineStr">
         <is>
-          <t>8.8</t>
+          <t>6.33</t>
         </is>
       </c>
       <c r="BB46" t="inlineStr">
         <is>
-          <t>37.08</t>
+          <t>36.97</t>
         </is>
       </c>
       <c r="BC46" t="inlineStr">
         <is>
-          <t>88.61</t>
+          <t>88.09</t>
         </is>
       </c>
       <c r="BD46" t="inlineStr">
         <is>
-          <t>0.3627</t>
+          <t>0.3502</t>
         </is>
       </c>
       <c r="BE46" t="inlineStr">
         <is>
-          <t>0.1408</t>
+          <t>0.127</t>
         </is>
       </c>
       <c r="BF46" t="inlineStr">
         <is>
-          <t>22.1</t>
+          <t>22.45</t>
         </is>
       </c>
       <c r="BG46" t="inlineStr">
         <is>
-          <t>Out To LF</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BH46" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>79</t>
         </is>
       </c>
       <c r="BI46" t="inlineStr">
         <is>
-          <t>Oriole Park at Camden Yards</t>
+          <t>UNIQLO Field at Dodger Stadium</t>
         </is>
       </c>
       <c r="BJ46" t="inlineStr"/>
@@ -13887,27 +13887,27 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>687221</t>
+          <t>683002</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Dalton Rushing</t>
+          <t>Gunnar Henderson</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-07-12T01:10:00Z</t>
+          <t>2026-07-11T23:05:00Z</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -13917,26 +13917,26 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Brandon Pfaadt</t>
+          <t>Noah Cameron</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>694297</t>
+          <t>702070</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L49" t="n">
-        <v>50.6</v>
+        <v>50.7</v>
       </c>
       <c r="M49" t="inlineStr">
         <is>
@@ -13950,26 +13950,26 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>Strong Barrel, Platoon Edge</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P49" t="n">
-        <v>45.3</v>
+        <v>37.5</v>
       </c>
       <c r="Q49" t="n">
-        <v>52.5</v>
+        <v>42.9</v>
       </c>
       <c r="R49" t="n">
-        <v>38.1</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="S49" t="n">
-        <v>52.4</v>
+        <v>93.2</v>
       </c>
       <c r="T49" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U49" t="n">
-        <v>54.9</v>
+        <v>0</v>
       </c>
       <c r="V49" t="inlineStr">
         <is>
@@ -13983,7 +13983,7 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y49" t="inlineStr">
@@ -14021,27 +14021,27 @@
       </c>
       <c r="AH49" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI49" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
         <is>
-          <t>Contact streak: 8/22 over last 7 games</t>
+          <t>Last 7 games: 3/27, 0 HR</t>
         </is>
       </c>
       <c r="AL49" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 10.8% barrel, 13.4 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.4% barrel, 12.4 HR allowed</t>
         </is>
       </c>
       <c r="AM49" t="inlineStr">
@@ -14051,112 +14051,112 @@
       </c>
       <c r="AN49" t="inlineStr">
         <is>
-          <t>12.46</t>
+          <t>7.55</t>
         </is>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>44.46</t>
+          <t>46.19</t>
         </is>
       </c>
       <c r="AP49" t="inlineStr">
         <is>
-          <t>89.82</t>
+          <t>90.42</t>
         </is>
       </c>
       <c r="AQ49" t="inlineStr">
         <is>
-          <t>101.812</t>
+          <t>101.3682</t>
         </is>
       </c>
       <c r="AR49" t="inlineStr">
         <is>
-          <t>0.4147</t>
+          <t>0.3998</t>
         </is>
       </c>
       <c r="AS49" t="inlineStr">
         <is>
-          <t>0.1774</t>
+          <t>0.1497</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr">
         <is>
-          <t>0.3222</t>
+          <t>0.3179</t>
         </is>
       </c>
       <c r="AU49" t="inlineStr">
         <is>
-          <t>72.61</t>
+          <t>74.67</t>
         </is>
       </c>
       <c r="AV49" t="inlineStr">
         <is>
-          <t>18.03</t>
+          <t>47.1</t>
         </is>
       </c>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>48.24</t>
+          <t>41.43</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>27.62</t>
+          <t>23.8</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>16.3</t>
         </is>
       </c>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>0.1935</t>
+          <t>0.1717</t>
         </is>
       </c>
       <c r="BA49" t="inlineStr">
         <is>
-          <t>10.76</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="BB49" t="inlineStr">
         <is>
-          <t>41.46</t>
+          <t>38.31</t>
         </is>
       </c>
       <c r="BC49" t="inlineStr">
         <is>
-          <t>89.82</t>
+          <t>88.74</t>
         </is>
       </c>
       <c r="BD49" t="inlineStr">
         <is>
-          <t>0.4457</t>
+          <t>0.4408</t>
         </is>
       </c>
       <c r="BE49" t="inlineStr">
         <is>
-          <t>0.1925</t>
+          <t>0.1751</t>
         </is>
       </c>
       <c r="BF49" t="inlineStr">
         <is>
-          <t>21.24</t>
+          <t>25.4</t>
         </is>
       </c>
       <c r="BG49" t="inlineStr">
         <is>
-          <t>In From CF</t>
+          <t>Out To LF</t>
         </is>
       </c>
       <c r="BH49" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>85</t>
         </is>
       </c>
       <c r="BI49" t="inlineStr">
         <is>
-          <t>UNIQLO Field at Dodger Stadium</t>
+          <t>Oriole Park at Camden Yards</t>
         </is>
       </c>
       <c r="BJ49" t="inlineStr"/>
@@ -14167,27 +14167,27 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>683002</t>
+          <t>687221</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Gunnar Henderson</t>
+          <t>Dalton Rushing</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-07-11T23:05:00Z</t>
+          <t>2026-07-12T01:10:00Z</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -14197,26 +14197,26 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Noah Cameron</t>
+          <t>Brandon Pfaadt</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>702070</t>
+          <t>694297</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L50" t="n">
-        <v>50.4</v>
+        <v>50.6</v>
       </c>
       <c r="M50" t="inlineStr">
         <is>
@@ -14230,26 +14230,26 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P50" t="n">
-        <v>37.5</v>
+        <v>45.3</v>
       </c>
       <c r="Q50" t="n">
-        <v>42.9</v>
+        <v>52.5</v>
       </c>
       <c r="R50" t="n">
-        <v>68.09999999999999</v>
+        <v>38.1</v>
       </c>
       <c r="S50" t="n">
-        <v>93.2</v>
+        <v>52.4</v>
       </c>
       <c r="T50" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U50" t="n">
-        <v>0</v>
+        <v>54.9</v>
       </c>
       <c r="V50" t="inlineStr">
         <is>
@@ -14263,7 +14263,7 @@
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y50" t="inlineStr">
@@ -14301,27 +14301,27 @@
       </c>
       <c r="AH50" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI50" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK50" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/27, 0 HR</t>
+          <t>Contact streak: 8/22 over last 7 games</t>
         </is>
       </c>
       <c r="AL50" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.4% barrel, 12.4 HR allowed</t>
+          <t>platoon edge; pitcher baseline 10.8% barrel, 13.4 HR allowed</t>
         </is>
       </c>
       <c r="AM50" t="inlineStr">
@@ -14331,112 +14331,112 @@
       </c>
       <c r="AN50" t="inlineStr">
         <is>
-          <t>7.55</t>
+          <t>12.46</t>
         </is>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
-          <t>46.19</t>
+          <t>44.46</t>
         </is>
       </c>
       <c r="AP50" t="inlineStr">
         <is>
-          <t>90.42</t>
+          <t>89.82</t>
         </is>
       </c>
       <c r="AQ50" t="inlineStr">
         <is>
-          <t>101.3682</t>
+          <t>101.812</t>
         </is>
       </c>
       <c r="AR50" t="inlineStr">
         <is>
-          <t>0.3998</t>
+          <t>0.4147</t>
         </is>
       </c>
       <c r="AS50" t="inlineStr">
         <is>
-          <t>0.1497</t>
+          <t>0.1774</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr">
         <is>
-          <t>0.3179</t>
+          <t>0.3222</t>
         </is>
       </c>
       <c r="AU50" t="inlineStr">
         <is>
-          <t>74.67</t>
+          <t>72.61</t>
         </is>
       </c>
       <c r="AV50" t="inlineStr">
         <is>
-          <t>47.1</t>
+          <t>18.03</t>
         </is>
       </c>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>41.43</t>
+          <t>48.24</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>23.8</t>
+          <t>27.62</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr">
         <is>
-          <t>16.3</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>0.1717</t>
+          <t>0.1935</t>
         </is>
       </c>
       <c r="BA50" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>10.76</t>
         </is>
       </c>
       <c r="BB50" t="inlineStr">
         <is>
-          <t>38.31</t>
+          <t>41.46</t>
         </is>
       </c>
       <c r="BC50" t="inlineStr">
         <is>
-          <t>88.74</t>
+          <t>89.82</t>
         </is>
       </c>
       <c r="BD50" t="inlineStr">
         <is>
-          <t>0.4408</t>
+          <t>0.4457</t>
         </is>
       </c>
       <c r="BE50" t="inlineStr">
         <is>
-          <t>0.1751</t>
+          <t>0.1925</t>
         </is>
       </c>
       <c r="BF50" t="inlineStr">
         <is>
-          <t>25.4</t>
+          <t>21.24</t>
         </is>
       </c>
       <c r="BG50" t="inlineStr">
         <is>
-          <t>Out To LF</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BH50" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>79</t>
         </is>
       </c>
       <c r="BI50" t="inlineStr">
         <is>
-          <t>Oriole Park at Camden Yards</t>
+          <t>UNIQLO Field at Dodger Stadium</t>
         </is>
       </c>
       <c r="BJ50" t="inlineStr"/>
@@ -15868,7 +15868,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -17523,27 +17523,27 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>605141</t>
+          <t>657041</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Mookie Betts</t>
+          <t>Lane Thomas</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-07-12T01:10:00Z</t>
+          <t>2026-07-11T23:05:00Z</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -17558,12 +17558,12 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Brandon Pfaadt</t>
+          <t>Kyle Bradish</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>694297</t>
+          <t>680694</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -17572,7 +17572,7 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>48.4</v>
+        <v>48.5</v>
       </c>
       <c r="M62" t="inlineStr">
         <is>
@@ -17586,17 +17586,17 @@
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot</t>
+          <t>Premium Lineup Spot, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P62" t="n">
-        <v>35.6</v>
+        <v>25.1</v>
       </c>
       <c r="Q62" t="n">
-        <v>52.5</v>
+        <v>35.2</v>
       </c>
       <c r="R62" t="n">
-        <v>38.1</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="S62" t="n">
         <v>94.90000000000001</v>
@@ -17605,7 +17605,7 @@
         <v>50</v>
       </c>
       <c r="U62" t="n">
-        <v>10.8</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="V62" t="inlineStr">
         <is>
@@ -17657,7 +17657,7 @@
       </c>
       <c r="AH62" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI62" t="inlineStr">
@@ -17667,132 +17667,132 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK62" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/26, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL62" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 10.8% barrel, 13.4 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.8% barrel, 9.3 HR allowed</t>
         </is>
       </c>
       <c r="AM62" t="inlineStr">
         <is>
-          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN62" t="inlineStr">
         <is>
-          <t>7.53</t>
+          <t>6.06</t>
         </is>
       </c>
       <c r="AO62" t="inlineStr">
         <is>
-          <t>38.67</t>
+          <t>38.09</t>
         </is>
       </c>
       <c r="AP62" t="inlineStr">
         <is>
-          <t>90.29</t>
+          <t>88.64</t>
         </is>
       </c>
       <c r="AQ62" t="inlineStr">
         <is>
-          <t>98.6587</t>
+          <t>99.4115</t>
         </is>
       </c>
       <c r="AR62" t="inlineStr">
         <is>
-          <t>0.4367</t>
+          <t>0.3455</t>
         </is>
       </c>
       <c r="AS62" t="inlineStr">
         <is>
-          <t>0.1616</t>
+          <t>0.1208</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr">
         <is>
-          <t>0.3349</t>
+          <t>0.3011</t>
         </is>
       </c>
       <c r="AU62" t="inlineStr">
         <is>
-          <t>69.35</t>
+          <t>72.42</t>
         </is>
       </c>
       <c r="AV62" t="inlineStr">
         <is>
-          <t>7.93</t>
+          <t>22.52</t>
         </is>
       </c>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>39.4</t>
+          <t>43.73</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>36.53</t>
+          <t>26.14</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr">
         <is>
-          <t>13.7</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>0.1746</t>
+          <t>0.1435</t>
         </is>
       </c>
       <c r="BA62" t="inlineStr">
         <is>
-          <t>10.76</t>
+          <t>8.8</t>
         </is>
       </c>
       <c r="BB62" t="inlineStr">
         <is>
-          <t>41.46</t>
+          <t>37.08</t>
         </is>
       </c>
       <c r="BC62" t="inlineStr">
         <is>
-          <t>89.82</t>
+          <t>88.61</t>
         </is>
       </c>
       <c r="BD62" t="inlineStr">
         <is>
-          <t>0.4457</t>
+          <t>0.3627</t>
         </is>
       </c>
       <c r="BE62" t="inlineStr">
         <is>
-          <t>0.1925</t>
+          <t>0.1408</t>
         </is>
       </c>
       <c r="BF62" t="inlineStr">
         <is>
-          <t>21.24</t>
+          <t>22.1</t>
         </is>
       </c>
       <c r="BG62" t="inlineStr">
         <is>
-          <t>In From CF</t>
+          <t>Out To LF</t>
         </is>
       </c>
       <c r="BH62" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>85</t>
         </is>
       </c>
       <c r="BI62" t="inlineStr">
         <is>
-          <t>UNIQLO Field at Dodger Stadium</t>
+          <t>Oriole Park at Camden Yards</t>
         </is>
       </c>
       <c r="BJ62" t="inlineStr"/>
@@ -17803,27 +17803,27 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>657041</t>
+          <t>605141</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Lane Thomas</t>
+          <t>Mookie Betts</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-07-11T23:05:00Z</t>
+          <t>2026-07-12T01:10:00Z</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -17838,12 +17838,12 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Kyle Bradish</t>
+          <t>Brandon Pfaadt</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>680694</t>
+          <t>694297</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -17852,7 +17852,7 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>48.3</v>
+        <v>48.4</v>
       </c>
       <c r="M63" t="inlineStr">
         <is>
@@ -17866,17 +17866,17 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Hot Hitter/Streak</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P63" t="n">
-        <v>25.1</v>
+        <v>35.6</v>
       </c>
       <c r="Q63" t="n">
-        <v>35.2</v>
+        <v>52.5</v>
       </c>
       <c r="R63" t="n">
-        <v>68.09999999999999</v>
+        <v>38.1</v>
       </c>
       <c r="S63" t="n">
         <v>94.90000000000001</v>
@@ -17885,7 +17885,7 @@
         <v>50</v>
       </c>
       <c r="U63" t="n">
-        <v>70.59999999999999</v>
+        <v>10.8</v>
       </c>
       <c r="V63" t="inlineStr">
         <is>
@@ -17937,7 +17937,7 @@
       </c>
       <c r="AH63" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI63" t="inlineStr">
@@ -17947,132 +17947,132 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 5/26, 0 HR</t>
         </is>
       </c>
       <c r="AL63" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.8% barrel, 9.3 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 10.8% barrel, 13.4 HR allowed</t>
         </is>
       </c>
       <c r="AM63" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN63" t="inlineStr">
         <is>
-          <t>6.06</t>
+          <t>7.53</t>
         </is>
       </c>
       <c r="AO63" t="inlineStr">
         <is>
-          <t>38.09</t>
+          <t>38.67</t>
         </is>
       </c>
       <c r="AP63" t="inlineStr">
         <is>
-          <t>88.64</t>
+          <t>90.29</t>
         </is>
       </c>
       <c r="AQ63" t="inlineStr">
         <is>
-          <t>99.4115</t>
+          <t>98.6587</t>
         </is>
       </c>
       <c r="AR63" t="inlineStr">
         <is>
-          <t>0.3455</t>
+          <t>0.4367</t>
         </is>
       </c>
       <c r="AS63" t="inlineStr">
         <is>
-          <t>0.1208</t>
+          <t>0.1616</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr">
         <is>
-          <t>0.3011</t>
+          <t>0.3349</t>
         </is>
       </c>
       <c r="AU63" t="inlineStr">
         <is>
-          <t>72.42</t>
+          <t>69.35</t>
         </is>
       </c>
       <c r="AV63" t="inlineStr">
         <is>
-          <t>22.52</t>
+          <t>7.93</t>
         </is>
       </c>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>43.73</t>
+          <t>39.4</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>26.14</t>
+          <t>36.53</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>13.7</t>
         </is>
       </c>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>0.1435</t>
+          <t>0.1746</t>
         </is>
       </c>
       <c r="BA63" t="inlineStr">
         <is>
-          <t>8.8</t>
+          <t>10.76</t>
         </is>
       </c>
       <c r="BB63" t="inlineStr">
         <is>
-          <t>37.08</t>
+          <t>41.46</t>
         </is>
       </c>
       <c r="BC63" t="inlineStr">
         <is>
-          <t>88.61</t>
+          <t>89.82</t>
         </is>
       </c>
       <c r="BD63" t="inlineStr">
         <is>
-          <t>0.3627</t>
+          <t>0.4457</t>
         </is>
       </c>
       <c r="BE63" t="inlineStr">
         <is>
-          <t>0.1408</t>
+          <t>0.1925</t>
         </is>
       </c>
       <c r="BF63" t="inlineStr">
         <is>
-          <t>22.1</t>
+          <t>21.24</t>
         </is>
       </c>
       <c r="BG63" t="inlineStr">
         <is>
-          <t>Out To LF</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BH63" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>79</t>
         </is>
       </c>
       <c r="BI63" t="inlineStr">
         <is>
-          <t>Oriole Park at Camden Yards</t>
+          <t>UNIQLO Field at Dodger Stadium</t>
         </is>
       </c>
       <c r="BJ63" t="inlineStr"/>
@@ -18108,7 +18108,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -19483,22 +19483,22 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>673962</t>
+          <t>686681</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Josh Jung</t>
+          <t>Michael Massey</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -19513,17 +19513,17 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Peter Lambert</t>
+          <t>Kyle Bradish</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>663567</t>
+          <t>680694</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -19532,7 +19532,7 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>46.8</v>
+        <v>46.9</v>
       </c>
       <c r="M69" t="inlineStr">
         <is>
@@ -19546,26 +19546,26 @@
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P69" t="n">
-        <v>34.9</v>
+        <v>31.9</v>
       </c>
       <c r="Q69" t="n">
-        <v>35.1</v>
+        <v>35.2</v>
       </c>
       <c r="R69" t="n">
-        <v>41.1</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="S69" t="n">
-        <v>96.59999999999999</v>
+        <v>64.3</v>
       </c>
       <c r="T69" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U69" t="n">
-        <v>52.3</v>
+        <v>24.9</v>
       </c>
       <c r="V69" t="inlineStr">
         <is>
@@ -19579,7 +19579,7 @@
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y69" t="inlineStr">
@@ -19600,7 +19600,7 @@
       <c r="AB69" t="inlineStr"/>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD69" t="inlineStr"/>
@@ -19617,142 +19617,142 @@
       </c>
       <c r="AH69" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI69" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
         <is>
-          <t>Contact streak: 9/26 over last 7 games</t>
+          <t>Last 7 games: 6/21, 0 HR</t>
         </is>
       </c>
       <c r="AL69" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.8% barrel, 10.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.8% barrel, 9.3 HR allowed</t>
         </is>
       </c>
       <c r="AM69" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN69" t="inlineStr">
         <is>
-          <t>6.69</t>
+          <t>6.17</t>
         </is>
       </c>
       <c r="AO69" t="inlineStr">
         <is>
-          <t>47.96</t>
+          <t>39.16</t>
         </is>
       </c>
       <c r="AP69" t="inlineStr">
         <is>
-          <t>90.21</t>
+          <t>89.67</t>
         </is>
       </c>
       <c r="AQ69" t="inlineStr">
         <is>
-          <t>100.5164</t>
+          <t>98.8462</t>
         </is>
       </c>
       <c r="AR69" t="inlineStr">
         <is>
-          <t>0.428</t>
+          <t>0.3978</t>
         </is>
       </c>
       <c r="AS69" t="inlineStr">
         <is>
-          <t>0.1522</t>
+          <t>0.1542</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr">
         <is>
-          <t>0.3341</t>
+          <t>0.2951</t>
         </is>
       </c>
       <c r="AU69" t="inlineStr">
         <is>
-          <t>70.51</t>
+          <t>71.43</t>
         </is>
       </c>
       <c r="AV69" t="inlineStr">
         <is>
-          <t>7.93</t>
+          <t>11.66</t>
         </is>
       </c>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>38.67</t>
+          <t>48.8</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>21.68</t>
+          <t>33.6</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr">
         <is>
-          <t>10.5</t>
+          <t>5.8</t>
         </is>
       </c>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>0.1474</t>
+          <t>0.1383</t>
         </is>
       </c>
       <c r="BA69" t="inlineStr">
         <is>
-          <t>6.8</t>
+          <t>8.8</t>
         </is>
       </c>
       <c r="BB69" t="inlineStr">
         <is>
-          <t>38.2</t>
+          <t>37.08</t>
         </is>
       </c>
       <c r="BC69" t="inlineStr">
         <is>
-          <t>89.1</t>
+          <t>88.61</t>
         </is>
       </c>
       <c r="BD69" t="inlineStr">
         <is>
-          <t>0.357</t>
+          <t>0.3627</t>
         </is>
       </c>
       <c r="BE69" t="inlineStr">
         <is>
-          <t>0.148</t>
+          <t>0.1408</t>
         </is>
       </c>
       <c r="BF69" t="inlineStr">
         <is>
-          <t>33.6</t>
+          <t>22.1</t>
         </is>
       </c>
       <c r="BG69" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Out To LF</t>
         </is>
       </c>
       <c r="BH69" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>85</t>
         </is>
       </c>
       <c r="BI69" t="inlineStr">
         <is>
-          <t>Globe Life Field</t>
+          <t>Oriole Park at Camden Yards</t>
         </is>
       </c>
       <c r="BJ69" t="inlineStr"/>
@@ -19763,22 +19763,22 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>686681</t>
+          <t>673962</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Michael Massey</t>
+          <t>Josh Jung</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -19793,17 +19793,17 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Kyle Bradish</t>
+          <t>Peter Lambert</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>680694</t>
+          <t>663567</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -19812,7 +19812,7 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>46.6</v>
+        <v>46.8</v>
       </c>
       <c r="M70" t="inlineStr">
         <is>
@@ -19826,26 +19826,26 @@
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P70" t="n">
-        <v>31.9</v>
+        <v>34.9</v>
       </c>
       <c r="Q70" t="n">
-        <v>35.2</v>
+        <v>35.1</v>
       </c>
       <c r="R70" t="n">
-        <v>68.09999999999999</v>
+        <v>41.1</v>
       </c>
       <c r="S70" t="n">
-        <v>64.3</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T70" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U70" t="n">
-        <v>24.9</v>
+        <v>52.3</v>
       </c>
       <c r="V70" t="inlineStr">
         <is>
@@ -19859,7 +19859,7 @@
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y70" t="inlineStr">
@@ -19880,7 +19880,7 @@
       <c r="AB70" t="inlineStr"/>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD70" t="inlineStr"/>
@@ -19897,142 +19897,142 @@
       </c>
       <c r="AH70" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI70" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK70" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/21, 0 HR</t>
+          <t>Contact streak: 9/26 over last 7 games</t>
         </is>
       </c>
       <c r="AL70" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.8% barrel, 9.3 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.8% barrel, 10.0 HR allowed</t>
         </is>
       </c>
       <c r="AM70" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN70" t="inlineStr">
         <is>
-          <t>6.17</t>
+          <t>6.69</t>
         </is>
       </c>
       <c r="AO70" t="inlineStr">
         <is>
-          <t>39.16</t>
+          <t>47.96</t>
         </is>
       </c>
       <c r="AP70" t="inlineStr">
         <is>
-          <t>89.67</t>
+          <t>90.21</t>
         </is>
       </c>
       <c r="AQ70" t="inlineStr">
         <is>
-          <t>98.8462</t>
+          <t>100.5164</t>
         </is>
       </c>
       <c r="AR70" t="inlineStr">
         <is>
-          <t>0.3978</t>
+          <t>0.428</t>
         </is>
       </c>
       <c r="AS70" t="inlineStr">
         <is>
-          <t>0.1542</t>
+          <t>0.1522</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr">
         <is>
-          <t>0.2951</t>
+          <t>0.3341</t>
         </is>
       </c>
       <c r="AU70" t="inlineStr">
         <is>
-          <t>71.43</t>
+          <t>70.51</t>
         </is>
       </c>
       <c r="AV70" t="inlineStr">
         <is>
-          <t>11.66</t>
+          <t>7.93</t>
         </is>
       </c>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>48.8</t>
+          <t>38.67</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
+          <t>21.68</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr">
+        <is>
+          <t>10.5</t>
+        </is>
+      </c>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>0.1474</t>
+        </is>
+      </c>
+      <c r="BA70" t="inlineStr">
+        <is>
+          <t>6.8</t>
+        </is>
+      </c>
+      <c r="BB70" t="inlineStr">
+        <is>
+          <t>38.2</t>
+        </is>
+      </c>
+      <c r="BC70" t="inlineStr">
+        <is>
+          <t>89.1</t>
+        </is>
+      </c>
+      <c r="BD70" t="inlineStr">
+        <is>
+          <t>0.357</t>
+        </is>
+      </c>
+      <c r="BE70" t="inlineStr">
+        <is>
+          <t>0.148</t>
+        </is>
+      </c>
+      <c r="BF70" t="inlineStr">
+        <is>
           <t>33.6</t>
         </is>
       </c>
-      <c r="AY70" t="inlineStr">
-        <is>
-          <t>5.8</t>
-        </is>
-      </c>
-      <c r="AZ70" t="inlineStr">
-        <is>
-          <t>0.1383</t>
-        </is>
-      </c>
-      <c r="BA70" t="inlineStr">
-        <is>
-          <t>8.8</t>
-        </is>
-      </c>
-      <c r="BB70" t="inlineStr">
-        <is>
-          <t>37.08</t>
-        </is>
-      </c>
-      <c r="BC70" t="inlineStr">
-        <is>
-          <t>88.61</t>
-        </is>
-      </c>
-      <c r="BD70" t="inlineStr">
-        <is>
-          <t>0.3627</t>
-        </is>
-      </c>
-      <c r="BE70" t="inlineStr">
-        <is>
-          <t>0.1408</t>
-        </is>
-      </c>
-      <c r="BF70" t="inlineStr">
-        <is>
-          <t>22.1</t>
-        </is>
-      </c>
       <c r="BG70" t="inlineStr">
         <is>
-          <t>Out To LF</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH70" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI70" t="inlineStr">
         <is>
-          <t>Oriole Park at Camden Yards</t>
+          <t>Globe Life Field</t>
         </is>
       </c>
       <c r="BJ70" t="inlineStr"/>
@@ -20908,7 +20908,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -21723,22 +21723,22 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>666211</t>
+          <t>702616</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Taylor Trammell</t>
+          <t>Jackson Holliday</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -21758,17 +21758,17 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Kumar Rocker</t>
+          <t>Noah Cameron</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>677958</t>
+          <t>702070</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L77" t="n">
@@ -21786,26 +21786,26 @@
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P77" t="n">
-        <v>37.8</v>
+        <v>33.7</v>
       </c>
       <c r="Q77" t="n">
-        <v>46.8</v>
+        <v>42.9</v>
       </c>
       <c r="R77" t="n">
-        <v>41.1</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="S77" t="n">
         <v>52.4</v>
       </c>
       <c r="T77" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U77" t="n">
-        <v>22.8</v>
+        <v>35.6</v>
       </c>
       <c r="V77" t="inlineStr">
         <is>
@@ -21857,27 +21857,27 @@
       </c>
       <c r="AH77" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI77" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/20, 1 HR</t>
+          <t>Contact streak: 5/14 over last 7 games</t>
         </is>
       </c>
       <c r="AL77" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.8% barrel, 9.6 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.4% barrel, 12.4 HR allowed</t>
         </is>
       </c>
       <c r="AM77" t="inlineStr">
@@ -21887,112 +21887,112 @@
       </c>
       <c r="AN77" t="inlineStr">
         <is>
-          <t>9.55</t>
+          <t>9.9</t>
         </is>
       </c>
       <c r="AO77" t="inlineStr">
         <is>
-          <t>37.85</t>
+          <t>38.35</t>
         </is>
       </c>
       <c r="AP77" t="inlineStr">
         <is>
-          <t>90.02</t>
+          <t>87.75</t>
         </is>
       </c>
       <c r="AQ77" t="inlineStr">
         <is>
-          <t>100.6513</t>
+          <t>98.5105</t>
         </is>
       </c>
       <c r="AR77" t="inlineStr">
         <is>
-          <t>0.3651</t>
+          <t>0.3963</t>
         </is>
       </c>
       <c r="AS77" t="inlineStr">
         <is>
-          <t>0.1585</t>
+          <t>0.1623</t>
         </is>
       </c>
       <c r="AT77" t="inlineStr">
         <is>
-          <t>0.2878</t>
+          <t>0.3238</t>
         </is>
       </c>
       <c r="AU77" t="inlineStr">
         <is>
-          <t>74.74</t>
+          <t>70.53</t>
         </is>
       </c>
       <c r="AV77" t="inlineStr">
         <is>
-          <t>48.14</t>
+          <t>8.32</t>
         </is>
       </c>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>44.79</t>
+          <t>38.84</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>32.12</t>
+          <t>28.6</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>0.1458</t>
+          <t>0.1603</t>
         </is>
       </c>
       <c r="BA77" t="inlineStr">
         <is>
-          <t>8.79</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="BB77" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>38.31</t>
         </is>
       </c>
       <c r="BC77" t="inlineStr">
         <is>
-          <t>89.8</t>
+          <t>88.74</t>
         </is>
       </c>
       <c r="BD77" t="inlineStr">
         <is>
-          <t>0.443</t>
+          <t>0.4408</t>
         </is>
       </c>
       <c r="BE77" t="inlineStr">
         <is>
-          <t>0.1752</t>
+          <t>0.1751</t>
         </is>
       </c>
       <c r="BF77" t="inlineStr">
         <is>
-          <t>22.09</t>
+          <t>25.4</t>
         </is>
       </c>
       <c r="BG77" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Out To LF</t>
         </is>
       </c>
       <c r="BH77" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>85</t>
         </is>
       </c>
       <c r="BI77" t="inlineStr">
         <is>
-          <t>Globe Life Field</t>
+          <t>Oriole Park at Camden Yards</t>
         </is>
       </c>
       <c r="BJ77" t="inlineStr"/>
@@ -22003,27 +22003,27 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>657757</t>
+          <t>666211</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Gavin Sheets</t>
+          <t>Taylor Trammell</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-07-12T00:40:00Z</t>
+          <t>2026-07-11T23:05:00Z</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -22033,17 +22033,17 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Trey Yesavage</t>
+          <t>Kumar Rocker</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>702056</t>
+          <t>677958</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -22052,7 +22052,7 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>45.4</v>
+        <v>45.5</v>
       </c>
       <c r="M78" t="inlineStr">
         <is>
@@ -22070,22 +22070,22 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>37.1</v>
+        <v>37.8</v>
       </c>
       <c r="Q78" t="n">
-        <v>31.7</v>
+        <v>46.8</v>
       </c>
       <c r="R78" t="n">
-        <v>41.6</v>
+        <v>41.1</v>
       </c>
       <c r="S78" t="n">
-        <v>86.40000000000001</v>
+        <v>52.4</v>
       </c>
       <c r="T78" t="n">
         <v>80</v>
       </c>
       <c r="U78" t="n">
-        <v>0.8</v>
+        <v>22.8</v>
       </c>
       <c r="V78" t="inlineStr">
         <is>
@@ -22099,7 +22099,7 @@
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y78" t="inlineStr">
@@ -22142,22 +22142,22 @@
       </c>
       <c r="AI78" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK78" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/24, 0 HR</t>
+          <t>Last 7 games: 3/20, 1 HR</t>
         </is>
       </c>
       <c r="AL78" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.2% barrel, 4.9 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.8% barrel, 9.6 HR allowed</t>
         </is>
       </c>
       <c r="AM78" t="inlineStr">
@@ -22167,112 +22167,112 @@
       </c>
       <c r="AN78" t="inlineStr">
         <is>
-          <t>8.27</t>
+          <t>9.55</t>
         </is>
       </c>
       <c r="AO78" t="inlineStr">
         <is>
-          <t>43.0</t>
+          <t>37.85</t>
         </is>
       </c>
       <c r="AP78" t="inlineStr">
         <is>
-          <t>88.78</t>
+          <t>90.02</t>
         </is>
       </c>
       <c r="AQ78" t="inlineStr">
         <is>
-          <t>100.0184</t>
+          <t>100.6513</t>
         </is>
       </c>
       <c r="AR78" t="inlineStr">
         <is>
-          <t>0.4229</t>
+          <t>0.3651</t>
         </is>
       </c>
       <c r="AS78" t="inlineStr">
         <is>
-          <t>0.1718</t>
+          <t>0.1585</t>
         </is>
       </c>
       <c r="AT78" t="inlineStr">
         <is>
-          <t>0.3337</t>
+          <t>0.2878</t>
         </is>
       </c>
       <c r="AU78" t="inlineStr">
         <is>
-          <t>74.45</t>
+          <t>74.74</t>
         </is>
       </c>
       <c r="AV78" t="inlineStr">
         <is>
-          <t>47.84</t>
+          <t>48.14</t>
         </is>
       </c>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>40.03</t>
+          <t>44.79</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>22.51</t>
+          <t>32.12</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr">
         <is>
-          <t>15.5</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>0.1987</t>
+          <t>0.1458</t>
         </is>
       </c>
       <c r="BA78" t="inlineStr">
         <is>
-          <t>6.23</t>
+          <t>8.79</t>
         </is>
       </c>
       <c r="BB78" t="inlineStr">
         <is>
-          <t>43.44</t>
+          <t>44.0</t>
         </is>
       </c>
       <c r="BC78" t="inlineStr">
         <is>
-          <t>90.22</t>
+          <t>89.8</t>
         </is>
       </c>
       <c r="BD78" t="inlineStr">
         <is>
-          <t>0.3354</t>
+          <t>0.443</t>
         </is>
       </c>
       <c r="BE78" t="inlineStr">
         <is>
-          <t>0.124</t>
+          <t>0.1752</t>
         </is>
       </c>
       <c r="BF78" t="inlineStr">
         <is>
-          <t>25.39</t>
+          <t>22.09</t>
         </is>
       </c>
       <c r="BG78" t="inlineStr">
         <is>
-          <t>R To L</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH78" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI78" t="inlineStr">
         <is>
-          <t>Petco Park</t>
+          <t>Globe Life Field</t>
         </is>
       </c>
       <c r="BJ78" t="inlineStr"/>
@@ -22283,27 +22283,27 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>702616</t>
+          <t>657757</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Jackson Holliday</t>
+          <t>Gavin Sheets</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-07-11T23:05:00Z</t>
+          <t>2026-07-12T00:40:00Z</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -22313,26 +22313,26 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Noah Cameron</t>
+          <t>Trey Yesavage</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>702070</t>
+          <t>702056</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L79" t="n">
-        <v>45.3</v>
+        <v>45.4</v>
       </c>
       <c r="M79" t="inlineStr">
         <is>
@@ -22346,26 +22346,26 @@
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>No major boost</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P79" t="n">
-        <v>33.7</v>
+        <v>37.1</v>
       </c>
       <c r="Q79" t="n">
-        <v>42.9</v>
+        <v>31.7</v>
       </c>
       <c r="R79" t="n">
-        <v>68.09999999999999</v>
+        <v>41.6</v>
       </c>
       <c r="S79" t="n">
-        <v>52.4</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T79" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U79" t="n">
-        <v>35.6</v>
+        <v>0.8</v>
       </c>
       <c r="V79" t="inlineStr">
         <is>
@@ -22379,7 +22379,7 @@
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y79" t="inlineStr">
@@ -22417,12 +22417,12 @@
       </c>
       <c r="AH79" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI79" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ79" t="inlineStr">
@@ -22432,12 +22432,12 @@
       </c>
       <c r="AK79" t="inlineStr">
         <is>
-          <t>Contact streak: 5/14 over last 7 games</t>
+          <t>Last 7 games: 3/24, 0 HR</t>
         </is>
       </c>
       <c r="AL79" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.4% barrel, 12.4 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.2% barrel, 4.9 HR allowed</t>
         </is>
       </c>
       <c r="AM79" t="inlineStr">
@@ -22447,112 +22447,112 @@
       </c>
       <c r="AN79" t="inlineStr">
         <is>
-          <t>9.9</t>
+          <t>8.27</t>
         </is>
       </c>
       <c r="AO79" t="inlineStr">
         <is>
-          <t>38.35</t>
+          <t>43.0</t>
         </is>
       </c>
       <c r="AP79" t="inlineStr">
         <is>
-          <t>87.75</t>
+          <t>88.78</t>
         </is>
       </c>
       <c r="AQ79" t="inlineStr">
         <is>
-          <t>98.5105</t>
+          <t>100.0184</t>
         </is>
       </c>
       <c r="AR79" t="inlineStr">
         <is>
-          <t>0.3963</t>
+          <t>0.4229</t>
         </is>
       </c>
       <c r="AS79" t="inlineStr">
         <is>
-          <t>0.1623</t>
+          <t>0.1718</t>
         </is>
       </c>
       <c r="AT79" t="inlineStr">
         <is>
-          <t>0.3238</t>
+          <t>0.3337</t>
         </is>
       </c>
       <c r="AU79" t="inlineStr">
         <is>
-          <t>70.53</t>
+          <t>74.45</t>
         </is>
       </c>
       <c r="AV79" t="inlineStr">
         <is>
-          <t>8.32</t>
+          <t>47.84</t>
         </is>
       </c>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>38.84</t>
+          <t>40.03</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>28.6</t>
+          <t>22.51</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>15.5</t>
         </is>
       </c>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>0.1603</t>
+          <t>0.1987</t>
         </is>
       </c>
       <c r="BA79" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>6.23</t>
         </is>
       </c>
       <c r="BB79" t="inlineStr">
         <is>
-          <t>38.31</t>
+          <t>43.44</t>
         </is>
       </c>
       <c r="BC79" t="inlineStr">
         <is>
-          <t>88.74</t>
+          <t>90.22</t>
         </is>
       </c>
       <c r="BD79" t="inlineStr">
         <is>
-          <t>0.4408</t>
+          <t>0.3354</t>
         </is>
       </c>
       <c r="BE79" t="inlineStr">
         <is>
-          <t>0.1751</t>
+          <t>0.124</t>
         </is>
       </c>
       <c r="BF79" t="inlineStr">
         <is>
-          <t>25.4</t>
+          <t>25.39</t>
         </is>
       </c>
       <c r="BG79" t="inlineStr">
         <is>
-          <t>Out To LF</t>
+          <t>R To L</t>
         </is>
       </c>
       <c r="BH79" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>71</t>
         </is>
       </c>
       <c r="BI79" t="inlineStr">
         <is>
-          <t>Oriole Park at Camden Yards</t>
+          <t>Petco Park</t>
         </is>
       </c>
       <c r="BJ79" t="inlineStr"/>
@@ -24239,27 +24239,27 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>681082</t>
+          <t>686555</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Bryson Stott</t>
+          <t>Isaac Collins</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-07-11T22:10:00Z</t>
+          <t>2026-07-11T23:05:00Z</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -24269,17 +24269,17 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>Casey Mize</t>
+          <t>Kyle Bradish</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>663554</t>
+          <t>680694</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
@@ -24288,7 +24288,7 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>42.7</v>
+        <v>42.8</v>
       </c>
       <c r="M86" t="inlineStr">
         <is>
@@ -24306,22 +24306,22 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>27.4</v>
+        <v>25.3</v>
       </c>
       <c r="Q86" t="n">
-        <v>34.5</v>
+        <v>34.2</v>
       </c>
       <c r="R86" t="n">
-        <v>44.6</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="S86" t="n">
-        <v>76.2</v>
+        <v>44.8</v>
       </c>
       <c r="T86" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="U86" t="n">
-        <v>16.6</v>
+        <v>55.6</v>
       </c>
       <c r="V86" t="inlineStr">
         <is>
@@ -24335,7 +24335,7 @@
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y86" t="inlineStr">
@@ -24373,27 +24373,27 @@
       </c>
       <c r="AH86" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI86" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK86" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/26, 0 HR</t>
+          <t>Contact streak: 7/19 over last 7 games</t>
         </is>
       </c>
       <c r="AL86" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.5% barrel, 9.8 HR allowed</t>
+          <t>switch hitter; pitcher baseline 8.8% barrel, 9.3 HR allowed</t>
         </is>
       </c>
       <c r="AM86" t="inlineStr">
@@ -24403,112 +24403,112 @@
       </c>
       <c r="AN86" t="inlineStr">
         <is>
-          <t>6.43</t>
+          <t>5.81</t>
         </is>
       </c>
       <c r="AO86" t="inlineStr">
         <is>
-          <t>36.08</t>
+          <t>40.37</t>
         </is>
       </c>
       <c r="AP86" t="inlineStr">
         <is>
-          <t>88.65</t>
+          <t>88.66</t>
         </is>
       </c>
       <c r="AQ86" t="inlineStr">
         <is>
-          <t>98.5842</t>
+          <t>100.1703</t>
         </is>
       </c>
       <c r="AR86" t="inlineStr">
         <is>
-          <t>0.4014</t>
+          <t>0.3471</t>
         </is>
       </c>
       <c r="AS86" t="inlineStr">
         <is>
-          <t>0.1453</t>
+          <t>0.1053</t>
         </is>
       </c>
       <c r="AT86" t="inlineStr">
         <is>
-          <t>0.3172</t>
+          <t>0.3192</t>
         </is>
       </c>
       <c r="AU86" t="inlineStr">
         <is>
-          <t>69.82</t>
+          <t>73.33</t>
         </is>
       </c>
       <c r="AV86" t="inlineStr">
         <is>
-          <t>6.19</t>
+          <t>30.97</t>
         </is>
       </c>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>34.94</t>
+          <t>41.38</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>29.2</t>
+          <t>26.79</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr">
         <is>
+          <t>6.2</t>
+        </is>
+      </c>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>0.1284</t>
+        </is>
+      </c>
+      <c r="BA86" t="inlineStr">
+        <is>
           <t>8.8</t>
         </is>
       </c>
-      <c r="AZ86" t="inlineStr">
-        <is>
-          <t>0.141</t>
-        </is>
-      </c>
-      <c r="BA86" t="inlineStr">
-        <is>
-          <t>7.52</t>
-        </is>
-      </c>
       <c r="BB86" t="inlineStr">
         <is>
-          <t>36.97</t>
+          <t>37.08</t>
         </is>
       </c>
       <c r="BC86" t="inlineStr">
         <is>
-          <t>88.67</t>
+          <t>88.61</t>
         </is>
       </c>
       <c r="BD86" t="inlineStr">
         <is>
-          <t>0.3665</t>
+          <t>0.3627</t>
         </is>
       </c>
       <c r="BE86" t="inlineStr">
         <is>
-          <t>0.1427</t>
+          <t>0.1408</t>
         </is>
       </c>
       <c r="BF86" t="inlineStr">
         <is>
-          <t>29.27</t>
+          <t>22.1</t>
         </is>
       </c>
       <c r="BG86" t="inlineStr">
         <is>
-          <t>In From CF</t>
+          <t>Out To LF</t>
         </is>
       </c>
       <c r="BH86" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>85</t>
         </is>
       </c>
       <c r="BI86" t="inlineStr">
         <is>
-          <t>Comerica Park</t>
+          <t>Oriole Park at Camden Yards</t>
         </is>
       </c>
       <c r="BJ86" t="inlineStr"/>
@@ -24519,12 +24519,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>687282</t>
+          <t>681082</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Gabriel Rincones Jr.</t>
+          <t>Bryson Stott</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -24544,12 +24544,12 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -24568,7 +24568,7 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>42.6</v>
+        <v>42.7</v>
       </c>
       <c r="M87" t="inlineStr">
         <is>
@@ -24586,7 +24586,7 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>34.5</v>
+        <v>27.4</v>
       </c>
       <c r="Q87" t="n">
         <v>34.5</v>
@@ -24595,13 +24595,13 @@
         <v>44.6</v>
       </c>
       <c r="S87" t="n">
-        <v>52.4</v>
+        <v>76.2</v>
       </c>
       <c r="T87" t="n">
         <v>80</v>
       </c>
       <c r="U87" t="n">
-        <v>34.4</v>
+        <v>16.6</v>
       </c>
       <c r="V87" t="inlineStr">
         <is>
@@ -24615,7 +24615,7 @@
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y87" t="inlineStr">
@@ -24636,7 +24636,7 @@
       <c r="AB87" t="inlineStr"/>
       <c r="AC87" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD87" t="inlineStr"/>
@@ -24653,22 +24653,22 @@
       </c>
       <c r="AH87" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI87" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/22, 1 HR</t>
+          <t>Last 7 games: 6/26, 0 HR</t>
         </is>
       </c>
       <c r="AL87" t="inlineStr">
@@ -24683,67 +24683,67 @@
       </c>
       <c r="AN87" t="inlineStr">
         <is>
-          <t>9.3</t>
+          <t>6.43</t>
         </is>
       </c>
       <c r="AO87" t="inlineStr">
         <is>
-          <t>39.1</t>
+          <t>36.08</t>
         </is>
       </c>
       <c r="AP87" t="inlineStr">
         <is>
-          <t>90.7</t>
+          <t>88.65</t>
         </is>
       </c>
       <c r="AQ87" t="inlineStr">
         <is>
-          <t>101.6285</t>
+          <t>98.5842</t>
         </is>
       </c>
       <c r="AR87" t="inlineStr">
         <is>
-          <t>0.293</t>
+          <t>0.4014</t>
         </is>
       </c>
       <c r="AS87" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.1453</t>
         </is>
       </c>
       <c r="AT87" t="inlineStr">
         <is>
-          <t>0.217</t>
+          <t>0.3172</t>
         </is>
       </c>
       <c r="AU87" t="inlineStr">
         <is>
-          <t>76.3</t>
+          <t>69.82</t>
         </is>
       </c>
       <c r="AV87" t="inlineStr">
         <is>
-          <t>61.3</t>
+          <t>6.19</t>
         </is>
       </c>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>28.3</t>
+          <t>34.94</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>26.1</t>
+          <t>29.2</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>8.8</t>
         </is>
       </c>
       <c r="AZ87" t="inlineStr">
         <is>
-          <t>0.143</t>
+          <t>0.141</t>
         </is>
       </c>
       <c r="BA87" t="inlineStr">
@@ -24799,47 +24799,47 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>686555</t>
+          <t>687282</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Isaac Collins</t>
+          <t>Gabriel Rincones Jr.</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-07-11T23:05:00Z</t>
+          <t>2026-07-11T22:10:00Z</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>Kyle Bradish</t>
+          <t>Casey Mize</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>680694</t>
+          <t>663554</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -24866,22 +24866,22 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>25.3</v>
+        <v>34.5</v>
       </c>
       <c r="Q88" t="n">
-        <v>34.2</v>
+        <v>34.5</v>
       </c>
       <c r="R88" t="n">
-        <v>68.09999999999999</v>
+        <v>44.6</v>
       </c>
       <c r="S88" t="n">
-        <v>44.8</v>
+        <v>52.4</v>
       </c>
       <c r="T88" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="U88" t="n">
-        <v>55.6</v>
+        <v>34.4</v>
       </c>
       <c r="V88" t="inlineStr">
         <is>
@@ -24895,7 +24895,7 @@
       </c>
       <c r="X88" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y88" t="inlineStr">
@@ -24916,7 +24916,7 @@
       <c r="AB88" t="inlineStr"/>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD88" t="inlineStr"/>
@@ -24933,12 +24933,12 @@
       </c>
       <c r="AH88" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI88" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ88" t="inlineStr">
@@ -24948,12 +24948,12 @@
       </c>
       <c r="AK88" t="inlineStr">
         <is>
-          <t>Contact streak: 7/19 over last 7 games</t>
+          <t>Last 7 games: 5/22, 1 HR</t>
         </is>
       </c>
       <c r="AL88" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 8.8% barrel, 9.3 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.5% barrel, 9.8 HR allowed</t>
         </is>
       </c>
       <c r="AM88" t="inlineStr">
@@ -24963,102 +24963,102 @@
       </c>
       <c r="AN88" t="inlineStr">
         <is>
-          <t>5.81</t>
+          <t>9.3</t>
         </is>
       </c>
       <c r="AO88" t="inlineStr">
         <is>
-          <t>40.37</t>
+          <t>39.1</t>
         </is>
       </c>
       <c r="AP88" t="inlineStr">
         <is>
-          <t>88.66</t>
+          <t>90.7</t>
         </is>
       </c>
       <c r="AQ88" t="inlineStr">
         <is>
-          <t>100.1703</t>
+          <t>101.6285</t>
         </is>
       </c>
       <c r="AR88" t="inlineStr">
         <is>
-          <t>0.3471</t>
+          <t>0.293</t>
         </is>
       </c>
       <c r="AS88" t="inlineStr">
         <is>
-          <t>0.1053</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="AT88" t="inlineStr">
         <is>
-          <t>0.3192</t>
+          <t>0.217</t>
         </is>
       </c>
       <c r="AU88" t="inlineStr">
         <is>
-          <t>73.33</t>
+          <t>76.3</t>
         </is>
       </c>
       <c r="AV88" t="inlineStr">
         <is>
-          <t>30.97</t>
+          <t>61.3</t>
         </is>
       </c>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>41.38</t>
+          <t>28.3</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>26.79</t>
+          <t>26.1</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr">
         <is>
-          <t>6.2</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AZ88" t="inlineStr">
         <is>
-          <t>0.1284</t>
+          <t>0.143</t>
         </is>
       </c>
       <c r="BA88" t="inlineStr">
         <is>
-          <t>8.8</t>
+          <t>7.52</t>
         </is>
       </c>
       <c r="BB88" t="inlineStr">
         <is>
-          <t>37.08</t>
+          <t>36.97</t>
         </is>
       </c>
       <c r="BC88" t="inlineStr">
         <is>
-          <t>88.61</t>
+          <t>88.67</t>
         </is>
       </c>
       <c r="BD88" t="inlineStr">
         <is>
-          <t>0.3627</t>
+          <t>0.3665</t>
         </is>
       </c>
       <c r="BE88" t="inlineStr">
         <is>
-          <t>0.1408</t>
+          <t>0.1427</t>
         </is>
       </c>
       <c r="BF88" t="inlineStr">
         <is>
-          <t>22.1</t>
+          <t>29.27</t>
         </is>
       </c>
       <c r="BG88" t="inlineStr">
         <is>
-          <t>Out To LF</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BH88" t="inlineStr">
@@ -25068,7 +25068,7 @@
       </c>
       <c r="BI88" t="inlineStr">
         <is>
-          <t>Oriole Park at Camden Yards</t>
+          <t>Comerica Park</t>
         </is>
       </c>
       <c r="BJ88" t="inlineStr"/>
@@ -25384,7 +25384,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -25664,7 +25664,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -25944,7 +25944,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -27064,7 +27064,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -27904,7 +27904,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -28208,7 +28208,7 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>40.2</v>
+        <v>40.4</v>
       </c>
       <c r="M100" t="inlineStr">
         <is>
@@ -28232,7 +28232,7 @@
         <v>35.2</v>
       </c>
       <c r="R100" t="n">
-        <v>68.09999999999999</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="S100" t="n">
         <v>52.4</v>
@@ -28423,7 +28423,7 @@
       </c>
       <c r="BH100" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>85</t>
         </is>
       </c>
       <c r="BI100" t="inlineStr">
@@ -28719,22 +28719,22 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>694497</t>
+          <t>665750</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Evan Carter</t>
+          <t>Leody Taveras</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -28749,22 +28749,22 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>Peter Lambert</t>
+          <t>Noah Cameron</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>663567</t>
+          <t>702070</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L102" t="n">
@@ -28786,22 +28786,22 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>23.7</v>
+        <v>17.3</v>
       </c>
       <c r="Q102" t="n">
-        <v>35.1</v>
+        <v>41.6</v>
       </c>
       <c r="R102" t="n">
-        <v>41.1</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="S102" t="n">
-        <v>64.3</v>
+        <v>44.8</v>
       </c>
       <c r="T102" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="U102" t="n">
-        <v>30.3</v>
+        <v>18.3</v>
       </c>
       <c r="V102" t="inlineStr">
         <is>
@@ -28815,7 +28815,7 @@
       </c>
       <c r="X102" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y102" t="inlineStr">
@@ -28836,7 +28836,7 @@
       <c r="AB102" t="inlineStr"/>
       <c r="AC102" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD102" t="inlineStr"/>
@@ -28853,12 +28853,12 @@
       </c>
       <c r="AH102" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI102" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AJ102" t="inlineStr">
@@ -28868,127 +28868,127 @@
       </c>
       <c r="AK102" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/15, 1 HR</t>
+          <t>Last 7 games: 2/19, 1 HR</t>
         </is>
       </c>
       <c r="AL102" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.8% barrel, 10.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 8.4% barrel, 12.4 HR allowed</t>
         </is>
       </c>
       <c r="AM102" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN102" t="inlineStr">
         <is>
-          <t>6.6</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AO102" t="inlineStr">
         <is>
-          <t>36.35</t>
+          <t>31.84</t>
         </is>
       </c>
       <c r="AP102" t="inlineStr">
         <is>
-          <t>87.26</t>
+          <t>87.66</t>
         </is>
       </c>
       <c r="AQ102" t="inlineStr">
         <is>
-          <t>98.8012</t>
+          <t>98.5524</t>
         </is>
       </c>
       <c r="AR102" t="inlineStr">
         <is>
-          <t>0.339</t>
+          <t>0.3223</t>
         </is>
       </c>
       <c r="AS102" t="inlineStr">
         <is>
-          <t>0.1295</t>
+          <t>0.1075</t>
         </is>
       </c>
       <c r="AT102" t="inlineStr">
         <is>
-          <t>0.2975</t>
+          <t>0.2698</t>
         </is>
       </c>
       <c r="AU102" t="inlineStr">
         <is>
-          <t>70.91</t>
+          <t>72.32</t>
         </is>
       </c>
       <c r="AV102" t="inlineStr">
         <is>
-          <t>17.05</t>
+          <t>24.63</t>
         </is>
       </c>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>36.74</t>
+          <t>32.95</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>29.52</t>
+          <t>23.05</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr">
         <is>
-          <t>6.4</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AZ102" t="inlineStr">
         <is>
-          <t>0.1436</t>
+          <t>0.1123</t>
         </is>
       </c>
       <c r="BA102" t="inlineStr">
         <is>
-          <t>6.8</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="BB102" t="inlineStr">
         <is>
-          <t>38.2</t>
+          <t>38.31</t>
         </is>
       </c>
       <c r="BC102" t="inlineStr">
         <is>
-          <t>89.1</t>
+          <t>88.74</t>
         </is>
       </c>
       <c r="BD102" t="inlineStr">
         <is>
-          <t>0.357</t>
+          <t>0.4408</t>
         </is>
       </c>
       <c r="BE102" t="inlineStr">
         <is>
-          <t>0.148</t>
+          <t>0.1751</t>
         </is>
       </c>
       <c r="BF102" t="inlineStr">
         <is>
-          <t>33.6</t>
+          <t>25.4</t>
         </is>
       </c>
       <c r="BG102" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Out To LF</t>
         </is>
       </c>
       <c r="BH102" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>85</t>
         </is>
       </c>
       <c r="BI102" t="inlineStr">
         <is>
-          <t>Globe Life Field</t>
+          <t>Oriole Park at Camden Yards</t>
         </is>
       </c>
       <c r="BJ102" t="inlineStr"/>
@@ -28999,22 +28999,22 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>665750</t>
+          <t>694497</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Leody Taveras</t>
+          <t>Evan Carter</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -29029,26 +29029,26 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>Noah Cameron</t>
+          <t>Peter Lambert</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>702070</t>
+          <t>663567</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L103" t="n">
-        <v>39.8</v>
+        <v>40.1</v>
       </c>
       <c r="M103" t="inlineStr">
         <is>
@@ -29066,22 +29066,22 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>17.3</v>
+        <v>23.7</v>
       </c>
       <c r="Q103" t="n">
-        <v>41.6</v>
+        <v>35.1</v>
       </c>
       <c r="R103" t="n">
-        <v>68.09999999999999</v>
+        <v>41.1</v>
       </c>
       <c r="S103" t="n">
-        <v>44.8</v>
+        <v>64.3</v>
       </c>
       <c r="T103" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="U103" t="n">
-        <v>18.3</v>
+        <v>30.3</v>
       </c>
       <c r="V103" t="inlineStr">
         <is>
@@ -29095,7 +29095,7 @@
       </c>
       <c r="X103" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y103" t="inlineStr">
@@ -29116,7 +29116,7 @@
       <c r="AB103" t="inlineStr"/>
       <c r="AC103" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD103" t="inlineStr"/>
@@ -29133,12 +29133,12 @@
       </c>
       <c r="AH103" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI103" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AJ103" t="inlineStr">
@@ -29148,127 +29148,127 @@
       </c>
       <c r="AK103" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/19, 1 HR</t>
+          <t>Last 7 games: 3/15, 1 HR</t>
         </is>
       </c>
       <c r="AL103" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 8.4% barrel, 12.4 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.8% barrel, 10.0 HR allowed</t>
         </is>
       </c>
       <c r="AM103" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN103" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>6.6</t>
         </is>
       </c>
       <c r="AO103" t="inlineStr">
         <is>
-          <t>31.84</t>
+          <t>36.35</t>
         </is>
       </c>
       <c r="AP103" t="inlineStr">
         <is>
-          <t>87.66</t>
+          <t>87.26</t>
         </is>
       </c>
       <c r="AQ103" t="inlineStr">
         <is>
-          <t>98.5524</t>
+          <t>98.8012</t>
         </is>
       </c>
       <c r="AR103" t="inlineStr">
         <is>
-          <t>0.3223</t>
+          <t>0.339</t>
         </is>
       </c>
       <c r="AS103" t="inlineStr">
         <is>
-          <t>0.1075</t>
+          <t>0.1295</t>
         </is>
       </c>
       <c r="AT103" t="inlineStr">
         <is>
-          <t>0.2698</t>
+          <t>0.2975</t>
         </is>
       </c>
       <c r="AU103" t="inlineStr">
         <is>
-          <t>72.32</t>
+          <t>70.91</t>
         </is>
       </c>
       <c r="AV103" t="inlineStr">
         <is>
-          <t>24.63</t>
+          <t>17.05</t>
         </is>
       </c>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>32.95</t>
+          <t>36.74</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>23.05</t>
+          <t>29.52</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>6.4</t>
         </is>
       </c>
       <c r="AZ103" t="inlineStr">
         <is>
-          <t>0.1123</t>
+          <t>0.1436</t>
         </is>
       </c>
       <c r="BA103" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>6.8</t>
         </is>
       </c>
       <c r="BB103" t="inlineStr">
         <is>
-          <t>38.31</t>
+          <t>38.2</t>
         </is>
       </c>
       <c r="BC103" t="inlineStr">
         <is>
-          <t>88.74</t>
+          <t>89.1</t>
         </is>
       </c>
       <c r="BD103" t="inlineStr">
         <is>
-          <t>0.4408</t>
+          <t>0.357</t>
         </is>
       </c>
       <c r="BE103" t="inlineStr">
         <is>
-          <t>0.1751</t>
+          <t>0.148</t>
         </is>
       </c>
       <c r="BF103" t="inlineStr">
         <is>
-          <t>25.4</t>
+          <t>33.6</t>
         </is>
       </c>
       <c r="BG103" t="inlineStr">
         <is>
-          <t>Out To LF</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH103" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI103" t="inlineStr">
         <is>
-          <t>Oriole Park at Camden Yards</t>
+          <t>Globe Life Field</t>
         </is>
       </c>
       <c r="BJ103" t="inlineStr"/>
@@ -32376,7 +32376,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -35444,7 +35444,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -36890,7 +36890,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -37170,7 +37170,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -37474,7 +37474,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>65.59999999999999</v>
+        <v>65.8</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -37498,7 +37498,7 @@
         <v>42.9</v>
       </c>
       <c r="R6" t="n">
-        <v>68.09999999999999</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="S6" t="n">
         <v>94.90000000000001</v>
@@ -37689,7 +37689,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>85</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -38034,7 +38034,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>61.3</v>
+        <v>61.5</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -38058,7 +38058,7 @@
         <v>35.2</v>
       </c>
       <c r="R8" t="n">
-        <v>68.09999999999999</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="S8" t="n">
         <v>96.59999999999999</v>
@@ -38249,7 +38249,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>85</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -39154,7 +39154,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>58.8</v>
+        <v>59</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -39178,7 +39178,7 @@
         <v>42.9</v>
       </c>
       <c r="R12" t="n">
-        <v>68.09999999999999</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="S12" t="n">
         <v>76.2</v>
@@ -39369,7 +39369,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>85</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -39434,7 +39434,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>58.7</v>
+        <v>58.9</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -39458,7 +39458,7 @@
         <v>35.2</v>
       </c>
       <c r="R13" t="n">
-        <v>68.09999999999999</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="S13" t="n">
         <v>100</v>
@@ -39649,7 +39649,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>85</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -40505,27 +40505,27 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>691023</t>
+          <t>695600</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Jordan Walker</t>
+          <t>Carter Jensen</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-07-11T23:15:00Z</t>
+          <t>2026-07-11T23:05:00Z</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -40535,17 +40535,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Reynaldo López</t>
+          <t>Kyle Bradish</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>625643</t>
+          <t>680694</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -40568,26 +40568,26 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot, Hot Hitter/Streak</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>61.5</v>
+        <v>53.7</v>
       </c>
       <c r="Q17" t="n">
-        <v>35.4</v>
+        <v>35.2</v>
       </c>
       <c r="R17" t="n">
-        <v>49.1</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="S17" t="n">
-        <v>94.90000000000001</v>
+        <v>93.2</v>
       </c>
       <c r="T17" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U17" t="n">
-        <v>87</v>
+        <v>29.2</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
@@ -40601,7 +40601,7 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
@@ -40639,27 +40639,27 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Hot streak: 3 HR in last 7 games</t>
+          <t>Last 7 games: 5/26, 1 HR</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 5.7% barrel, 5.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.8% barrel, 9.3 HR allowed</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
@@ -40669,112 +40669,112 @@
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>13.42</t>
+          <t>12.54</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>51.4</t>
+          <t>48.01</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>93.63</t>
+          <t>92.18</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>105.2795</t>
+          <t>102.93</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>0.4736</t>
+          <t>0.4489</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>0.211</t>
+          <t>0.1976</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>0.3452</t>
+          <t>0.3364</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>78.87</t>
+          <t>74.27</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>83.54</t>
+          <t>40.5</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>38.24</t>
+          <t>39.04</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>24.19</t>
+          <t>29.23</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>17.2</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>0.1974</t>
+          <t>0.2073</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>5.69</t>
+          <t>8.8</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>39.22</t>
+          <t>37.08</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>87.94</t>
+          <t>88.61</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>0.4726</t>
+          <t>0.3627</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
-          <t>0.1699</t>
+          <t>0.1408</t>
         </is>
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>27.23</t>
+          <t>22.1</t>
         </is>
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>R To L</t>
+          <t>Out To LF</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>85</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
         <is>
-          <t>Busch Stadium</t>
+          <t>Oriole Park at Camden Yards</t>
         </is>
       </c>
       <c r="BJ17" t="inlineStr"/>
@@ -40785,27 +40785,27 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>695600</t>
+          <t>691023</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Carter Jensen</t>
+          <t>Jordan Walker</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-07-11T23:05:00Z</t>
+          <t>2026-07-11T23:15:00Z</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -40815,17 +40815,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Kyle Bradish</t>
+          <t>Reynaldo López</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>680694</t>
+          <t>625643</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -40834,7 +40834,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>58.1</v>
+        <v>58.3</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -40848,26 +40848,26 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>53.7</v>
+        <v>61.5</v>
       </c>
       <c r="Q18" t="n">
-        <v>35.2</v>
+        <v>35.4</v>
       </c>
       <c r="R18" t="n">
-        <v>68.09999999999999</v>
+        <v>49.1</v>
       </c>
       <c r="S18" t="n">
-        <v>93.2</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T18" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U18" t="n">
-        <v>29.2</v>
+        <v>87</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
@@ -40881,7 +40881,7 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
@@ -40919,27 +40919,27 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/26, 1 HR</t>
+          <t>Hot streak: 3 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.8% barrel, 9.3 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 5.7% barrel, 5.2 HR allowed</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
@@ -40949,112 +40949,112 @@
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>12.54</t>
+          <t>13.42</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>48.01</t>
+          <t>51.4</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>92.18</t>
+          <t>93.63</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>102.93</t>
+          <t>105.2795</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>0.4489</t>
+          <t>0.4736</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>0.1976</t>
+          <t>0.211</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>0.3364</t>
+          <t>0.3452</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>74.27</t>
+          <t>78.87</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>40.5</t>
+          <t>83.54</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>39.04</t>
+          <t>38.24</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>29.23</t>
+          <t>24.19</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>17.2</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>0.2073</t>
+          <t>0.1974</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>8.8</t>
+          <t>5.69</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>37.08</t>
+          <t>39.22</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>88.61</t>
+          <t>87.94</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>0.3627</t>
+          <t>0.4726</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
-          <t>0.1408</t>
+          <t>0.1699</t>
         </is>
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>22.1</t>
+          <t>27.23</t>
         </is>
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>Out To LF</t>
+          <t>R To L</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>81</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
         <is>
-          <t>Oriole Park at Camden Yards</t>
+          <t>Busch Stadium</t>
         </is>
       </c>
       <c r="BJ18" t="inlineStr"/>
@@ -41674,7 +41674,7 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>56.6</v>
+        <v>56.8</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
@@ -41698,7 +41698,7 @@
         <v>42.9</v>
       </c>
       <c r="R21" t="n">
-        <v>68.09999999999999</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="S21" t="n">
         <v>86.40000000000001</v>
@@ -41889,7 +41889,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>85</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">

--- a/outputs/hr_rankings.xlsx
+++ b/outputs/hr_rankings.xlsx
@@ -760,7 +760,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1600,7 +1600,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -2720,7 +2720,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -3000,7 +3000,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -3280,7 +3280,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -3560,7 +3560,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -4120,7 +4120,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -4680,7 +4680,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -5520,7 +5520,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -6080,7 +6080,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -6360,7 +6360,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -6640,7 +6640,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -6920,7 +6920,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -7200,7 +7200,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -7480,7 +7480,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -7760,7 +7760,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -8040,7 +8040,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -8320,7 +8320,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -8600,7 +8600,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -8880,7 +8880,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -9160,7 +9160,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -9440,7 +9440,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -10276,7 +10276,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -10556,7 +10556,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -10836,7 +10836,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -11392,7 +11392,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -11952,7 +11952,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -12512,7 +12512,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -14188,7 +14188,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -14468,7 +14468,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -14748,7 +14748,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -15028,7 +15028,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -15308,7 +15308,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -15868,7 +15868,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -16708,7 +16708,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -16988,7 +16988,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -17268,7 +17268,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -17828,7 +17828,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -18108,7 +18108,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -18388,7 +18388,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -18668,7 +18668,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -18948,7 +18948,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -19508,7 +19508,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -19788,7 +19788,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -20068,7 +20068,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -20348,7 +20348,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -20628,7 +20628,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -21464,7 +21464,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -21744,7 +21744,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -22024,7 +22024,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -22864,7 +22864,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -23144,7 +23144,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -23424,7 +23424,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -23704,7 +23704,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -23984,7 +23984,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -24544,7 +24544,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -24824,7 +24824,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -25380,7 +25380,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -26780,7 +26780,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -27336,7 +27336,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -27616,7 +27616,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -27896,7 +27896,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -28176,7 +28176,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -29288,7 +29288,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -30124,7 +30124,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -30684,7 +30684,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -31290,7 +31290,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -31850,7 +31850,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -32130,7 +32130,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -32410,7 +32410,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -32690,7 +32690,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -32970,7 +32970,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -33250,7 +33250,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -33530,7 +33530,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -33810,7 +33810,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -34090,7 +34090,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -34370,7 +34370,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -34650,7 +34650,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -35210,7 +35210,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -35490,7 +35490,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -36050,7 +36050,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -36610,7 +36610,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">

--- a/outputs/hr_rankings.xlsx
+++ b/outputs/hr_rankings.xlsx
@@ -1295,27 +1295,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>518692</t>
+          <t>672960</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Freddie Freeman</t>
+          <t>Kazuma Okamoto</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-07-12T01:10:00Z</t>
+          <t>2026-07-12T00:40:00Z</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1325,17 +1325,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Brandon Pfaadt</t>
+          <t>Walker Buehler</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>694297</t>
+          <t>621111</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1358,26 +1358,26 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>47.6</v>
+        <v>58</v>
       </c>
       <c r="Q4" t="n">
-        <v>52.5</v>
+        <v>46</v>
       </c>
       <c r="R4" t="n">
-        <v>38.1</v>
+        <v>44.1</v>
       </c>
       <c r="S4" t="n">
-        <v>96.59999999999999</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T4" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U4" t="n">
-        <v>43.2</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="V4" t="inlineStr">
         <is>
@@ -1391,7 +1391,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1412,7 +1412,7 @@
       <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr"/>
@@ -1429,7 +1429,7 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
@@ -1439,17 +1439,17 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Last 7 games: 8/28, 1 HR</t>
+          <t>Hot streak: 3 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 10.8% barrel, 13.4 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 9.3% barrel, 14.3 HR allowed</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
@@ -1459,112 +1459,112 @@
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>10.68</t>
+          <t>14.7</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>45.28</t>
+          <t>47.7</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>90.62</t>
+          <t>91.4</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>100.8959</t>
+          <t>102.5213</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.4943</t>
+          <t>0.451</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>0.2091</t>
+          <t>0.229</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>0.3745</t>
+          <t>0.329</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>70.32</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>8.89</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>36.54</t>
+          <t>51.4</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>29.03</t>
+          <t>31.7</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>0.2028</t>
+          <t>0.232</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>10.76</t>
+          <t>9.29</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>41.46</t>
+          <t>40.95</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>89.82</t>
+          <t>89.72</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>0.4457</t>
+          <t>0.4262</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>0.1925</t>
+          <t>0.1638</t>
         </is>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>21.24</t>
+          <t>22.25</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>In From CF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>UNIQLO Field at Dodger Stadium</t>
+          <t>Petco Park</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr"/>
@@ -1575,27 +1575,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>672960</t>
+          <t>518692</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Kazuma Okamoto</t>
+          <t>Freddie Freeman</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-07-12T00:40:00Z</t>
+          <t>2026-07-12T01:10:00Z</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1605,17 +1605,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Walker Buehler</t>
+          <t>Brandon Pfaadt</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>621111</t>
+          <t>694297</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1624,7 +1624,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>56.5</v>
+        <v>56.9</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1638,26 +1638,26 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Strong Barrel</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>58</v>
+        <v>47.6</v>
       </c>
       <c r="Q5" t="n">
-        <v>46</v>
+        <v>52.5</v>
       </c>
       <c r="R5" t="n">
-        <v>41.6</v>
+        <v>38.1</v>
       </c>
       <c r="S5" t="n">
-        <v>86.40000000000001</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T5" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U5" t="n">
-        <v>69.09999999999999</v>
+        <v>43.2</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1692,7 +1692,7 @@
       <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr"/>
@@ -1709,7 +1709,7 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
@@ -1719,17 +1719,17 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Hot streak: 3 HR in last 7 games</t>
+          <t>Last 7 games: 8/28, 1 HR</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 9.3% barrel, 14.3 HR allowed</t>
+          <t>platoon edge; pitcher baseline 10.8% barrel, 13.4 HR allowed</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
@@ -1739,112 +1739,112 @@
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>14.7</t>
+          <t>10.68</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>47.7</t>
+          <t>45.28</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>91.4</t>
+          <t>90.62</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>102.5213</t>
+          <t>100.8959</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.451</t>
+          <t>0.4943</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>0.229</t>
+          <t>0.2091</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>0.329</t>
+          <t>0.3745</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>70.32</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>8.89</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>51.4</t>
+          <t>36.54</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>31.7</t>
+          <t>29.03</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>17.7</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>0.232</t>
+          <t>0.2028</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>9.29</t>
+          <t>10.76</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>40.95</t>
+          <t>41.46</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>89.72</t>
+          <t>89.82</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>0.4262</t>
+          <t>0.4457</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>0.1638</t>
+          <t>0.1925</t>
         </is>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>22.25</t>
+          <t>21.24</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>R To L</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>79</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>Petco Park</t>
+          <t>UNIQLO Field at Dodger Stadium</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr"/>
@@ -2411,27 +2411,27 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>682998</t>
+          <t>592518</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Corbin Carroll</t>
+          <t>Manny Machado</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-07-12T01:10:00Z</t>
+          <t>2026-07-12T00:40:00Z</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -2441,17 +2441,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Yoshinobu Yamamoto</t>
+          <t>Trey Yesavage</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>808967</t>
+          <t>702056</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -2460,7 +2460,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>51</v>
+        <v>51.2</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -2474,54 +2474,58 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>54.5</v>
+        <v>49.3</v>
       </c>
       <c r="Q8" t="n">
-        <v>27.3</v>
+        <v>31.7</v>
       </c>
       <c r="R8" t="n">
-        <v>38.1</v>
+        <v>44.1</v>
       </c>
       <c r="S8" t="n">
-        <v>96.59999999999999</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T8" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U8" t="n">
-        <v>0.8</v>
+        <v>57.8</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr"/>
-      <c r="X8" t="inlineStr"/>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="Y8" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2541,27 +2545,27 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/24, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.3% barrel, 11.9 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.2% barrel, 4.9 HR allowed</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
@@ -2571,112 +2575,112 @@
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>12.26</t>
+          <t>11.43</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>47.45</t>
+          <t>45.83</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>91.54</t>
+          <t>90.94</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>102.4703</t>
+          <t>101.8062</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>0.4695</t>
+          <t>0.4397</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>0.2138</t>
+          <t>0.1981</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>0.3538</t>
+          <t>0.3298</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>75.33</t>
+          <t>74.64</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>55.82</t>
+          <t>44.4</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>46.18</t>
+          <t>39.94</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>28.57</t>
+          <t>28.29</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>18.4</t>
+          <t>21.4</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>0.247</t>
+          <t>0.2102</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>6.33</t>
+          <t>6.23</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>36.97</t>
+          <t>43.44</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>88.09</t>
+          <t>90.22</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>0.3502</t>
+          <t>0.3354</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
-          <t>0.127</t>
+          <t>0.124</t>
         </is>
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>22.45</t>
+          <t>25.39</t>
         </is>
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>In From CF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>UNIQLO Field at Dodger Stadium</t>
+          <t>Petco Park</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr"/>
@@ -2687,27 +2691,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>592518</t>
+          <t>682998</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Manny Machado</t>
+          <t>Corbin Carroll</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-07-12T00:40:00Z</t>
+          <t>2026-07-12T01:10:00Z</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -2717,17 +2721,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Trey Yesavage</t>
+          <t>Yoshinobu Yamamoto</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>702056</t>
+          <t>808967</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -2736,7 +2740,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>50.8</v>
+        <v>51</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -2750,58 +2754,54 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>49.3</v>
+        <v>54.5</v>
       </c>
       <c r="Q9" t="n">
-        <v>31.7</v>
+        <v>27.3</v>
       </c>
       <c r="R9" t="n">
-        <v>41.6</v>
+        <v>38.1</v>
       </c>
       <c r="S9" t="n">
-        <v>94.90000000000001</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T9" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U9" t="n">
-        <v>57.8</v>
+        <v>0.8</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr"/>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>not found on RotoWire</t>
+        </is>
+      </c>
       <c r="AC9" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2821,27 +2821,27 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 3/24, 0 HR</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.2% barrel, 4.9 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.3% barrel, 11.9 HR allowed</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
@@ -2851,112 +2851,112 @@
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>11.43</t>
+          <t>12.26</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>45.83</t>
+          <t>47.45</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>90.94</t>
+          <t>91.54</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>101.8062</t>
+          <t>102.4703</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>0.4397</t>
+          <t>0.4695</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>0.1981</t>
+          <t>0.2138</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>0.3298</t>
+          <t>0.3538</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>74.64</t>
+          <t>75.33</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>44.4</t>
+          <t>55.82</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>39.94</t>
+          <t>46.18</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>28.29</t>
+          <t>28.57</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>21.4</t>
+          <t>18.4</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>0.2102</t>
+          <t>0.247</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>6.23</t>
+          <t>6.33</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>43.44</t>
+          <t>36.97</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>90.22</t>
+          <t>88.09</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>0.3354</t>
+          <t>0.3502</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
-          <t>0.124</t>
+          <t>0.127</t>
         </is>
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>25.39</t>
+          <t>22.45</t>
         </is>
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>R To L</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>79</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>Petco Park</t>
+          <t>UNIQLO Field at Dodger Stadium</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr"/>
@@ -2967,27 +2967,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>687221</t>
+          <t>701538</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Dalton Rushing</t>
+          <t>Jackson Merrill</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-07-12T01:10:00Z</t>
+          <t>2026-07-12T00:40:00Z</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -2997,17 +2997,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Brandon Pfaadt</t>
+          <t>Trey Yesavage</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>694297</t>
+          <t>702056</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -3016,7 +3016,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>50.6</v>
+        <v>50.7</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -3030,26 +3030,26 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Strong Barrel, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>45.3</v>
+        <v>43.3</v>
       </c>
       <c r="Q10" t="n">
-        <v>52.5</v>
+        <v>31.7</v>
       </c>
       <c r="R10" t="n">
-        <v>38.1</v>
+        <v>44.1</v>
       </c>
       <c r="S10" t="n">
-        <v>52.4</v>
+        <v>100</v>
       </c>
       <c r="T10" t="n">
         <v>80</v>
       </c>
       <c r="U10" t="n">
-        <v>54.9</v>
+        <v>19.5</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
@@ -3063,7 +3063,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -3101,27 +3101,27 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Contact streak: 8/22 over last 7 games</t>
+          <t>Last 7 games: 7/28, 0 HR</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 10.8% barrel, 13.4 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.2% barrel, 4.9 HR allowed</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
@@ -3131,112 +3131,112 @@
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>12.46</t>
+          <t>10.41</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>44.46</t>
+          <t>44.09</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>89.82</t>
+          <t>89.56</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>101.812</t>
+          <t>100.25</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>0.4147</t>
+          <t>0.4326</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>0.1774</t>
+          <t>0.1864</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>0.3222</t>
+          <t>0.3162</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>72.61</t>
+          <t>73.05</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>18.03</t>
+          <t>28.02</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>48.24</t>
+          <t>38.26</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>27.62</t>
+          <t>27.89</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>11.8</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>0.1935</t>
+          <t>0.151</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>10.76</t>
+          <t>6.23</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>41.46</t>
+          <t>43.44</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>89.82</t>
+          <t>90.22</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>0.4457</t>
+          <t>0.3354</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
-          <t>0.1925</t>
+          <t>0.124</t>
         </is>
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>21.24</t>
+          <t>25.39</t>
         </is>
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>In From CF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>UNIQLO Field at Dodger Stadium</t>
+          <t>Petco Park</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr"/>
@@ -3247,27 +3247,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>701538</t>
+          <t>687221</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Jackson Merrill</t>
+          <t>Dalton Rushing</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-07-12T00:40:00Z</t>
+          <t>2026-07-12T01:10:00Z</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -3277,17 +3277,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Trey Yesavage</t>
+          <t>Brandon Pfaadt</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>702056</t>
+          <t>694297</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -3296,7 +3296,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>50.3</v>
+        <v>50.6</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -3310,26 +3310,26 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>43.3</v>
+        <v>45.3</v>
       </c>
       <c r="Q11" t="n">
-        <v>31.7</v>
+        <v>52.5</v>
       </c>
       <c r="R11" t="n">
-        <v>41.6</v>
+        <v>38.1</v>
       </c>
       <c r="S11" t="n">
-        <v>100</v>
+        <v>52.4</v>
       </c>
       <c r="T11" t="n">
         <v>80</v>
       </c>
       <c r="U11" t="n">
-        <v>19.5</v>
+        <v>54.9</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
@@ -3343,7 +3343,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -3381,27 +3381,27 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/28, 0 HR</t>
+          <t>Contact streak: 8/22 over last 7 games</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.2% barrel, 4.9 HR allowed</t>
+          <t>platoon edge; pitcher baseline 10.8% barrel, 13.4 HR allowed</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
@@ -3411,112 +3411,112 @@
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>10.41</t>
+          <t>12.46</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>44.09</t>
+          <t>44.46</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>89.56</t>
+          <t>89.82</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>100.25</t>
+          <t>101.812</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>0.4326</t>
+          <t>0.4147</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>0.1864</t>
+          <t>0.1774</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>0.3162</t>
+          <t>0.3222</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>73.05</t>
+          <t>72.61</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>28.02</t>
+          <t>18.03</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>38.26</t>
+          <t>48.24</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>27.89</t>
+          <t>27.62</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>11.8</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>0.151</t>
+          <t>0.1935</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>6.23</t>
+          <t>10.76</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>43.44</t>
+          <t>41.46</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>90.22</t>
+          <t>89.82</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>0.3354</t>
+          <t>0.4457</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
-          <t>0.124</t>
+          <t>0.1925</t>
         </is>
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>25.39</t>
+          <t>21.24</t>
         </is>
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>R To L</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>79</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>Petco Park</t>
+          <t>UNIQLO Field at Dodger Stadium</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr"/>
@@ -3576,7 +3576,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>50.1</v>
+        <v>50.5</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -3600,7 +3600,7 @@
         <v>46</v>
       </c>
       <c r="R12" t="n">
-        <v>41.6</v>
+        <v>44.1</v>
       </c>
       <c r="S12" t="n">
         <v>96.59999999999999</v>
@@ -3786,12 +3786,12 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>R To L</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -3856,7 +3856,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>50.1</v>
+        <v>50.5</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -3880,7 +3880,7 @@
         <v>46</v>
       </c>
       <c r="R13" t="n">
-        <v>41.6</v>
+        <v>44.1</v>
       </c>
       <c r="S13" t="n">
         <v>94.90000000000001</v>
@@ -4066,12 +4066,12 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>R To L</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -4087,27 +4087,27 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>606466</t>
+          <t>665487</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ketel Marte</t>
+          <t>Fernando Tatis Jr.</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-07-12T01:10:00Z</t>
+          <t>2026-07-12T00:40:00Z</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Yoshinobu Yamamoto</t>
+          <t>Trey Yesavage</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>808967</t>
+          <t>702056</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -4136,68 +4136,72 @@
         </is>
       </c>
       <c r="L14" t="n">
+        <v>49.9</v>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>Longshot</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Watch List</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>Strong Barrel, Premium Lineup Spot</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
         <v>49.8</v>
       </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>Longshot</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>Watch List</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
-        </is>
-      </c>
-      <c r="P14" t="n">
-        <v>53.4</v>
-      </c>
       <c r="Q14" t="n">
-        <v>26.1</v>
+        <v>31.7</v>
       </c>
       <c r="R14" t="n">
-        <v>38.1</v>
+        <v>44.1</v>
       </c>
       <c r="S14" t="n">
         <v>93.2</v>
       </c>
       <c r="T14" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U14" t="n">
-        <v>8.800000000000001</v>
+        <v>33.7</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr"/>
-      <c r="X14" t="inlineStr"/>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="Y14" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -4217,12 +4221,12 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
@@ -4232,127 +4236,127 @@
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/28, 0 HR</t>
+          <t>Contact streak: 10/29 over last 7 games</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 6.3% barrel, 11.9 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.2% barrel, 4.9 HR allowed</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>11.75</t>
+          <t>10.86</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>45.81</t>
+          <t>52.64</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>91.08</t>
+          <t>92.32</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>102.9323</t>
+          <t>104.4219</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>0.5123</t>
+          <t>0.4453</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>0.2189</t>
+          <t>0.1652</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>0.3753</t>
+          <t>0.3539</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>74.6</t>
+          <t>75.26</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>45.22</t>
+          <t>56.56</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>50.17</t>
+          <t>32.56</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>27.36</t>
+          <t>21.03</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>20.3</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>0.2172</t>
+          <t>0.1227</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>6.33</t>
+          <t>6.23</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>36.97</t>
+          <t>43.44</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>88.09</t>
+          <t>90.22</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>0.3502</t>
+          <t>0.3354</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
-          <t>0.127</t>
+          <t>0.124</t>
         </is>
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>22.45</t>
+          <t>25.39</t>
         </is>
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>In From CF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
         <is>
-          <t>UNIQLO Field at Dodger Stadium</t>
+          <t>Petco Park</t>
         </is>
       </c>
       <c r="BJ14" t="inlineStr"/>
@@ -4363,27 +4367,27 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>665487</t>
+          <t>606466</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Fernando Tatis Jr.</t>
+          <t>Ketel Marte</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-07-12T00:40:00Z</t>
+          <t>2026-07-12T01:10:00Z</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -4398,12 +4402,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Trey Yesavage</t>
+          <t>Yoshinobu Yamamoto</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>702056</t>
+          <t>808967</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -4412,7 +4416,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>49.5</v>
+        <v>49.8</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -4426,58 +4430,54 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>49.8</v>
+        <v>53.4</v>
       </c>
       <c r="Q15" t="n">
-        <v>31.7</v>
+        <v>26.1</v>
       </c>
       <c r="R15" t="n">
-        <v>41.6</v>
+        <v>38.1</v>
       </c>
       <c r="S15" t="n">
         <v>93.2</v>
       </c>
       <c r="T15" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="U15" t="n">
-        <v>33.7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
+      <c r="W15" t="inlineStr"/>
+      <c r="X15" t="inlineStr"/>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr"/>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>not found on RotoWire</t>
+        </is>
+      </c>
       <c r="AC15" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -4497,12 +4497,12 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
@@ -4512,127 +4512,127 @@
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Contact streak: 10/29 over last 7 games</t>
+          <t>Last 7 games: 5/28, 0 HR</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.2% barrel, 4.9 HR allowed</t>
+          <t>switch hitter; pitcher baseline 6.3% barrel, 11.9 HR allowed</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>EV profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>10.86</t>
+          <t>11.75</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>52.64</t>
+          <t>45.81</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>92.32</t>
+          <t>91.08</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>104.4219</t>
+          <t>102.9323</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>0.4453</t>
+          <t>0.5123</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>0.1652</t>
+          <t>0.2189</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>0.3539</t>
+          <t>0.3753</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>75.26</t>
+          <t>74.6</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>56.56</t>
+          <t>45.22</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>32.56</t>
+          <t>50.17</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>21.03</t>
+          <t>27.36</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>11.0</t>
+          <t>20.3</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>0.1227</t>
+          <t>0.2172</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>6.23</t>
+          <t>6.33</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>43.44</t>
+          <t>36.97</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>90.22</t>
+          <t>88.09</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>0.3354</t>
+          <t>0.3502</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
-          <t>0.124</t>
+          <t>0.127</t>
         </is>
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>25.39</t>
+          <t>22.45</t>
         </is>
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>R To L</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>79</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
         <is>
-          <t>Petco Park</t>
+          <t>UNIQLO Field at Dodger Stadium</t>
         </is>
       </c>
       <c r="BJ15" t="inlineStr"/>
@@ -5532,7 +5532,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>46.3</v>
+        <v>46.7</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -5556,7 +5556,7 @@
         <v>46</v>
       </c>
       <c r="R19" t="n">
-        <v>41.6</v>
+        <v>44.1</v>
       </c>
       <c r="S19" t="n">
         <v>76.2</v>
@@ -5742,12 +5742,12 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>R To L</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -5812,7 +5812,7 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>45.4</v>
+        <v>45.8</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
@@ -5836,7 +5836,7 @@
         <v>31.7</v>
       </c>
       <c r="R20" t="n">
-        <v>41.6</v>
+        <v>44.1</v>
       </c>
       <c r="S20" t="n">
         <v>86.40000000000001</v>
@@ -6022,12 +6022,12 @@
       </c>
       <c r="BG20" t="inlineStr">
         <is>
-          <t>R To L</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -6368,7 +6368,7 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>43.1</v>
+        <v>43.5</v>
       </c>
       <c r="M22" t="inlineStr">
         <is>
@@ -6392,7 +6392,7 @@
         <v>31.7</v>
       </c>
       <c r="R22" t="n">
-        <v>41.6</v>
+        <v>44.1</v>
       </c>
       <c r="S22" t="n">
         <v>76.2</v>
@@ -6578,12 +6578,12 @@
       </c>
       <c r="BG22" t="inlineStr">
         <is>
-          <t>R To L</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -6648,7 +6648,7 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>42.3</v>
+        <v>42.7</v>
       </c>
       <c r="M23" t="inlineStr">
         <is>
@@ -6672,7 +6672,7 @@
         <v>46</v>
       </c>
       <c r="R23" t="n">
-        <v>41.6</v>
+        <v>44.1</v>
       </c>
       <c r="S23" t="n">
         <v>100</v>
@@ -6858,12 +6858,12 @@
       </c>
       <c r="BG23" t="inlineStr">
         <is>
-          <t>R To L</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -6928,7 +6928,7 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>41.7</v>
+        <v>42.1</v>
       </c>
       <c r="M24" t="inlineStr">
         <is>
@@ -6952,7 +6952,7 @@
         <v>31.7</v>
       </c>
       <c r="R24" t="n">
-        <v>41.6</v>
+        <v>44.1</v>
       </c>
       <c r="S24" t="n">
         <v>96.59999999999999</v>
@@ -7138,12 +7138,12 @@
       </c>
       <c r="BG24" t="inlineStr">
         <is>
-          <t>R To L</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI24" t="inlineStr">
@@ -7764,7 +7764,7 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>38.6</v>
+        <v>39</v>
       </c>
       <c r="M27" t="inlineStr">
         <is>
@@ -7788,7 +7788,7 @@
         <v>31.7</v>
       </c>
       <c r="R27" t="n">
-        <v>41.6</v>
+        <v>44.1</v>
       </c>
       <c r="S27" t="n">
         <v>64.3</v>
@@ -7974,12 +7974,12 @@
       </c>
       <c r="BG27" t="inlineStr">
         <is>
-          <t>R To L</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI27" t="inlineStr">
@@ -8044,7 +8044,7 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>38.3</v>
+        <v>38.7</v>
       </c>
       <c r="M28" t="inlineStr">
         <is>
@@ -8068,7 +8068,7 @@
         <v>46</v>
       </c>
       <c r="R28" t="n">
-        <v>41.6</v>
+        <v>44.1</v>
       </c>
       <c r="S28" t="n">
         <v>93.2</v>
@@ -8254,12 +8254,12 @@
       </c>
       <c r="BG28" t="inlineStr">
         <is>
-          <t>R To L</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI28" t="inlineStr">
@@ -8324,7 +8324,7 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>38.1</v>
+        <v>38.5</v>
       </c>
       <c r="M29" t="inlineStr">
         <is>
@@ -8348,7 +8348,7 @@
         <v>46</v>
       </c>
       <c r="R29" t="n">
-        <v>41.6</v>
+        <v>44.1</v>
       </c>
       <c r="S29" t="n">
         <v>64.3</v>
@@ -8534,12 +8534,12 @@
       </c>
       <c r="BG29" t="inlineStr">
         <is>
-          <t>R To L</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI29" t="inlineStr">
@@ -8604,7 +8604,7 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>37.9</v>
+        <v>38.3</v>
       </c>
       <c r="M30" t="inlineStr">
         <is>
@@ -8628,7 +8628,7 @@
         <v>31.7</v>
       </c>
       <c r="R30" t="n">
-        <v>41.6</v>
+        <v>44.1</v>
       </c>
       <c r="S30" t="n">
         <v>52.4</v>
@@ -8814,12 +8814,12 @@
       </c>
       <c r="BG30" t="inlineStr">
         <is>
-          <t>R To L</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI30" t="inlineStr">
@@ -9111,27 +9111,27 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>543510</t>
+          <t>665926</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>James McCann</t>
+          <t>Andrés Giménez</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-07-12T01:10:00Z</t>
+          <t>2026-07-12T00:40:00Z</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -9146,12 +9146,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Yoshinobu Yamamoto</t>
+          <t>Walker Buehler</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>808967</t>
+          <t>621111</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -9160,7 +9160,7 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>34.7</v>
+        <v>34.9</v>
       </c>
       <c r="M32" t="inlineStr">
         <is>
@@ -9174,54 +9174,58 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>No major boost</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P32" t="n">
-        <v>29.7</v>
+        <v>7.2</v>
       </c>
       <c r="Q32" t="n">
-        <v>27.3</v>
+        <v>46</v>
       </c>
       <c r="R32" t="n">
-        <v>38.1</v>
+        <v>44.1</v>
       </c>
       <c r="S32" t="n">
         <v>52.4</v>
       </c>
       <c r="T32" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U32" t="n">
-        <v>15.3</v>
+        <v>5.7</v>
       </c>
       <c r="V32" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W32" t="inlineStr"/>
-      <c r="X32" t="inlineStr"/>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="Y32" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB32" t="inlineStr"/>
       <c r="AC32" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9241,12 +9245,12 @@
       </c>
       <c r="AH32" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AJ32" t="inlineStr">
@@ -9256,12 +9260,12 @@
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/18, 0 HR</t>
+          <t>Last 7 games: 3/19, 0 HR</t>
         </is>
       </c>
       <c r="AL32" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.3% barrel, 11.9 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.3% barrel, 14.3 HR allowed</t>
         </is>
       </c>
       <c r="AM32" t="inlineStr">
@@ -9271,112 +9275,112 @@
       </c>
       <c r="AN32" t="inlineStr">
         <is>
-          <t>6.76</t>
+          <t>3.35</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>45.48</t>
+          <t>24.97</t>
         </is>
       </c>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>90.55</t>
+          <t>86.3</t>
         </is>
       </c>
       <c r="AQ32" t="inlineStr">
         <is>
-          <t>100.7366</t>
+          <t>95.9329</t>
         </is>
       </c>
       <c r="AR32" t="inlineStr">
         <is>
-          <t>0.3212</t>
+          <t>0.3295</t>
         </is>
       </c>
       <c r="AS32" t="inlineStr">
         <is>
-          <t>0.1193</t>
+          <t>0.095</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr">
         <is>
-          <t>0.2409</t>
+          <t>0.2786</t>
         </is>
       </c>
       <c r="AU32" t="inlineStr">
         <is>
-          <t>72.47</t>
+          <t>68.39</t>
         </is>
       </c>
       <c r="AV32" t="inlineStr">
         <is>
-          <t>28.05</t>
+          <t>4.79</t>
         </is>
       </c>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>20.21</t>
+          <t>37.61</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>19.73</t>
+          <t>22.53</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>0.0849</t>
+          <t>0.1226</t>
         </is>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
-          <t>6.33</t>
+          <t>9.29</t>
         </is>
       </c>
       <c r="BB32" t="inlineStr">
         <is>
-          <t>36.97</t>
+          <t>40.95</t>
         </is>
       </c>
       <c r="BC32" t="inlineStr">
         <is>
-          <t>88.09</t>
+          <t>89.72</t>
         </is>
       </c>
       <c r="BD32" t="inlineStr">
         <is>
-          <t>0.3502</t>
+          <t>0.4262</t>
         </is>
       </c>
       <c r="BE32" t="inlineStr">
         <is>
-          <t>0.127</t>
+          <t>0.1638</t>
         </is>
       </c>
       <c r="BF32" t="inlineStr">
         <is>
-          <t>22.45</t>
+          <t>22.25</t>
         </is>
       </c>
       <c r="BG32" t="inlineStr">
         <is>
-          <t>In From CF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI32" t="inlineStr">
         <is>
-          <t>UNIQLO Field at Dodger Stadium</t>
+          <t>Petco Park</t>
         </is>
       </c>
       <c r="BJ32" t="inlineStr"/>
@@ -9387,27 +9391,27 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>571448</t>
+          <t>682729</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Nolan Arenado</t>
+          <t>Jonatan Clase</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-07-12T01:10:00Z</t>
+          <t>2026-07-12T00:40:00Z</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -9417,17 +9421,17 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Yoshinobu Yamamoto</t>
+          <t>Walker Buehler</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>808967</t>
+          <t>621111</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -9436,7 +9440,7 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>34.6</v>
+        <v>34.8</v>
       </c>
       <c r="M33" t="inlineStr">
         <is>
@@ -9450,54 +9454,58 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>No major boost</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P33" t="n">
-        <v>18.6</v>
+        <v>7.3</v>
       </c>
       <c r="Q33" t="n">
-        <v>27.3</v>
+        <v>44.5</v>
       </c>
       <c r="R33" t="n">
-        <v>38.1</v>
+        <v>44.1</v>
       </c>
       <c r="S33" t="n">
-        <v>64.3</v>
+        <v>44.8</v>
       </c>
       <c r="T33" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="U33" t="n">
-        <v>53.3</v>
+        <v>41.2</v>
       </c>
       <c r="V33" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W33" t="inlineStr"/>
-      <c r="X33" t="inlineStr"/>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="Y33" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB33" t="inlineStr"/>
       <c r="AC33" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9512,147 +9520,147 @@
       </c>
       <c r="AG33" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 4 games: 3/11, 1 HR</t>
         </is>
       </c>
       <c r="AL33" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.3% barrel, 11.9 HR allowed</t>
+          <t>switch hitter; pitcher baseline 9.3% barrel, 14.3 HR allowed</t>
         </is>
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN33" t="inlineStr">
         <is>
-          <t>5.75</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>32.32</t>
+          <t>19.43</t>
         </is>
       </c>
       <c r="AP33" t="inlineStr">
         <is>
-          <t>85.68</t>
+          <t>85.09</t>
         </is>
       </c>
       <c r="AQ33" t="inlineStr">
         <is>
-          <t>97.0227</t>
+          <t>93.3128</t>
         </is>
       </c>
       <c r="AR33" t="inlineStr">
         <is>
-          <t>0.3555</t>
+          <t>0.2528</t>
         </is>
       </c>
       <c r="AS33" t="inlineStr">
         <is>
-          <t>0.1206</t>
+          <t>0.0876</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr">
         <is>
-          <t>0.2918</t>
+          <t>0.1909</t>
         </is>
       </c>
       <c r="AU33" t="inlineStr">
         <is>
-          <t>71.4</t>
+          <t>69.35</t>
         </is>
       </c>
       <c r="AV33" t="inlineStr">
         <is>
-          <t>16.62</t>
+          <t>10.98</t>
         </is>
       </c>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>42.94</t>
+          <t>64.83</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>28.14</t>
+          <t>37.35</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
-          <t>11.3</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>0.1554</t>
+          <t>0.2174</t>
         </is>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
-          <t>6.33</t>
+          <t>9.29</t>
         </is>
       </c>
       <c r="BB33" t="inlineStr">
         <is>
-          <t>36.97</t>
+          <t>40.95</t>
         </is>
       </c>
       <c r="BC33" t="inlineStr">
         <is>
-          <t>88.09</t>
+          <t>89.72</t>
         </is>
       </c>
       <c r="BD33" t="inlineStr">
         <is>
-          <t>0.3502</t>
+          <t>0.4262</t>
         </is>
       </c>
       <c r="BE33" t="inlineStr">
         <is>
-          <t>0.127</t>
+          <t>0.1638</t>
         </is>
       </c>
       <c r="BF33" t="inlineStr">
         <is>
-          <t>22.45</t>
+          <t>22.25</t>
         </is>
       </c>
       <c r="BG33" t="inlineStr">
         <is>
-          <t>In From CF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI33" t="inlineStr">
         <is>
-          <t>UNIQLO Field at Dodger Stadium</t>
+          <t>Petco Park</t>
         </is>
       </c>
       <c r="BJ33" t="inlineStr"/>
@@ -9663,27 +9671,27 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>665926</t>
+          <t>543510</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Andrés Giménez</t>
+          <t>James McCann</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-07-12T00:40:00Z</t>
+          <t>2026-07-12T01:10:00Z</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -9698,12 +9706,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Walker Buehler</t>
+          <t>Yoshinobu Yamamoto</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>621111</t>
+          <t>808967</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -9712,7 +9720,7 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>34.5</v>
+        <v>34.7</v>
       </c>
       <c r="M34" t="inlineStr">
         <is>
@@ -9726,58 +9734,54 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P34" t="n">
-        <v>7.2</v>
+        <v>29.7</v>
       </c>
       <c r="Q34" t="n">
-        <v>46</v>
+        <v>27.3</v>
       </c>
       <c r="R34" t="n">
-        <v>41.6</v>
+        <v>38.1</v>
       </c>
       <c r="S34" t="n">
         <v>52.4</v>
       </c>
       <c r="T34" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U34" t="n">
-        <v>5.7</v>
+        <v>15.3</v>
       </c>
       <c r="V34" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W34" t="inlineStr">
+      <c r="W34" t="inlineStr"/>
+      <c r="X34" t="inlineStr"/>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X34" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y34" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB34" t="inlineStr"/>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>not found on RotoWire</t>
+        </is>
+      </c>
       <c r="AC34" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9797,12 +9801,12 @@
       </c>
       <c r="AH34" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AJ34" t="inlineStr">
@@ -9812,12 +9816,12 @@
       </c>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/19, 0 HR</t>
+          <t>Last 7 games: 4/18, 0 HR</t>
         </is>
       </c>
       <c r="AL34" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 9.3% barrel, 14.3 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.3% barrel, 11.9 HR allowed</t>
         </is>
       </c>
       <c r="AM34" t="inlineStr">
@@ -9827,112 +9831,112 @@
       </c>
       <c r="AN34" t="inlineStr">
         <is>
-          <t>3.35</t>
+          <t>6.76</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>24.97</t>
+          <t>45.48</t>
         </is>
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>86.3</t>
+          <t>90.55</t>
         </is>
       </c>
       <c r="AQ34" t="inlineStr">
         <is>
-          <t>95.9329</t>
+          <t>100.7366</t>
         </is>
       </c>
       <c r="AR34" t="inlineStr">
         <is>
-          <t>0.3295</t>
+          <t>0.3212</t>
         </is>
       </c>
       <c r="AS34" t="inlineStr">
         <is>
-          <t>0.095</t>
+          <t>0.1193</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr">
         <is>
-          <t>0.2786</t>
+          <t>0.2409</t>
         </is>
       </c>
       <c r="AU34" t="inlineStr">
         <is>
-          <t>68.39</t>
+          <t>72.47</t>
         </is>
       </c>
       <c r="AV34" t="inlineStr">
         <is>
-          <t>4.79</t>
+          <t>28.05</t>
         </is>
       </c>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>37.61</t>
+          <t>20.21</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>22.53</t>
+          <t>19.73</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>0.1226</t>
+          <t>0.0849</t>
         </is>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
-          <t>9.29</t>
+          <t>6.33</t>
         </is>
       </c>
       <c r="BB34" t="inlineStr">
         <is>
-          <t>40.95</t>
+          <t>36.97</t>
         </is>
       </c>
       <c r="BC34" t="inlineStr">
         <is>
-          <t>89.72</t>
+          <t>88.09</t>
         </is>
       </c>
       <c r="BD34" t="inlineStr">
         <is>
-          <t>0.4262</t>
+          <t>0.3502</t>
         </is>
       </c>
       <c r="BE34" t="inlineStr">
         <is>
-          <t>0.1638</t>
+          <t>0.127</t>
         </is>
       </c>
       <c r="BF34" t="inlineStr">
         <is>
-          <t>22.25</t>
+          <t>22.45</t>
         </is>
       </c>
       <c r="BG34" t="inlineStr">
         <is>
-          <t>R To L</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>79</t>
         </is>
       </c>
       <c r="BI34" t="inlineStr">
         <is>
-          <t>Petco Park</t>
+          <t>UNIQLO Field at Dodger Stadium</t>
         </is>
       </c>
       <c r="BJ34" t="inlineStr"/>
@@ -9943,27 +9947,27 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>682729</t>
+          <t>571448</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Jonatan Clase</t>
+          <t>Nolan Arenado</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-07-12T00:40:00Z</t>
+          <t>2026-07-12T01:10:00Z</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -9973,17 +9977,17 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Walker Buehler</t>
+          <t>Yoshinobu Yamamoto</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>621111</t>
+          <t>808967</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -9992,7 +9996,7 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>34.4</v>
+        <v>34.6</v>
       </c>
       <c r="M35" t="inlineStr">
         <is>
@@ -10006,58 +10010,54 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P35" t="n">
-        <v>7.3</v>
+        <v>18.6</v>
       </c>
       <c r="Q35" t="n">
-        <v>44.5</v>
+        <v>27.3</v>
       </c>
       <c r="R35" t="n">
-        <v>41.6</v>
+        <v>38.1</v>
       </c>
       <c r="S35" t="n">
-        <v>44.8</v>
+        <v>64.3</v>
       </c>
       <c r="T35" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U35" t="n">
-        <v>41.2</v>
+        <v>53.3</v>
       </c>
       <c r="V35" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W35" t="inlineStr">
+      <c r="W35" t="inlineStr"/>
+      <c r="X35" t="inlineStr"/>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y35" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB35" t="inlineStr"/>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>not found on RotoWire</t>
+        </is>
+      </c>
       <c r="AC35" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -10072,147 +10072,147 @@
       </c>
       <c r="AG35" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI35" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
         <is>
-          <t>Last 4 games: 3/11, 1 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL35" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 9.3% barrel, 14.3 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.3% barrel, 11.9 HR allowed</t>
         </is>
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN35" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>5.75</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>19.43</t>
+          <t>32.32</t>
         </is>
       </c>
       <c r="AP35" t="inlineStr">
         <is>
-          <t>85.09</t>
+          <t>85.68</t>
         </is>
       </c>
       <c r="AQ35" t="inlineStr">
         <is>
-          <t>93.3128</t>
+          <t>97.0227</t>
         </is>
       </c>
       <c r="AR35" t="inlineStr">
         <is>
-          <t>0.2528</t>
+          <t>0.3555</t>
         </is>
       </c>
       <c r="AS35" t="inlineStr">
         <is>
-          <t>0.0876</t>
+          <t>0.1206</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr">
         <is>
-          <t>0.1909</t>
+          <t>0.2918</t>
         </is>
       </c>
       <c r="AU35" t="inlineStr">
         <is>
-          <t>69.35</t>
+          <t>71.4</t>
         </is>
       </c>
       <c r="AV35" t="inlineStr">
         <is>
-          <t>10.98</t>
+          <t>16.62</t>
         </is>
       </c>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>64.83</t>
+          <t>42.94</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>37.35</t>
+          <t>28.14</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>11.3</t>
         </is>
       </c>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>0.2174</t>
+          <t>0.1554</t>
         </is>
       </c>
       <c r="BA35" t="inlineStr">
         <is>
-          <t>9.29</t>
+          <t>6.33</t>
         </is>
       </c>
       <c r="BB35" t="inlineStr">
         <is>
-          <t>40.95</t>
+          <t>36.97</t>
         </is>
       </c>
       <c r="BC35" t="inlineStr">
         <is>
-          <t>89.72</t>
+          <t>88.09</t>
         </is>
       </c>
       <c r="BD35" t="inlineStr">
         <is>
-          <t>0.4262</t>
+          <t>0.3502</t>
         </is>
       </c>
       <c r="BE35" t="inlineStr">
         <is>
-          <t>0.1638</t>
+          <t>0.127</t>
         </is>
       </c>
       <c r="BF35" t="inlineStr">
         <is>
-          <t>22.25</t>
+          <t>22.45</t>
         </is>
       </c>
       <c r="BG35" t="inlineStr">
         <is>
-          <t>R To L</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>79</t>
         </is>
       </c>
       <c r="BI35" t="inlineStr">
         <is>
-          <t>Petco Park</t>
+          <t>UNIQLO Field at Dodger Stadium</t>
         </is>
       </c>
       <c r="BJ35" t="inlineStr"/>
@@ -10548,7 +10548,7 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>32</v>
+        <v>32.4</v>
       </c>
       <c r="M37" t="inlineStr">
         <is>
@@ -10572,7 +10572,7 @@
         <v>31.7</v>
       </c>
       <c r="R37" t="n">
-        <v>41.6</v>
+        <v>44.1</v>
       </c>
       <c r="S37" t="n">
         <v>44.8</v>
@@ -10758,12 +10758,12 @@
       </c>
       <c r="BG37" t="inlineStr">
         <is>
-          <t>R To L</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI37" t="inlineStr">
@@ -11665,27 +11665,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>518692</t>
+          <t>672960</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Freddie Freeman</t>
+          <t>Kazuma Okamoto</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-07-12T01:10:00Z</t>
+          <t>2026-07-12T00:40:00Z</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -11695,17 +11695,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Brandon Pfaadt</t>
+          <t>Walker Buehler</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>694297</t>
+          <t>621111</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -11728,26 +11728,26 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>47.6</v>
+        <v>58</v>
       </c>
       <c r="Q4" t="n">
-        <v>52.5</v>
+        <v>46</v>
       </c>
       <c r="R4" t="n">
-        <v>38.1</v>
+        <v>44.1</v>
       </c>
       <c r="S4" t="n">
-        <v>96.59999999999999</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T4" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U4" t="n">
-        <v>43.2</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="V4" t="inlineStr">
         <is>
@@ -11761,7 +11761,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -11782,7 +11782,7 @@
       <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr"/>
@@ -11799,7 +11799,7 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
@@ -11809,17 +11809,17 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Last 7 games: 8/28, 1 HR</t>
+          <t>Hot streak: 3 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 10.8% barrel, 13.4 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 9.3% barrel, 14.3 HR allowed</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
@@ -11829,112 +11829,112 @@
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>10.68</t>
+          <t>14.7</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>45.28</t>
+          <t>47.7</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>90.62</t>
+          <t>91.4</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>100.8959</t>
+          <t>102.5213</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.4943</t>
+          <t>0.451</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>0.2091</t>
+          <t>0.229</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>0.3745</t>
+          <t>0.329</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>70.32</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>8.89</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>36.54</t>
+          <t>51.4</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>29.03</t>
+          <t>31.7</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>0.2028</t>
+          <t>0.232</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>10.76</t>
+          <t>9.29</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>41.46</t>
+          <t>40.95</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>89.82</t>
+          <t>89.72</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>0.4457</t>
+          <t>0.4262</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>0.1925</t>
+          <t>0.1638</t>
         </is>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>21.24</t>
+          <t>22.25</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>In From CF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>UNIQLO Field at Dodger Stadium</t>
+          <t>Petco Park</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr"/>
@@ -11945,27 +11945,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>672960</t>
+          <t>518692</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Kazuma Okamoto</t>
+          <t>Freddie Freeman</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-07-12T00:40:00Z</t>
+          <t>2026-07-12T01:10:00Z</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -11975,17 +11975,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Walker Buehler</t>
+          <t>Brandon Pfaadt</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>621111</t>
+          <t>694297</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -11994,7 +11994,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>56.5</v>
+        <v>56.9</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -12008,26 +12008,26 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Strong Barrel</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>58</v>
+        <v>47.6</v>
       </c>
       <c r="Q5" t="n">
-        <v>46</v>
+        <v>52.5</v>
       </c>
       <c r="R5" t="n">
-        <v>41.6</v>
+        <v>38.1</v>
       </c>
       <c r="S5" t="n">
-        <v>86.40000000000001</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T5" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U5" t="n">
-        <v>69.09999999999999</v>
+        <v>43.2</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
@@ -12041,7 +12041,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -12062,7 +12062,7 @@
       <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr"/>
@@ -12079,7 +12079,7 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
@@ -12089,17 +12089,17 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Hot streak: 3 HR in last 7 games</t>
+          <t>Last 7 games: 8/28, 1 HR</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 9.3% barrel, 14.3 HR allowed</t>
+          <t>platoon edge; pitcher baseline 10.8% barrel, 13.4 HR allowed</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
@@ -12109,112 +12109,112 @@
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>14.7</t>
+          <t>10.68</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>47.7</t>
+          <t>45.28</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>91.4</t>
+          <t>90.62</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>102.5213</t>
+          <t>100.8959</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.451</t>
+          <t>0.4943</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>0.229</t>
+          <t>0.2091</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>0.329</t>
+          <t>0.3745</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>70.32</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>8.89</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>51.4</t>
+          <t>36.54</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>31.7</t>
+          <t>29.03</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>17.7</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>0.232</t>
+          <t>0.2028</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>9.29</t>
+          <t>10.76</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>40.95</t>
+          <t>41.46</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>89.72</t>
+          <t>89.82</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>0.4262</t>
+          <t>0.4457</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>0.1638</t>
+          <t>0.1925</t>
         </is>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>22.25</t>
+          <t>21.24</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>R To L</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>79</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>Petco Park</t>
+          <t>UNIQLO Field at Dodger Stadium</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr"/>
@@ -12781,27 +12781,27 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>682998</t>
+          <t>592518</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Corbin Carroll</t>
+          <t>Manny Machado</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-07-12T01:10:00Z</t>
+          <t>2026-07-12T00:40:00Z</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -12811,17 +12811,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Yoshinobu Yamamoto</t>
+          <t>Trey Yesavage</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>808967</t>
+          <t>702056</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -12830,7 +12830,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>51</v>
+        <v>51.2</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -12844,54 +12844,58 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>54.5</v>
+        <v>49.3</v>
       </c>
       <c r="Q8" t="n">
-        <v>27.3</v>
+        <v>31.7</v>
       </c>
       <c r="R8" t="n">
-        <v>38.1</v>
+        <v>44.1</v>
       </c>
       <c r="S8" t="n">
-        <v>96.59999999999999</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T8" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U8" t="n">
-        <v>0.8</v>
+        <v>57.8</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr"/>
-      <c r="X8" t="inlineStr"/>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="Y8" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -12911,27 +12915,27 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/24, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.3% barrel, 11.9 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.2% barrel, 4.9 HR allowed</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
@@ -12941,112 +12945,112 @@
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>12.26</t>
+          <t>11.43</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>47.45</t>
+          <t>45.83</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>91.54</t>
+          <t>90.94</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>102.4703</t>
+          <t>101.8062</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>0.4695</t>
+          <t>0.4397</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>0.2138</t>
+          <t>0.1981</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>0.3538</t>
+          <t>0.3298</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>75.33</t>
+          <t>74.64</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>55.82</t>
+          <t>44.4</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>46.18</t>
+          <t>39.94</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>28.57</t>
+          <t>28.29</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>18.4</t>
+          <t>21.4</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>0.247</t>
+          <t>0.2102</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>6.33</t>
+          <t>6.23</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>36.97</t>
+          <t>43.44</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>88.09</t>
+          <t>90.22</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>0.3502</t>
+          <t>0.3354</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
-          <t>0.127</t>
+          <t>0.124</t>
         </is>
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>22.45</t>
+          <t>25.39</t>
         </is>
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>In From CF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>UNIQLO Field at Dodger Stadium</t>
+          <t>Petco Park</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr"/>
@@ -13057,27 +13061,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>592518</t>
+          <t>682998</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Manny Machado</t>
+          <t>Corbin Carroll</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-07-12T00:40:00Z</t>
+          <t>2026-07-12T01:10:00Z</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -13087,17 +13091,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Trey Yesavage</t>
+          <t>Yoshinobu Yamamoto</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>702056</t>
+          <t>808967</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -13106,7 +13110,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>50.8</v>
+        <v>51</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -13120,58 +13124,54 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>49.3</v>
+        <v>54.5</v>
       </c>
       <c r="Q9" t="n">
-        <v>31.7</v>
+        <v>27.3</v>
       </c>
       <c r="R9" t="n">
-        <v>41.6</v>
+        <v>38.1</v>
       </c>
       <c r="S9" t="n">
-        <v>94.90000000000001</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T9" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U9" t="n">
-        <v>57.8</v>
+        <v>0.8</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr"/>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>not found on RotoWire</t>
+        </is>
+      </c>
       <c r="AC9" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -13191,27 +13191,27 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 3/24, 0 HR</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.2% barrel, 4.9 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.3% barrel, 11.9 HR allowed</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
@@ -13221,112 +13221,112 @@
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>11.43</t>
+          <t>12.26</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>45.83</t>
+          <t>47.45</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>90.94</t>
+          <t>91.54</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>101.8062</t>
+          <t>102.4703</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>0.4397</t>
+          <t>0.4695</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>0.1981</t>
+          <t>0.2138</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>0.3298</t>
+          <t>0.3538</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>74.64</t>
+          <t>75.33</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>44.4</t>
+          <t>55.82</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>39.94</t>
+          <t>46.18</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>28.29</t>
+          <t>28.57</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>21.4</t>
+          <t>18.4</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>0.2102</t>
+          <t>0.247</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>6.23</t>
+          <t>6.33</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>43.44</t>
+          <t>36.97</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>90.22</t>
+          <t>88.09</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>0.3354</t>
+          <t>0.3502</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
-          <t>0.124</t>
+          <t>0.127</t>
         </is>
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>25.39</t>
+          <t>22.45</t>
         </is>
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>R To L</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>79</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>Petco Park</t>
+          <t>UNIQLO Field at Dodger Stadium</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr"/>
@@ -13337,27 +13337,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>687221</t>
+          <t>701538</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Dalton Rushing</t>
+          <t>Jackson Merrill</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-07-12T01:10:00Z</t>
+          <t>2026-07-12T00:40:00Z</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -13367,17 +13367,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Brandon Pfaadt</t>
+          <t>Trey Yesavage</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>694297</t>
+          <t>702056</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -13386,7 +13386,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>50.6</v>
+        <v>50.7</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -13400,26 +13400,26 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Strong Barrel, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>45.3</v>
+        <v>43.3</v>
       </c>
       <c r="Q10" t="n">
-        <v>52.5</v>
+        <v>31.7</v>
       </c>
       <c r="R10" t="n">
-        <v>38.1</v>
+        <v>44.1</v>
       </c>
       <c r="S10" t="n">
-        <v>52.4</v>
+        <v>100</v>
       </c>
       <c r="T10" t="n">
         <v>80</v>
       </c>
       <c r="U10" t="n">
-        <v>54.9</v>
+        <v>19.5</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
@@ -13433,7 +13433,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -13471,27 +13471,27 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Contact streak: 8/22 over last 7 games</t>
+          <t>Last 7 games: 7/28, 0 HR</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 10.8% barrel, 13.4 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.2% barrel, 4.9 HR allowed</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
@@ -13501,112 +13501,112 @@
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>12.46</t>
+          <t>10.41</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>44.46</t>
+          <t>44.09</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>89.82</t>
+          <t>89.56</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>101.812</t>
+          <t>100.25</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>0.4147</t>
+          <t>0.4326</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>0.1774</t>
+          <t>0.1864</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>0.3222</t>
+          <t>0.3162</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>72.61</t>
+          <t>73.05</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>18.03</t>
+          <t>28.02</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>48.24</t>
+          <t>38.26</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>27.62</t>
+          <t>27.89</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>11.8</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>0.1935</t>
+          <t>0.151</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>10.76</t>
+          <t>6.23</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>41.46</t>
+          <t>43.44</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>89.82</t>
+          <t>90.22</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>0.4457</t>
+          <t>0.3354</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
-          <t>0.1925</t>
+          <t>0.124</t>
         </is>
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>21.24</t>
+          <t>25.39</t>
         </is>
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>In From CF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>UNIQLO Field at Dodger Stadium</t>
+          <t>Petco Park</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr"/>
@@ -13617,27 +13617,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>701538</t>
+          <t>687221</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Jackson Merrill</t>
+          <t>Dalton Rushing</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-07-12T00:40:00Z</t>
+          <t>2026-07-12T01:10:00Z</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -13647,17 +13647,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Trey Yesavage</t>
+          <t>Brandon Pfaadt</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>702056</t>
+          <t>694297</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -13666,7 +13666,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>50.3</v>
+        <v>50.6</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -13680,26 +13680,26 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>43.3</v>
+        <v>45.3</v>
       </c>
       <c r="Q11" t="n">
-        <v>31.7</v>
+        <v>52.5</v>
       </c>
       <c r="R11" t="n">
-        <v>41.6</v>
+        <v>38.1</v>
       </c>
       <c r="S11" t="n">
-        <v>100</v>
+        <v>52.4</v>
       </c>
       <c r="T11" t="n">
         <v>80</v>
       </c>
       <c r="U11" t="n">
-        <v>19.5</v>
+        <v>54.9</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
@@ -13713,7 +13713,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -13751,27 +13751,27 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/28, 0 HR</t>
+          <t>Contact streak: 8/22 over last 7 games</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.2% barrel, 4.9 HR allowed</t>
+          <t>platoon edge; pitcher baseline 10.8% barrel, 13.4 HR allowed</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
@@ -13781,112 +13781,112 @@
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>10.41</t>
+          <t>12.46</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>44.09</t>
+          <t>44.46</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>89.56</t>
+          <t>89.82</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>100.25</t>
+          <t>101.812</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>0.4326</t>
+          <t>0.4147</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>0.1864</t>
+          <t>0.1774</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>0.3162</t>
+          <t>0.3222</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>73.05</t>
+          <t>72.61</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>28.02</t>
+          <t>18.03</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>38.26</t>
+          <t>48.24</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>27.89</t>
+          <t>27.62</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>11.8</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>0.151</t>
+          <t>0.1935</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>6.23</t>
+          <t>10.76</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>43.44</t>
+          <t>41.46</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>90.22</t>
+          <t>89.82</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>0.3354</t>
+          <t>0.4457</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
-          <t>0.124</t>
+          <t>0.1925</t>
         </is>
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>25.39</t>
+          <t>21.24</t>
         </is>
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>R To L</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>79</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>Petco Park</t>
+          <t>UNIQLO Field at Dodger Stadium</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr"/>
@@ -13946,7 +13946,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>50.1</v>
+        <v>50.5</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -13970,7 +13970,7 @@
         <v>46</v>
       </c>
       <c r="R12" t="n">
-        <v>41.6</v>
+        <v>44.1</v>
       </c>
       <c r="S12" t="n">
         <v>96.59999999999999</v>
@@ -14156,12 +14156,12 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>R To L</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -14226,7 +14226,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>50.1</v>
+        <v>50.5</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -14250,7 +14250,7 @@
         <v>46</v>
       </c>
       <c r="R13" t="n">
-        <v>41.6</v>
+        <v>44.1</v>
       </c>
       <c r="S13" t="n">
         <v>94.90000000000001</v>
@@ -14436,12 +14436,12 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>R To L</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -14457,27 +14457,27 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>606466</t>
+          <t>665487</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ketel Marte</t>
+          <t>Fernando Tatis Jr.</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-07-12T01:10:00Z</t>
+          <t>2026-07-12T00:40:00Z</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -14492,12 +14492,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Yoshinobu Yamamoto</t>
+          <t>Trey Yesavage</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>808967</t>
+          <t>702056</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -14506,68 +14506,72 @@
         </is>
       </c>
       <c r="L14" t="n">
+        <v>49.9</v>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>Longshot</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Watch List</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>Strong Barrel, Premium Lineup Spot</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
         <v>49.8</v>
       </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>Longshot</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>Watch List</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
-        </is>
-      </c>
-      <c r="P14" t="n">
-        <v>53.4</v>
-      </c>
       <c r="Q14" t="n">
-        <v>26.1</v>
+        <v>31.7</v>
       </c>
       <c r="R14" t="n">
-        <v>38.1</v>
+        <v>44.1</v>
       </c>
       <c r="S14" t="n">
         <v>93.2</v>
       </c>
       <c r="T14" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U14" t="n">
-        <v>8.800000000000001</v>
+        <v>33.7</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr"/>
-      <c r="X14" t="inlineStr"/>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="Y14" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -14587,12 +14591,12 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
@@ -14602,127 +14606,127 @@
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/28, 0 HR</t>
+          <t>Contact streak: 10/29 over last 7 games</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 6.3% barrel, 11.9 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.2% barrel, 4.9 HR allowed</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>11.75</t>
+          <t>10.86</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>45.81</t>
+          <t>52.64</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>91.08</t>
+          <t>92.32</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>102.9323</t>
+          <t>104.4219</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>0.5123</t>
+          <t>0.4453</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>0.2189</t>
+          <t>0.1652</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>0.3753</t>
+          <t>0.3539</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>74.6</t>
+          <t>75.26</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>45.22</t>
+          <t>56.56</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>50.17</t>
+          <t>32.56</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>27.36</t>
+          <t>21.03</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>20.3</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>0.2172</t>
+          <t>0.1227</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>6.33</t>
+          <t>6.23</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>36.97</t>
+          <t>43.44</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>88.09</t>
+          <t>90.22</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>0.3502</t>
+          <t>0.3354</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
-          <t>0.127</t>
+          <t>0.124</t>
         </is>
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>22.45</t>
+          <t>25.39</t>
         </is>
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>In From CF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
         <is>
-          <t>UNIQLO Field at Dodger Stadium</t>
+          <t>Petco Park</t>
         </is>
       </c>
       <c r="BJ14" t="inlineStr"/>
@@ -14733,27 +14737,27 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>665487</t>
+          <t>606466</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Fernando Tatis Jr.</t>
+          <t>Ketel Marte</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-07-12T00:40:00Z</t>
+          <t>2026-07-12T01:10:00Z</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -14768,12 +14772,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Trey Yesavage</t>
+          <t>Yoshinobu Yamamoto</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>702056</t>
+          <t>808967</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -14782,7 +14786,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>49.5</v>
+        <v>49.8</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -14796,58 +14800,54 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>49.8</v>
+        <v>53.4</v>
       </c>
       <c r="Q15" t="n">
-        <v>31.7</v>
+        <v>26.1</v>
       </c>
       <c r="R15" t="n">
-        <v>41.6</v>
+        <v>38.1</v>
       </c>
       <c r="S15" t="n">
         <v>93.2</v>
       </c>
       <c r="T15" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="U15" t="n">
-        <v>33.7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
+      <c r="W15" t="inlineStr"/>
+      <c r="X15" t="inlineStr"/>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr"/>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>not found on RotoWire</t>
+        </is>
+      </c>
       <c r="AC15" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -14867,12 +14867,12 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
@@ -14882,127 +14882,127 @@
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Contact streak: 10/29 over last 7 games</t>
+          <t>Last 7 games: 5/28, 0 HR</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.2% barrel, 4.9 HR allowed</t>
+          <t>switch hitter; pitcher baseline 6.3% barrel, 11.9 HR allowed</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>EV profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>10.86</t>
+          <t>11.75</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>52.64</t>
+          <t>45.81</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>92.32</t>
+          <t>91.08</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>104.4219</t>
+          <t>102.9323</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>0.4453</t>
+          <t>0.5123</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>0.1652</t>
+          <t>0.2189</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>0.3539</t>
+          <t>0.3753</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>75.26</t>
+          <t>74.6</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>56.56</t>
+          <t>45.22</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>32.56</t>
+          <t>50.17</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>21.03</t>
+          <t>27.36</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>11.0</t>
+          <t>20.3</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>0.1227</t>
+          <t>0.2172</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>6.23</t>
+          <t>6.33</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>43.44</t>
+          <t>36.97</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>90.22</t>
+          <t>88.09</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>0.3354</t>
+          <t>0.3502</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
-          <t>0.124</t>
+          <t>0.127</t>
         </is>
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>25.39</t>
+          <t>22.45</t>
         </is>
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>R To L</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>79</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
         <is>
-          <t>Petco Park</t>
+          <t>UNIQLO Field at Dodger Stadium</t>
         </is>
       </c>
       <c r="BJ15" t="inlineStr"/>
@@ -15902,7 +15902,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>46.3</v>
+        <v>46.7</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -15926,7 +15926,7 @@
         <v>46</v>
       </c>
       <c r="R19" t="n">
-        <v>41.6</v>
+        <v>44.1</v>
       </c>
       <c r="S19" t="n">
         <v>76.2</v>
@@ -16112,12 +16112,12 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>R To L</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -16182,7 +16182,7 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>45.4</v>
+        <v>45.8</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
@@ -16206,7 +16206,7 @@
         <v>31.7</v>
       </c>
       <c r="R20" t="n">
-        <v>41.6</v>
+        <v>44.1</v>
       </c>
       <c r="S20" t="n">
         <v>86.40000000000001</v>
@@ -16392,12 +16392,12 @@
       </c>
       <c r="BG20" t="inlineStr">
         <is>
-          <t>R To L</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">

--- a/outputs/hr_rankings.xlsx
+++ b/outputs/hr_rankings.xlsx
@@ -784,7 +784,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>68.09999999999999</v>
+        <v>69</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Elite Power, Strong Barrel, Premium Lineup Spot</t>
+          <t>Elite Power, Strong Barrel, Good Environment, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -808,7 +808,7 @@
         <v>35.9</v>
       </c>
       <c r="R2" t="n">
-        <v>67.3</v>
+        <v>73.3</v>
       </c>
       <c r="S2" t="n">
         <v>100</v>
@@ -994,12 +994,12 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>88</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1064,7 +1064,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>66.59999999999999</v>
+        <v>67.5</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -1078,7 +1078,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Strong Barrel, Good Environment, Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -1088,7 +1088,7 @@
         <v>35.9</v>
       </c>
       <c r="R3" t="n">
-        <v>67.3</v>
+        <v>73.3</v>
       </c>
       <c r="S3" t="n">
         <v>93.2</v>
@@ -1274,12 +1274,12 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>88</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1344,7 +1344,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>64.5</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -1358,7 +1358,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Elite Power, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Elite Power, Strong Barrel, Good Environment, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P4" t="n">
@@ -1368,7 +1368,7 @@
         <v>18.2</v>
       </c>
       <c r="R4" t="n">
-        <v>67.3</v>
+        <v>73.3</v>
       </c>
       <c r="S4" t="n">
         <v>93.2</v>
@@ -1554,12 +1554,12 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>88</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -1624,7 +1624,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>63.2</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1638,7 +1638,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Good Environment, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P5" t="n">
@@ -1648,7 +1648,7 @@
         <v>18.2</v>
       </c>
       <c r="R5" t="n">
-        <v>67.3</v>
+        <v>73.3</v>
       </c>
       <c r="S5" t="n">
         <v>100</v>
@@ -1834,12 +1834,12 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>88</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -1904,7 +1904,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>62.4</v>
+        <v>63.3</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -1918,7 +1918,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Good Environment, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P6" t="n">
@@ -1928,7 +1928,7 @@
         <v>35.9</v>
       </c>
       <c r="R6" t="n">
-        <v>67.3</v>
+        <v>73.3</v>
       </c>
       <c r="S6" t="n">
         <v>94.90000000000001</v>
@@ -2114,12 +2114,12 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>88</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2184,11 +2184,11 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>59.4</v>
+        <v>60.3</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Longshot</t>
+          <t>Tier 3</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -2198,7 +2198,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Good Environment, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P7" t="n">
@@ -2208,7 +2208,7 @@
         <v>35.9</v>
       </c>
       <c r="R7" t="n">
-        <v>67.3</v>
+        <v>73.3</v>
       </c>
       <c r="S7" t="n">
         <v>96.59999999999999</v>
@@ -2394,12 +2394,12 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>88</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -2464,7 +2464,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>59</v>
+        <v>59.9</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -2478,7 +2478,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Strong Barrel, Platoon Edge</t>
+          <t>Strong Barrel, Good Environment, Platoon Edge</t>
         </is>
       </c>
       <c r="P8" t="n">
@@ -2488,7 +2488,7 @@
         <v>35.9</v>
       </c>
       <c r="R8" t="n">
-        <v>67.3</v>
+        <v>73.3</v>
       </c>
       <c r="S8" t="n">
         <v>86.40000000000001</v>
@@ -2674,12 +2674,12 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>88</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -2744,7 +2744,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>58.6</v>
+        <v>59.5</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -2758,7 +2758,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Strong Barrel, Hot Hitter/Streak</t>
+          <t>Strong Barrel, Good Environment, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P9" t="n">
@@ -2768,7 +2768,7 @@
         <v>35.9</v>
       </c>
       <c r="R9" t="n">
-        <v>67.3</v>
+        <v>73.3</v>
       </c>
       <c r="S9" t="n">
         <v>64.3</v>
@@ -2954,12 +2954,12 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>88</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -3024,7 +3024,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>52.8</v>
+        <v>53.7</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -3038,7 +3038,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Strong Barrel</t>
+          <t>Strong Barrel, Good Environment</t>
         </is>
       </c>
       <c r="P10" t="n">
@@ -3048,7 +3048,7 @@
         <v>35.9</v>
       </c>
       <c r="R10" t="n">
-        <v>67.3</v>
+        <v>73.3</v>
       </c>
       <c r="S10" t="n">
         <v>52.4</v>
@@ -3234,12 +3234,12 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>88</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -3304,7 +3304,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>52.5</v>
+        <v>53.4</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -3318,7 +3318,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Strong Barrel, Platoon Edge</t>
+          <t>Strong Barrel, Good Environment, Platoon Edge</t>
         </is>
       </c>
       <c r="P11" t="n">
@@ -3328,7 +3328,7 @@
         <v>18.2</v>
       </c>
       <c r="R11" t="n">
-        <v>67.3</v>
+        <v>73.3</v>
       </c>
       <c r="S11" t="n">
         <v>86.40000000000001</v>
@@ -3514,12 +3514,12 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>88</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -3584,7 +3584,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>51.5</v>
+        <v>52.4</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Good Environment, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P12" t="n">
@@ -3608,7 +3608,7 @@
         <v>18.2</v>
       </c>
       <c r="R12" t="n">
-        <v>67.3</v>
+        <v>73.3</v>
       </c>
       <c r="S12" t="n">
         <v>96.59999999999999</v>
@@ -3794,12 +3794,12 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>88</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -3864,7 +3864,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>51.4</v>
+        <v>52.3</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -3878,7 +3878,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Good Environment, Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P13" t="n">
@@ -3888,7 +3888,7 @@
         <v>18.2</v>
       </c>
       <c r="R13" t="n">
-        <v>67.3</v>
+        <v>73.3</v>
       </c>
       <c r="S13" t="n">
         <v>94.90000000000001</v>
@@ -4074,12 +4074,12 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>88</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -4144,7 +4144,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>48.8</v>
+        <v>49.7</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -4158,7 +4158,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Strong Barrel, Platoon Edge</t>
+          <t>Strong Barrel, Good Environment, Platoon Edge</t>
         </is>
       </c>
       <c r="P14" t="n">
@@ -4168,7 +4168,7 @@
         <v>18.2</v>
       </c>
       <c r="R14" t="n">
-        <v>67.3</v>
+        <v>73.3</v>
       </c>
       <c r="S14" t="n">
         <v>44.8</v>
@@ -4354,12 +4354,12 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>88</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -4424,7 +4424,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>45.2</v>
+        <v>46.1</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -4438,7 +4438,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>No major boost</t>
+          <t>Good Environment</t>
         </is>
       </c>
       <c r="P15" t="n">
@@ -4448,7 +4448,7 @@
         <v>35.9</v>
       </c>
       <c r="R15" t="n">
-        <v>67.3</v>
+        <v>73.3</v>
       </c>
       <c r="S15" t="n">
         <v>76.2</v>
@@ -4634,12 +4634,12 @@
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>88</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -4704,7 +4704,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>44.5</v>
+        <v>45.4</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -4718,7 +4718,7 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Good Environment, Platoon Edge</t>
         </is>
       </c>
       <c r="P16" t="n">
@@ -4728,7 +4728,7 @@
         <v>18.2</v>
       </c>
       <c r="R16" t="n">
-        <v>67.3</v>
+        <v>73.3</v>
       </c>
       <c r="S16" t="n">
         <v>64.3</v>
@@ -4914,12 +4914,12 @@
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>88</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -4984,7 +4984,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>41.3</v>
+        <v>42.2</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -4998,7 +4998,7 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>No major boost</t>
+          <t>Good Environment</t>
         </is>
       </c>
       <c r="P17" t="n">
@@ -5008,7 +5008,7 @@
         <v>18.2</v>
       </c>
       <c r="R17" t="n">
-        <v>67.3</v>
+        <v>73.3</v>
       </c>
       <c r="S17" t="n">
         <v>52.4</v>
@@ -5194,12 +5194,12 @@
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>88</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -5264,7 +5264,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>37.9</v>
+        <v>38.8</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -5278,7 +5278,7 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Good Environment, Platoon Edge</t>
         </is>
       </c>
       <c r="P18" t="n">
@@ -5288,7 +5288,7 @@
         <v>17.2</v>
       </c>
       <c r="R18" t="n">
-        <v>67.3</v>
+        <v>73.3</v>
       </c>
       <c r="S18" t="n">
         <v>76.2</v>
@@ -5474,12 +5474,12 @@
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>88</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -5544,7 +5544,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>36.7</v>
+        <v>37.6</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -5558,7 +5558,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Good Environment, Platoon Edge</t>
         </is>
       </c>
       <c r="P19" t="n">
@@ -5568,7 +5568,7 @@
         <v>35.9</v>
       </c>
       <c r="R19" t="n">
-        <v>67.3</v>
+        <v>73.3</v>
       </c>
       <c r="S19" t="n">
         <v>44.8</v>
@@ -5754,12 +5754,12 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>88</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -6150,7 +6150,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>68.09999999999999</v>
+        <v>69</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -6164,7 +6164,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Elite Power, Strong Barrel, Premium Lineup Spot</t>
+          <t>Elite Power, Strong Barrel, Good Environment, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -6174,7 +6174,7 @@
         <v>35.9</v>
       </c>
       <c r="R2" t="n">
-        <v>67.3</v>
+        <v>73.3</v>
       </c>
       <c r="S2" t="n">
         <v>100</v>
@@ -6360,12 +6360,12 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>88</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -6430,7 +6430,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>66.59999999999999</v>
+        <v>67.5</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -6444,7 +6444,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Strong Barrel, Good Environment, Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -6454,7 +6454,7 @@
         <v>35.9</v>
       </c>
       <c r="R3" t="n">
-        <v>67.3</v>
+        <v>73.3</v>
       </c>
       <c r="S3" t="n">
         <v>93.2</v>
@@ -6640,12 +6640,12 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>88</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -6710,7 +6710,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>64.5</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -6724,7 +6724,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Elite Power, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Elite Power, Strong Barrel, Good Environment, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P4" t="n">
@@ -6734,7 +6734,7 @@
         <v>18.2</v>
       </c>
       <c r="R4" t="n">
-        <v>67.3</v>
+        <v>73.3</v>
       </c>
       <c r="S4" t="n">
         <v>93.2</v>
@@ -6920,12 +6920,12 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>88</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -6990,7 +6990,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>63.2</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -7004,7 +7004,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Good Environment, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P5" t="n">
@@ -7014,7 +7014,7 @@
         <v>18.2</v>
       </c>
       <c r="R5" t="n">
-        <v>67.3</v>
+        <v>73.3</v>
       </c>
       <c r="S5" t="n">
         <v>100</v>
@@ -7200,12 +7200,12 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>88</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -7270,7 +7270,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>62.4</v>
+        <v>63.3</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -7284,7 +7284,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Good Environment, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P6" t="n">
@@ -7294,7 +7294,7 @@
         <v>35.9</v>
       </c>
       <c r="R6" t="n">
-        <v>67.3</v>
+        <v>73.3</v>
       </c>
       <c r="S6" t="n">
         <v>94.90000000000001</v>
@@ -7480,12 +7480,12 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>88</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -7550,11 +7550,11 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>59.4</v>
+        <v>60.3</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Longshot</t>
+          <t>Tier 3</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -7564,7 +7564,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Good Environment, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P7" t="n">
@@ -7574,7 +7574,7 @@
         <v>35.9</v>
       </c>
       <c r="R7" t="n">
-        <v>67.3</v>
+        <v>73.3</v>
       </c>
       <c r="S7" t="n">
         <v>96.59999999999999</v>
@@ -7760,12 +7760,12 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>88</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -7830,7 +7830,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>59</v>
+        <v>59.9</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -7844,7 +7844,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Strong Barrel, Platoon Edge</t>
+          <t>Strong Barrel, Good Environment, Platoon Edge</t>
         </is>
       </c>
       <c r="P8" t="n">
@@ -7854,7 +7854,7 @@
         <v>35.9</v>
       </c>
       <c r="R8" t="n">
-        <v>67.3</v>
+        <v>73.3</v>
       </c>
       <c r="S8" t="n">
         <v>86.40000000000001</v>
@@ -8040,12 +8040,12 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>88</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -8110,7 +8110,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>58.6</v>
+        <v>59.5</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -8124,7 +8124,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Strong Barrel, Hot Hitter/Streak</t>
+          <t>Strong Barrel, Good Environment, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P9" t="n">
@@ -8134,7 +8134,7 @@
         <v>35.9</v>
       </c>
       <c r="R9" t="n">
-        <v>67.3</v>
+        <v>73.3</v>
       </c>
       <c r="S9" t="n">
         <v>64.3</v>
@@ -8320,12 +8320,12 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>88</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -8390,7 +8390,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>52.8</v>
+        <v>53.7</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -8404,7 +8404,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Strong Barrel</t>
+          <t>Strong Barrel, Good Environment</t>
         </is>
       </c>
       <c r="P10" t="n">
@@ -8414,7 +8414,7 @@
         <v>35.9</v>
       </c>
       <c r="R10" t="n">
-        <v>67.3</v>
+        <v>73.3</v>
       </c>
       <c r="S10" t="n">
         <v>52.4</v>
@@ -8600,12 +8600,12 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>88</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -8670,7 +8670,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>52.5</v>
+        <v>53.4</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -8684,7 +8684,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Strong Barrel, Platoon Edge</t>
+          <t>Strong Barrel, Good Environment, Platoon Edge</t>
         </is>
       </c>
       <c r="P11" t="n">
@@ -8694,7 +8694,7 @@
         <v>18.2</v>
       </c>
       <c r="R11" t="n">
-        <v>67.3</v>
+        <v>73.3</v>
       </c>
       <c r="S11" t="n">
         <v>86.40000000000001</v>
@@ -8880,12 +8880,12 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>88</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -8950,7 +8950,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>51.5</v>
+        <v>52.4</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -8964,7 +8964,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Good Environment, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P12" t="n">
@@ -8974,7 +8974,7 @@
         <v>18.2</v>
       </c>
       <c r="R12" t="n">
-        <v>67.3</v>
+        <v>73.3</v>
       </c>
       <c r="S12" t="n">
         <v>96.59999999999999</v>
@@ -9160,12 +9160,12 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>88</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -9230,7 +9230,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>51.4</v>
+        <v>52.3</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -9244,7 +9244,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Good Environment, Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P13" t="n">
@@ -9254,7 +9254,7 @@
         <v>18.2</v>
       </c>
       <c r="R13" t="n">
-        <v>67.3</v>
+        <v>73.3</v>
       </c>
       <c r="S13" t="n">
         <v>94.90000000000001</v>
@@ -9440,12 +9440,12 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>88</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -9510,7 +9510,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>48.8</v>
+        <v>49.7</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -9524,7 +9524,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Strong Barrel, Platoon Edge</t>
+          <t>Strong Barrel, Good Environment, Platoon Edge</t>
         </is>
       </c>
       <c r="P14" t="n">
@@ -9534,7 +9534,7 @@
         <v>18.2</v>
       </c>
       <c r="R14" t="n">
-        <v>67.3</v>
+        <v>73.3</v>
       </c>
       <c r="S14" t="n">
         <v>44.8</v>
@@ -9720,12 +9720,12 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>88</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -9790,7 +9790,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>45.2</v>
+        <v>46.1</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -9804,7 +9804,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>No major boost</t>
+          <t>Good Environment</t>
         </is>
       </c>
       <c r="P15" t="n">
@@ -9814,7 +9814,7 @@
         <v>35.9</v>
       </c>
       <c r="R15" t="n">
-        <v>67.3</v>
+        <v>73.3</v>
       </c>
       <c r="S15" t="n">
         <v>76.2</v>
@@ -10000,12 +10000,12 @@
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>88</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -10070,7 +10070,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>44.5</v>
+        <v>45.4</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -10084,7 +10084,7 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Good Environment, Platoon Edge</t>
         </is>
       </c>
       <c r="P16" t="n">
@@ -10094,7 +10094,7 @@
         <v>18.2</v>
       </c>
       <c r="R16" t="n">
-        <v>67.3</v>
+        <v>73.3</v>
       </c>
       <c r="S16" t="n">
         <v>64.3</v>
@@ -10280,12 +10280,12 @@
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>88</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -10350,7 +10350,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>41.3</v>
+        <v>42.2</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -10364,7 +10364,7 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>No major boost</t>
+          <t>Good Environment</t>
         </is>
       </c>
       <c r="P17" t="n">
@@ -10374,7 +10374,7 @@
         <v>18.2</v>
       </c>
       <c r="R17" t="n">
-        <v>67.3</v>
+        <v>73.3</v>
       </c>
       <c r="S17" t="n">
         <v>52.4</v>
@@ -10560,12 +10560,12 @@
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>88</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -10630,7 +10630,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>37.9</v>
+        <v>38.8</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -10644,7 +10644,7 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Good Environment, Platoon Edge</t>
         </is>
       </c>
       <c r="P18" t="n">
@@ -10654,7 +10654,7 @@
         <v>17.2</v>
       </c>
       <c r="R18" t="n">
-        <v>67.3</v>
+        <v>73.3</v>
       </c>
       <c r="S18" t="n">
         <v>76.2</v>
@@ -10840,12 +10840,12 @@
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>88</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -10910,7 +10910,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>36.7</v>
+        <v>37.6</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -10924,7 +10924,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Good Environment, Platoon Edge</t>
         </is>
       </c>
       <c r="P19" t="n">
@@ -10934,7 +10934,7 @@
         <v>35.9</v>
       </c>
       <c r="R19" t="n">
-        <v>67.3</v>
+        <v>73.3</v>
       </c>
       <c r="S19" t="n">
         <v>44.8</v>
@@ -11120,12 +11120,12 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>88</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">

--- a/outputs/hr_rankings.xlsx
+++ b/outputs/hr_rankings.xlsx
@@ -760,7 +760,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -784,11 +784,11 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>69.59999999999999</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Tier 3</t>
+          <t>Tier 2</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -798,7 +798,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Good Environment, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -808,7 +808,7 @@
         <v>49.2</v>
       </c>
       <c r="R2" t="n">
-        <v>60.8</v>
+        <v>74.3</v>
       </c>
       <c r="S2" t="n">
         <v>100</v>
@@ -994,7 +994,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -1064,11 +1064,11 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>68.59999999999999</v>
+        <v>70.7</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Tier 3</t>
+          <t>Tier 2</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -1078,7 +1078,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Elite Power, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Elite Power, Strong Barrel, Good Environment, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -1088,7 +1088,7 @@
         <v>35.4</v>
       </c>
       <c r="R3" t="n">
-        <v>60.8</v>
+        <v>74.3</v>
       </c>
       <c r="S3" t="n">
         <v>100</v>
@@ -1274,7 +1274,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1344,7 +1344,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>56.7</v>
+        <v>58.7</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -1358,7 +1358,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge</t>
+          <t>Good Environment, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P4" t="n">
@@ -1368,7 +1368,7 @@
         <v>47.2</v>
       </c>
       <c r="R4" t="n">
-        <v>60.8</v>
+        <v>74.3</v>
       </c>
       <c r="S4" t="n">
         <v>94.90000000000001</v>
@@ -1554,7 +1554,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -1600,7 +1600,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1624,7 +1624,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>56.4</v>
+        <v>58.5</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1638,7 +1638,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge</t>
+          <t>Good Environment, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P5" t="n">
@@ -1648,7 +1648,7 @@
         <v>49.2</v>
       </c>
       <c r="R5" t="n">
-        <v>60.8</v>
+        <v>74.3</v>
       </c>
       <c r="S5" t="n">
         <v>93.2</v>
@@ -1834,7 +1834,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1904,7 +1904,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>56.1</v>
+        <v>58.1</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -1918,7 +1918,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Good Environment, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P6" t="n">
@@ -1928,7 +1928,7 @@
         <v>35.4</v>
       </c>
       <c r="R6" t="n">
-        <v>60.8</v>
+        <v>74.3</v>
       </c>
       <c r="S6" t="n">
         <v>96.59999999999999</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -2184,7 +2184,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>54.8</v>
+        <v>56.8</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -2198,7 +2198,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Good Environment, Platoon Edge</t>
         </is>
       </c>
       <c r="P7" t="n">
@@ -2208,7 +2208,7 @@
         <v>49.2</v>
       </c>
       <c r="R7" t="n">
-        <v>60.8</v>
+        <v>74.3</v>
       </c>
       <c r="S7" t="n">
         <v>86.40000000000001</v>
@@ -2394,7 +2394,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -2464,7 +2464,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -2478,7 +2478,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Strong Barrel, Platoon Edge</t>
+          <t>Strong Barrel, Good Environment, Platoon Edge</t>
         </is>
       </c>
       <c r="P8" t="n">
@@ -2488,7 +2488,7 @@
         <v>49.2</v>
       </c>
       <c r="R8" t="n">
-        <v>60.8</v>
+        <v>74.3</v>
       </c>
       <c r="S8" t="n">
         <v>64.3</v>
@@ -2674,7 +2674,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -2720,7 +2720,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -2744,7 +2744,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -2758,7 +2758,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot</t>
+          <t>Good Environment, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P9" t="n">
@@ -2768,7 +2768,7 @@
         <v>49.2</v>
       </c>
       <c r="R9" t="n">
-        <v>60.8</v>
+        <v>74.3</v>
       </c>
       <c r="S9" t="n">
         <v>96.59999999999999</v>
@@ -2954,7 +2954,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -3000,7 +3000,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -3024,7 +3024,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -3038,7 +3038,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge</t>
+          <t>Good Environment, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P10" t="n">
@@ -3048,7 +3048,7 @@
         <v>35.4</v>
       </c>
       <c r="R10" t="n">
-        <v>60.8</v>
+        <v>74.3</v>
       </c>
       <c r="S10" t="n">
         <v>94.90000000000001</v>
@@ -3234,7 +3234,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -3280,7 +3280,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -3304,7 +3304,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>51.1</v>
+        <v>53.1</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -3318,7 +3318,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Strong Barrel</t>
+          <t>Strong Barrel, Good Environment</t>
         </is>
       </c>
       <c r="P11" t="n">
@@ -3328,7 +3328,7 @@
         <v>49.2</v>
       </c>
       <c r="R11" t="n">
-        <v>60.8</v>
+        <v>74.3</v>
       </c>
       <c r="S11" t="n">
         <v>44.8</v>
@@ -3514,7 +3514,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -3560,7 +3560,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -3584,7 +3584,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>50.3</v>
+        <v>52.3</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Strong Barrel, Platoon Edge</t>
+          <t>Strong Barrel, Good Environment, Platoon Edge</t>
         </is>
       </c>
       <c r="P12" t="n">
@@ -3608,7 +3608,7 @@
         <v>49.2</v>
       </c>
       <c r="R12" t="n">
-        <v>60.8</v>
+        <v>74.3</v>
       </c>
       <c r="S12" t="n">
         <v>52.4</v>
@@ -3794,7 +3794,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -3864,7 +3864,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>45.5</v>
+        <v>47.5</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -3878,7 +3878,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Good Environment, Platoon Edge</t>
         </is>
       </c>
       <c r="P13" t="n">
@@ -3888,7 +3888,7 @@
         <v>35.4</v>
       </c>
       <c r="R13" t="n">
-        <v>60.8</v>
+        <v>74.3</v>
       </c>
       <c r="S13" t="n">
         <v>76.2</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
@@ -4120,7 +4120,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -4144,7 +4144,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>44.7</v>
+        <v>46.8</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -4158,7 +4158,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot</t>
+          <t>Good Environment, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P14" t="n">
@@ -4168,7 +4168,7 @@
         <v>35.4</v>
       </c>
       <c r="R14" t="n">
-        <v>60.8</v>
+        <v>74.3</v>
       </c>
       <c r="S14" t="n">
         <v>93.2</v>
@@ -4354,7 +4354,7 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
@@ -4400,7 +4400,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -4424,7 +4424,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>44.4</v>
+        <v>46.4</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -4438,7 +4438,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Good Environment, Platoon Edge</t>
         </is>
       </c>
       <c r="P15" t="n">
@@ -4448,7 +4448,7 @@
         <v>47.2</v>
       </c>
       <c r="R15" t="n">
-        <v>60.8</v>
+        <v>74.3</v>
       </c>
       <c r="S15" t="n">
         <v>76.2</v>
@@ -4634,7 +4634,7 @@
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
@@ -4680,7 +4680,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -4704,7 +4704,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>44.4</v>
+        <v>46.4</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -4718,7 +4718,7 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Good Environment, Platoon Edge</t>
         </is>
       </c>
       <c r="P16" t="n">
@@ -4728,7 +4728,7 @@
         <v>35.4</v>
       </c>
       <c r="R16" t="n">
-        <v>60.8</v>
+        <v>74.3</v>
       </c>
       <c r="S16" t="n">
         <v>52.4</v>
@@ -4914,7 +4914,7 @@
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -4984,7 +4984,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -4998,7 +4998,7 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>No major boost</t>
+          <t>Good Environment</t>
         </is>
       </c>
       <c r="P17" t="n">
@@ -5008,7 +5008,7 @@
         <v>35.4</v>
       </c>
       <c r="R17" t="n">
-        <v>60.8</v>
+        <v>74.3</v>
       </c>
       <c r="S17" t="n">
         <v>64.3</v>
@@ -5194,7 +5194,7 @@
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
@@ -5240,7 +5240,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -5264,7 +5264,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>43.5</v>
+        <v>45.6</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -5278,7 +5278,7 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>No major boost</t>
+          <t>Good Environment</t>
         </is>
       </c>
       <c r="P18" t="n">
@@ -5288,7 +5288,7 @@
         <v>35.4</v>
       </c>
       <c r="R18" t="n">
-        <v>60.8</v>
+        <v>74.3</v>
       </c>
       <c r="S18" t="n">
         <v>86.40000000000001</v>
@@ -5474,7 +5474,7 @@
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
@@ -5520,7 +5520,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -5544,7 +5544,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>35.9</v>
+        <v>37.9</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -5558,7 +5558,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Good Environment, Platoon Edge</t>
         </is>
       </c>
       <c r="P19" t="n">
@@ -5568,7 +5568,7 @@
         <v>35.4</v>
       </c>
       <c r="R19" t="n">
-        <v>60.8</v>
+        <v>74.3</v>
       </c>
       <c r="S19" t="n">
         <v>44.8</v>
@@ -5754,7 +5754,7 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
@@ -6126,7 +6126,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -6150,11 +6150,11 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>69.59999999999999</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Tier 3</t>
+          <t>Tier 2</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -6164,7 +6164,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Good Environment, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -6174,7 +6174,7 @@
         <v>49.2</v>
       </c>
       <c r="R2" t="n">
-        <v>60.8</v>
+        <v>74.3</v>
       </c>
       <c r="S2" t="n">
         <v>100</v>
@@ -6360,7 +6360,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -6406,7 +6406,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -6430,11 +6430,11 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>68.59999999999999</v>
+        <v>70.7</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Tier 3</t>
+          <t>Tier 2</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -6444,7 +6444,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Elite Power, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Elite Power, Strong Barrel, Good Environment, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -6454,7 +6454,7 @@
         <v>35.4</v>
       </c>
       <c r="R3" t="n">
-        <v>60.8</v>
+        <v>74.3</v>
       </c>
       <c r="S3" t="n">
         <v>100</v>
@@ -6640,7 +6640,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -6686,7 +6686,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -6710,7 +6710,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>56.7</v>
+        <v>58.7</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -6724,7 +6724,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge</t>
+          <t>Good Environment, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P4" t="n">
@@ -6734,7 +6734,7 @@
         <v>47.2</v>
       </c>
       <c r="R4" t="n">
-        <v>60.8</v>
+        <v>74.3</v>
       </c>
       <c r="S4" t="n">
         <v>94.90000000000001</v>
@@ -6920,7 +6920,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -6966,7 +6966,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -6990,7 +6990,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>56.4</v>
+        <v>58.5</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -7004,7 +7004,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge</t>
+          <t>Good Environment, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P5" t="n">
@@ -7014,7 +7014,7 @@
         <v>49.2</v>
       </c>
       <c r="R5" t="n">
-        <v>60.8</v>
+        <v>74.3</v>
       </c>
       <c r="S5" t="n">
         <v>93.2</v>
@@ -7200,7 +7200,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -7270,7 +7270,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>56.1</v>
+        <v>58.1</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -7284,7 +7284,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Good Environment, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P6" t="n">
@@ -7294,7 +7294,7 @@
         <v>35.4</v>
       </c>
       <c r="R6" t="n">
-        <v>60.8</v>
+        <v>74.3</v>
       </c>
       <c r="S6" t="n">
         <v>96.59999999999999</v>
@@ -7480,7 +7480,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -7526,7 +7526,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -7550,7 +7550,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>54.8</v>
+        <v>56.8</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -7564,7 +7564,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Good Environment, Platoon Edge</t>
         </is>
       </c>
       <c r="P7" t="n">
@@ -7574,7 +7574,7 @@
         <v>49.2</v>
       </c>
       <c r="R7" t="n">
-        <v>60.8</v>
+        <v>74.3</v>
       </c>
       <c r="S7" t="n">
         <v>86.40000000000001</v>
@@ -7760,7 +7760,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -7806,7 +7806,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -7830,7 +7830,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -7844,7 +7844,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Strong Barrel, Platoon Edge</t>
+          <t>Strong Barrel, Good Environment, Platoon Edge</t>
         </is>
       </c>
       <c r="P8" t="n">
@@ -7854,7 +7854,7 @@
         <v>49.2</v>
       </c>
       <c r="R8" t="n">
-        <v>60.8</v>
+        <v>74.3</v>
       </c>
       <c r="S8" t="n">
         <v>64.3</v>
@@ -8040,7 +8040,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -8086,7 +8086,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -8110,7 +8110,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -8124,7 +8124,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot</t>
+          <t>Good Environment, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P9" t="n">
@@ -8134,7 +8134,7 @@
         <v>49.2</v>
       </c>
       <c r="R9" t="n">
-        <v>60.8</v>
+        <v>74.3</v>
       </c>
       <c r="S9" t="n">
         <v>96.59999999999999</v>
@@ -8320,7 +8320,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -8366,7 +8366,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -8390,7 +8390,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -8404,7 +8404,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge</t>
+          <t>Good Environment, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P10" t="n">
@@ -8414,7 +8414,7 @@
         <v>35.4</v>
       </c>
       <c r="R10" t="n">
-        <v>60.8</v>
+        <v>74.3</v>
       </c>
       <c r="S10" t="n">
         <v>94.90000000000001</v>
@@ -8600,7 +8600,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -8646,7 +8646,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -8670,7 +8670,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>51.1</v>
+        <v>53.1</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -8684,7 +8684,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Strong Barrel</t>
+          <t>Strong Barrel, Good Environment</t>
         </is>
       </c>
       <c r="P11" t="n">
@@ -8694,7 +8694,7 @@
         <v>49.2</v>
       </c>
       <c r="R11" t="n">
-        <v>60.8</v>
+        <v>74.3</v>
       </c>
       <c r="S11" t="n">
         <v>44.8</v>
@@ -8880,7 +8880,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -8926,7 +8926,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -8950,7 +8950,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>50.3</v>
+        <v>52.3</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -8964,7 +8964,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Strong Barrel, Platoon Edge</t>
+          <t>Strong Barrel, Good Environment, Platoon Edge</t>
         </is>
       </c>
       <c r="P12" t="n">
@@ -8974,7 +8974,7 @@
         <v>49.2</v>
       </c>
       <c r="R12" t="n">
-        <v>60.8</v>
+        <v>74.3</v>
       </c>
       <c r="S12" t="n">
         <v>52.4</v>
@@ -9160,7 +9160,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -9206,7 +9206,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -9230,7 +9230,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>45.5</v>
+        <v>47.5</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -9244,7 +9244,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Good Environment, Platoon Edge</t>
         </is>
       </c>
       <c r="P13" t="n">
@@ -9254,7 +9254,7 @@
         <v>35.4</v>
       </c>
       <c r="R13" t="n">
-        <v>60.8</v>
+        <v>74.3</v>
       </c>
       <c r="S13" t="n">
         <v>76.2</v>
@@ -9440,7 +9440,7 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
@@ -9486,7 +9486,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -9510,7 +9510,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>44.7</v>
+        <v>46.8</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -9524,7 +9524,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot</t>
+          <t>Good Environment, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P14" t="n">
@@ -9534,7 +9534,7 @@
         <v>35.4</v>
       </c>
       <c r="R14" t="n">
-        <v>60.8</v>
+        <v>74.3</v>
       </c>
       <c r="S14" t="n">
         <v>93.2</v>
@@ -9720,7 +9720,7 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
@@ -9766,7 +9766,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -9790,7 +9790,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>44.4</v>
+        <v>46.4</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -9804,7 +9804,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Good Environment, Platoon Edge</t>
         </is>
       </c>
       <c r="P15" t="n">
@@ -9814,7 +9814,7 @@
         <v>47.2</v>
       </c>
       <c r="R15" t="n">
-        <v>60.8</v>
+        <v>74.3</v>
       </c>
       <c r="S15" t="n">
         <v>76.2</v>
@@ -10000,7 +10000,7 @@
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
@@ -10046,7 +10046,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -10070,7 +10070,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>44.4</v>
+        <v>46.4</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -10084,7 +10084,7 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Good Environment, Platoon Edge</t>
         </is>
       </c>
       <c r="P16" t="n">
@@ -10094,7 +10094,7 @@
         <v>35.4</v>
       </c>
       <c r="R16" t="n">
-        <v>60.8</v>
+        <v>74.3</v>
       </c>
       <c r="S16" t="n">
         <v>52.4</v>
@@ -10280,7 +10280,7 @@
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
@@ -10326,7 +10326,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -10350,7 +10350,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -10364,7 +10364,7 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>No major boost</t>
+          <t>Good Environment</t>
         </is>
       </c>
       <c r="P17" t="n">
@@ -10374,7 +10374,7 @@
         <v>35.4</v>
       </c>
       <c r="R17" t="n">
-        <v>60.8</v>
+        <v>74.3</v>
       </c>
       <c r="S17" t="n">
         <v>64.3</v>
@@ -10560,7 +10560,7 @@
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
@@ -10606,7 +10606,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -10630,7 +10630,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>43.5</v>
+        <v>45.6</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -10644,7 +10644,7 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>No major boost</t>
+          <t>Good Environment</t>
         </is>
       </c>
       <c r="P18" t="n">
@@ -10654,7 +10654,7 @@
         <v>35.4</v>
       </c>
       <c r="R18" t="n">
-        <v>60.8</v>
+        <v>74.3</v>
       </c>
       <c r="S18" t="n">
         <v>86.40000000000001</v>
@@ -10840,7 +10840,7 @@
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
@@ -10886,7 +10886,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -10910,7 +10910,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>35.9</v>
+        <v>37.9</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -10924,7 +10924,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Good Environment, Platoon Edge</t>
         </is>
       </c>
       <c r="P19" t="n">
@@ -10934,7 +10934,7 @@
         <v>35.4</v>
       </c>
       <c r="R19" t="n">
-        <v>60.8</v>
+        <v>74.3</v>
       </c>
       <c r="S19" t="n">
         <v>44.8</v>
@@ -11120,7 +11120,7 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">

--- a/outputs/hr_rankings.xlsx
+++ b/outputs/hr_rankings.xlsx
@@ -784,7 +784,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>77</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -808,7 +808,7 @@
         <v>68.2</v>
       </c>
       <c r="R2" t="n">
-        <v>57.6</v>
+        <v>57.1</v>
       </c>
       <c r="S2" t="n">
         <v>94.90000000000001</v>
@@ -999,7 +999,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>84</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1064,7 +1064,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>68.5</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -1088,7 +1088,7 @@
         <v>68.2</v>
       </c>
       <c r="R3" t="n">
-        <v>57.6</v>
+        <v>57.1</v>
       </c>
       <c r="S3" t="n">
         <v>52.4</v>
@@ -1279,7 +1279,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>84</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1924,7 +1924,7 @@
         <v>67.59999999999999</v>
       </c>
       <c r="R6" t="n">
-        <v>57.6</v>
+        <v>57.1</v>
       </c>
       <c r="S6" t="n">
         <v>96.59999999999999</v>
@@ -2115,7 +2115,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>84</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2407,52 +2407,52 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>542303</t>
+          <t>682985</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Marcell Ozuna</t>
+          <t>Riley Greene</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-07-18T23:10:00Z</t>
+          <t>2026-07-19T02:07:00Z</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Logan Allen</t>
+          <t>Grayson Rodriguez</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>671106</t>
+          <t>680570</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L8" t="n">
@@ -2470,61 +2470,65 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>42</v>
+        <v>60.2</v>
       </c>
       <c r="Q8" t="n">
-        <v>68.2</v>
+        <v>60.5</v>
       </c>
       <c r="R8" t="n">
-        <v>57.6</v>
+        <v>28.2</v>
       </c>
       <c r="S8" t="n">
-        <v>76.2</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="T8" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U8" t="n">
-        <v>54.7</v>
+        <v>16.1</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr"/>
@@ -2541,142 +2545,134 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 5/22, 0 HR</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 15.5% barrel, 5.4 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.7% barrel, 4.0 HR allowed</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>9.75</t>
+          <t>14.72</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>40.54</t>
+          <t>48.51</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>89.76</t>
+          <t>90.95</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>100.2738</t>
+          <t>102.8018</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>0.4207</t>
+          <t>0.4833</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>0.1915</t>
+          <t>0.2277</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>0.3253</t>
+          <t>0.3551</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>73.39</t>
+          <t>75.67</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>36.43</t>
+          <t>58.67</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>40.03</t>
+          <t>39.82</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>31.2</t>
+          <t>32.47</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>11.9</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>0.1414</t>
+          <t>0.1937</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>15.47</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>49.4</t>
+          <t>51.0</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>92.38</t>
+          <t>91.4</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>0.428</t>
+          <t>0.531</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
-          <t>0.1845</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>32.53</t>
-        </is>
-      </c>
-      <c r="BG8" t="inlineStr">
-        <is>
-          <t>L To R</t>
-        </is>
-      </c>
-      <c r="BH8" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
+          <t>28.8</t>
+        </is>
+      </c>
+      <c r="BG8" t="inlineStr"/>
+      <c r="BH8" t="inlineStr"/>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>Progressive Field</t>
+          <t>Angel Stadium</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr"/>
@@ -2687,56 +2683,56 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>682985</t>
+          <t>542303</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Riley Greene</t>
+          <t>Marcell Ozuna</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-07-19T02:07:00Z</t>
+          <t>2026-07-18T23:10:00Z</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Grayson Rodriguez</t>
+          <t>Logan Allen</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>680570</t>
+          <t>671106</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>59.3</v>
+        <v>59.2</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -2750,65 +2746,61 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>60.2</v>
+        <v>42</v>
       </c>
       <c r="Q9" t="n">
-        <v>60.5</v>
+        <v>68.2</v>
       </c>
       <c r="R9" t="n">
-        <v>28.2</v>
+        <v>57.1</v>
       </c>
       <c r="S9" t="n">
-        <v>90.40000000000001</v>
+        <v>76.2</v>
       </c>
       <c r="T9" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="U9" t="n">
-        <v>16.1</v>
+        <v>54.7</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr"/>
@@ -2825,134 +2817,142 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/22, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.7% barrel, 4.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 15.5% barrel, 5.4 HR allowed</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>14.72</t>
+          <t>9.75</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>48.51</t>
+          <t>40.54</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>90.95</t>
+          <t>89.76</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>102.8018</t>
+          <t>100.2738</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>0.4833</t>
+          <t>0.4207</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>0.2277</t>
+          <t>0.1915</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>0.3551</t>
+          <t>0.3253</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>75.67</t>
+          <t>73.39</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>58.67</t>
+          <t>36.43</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>39.82</t>
+          <t>40.03</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>32.47</t>
+          <t>31.2</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>11.9</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>0.1937</t>
+          <t>0.1414</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>15.47</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>51.0</t>
+          <t>49.4</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>91.4</t>
+          <t>92.38</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>0.531</t>
+          <t>0.428</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.1845</t>
         </is>
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>28.8</t>
-        </is>
-      </c>
-      <c r="BG9" t="inlineStr"/>
-      <c r="BH9" t="inlineStr"/>
+          <t>32.53</t>
+        </is>
+      </c>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>Angel Stadium</t>
+          <t>Progressive Field</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr"/>
@@ -3564,7 +3564,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>58</v>
+        <v>57.9</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -3588,7 +3588,7 @@
         <v>68.2</v>
       </c>
       <c r="R12" t="n">
-        <v>57.6</v>
+        <v>57.1</v>
       </c>
       <c r="S12" t="n">
         <v>86.40000000000001</v>
@@ -3779,7 +3779,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>84</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -3868,7 +3868,7 @@
         <v>68.2</v>
       </c>
       <c r="R13" t="n">
-        <v>57.6</v>
+        <v>57.1</v>
       </c>
       <c r="S13" t="n">
         <v>64.3</v>
@@ -4059,7 +4059,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>84</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -5516,7 +5516,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>53.2</v>
+        <v>53.1</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -5540,7 +5540,7 @@
         <v>68.2</v>
       </c>
       <c r="R19" t="n">
-        <v>57.6</v>
+        <v>57.1</v>
       </c>
       <c r="S19" t="n">
         <v>100</v>
@@ -5731,7 +5731,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>84</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -6904,7 +6904,7 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>51.5</v>
+        <v>51.4</v>
       </c>
       <c r="M24" t="inlineStr">
         <is>
@@ -6928,7 +6928,7 @@
         <v>34.4</v>
       </c>
       <c r="R24" t="n">
-        <v>57.6</v>
+        <v>57.1</v>
       </c>
       <c r="S24" t="n">
         <v>94.90000000000001</v>
@@ -7119,7 +7119,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>84</t>
         </is>
       </c>
       <c r="BI24" t="inlineStr">
@@ -7460,7 +7460,7 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>50.8</v>
+        <v>50.7</v>
       </c>
       <c r="M26" t="inlineStr">
         <is>
@@ -7484,7 +7484,7 @@
         <v>34.4</v>
       </c>
       <c r="R26" t="n">
-        <v>57.6</v>
+        <v>57.1</v>
       </c>
       <c r="S26" t="n">
         <v>96.59999999999999</v>
@@ -7675,7 +7675,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>84</t>
         </is>
       </c>
       <c r="BI26" t="inlineStr">
@@ -9124,7 +9124,7 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>48.5</v>
+        <v>48.4</v>
       </c>
       <c r="M32" t="inlineStr">
         <is>
@@ -9148,7 +9148,7 @@
         <v>67.59999999999999</v>
       </c>
       <c r="R32" t="n">
-        <v>57.6</v>
+        <v>57.1</v>
       </c>
       <c r="S32" t="n">
         <v>93.2</v>
@@ -9339,7 +9339,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>84</t>
         </is>
       </c>
       <c r="BI32" t="inlineStr">
@@ -11352,7 +11352,7 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>44.9</v>
+        <v>44.8</v>
       </c>
       <c r="M40" t="inlineStr">
         <is>
@@ -11376,7 +11376,7 @@
         <v>33.9</v>
       </c>
       <c r="R40" t="n">
-        <v>57.6</v>
+        <v>57.1</v>
       </c>
       <c r="S40" t="n">
         <v>100</v>
@@ -11567,7 +11567,7 @@
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>84</t>
         </is>
       </c>
       <c r="BI40" t="inlineStr">
@@ -12135,32 +12135,32 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>682177</t>
+          <t>811965</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Daniel Schneemann</t>
+          <t>Joshua Kuroda-Grauer</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>WSH</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-07-18T23:10:00Z</t>
+          <t>2026-07-19T02:05:00Z</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -12170,17 +12170,17 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Mason Montgomery</t>
+          <t>Zack Littell</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>682254</t>
+          <t>641793</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L43" t="n">
@@ -12198,61 +12198,65 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>No major boost</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P43" t="n">
-        <v>32.5</v>
+        <v>16.1</v>
       </c>
       <c r="Q43" t="n">
-        <v>34.4</v>
+        <v>67.7</v>
       </c>
       <c r="R43" t="n">
-        <v>57.6</v>
+        <v>30.9</v>
       </c>
       <c r="S43" t="n">
-        <v>86.40000000000001</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T43" t="n">
         <v>50</v>
       </c>
       <c r="U43" t="n">
-        <v>3.4</v>
+        <v>45</v>
       </c>
       <c r="V43" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W43" t="inlineStr">
+      <c r="Z43" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X43" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y43" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD43" t="inlineStr"/>
@@ -12269,12 +12273,12 @@
       </c>
       <c r="AH43" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AI43" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ43" t="inlineStr">
@@ -12284,127 +12288,119 @@
       </c>
       <c r="AK43" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/21, 0 HR</t>
+          <t>Contact streak: 12/27 over last 7 games</t>
         </is>
       </c>
       <c r="AL43" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 9.3% barrel, 4.6 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 10.9% barrel, 26.9 HR allowed</t>
         </is>
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN43" t="inlineStr">
         <is>
-          <t>9.05</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>39.32</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="AP43" t="inlineStr">
         <is>
-          <t>88.27</t>
+          <t>89.1</t>
         </is>
       </c>
       <c r="AQ43" t="inlineStr">
         <is>
-          <t>99.0368</t>
+          <t>99.1611</t>
         </is>
       </c>
       <c r="AR43" t="inlineStr">
         <is>
-          <t>0.3723</t>
+          <t>0.392</t>
         </is>
       </c>
       <c r="AS43" t="inlineStr">
         <is>
-          <t>0.1527</t>
+          <t>0.068</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr">
         <is>
-          <t>0.2907</t>
+          <t>0.319</t>
         </is>
       </c>
       <c r="AU43" t="inlineStr">
         <is>
-          <t>71.11</t>
+          <t>68.6</t>
         </is>
       </c>
       <c r="AV43" t="inlineStr">
         <is>
-          <t>11.86</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>46.37</t>
+          <t>39.5</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>29.02</t>
+          <t>11.6</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">
         <is>
-          <t>7.8</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>0.1298</t>
+          <t>0.122</t>
         </is>
       </c>
       <c r="BA43" t="inlineStr">
         <is>
-          <t>9.33</t>
+          <t>10.95</t>
         </is>
       </c>
       <c r="BB43" t="inlineStr">
         <is>
-          <t>40.19</t>
+          <t>44.12</t>
         </is>
       </c>
       <c r="BC43" t="inlineStr">
         <is>
-          <t>87.83</t>
+          <t>91.39</t>
         </is>
       </c>
       <c r="BD43" t="inlineStr">
         <is>
-          <t>0.3499</t>
+          <t>0.5154</t>
         </is>
       </c>
       <c r="BE43" t="inlineStr">
         <is>
-          <t>0.1321</t>
+          <t>0.2341</t>
         </is>
       </c>
       <c r="BF43" t="inlineStr">
         <is>
-          <t>22.01</t>
-        </is>
-      </c>
-      <c r="BG43" t="inlineStr">
-        <is>
-          <t>L To R</t>
-        </is>
-      </c>
-      <c r="BH43" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
+          <t>32.0</t>
+        </is>
+      </c>
+      <c r="BG43" t="inlineStr"/>
+      <c r="BH43" t="inlineStr"/>
       <c r="BI43" t="inlineStr">
         <is>
-          <t>Progressive Field</t>
+          <t>Sutter Health Park</t>
         </is>
       </c>
       <c r="BJ43" t="inlineStr"/>
@@ -12415,32 +12411,32 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>811965</t>
+          <t>682177</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Joshua Kuroda-Grauer</t>
+          <t>Daniel Schneemann</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>WSH</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-07-19T02:05:00Z</t>
+          <t>2026-07-18T23:10:00Z</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -12450,21 +12446,21 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Zack Littell</t>
+          <t>Mason Montgomery</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>641793</t>
+          <t>682254</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L44" t="n">
-        <v>44.4</v>
+        <v>44.3</v>
       </c>
       <c r="M44" t="inlineStr">
         <is>
@@ -12478,65 +12474,61 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P44" t="n">
-        <v>16.1</v>
+        <v>32.5</v>
       </c>
       <c r="Q44" t="n">
-        <v>67.7</v>
+        <v>34.4</v>
       </c>
       <c r="R44" t="n">
-        <v>30.9</v>
+        <v>57.1</v>
       </c>
       <c r="S44" t="n">
-        <v>81.90000000000001</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T44" t="n">
         <v>50</v>
       </c>
       <c r="U44" t="n">
-        <v>45</v>
+        <v>3.4</v>
       </c>
       <c r="V44" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W44" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X44" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y44" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr"/>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD44" t="inlineStr"/>
@@ -12553,12 +12545,12 @@
       </c>
       <c r="AH44" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI44" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ44" t="inlineStr">
@@ -12568,119 +12560,127 @@
       </c>
       <c r="AK44" t="inlineStr">
         <is>
-          <t>Contact streak: 12/27 over last 7 games</t>
+          <t>Last 7 games: 3/21, 0 HR</t>
         </is>
       </c>
       <c r="AL44" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 10.9% barrel, 26.9 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 9.3% barrel, 4.6 HR allowed</t>
         </is>
       </c>
       <c r="AM44" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN44" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.05</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>39.32</t>
         </is>
       </c>
       <c r="AP44" t="inlineStr">
         <is>
-          <t>89.1</t>
+          <t>88.27</t>
         </is>
       </c>
       <c r="AQ44" t="inlineStr">
         <is>
-          <t>99.1611</t>
+          <t>99.0368</t>
         </is>
       </c>
       <c r="AR44" t="inlineStr">
         <is>
-          <t>0.392</t>
+          <t>0.3723</t>
         </is>
       </c>
       <c r="AS44" t="inlineStr">
         <is>
-          <t>0.068</t>
+          <t>0.1527</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr">
         <is>
-          <t>0.319</t>
+          <t>0.2907</t>
         </is>
       </c>
       <c r="AU44" t="inlineStr">
         <is>
-          <t>68.6</t>
+          <t>71.11</t>
         </is>
       </c>
       <c r="AV44" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>11.86</t>
         </is>
       </c>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>39.5</t>
+          <t>46.37</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>11.6</t>
+          <t>29.02</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.8</t>
         </is>
       </c>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>0.122</t>
+          <t>0.1298</t>
         </is>
       </c>
       <c r="BA44" t="inlineStr">
         <is>
-          <t>10.95</t>
+          <t>9.33</t>
         </is>
       </c>
       <c r="BB44" t="inlineStr">
         <is>
-          <t>44.12</t>
+          <t>40.19</t>
         </is>
       </c>
       <c r="BC44" t="inlineStr">
         <is>
-          <t>91.39</t>
+          <t>87.83</t>
         </is>
       </c>
       <c r="BD44" t="inlineStr">
         <is>
-          <t>0.5154</t>
+          <t>0.3499</t>
         </is>
       </c>
       <c r="BE44" t="inlineStr">
         <is>
-          <t>0.2341</t>
+          <t>0.1321</t>
         </is>
       </c>
       <c r="BF44" t="inlineStr">
         <is>
-          <t>32.0</t>
-        </is>
-      </c>
-      <c r="BG44" t="inlineStr"/>
-      <c r="BH44" t="inlineStr"/>
+          <t>22.01</t>
+        </is>
+      </c>
+      <c r="BG44" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH44" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
       <c r="BI44" t="inlineStr">
         <is>
-          <t>Sutter Health Park</t>
+          <t>Progressive Field</t>
         </is>
       </c>
       <c r="BJ44" t="inlineStr"/>
@@ -12740,7 +12740,7 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>43.9</v>
+        <v>43.8</v>
       </c>
       <c r="M45" t="inlineStr">
         <is>
@@ -12764,7 +12764,7 @@
         <v>68.2</v>
       </c>
       <c r="R45" t="n">
-        <v>57.6</v>
+        <v>57.1</v>
       </c>
       <c r="S45" t="n">
         <v>44.8</v>
@@ -12955,7 +12955,7 @@
       </c>
       <c r="BH45" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>84</t>
         </is>
       </c>
       <c r="BI45" t="inlineStr">
@@ -13020,7 +13020,7 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>42.8</v>
+        <v>42.7</v>
       </c>
       <c r="M46" t="inlineStr">
         <is>
@@ -13044,7 +13044,7 @@
         <v>34.4</v>
       </c>
       <c r="R46" t="n">
-        <v>57.6</v>
+        <v>57.1</v>
       </c>
       <c r="S46" t="n">
         <v>76.2</v>
@@ -13235,7 +13235,7 @@
       </c>
       <c r="BH46" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>84</t>
         </is>
       </c>
       <c r="BI46" t="inlineStr">
@@ -14712,7 +14712,7 @@
         <v>34.4</v>
       </c>
       <c r="R52" t="n">
-        <v>57.6</v>
+        <v>57.1</v>
       </c>
       <c r="S52" t="n">
         <v>93.2</v>
@@ -14903,7 +14903,7 @@
       </c>
       <c r="BH52" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>84</t>
         </is>
       </c>
       <c r="BI52" t="inlineStr">
@@ -15796,7 +15796,7 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>40.4</v>
+        <v>40.3</v>
       </c>
       <c r="M56" t="inlineStr">
         <is>
@@ -15820,7 +15820,7 @@
         <v>34.4</v>
       </c>
       <c r="R56" t="n">
-        <v>57.6</v>
+        <v>57.1</v>
       </c>
       <c r="S56" t="n">
         <v>52.4</v>
@@ -16011,7 +16011,7 @@
       </c>
       <c r="BH56" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>84</t>
         </is>
       </c>
       <c r="BI56" t="inlineStr">
@@ -18852,7 +18852,7 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>34.3</v>
+        <v>34.2</v>
       </c>
       <c r="M67" t="inlineStr">
         <is>
@@ -18876,7 +18876,7 @@
         <v>34.4</v>
       </c>
       <c r="R67" t="n">
-        <v>57.6</v>
+        <v>57.1</v>
       </c>
       <c r="S67" t="n">
         <v>64.3</v>
@@ -19067,7 +19067,7 @@
       </c>
       <c r="BH67" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>84</t>
         </is>
       </c>
       <c r="BI67" t="inlineStr">
@@ -20244,7 +20244,7 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>30.1</v>
+        <v>30</v>
       </c>
       <c r="M72" t="inlineStr">
         <is>
@@ -20268,7 +20268,7 @@
         <v>34.4</v>
       </c>
       <c r="R72" t="n">
-        <v>57.6</v>
+        <v>57.1</v>
       </c>
       <c r="S72" t="n">
         <v>44.8</v>
@@ -20459,7 +20459,7 @@
       </c>
       <c r="BH72" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>84</t>
         </is>
       </c>
       <c r="BI72" t="inlineStr">
@@ -21126,7 +21126,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>77</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -21150,7 +21150,7 @@
         <v>68.2</v>
       </c>
       <c r="R2" t="n">
-        <v>57.6</v>
+        <v>57.1</v>
       </c>
       <c r="S2" t="n">
         <v>94.90000000000001</v>
@@ -21341,7 +21341,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>84</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -21406,7 +21406,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>68.5</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -21430,7 +21430,7 @@
         <v>68.2</v>
       </c>
       <c r="R3" t="n">
-        <v>57.6</v>
+        <v>57.1</v>
       </c>
       <c r="S3" t="n">
         <v>52.4</v>
@@ -21621,7 +21621,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>84</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -22266,7 +22266,7 @@
         <v>67.59999999999999</v>
       </c>
       <c r="R6" t="n">
-        <v>57.6</v>
+        <v>57.1</v>
       </c>
       <c r="S6" t="n">
         <v>96.59999999999999</v>
@@ -22457,7 +22457,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>84</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -22749,52 +22749,52 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>542303</t>
+          <t>682985</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Marcell Ozuna</t>
+          <t>Riley Greene</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-07-18T23:10:00Z</t>
+          <t>2026-07-19T02:07:00Z</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Logan Allen</t>
+          <t>Grayson Rodriguez</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>671106</t>
+          <t>680570</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L8" t="n">
@@ -22812,61 +22812,65 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>42</v>
+        <v>60.2</v>
       </c>
       <c r="Q8" t="n">
-        <v>68.2</v>
+        <v>60.5</v>
       </c>
       <c r="R8" t="n">
-        <v>57.6</v>
+        <v>28.2</v>
       </c>
       <c r="S8" t="n">
-        <v>76.2</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="T8" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U8" t="n">
-        <v>54.7</v>
+        <v>16.1</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr"/>
@@ -22883,142 +22887,134 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 5/22, 0 HR</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 15.5% barrel, 5.4 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.7% barrel, 4.0 HR allowed</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>9.75</t>
+          <t>14.72</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>40.54</t>
+          <t>48.51</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>89.76</t>
+          <t>90.95</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>100.2738</t>
+          <t>102.8018</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>0.4207</t>
+          <t>0.4833</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>0.1915</t>
+          <t>0.2277</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>0.3253</t>
+          <t>0.3551</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>73.39</t>
+          <t>75.67</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>36.43</t>
+          <t>58.67</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>40.03</t>
+          <t>39.82</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>31.2</t>
+          <t>32.47</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>11.9</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>0.1414</t>
+          <t>0.1937</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>15.47</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>49.4</t>
+          <t>51.0</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>92.38</t>
+          <t>91.4</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>0.428</t>
+          <t>0.531</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
-          <t>0.1845</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>32.53</t>
-        </is>
-      </c>
-      <c r="BG8" t="inlineStr">
-        <is>
-          <t>L To R</t>
-        </is>
-      </c>
-      <c r="BH8" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
+          <t>28.8</t>
+        </is>
+      </c>
+      <c r="BG8" t="inlineStr"/>
+      <c r="BH8" t="inlineStr"/>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>Progressive Field</t>
+          <t>Angel Stadium</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr"/>
@@ -23029,56 +23025,56 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>682985</t>
+          <t>542303</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Riley Greene</t>
+          <t>Marcell Ozuna</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-07-19T02:07:00Z</t>
+          <t>2026-07-18T23:10:00Z</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Grayson Rodriguez</t>
+          <t>Logan Allen</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>680570</t>
+          <t>671106</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>59.3</v>
+        <v>59.2</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -23092,65 +23088,61 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>60.2</v>
+        <v>42</v>
       </c>
       <c r="Q9" t="n">
-        <v>60.5</v>
+        <v>68.2</v>
       </c>
       <c r="R9" t="n">
-        <v>28.2</v>
+        <v>57.1</v>
       </c>
       <c r="S9" t="n">
-        <v>90.40000000000001</v>
+        <v>76.2</v>
       </c>
       <c r="T9" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="U9" t="n">
-        <v>16.1</v>
+        <v>54.7</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr"/>
@@ -23167,134 +23159,142 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/22, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.7% barrel, 4.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 15.5% barrel, 5.4 HR allowed</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>14.72</t>
+          <t>9.75</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>48.51</t>
+          <t>40.54</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>90.95</t>
+          <t>89.76</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>102.8018</t>
+          <t>100.2738</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>0.4833</t>
+          <t>0.4207</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>0.2277</t>
+          <t>0.1915</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>0.3551</t>
+          <t>0.3253</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>75.67</t>
+          <t>73.39</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>58.67</t>
+          <t>36.43</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>39.82</t>
+          <t>40.03</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>32.47</t>
+          <t>31.2</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>11.9</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>0.1937</t>
+          <t>0.1414</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>15.47</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>51.0</t>
+          <t>49.4</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>91.4</t>
+          <t>92.38</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>0.531</t>
+          <t>0.428</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.1845</t>
         </is>
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>28.8</t>
-        </is>
-      </c>
-      <c r="BG9" t="inlineStr"/>
-      <c r="BH9" t="inlineStr"/>
+          <t>32.53</t>
+        </is>
+      </c>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>Angel Stadium</t>
+          <t>Progressive Field</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr"/>
@@ -23906,7 +23906,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>58</v>
+        <v>57.9</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -23930,7 +23930,7 @@
         <v>68.2</v>
       </c>
       <c r="R12" t="n">
-        <v>57.6</v>
+        <v>57.1</v>
       </c>
       <c r="S12" t="n">
         <v>86.40000000000001</v>
@@ -24121,7 +24121,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>84</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -24210,7 +24210,7 @@
         <v>68.2</v>
       </c>
       <c r="R13" t="n">
-        <v>57.6</v>
+        <v>57.1</v>
       </c>
       <c r="S13" t="n">
         <v>64.3</v>
@@ -24401,7 +24401,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>84</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -25858,7 +25858,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>53.2</v>
+        <v>53.1</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -25882,7 +25882,7 @@
         <v>68.2</v>
       </c>
       <c r="R19" t="n">
-        <v>57.6</v>
+        <v>57.1</v>
       </c>
       <c r="S19" t="n">
         <v>100</v>
@@ -26073,7 +26073,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>84</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">

--- a/outputs/hr_rankings.xlsx
+++ b/outputs/hr_rankings.xlsx
@@ -826,34 +826,30 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3078,34 +3074,30 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -5058,34 +5050,30 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -5900,28 +5888,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W20" t="inlineStr"/>
-      <c r="X20" t="inlineStr"/>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="Y20" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB20" t="inlineStr"/>
       <c r="AC20" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8698,34 +8690,30 @@
       </c>
       <c r="W30" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y30" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB30" t="inlineStr"/>
       <c r="AC30" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -10950,34 +10938,30 @@
       </c>
       <c r="W38" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X38" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y38" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 5 vs RotoWire 7</t>
-        </is>
-      </c>
+      <c r="AB38" t="inlineStr"/>
       <c r="AC38" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -12638,34 +12622,30 @@
       </c>
       <c r="W44" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X44" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y44" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 9 vs RotoWire 5</t>
-        </is>
-      </c>
+      <c r="AB44" t="inlineStr"/>
       <c r="AC44" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -14602,34 +14582,30 @@
       </c>
       <c r="W51" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X51" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y51" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 7 vs RotoWire 9</t>
-        </is>
-      </c>
+      <c r="AB51" t="inlineStr"/>
       <c r="AC51" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -15164,28 +15140,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W53" t="inlineStr"/>
-      <c r="X53" t="inlineStr"/>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="Y53" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB53" t="inlineStr"/>
       <c r="AC53" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -16328,34 +16308,30 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -18580,34 +18556,30 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -20560,34 +20532,30 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -21402,28 +21370,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W20" t="inlineStr"/>
-      <c r="X20" t="inlineStr"/>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="Y20" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB20" t="inlineStr"/>
       <c r="AC20" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>

--- a/outputs/hr_rankings.xlsx
+++ b/outputs/hr_rankings.xlsx
@@ -2716,7 +2716,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>60.8</v>
+        <v>60.7</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -2749,7 +2749,7 @@
         <v>50</v>
       </c>
       <c r="U9" t="n">
-        <v>57.6</v>
+        <v>56.2</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
@@ -3820,7 +3820,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>60</v>
+        <v>59.9</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -3853,7 +3853,7 @@
         <v>80</v>
       </c>
       <c r="U13" t="n">
-        <v>97</v>
+        <v>94.7</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
@@ -3914,7 +3914,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
@@ -13431,27 +13431,27 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>663757</t>
+          <t>695670</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Trent Grisham</t>
+          <t>Harry Ford</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>WSH</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-07-20T23:05:00Z</t>
+          <t>2026-07-21T00:40:00Z</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -13461,22 +13461,22 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Braxton Ashcraft</t>
+          <t>Kyle Freeland</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>677952</t>
+          <t>607536</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L48" t="n">
@@ -13494,26 +13494,26 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P48" t="n">
-        <v>50.8</v>
+        <v>35.1</v>
       </c>
       <c r="Q48" t="n">
-        <v>30.1</v>
+        <v>61.8</v>
       </c>
       <c r="R48" t="n">
-        <v>38.2</v>
+        <v>38.7</v>
       </c>
       <c r="S48" t="n">
-        <v>88.7</v>
+        <v>71.7</v>
       </c>
       <c r="T48" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="U48" t="n">
-        <v>54.7</v>
+        <v>56.6</v>
       </c>
       <c r="V48" t="inlineStr">
         <is>
@@ -13527,7 +13527,7 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y48" t="inlineStr">
@@ -13564,139 +13564,139 @@
       </c>
       <c r="AG48" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI48" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Contact streak: 3/8 over last 2 games</t>
         </is>
       </c>
       <c r="AL48" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 5.6% barrel, 10.7 HR allowed</t>
+          <t>platoon edge; pitcher baseline 10.5% barrel, 19.2 HR allowed</t>
         </is>
       </c>
       <c r="AM48" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN48" t="inlineStr">
         <is>
-          <t>11.82</t>
+          <t>7.5</t>
         </is>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>47.1</t>
+          <t>38.31</t>
         </is>
       </c>
       <c r="AP48" t="inlineStr">
         <is>
-          <t>91.1</t>
+          <t>89.49</t>
         </is>
       </c>
       <c r="AQ48" t="inlineStr">
         <is>
-          <t>101.1264</t>
+          <t>96.3391</t>
         </is>
       </c>
       <c r="AR48" t="inlineStr">
         <is>
-          <t>0.4679</t>
+          <t>0.2995</t>
         </is>
       </c>
       <c r="AS48" t="inlineStr">
         <is>
-          <t>0.2122</t>
+          <t>0.1681</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr">
         <is>
-          <t>0.3609</t>
+          <t>0.253</t>
         </is>
       </c>
       <c r="AU48" t="inlineStr">
         <is>
-          <t>70.51</t>
+          <t>70.11</t>
         </is>
       </c>
       <c r="AV48" t="inlineStr">
         <is>
-          <t>8.63</t>
+          <t>19.63</t>
         </is>
       </c>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>44.93</t>
+          <t>7.5</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>31.75</t>
+          <t>61.69</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr">
         <is>
-          <t>17.2</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>0.1975</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="BA48" t="inlineStr">
         <is>
-          <t>5.61</t>
+          <t>10.52</t>
         </is>
       </c>
       <c r="BB48" t="inlineStr">
         <is>
-          <t>40.25</t>
+          <t>44.78</t>
         </is>
       </c>
       <c r="BC48" t="inlineStr">
         <is>
-          <t>89.61</t>
+          <t>90.96</t>
         </is>
       </c>
       <c r="BD48" t="inlineStr">
         <is>
-          <t>0.3542</t>
+          <t>0.4898</t>
         </is>
       </c>
       <c r="BE48" t="inlineStr">
         <is>
-          <t>0.1255</t>
+          <t>0.1994</t>
         </is>
       </c>
       <c r="BF48" t="inlineStr">
         <is>
-          <t>25.53</t>
+          <t>29.5</t>
         </is>
       </c>
       <c r="BG48" t="inlineStr"/>
       <c r="BH48" t="inlineStr"/>
       <c r="BI48" t="inlineStr">
         <is>
-          <t>Yankee Stadium</t>
+          <t>Coors Field</t>
         </is>
       </c>
       <c r="BJ48" t="inlineStr"/>
@@ -13707,27 +13707,27 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>695670</t>
+          <t>663757</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Harry Ford</t>
+          <t>Trent Grisham</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>WSH</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-07-21T00:40:00Z</t>
+          <t>2026-07-20T23:05:00Z</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -13737,26 +13737,26 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Kyle Freeland</t>
+          <t>Braxton Ashcraft</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>607536</t>
+          <t>677952</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L49" t="n">
-        <v>52.1</v>
+        <v>51.9</v>
       </c>
       <c r="M49" t="inlineStr">
         <is>
@@ -13770,26 +13770,26 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P49" t="n">
-        <v>35.1</v>
+        <v>50.8</v>
       </c>
       <c r="Q49" t="n">
-        <v>61.8</v>
+        <v>30.1</v>
       </c>
       <c r="R49" t="n">
-        <v>38.7</v>
+        <v>38.2</v>
       </c>
       <c r="S49" t="n">
-        <v>71.7</v>
+        <v>88.7</v>
       </c>
       <c r="T49" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U49" t="n">
-        <v>56.6</v>
+        <v>52</v>
       </c>
       <c r="V49" t="inlineStr">
         <is>
@@ -13803,7 +13803,7 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y49" t="inlineStr">
@@ -13840,139 +13840,139 @@
       </c>
       <c r="AG49" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AH49" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AI49" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AH49" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AI49" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AJ49" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AK49" t="inlineStr">
         <is>
-          <t>Contact streak: 3/8 over last 2 games</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL49" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 10.5% barrel, 19.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 5.6% barrel, 10.7 HR allowed</t>
         </is>
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN49" t="inlineStr">
         <is>
-          <t>7.5</t>
+          <t>11.82</t>
         </is>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>38.31</t>
+          <t>47.1</t>
         </is>
       </c>
       <c r="AP49" t="inlineStr">
         <is>
-          <t>89.49</t>
+          <t>91.1</t>
         </is>
       </c>
       <c r="AQ49" t="inlineStr">
         <is>
-          <t>96.3391</t>
+          <t>101.1264</t>
         </is>
       </c>
       <c r="AR49" t="inlineStr">
         <is>
-          <t>0.2995</t>
+          <t>0.4679</t>
         </is>
       </c>
       <c r="AS49" t="inlineStr">
         <is>
-          <t>0.1681</t>
+          <t>0.2122</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr">
         <is>
-          <t>0.253</t>
+          <t>0.3609</t>
         </is>
       </c>
       <c r="AU49" t="inlineStr">
         <is>
-          <t>70.11</t>
+          <t>70.51</t>
         </is>
       </c>
       <c r="AV49" t="inlineStr">
         <is>
-          <t>19.63</t>
+          <t>8.63</t>
         </is>
       </c>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>7.5</t>
+          <t>44.93</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>61.69</t>
+          <t>31.75</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>17.2</t>
         </is>
       </c>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.1975</t>
         </is>
       </c>
       <c r="BA49" t="inlineStr">
         <is>
-          <t>10.52</t>
+          <t>5.61</t>
         </is>
       </c>
       <c r="BB49" t="inlineStr">
         <is>
-          <t>44.78</t>
+          <t>40.25</t>
         </is>
       </c>
       <c r="BC49" t="inlineStr">
         <is>
-          <t>90.96</t>
+          <t>89.61</t>
         </is>
       </c>
       <c r="BD49" t="inlineStr">
         <is>
-          <t>0.4898</t>
+          <t>0.3542</t>
         </is>
       </c>
       <c r="BE49" t="inlineStr">
         <is>
-          <t>0.1994</t>
+          <t>0.1255</t>
         </is>
       </c>
       <c r="BF49" t="inlineStr">
         <is>
-          <t>29.5</t>
+          <t>25.53</t>
         </is>
       </c>
       <c r="BG49" t="inlineStr"/>
       <c r="BH49" t="inlineStr"/>
       <c r="BI49" t="inlineStr">
         <is>
-          <t>Coors Field</t>
+          <t>Yankee Stadium</t>
         </is>
       </c>
       <c r="BJ49" t="inlineStr"/>
@@ -18951,27 +18951,27 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>681624</t>
+          <t>643217</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Andy Pages</t>
+          <t>Andrew Benintendi</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-07-20T23:10:00Z</t>
+          <t>2026-07-21T00:05:00Z</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -18981,22 +18981,22 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Cristopher Sánchez</t>
+          <t>Jacob deGrom</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>650911</t>
+          <t>594798</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L68" t="n">
@@ -19014,26 +19014,26 @@
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P68" t="n">
-        <v>38.9</v>
+        <v>40.8</v>
       </c>
       <c r="Q68" t="n">
-        <v>35.9</v>
+        <v>49.8</v>
       </c>
       <c r="R68" t="n">
-        <v>34.3</v>
+        <v>27.6</v>
       </c>
       <c r="S68" t="n">
-        <v>95.5</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T68" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U68" t="n">
-        <v>50.3</v>
+        <v>26.1</v>
       </c>
       <c r="V68" t="inlineStr">
         <is>
@@ -19047,7 +19047,7 @@
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y68" t="inlineStr">
@@ -19089,134 +19089,134 @@
       </c>
       <c r="AH68" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI68" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK68" t="inlineStr">
         <is>
-          <t>Contact streak: 7/21 over last 7 games</t>
+          <t>Last 7 games: 5/17, 0 HR</t>
         </is>
       </c>
       <c r="AL68" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.9% barrel, 12.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.0% barrel, 19.0 HR allowed</t>
         </is>
       </c>
       <c r="AM68" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN68" t="inlineStr">
         <is>
-          <t>8.47</t>
+          <t>10.05</t>
         </is>
       </c>
       <c r="AO68" t="inlineStr">
         <is>
-          <t>42.59</t>
+          <t>45.02</t>
         </is>
       </c>
       <c r="AP68" t="inlineStr">
         <is>
-          <t>88.95</t>
+          <t>88.77</t>
         </is>
       </c>
       <c r="AQ68" t="inlineStr">
         <is>
-          <t>100.2268</t>
+          <t>98.9931</t>
         </is>
       </c>
       <c r="AR68" t="inlineStr">
         <is>
-          <t>0.4427</t>
+          <t>0.4328</t>
         </is>
       </c>
       <c r="AS68" t="inlineStr">
         <is>
-          <t>0.177</t>
+          <t>0.1837</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr">
         <is>
-          <t>0.3335</t>
+          <t>0.3249</t>
         </is>
       </c>
       <c r="AU68" t="inlineStr">
         <is>
-          <t>72.88</t>
+          <t>69.54</t>
         </is>
       </c>
       <c r="AV68" t="inlineStr">
         <is>
-          <t>26.89</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>36.5</t>
+          <t>52.48</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>29.49</t>
+          <t>31.78</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>0.196</t>
+          <t>0.184</t>
         </is>
       </c>
       <c r="BA68" t="inlineStr">
         <is>
-          <t>7.87</t>
+          <t>9.02</t>
         </is>
       </c>
       <c r="BB68" t="inlineStr">
         <is>
-          <t>42.6</t>
+          <t>43.37</t>
         </is>
       </c>
       <c r="BC68" t="inlineStr">
         <is>
-          <t>89.28</t>
+          <t>90.52</t>
         </is>
       </c>
       <c r="BD68" t="inlineStr">
         <is>
-          <t>0.3611</t>
+          <t>0.3945</t>
         </is>
       </c>
       <c r="BE68" t="inlineStr">
         <is>
-          <t>0.1312</t>
+          <t>0.1665</t>
         </is>
       </c>
       <c r="BF68" t="inlineStr">
         <is>
-          <t>18.09</t>
+          <t>30.09</t>
         </is>
       </c>
       <c r="BG68" t="inlineStr"/>
       <c r="BH68" t="inlineStr"/>
       <c r="BI68" t="inlineStr">
         <is>
-          <t>Citizens Bank Park</t>
+          <t>Globe Life Field</t>
         </is>
       </c>
       <c r="BJ68" t="inlineStr"/>
@@ -19227,27 +19227,27 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>643217</t>
+          <t>681624</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Andrew Benintendi</t>
+          <t>Andy Pages</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-07-21T00:05:00Z</t>
+          <t>2026-07-20T23:10:00Z</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -19257,26 +19257,26 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Jacob deGrom</t>
+          <t>Cristopher Sánchez</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>594798</t>
+          <t>650911</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L69" t="n">
-        <v>49.5</v>
+        <v>49.4</v>
       </c>
       <c r="M69" t="inlineStr">
         <is>
@@ -19290,26 +19290,26 @@
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P69" t="n">
-        <v>40.8</v>
+        <v>38.9</v>
       </c>
       <c r="Q69" t="n">
-        <v>49.8</v>
+        <v>35.9</v>
       </c>
       <c r="R69" t="n">
-        <v>27.6</v>
+        <v>34.3</v>
       </c>
       <c r="S69" t="n">
-        <v>81.90000000000001</v>
+        <v>95.5</v>
       </c>
       <c r="T69" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="U69" t="n">
-        <v>26.1</v>
+        <v>48.1</v>
       </c>
       <c r="V69" t="inlineStr">
         <is>
@@ -19323,7 +19323,7 @@
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y69" t="inlineStr">
@@ -19365,134 +19365,134 @@
       </c>
       <c r="AH69" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI69" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/17, 0 HR</t>
+          <t>Last 7 games: 7/22, 1 HR</t>
         </is>
       </c>
       <c r="AL69" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 9.0% barrel, 19.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.9% barrel, 12.0 HR allowed</t>
         </is>
       </c>
       <c r="AM69" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN69" t="inlineStr">
         <is>
-          <t>10.05</t>
+          <t>8.47</t>
         </is>
       </c>
       <c r="AO69" t="inlineStr">
         <is>
-          <t>45.02</t>
+          <t>42.59</t>
         </is>
       </c>
       <c r="AP69" t="inlineStr">
         <is>
-          <t>88.77</t>
+          <t>88.95</t>
         </is>
       </c>
       <c r="AQ69" t="inlineStr">
         <is>
-          <t>98.9931</t>
+          <t>100.2268</t>
         </is>
       </c>
       <c r="AR69" t="inlineStr">
         <is>
-          <t>0.4328</t>
+          <t>0.4427</t>
         </is>
       </c>
       <c r="AS69" t="inlineStr">
         <is>
-          <t>0.1837</t>
+          <t>0.177</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr">
         <is>
-          <t>0.3249</t>
+          <t>0.3335</t>
         </is>
       </c>
       <c r="AU69" t="inlineStr">
         <is>
-          <t>69.54</t>
+          <t>72.88</t>
         </is>
       </c>
       <c r="AV69" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>26.89</t>
         </is>
       </c>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>52.48</t>
+          <t>36.5</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>31.78</t>
+          <t>29.49</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>0.184</t>
+          <t>0.196</t>
         </is>
       </c>
       <c r="BA69" t="inlineStr">
         <is>
-          <t>9.02</t>
+          <t>7.87</t>
         </is>
       </c>
       <c r="BB69" t="inlineStr">
         <is>
-          <t>43.37</t>
+          <t>42.6</t>
         </is>
       </c>
       <c r="BC69" t="inlineStr">
         <is>
-          <t>90.52</t>
+          <t>89.28</t>
         </is>
       </c>
       <c r="BD69" t="inlineStr">
         <is>
-          <t>0.3945</t>
+          <t>0.3611</t>
         </is>
       </c>
       <c r="BE69" t="inlineStr">
         <is>
-          <t>0.1665</t>
+          <t>0.1312</t>
         </is>
       </c>
       <c r="BF69" t="inlineStr">
         <is>
-          <t>30.09</t>
+          <t>18.09</t>
         </is>
       </c>
       <c r="BG69" t="inlineStr"/>
       <c r="BH69" t="inlineStr"/>
       <c r="BI69" t="inlineStr">
         <is>
-          <t>Globe Life Field</t>
+          <t>Citizens Bank Park</t>
         </is>
       </c>
       <c r="BJ69" t="inlineStr"/>
@@ -24747,27 +24747,27 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>518692</t>
+          <t>671218</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Freddie Freeman</t>
+          <t>Heliot Ramos</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-07-20T23:10:00Z</t>
+          <t>2026-07-20T23:40:00Z</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -24777,22 +24777,22 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>Cristopher Sánchez</t>
+          <t>Michael Wacha</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>650911</t>
+          <t>608379</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L89" t="n">
@@ -24810,26 +24810,26 @@
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Projected Lineup, Strong Barrel</t>
         </is>
       </c>
       <c r="P89" t="n">
-        <v>47</v>
+        <v>54.9</v>
       </c>
       <c r="Q89" t="n">
-        <v>35.9</v>
+        <v>35.1</v>
       </c>
       <c r="R89" t="n">
-        <v>34.3</v>
+        <v>23.2</v>
       </c>
       <c r="S89" t="n">
-        <v>92.09999999999999</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T89" t="n">
         <v>50</v>
       </c>
       <c r="U89" t="n">
-        <v>8.1</v>
+        <v>22</v>
       </c>
       <c r="V89" t="inlineStr">
         <is>
@@ -24843,7 +24843,7 @@
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y89" t="inlineStr">
@@ -24885,12 +24885,12 @@
       </c>
       <c r="AH89" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI89" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AJ89" t="inlineStr">
@@ -24900,119 +24900,119 @@
       </c>
       <c r="AK89" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/23, 0 HR</t>
+          <t>Last 7 games: 8/30, 0 HR</t>
         </is>
       </c>
       <c r="AL89" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.9% barrel, 12.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.6% barrel, 14.3 HR allowed</t>
         </is>
       </c>
       <c r="AM89" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN89" t="inlineStr">
         <is>
-          <t>10.47</t>
+          <t>13.7</t>
         </is>
       </c>
       <c r="AO89" t="inlineStr">
         <is>
-          <t>45.14</t>
+          <t>49.22</t>
         </is>
       </c>
       <c r="AP89" t="inlineStr">
         <is>
-          <t>90.62</t>
+          <t>92.29</t>
         </is>
       </c>
       <c r="AQ89" t="inlineStr">
         <is>
-          <t>100.8553</t>
+          <t>103.2576</t>
         </is>
       </c>
       <c r="AR89" t="inlineStr">
         <is>
-          <t>0.4894</t>
+          <t>0.4674</t>
         </is>
       </c>
       <c r="AS89" t="inlineStr">
         <is>
-          <t>0.2063</t>
+          <t>0.2023</t>
         </is>
       </c>
       <c r="AT89" t="inlineStr">
         <is>
-          <t>0.371</t>
+          <t>0.334</t>
         </is>
       </c>
       <c r="AU89" t="inlineStr">
         <is>
-          <t>70.32</t>
+          <t>72.74</t>
         </is>
       </c>
       <c r="AV89" t="inlineStr">
         <is>
-          <t>8.96</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>36.33</t>
+          <t>35.34</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>29.45</t>
+          <t>23.86</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>11.9</t>
         </is>
       </c>
       <c r="AZ89" t="inlineStr">
         <is>
-          <t>0.1986</t>
+          <t>0.1734</t>
         </is>
       </c>
       <c r="BA89" t="inlineStr">
         <is>
-          <t>7.87</t>
+          <t>6.63</t>
         </is>
       </c>
       <c r="BB89" t="inlineStr">
         <is>
-          <t>42.6</t>
+          <t>35.86</t>
         </is>
       </c>
       <c r="BC89" t="inlineStr">
         <is>
-          <t>89.28</t>
+          <t>88.13</t>
         </is>
       </c>
       <c r="BD89" t="inlineStr">
         <is>
-          <t>0.3611</t>
+          <t>0.413</t>
         </is>
       </c>
       <c r="BE89" t="inlineStr">
         <is>
-          <t>0.1312</t>
+          <t>0.1605</t>
         </is>
       </c>
       <c r="BF89" t="inlineStr">
         <is>
-          <t>18.09</t>
+          <t>27.48</t>
         </is>
       </c>
       <c r="BG89" t="inlineStr"/>
       <c r="BH89" t="inlineStr"/>
       <c r="BI89" t="inlineStr">
         <is>
-          <t>Citizens Bank Park</t>
+          <t>Kauffman Stadium</t>
         </is>
       </c>
       <c r="BJ89" t="inlineStr"/>
@@ -25023,22 +25023,22 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>671218</t>
+          <t>668930</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Heliot Ramos</t>
+          <t>Brice Turang</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>NYM</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -25053,17 +25053,17 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>Michael Wacha</t>
+          <t>Freddy Peralta</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>608379</t>
+          <t>642547</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
@@ -25086,26 +25086,26 @@
       </c>
       <c r="O90" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P90" t="n">
-        <v>54.9</v>
+        <v>39.9</v>
       </c>
       <c r="Q90" t="n">
-        <v>35.1</v>
+        <v>31.8</v>
       </c>
       <c r="R90" t="n">
-        <v>23.2</v>
+        <v>27.6</v>
       </c>
       <c r="S90" t="n">
-        <v>81.90000000000001</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="T90" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U90" t="n">
-        <v>22</v>
+        <v>40.9</v>
       </c>
       <c r="V90" t="inlineStr">
         <is>
@@ -25119,7 +25119,7 @@
       </c>
       <c r="X90" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y90" t="inlineStr">
@@ -25161,134 +25161,134 @@
       </c>
       <c r="AH90" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI90" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK90" t="inlineStr">
         <is>
-          <t>Last 7 games: 8/30, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL90" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.6% barrel, 14.3 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.6% barrel, 16.8 HR allowed</t>
         </is>
       </c>
       <c r="AM90" t="inlineStr">
         <is>
-          <t>EV profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN90" t="inlineStr">
         <is>
-          <t>13.7</t>
+          <t>8.28</t>
         </is>
       </c>
       <c r="AO90" t="inlineStr">
         <is>
-          <t>49.22</t>
+          <t>45.23</t>
         </is>
       </c>
       <c r="AP90" t="inlineStr">
         <is>
-          <t>92.29</t>
+          <t>90.96</t>
         </is>
       </c>
       <c r="AQ90" t="inlineStr">
         <is>
-          <t>103.2576</t>
+          <t>100.6415</t>
         </is>
       </c>
       <c r="AR90" t="inlineStr">
         <is>
-          <t>0.4674</t>
+          <t>0.4381</t>
         </is>
       </c>
       <c r="AS90" t="inlineStr">
         <is>
-          <t>0.2023</t>
+          <t>0.1817</t>
         </is>
       </c>
       <c r="AT90" t="inlineStr">
         <is>
-          <t>0.334</t>
+          <t>0.3427</t>
         </is>
       </c>
       <c r="AU90" t="inlineStr">
         <is>
-          <t>72.74</t>
+          <t>70.18</t>
         </is>
       </c>
       <c r="AV90" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>12.22</t>
         </is>
       </c>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>35.34</t>
+          <t>27.3</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>23.86</t>
+          <t>24.48</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr">
         <is>
-          <t>11.9</t>
+          <t>15.2</t>
         </is>
       </c>
       <c r="AZ90" t="inlineStr">
         <is>
-          <t>0.1734</t>
+          <t>0.182</t>
         </is>
       </c>
       <c r="BA90" t="inlineStr">
         <is>
-          <t>6.63</t>
+          <t>6.57</t>
         </is>
       </c>
       <c r="BB90" t="inlineStr">
         <is>
-          <t>35.86</t>
+          <t>37.65</t>
         </is>
       </c>
       <c r="BC90" t="inlineStr">
         <is>
-          <t>88.13</t>
+          <t>87.86</t>
         </is>
       </c>
       <c r="BD90" t="inlineStr">
         <is>
-          <t>0.413</t>
+          <t>0.3624</t>
         </is>
       </c>
       <c r="BE90" t="inlineStr">
         <is>
-          <t>0.1605</t>
+          <t>0.1382</t>
         </is>
       </c>
       <c r="BF90" t="inlineStr">
         <is>
-          <t>27.48</t>
+          <t>27.01</t>
         </is>
       </c>
       <c r="BG90" t="inlineStr"/>
       <c r="BH90" t="inlineStr"/>
       <c r="BI90" t="inlineStr">
         <is>
-          <t>Kauffman Stadium</t>
+          <t>American Family Field</t>
         </is>
       </c>
       <c r="BJ90" t="inlineStr"/>
@@ -25299,27 +25299,27 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>668930</t>
+          <t>666160</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Brice Turang</t>
+          <t>Mickey Moniak</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>NYM</t>
+          <t>WSH</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-07-20T23:40:00Z</t>
+          <t>2026-07-21T00:40:00Z</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -25329,22 +25329,22 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>Freddy Peralta</t>
+          <t>Andrew Alvarez</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>642547</t>
+          <t>674841</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L91" t="n">
@@ -25362,26 +25362,26 @@
       </c>
       <c r="O91" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P91" t="n">
-        <v>39.9</v>
+        <v>52.7</v>
       </c>
       <c r="Q91" t="n">
-        <v>31.8</v>
+        <v>21.8</v>
       </c>
       <c r="R91" t="n">
-        <v>27.6</v>
+        <v>38.7</v>
       </c>
       <c r="S91" t="n">
-        <v>92.09999999999999</v>
+        <v>95.5</v>
       </c>
       <c r="T91" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U91" t="n">
-        <v>40.9</v>
+        <v>16.6</v>
       </c>
       <c r="V91" t="inlineStr">
         <is>
@@ -25395,7 +25395,7 @@
       </c>
       <c r="X91" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y91" t="inlineStr">
@@ -25437,134 +25437,134 @@
       </c>
       <c r="AH91" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI91" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 6/26, 0 HR</t>
         </is>
       </c>
       <c r="AL91" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.6% barrel, 16.8 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 4.5% barrel, 1.7 HR allowed</t>
         </is>
       </c>
       <c r="AM91" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN91" t="inlineStr">
         <is>
-          <t>8.28</t>
+          <t>12.47</t>
         </is>
       </c>
       <c r="AO91" t="inlineStr">
         <is>
-          <t>45.23</t>
+          <t>44.25</t>
         </is>
       </c>
       <c r="AP91" t="inlineStr">
         <is>
-          <t>90.96</t>
+          <t>89.77</t>
         </is>
       </c>
       <c r="AQ91" t="inlineStr">
         <is>
-          <t>100.6415</t>
+          <t>100.6203</t>
         </is>
       </c>
       <c r="AR91" t="inlineStr">
         <is>
-          <t>0.4381</t>
+          <t>0.4592</t>
         </is>
       </c>
       <c r="AS91" t="inlineStr">
         <is>
-          <t>0.1817</t>
+          <t>0.2196</t>
         </is>
       </c>
       <c r="AT91" t="inlineStr">
         <is>
-          <t>0.3427</t>
+          <t>0.3188</t>
         </is>
       </c>
       <c r="AU91" t="inlineStr">
         <is>
-          <t>70.18</t>
+          <t>74.15</t>
         </is>
       </c>
       <c r="AV91" t="inlineStr">
         <is>
-          <t>12.22</t>
+          <t>43.14</t>
         </is>
       </c>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>27.3</t>
+          <t>48.62</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>24.48</t>
+          <t>38.59</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr">
         <is>
-          <t>15.2</t>
+          <t>17.7</t>
         </is>
       </c>
       <c r="AZ91" t="inlineStr">
         <is>
-          <t>0.182</t>
+          <t>0.2746</t>
         </is>
       </c>
       <c r="BA91" t="inlineStr">
         <is>
-          <t>6.57</t>
+          <t>4.54</t>
         </is>
       </c>
       <c r="BB91" t="inlineStr">
         <is>
-          <t>37.65</t>
+          <t>41.29</t>
         </is>
       </c>
       <c r="BC91" t="inlineStr">
         <is>
-          <t>87.86</t>
+          <t>89.18</t>
         </is>
       </c>
       <c r="BD91" t="inlineStr">
         <is>
-          <t>0.3624</t>
+          <t>0.3479</t>
         </is>
       </c>
       <c r="BE91" t="inlineStr">
         <is>
-          <t>0.1382</t>
+          <t>0.1046</t>
         </is>
       </c>
       <c r="BF91" t="inlineStr">
         <is>
-          <t>27.01</t>
+          <t>14.19</t>
         </is>
       </c>
       <c r="BG91" t="inlineStr"/>
       <c r="BH91" t="inlineStr"/>
       <c r="BI91" t="inlineStr">
         <is>
-          <t>American Family Field</t>
+          <t>Coors Field</t>
         </is>
       </c>
       <c r="BJ91" t="inlineStr"/>
@@ -25575,27 +25575,27 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>666160</t>
+          <t>518692</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Mickey Moniak</t>
+          <t>Freddie Freeman</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>WSH</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-07-21T00:40:00Z</t>
+          <t>2026-07-20T23:10:00Z</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -25605,17 +25605,17 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>Andrew Alvarez</t>
+          <t>Cristopher Sánchez</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>674841</t>
+          <t>650911</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
@@ -25624,7 +25624,7 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>47.1</v>
+        <v>47</v>
       </c>
       <c r="M92" t="inlineStr">
         <is>
@@ -25642,22 +25642,22 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>52.7</v>
+        <v>47</v>
       </c>
       <c r="Q92" t="n">
-        <v>21.8</v>
+        <v>35.9</v>
       </c>
       <c r="R92" t="n">
-        <v>38.7</v>
+        <v>34.3</v>
       </c>
       <c r="S92" t="n">
-        <v>95.5</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="T92" t="n">
         <v>50</v>
       </c>
       <c r="U92" t="n">
-        <v>16.6</v>
+        <v>7</v>
       </c>
       <c r="V92" t="inlineStr">
         <is>
@@ -25671,7 +25671,7 @@
       </c>
       <c r="X92" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y92" t="inlineStr">
@@ -25713,12 +25713,12 @@
       </c>
       <c r="AH92" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI92" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ92" t="inlineStr">
@@ -25728,72 +25728,72 @@
       </c>
       <c r="AK92" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/26, 0 HR</t>
+          <t>Last 7 games: 4/24, 0 HR</t>
         </is>
       </c>
       <c r="AL92" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 4.5% barrel, 1.7 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.9% barrel, 12.0 HR allowed</t>
         </is>
       </c>
       <c r="AM92" t="inlineStr">
         <is>
-          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN92" t="inlineStr">
         <is>
-          <t>12.47</t>
+          <t>10.47</t>
         </is>
       </c>
       <c r="AO92" t="inlineStr">
         <is>
-          <t>44.25</t>
+          <t>45.14</t>
         </is>
       </c>
       <c r="AP92" t="inlineStr">
         <is>
-          <t>89.77</t>
+          <t>90.62</t>
         </is>
       </c>
       <c r="AQ92" t="inlineStr">
         <is>
-          <t>100.6203</t>
+          <t>100.8553</t>
         </is>
       </c>
       <c r="AR92" t="inlineStr">
         <is>
-          <t>0.4592</t>
+          <t>0.4894</t>
         </is>
       </c>
       <c r="AS92" t="inlineStr">
         <is>
-          <t>0.2196</t>
+          <t>0.2063</t>
         </is>
       </c>
       <c r="AT92" t="inlineStr">
         <is>
-          <t>0.3188</t>
+          <t>0.371</t>
         </is>
       </c>
       <c r="AU92" t="inlineStr">
         <is>
-          <t>74.15</t>
+          <t>70.32</t>
         </is>
       </c>
       <c r="AV92" t="inlineStr">
         <is>
-          <t>43.14</t>
+          <t>8.96</t>
         </is>
       </c>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>48.62</t>
+          <t>36.33</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>38.59</t>
+          <t>29.45</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr">
@@ -25803,44 +25803,44 @@
       </c>
       <c r="AZ92" t="inlineStr">
         <is>
-          <t>0.2746</t>
+          <t>0.1986</t>
         </is>
       </c>
       <c r="BA92" t="inlineStr">
         <is>
-          <t>4.54</t>
+          <t>7.87</t>
         </is>
       </c>
       <c r="BB92" t="inlineStr">
         <is>
-          <t>41.29</t>
+          <t>42.6</t>
         </is>
       </c>
       <c r="BC92" t="inlineStr">
         <is>
-          <t>89.18</t>
+          <t>89.28</t>
         </is>
       </c>
       <c r="BD92" t="inlineStr">
         <is>
-          <t>0.3479</t>
+          <t>0.3611</t>
         </is>
       </c>
       <c r="BE92" t="inlineStr">
         <is>
-          <t>0.1046</t>
+          <t>0.1312</t>
         </is>
       </c>
       <c r="BF92" t="inlineStr">
         <is>
-          <t>14.19</t>
+          <t>18.09</t>
         </is>
       </c>
       <c r="BG92" t="inlineStr"/>
       <c r="BH92" t="inlineStr"/>
       <c r="BI92" t="inlineStr">
         <is>
-          <t>Coors Field</t>
+          <t>Citizens Bank Park</t>
         </is>
       </c>
       <c r="BJ92" t="inlineStr"/>
@@ -26403,27 +26403,27 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>665489</t>
+          <t>665862</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Vladimir Guerrero</t>
+          <t>Jazz Chisholm</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-07-20T23:07:00Z</t>
+          <t>2026-07-20T23:05:00Z</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -26433,17 +26433,17 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>Nick Martinez</t>
+          <t>Braxton Ashcraft</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>607259</t>
+          <t>677952</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
@@ -26466,26 +26466,26 @@
       </c>
       <c r="O95" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P95" t="n">
-        <v>40.9</v>
+        <v>42.5</v>
       </c>
       <c r="Q95" t="n">
-        <v>35.5</v>
+        <v>30.1</v>
       </c>
       <c r="R95" t="n">
-        <v>30.4</v>
+        <v>38.2</v>
       </c>
       <c r="S95" t="n">
-        <v>92.09999999999999</v>
+        <v>71.7</v>
       </c>
       <c r="T95" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U95" t="n">
-        <v>57.6</v>
+        <v>53.3</v>
       </c>
       <c r="V95" t="inlineStr">
         <is>
@@ -26499,7 +26499,7 @@
       </c>
       <c r="X95" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y95" t="inlineStr">
@@ -26541,12 +26541,12 @@
       </c>
       <c r="AH95" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI95" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ95" t="inlineStr">
@@ -26561,7 +26561,7 @@
       </c>
       <c r="AL95" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.2% barrel, 14.3 HR allowed</t>
+          <t>platoon edge; pitcher baseline 5.6% barrel, 10.7 HR allowed</t>
         </is>
       </c>
       <c r="AM95" t="inlineStr">
@@ -26571,104 +26571,104 @@
       </c>
       <c r="AN95" t="inlineStr">
         <is>
-          <t>8.63</t>
+          <t>10.59</t>
         </is>
       </c>
       <c r="AO95" t="inlineStr">
         <is>
-          <t>46.57</t>
+          <t>41.76</t>
         </is>
       </c>
       <c r="AP95" t="inlineStr">
         <is>
-          <t>90.67</t>
+          <t>90.26</t>
         </is>
       </c>
       <c r="AQ95" t="inlineStr">
         <is>
-          <t>103.2609</t>
+          <t>100.3793</t>
         </is>
       </c>
       <c r="AR95" t="inlineStr">
         <is>
-          <t>0.443</t>
+          <t>0.3977</t>
         </is>
       </c>
       <c r="AS95" t="inlineStr">
         <is>
-          <t>0.1486</t>
+          <t>0.1805</t>
         </is>
       </c>
       <c r="AT95" t="inlineStr">
         <is>
-          <t>0.3588</t>
+          <t>0.3075</t>
         </is>
       </c>
       <c r="AU95" t="inlineStr">
         <is>
-          <t>76.28</t>
+          <t>73.34</t>
         </is>
       </c>
       <c r="AV95" t="inlineStr">
         <is>
-          <t>63.43</t>
+          <t>34.41</t>
         </is>
       </c>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>35.95</t>
+          <t>52.68</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>18.68</t>
+          <t>29.49</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr">
         <is>
-          <t>11.1</t>
+          <t>18.4</t>
         </is>
       </c>
       <c r="AZ95" t="inlineStr">
         <is>
-          <t>0.1204</t>
+          <t>0.1907</t>
         </is>
       </c>
       <c r="BA95" t="inlineStr">
         <is>
-          <t>7.21</t>
+          <t>5.61</t>
         </is>
       </c>
       <c r="BB95" t="inlineStr">
         <is>
-          <t>33.73</t>
+          <t>40.25</t>
         </is>
       </c>
       <c r="BC95" t="inlineStr">
         <is>
-          <t>87.46</t>
+          <t>89.61</t>
         </is>
       </c>
       <c r="BD95" t="inlineStr">
         <is>
-          <t>0.4338</t>
+          <t>0.3542</t>
         </is>
       </c>
       <c r="BE95" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.1255</t>
         </is>
       </c>
       <c r="BF95" t="inlineStr">
         <is>
-          <t>27.84</t>
+          <t>25.53</t>
         </is>
       </c>
       <c r="BG95" t="inlineStr"/>
       <c r="BH95" t="inlineStr"/>
       <c r="BI95" t="inlineStr">
         <is>
-          <t>Rogers Centre</t>
+          <t>Yankee Stadium</t>
         </is>
       </c>
       <c r="BJ95" t="inlineStr"/>
@@ -26679,27 +26679,27 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>803011</t>
+          <t>665489</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Sam Antonacci</t>
+          <t>Vladimir Guerrero</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-07-21T00:05:00Z</t>
+          <t>2026-07-20T23:07:00Z</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -26709,17 +26709,17 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>Jacob deGrom</t>
+          <t>Nick Martinez</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>594798</t>
+          <t>607259</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
@@ -26728,7 +26728,7 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>46.7</v>
+        <v>46.9</v>
       </c>
       <c r="M96" t="inlineStr">
         <is>
@@ -26742,26 +26742,26 @@
       </c>
       <c r="O96" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P96" t="n">
-        <v>26.2</v>
+        <v>40.9</v>
       </c>
       <c r="Q96" t="n">
-        <v>49.8</v>
+        <v>35.5</v>
       </c>
       <c r="R96" t="n">
-        <v>27.6</v>
+        <v>30.4</v>
       </c>
       <c r="S96" t="n">
-        <v>88.7</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="T96" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U96" t="n">
-        <v>46.4</v>
+        <v>57.6</v>
       </c>
       <c r="V96" t="inlineStr">
         <is>
@@ -26775,7 +26775,7 @@
       </c>
       <c r="X96" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y96" t="inlineStr">
@@ -26800,7 +26800,7 @@
       </c>
       <c r="AC96" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD96" t="inlineStr"/>
@@ -26817,7 +26817,7 @@
       </c>
       <c r="AH96" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI96" t="inlineStr">
@@ -26837,114 +26837,114 @@
       </c>
       <c r="AL96" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 9.0% barrel, 19.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.2% barrel, 14.3 HR allowed</t>
         </is>
       </c>
       <c r="AM96" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN96" t="inlineStr">
         <is>
-          <t>6.7</t>
+          <t>8.63</t>
         </is>
       </c>
       <c r="AO96" t="inlineStr">
         <is>
-          <t>37.1</t>
+          <t>46.57</t>
         </is>
       </c>
       <c r="AP96" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>90.67</t>
         </is>
       </c>
       <c r="AQ96" t="inlineStr">
         <is>
-          <t>98.3371</t>
+          <t>103.2609</t>
         </is>
       </c>
       <c r="AR96" t="inlineStr">
         <is>
-          <t>0.433</t>
+          <t>0.443</t>
         </is>
       </c>
       <c r="AS96" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>0.1486</t>
         </is>
       </c>
       <c r="AT96" t="inlineStr">
         <is>
-          <t>0.363</t>
+          <t>0.3588</t>
         </is>
       </c>
       <c r="AU96" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>76.28</t>
         </is>
       </c>
       <c r="AV96" t="inlineStr">
         <is>
-          <t>9.1</t>
+          <t>63.43</t>
         </is>
       </c>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>32.9</t>
+          <t>35.95</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>22.7</t>
+          <t>18.68</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>11.1</t>
         </is>
       </c>
       <c r="AZ96" t="inlineStr">
         <is>
-          <t>0.137</t>
+          <t>0.1204</t>
         </is>
       </c>
       <c r="BA96" t="inlineStr">
         <is>
-          <t>9.02</t>
+          <t>7.21</t>
         </is>
       </c>
       <c r="BB96" t="inlineStr">
         <is>
-          <t>43.37</t>
+          <t>33.73</t>
         </is>
       </c>
       <c r="BC96" t="inlineStr">
         <is>
-          <t>90.52</t>
+          <t>87.46</t>
         </is>
       </c>
       <c r="BD96" t="inlineStr">
         <is>
-          <t>0.3945</t>
+          <t>0.4338</t>
         </is>
       </c>
       <c r="BE96" t="inlineStr">
         <is>
-          <t>0.1665</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="BF96" t="inlineStr">
         <is>
-          <t>30.09</t>
+          <t>27.84</t>
         </is>
       </c>
       <c r="BG96" t="inlineStr"/>
       <c r="BH96" t="inlineStr"/>
       <c r="BI96" t="inlineStr">
         <is>
-          <t>Globe Life Field</t>
+          <t>Rogers Centre</t>
         </is>
       </c>
       <c r="BJ96" t="inlineStr"/>
@@ -26955,27 +26955,27 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>695600</t>
+          <t>803011</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Carter Jensen</t>
+          <t>Sam Antonacci</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-07-20T23:40:00Z</t>
+          <t>2026-07-21T00:05:00Z</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -26990,12 +26990,12 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>Trevor McDonald</t>
+          <t>Jacob deGrom</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>686790</t>
+          <t>594798</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
@@ -27004,7 +27004,7 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>46.5</v>
+        <v>46.7</v>
       </c>
       <c r="M97" t="inlineStr">
         <is>
@@ -27018,17 +27018,17 @@
       </c>
       <c r="O97" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P97" t="n">
-        <v>53.4</v>
+        <v>26.2</v>
       </c>
       <c r="Q97" t="n">
-        <v>20.3</v>
+        <v>49.8</v>
       </c>
       <c r="R97" t="n">
-        <v>23.2</v>
+        <v>27.6</v>
       </c>
       <c r="S97" t="n">
         <v>88.7</v>
@@ -27037,7 +27037,7 @@
         <v>80</v>
       </c>
       <c r="U97" t="n">
-        <v>18</v>
+        <v>46.4</v>
       </c>
       <c r="V97" t="inlineStr">
         <is>
@@ -27076,7 +27076,7 @@
       </c>
       <c r="AC97" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD97" t="inlineStr"/>
@@ -27093,134 +27093,134 @@
       </c>
       <c r="AH97" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI97" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/25, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL97" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 4.1% barrel, 4.5 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.0% barrel, 19.0 HR allowed</t>
         </is>
       </c>
       <c r="AM97" t="inlineStr">
         <is>
-          <t>EV profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN97" t="inlineStr">
         <is>
-          <t>12.61</t>
+          <t>6.7</t>
         </is>
       </c>
       <c r="AO97" t="inlineStr">
         <is>
-          <t>47.73</t>
+          <t>37.1</t>
         </is>
       </c>
       <c r="AP97" t="inlineStr">
         <is>
-          <t>92.04</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AQ97" t="inlineStr">
         <is>
-          <t>102.8609</t>
+          <t>98.3371</t>
         </is>
       </c>
       <c r="AR97" t="inlineStr">
         <is>
-          <t>0.4468</t>
+          <t>0.433</t>
         </is>
       </c>
       <c r="AS97" t="inlineStr">
         <is>
-          <t>0.1976</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="AT97" t="inlineStr">
         <is>
-          <t>0.3357</t>
+          <t>0.363</t>
         </is>
       </c>
       <c r="AU97" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="AV97" t="inlineStr">
         <is>
-          <t>40.5</t>
+          <t>9.1</t>
         </is>
       </c>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>39.25</t>
+          <t>32.9</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>29.51</t>
+          <t>22.7</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="AZ97" t="inlineStr">
         <is>
-          <t>0.2073</t>
+          <t>0.137</t>
         </is>
       </c>
       <c r="BA97" t="inlineStr">
         <is>
-          <t>4.08</t>
+          <t>9.02</t>
         </is>
       </c>
       <c r="BB97" t="inlineStr">
         <is>
-          <t>37.9</t>
+          <t>43.37</t>
         </is>
       </c>
       <c r="BC97" t="inlineStr">
         <is>
-          <t>89.09</t>
+          <t>90.52</t>
         </is>
       </c>
       <c r="BD97" t="inlineStr">
         <is>
-          <t>0.3571</t>
+          <t>0.3945</t>
         </is>
       </c>
       <c r="BE97" t="inlineStr">
         <is>
-          <t>0.1101</t>
+          <t>0.1665</t>
         </is>
       </c>
       <c r="BF97" t="inlineStr">
         <is>
-          <t>16.74</t>
+          <t>30.09</t>
         </is>
       </c>
       <c r="BG97" t="inlineStr"/>
       <c r="BH97" t="inlineStr"/>
       <c r="BI97" t="inlineStr">
         <is>
-          <t>Kauffman Stadium</t>
+          <t>Globe Life Field</t>
         </is>
       </c>
       <c r="BJ97" t="inlineStr"/>
@@ -27231,27 +27231,27 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>672356</t>
+          <t>695600</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Gabriel Arias</t>
+          <t>Carter Jensen</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-07-20T22:40:00Z</t>
+          <t>2026-07-20T23:40:00Z</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -27261,17 +27261,17 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>Joe Ryan</t>
+          <t>Trevor McDonald</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>657746</t>
+          <t>686790</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
@@ -27280,7 +27280,7 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>46.3</v>
+        <v>46.5</v>
       </c>
       <c r="M98" t="inlineStr">
         <is>
@@ -27294,26 +27294,26 @@
       </c>
       <c r="O98" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P98" t="n">
-        <v>45.9</v>
+        <v>53.4</v>
       </c>
       <c r="Q98" t="n">
-        <v>49.8</v>
+        <v>20.3</v>
       </c>
       <c r="R98" t="n">
-        <v>27.6</v>
+        <v>23.2</v>
       </c>
       <c r="S98" t="n">
-        <v>59.8</v>
+        <v>88.7</v>
       </c>
       <c r="T98" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U98" t="n">
-        <v>43.2</v>
+        <v>18</v>
       </c>
       <c r="V98" t="inlineStr">
         <is>
@@ -27327,7 +27327,7 @@
       </c>
       <c r="X98" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y98" t="inlineStr">
@@ -27374,129 +27374,129 @@
       </c>
       <c r="AI98" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK98" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/21, 1 HR</t>
+          <t>Last 7 games: 6/25, 0 HR</t>
         </is>
       </c>
       <c r="AL98" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 10.9% barrel, 14.8 HR allowed</t>
+          <t>platoon edge; pitcher baseline 4.1% barrel, 4.5 HR allowed</t>
         </is>
       </c>
       <c r="AM98" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN98" t="inlineStr">
         <is>
-          <t>11.3</t>
+          <t>12.61</t>
         </is>
       </c>
       <c r="AO98" t="inlineStr">
         <is>
-          <t>47.36</t>
+          <t>47.73</t>
         </is>
       </c>
       <c r="AP98" t="inlineStr">
         <is>
-          <t>91.11</t>
+          <t>92.04</t>
         </is>
       </c>
       <c r="AQ98" t="inlineStr">
         <is>
-          <t>103.0932</t>
+          <t>102.8609</t>
         </is>
       </c>
       <c r="AR98" t="inlineStr">
         <is>
-          <t>0.4032</t>
+          <t>0.4468</t>
         </is>
       </c>
       <c r="AS98" t="inlineStr">
         <is>
-          <t>0.1794</t>
+          <t>0.1976</t>
         </is>
       </c>
       <c r="AT98" t="inlineStr">
         <is>
-          <t>0.2874</t>
+          <t>0.3357</t>
         </is>
       </c>
       <c r="AU98" t="inlineStr">
         <is>
-          <t>74.68</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="AV98" t="inlineStr">
         <is>
-          <t>46.89</t>
+          <t>40.5</t>
         </is>
       </c>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>36.52</t>
+          <t>39.25</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>19.68</t>
+          <t>29.51</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr">
         <is>
-          <t>6.8</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="AZ98" t="inlineStr">
         <is>
-          <t>0.1654</t>
+          <t>0.2073</t>
         </is>
       </c>
       <c r="BA98" t="inlineStr">
         <is>
-          <t>10.87</t>
+          <t>4.08</t>
         </is>
       </c>
       <c r="BB98" t="inlineStr">
         <is>
-          <t>41.83</t>
+          <t>37.9</t>
         </is>
       </c>
       <c r="BC98" t="inlineStr">
         <is>
-          <t>89.71</t>
+          <t>89.09</t>
         </is>
       </c>
       <c r="BD98" t="inlineStr">
         <is>
-          <t>0.3746</t>
+          <t>0.3571</t>
         </is>
       </c>
       <c r="BE98" t="inlineStr">
         <is>
-          <t>0.1614</t>
+          <t>0.1101</t>
         </is>
       </c>
       <c r="BF98" t="inlineStr">
         <is>
-          <t>29.33</t>
+          <t>16.74</t>
         </is>
       </c>
       <c r="BG98" t="inlineStr"/>
       <c r="BH98" t="inlineStr"/>
       <c r="BI98" t="inlineStr">
         <is>
-          <t>Progressive Field</t>
+          <t>Kauffman Stadium</t>
         </is>
       </c>
       <c r="BJ98" t="inlineStr"/>
@@ -27507,27 +27507,27 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>656811</t>
+          <t>672356</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Ryan O'Hearn</t>
+          <t>Gabriel Arias</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-07-20T23:05:00Z</t>
+          <t>2026-07-20T22:40:00Z</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -27537,26 +27537,26 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>Ryan Weathers</t>
+          <t>Joe Ryan</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>677960</t>
+          <t>657746</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L99" t="n">
-        <v>46.2</v>
+        <v>46.3</v>
       </c>
       <c r="M99" t="inlineStr">
         <is>
@@ -27570,26 +27570,26 @@
       </c>
       <c r="O99" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Strong Barrel</t>
         </is>
       </c>
       <c r="P99" t="n">
-        <v>37.2</v>
+        <v>45.9</v>
       </c>
       <c r="Q99" t="n">
-        <v>50.8</v>
+        <v>49.8</v>
       </c>
       <c r="R99" t="n">
-        <v>38.2</v>
+        <v>27.6</v>
       </c>
       <c r="S99" t="n">
-        <v>81.90000000000001</v>
+        <v>59.8</v>
       </c>
       <c r="T99" t="n">
         <v>50</v>
       </c>
       <c r="U99" t="n">
-        <v>0</v>
+        <v>43.2</v>
       </c>
       <c r="V99" t="inlineStr">
         <is>
@@ -27603,7 +27603,7 @@
       </c>
       <c r="X99" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y99" t="inlineStr">
@@ -27645,27 +27645,27 @@
       </c>
       <c r="AH99" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI99" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/22, 0 HR</t>
+          <t>Last 7 games: 6/21, 1 HR</t>
         </is>
       </c>
       <c r="AL99" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 9.9% barrel, 13.3 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 10.9% barrel, 14.8 HR allowed</t>
         </is>
       </c>
       <c r="AM99" t="inlineStr">
@@ -27675,104 +27675,104 @@
       </c>
       <c r="AN99" t="inlineStr">
         <is>
-          <t>7.81</t>
+          <t>11.3</t>
         </is>
       </c>
       <c r="AO99" t="inlineStr">
         <is>
-          <t>44.67</t>
+          <t>47.36</t>
         </is>
       </c>
       <c r="AP99" t="inlineStr">
         <is>
-          <t>89.68</t>
+          <t>91.11</t>
         </is>
       </c>
       <c r="AQ99" t="inlineStr">
         <is>
-          <t>99.5988</t>
+          <t>103.0932</t>
         </is>
       </c>
       <c r="AR99" t="inlineStr">
         <is>
-          <t>0.4246</t>
+          <t>0.4032</t>
         </is>
       </c>
       <c r="AS99" t="inlineStr">
         <is>
-          <t>0.1642</t>
+          <t>0.1794</t>
         </is>
       </c>
       <c r="AT99" t="inlineStr">
         <is>
-          <t>0.3323</t>
+          <t>0.2874</t>
         </is>
       </c>
       <c r="AU99" t="inlineStr">
         <is>
-          <t>71.1</t>
+          <t>74.68</t>
         </is>
       </c>
       <c r="AV99" t="inlineStr">
         <is>
-          <t>11.85</t>
+          <t>46.89</t>
         </is>
       </c>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>37.47</t>
+          <t>36.52</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>29.41</t>
+          <t>19.68</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr">
         <is>
-          <t>16.3</t>
+          <t>6.8</t>
         </is>
       </c>
       <c r="AZ99" t="inlineStr">
         <is>
-          <t>0.184</t>
+          <t>0.1654</t>
         </is>
       </c>
       <c r="BA99" t="inlineStr">
         <is>
-          <t>9.95</t>
+          <t>10.87</t>
         </is>
       </c>
       <c r="BB99" t="inlineStr">
         <is>
-          <t>41.71</t>
+          <t>41.83</t>
         </is>
       </c>
       <c r="BC99" t="inlineStr">
         <is>
-          <t>89.6</t>
+          <t>89.71</t>
         </is>
       </c>
       <c r="BD99" t="inlineStr">
         <is>
-          <t>0.4327</t>
+          <t>0.3746</t>
         </is>
       </c>
       <c r="BE99" t="inlineStr">
         <is>
-          <t>0.1848</t>
+          <t>0.1614</t>
         </is>
       </c>
       <c r="BF99" t="inlineStr">
         <is>
-          <t>27.16</t>
+          <t>29.33</t>
         </is>
       </c>
       <c r="BG99" t="inlineStr"/>
       <c r="BH99" t="inlineStr"/>
       <c r="BI99" t="inlineStr">
         <is>
-          <t>Yankee Stadium</t>
+          <t>Progressive Field</t>
         </is>
       </c>
       <c r="BJ99" t="inlineStr"/>
@@ -27783,27 +27783,27 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>676551</t>
+          <t>656811</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Brewer Hicklen</t>
+          <t>Ryan O'Hearn</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-07-20T23:15:00Z</t>
+          <t>2026-07-20T23:05:00Z</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -27813,17 +27813,17 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>JP Sears</t>
+          <t>Ryan Weathers</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>676664</t>
+          <t>677960</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
@@ -27832,7 +27832,7 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>46</v>
+        <v>46.2</v>
       </c>
       <c r="M100" t="inlineStr">
         <is>
@@ -27846,26 +27846,26 @@
       </c>
       <c r="O100" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P100" t="n">
-        <v>40.2</v>
+        <v>37.2</v>
       </c>
       <c r="Q100" t="n">
-        <v>55.2</v>
+        <v>50.8</v>
       </c>
       <c r="R100" t="n">
-        <v>30.9</v>
+        <v>38.2</v>
       </c>
       <c r="S100" t="n">
-        <v>40.2</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T100" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U100" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="V100" t="inlineStr">
         <is>
@@ -27879,7 +27879,7 @@
       </c>
       <c r="X100" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y100" t="inlineStr">
@@ -27916,17 +27916,17 @@
       </c>
       <c r="AG100" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AH100" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI100" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ100" t="inlineStr">
@@ -27936,119 +27936,119 @@
       </c>
       <c r="AK100" t="inlineStr">
         <is>
-          <t>Contact streak: 5/11 over last 3 games</t>
+          <t>Last 7 games: 2/22, 0 HR</t>
         </is>
       </c>
       <c r="AL100" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.6% barrel, 11.8 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 9.9% barrel, 13.3 HR allowed</t>
         </is>
       </c>
       <c r="AM100" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN100" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>7.81</t>
         </is>
       </c>
       <c r="AO100" t="inlineStr">
         <is>
-          <t>38.31</t>
+          <t>44.67</t>
         </is>
       </c>
       <c r="AP100" t="inlineStr">
         <is>
-          <t>91.98</t>
+          <t>89.68</t>
         </is>
       </c>
       <c r="AQ100" t="inlineStr">
         <is>
-          <t>103.1078</t>
+          <t>99.5988</t>
         </is>
       </c>
       <c r="AR100" t="inlineStr">
         <is>
-          <t>0.3363</t>
+          <t>0.4246</t>
         </is>
       </c>
       <c r="AS100" t="inlineStr">
         <is>
-          <t>0.1114</t>
+          <t>0.1642</t>
         </is>
       </c>
       <c r="AT100" t="inlineStr">
         <is>
-          <t>0.3089</t>
+          <t>0.3323</t>
         </is>
       </c>
       <c r="AU100" t="inlineStr">
         <is>
-          <t>72.11</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="AV100" t="inlineStr">
         <is>
-          <t>24.97</t>
+          <t>11.85</t>
         </is>
       </c>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>35.0</t>
+          <t>37.47</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>11.69</t>
+          <t>29.41</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>16.3</t>
         </is>
       </c>
       <c r="AZ100" t="inlineStr">
         <is>
-          <t>0.175</t>
+          <t>0.184</t>
         </is>
       </c>
       <c r="BA100" t="inlineStr">
         <is>
-          <t>8.63</t>
+          <t>9.95</t>
         </is>
       </c>
       <c r="BB100" t="inlineStr">
         <is>
-          <t>45.07</t>
+          <t>41.71</t>
         </is>
       </c>
       <c r="BC100" t="inlineStr">
         <is>
-          <t>90.6</t>
+          <t>89.6</t>
         </is>
       </c>
       <c r="BD100" t="inlineStr">
         <is>
-          <t>0.4621</t>
+          <t>0.4327</t>
         </is>
       </c>
       <c r="BE100" t="inlineStr">
         <is>
-          <t>0.1966</t>
+          <t>0.1848</t>
         </is>
       </c>
       <c r="BF100" t="inlineStr">
         <is>
-          <t>36.25</t>
+          <t>27.16</t>
         </is>
       </c>
       <c r="BG100" t="inlineStr"/>
       <c r="BH100" t="inlineStr"/>
       <c r="BI100" t="inlineStr">
         <is>
-          <t>Truist Park</t>
+          <t>Yankee Stadium</t>
         </is>
       </c>
       <c r="BJ100" t="inlineStr"/>
@@ -28059,27 +28059,27 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>691777</t>
+          <t>676551</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Max Muncy</t>
+          <t>Brewer Hicklen</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-07-20T23:10:00Z</t>
+          <t>2026-07-20T23:15:00Z</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -28089,17 +28089,17 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>Cristopher Sánchez</t>
+          <t>JP Sears</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>650911</t>
+          <t>676664</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
@@ -28108,7 +28108,7 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>45.9</v>
+        <v>46</v>
       </c>
       <c r="M101" t="inlineStr">
         <is>
@@ -28126,22 +28126,22 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>39.2</v>
+        <v>40.2</v>
       </c>
       <c r="Q101" t="n">
-        <v>35.9</v>
+        <v>55.2</v>
       </c>
       <c r="R101" t="n">
-        <v>34.3</v>
+        <v>30.9</v>
       </c>
       <c r="S101" t="n">
-        <v>81.90000000000001</v>
+        <v>40.2</v>
       </c>
       <c r="T101" t="n">
         <v>78</v>
       </c>
       <c r="U101" t="n">
-        <v>14.6</v>
+        <v>45</v>
       </c>
       <c r="V101" t="inlineStr">
         <is>
@@ -28155,7 +28155,7 @@
       </c>
       <c r="X101" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y101" t="inlineStr">
@@ -28175,7 +28175,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed; order MLB 5 vs RotoWire 8</t>
+          <t>lineup projected / unconfirmed</t>
         </is>
       </c>
       <c r="AC101" t="inlineStr">
@@ -28192,7 +28192,7 @@
       </c>
       <c r="AG101" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AH101" t="inlineStr">
@@ -28202,7 +28202,7 @@
       </c>
       <c r="AI101" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AJ101" t="inlineStr">
@@ -28212,119 +28212,119 @@
       </c>
       <c r="AK101" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/23, 0 HR</t>
+          <t>Contact streak: 5/11 over last 3 games</t>
         </is>
       </c>
       <c r="AL101" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.9% barrel, 12.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.6% barrel, 11.8 HR allowed</t>
         </is>
       </c>
       <c r="AM101" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN101" t="inlineStr">
         <is>
-          <t>10.8</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="AO101" t="inlineStr">
         <is>
-          <t>43.67</t>
+          <t>38.31</t>
         </is>
       </c>
       <c r="AP101" t="inlineStr">
         <is>
-          <t>89.69</t>
+          <t>91.98</t>
         </is>
       </c>
       <c r="AQ101" t="inlineStr">
         <is>
-          <t>101.5962</t>
+          <t>103.1078</t>
         </is>
       </c>
       <c r="AR101" t="inlineStr">
         <is>
-          <t>0.3663</t>
+          <t>0.3363</t>
         </is>
       </c>
       <c r="AS101" t="inlineStr">
         <is>
-          <t>0.1528</t>
+          <t>0.1114</t>
         </is>
       </c>
       <c r="AT101" t="inlineStr">
         <is>
-          <t>0.2866</t>
+          <t>0.3089</t>
         </is>
       </c>
       <c r="AU101" t="inlineStr">
         <is>
-          <t>74.08</t>
+          <t>72.11</t>
         </is>
       </c>
       <c r="AV101" t="inlineStr">
         <is>
-          <t>44.98</t>
+          <t>24.97</t>
         </is>
       </c>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>43.1</t>
+          <t>35.0</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>23.63</t>
+          <t>11.69</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr">
         <is>
-          <t>6.2</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ101" t="inlineStr">
         <is>
-          <t>0.1678</t>
+          <t>0.175</t>
         </is>
       </c>
       <c r="BA101" t="inlineStr">
         <is>
-          <t>7.87</t>
+          <t>8.63</t>
         </is>
       </c>
       <c r="BB101" t="inlineStr">
         <is>
-          <t>42.6</t>
+          <t>45.07</t>
         </is>
       </c>
       <c r="BC101" t="inlineStr">
         <is>
-          <t>89.28</t>
+          <t>90.6</t>
         </is>
       </c>
       <c r="BD101" t="inlineStr">
         <is>
-          <t>0.3611</t>
+          <t>0.4621</t>
         </is>
       </c>
       <c r="BE101" t="inlineStr">
         <is>
-          <t>0.1312</t>
+          <t>0.1966</t>
         </is>
       </c>
       <c r="BF101" t="inlineStr">
         <is>
-          <t>18.09</t>
+          <t>36.25</t>
         </is>
       </c>
       <c r="BG101" t="inlineStr"/>
       <c r="BH101" t="inlineStr"/>
       <c r="BI101" t="inlineStr">
         <is>
-          <t>Citizens Bank Park</t>
+          <t>Truist Park</t>
         </is>
       </c>
       <c r="BJ101" t="inlineStr"/>
@@ -28335,22 +28335,22 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>694212</t>
+          <t>691777</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Samuel Basallo</t>
+          <t>Max Muncy</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -28370,12 +28370,12 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>Payton Tolle</t>
+          <t>Cristopher Sánchez</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>801139</t>
+          <t>650911</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
@@ -28384,7 +28384,7 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>45.8</v>
+        <v>45.9</v>
       </c>
       <c r="M102" t="inlineStr">
         <is>
@@ -28398,26 +28398,26 @@
       </c>
       <c r="O102" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel</t>
+          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P102" t="n">
-        <v>49.9</v>
+        <v>39.2</v>
       </c>
       <c r="Q102" t="n">
-        <v>30</v>
+        <v>35.9</v>
       </c>
       <c r="R102" t="n">
-        <v>28.7</v>
+        <v>34.3</v>
       </c>
       <c r="S102" t="n">
         <v>81.90000000000001</v>
       </c>
       <c r="T102" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U102" t="n">
-        <v>37.4</v>
+        <v>14.6</v>
       </c>
       <c r="V102" t="inlineStr">
         <is>
@@ -28431,7 +28431,7 @@
       </c>
       <c r="X102" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y102" t="inlineStr">
@@ -28451,7 +28451,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>lineup projected / unconfirmed; order MLB 5 vs RotoWire 8</t>
         </is>
       </c>
       <c r="AC102" t="inlineStr">
@@ -28473,27 +28473,27 @@
       </c>
       <c r="AH102" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI102" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK102" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 5/23, 0 HR</t>
         </is>
       </c>
       <c r="AL102" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.9% barrel, 7.1 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.9% barrel, 12.0 HR allowed</t>
         </is>
       </c>
       <c r="AM102" t="inlineStr">
@@ -28503,104 +28503,104 @@
       </c>
       <c r="AN102" t="inlineStr">
         <is>
-          <t>11.77</t>
+          <t>10.8</t>
         </is>
       </c>
       <c r="AO102" t="inlineStr">
         <is>
-          <t>44.96</t>
+          <t>43.67</t>
         </is>
       </c>
       <c r="AP102" t="inlineStr">
         <is>
-          <t>90.71</t>
+          <t>89.69</t>
         </is>
       </c>
       <c r="AQ102" t="inlineStr">
         <is>
-          <t>102.5297</t>
+          <t>101.5962</t>
         </is>
       </c>
       <c r="AR102" t="inlineStr">
         <is>
-          <t>0.4422</t>
+          <t>0.3663</t>
         </is>
       </c>
       <c r="AS102" t="inlineStr">
         <is>
-          <t>0.2029</t>
+          <t>0.1528</t>
         </is>
       </c>
       <c r="AT102" t="inlineStr">
         <is>
-          <t>0.3204</t>
+          <t>0.2866</t>
         </is>
       </c>
       <c r="AU102" t="inlineStr">
         <is>
-          <t>74.87</t>
+          <t>74.08</t>
         </is>
       </c>
       <c r="AV102" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>44.98</t>
         </is>
       </c>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>42.46</t>
+          <t>43.1</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>29.05</t>
+          <t>23.63</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr">
         <is>
-          <t>12.4</t>
+          <t>6.2</t>
         </is>
       </c>
       <c r="AZ102" t="inlineStr">
         <is>
-          <t>0.1965</t>
+          <t>0.1678</t>
         </is>
       </c>
       <c r="BA102" t="inlineStr">
         <is>
-          <t>6.89</t>
+          <t>7.87</t>
         </is>
       </c>
       <c r="BB102" t="inlineStr">
         <is>
-          <t>35.57</t>
+          <t>42.6</t>
         </is>
       </c>
       <c r="BC102" t="inlineStr">
         <is>
-          <t>87.87</t>
+          <t>89.28</t>
         </is>
       </c>
       <c r="BD102" t="inlineStr">
         <is>
-          <t>0.3637</t>
+          <t>0.3611</t>
         </is>
       </c>
       <c r="BE102" t="inlineStr">
         <is>
-          <t>0.1408</t>
+          <t>0.1312</t>
         </is>
       </c>
       <c r="BF102" t="inlineStr">
         <is>
-          <t>28.93</t>
+          <t>18.09</t>
         </is>
       </c>
       <c r="BG102" t="inlineStr"/>
       <c r="BH102" t="inlineStr"/>
       <c r="BI102" t="inlineStr">
         <is>
-          <t>Fenway Park</t>
+          <t>Citizens Bank Park</t>
         </is>
       </c>
       <c r="BJ102" t="inlineStr"/>
@@ -28611,27 +28611,27 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>641680</t>
+          <t>694212</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Jonah Heim</t>
+          <t>Samuel Basallo</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-07-21T01:40:00Z</t>
+          <t>2026-07-20T23:10:00Z</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -28641,17 +28641,17 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>Mitch Bratt</t>
+          <t>Payton Tolle</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>683352</t>
+          <t>801139</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
@@ -28674,26 +28674,26 @@
       </c>
       <c r="O103" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel</t>
         </is>
       </c>
       <c r="P103" t="n">
-        <v>23.4</v>
+        <v>49.9</v>
       </c>
       <c r="Q103" t="n">
-        <v>58.6</v>
+        <v>30</v>
       </c>
       <c r="R103" t="n">
-        <v>28.2</v>
+        <v>28.7</v>
       </c>
       <c r="S103" t="n">
-        <v>90.40000000000001</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T103" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U103" t="n">
-        <v>8.800000000000001</v>
+        <v>37.4</v>
       </c>
       <c r="V103" t="inlineStr">
         <is>
@@ -28707,7 +28707,7 @@
       </c>
       <c r="X103" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y103" t="inlineStr">
@@ -28732,7 +28732,7 @@
       </c>
       <c r="AC103" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD103" t="inlineStr"/>
@@ -28749,134 +28749,134 @@
       </c>
       <c r="AH103" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI103" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/28, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL103" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 10.0% barrel, 1.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.9% barrel, 7.1 HR allowed</t>
         </is>
       </c>
       <c r="AM103" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN103" t="inlineStr">
         <is>
-          <t>6.52</t>
+          <t>11.77</t>
         </is>
       </c>
       <c r="AO103" t="inlineStr">
         <is>
-          <t>31.7</t>
+          <t>44.96</t>
         </is>
       </c>
       <c r="AP103" t="inlineStr">
         <is>
-          <t>87.47</t>
+          <t>90.71</t>
         </is>
       </c>
       <c r="AQ103" t="inlineStr">
         <is>
-          <t>97.861</t>
+          <t>102.5297</t>
         </is>
       </c>
       <c r="AR103" t="inlineStr">
         <is>
-          <t>0.3761</t>
+          <t>0.4422</t>
         </is>
       </c>
       <c r="AS103" t="inlineStr">
         <is>
-          <t>0.1466</t>
+          <t>0.2029</t>
         </is>
       </c>
       <c r="AT103" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>0.3204</t>
         </is>
       </c>
       <c r="AU103" t="inlineStr">
         <is>
-          <t>69.77</t>
+          <t>74.87</t>
         </is>
       </c>
       <c r="AV103" t="inlineStr">
         <is>
-          <t>9.52</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>39.37</t>
+          <t>42.46</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>28.53</t>
+          <t>29.05</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>12.4</t>
         </is>
       </c>
       <c r="AZ103" t="inlineStr">
         <is>
-          <t>0.1848</t>
+          <t>0.1965</t>
         </is>
       </c>
       <c r="BA103" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>6.89</t>
         </is>
       </c>
       <c r="BB103" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>35.57</t>
         </is>
       </c>
       <c r="BC103" t="inlineStr">
         <is>
-          <t>89.5</t>
+          <t>87.87</t>
         </is>
       </c>
       <c r="BD103" t="inlineStr">
         <is>
-          <t>0.481</t>
+          <t>0.3637</t>
         </is>
       </c>
       <c r="BE103" t="inlineStr">
         <is>
-          <t>0.218</t>
+          <t>0.1408</t>
         </is>
       </c>
       <c r="BF103" t="inlineStr">
         <is>
-          <t>35.0</t>
+          <t>28.93</t>
         </is>
       </c>
       <c r="BG103" t="inlineStr"/>
       <c r="BH103" t="inlineStr"/>
       <c r="BI103" t="inlineStr">
         <is>
-          <t>Chase Field</t>
+          <t>Fenway Park</t>
         </is>
       </c>
       <c r="BJ103" t="inlineStr"/>
@@ -28887,27 +28887,27 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>665862</t>
+          <t>641680</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Jazz Chisholm</t>
+          <t>Jonah Heim</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-07-20T23:05:00Z</t>
+          <t>2026-07-21T01:40:00Z</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -28917,26 +28917,26 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>Braxton Ashcraft</t>
+          <t>Mitch Bratt</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>677952</t>
+          <t>683352</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L104" t="n">
-        <v>45.7</v>
+        <v>45.8</v>
       </c>
       <c r="M104" t="inlineStr">
         <is>
@@ -28950,26 +28950,26 @@
       </c>
       <c r="O104" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P104" t="n">
-        <v>42.5</v>
+        <v>23.4</v>
       </c>
       <c r="Q104" t="n">
-        <v>30.1</v>
+        <v>58.6</v>
       </c>
       <c r="R104" t="n">
-        <v>38.2</v>
+        <v>28.2</v>
       </c>
       <c r="S104" t="n">
-        <v>71.7</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="T104" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="U104" t="n">
-        <v>30.3</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="V104" t="inlineStr">
         <is>
@@ -28983,7 +28983,7 @@
       </c>
       <c r="X104" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y104" t="inlineStr">
@@ -29008,7 +29008,7 @@
       </c>
       <c r="AC104" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD104" t="inlineStr"/>
@@ -29030,129 +29030,129 @@
       </c>
       <c r="AI104" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK104" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/25, 1 HR</t>
+          <t>Last 7 games: 5/28, 0 HR</t>
         </is>
       </c>
       <c r="AL104" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 5.6% barrel, 10.7 HR allowed</t>
+          <t>switch hitter; pitcher baseline 10.0% barrel, 1.0 HR allowed</t>
         </is>
       </c>
       <c r="AM104" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN104" t="inlineStr">
         <is>
-          <t>10.59</t>
+          <t>6.52</t>
         </is>
       </c>
       <c r="AO104" t="inlineStr">
         <is>
-          <t>41.76</t>
+          <t>31.7</t>
         </is>
       </c>
       <c r="AP104" t="inlineStr">
         <is>
-          <t>90.26</t>
+          <t>87.47</t>
         </is>
       </c>
       <c r="AQ104" t="inlineStr">
         <is>
-          <t>100.3793</t>
+          <t>97.861</t>
         </is>
       </c>
       <c r="AR104" t="inlineStr">
         <is>
-          <t>0.3977</t>
+          <t>0.3761</t>
         </is>
       </c>
       <c r="AS104" t="inlineStr">
         <is>
-          <t>0.1805</t>
+          <t>0.1466</t>
         </is>
       </c>
       <c r="AT104" t="inlineStr">
         <is>
-          <t>0.3075</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="AU104" t="inlineStr">
         <is>
-          <t>73.34</t>
+          <t>69.77</t>
         </is>
       </c>
       <c r="AV104" t="inlineStr">
         <is>
-          <t>34.41</t>
+          <t>9.52</t>
         </is>
       </c>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>52.68</t>
+          <t>39.37</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>29.49</t>
+          <t>28.53</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr">
         <is>
-          <t>18.4</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="AZ104" t="inlineStr">
         <is>
-          <t>0.1907</t>
+          <t>0.1848</t>
         </is>
       </c>
       <c r="BA104" t="inlineStr">
         <is>
-          <t>5.61</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BB104" t="inlineStr">
         <is>
-          <t>40.25</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="BC104" t="inlineStr">
         <is>
-          <t>89.61</t>
+          <t>89.5</t>
         </is>
       </c>
       <c r="BD104" t="inlineStr">
         <is>
-          <t>0.3542</t>
+          <t>0.481</t>
         </is>
       </c>
       <c r="BE104" t="inlineStr">
         <is>
-          <t>0.1255</t>
+          <t>0.218</t>
         </is>
       </c>
       <c r="BF104" t="inlineStr">
         <is>
-          <t>25.53</t>
+          <t>35.0</t>
         </is>
       </c>
       <c r="BG104" t="inlineStr"/>
       <c r="BH104" t="inlineStr"/>
       <c r="BI104" t="inlineStr">
         <is>
-          <t>Yankee Stadium</t>
+          <t>Chase Field</t>
         </is>
       </c>
       <c r="BJ104" t="inlineStr"/>
@@ -31095,27 +31095,27 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>641355</t>
+          <t>596019</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Cody Bellinger</t>
+          <t>Francisco Lindor</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>NYM</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-07-20T23:05:00Z</t>
+          <t>2026-07-20T23:40:00Z</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
@@ -31130,12 +31130,12 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>Braxton Ashcraft</t>
+          <t>Jacob Misiorowski</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>677952</t>
+          <t>694819</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
@@ -31162,22 +31162,22 @@
         </is>
       </c>
       <c r="P112" t="n">
-        <v>30.2</v>
+        <v>43.9</v>
       </c>
       <c r="Q112" t="n">
-        <v>30.1</v>
+        <v>16.2</v>
       </c>
       <c r="R112" t="n">
-        <v>38.2</v>
+        <v>27.6</v>
       </c>
       <c r="S112" t="n">
         <v>90.40000000000001</v>
       </c>
       <c r="T112" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="U112" t="n">
-        <v>42</v>
+        <v>59.6</v>
       </c>
       <c r="V112" t="inlineStr">
         <is>
@@ -31233,27 +31233,27 @@
       </c>
       <c r="AH112" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI112" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK112" t="inlineStr">
         <is>
-          <t>Contact streak: 10/25 over last 7 games</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL112" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 5.6% barrel, 10.7 HR allowed</t>
+          <t>switch hitter; pitcher baseline 4.6% barrel, 8.7 HR allowed</t>
         </is>
       </c>
       <c r="AM112" t="inlineStr">
@@ -31263,104 +31263,104 @@
       </c>
       <c r="AN112" t="inlineStr">
         <is>
-          <t>6.8</t>
+          <t>8.55</t>
         </is>
       </c>
       <c r="AO112" t="inlineStr">
         <is>
-          <t>36.92</t>
+          <t>47.55</t>
         </is>
       </c>
       <c r="AP112" t="inlineStr">
         <is>
-          <t>88.79</t>
+          <t>91.48</t>
         </is>
       </c>
       <c r="AQ112" t="inlineStr">
         <is>
-          <t>98.5451</t>
+          <t>100.3117</t>
         </is>
       </c>
       <c r="AR112" t="inlineStr">
         <is>
-          <t>0.4229</t>
+          <t>0.4365</t>
         </is>
       </c>
       <c r="AS112" t="inlineStr">
         <is>
-          <t>0.154</t>
+          <t>0.1835</t>
         </is>
       </c>
       <c r="AT112" t="inlineStr">
         <is>
-          <t>0.3426</t>
+          <t>0.3352</t>
         </is>
       </c>
       <c r="AU112" t="inlineStr">
         <is>
-          <t>69.68</t>
+          <t>72.12</t>
         </is>
       </c>
       <c r="AV112" t="inlineStr">
         <is>
-          <t>3.91</t>
+          <t>21.44</t>
         </is>
       </c>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>42.75</t>
+          <t>44.69</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>32.13</t>
+          <t>28.55</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr">
         <is>
-          <t>16.4</t>
+          <t>12.8</t>
         </is>
       </c>
       <c r="AZ112" t="inlineStr">
         <is>
-          <t>0.1779</t>
+          <t>0.164</t>
         </is>
       </c>
       <c r="BA112" t="inlineStr">
         <is>
-          <t>5.61</t>
+          <t>4.61</t>
         </is>
       </c>
       <c r="BB112" t="inlineStr">
         <is>
-          <t>40.25</t>
+          <t>35.12</t>
         </is>
       </c>
       <c r="BC112" t="inlineStr">
         <is>
-          <t>89.61</t>
+          <t>87.81</t>
         </is>
       </c>
       <c r="BD112" t="inlineStr">
         <is>
-          <t>0.3542</t>
+          <t>0.2768</t>
         </is>
       </c>
       <c r="BE112" t="inlineStr">
         <is>
-          <t>0.1255</t>
+          <t>0.0975</t>
         </is>
       </c>
       <c r="BF112" t="inlineStr">
         <is>
-          <t>25.53</t>
+          <t>25.01</t>
         </is>
       </c>
       <c r="BG112" t="inlineStr"/>
       <c r="BH112" t="inlineStr"/>
       <c r="BI112" t="inlineStr">
         <is>
-          <t>Yankee Stadium</t>
+          <t>American Family Field</t>
         </is>
       </c>
       <c r="BJ112" t="inlineStr"/>
@@ -31371,27 +31371,27 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>596019</t>
+          <t>695734</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Francisco Lindor</t>
+          <t>Daylen Lile</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NYM</t>
+          <t>WSH</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2026-07-20T23:40:00Z</t>
+          <t>2026-07-21T00:40:00Z</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
@@ -31401,22 +31401,22 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>4</t>